--- a/Simulations_IDS.xlsx
+++ b/Simulations_IDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documentos_Betran\DropletEvaporation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04F3E901-D606-473C-AA7C-696FF478FFE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77B02EF-8920-4D54-A30C-C563ED8F318A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{73239687-5BB6-4FA0-A3B4-8BE280184789}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="65">
   <si>
     <t>ID</t>
   </si>
@@ -73,9 +73,6 @@
   </si>
   <si>
     <t>0.79,0.21,0.0,0.0</t>
-  </si>
-  <si>
-    <t>Min size Liq</t>
   </si>
   <si>
     <t>Initial time</t>
@@ -144,15 +141,6 @@
     <t>Ambient</t>
   </si>
   <si>
-    <t>Mass</t>
-  </si>
-  <si>
-    <t>fraction in Liq</t>
-  </si>
-  <si>
-    <t>fraction in Gas</t>
-  </si>
-  <si>
     <t>Pre-</t>
   </si>
   <si>
@@ -167,12 +155,90 @@
   <si>
     <t>Heptano</t>
   </si>
+  <si>
+    <t xml:space="preserve">Fuel </t>
+  </si>
+  <si>
+    <t>Exponent</t>
+  </si>
+  <si>
+    <t>O2</t>
+  </si>
+  <si>
+    <t>Min size</t>
+  </si>
+  <si>
+    <t>Liq</t>
+  </si>
+  <si>
+    <t>Gas</t>
+  </si>
+  <si>
+    <t>Liq mass</t>
+  </si>
+  <si>
+    <t>fraction</t>
+  </si>
+  <si>
+    <t>Gas mass</t>
+  </si>
+  <si>
+    <t>Kurman intento 1</t>
+  </si>
+  <si>
+    <t>Kurman intento 2 -&gt; k_gas = 0.025</t>
+  </si>
+  <si>
+    <t>Kurman int. 2 -&gt; props no cte (PolyFit)</t>
+  </si>
+  <si>
+    <t>Kurman int. 3 -&gt; quito if props H20</t>
+  </si>
+  <si>
+    <t>Mismo que 105 con bucles en Q</t>
+  </si>
+  <si>
+    <t>Mismo que 104 cambiando Pre-exponenical y elementos según pre-exponencial</t>
+  </si>
+  <si>
+    <t>Es la 111 que se ha bugueado</t>
+  </si>
+  <si>
+    <t>Mismo que 104 con más elementos -&gt; Diferencia 0.7%</t>
+  </si>
+  <si>
+    <t>Igual que 104 pero Q = 0</t>
+  </si>
+  <si>
+    <t>126 pero menos elementos</t>
+  </si>
+  <si>
+    <t>Igual que 104 pero Q = [SI]</t>
+  </si>
+  <si>
+    <t>Igual que 105 pero Ea cambiado</t>
+  </si>
+  <si>
+    <t>105 pero R_inf &gt;&gt;</t>
+  </si>
+  <si>
+    <t>Tirada de la 137 a 143 con menos elementos</t>
+  </si>
+  <si>
+    <t>Igual que 105 pero Ea cambiado y más elementos</t>
+  </si>
+  <si>
+    <t>Mismas que 104 pero cambiando Pre-exp para ver si converge siempre a la misma solución cuando aumento cinética. PreExp.txt</t>
+  </si>
+  <si>
+    <t>No picos en CI</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,8 +246,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -200,8 +272,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -306,11 +402,119 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -323,6 +527,86 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -332,8 +616,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -649,13 +936,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC78505-487D-4D76-94E1-903AFBAADA28}">
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:AF87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="2.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
@@ -669,50 +956,54 @@
     <col min="16" max="16" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="17" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B1" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="12" t="s">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B1" s="73" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="13" t="s">
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="14"/>
-      <c r="M1" s="12" t="s">
+      <c r="L1" s="76"/>
+      <c r="M1" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="12" t="s">
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="13"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="12" t="s">
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="V1" s="13"/>
-      <c r="W1" s="14"/>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V1" s="75"/>
+      <c r="W1" s="75"/>
+      <c r="X1" s="75"/>
+      <c r="Y1" s="76"/>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -723,132 +1014,148 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P2" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="R2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="S2" s="10" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="U2" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="V2" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+      <c r="W2" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="X2" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="9"/>
       <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
+      <c r="D3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>44</v>
+      </c>
       <c r="F3" s="2"/>
       <c r="G3" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>27</v>
-      </c>
       <c r="P3" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R3" s="9"/>
       <c r="S3" s="11" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="T3" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="V3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="U3" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="W3" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="X3" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y3" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21">
         <v>101</v>
       </c>
       <c r="B4" s="4">
         <v>12</v>
       </c>
       <c r="C4" s="4">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="D4" s="5">
         <v>9.9999999999999995E-7</v>
@@ -863,22 +1170,22 @@
         <v>1.0000000000000001E-9</v>
       </c>
       <c r="H4" s="5">
-        <v>0.1</v>
+        <v>100</v>
       </c>
       <c r="I4" s="4">
         <v>1</v>
       </c>
       <c r="J4" s="6">
-        <v>9.9999999999999995E-8</v>
+        <v>1E-4</v>
       </c>
       <c r="K4" s="4">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="L4" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
-        <v>1.25E-4</v>
+        <v>4.2000000000000002E-4</v>
       </c>
       <c r="N4" s="4">
         <v>150</v>
@@ -893,7 +1200,7 @@
         <v>400</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="S4" s="4">
         <v>1</v>
@@ -905,21 +1212,6874 @@
         <v>81600000000000</v>
       </c>
       <c r="V4" s="4">
-        <f>30*4184</f>
+        <f t="shared" ref="V4:V16" si="0">30*4184</f>
         <v>125520</v>
       </c>
-      <c r="W4" s="3">
-        <v>0</v>
+      <c r="W4" s="4">
+        <v>0</v>
+      </c>
+      <c r="X4" s="18">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="71" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA4" s="77"/>
+      <c r="AB4" s="77"/>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A5" s="22">
+        <v>102</v>
+      </c>
+      <c r="B5" s="13">
+        <v>12</v>
+      </c>
+      <c r="C5" s="13">
+        <v>700</v>
+      </c>
+      <c r="D5" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E5" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F5" s="1">
+        <v>5</v>
+      </c>
+      <c r="G5" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H5" s="16">
+        <v>100</v>
+      </c>
+      <c r="I5" s="13">
+        <v>1</v>
+      </c>
+      <c r="J5" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K5" s="13">
+        <v>2</v>
+      </c>
+      <c r="L5" s="1">
+        <v>2</v>
+      </c>
+      <c r="M5" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N5" s="13">
+        <v>150</v>
+      </c>
+      <c r="O5" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P5" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>400</v>
+      </c>
+      <c r="R5" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S5" s="13">
+        <v>1</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U5" s="16">
+        <v>81600000000000</v>
+      </c>
+      <c r="V5" s="13">
+        <f t="shared" si="0"/>
+        <v>125520</v>
+      </c>
+      <c r="W5" s="13">
+        <v>0</v>
+      </c>
+      <c r="X5" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="71" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA5" s="77"/>
+      <c r="AB5" s="77"/>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A6" s="22">
+        <v>103</v>
+      </c>
+      <c r="B6" s="13">
+        <v>12</v>
+      </c>
+      <c r="C6" s="13">
+        <v>700</v>
+      </c>
+      <c r="D6" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E6" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F6" s="1">
+        <v>5</v>
+      </c>
+      <c r="G6" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H6" s="16">
+        <v>100</v>
+      </c>
+      <c r="I6" s="13">
+        <v>1</v>
+      </c>
+      <c r="J6" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K6" s="13">
+        <v>2</v>
+      </c>
+      <c r="L6" s="1">
+        <v>2</v>
+      </c>
+      <c r="M6" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N6" s="13">
+        <v>150</v>
+      </c>
+      <c r="O6" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P6" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>400</v>
+      </c>
+      <c r="R6" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S6" s="13">
+        <v>1</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U6" s="16">
+        <v>81600000000000</v>
+      </c>
+      <c r="V6" s="13">
+        <f t="shared" si="0"/>
+        <v>125520</v>
+      </c>
+      <c r="W6" s="13">
+        <v>0</v>
+      </c>
+      <c r="X6" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="71" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA6" s="77"/>
+      <c r="AB6" s="77"/>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A7" s="22">
+        <v>104</v>
+      </c>
+      <c r="B7" s="13">
+        <v>12</v>
+      </c>
+      <c r="C7" s="13">
+        <v>300</v>
+      </c>
+      <c r="D7" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E7" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F7" s="1">
+        <v>5</v>
+      </c>
+      <c r="G7" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H7" s="16">
+        <v>100</v>
+      </c>
+      <c r="I7" s="13">
+        <v>1</v>
+      </c>
+      <c r="J7" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K7" s="13">
+        <v>2</v>
+      </c>
+      <c r="L7" s="1">
+        <v>2</v>
+      </c>
+      <c r="M7" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N7" s="13">
+        <v>150</v>
+      </c>
+      <c r="O7" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P7" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>400</v>
+      </c>
+      <c r="R7" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S7" s="13">
+        <v>1</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U7" s="16">
+        <v>81600000000000</v>
+      </c>
+      <c r="V7" s="13">
+        <f t="shared" si="0"/>
+        <v>125520</v>
+      </c>
+      <c r="W7" s="13">
+        <v>0</v>
+      </c>
+      <c r="X7" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="71" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA7" s="77"/>
+      <c r="AB7" s="77"/>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A8" s="22">
+        <v>105</v>
+      </c>
+      <c r="B8" s="37">
+        <v>12</v>
+      </c>
+      <c r="C8" s="37">
+        <v>700</v>
+      </c>
+      <c r="D8" s="38">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E8" s="38">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F8" s="39">
+        <v>5</v>
+      </c>
+      <c r="G8" s="38">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H8" s="38">
+        <v>100</v>
+      </c>
+      <c r="I8" s="37">
+        <v>1</v>
+      </c>
+      <c r="J8" s="40">
+        <v>1E-4</v>
+      </c>
+      <c r="K8" s="37">
+        <v>2</v>
+      </c>
+      <c r="L8" s="39">
+        <v>2</v>
+      </c>
+      <c r="M8" s="38">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N8" s="37">
+        <v>150</v>
+      </c>
+      <c r="O8" s="37">
+        <v>0.2</v>
+      </c>
+      <c r="P8" s="37">
+        <v>300</v>
+      </c>
+      <c r="Q8" s="39">
+        <v>400</v>
+      </c>
+      <c r="R8" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="S8" s="37">
+        <v>1</v>
+      </c>
+      <c r="T8" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="U8" s="38">
+        <v>81600000000000</v>
+      </c>
+      <c r="V8" s="37">
+        <f t="shared" si="0"/>
+        <v>125520</v>
+      </c>
+      <c r="W8" s="37">
+        <v>0</v>
+      </c>
+      <c r="X8" s="37">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="39">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="71" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA8" s="72"/>
+      <c r="AB8" s="72"/>
+      <c r="AC8" s="72"/>
+      <c r="AD8" s="72"/>
+      <c r="AE8" s="20"/>
+      <c r="AF8" s="20"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>106</v>
+      </c>
+      <c r="B9" s="13">
+        <v>12</v>
+      </c>
+      <c r="C9" s="13">
+        <v>700</v>
+      </c>
+      <c r="D9" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E9" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F9" s="1">
+        <v>5</v>
+      </c>
+      <c r="G9" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H9" s="16">
+        <v>100</v>
+      </c>
+      <c r="I9" s="13">
+        <v>1</v>
+      </c>
+      <c r="J9" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K9" s="13">
+        <v>2</v>
+      </c>
+      <c r="L9" s="1">
+        <v>2</v>
+      </c>
+      <c r="M9" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N9" s="13">
+        <v>150</v>
+      </c>
+      <c r="O9" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P9" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>400</v>
+      </c>
+      <c r="R9" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S9" s="13">
+        <v>1</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U9" s="16">
+        <v>81600000000000</v>
+      </c>
+      <c r="V9" s="13">
+        <f t="shared" si="0"/>
+        <v>125520</v>
+      </c>
+      <c r="W9" s="13">
+        <v>0</v>
+      </c>
+      <c r="X9" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="71" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA9" s="72"/>
+      <c r="AB9" s="72"/>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A10" s="47">
+        <v>107</v>
+      </c>
+      <c r="B10" s="42">
+        <v>12</v>
+      </c>
+      <c r="C10" s="42">
+        <v>300</v>
+      </c>
+      <c r="D10" s="43">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E10" s="43">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F10" s="44">
+        <v>5</v>
+      </c>
+      <c r="G10" s="43">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H10" s="43">
+        <v>100</v>
+      </c>
+      <c r="I10" s="42">
+        <v>1</v>
+      </c>
+      <c r="J10" s="45">
+        <v>1E-4</v>
+      </c>
+      <c r="K10" s="42">
+        <v>2</v>
+      </c>
+      <c r="L10" s="44">
+        <v>2</v>
+      </c>
+      <c r="M10" s="43">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N10" s="42">
+        <v>150</v>
+      </c>
+      <c r="O10" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="P10" s="42">
+        <v>300</v>
+      </c>
+      <c r="Q10" s="44">
+        <v>400</v>
+      </c>
+      <c r="R10" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="S10" s="42">
+        <v>1</v>
+      </c>
+      <c r="T10" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="U10" s="43">
+        <v>81600000000000</v>
+      </c>
+      <c r="V10" s="42">
+        <f t="shared" si="0"/>
+        <v>125520</v>
+      </c>
+      <c r="W10" s="42">
+        <v>0</v>
+      </c>
+      <c r="X10" s="46">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="44">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA10" s="70"/>
+      <c r="AB10" s="70"/>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A11" s="22">
+        <v>108</v>
+      </c>
+      <c r="B11" s="13">
+        <v>12</v>
+      </c>
+      <c r="C11" s="13">
+        <f>C10*(4/3)</f>
+        <v>400</v>
+      </c>
+      <c r="D11" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E11" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F11" s="1">
+        <v>5</v>
+      </c>
+      <c r="G11" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H11" s="16">
+        <v>100</v>
+      </c>
+      <c r="I11" s="13">
+        <v>1</v>
+      </c>
+      <c r="J11" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K11" s="13">
+        <v>2</v>
+      </c>
+      <c r="L11" s="1">
+        <v>2</v>
+      </c>
+      <c r="M11" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N11" s="13">
+        <v>150</v>
+      </c>
+      <c r="O11" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P11" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>400</v>
+      </c>
+      <c r="R11" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S11" s="13">
+        <v>1</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U11" s="19">
+        <f>U10*(4/3)</f>
+        <v>108800000000000</v>
+      </c>
+      <c r="V11" s="13">
+        <f t="shared" si="0"/>
+        <v>125520</v>
+      </c>
+      <c r="W11" s="13">
+        <v>0</v>
+      </c>
+      <c r="X11" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="69"/>
+      <c r="AA11" s="70"/>
+      <c r="AB11" s="70"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A12" s="22">
+        <v>109</v>
+      </c>
+      <c r="B12" s="13">
+        <v>12</v>
+      </c>
+      <c r="C12" s="13">
+        <v>500</v>
+      </c>
+      <c r="D12" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E12" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F12" s="1">
+        <v>5</v>
+      </c>
+      <c r="G12" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H12" s="16">
+        <v>100</v>
+      </c>
+      <c r="I12" s="13">
+        <v>1</v>
+      </c>
+      <c r="J12" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K12" s="13">
+        <v>2</v>
+      </c>
+      <c r="L12" s="1">
+        <v>2</v>
+      </c>
+      <c r="M12" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N12" s="13">
+        <v>150</v>
+      </c>
+      <c r="O12" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P12" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>400</v>
+      </c>
+      <c r="R12" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S12" s="13">
+        <v>1</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U12" s="19">
+        <f t="shared" ref="U12:U27" si="1">U11*(4/3)</f>
+        <v>145066666666666.66</v>
+      </c>
+      <c r="V12" s="13">
+        <f t="shared" si="0"/>
+        <v>125520</v>
+      </c>
+      <c r="W12" s="13">
+        <v>0</v>
+      </c>
+      <c r="X12" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="69"/>
+      <c r="AA12" s="70"/>
+      <c r="AB12" s="70"/>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>110</v>
+      </c>
+      <c r="B13" s="13">
+        <v>12</v>
+      </c>
+      <c r="C13" s="13">
+        <v>700</v>
+      </c>
+      <c r="D13" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E13" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F13" s="1">
+        <v>5</v>
+      </c>
+      <c r="G13" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H13" s="16">
+        <v>100</v>
+      </c>
+      <c r="I13" s="13">
+        <v>1</v>
+      </c>
+      <c r="J13" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K13" s="13">
+        <v>2</v>
+      </c>
+      <c r="L13" s="1">
+        <v>2</v>
+      </c>
+      <c r="M13" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N13" s="13">
+        <v>150</v>
+      </c>
+      <c r="O13" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P13" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>400</v>
+      </c>
+      <c r="R13" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S13" s="13">
+        <v>1</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U13" s="19">
+        <f t="shared" si="1"/>
+        <v>193422222222222.19</v>
+      </c>
+      <c r="V13" s="13">
+        <f t="shared" si="0"/>
+        <v>125520</v>
+      </c>
+      <c r="W13" s="13">
+        <v>0</v>
+      </c>
+      <c r="X13" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="69"/>
+      <c r="AA13" s="70"/>
+      <c r="AB13" s="70"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A14" s="23">
+        <v>111</v>
+      </c>
+      <c r="B14" s="13">
+        <v>12</v>
+      </c>
+      <c r="C14" s="13">
+        <v>1000</v>
+      </c>
+      <c r="D14" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E14" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F14" s="1">
+        <v>5</v>
+      </c>
+      <c r="G14" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H14" s="16">
+        <v>100</v>
+      </c>
+      <c r="I14" s="13">
+        <v>1</v>
+      </c>
+      <c r="J14" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K14" s="13">
+        <v>2</v>
+      </c>
+      <c r="L14" s="1">
+        <v>2</v>
+      </c>
+      <c r="M14" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N14" s="13">
+        <v>150</v>
+      </c>
+      <c r="O14" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P14" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>400</v>
+      </c>
+      <c r="R14" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S14" s="13">
+        <v>1</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U14" s="19">
+        <f t="shared" si="1"/>
+        <v>257896296296296.25</v>
+      </c>
+      <c r="V14" s="13">
+        <f t="shared" si="0"/>
+        <v>125520</v>
+      </c>
+      <c r="W14" s="13">
+        <v>0</v>
+      </c>
+      <c r="X14" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="69"/>
+      <c r="AA14" s="70"/>
+      <c r="AB14" s="70"/>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>112</v>
+      </c>
+      <c r="B15" s="13">
+        <v>12</v>
+      </c>
+      <c r="C15" s="13">
+        <v>1200</v>
+      </c>
+      <c r="D15" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E15" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F15" s="1">
+        <v>5</v>
+      </c>
+      <c r="G15" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H15" s="16">
+        <v>100</v>
+      </c>
+      <c r="I15" s="13">
+        <v>1</v>
+      </c>
+      <c r="J15" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K15" s="13">
+        <v>2</v>
+      </c>
+      <c r="L15" s="1">
+        <v>2</v>
+      </c>
+      <c r="M15" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N15" s="13">
+        <v>150</v>
+      </c>
+      <c r="O15" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P15" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>400</v>
+      </c>
+      <c r="R15" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S15" s="13">
+        <v>1</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U15" s="19">
+        <f t="shared" si="1"/>
+        <v>343861728395061.63</v>
+      </c>
+      <c r="V15" s="13">
+        <f t="shared" si="0"/>
+        <v>125520</v>
+      </c>
+      <c r="W15" s="13">
+        <v>0</v>
+      </c>
+      <c r="X15" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="69"/>
+      <c r="AA15" s="70"/>
+      <c r="AB15" s="70"/>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A16" s="23">
+        <v>113</v>
+      </c>
+      <c r="B16" s="13">
+        <v>12</v>
+      </c>
+      <c r="C16" s="13">
+        <v>1800</v>
+      </c>
+      <c r="D16" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E16" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F16" s="1">
+        <v>5</v>
+      </c>
+      <c r="G16" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H16" s="16">
+        <v>100</v>
+      </c>
+      <c r="I16" s="13">
+        <v>1</v>
+      </c>
+      <c r="J16" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K16" s="13">
+        <v>2</v>
+      </c>
+      <c r="L16" s="1">
+        <v>2</v>
+      </c>
+      <c r="M16" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N16" s="13">
+        <v>150</v>
+      </c>
+      <c r="O16" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P16" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>400</v>
+      </c>
+      <c r="R16" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S16" s="13">
+        <v>1</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U16" s="19">
+        <f t="shared" si="1"/>
+        <v>458482304526748.81</v>
+      </c>
+      <c r="V16" s="13">
+        <f t="shared" si="0"/>
+        <v>125520</v>
+      </c>
+      <c r="W16" s="13">
+        <v>0</v>
+      </c>
+      <c r="X16" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="69"/>
+      <c r="AA16" s="70"/>
+      <c r="AB16" s="70"/>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>114</v>
+      </c>
+      <c r="B17" s="13">
+        <v>12</v>
+      </c>
+      <c r="C17" s="13">
+        <v>2000</v>
+      </c>
+      <c r="D17" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E17" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F17" s="1">
+        <v>5</v>
+      </c>
+      <c r="G17" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H17" s="16">
+        <v>100</v>
+      </c>
+      <c r="I17" s="13">
+        <v>1</v>
+      </c>
+      <c r="J17" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K17" s="13">
+        <v>2</v>
+      </c>
+      <c r="L17" s="1">
+        <v>2</v>
+      </c>
+      <c r="M17" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N17" s="13">
+        <v>150</v>
+      </c>
+      <c r="O17" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P17" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>400</v>
+      </c>
+      <c r="R17" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S17" s="13">
+        <v>1</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U17" s="19">
+        <f t="shared" si="1"/>
+        <v>611309739368998.38</v>
+      </c>
+      <c r="V17" s="13">
+        <f t="shared" ref="V17:V58" si="2">30*4184</f>
+        <v>125520</v>
+      </c>
+      <c r="W17" s="13">
+        <v>0</v>
+      </c>
+      <c r="X17" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="69"/>
+      <c r="AA17" s="70"/>
+      <c r="AB17" s="70"/>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>115</v>
+      </c>
+      <c r="B18" s="13">
+        <v>12</v>
+      </c>
+      <c r="C18" s="13">
+        <v>2000</v>
+      </c>
+      <c r="D18" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E18" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F18" s="1">
+        <v>5</v>
+      </c>
+      <c r="G18" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H18" s="16">
+        <v>100</v>
+      </c>
+      <c r="I18" s="13">
+        <v>1</v>
+      </c>
+      <c r="J18" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K18" s="13">
+        <v>2</v>
+      </c>
+      <c r="L18" s="1">
+        <v>2</v>
+      </c>
+      <c r="M18" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N18" s="13">
+        <v>150</v>
+      </c>
+      <c r="O18" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P18" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>400</v>
+      </c>
+      <c r="R18" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S18" s="13">
+        <v>1</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U18" s="19">
+        <f t="shared" si="1"/>
+        <v>815079652491997.75</v>
+      </c>
+      <c r="V18" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W18" s="13">
+        <v>0</v>
+      </c>
+      <c r="X18" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="69"/>
+      <c r="AA18" s="70"/>
+      <c r="AB18" s="70"/>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>116</v>
+      </c>
+      <c r="B19" s="13">
+        <v>12</v>
+      </c>
+      <c r="C19" s="13">
+        <v>2000</v>
+      </c>
+      <c r="D19" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E19" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F19" s="1">
+        <v>5</v>
+      </c>
+      <c r="G19" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H19" s="16">
+        <v>100</v>
+      </c>
+      <c r="I19" s="13">
+        <v>1</v>
+      </c>
+      <c r="J19" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K19" s="13">
+        <v>2</v>
+      </c>
+      <c r="L19" s="1">
+        <v>2</v>
+      </c>
+      <c r="M19" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N19" s="13">
+        <v>150</v>
+      </c>
+      <c r="O19" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P19" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>400</v>
+      </c>
+      <c r="R19" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S19" s="13">
+        <v>1</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U19" s="19">
+        <f t="shared" si="1"/>
+        <v>1086772869989330.3</v>
+      </c>
+      <c r="V19" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W19" s="13">
+        <v>0</v>
+      </c>
+      <c r="X19" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="69"/>
+      <c r="AA19" s="70"/>
+      <c r="AB19" s="70"/>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>117</v>
+      </c>
+      <c r="B20" s="13">
+        <v>12</v>
+      </c>
+      <c r="C20" s="13">
+        <v>2000</v>
+      </c>
+      <c r="D20" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E20" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F20" s="1">
+        <v>5</v>
+      </c>
+      <c r="G20" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H20" s="16">
+        <v>100</v>
+      </c>
+      <c r="I20" s="13">
+        <v>1</v>
+      </c>
+      <c r="J20" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K20" s="13">
+        <v>2</v>
+      </c>
+      <c r="L20" s="1">
+        <v>2</v>
+      </c>
+      <c r="M20" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N20" s="13">
+        <v>150</v>
+      </c>
+      <c r="O20" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P20" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>400</v>
+      </c>
+      <c r="R20" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S20" s="13">
+        <v>1</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U20" s="19">
+        <f t="shared" si="1"/>
+        <v>1449030493319107</v>
+      </c>
+      <c r="V20" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W20" s="13">
+        <v>0</v>
+      </c>
+      <c r="X20" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="69"/>
+      <c r="AA20" s="70"/>
+      <c r="AB20" s="70"/>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>118</v>
+      </c>
+      <c r="B21" s="13">
+        <v>12</v>
+      </c>
+      <c r="C21" s="13">
+        <v>2000</v>
+      </c>
+      <c r="D21" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E21" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F21" s="1">
+        <v>5</v>
+      </c>
+      <c r="G21" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H21" s="16">
+        <v>100</v>
+      </c>
+      <c r="I21" s="13">
+        <v>1</v>
+      </c>
+      <c r="J21" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K21" s="13">
+        <v>2</v>
+      </c>
+      <c r="L21" s="1">
+        <v>2</v>
+      </c>
+      <c r="M21" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N21" s="13">
+        <v>150</v>
+      </c>
+      <c r="O21" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P21" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>400</v>
+      </c>
+      <c r="R21" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S21" s="13">
+        <v>1</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U21" s="19">
+        <f t="shared" si="1"/>
+        <v>1932040657758809.3</v>
+      </c>
+      <c r="V21" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W21" s="13">
+        <v>0</v>
+      </c>
+      <c r="X21" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="69"/>
+      <c r="AA21" s="70"/>
+      <c r="AB21" s="70"/>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>119</v>
+      </c>
+      <c r="B22" s="13">
+        <v>12</v>
+      </c>
+      <c r="C22" s="13">
+        <v>2000</v>
+      </c>
+      <c r="D22" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E22" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F22" s="1">
+        <v>5</v>
+      </c>
+      <c r="G22" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H22" s="16">
+        <v>100</v>
+      </c>
+      <c r="I22" s="13">
+        <v>1</v>
+      </c>
+      <c r="J22" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K22" s="13">
+        <v>2</v>
+      </c>
+      <c r="L22" s="1">
+        <v>2</v>
+      </c>
+      <c r="M22" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N22" s="13">
+        <v>150</v>
+      </c>
+      <c r="O22" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P22" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>400</v>
+      </c>
+      <c r="R22" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S22" s="13">
+        <v>1</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U22" s="19">
+        <f t="shared" si="1"/>
+        <v>2576054210345079</v>
+      </c>
+      <c r="V22" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W22" s="13">
+        <v>0</v>
+      </c>
+      <c r="X22" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="69"/>
+      <c r="AA22" s="70"/>
+      <c r="AB22" s="70"/>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>120</v>
+      </c>
+      <c r="B23" s="13">
+        <v>12</v>
+      </c>
+      <c r="C23" s="13">
+        <v>2000</v>
+      </c>
+      <c r="D23" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E23" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F23" s="1">
+        <v>5</v>
+      </c>
+      <c r="G23" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H23" s="16">
+        <v>100</v>
+      </c>
+      <c r="I23" s="13">
+        <v>1</v>
+      </c>
+      <c r="J23" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K23" s="13">
+        <v>2</v>
+      </c>
+      <c r="L23" s="1">
+        <v>2</v>
+      </c>
+      <c r="M23" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N23" s="13">
+        <v>150</v>
+      </c>
+      <c r="O23" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P23" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>400</v>
+      </c>
+      <c r="R23" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S23" s="13">
+        <v>1</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U23" s="19">
+        <f t="shared" si="1"/>
+        <v>3434738947126772</v>
+      </c>
+      <c r="V23" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W23" s="13">
+        <v>0</v>
+      </c>
+      <c r="X23" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="69"/>
+      <c r="AA23" s="70"/>
+      <c r="AB23" s="70"/>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>121</v>
+      </c>
+      <c r="B24" s="13">
+        <v>12</v>
+      </c>
+      <c r="C24" s="13">
+        <v>2000</v>
+      </c>
+      <c r="D24" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E24" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F24" s="1">
+        <v>5</v>
+      </c>
+      <c r="G24" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H24" s="16">
+        <v>100</v>
+      </c>
+      <c r="I24" s="13">
+        <v>1</v>
+      </c>
+      <c r="J24" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K24" s="13">
+        <v>2</v>
+      </c>
+      <c r="L24" s="1">
+        <v>2</v>
+      </c>
+      <c r="M24" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N24" s="13">
+        <v>150</v>
+      </c>
+      <c r="O24" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P24" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>400</v>
+      </c>
+      <c r="R24" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S24" s="13">
+        <v>1</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U24" s="19">
+        <f t="shared" si="1"/>
+        <v>4579651929502362</v>
+      </c>
+      <c r="V24" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W24" s="13">
+        <v>0</v>
+      </c>
+      <c r="X24" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="69"/>
+      <c r="AA24" s="70"/>
+      <c r="AB24" s="70"/>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>122</v>
+      </c>
+      <c r="B25" s="13">
+        <v>12</v>
+      </c>
+      <c r="C25" s="13">
+        <v>2000</v>
+      </c>
+      <c r="D25" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E25" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F25" s="1">
+        <v>5</v>
+      </c>
+      <c r="G25" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H25" s="16">
+        <v>100</v>
+      </c>
+      <c r="I25" s="13">
+        <v>1</v>
+      </c>
+      <c r="J25" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K25" s="13">
+        <v>2</v>
+      </c>
+      <c r="L25" s="1">
+        <v>2</v>
+      </c>
+      <c r="M25" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N25" s="13">
+        <v>150</v>
+      </c>
+      <c r="O25" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P25" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>400</v>
+      </c>
+      <c r="R25" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S25" s="13">
+        <v>1</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U25" s="19">
+        <f t="shared" si="1"/>
+        <v>6106202572669816</v>
+      </c>
+      <c r="V25" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W25" s="13">
+        <v>0</v>
+      </c>
+      <c r="X25" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="69"/>
+      <c r="AA25" s="70"/>
+      <c r="AB25" s="70"/>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>123</v>
+      </c>
+      <c r="B26" s="13">
+        <v>12</v>
+      </c>
+      <c r="C26" s="13">
+        <v>2000</v>
+      </c>
+      <c r="D26" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E26" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F26" s="1">
+        <v>5</v>
+      </c>
+      <c r="G26" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H26" s="16">
+        <v>100</v>
+      </c>
+      <c r="I26" s="13">
+        <v>1</v>
+      </c>
+      <c r="J26" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K26" s="13">
+        <v>2</v>
+      </c>
+      <c r="L26" s="1">
+        <v>2</v>
+      </c>
+      <c r="M26" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N26" s="13">
+        <v>150</v>
+      </c>
+      <c r="O26" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P26" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>400</v>
+      </c>
+      <c r="R26" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S26" s="13">
+        <v>1</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U26" s="19">
+        <f t="shared" si="1"/>
+        <v>8141603430226421</v>
+      </c>
+      <c r="V26" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W26" s="13">
+        <v>0</v>
+      </c>
+      <c r="X26" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="69"/>
+      <c r="AA26" s="70"/>
+      <c r="AB26" s="70"/>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" s="22">
+        <v>124</v>
+      </c>
+      <c r="B27" s="25">
+        <v>12</v>
+      </c>
+      <c r="C27" s="26">
+        <v>2000</v>
+      </c>
+      <c r="D27" s="27">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E27" s="27">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F27" s="28">
+        <v>5</v>
+      </c>
+      <c r="G27" s="27">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H27" s="27">
+        <v>100</v>
+      </c>
+      <c r="I27" s="26">
+        <v>1</v>
+      </c>
+      <c r="J27" s="29">
+        <v>1E-4</v>
+      </c>
+      <c r="K27" s="26">
+        <v>2</v>
+      </c>
+      <c r="L27" s="28">
+        <v>2</v>
+      </c>
+      <c r="M27" s="27">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N27" s="26">
+        <v>150</v>
+      </c>
+      <c r="O27" s="26">
+        <v>0.2</v>
+      </c>
+      <c r="P27" s="26">
+        <v>300</v>
+      </c>
+      <c r="Q27" s="28">
+        <v>400</v>
+      </c>
+      <c r="R27" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="S27" s="26">
+        <v>1</v>
+      </c>
+      <c r="T27" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="U27" s="27">
+        <f t="shared" si="1"/>
+        <v>1.0855471240301894E+16</v>
+      </c>
+      <c r="V27" s="26">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W27" s="26">
+        <v>0</v>
+      </c>
+      <c r="X27" s="30">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="28">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="69"/>
+      <c r="AA27" s="70"/>
+      <c r="AB27" s="70"/>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" s="34">
+        <v>125</v>
+      </c>
+      <c r="B28" s="31">
+        <v>12</v>
+      </c>
+      <c r="C28" s="32">
+        <v>1000</v>
+      </c>
+      <c r="D28" s="33">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E28" s="33">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F28" s="34">
+        <v>5</v>
+      </c>
+      <c r="G28" s="33">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H28" s="33">
+        <v>100</v>
+      </c>
+      <c r="I28" s="32">
+        <v>1</v>
+      </c>
+      <c r="J28" s="35">
+        <v>1E-4</v>
+      </c>
+      <c r="K28" s="32">
+        <v>2</v>
+      </c>
+      <c r="L28" s="34">
+        <v>2</v>
+      </c>
+      <c r="M28" s="33">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N28" s="32">
+        <v>150</v>
+      </c>
+      <c r="O28" s="32">
+        <v>0.2</v>
+      </c>
+      <c r="P28" s="32">
+        <v>300</v>
+      </c>
+      <c r="Q28" s="34">
+        <v>400</v>
+      </c>
+      <c r="R28" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="S28" s="32">
+        <v>1</v>
+      </c>
+      <c r="T28" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="U28" s="33">
+        <v>257896296296296.25</v>
+      </c>
+      <c r="V28" s="32">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W28" s="32">
+        <v>0</v>
+      </c>
+      <c r="X28" s="36">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="34">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="71" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA28" s="72"/>
+      <c r="AB28" s="72"/>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" s="22">
+        <v>126</v>
+      </c>
+      <c r="B29" s="13">
+        <v>12</v>
+      </c>
+      <c r="C29" s="15">
+        <v>3500</v>
+      </c>
+      <c r="D29" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E29" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F29" s="1">
+        <v>5</v>
+      </c>
+      <c r="G29" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H29" s="16">
+        <v>100</v>
+      </c>
+      <c r="I29" s="13">
+        <v>1</v>
+      </c>
+      <c r="J29" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K29" s="13">
+        <v>2</v>
+      </c>
+      <c r="L29" s="1">
+        <v>2</v>
+      </c>
+      <c r="M29" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N29" s="13">
+        <v>150</v>
+      </c>
+      <c r="O29" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P29" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>400</v>
+      </c>
+      <c r="R29" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S29" s="13">
+        <v>1</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U29" s="19">
+        <f>U27*2</f>
+        <v>2.1710942480603788E+16</v>
+      </c>
+      <c r="V29" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W29" s="13">
+        <v>0</v>
+      </c>
+      <c r="X29" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z29" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA29" s="70"/>
+      <c r="AB29" s="70"/>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30" s="22">
+        <v>127</v>
+      </c>
+      <c r="B30" s="13">
+        <v>12</v>
+      </c>
+      <c r="C30" s="15">
+        <v>3500</v>
+      </c>
+      <c r="D30" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E30" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F30" s="1">
+        <v>5</v>
+      </c>
+      <c r="G30" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H30" s="16">
+        <v>100</v>
+      </c>
+      <c r="I30" s="13">
+        <v>1</v>
+      </c>
+      <c r="J30" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K30" s="13">
+        <v>2</v>
+      </c>
+      <c r="L30" s="1">
+        <v>2</v>
+      </c>
+      <c r="M30" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N30" s="13">
+        <v>150</v>
+      </c>
+      <c r="O30" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P30" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>400</v>
+      </c>
+      <c r="R30" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S30" s="13">
+        <v>1</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U30" s="19">
+        <f t="shared" ref="U30:U31" si="3">U28*2</f>
+        <v>515792592592592.5</v>
+      </c>
+      <c r="V30" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W30" s="13">
+        <v>0</v>
+      </c>
+      <c r="X30" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="69"/>
+      <c r="AA30" s="70"/>
+      <c r="AB30" s="70"/>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" s="23">
+        <v>128</v>
+      </c>
+      <c r="B31" s="13">
+        <v>12</v>
+      </c>
+      <c r="C31" s="15">
+        <v>3500</v>
+      </c>
+      <c r="D31" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E31" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F31" s="1">
+        <v>5</v>
+      </c>
+      <c r="G31" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H31" s="16">
+        <v>100</v>
+      </c>
+      <c r="I31" s="13">
+        <v>1</v>
+      </c>
+      <c r="J31" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K31" s="13">
+        <v>2</v>
+      </c>
+      <c r="L31" s="1">
+        <v>2</v>
+      </c>
+      <c r="M31" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N31" s="13">
+        <v>150</v>
+      </c>
+      <c r="O31" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P31" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>400</v>
+      </c>
+      <c r="R31" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S31" s="13">
+        <v>1</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U31" s="19">
+        <f t="shared" si="3"/>
+        <v>4.3421884961207576E+16</v>
+      </c>
+      <c r="V31" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W31" s="13">
+        <v>0</v>
+      </c>
+      <c r="X31" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z31" s="69"/>
+      <c r="AA31" s="70"/>
+      <c r="AB31" s="70"/>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A32" s="23">
+        <v>129</v>
+      </c>
+      <c r="B32" s="13">
+        <v>12</v>
+      </c>
+      <c r="C32" s="15">
+        <v>3500</v>
+      </c>
+      <c r="D32" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E32" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F32" s="1">
+        <v>5</v>
+      </c>
+      <c r="G32" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H32" s="16">
+        <v>100</v>
+      </c>
+      <c r="I32" s="13">
+        <v>1</v>
+      </c>
+      <c r="J32" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K32" s="13">
+        <v>2</v>
+      </c>
+      <c r="L32" s="1">
+        <v>2</v>
+      </c>
+      <c r="M32" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N32" s="13">
+        <v>150</v>
+      </c>
+      <c r="O32" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P32" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>400</v>
+      </c>
+      <c r="R32" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S32" s="13">
+        <v>1</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U32" s="19">
+        <f>U31*2</f>
+        <v>8.6843769922415152E+16</v>
+      </c>
+      <c r="V32" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W32" s="13">
+        <v>0</v>
+      </c>
+      <c r="X32" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="69"/>
+      <c r="AA32" s="70"/>
+      <c r="AB32" s="70"/>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A33" s="22">
+        <v>130</v>
+      </c>
+      <c r="B33" s="13">
+        <v>12</v>
+      </c>
+      <c r="C33" s="15">
+        <v>3500</v>
+      </c>
+      <c r="D33" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E33" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F33" s="1">
+        <v>5</v>
+      </c>
+      <c r="G33" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H33" s="16">
+        <v>100</v>
+      </c>
+      <c r="I33" s="13">
+        <v>1</v>
+      </c>
+      <c r="J33" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K33" s="13">
+        <v>2</v>
+      </c>
+      <c r="L33" s="1">
+        <v>2</v>
+      </c>
+      <c r="M33" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N33" s="13">
+        <v>150</v>
+      </c>
+      <c r="O33" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P33" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>400</v>
+      </c>
+      <c r="R33" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S33" s="13">
+        <v>1</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U33" s="19">
+        <f t="shared" ref="U33:U45" si="4">U32*2</f>
+        <v>1.736875398448303E+17</v>
+      </c>
+      <c r="V33" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W33" s="13">
+        <v>0</v>
+      </c>
+      <c r="X33" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y33" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="69"/>
+      <c r="AA33" s="70"/>
+      <c r="AB33" s="70"/>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A34" s="22">
+        <v>131</v>
+      </c>
+      <c r="B34" s="13">
+        <v>12</v>
+      </c>
+      <c r="C34" s="15">
+        <v>3500</v>
+      </c>
+      <c r="D34" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E34" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F34" s="1">
+        <v>5</v>
+      </c>
+      <c r="G34" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H34" s="16">
+        <v>100</v>
+      </c>
+      <c r="I34" s="13">
+        <v>1</v>
+      </c>
+      <c r="J34" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K34" s="13">
+        <v>2</v>
+      </c>
+      <c r="L34" s="1">
+        <v>2</v>
+      </c>
+      <c r="M34" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N34" s="13">
+        <v>150</v>
+      </c>
+      <c r="O34" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P34" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>400</v>
+      </c>
+      <c r="R34" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S34" s="13">
+        <v>1</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U34" s="19">
+        <f t="shared" si="4"/>
+        <v>3.4737507968966061E+17</v>
+      </c>
+      <c r="V34" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W34" s="13">
+        <v>0</v>
+      </c>
+      <c r="X34" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="69"/>
+      <c r="AA34" s="70"/>
+      <c r="AB34" s="70"/>
+    </row>
+    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A35" s="22">
+        <v>132</v>
+      </c>
+      <c r="B35" s="13">
+        <v>12</v>
+      </c>
+      <c r="C35" s="15">
+        <v>3500</v>
+      </c>
+      <c r="D35" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E35" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F35" s="1">
+        <v>5</v>
+      </c>
+      <c r="G35" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H35" s="16">
+        <v>100</v>
+      </c>
+      <c r="I35" s="13">
+        <v>1</v>
+      </c>
+      <c r="J35" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K35" s="13">
+        <v>2</v>
+      </c>
+      <c r="L35" s="1">
+        <v>2</v>
+      </c>
+      <c r="M35" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N35" s="13">
+        <v>150</v>
+      </c>
+      <c r="O35" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P35" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>400</v>
+      </c>
+      <c r="R35" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S35" s="13">
+        <v>1</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U35" s="19">
+        <f t="shared" si="4"/>
+        <v>6.9475015937932122E+17</v>
+      </c>
+      <c r="V35" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W35" s="13">
+        <v>0</v>
+      </c>
+      <c r="X35" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y35" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="69"/>
+      <c r="AA35" s="70"/>
+      <c r="AB35" s="70"/>
+    </row>
+    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A36" s="23">
+        <v>133</v>
+      </c>
+      <c r="B36" s="13">
+        <v>12</v>
+      </c>
+      <c r="C36" s="15">
+        <v>3500</v>
+      </c>
+      <c r="D36" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E36" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F36" s="1">
+        <v>5</v>
+      </c>
+      <c r="G36" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H36" s="16">
+        <v>100</v>
+      </c>
+      <c r="I36" s="13">
+        <v>1</v>
+      </c>
+      <c r="J36" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K36" s="13">
+        <v>2</v>
+      </c>
+      <c r="L36" s="1">
+        <v>2</v>
+      </c>
+      <c r="M36" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N36" s="13">
+        <v>150</v>
+      </c>
+      <c r="O36" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P36" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>400</v>
+      </c>
+      <c r="R36" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S36" s="13">
+        <v>1</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U36" s="19">
+        <f t="shared" si="4"/>
+        <v>1.3895003187586424E+18</v>
+      </c>
+      <c r="V36" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W36" s="13">
+        <v>0</v>
+      </c>
+      <c r="X36" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y36" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="69"/>
+      <c r="AA36" s="70"/>
+      <c r="AB36" s="70"/>
+    </row>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A37" s="23">
+        <v>134</v>
+      </c>
+      <c r="B37" s="13">
+        <v>12</v>
+      </c>
+      <c r="C37" s="15">
+        <v>3500</v>
+      </c>
+      <c r="D37" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E37" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F37" s="1">
+        <v>5</v>
+      </c>
+      <c r="G37" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H37" s="16">
+        <v>100</v>
+      </c>
+      <c r="I37" s="13">
+        <v>1</v>
+      </c>
+      <c r="J37" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K37" s="13">
+        <v>2</v>
+      </c>
+      <c r="L37" s="1">
+        <v>2</v>
+      </c>
+      <c r="M37" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N37" s="13">
+        <v>150</v>
+      </c>
+      <c r="O37" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P37" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>400</v>
+      </c>
+      <c r="R37" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S37" s="13">
+        <v>1</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U37" s="19">
+        <f t="shared" si="4"/>
+        <v>2.7790006375172849E+18</v>
+      </c>
+      <c r="V37" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W37" s="13">
+        <v>0</v>
+      </c>
+      <c r="X37" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y37" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z37" s="69"/>
+      <c r="AA37" s="70"/>
+      <c r="AB37" s="70"/>
+    </row>
+    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A38" s="22">
+        <v>135</v>
+      </c>
+      <c r="B38" s="13">
+        <v>12</v>
+      </c>
+      <c r="C38" s="15">
+        <v>3500</v>
+      </c>
+      <c r="D38" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E38" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F38" s="1">
+        <v>5</v>
+      </c>
+      <c r="G38" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H38" s="16">
+        <v>100</v>
+      </c>
+      <c r="I38" s="13">
+        <v>1</v>
+      </c>
+      <c r="J38" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K38" s="13">
+        <v>2</v>
+      </c>
+      <c r="L38" s="1">
+        <v>2</v>
+      </c>
+      <c r="M38" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N38" s="13">
+        <v>150</v>
+      </c>
+      <c r="O38" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P38" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>400</v>
+      </c>
+      <c r="R38" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S38" s="13">
+        <v>1</v>
+      </c>
+      <c r="T38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U38" s="19">
+        <f t="shared" si="4"/>
+        <v>5.5580012750345697E+18</v>
+      </c>
+      <c r="V38" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W38" s="13">
+        <v>0</v>
+      </c>
+      <c r="X38" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y38" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z38" s="69"/>
+      <c r="AA38" s="70"/>
+      <c r="AB38" s="70"/>
+    </row>
+    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A39" s="23">
+        <v>136</v>
+      </c>
+      <c r="B39" s="13">
+        <v>12</v>
+      </c>
+      <c r="C39" s="15">
+        <v>3500</v>
+      </c>
+      <c r="D39" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E39" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F39" s="1">
+        <v>5</v>
+      </c>
+      <c r="G39" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H39" s="16">
+        <v>100</v>
+      </c>
+      <c r="I39" s="13">
+        <v>1</v>
+      </c>
+      <c r="J39" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K39" s="13">
+        <v>2</v>
+      </c>
+      <c r="L39" s="1">
+        <v>2</v>
+      </c>
+      <c r="M39" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N39" s="13">
+        <v>150</v>
+      </c>
+      <c r="O39" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P39" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>400</v>
+      </c>
+      <c r="R39" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S39" s="13">
+        <v>1</v>
+      </c>
+      <c r="T39" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U39" s="19">
+        <f t="shared" si="4"/>
+        <v>1.1116002550069139E+19</v>
+      </c>
+      <c r="V39" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W39" s="13">
+        <v>0</v>
+      </c>
+      <c r="X39" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y39" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="69"/>
+      <c r="AA39" s="70"/>
+      <c r="AB39" s="70"/>
+    </row>
+    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A40" s="62">
+        <v>137</v>
+      </c>
+      <c r="B40" s="13">
+        <v>12</v>
+      </c>
+      <c r="C40" s="15">
+        <v>3500</v>
+      </c>
+      <c r="D40" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E40" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F40" s="1">
+        <v>5</v>
+      </c>
+      <c r="G40" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H40" s="16">
+        <v>100</v>
+      </c>
+      <c r="I40" s="13">
+        <v>1</v>
+      </c>
+      <c r="J40" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K40" s="13">
+        <v>2</v>
+      </c>
+      <c r="L40" s="1">
+        <v>2</v>
+      </c>
+      <c r="M40" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N40" s="13">
+        <v>150</v>
+      </c>
+      <c r="O40" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P40" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>400</v>
+      </c>
+      <c r="R40" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S40" s="13">
+        <v>1</v>
+      </c>
+      <c r="T40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U40" s="19">
+        <f t="shared" si="4"/>
+        <v>2.2232005100138279E+19</v>
+      </c>
+      <c r="V40" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W40" s="13">
+        <v>0</v>
+      </c>
+      <c r="X40" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y40" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z40" s="69"/>
+      <c r="AA40" s="70"/>
+      <c r="AB40" s="70"/>
+    </row>
+    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A41" s="62">
+        <v>138</v>
+      </c>
+      <c r="B41" s="13">
+        <v>12</v>
+      </c>
+      <c r="C41" s="15">
+        <v>3500</v>
+      </c>
+      <c r="D41" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E41" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F41" s="1">
+        <v>5</v>
+      </c>
+      <c r="G41" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H41" s="16">
+        <v>100</v>
+      </c>
+      <c r="I41" s="13">
+        <v>1</v>
+      </c>
+      <c r="J41" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K41" s="13">
+        <v>2</v>
+      </c>
+      <c r="L41" s="1">
+        <v>2</v>
+      </c>
+      <c r="M41" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N41" s="13">
+        <v>150</v>
+      </c>
+      <c r="O41" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P41" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>400</v>
+      </c>
+      <c r="R41" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S41" s="13">
+        <v>1</v>
+      </c>
+      <c r="T41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U41" s="19">
+        <f t="shared" si="4"/>
+        <v>4.4464010200276558E+19</v>
+      </c>
+      <c r="V41" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W41" s="13">
+        <v>0</v>
+      </c>
+      <c r="X41" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y41" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z41" s="69"/>
+      <c r="AA41" s="70"/>
+      <c r="AB41" s="70"/>
+    </row>
+    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A42" s="62">
+        <v>139</v>
+      </c>
+      <c r="B42" s="13">
+        <v>12</v>
+      </c>
+      <c r="C42" s="15">
+        <v>3500</v>
+      </c>
+      <c r="D42" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E42" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F42" s="1">
+        <v>5</v>
+      </c>
+      <c r="G42" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H42" s="16">
+        <v>100</v>
+      </c>
+      <c r="I42" s="13">
+        <v>1</v>
+      </c>
+      <c r="J42" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K42" s="13">
+        <v>2</v>
+      </c>
+      <c r="L42" s="1">
+        <v>2</v>
+      </c>
+      <c r="M42" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N42" s="13">
+        <v>150</v>
+      </c>
+      <c r="O42" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P42" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>400</v>
+      </c>
+      <c r="R42" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S42" s="13">
+        <v>1</v>
+      </c>
+      <c r="T42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U42" s="19">
+        <f t="shared" si="4"/>
+        <v>8.8928020400553116E+19</v>
+      </c>
+      <c r="V42" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W42" s="13">
+        <v>0</v>
+      </c>
+      <c r="X42" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y42" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z42" s="69"/>
+      <c r="AA42" s="70"/>
+      <c r="AB42" s="70"/>
+    </row>
+    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A43" s="62">
+        <v>140</v>
+      </c>
+      <c r="B43" s="13">
+        <v>12</v>
+      </c>
+      <c r="C43" s="15">
+        <v>3500</v>
+      </c>
+      <c r="D43" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E43" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F43" s="1">
+        <v>5</v>
+      </c>
+      <c r="G43" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H43" s="16">
+        <v>100</v>
+      </c>
+      <c r="I43" s="13">
+        <v>1</v>
+      </c>
+      <c r="J43" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K43" s="13">
+        <v>2</v>
+      </c>
+      <c r="L43" s="1">
+        <v>2</v>
+      </c>
+      <c r="M43" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N43" s="13">
+        <v>150</v>
+      </c>
+      <c r="O43" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P43" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>400</v>
+      </c>
+      <c r="R43" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S43" s="13">
+        <v>1</v>
+      </c>
+      <c r="T43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U43" s="19">
+        <f t="shared" si="4"/>
+        <v>1.7785604080110623E+20</v>
+      </c>
+      <c r="V43" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W43" s="13">
+        <v>0</v>
+      </c>
+      <c r="X43" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y43" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z43" s="69"/>
+      <c r="AA43" s="70"/>
+      <c r="AB43" s="70"/>
+    </row>
+    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A44" s="62">
+        <v>141</v>
+      </c>
+      <c r="B44" s="13">
+        <v>12</v>
+      </c>
+      <c r="C44" s="15">
+        <v>3500</v>
+      </c>
+      <c r="D44" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E44" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F44" s="1">
+        <v>5</v>
+      </c>
+      <c r="G44" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H44" s="16">
+        <v>100</v>
+      </c>
+      <c r="I44" s="13">
+        <v>1</v>
+      </c>
+      <c r="J44" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K44" s="13">
+        <v>2</v>
+      </c>
+      <c r="L44" s="1">
+        <v>2</v>
+      </c>
+      <c r="M44" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N44" s="13">
+        <v>150</v>
+      </c>
+      <c r="O44" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P44" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>400</v>
+      </c>
+      <c r="R44" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S44" s="13">
+        <v>1</v>
+      </c>
+      <c r="T44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U44" s="19">
+        <f t="shared" si="4"/>
+        <v>3.5571208160221246E+20</v>
+      </c>
+      <c r="V44" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W44" s="13">
+        <v>0</v>
+      </c>
+      <c r="X44" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y44" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z44" s="69"/>
+      <c r="AA44" s="70"/>
+      <c r="AB44" s="70"/>
+    </row>
+    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A45" s="61">
+        <v>142</v>
+      </c>
+      <c r="B45" s="13">
+        <v>12</v>
+      </c>
+      <c r="C45" s="15">
+        <v>3500</v>
+      </c>
+      <c r="D45" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E45" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F45" s="1">
+        <v>5</v>
+      </c>
+      <c r="G45" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H45" s="16">
+        <v>100</v>
+      </c>
+      <c r="I45" s="13">
+        <v>1</v>
+      </c>
+      <c r="J45" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K45" s="13">
+        <v>2</v>
+      </c>
+      <c r="L45" s="1">
+        <v>2</v>
+      </c>
+      <c r="M45" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N45" s="13">
+        <v>150</v>
+      </c>
+      <c r="O45" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P45" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>400</v>
+      </c>
+      <c r="R45" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S45" s="13">
+        <v>1</v>
+      </c>
+      <c r="T45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U45" s="19">
+        <f t="shared" si="4"/>
+        <v>7.1142416320442493E+20</v>
+      </c>
+      <c r="V45" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W45" s="13">
+        <v>0</v>
+      </c>
+      <c r="X45" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y45" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z45" s="69"/>
+      <c r="AA45" s="70"/>
+      <c r="AB45" s="70"/>
+    </row>
+    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A46" s="61">
+        <v>143</v>
+      </c>
+      <c r="B46" s="13">
+        <v>12</v>
+      </c>
+      <c r="C46" s="15">
+        <v>3500</v>
+      </c>
+      <c r="D46" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E46" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F46" s="1">
+        <v>5</v>
+      </c>
+      <c r="G46" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H46" s="16">
+        <v>100</v>
+      </c>
+      <c r="I46" s="13">
+        <v>1</v>
+      </c>
+      <c r="J46" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K46" s="13">
+        <v>2</v>
+      </c>
+      <c r="L46" s="1">
+        <v>2</v>
+      </c>
+      <c r="M46" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N46" s="13">
+        <v>150</v>
+      </c>
+      <c r="O46" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P46" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>400</v>
+      </c>
+      <c r="R46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S46" s="13">
+        <v>1</v>
+      </c>
+      <c r="T46" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U46" s="19">
+        <f>U45*2</f>
+        <v>1.4228483264088499E+21</v>
+      </c>
+      <c r="V46" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W46" s="13">
+        <v>0</v>
+      </c>
+      <c r="X46" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y46" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z46" s="69"/>
+      <c r="AA46" s="70"/>
+      <c r="AB46" s="70"/>
+    </row>
+    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A47" s="41">
+        <v>144</v>
+      </c>
+      <c r="B47" s="42">
+        <v>12</v>
+      </c>
+      <c r="C47" s="42">
+        <v>300</v>
+      </c>
+      <c r="D47" s="43">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E47" s="43">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F47" s="44">
+        <v>5</v>
+      </c>
+      <c r="G47" s="43">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H47" s="43">
+        <v>100</v>
+      </c>
+      <c r="I47" s="42">
+        <v>1</v>
+      </c>
+      <c r="J47" s="45">
+        <v>1E-4</v>
+      </c>
+      <c r="K47" s="42">
+        <v>2</v>
+      </c>
+      <c r="L47" s="44">
+        <v>2</v>
+      </c>
+      <c r="M47" s="43">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N47" s="42">
+        <v>150</v>
+      </c>
+      <c r="O47" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="P47" s="42">
+        <v>300</v>
+      </c>
+      <c r="Q47" s="44">
+        <v>400</v>
+      </c>
+      <c r="R47" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="S47" s="42">
+        <v>1</v>
+      </c>
+      <c r="T47" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="U47" s="43">
+        <v>81600000000000</v>
+      </c>
+      <c r="V47" s="42">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W47" s="42">
+        <v>0</v>
+      </c>
+      <c r="X47" s="46">
+        <v>1</v>
+      </c>
+      <c r="Y47" s="44">
+        <v>1</v>
+      </c>
+      <c r="Z47" s="71" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA47" s="72"/>
+      <c r="AB47" s="72"/>
+      <c r="AC47" s="20"/>
+    </row>
+    <row r="48" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="41">
+        <v>145</v>
+      </c>
+      <c r="B48" s="42">
+        <v>12</v>
+      </c>
+      <c r="C48" s="46">
+        <v>2000</v>
+      </c>
+      <c r="D48" s="43">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E48" s="43">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F48" s="44">
+        <v>5</v>
+      </c>
+      <c r="G48" s="43">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H48" s="43">
+        <v>100</v>
+      </c>
+      <c r="I48" s="42">
+        <v>1</v>
+      </c>
+      <c r="J48" s="45">
+        <v>1E-4</v>
+      </c>
+      <c r="K48" s="42">
+        <v>2</v>
+      </c>
+      <c r="L48" s="44">
+        <v>2</v>
+      </c>
+      <c r="M48" s="43">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N48" s="42">
+        <v>150</v>
+      </c>
+      <c r="O48" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="P48" s="42">
+        <v>300</v>
+      </c>
+      <c r="Q48" s="44">
+        <v>400</v>
+      </c>
+      <c r="R48" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="S48" s="42">
+        <v>1</v>
+      </c>
+      <c r="T48" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="U48" s="43">
+        <f>U29</f>
+        <v>2.1710942480603788E+16</v>
+      </c>
+      <c r="V48" s="42">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W48" s="42">
+        <v>0</v>
+      </c>
+      <c r="X48" s="46">
+        <v>1</v>
+      </c>
+      <c r="Y48" s="44">
+        <v>1</v>
+      </c>
+      <c r="Z48" s="66" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA48" s="68"/>
+      <c r="AB48" s="68"/>
+      <c r="AC48" s="24"/>
+    </row>
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A49" s="41">
+        <v>146</v>
+      </c>
+      <c r="B49" s="42">
+        <v>12</v>
+      </c>
+      <c r="C49" s="42">
+        <v>300</v>
+      </c>
+      <c r="D49" s="43">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E49" s="43">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F49" s="44">
+        <v>5</v>
+      </c>
+      <c r="G49" s="43">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H49" s="43">
+        <v>100</v>
+      </c>
+      <c r="I49" s="42">
+        <v>1</v>
+      </c>
+      <c r="J49" s="45">
+        <v>1E-4</v>
+      </c>
+      <c r="K49" s="42">
+        <v>2</v>
+      </c>
+      <c r="L49" s="44">
+        <v>2</v>
+      </c>
+      <c r="M49" s="43">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N49" s="42">
+        <v>150</v>
+      </c>
+      <c r="O49" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="P49" s="42">
+        <v>300</v>
+      </c>
+      <c r="Q49" s="44">
+        <v>400</v>
+      </c>
+      <c r="R49" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="S49" s="42">
+        <v>1</v>
+      </c>
+      <c r="T49" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="U49" s="43">
+        <v>81600000000</v>
+      </c>
+      <c r="V49" s="42">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W49" s="42">
+        <v>0</v>
+      </c>
+      <c r="X49" s="46">
+        <v>1</v>
+      </c>
+      <c r="Y49" s="44">
+        <v>1</v>
+      </c>
+      <c r="Z49" s="71" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA49" s="72"/>
+      <c r="AB49" s="72"/>
+    </row>
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A50" s="41">
+        <v>147</v>
+      </c>
+      <c r="B50" s="46">
+        <v>12</v>
+      </c>
+      <c r="C50" s="46">
+        <v>2000</v>
+      </c>
+      <c r="D50" s="48">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E50" s="48">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F50" s="41">
+        <v>5</v>
+      </c>
+      <c r="G50" s="48">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H50" s="48">
+        <v>100</v>
+      </c>
+      <c r="I50" s="46">
+        <v>1</v>
+      </c>
+      <c r="J50" s="49">
+        <v>1E-4</v>
+      </c>
+      <c r="K50" s="46">
+        <v>2</v>
+      </c>
+      <c r="L50" s="41">
+        <v>2</v>
+      </c>
+      <c r="M50" s="48">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N50" s="46">
+        <v>150</v>
+      </c>
+      <c r="O50" s="46">
+        <v>0.2</v>
+      </c>
+      <c r="P50" s="46">
+        <v>300</v>
+      </c>
+      <c r="Q50" s="41">
+        <v>400</v>
+      </c>
+      <c r="R50" s="46" t="s">
+        <v>38</v>
+      </c>
+      <c r="S50" s="46">
+        <v>1</v>
+      </c>
+      <c r="T50" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="U50" s="50">
+        <v>81600000000000</v>
+      </c>
+      <c r="V50" s="36">
+        <v>83000</v>
+      </c>
+      <c r="W50" s="46">
+        <v>0</v>
+      </c>
+      <c r="X50" s="46">
+        <v>1</v>
+      </c>
+      <c r="Y50" s="41">
+        <v>1</v>
+      </c>
+      <c r="Z50" s="71" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA50" s="72"/>
+      <c r="AB50" s="72"/>
+    </row>
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A51" s="44">
+        <v>148</v>
+      </c>
+      <c r="B51" s="42">
+        <v>12</v>
+      </c>
+      <c r="C51" s="46">
+        <v>2000</v>
+      </c>
+      <c r="D51" s="43">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E51" s="43">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F51" s="44">
+        <v>5</v>
+      </c>
+      <c r="G51" s="43">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H51" s="43">
+        <v>100</v>
+      </c>
+      <c r="I51" s="42">
+        <v>1</v>
+      </c>
+      <c r="J51" s="45">
+        <v>1E-4</v>
+      </c>
+      <c r="K51" s="42">
+        <v>2</v>
+      </c>
+      <c r="L51" s="44">
+        <v>2</v>
+      </c>
+      <c r="M51" s="43">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N51" s="42">
+        <v>150</v>
+      </c>
+      <c r="O51" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="P51" s="42">
+        <v>300</v>
+      </c>
+      <c r="Q51" s="44">
+        <v>400</v>
+      </c>
+      <c r="R51" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="S51" s="42">
+        <v>1</v>
+      </c>
+      <c r="T51" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="U51" s="16">
+        <f>U40</f>
+        <v>2.2232005100138279E+19</v>
+      </c>
+      <c r="V51" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W51" s="42">
+        <v>0</v>
+      </c>
+      <c r="X51" s="46">
+        <v>1</v>
+      </c>
+      <c r="Y51" s="44">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA51" s="70"/>
+      <c r="AB51" s="70"/>
+    </row>
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>149</v>
+      </c>
+      <c r="B52" s="13">
+        <v>12</v>
+      </c>
+      <c r="C52" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D52" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E52" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F52" s="1">
+        <v>5</v>
+      </c>
+      <c r="G52" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H52" s="16">
+        <v>100</v>
+      </c>
+      <c r="I52" s="13">
+        <v>1</v>
+      </c>
+      <c r="J52" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K52" s="13">
+        <v>2</v>
+      </c>
+      <c r="L52" s="1">
+        <v>2</v>
+      </c>
+      <c r="M52" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N52" s="13">
+        <v>150</v>
+      </c>
+      <c r="O52" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P52" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q52" s="1">
+        <v>400</v>
+      </c>
+      <c r="R52" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S52" s="13">
+        <v>1</v>
+      </c>
+      <c r="T52" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U52" s="16">
+        <f t="shared" ref="U52:U57" si="5">U41</f>
+        <v>4.4464010200276558E+19</v>
+      </c>
+      <c r="V52" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W52" s="13">
+        <v>0</v>
+      </c>
+      <c r="X52" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y52" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z52" s="69"/>
+      <c r="AA52" s="70"/>
+      <c r="AB52" s="70"/>
+    </row>
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>150</v>
+      </c>
+      <c r="B53" s="13">
+        <v>12</v>
+      </c>
+      <c r="C53" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D53" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E53" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F53" s="1">
+        <v>5</v>
+      </c>
+      <c r="G53" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H53" s="16">
+        <v>100</v>
+      </c>
+      <c r="I53" s="13">
+        <v>1</v>
+      </c>
+      <c r="J53" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K53" s="13">
+        <v>2</v>
+      </c>
+      <c r="L53" s="1">
+        <v>2</v>
+      </c>
+      <c r="M53" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N53" s="13">
+        <v>150</v>
+      </c>
+      <c r="O53" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P53" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q53" s="1">
+        <v>400</v>
+      </c>
+      <c r="R53" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S53" s="13">
+        <v>1</v>
+      </c>
+      <c r="T53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U53" s="16">
+        <f t="shared" si="5"/>
+        <v>8.8928020400553116E+19</v>
+      </c>
+      <c r="V53" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W53" s="13">
+        <v>0</v>
+      </c>
+      <c r="X53" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y53" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z53" s="69"/>
+      <c r="AA53" s="70"/>
+      <c r="AB53" s="70"/>
+    </row>
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>151</v>
+      </c>
+      <c r="B54" s="13">
+        <v>12</v>
+      </c>
+      <c r="C54" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D54" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E54" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F54" s="1">
+        <v>5</v>
+      </c>
+      <c r="G54" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H54" s="16">
+        <v>100</v>
+      </c>
+      <c r="I54" s="13">
+        <v>1</v>
+      </c>
+      <c r="J54" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K54" s="13">
+        <v>2</v>
+      </c>
+      <c r="L54" s="1">
+        <v>2</v>
+      </c>
+      <c r="M54" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N54" s="13">
+        <v>150</v>
+      </c>
+      <c r="O54" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P54" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q54" s="1">
+        <v>400</v>
+      </c>
+      <c r="R54" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S54" s="13">
+        <v>1</v>
+      </c>
+      <c r="T54" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U54" s="16">
+        <f t="shared" si="5"/>
+        <v>1.7785604080110623E+20</v>
+      </c>
+      <c r="V54" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W54" s="13">
+        <v>0</v>
+      </c>
+      <c r="X54" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y54" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z54" s="69"/>
+      <c r="AA54" s="70"/>
+      <c r="AB54" s="70"/>
+    </row>
+    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A55" s="61">
+        <v>152</v>
+      </c>
+      <c r="B55" s="13">
+        <v>12</v>
+      </c>
+      <c r="C55" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D55" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E55" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F55" s="1">
+        <v>5</v>
+      </c>
+      <c r="G55" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H55" s="16">
+        <v>100</v>
+      </c>
+      <c r="I55" s="13">
+        <v>1</v>
+      </c>
+      <c r="J55" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K55" s="13">
+        <v>2</v>
+      </c>
+      <c r="L55" s="1">
+        <v>2</v>
+      </c>
+      <c r="M55" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N55" s="13">
+        <v>150</v>
+      </c>
+      <c r="O55" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P55" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>400</v>
+      </c>
+      <c r="R55" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S55" s="13">
+        <v>1</v>
+      </c>
+      <c r="T55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U55" s="16">
+        <f t="shared" si="5"/>
+        <v>3.5571208160221246E+20</v>
+      </c>
+      <c r="V55" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W55" s="13">
+        <v>0</v>
+      </c>
+      <c r="X55" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y55" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z55" s="69"/>
+      <c r="AA55" s="70"/>
+      <c r="AB55" s="70"/>
+    </row>
+    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A56" s="61">
+        <v>153</v>
+      </c>
+      <c r="B56" s="13">
+        <v>12</v>
+      </c>
+      <c r="C56" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D56" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E56" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F56" s="1">
+        <v>5</v>
+      </c>
+      <c r="G56" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H56" s="16">
+        <v>100</v>
+      </c>
+      <c r="I56" s="13">
+        <v>1</v>
+      </c>
+      <c r="J56" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K56" s="13">
+        <v>2</v>
+      </c>
+      <c r="L56" s="1">
+        <v>2</v>
+      </c>
+      <c r="M56" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N56" s="13">
+        <v>150</v>
+      </c>
+      <c r="O56" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P56" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q56" s="1">
+        <v>400</v>
+      </c>
+      <c r="R56" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S56" s="13">
+        <v>1</v>
+      </c>
+      <c r="T56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U56" s="16">
+        <f t="shared" si="5"/>
+        <v>7.1142416320442493E+20</v>
+      </c>
+      <c r="V56" s="13">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W56" s="13">
+        <v>0</v>
+      </c>
+      <c r="X56" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y56" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z56" s="69"/>
+      <c r="AA56" s="70"/>
+      <c r="AB56" s="70"/>
+    </row>
+    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A57" s="63">
+        <v>154</v>
+      </c>
+      <c r="B57" s="26">
+        <v>12</v>
+      </c>
+      <c r="C57" s="30">
+        <v>2000</v>
+      </c>
+      <c r="D57" s="27">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E57" s="27">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F57" s="28">
+        <v>5</v>
+      </c>
+      <c r="G57" s="27">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H57" s="27">
+        <v>100</v>
+      </c>
+      <c r="I57" s="26">
+        <v>1</v>
+      </c>
+      <c r="J57" s="29">
+        <v>1E-4</v>
+      </c>
+      <c r="K57" s="26">
+        <v>2</v>
+      </c>
+      <c r="L57" s="28">
+        <v>2</v>
+      </c>
+      <c r="M57" s="27">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N57" s="26">
+        <v>150</v>
+      </c>
+      <c r="O57" s="26">
+        <v>0.2</v>
+      </c>
+      <c r="P57" s="26">
+        <v>300</v>
+      </c>
+      <c r="Q57" s="28">
+        <v>400</v>
+      </c>
+      <c r="R57" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="S57" s="26">
+        <v>1</v>
+      </c>
+      <c r="T57" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="U57" s="27">
+        <f t="shared" si="5"/>
+        <v>1.4228483264088499E+21</v>
+      </c>
+      <c r="V57" s="26">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W57" s="26">
+        <v>0</v>
+      </c>
+      <c r="X57" s="30">
+        <v>1</v>
+      </c>
+      <c r="Y57" s="28">
+        <v>1</v>
+      </c>
+      <c r="Z57" s="69"/>
+      <c r="AA57" s="70"/>
+      <c r="AB57" s="70"/>
+    </row>
+    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A58" s="57">
+        <v>155</v>
+      </c>
+      <c r="B58" s="36">
+        <v>12</v>
+      </c>
+      <c r="C58" s="36">
+        <v>2000</v>
+      </c>
+      <c r="D58" s="55">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E58" s="55">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F58" s="54">
+        <v>5</v>
+      </c>
+      <c r="G58" s="55">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H58" s="55">
+        <v>100</v>
+      </c>
+      <c r="I58" s="36">
+        <v>1</v>
+      </c>
+      <c r="J58" s="56">
+        <v>1E-4</v>
+      </c>
+      <c r="K58" s="36">
+        <v>2</v>
+      </c>
+      <c r="L58" s="54">
+        <v>2</v>
+      </c>
+      <c r="M58" s="55">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N58" s="36">
+        <v>3000</v>
+      </c>
+      <c r="O58" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="P58" s="36">
+        <v>300</v>
+      </c>
+      <c r="Q58" s="54">
+        <v>400</v>
+      </c>
+      <c r="R58" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="S58" s="36">
+        <v>1</v>
+      </c>
+      <c r="T58" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="U58" s="55">
+        <v>81600000000000</v>
+      </c>
+      <c r="V58" s="36">
+        <f t="shared" si="2"/>
+        <v>125520</v>
+      </c>
+      <c r="W58" s="36">
+        <v>0</v>
+      </c>
+      <c r="X58" s="36">
+        <v>1</v>
+      </c>
+      <c r="Y58" s="54">
+        <v>1</v>
+      </c>
+      <c r="Z58" s="66" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA58" s="68"/>
+      <c r="AB58" s="68"/>
+    </row>
+    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A59" s="51">
+        <v>156</v>
+      </c>
+      <c r="B59" s="15">
+        <v>12</v>
+      </c>
+      <c r="C59" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D59" s="52">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E59" s="52">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F59" s="51">
+        <v>5</v>
+      </c>
+      <c r="G59" s="52">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H59" s="52">
+        <v>100</v>
+      </c>
+      <c r="I59" s="15">
+        <v>1</v>
+      </c>
+      <c r="J59" s="53">
+        <v>1E-4</v>
+      </c>
+      <c r="K59" s="15">
+        <v>2</v>
+      </c>
+      <c r="L59" s="51">
+        <v>2</v>
+      </c>
+      <c r="M59" s="52">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N59" s="15">
+        <v>150</v>
+      </c>
+      <c r="O59" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P59" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q59" s="51">
+        <v>400</v>
+      </c>
+      <c r="R59" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="S59" s="15">
+        <v>1</v>
+      </c>
+      <c r="T59" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="U59" s="52">
+        <v>81600000000000</v>
+      </c>
+      <c r="V59" s="15">
+        <f>20*4184</f>
+        <v>83680</v>
+      </c>
+      <c r="W59" s="15">
+        <v>0</v>
+      </c>
+      <c r="X59" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y59" s="51">
+        <v>1</v>
+      </c>
+      <c r="Z59" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA59" s="70"/>
+      <c r="AB59" s="70"/>
+    </row>
+    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A60" s="51">
+        <v>157</v>
+      </c>
+      <c r="B60" s="15">
+        <v>12</v>
+      </c>
+      <c r="C60" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D60" s="52">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E60" s="52">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F60" s="51">
+        <v>5</v>
+      </c>
+      <c r="G60" s="52">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H60" s="52">
+        <v>100</v>
+      </c>
+      <c r="I60" s="15">
+        <v>1</v>
+      </c>
+      <c r="J60" s="53">
+        <v>1E-4</v>
+      </c>
+      <c r="K60" s="15">
+        <v>2</v>
+      </c>
+      <c r="L60" s="51">
+        <v>2</v>
+      </c>
+      <c r="M60" s="52">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N60" s="15">
+        <v>150</v>
+      </c>
+      <c r="O60" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P60" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q60" s="51">
+        <v>400</v>
+      </c>
+      <c r="R60" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="S60" s="15">
+        <v>1</v>
+      </c>
+      <c r="T60" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="U60" s="52">
+        <v>81600000000000</v>
+      </c>
+      <c r="V60" s="15">
+        <f>15*4184</f>
+        <v>62760</v>
+      </c>
+      <c r="W60" s="15">
+        <v>0</v>
+      </c>
+      <c r="X60" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y60" s="51">
+        <v>1</v>
+      </c>
+      <c r="Z60" s="69"/>
+      <c r="AA60" s="70"/>
+      <c r="AB60" s="70"/>
+    </row>
+    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>158</v>
+      </c>
+      <c r="B61" s="15">
+        <v>12</v>
+      </c>
+      <c r="C61" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D61" s="52">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E61" s="52">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F61" s="51">
+        <v>5</v>
+      </c>
+      <c r="G61" s="52">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H61" s="52">
+        <v>100</v>
+      </c>
+      <c r="I61" s="15">
+        <v>1</v>
+      </c>
+      <c r="J61" s="53">
+        <v>1E-4</v>
+      </c>
+      <c r="K61" s="15">
+        <v>2</v>
+      </c>
+      <c r="L61" s="51">
+        <v>2</v>
+      </c>
+      <c r="M61" s="52">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N61" s="15">
+        <v>150</v>
+      </c>
+      <c r="O61" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P61" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q61" s="51">
+        <v>400</v>
+      </c>
+      <c r="R61" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="S61" s="15">
+        <v>1</v>
+      </c>
+      <c r="T61" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="U61" s="52">
+        <v>81600000000000</v>
+      </c>
+      <c r="V61" s="15">
+        <f>10*4184</f>
+        <v>41840</v>
+      </c>
+      <c r="W61" s="15">
+        <v>0</v>
+      </c>
+      <c r="X61" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y61" s="51">
+        <v>1</v>
+      </c>
+      <c r="Z61" s="69"/>
+      <c r="AA61" s="70"/>
+      <c r="AB61" s="70"/>
+    </row>
+    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A62" s="51">
+        <v>159</v>
+      </c>
+      <c r="B62" s="15">
+        <v>12</v>
+      </c>
+      <c r="C62" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D62" s="52">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E62" s="52">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F62" s="51">
+        <v>5</v>
+      </c>
+      <c r="G62" s="52">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H62" s="52">
+        <v>100</v>
+      </c>
+      <c r="I62" s="15">
+        <v>1</v>
+      </c>
+      <c r="J62" s="53">
+        <v>1E-4</v>
+      </c>
+      <c r="K62" s="15">
+        <v>2</v>
+      </c>
+      <c r="L62" s="51">
+        <v>2</v>
+      </c>
+      <c r="M62" s="52">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N62" s="15">
+        <v>150</v>
+      </c>
+      <c r="O62" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P62" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q62" s="51">
+        <v>400</v>
+      </c>
+      <c r="R62" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="S62" s="15">
+        <v>1</v>
+      </c>
+      <c r="T62" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="U62" s="52">
+        <v>81600000000000</v>
+      </c>
+      <c r="V62" s="15">
+        <f>5*4184</f>
+        <v>20920</v>
+      </c>
+      <c r="W62" s="15">
+        <v>0</v>
+      </c>
+      <c r="X62" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y62" s="51">
+        <v>1</v>
+      </c>
+      <c r="Z62" s="69"/>
+      <c r="AA62" s="70"/>
+      <c r="AB62" s="70"/>
+    </row>
+    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>160</v>
+      </c>
+      <c r="B63" s="15">
+        <v>12</v>
+      </c>
+      <c r="C63" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D63" s="52">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E63" s="52">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F63" s="51">
+        <v>5</v>
+      </c>
+      <c r="G63" s="52">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H63" s="52">
+        <v>100</v>
+      </c>
+      <c r="I63" s="15">
+        <v>1</v>
+      </c>
+      <c r="J63" s="53">
+        <v>1E-4</v>
+      </c>
+      <c r="K63" s="15">
+        <v>2</v>
+      </c>
+      <c r="L63" s="51">
+        <v>2</v>
+      </c>
+      <c r="M63" s="52">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N63" s="15">
+        <v>150</v>
+      </c>
+      <c r="O63" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P63" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q63" s="51">
+        <v>400</v>
+      </c>
+      <c r="R63" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="S63" s="15">
+        <v>1</v>
+      </c>
+      <c r="T63" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="U63" s="52">
+        <v>81600000000000</v>
+      </c>
+      <c r="V63" s="15">
+        <f>35*4184</f>
+        <v>146440</v>
+      </c>
+      <c r="W63" s="15">
+        <v>0</v>
+      </c>
+      <c r="X63" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y63" s="51">
+        <v>1</v>
+      </c>
+      <c r="Z63" s="69"/>
+      <c r="AA63" s="70"/>
+      <c r="AB63" s="70"/>
+    </row>
+    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A64" s="51">
+        <v>161</v>
+      </c>
+      <c r="B64" s="15">
+        <v>12</v>
+      </c>
+      <c r="C64" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D64" s="52">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E64" s="52">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F64" s="51">
+        <v>5</v>
+      </c>
+      <c r="G64" s="52">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H64" s="52">
+        <v>100</v>
+      </c>
+      <c r="I64" s="15">
+        <v>1</v>
+      </c>
+      <c r="J64" s="53">
+        <v>1E-4</v>
+      </c>
+      <c r="K64" s="15">
+        <v>2</v>
+      </c>
+      <c r="L64" s="51">
+        <v>2</v>
+      </c>
+      <c r="M64" s="52">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N64" s="15">
+        <v>150</v>
+      </c>
+      <c r="O64" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P64" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q64" s="51">
+        <v>400</v>
+      </c>
+      <c r="R64" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="S64" s="15">
+        <v>1</v>
+      </c>
+      <c r="T64" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="U64" s="52">
+        <v>81600000000000</v>
+      </c>
+      <c r="V64" s="15">
+        <f>40*4184</f>
+        <v>167360</v>
+      </c>
+      <c r="W64" s="15">
+        <v>0</v>
+      </c>
+      <c r="X64" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y64" s="51">
+        <v>1</v>
+      </c>
+      <c r="Z64" s="69"/>
+      <c r="AA64" s="70"/>
+      <c r="AB64" s="70"/>
+    </row>
+    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>162</v>
+      </c>
+      <c r="B65" s="15">
+        <v>12</v>
+      </c>
+      <c r="C65" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D65" s="52">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E65" s="52">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F65" s="51">
+        <v>5</v>
+      </c>
+      <c r="G65" s="52">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H65" s="52">
+        <v>100</v>
+      </c>
+      <c r="I65" s="15">
+        <v>1</v>
+      </c>
+      <c r="J65" s="53">
+        <v>1E-4</v>
+      </c>
+      <c r="K65" s="15">
+        <v>2</v>
+      </c>
+      <c r="L65" s="51">
+        <v>2</v>
+      </c>
+      <c r="M65" s="52">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N65" s="15">
+        <v>150</v>
+      </c>
+      <c r="O65" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P65" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q65" s="51">
+        <v>400</v>
+      </c>
+      <c r="R65" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="S65" s="15">
+        <v>1</v>
+      </c>
+      <c r="T65" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="U65" s="52">
+        <v>81600000000000</v>
+      </c>
+      <c r="V65" s="15">
+        <f>45*4184</f>
+        <v>188280</v>
+      </c>
+      <c r="W65" s="15">
+        <v>0</v>
+      </c>
+      <c r="X65" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y65" s="51">
+        <v>1</v>
+      </c>
+      <c r="Z65" s="69"/>
+      <c r="AA65" s="70"/>
+      <c r="AB65" s="70"/>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A66" s="58">
+        <v>163</v>
+      </c>
+      <c r="B66" s="30">
+        <v>12</v>
+      </c>
+      <c r="C66" s="30">
+        <v>2000</v>
+      </c>
+      <c r="D66" s="59">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E66" s="59">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F66" s="58">
+        <v>5</v>
+      </c>
+      <c r="G66" s="59">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H66" s="59">
+        <v>100</v>
+      </c>
+      <c r="I66" s="30">
+        <v>1</v>
+      </c>
+      <c r="J66" s="60">
+        <v>1E-4</v>
+      </c>
+      <c r="K66" s="30">
+        <v>2</v>
+      </c>
+      <c r="L66" s="58">
+        <v>2</v>
+      </c>
+      <c r="M66" s="59">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N66" s="30">
+        <v>150</v>
+      </c>
+      <c r="O66" s="30">
+        <v>0.2</v>
+      </c>
+      <c r="P66" s="30">
+        <v>300</v>
+      </c>
+      <c r="Q66" s="58">
+        <v>400</v>
+      </c>
+      <c r="R66" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="S66" s="30">
+        <v>1</v>
+      </c>
+      <c r="T66" s="58" t="s">
+        <v>11</v>
+      </c>
+      <c r="U66" s="59">
+        <v>81600000000000</v>
+      </c>
+      <c r="V66" s="30">
+        <f>50*4184</f>
+        <v>209200</v>
+      </c>
+      <c r="W66" s="30">
+        <v>0</v>
+      </c>
+      <c r="X66" s="30">
+        <v>1</v>
+      </c>
+      <c r="Y66" s="58">
+        <v>1</v>
+      </c>
+      <c r="Z66" s="69"/>
+      <c r="AA66" s="70"/>
+      <c r="AB66" s="70"/>
+    </row>
+    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A67" s="47">
+        <v>164</v>
+      </c>
+      <c r="B67" s="64">
+        <v>12</v>
+      </c>
+      <c r="C67" s="46">
+        <v>2000</v>
+      </c>
+      <c r="D67" s="43">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E67" s="43">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F67" s="44">
+        <v>5</v>
+      </c>
+      <c r="G67" s="43">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H67" s="43">
+        <v>100</v>
+      </c>
+      <c r="I67" s="42">
+        <v>1</v>
+      </c>
+      <c r="J67" s="45">
+        <v>1E-4</v>
+      </c>
+      <c r="K67" s="42">
+        <v>2</v>
+      </c>
+      <c r="L67" s="44">
+        <v>2</v>
+      </c>
+      <c r="M67" s="43">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N67" s="42">
+        <v>150</v>
+      </c>
+      <c r="O67" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="P67" s="42">
+        <v>300</v>
+      </c>
+      <c r="Q67" s="44">
+        <v>400</v>
+      </c>
+      <c r="R67" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="S67" s="42">
+        <v>1</v>
+      </c>
+      <c r="T67" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="U67" s="16">
+        <f>U51</f>
+        <v>2.2232005100138279E+19</v>
+      </c>
+      <c r="V67" s="13">
+        <f t="shared" ref="V67:V87" si="6">30*4184</f>
+        <v>125520</v>
+      </c>
+      <c r="W67" s="42">
+        <v>0</v>
+      </c>
+      <c r="X67" s="46">
+        <v>1</v>
+      </c>
+      <c r="Y67" s="44">
+        <v>1</v>
+      </c>
+      <c r="Z67" s="69" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA67" s="78"/>
+      <c r="AB67" s="78"/>
+    </row>
+    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A68" s="22">
+        <v>165</v>
+      </c>
+      <c r="B68" s="13">
+        <v>12</v>
+      </c>
+      <c r="C68" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D68" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E68" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F68" s="1">
+        <v>5</v>
+      </c>
+      <c r="G68" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H68" s="16">
+        <v>100</v>
+      </c>
+      <c r="I68" s="13">
+        <v>1</v>
+      </c>
+      <c r="J68" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K68" s="13">
+        <v>2</v>
+      </c>
+      <c r="L68" s="1">
+        <v>2</v>
+      </c>
+      <c r="M68" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N68" s="13">
+        <v>150</v>
+      </c>
+      <c r="O68" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P68" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>400</v>
+      </c>
+      <c r="R68" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S68" s="13">
+        <v>1</v>
+      </c>
+      <c r="T68" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U68" s="19">
+        <f>U67/5</f>
+        <v>4.4464010200276557E+18</v>
+      </c>
+      <c r="V68" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W68" s="13">
+        <v>0</v>
+      </c>
+      <c r="X68" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y68" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z68" s="69"/>
+      <c r="AA68" s="78"/>
+      <c r="AB68" s="78"/>
+    </row>
+    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A69" s="22">
+        <v>166</v>
+      </c>
+      <c r="B69" s="13">
+        <v>12</v>
+      </c>
+      <c r="C69" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D69" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E69" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F69" s="1">
+        <v>5</v>
+      </c>
+      <c r="G69" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H69" s="16">
+        <v>100</v>
+      </c>
+      <c r="I69" s="13">
+        <v>1</v>
+      </c>
+      <c r="J69" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K69" s="13">
+        <v>2</v>
+      </c>
+      <c r="L69" s="1">
+        <v>2</v>
+      </c>
+      <c r="M69" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N69" s="13">
+        <v>150</v>
+      </c>
+      <c r="O69" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P69" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q69" s="1">
+        <v>400</v>
+      </c>
+      <c r="R69" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S69" s="13">
+        <v>1</v>
+      </c>
+      <c r="T69" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U69" s="19">
+        <f t="shared" ref="U69:U84" si="7">U68/5</f>
+        <v>8.8928020400553114E+17</v>
+      </c>
+      <c r="V69" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W69" s="13">
+        <v>0</v>
+      </c>
+      <c r="X69" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y69" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z69" s="69"/>
+      <c r="AA69" s="78"/>
+      <c r="AB69" s="78"/>
+    </row>
+    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A70" s="22">
+        <v>167</v>
+      </c>
+      <c r="B70" s="13">
+        <v>12</v>
+      </c>
+      <c r="C70" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D70" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E70" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F70" s="1">
+        <v>5</v>
+      </c>
+      <c r="G70" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H70" s="16">
+        <v>100</v>
+      </c>
+      <c r="I70" s="13">
+        <v>1</v>
+      </c>
+      <c r="J70" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K70" s="13">
+        <v>2</v>
+      </c>
+      <c r="L70" s="1">
+        <v>2</v>
+      </c>
+      <c r="M70" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N70" s="13">
+        <v>150</v>
+      </c>
+      <c r="O70" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P70" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q70" s="1">
+        <v>400</v>
+      </c>
+      <c r="R70" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S70" s="13">
+        <v>1</v>
+      </c>
+      <c r="T70" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U70" s="19">
+        <f t="shared" si="7"/>
+        <v>1.7785604080110624E+17</v>
+      </c>
+      <c r="V70" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W70" s="13">
+        <v>0</v>
+      </c>
+      <c r="X70" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y70" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z70" s="69"/>
+      <c r="AA70" s="78"/>
+      <c r="AB70" s="78"/>
+    </row>
+    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A71" s="61">
+        <v>168</v>
+      </c>
+      <c r="B71" s="13">
+        <v>12</v>
+      </c>
+      <c r="C71" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D71" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E71" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F71" s="1">
+        <v>5</v>
+      </c>
+      <c r="G71" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H71" s="16">
+        <v>100</v>
+      </c>
+      <c r="I71" s="13">
+        <v>1</v>
+      </c>
+      <c r="J71" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K71" s="13">
+        <v>2</v>
+      </c>
+      <c r="L71" s="1">
+        <v>2</v>
+      </c>
+      <c r="M71" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N71" s="13">
+        <v>150</v>
+      </c>
+      <c r="O71" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P71" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q71" s="1">
+        <v>400</v>
+      </c>
+      <c r="R71" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S71" s="13">
+        <v>1</v>
+      </c>
+      <c r="T71" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U71" s="19">
+        <f t="shared" si="7"/>
+        <v>3.5571208160221248E+16</v>
+      </c>
+      <c r="V71" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W71" s="13">
+        <v>0</v>
+      </c>
+      <c r="X71" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y71" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z71" s="69"/>
+      <c r="AA71" s="78"/>
+      <c r="AB71" s="78"/>
+    </row>
+    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A72" s="22">
+        <v>169</v>
+      </c>
+      <c r="B72" s="13">
+        <v>12</v>
+      </c>
+      <c r="C72" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D72" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E72" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F72" s="1">
+        <v>5</v>
+      </c>
+      <c r="G72" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H72" s="16">
+        <v>100</v>
+      </c>
+      <c r="I72" s="13">
+        <v>1</v>
+      </c>
+      <c r="J72" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K72" s="13">
+        <v>2</v>
+      </c>
+      <c r="L72" s="1">
+        <v>2</v>
+      </c>
+      <c r="M72" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N72" s="13">
+        <v>150</v>
+      </c>
+      <c r="O72" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P72" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q72" s="1">
+        <v>400</v>
+      </c>
+      <c r="R72" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S72" s="13">
+        <v>1</v>
+      </c>
+      <c r="T72" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U72" s="19">
+        <f t="shared" si="7"/>
+        <v>7114241632044250</v>
+      </c>
+      <c r="V72" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W72" s="13">
+        <v>0</v>
+      </c>
+      <c r="X72" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y72" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z72" s="69"/>
+      <c r="AA72" s="78"/>
+      <c r="AB72" s="78"/>
+    </row>
+    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A73" s="22">
+        <v>170</v>
+      </c>
+      <c r="B73" s="13">
+        <v>12</v>
+      </c>
+      <c r="C73" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D73" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E73" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F73" s="1">
+        <v>5</v>
+      </c>
+      <c r="G73" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H73" s="16">
+        <v>100</v>
+      </c>
+      <c r="I73" s="13">
+        <v>1</v>
+      </c>
+      <c r="J73" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K73" s="13">
+        <v>2</v>
+      </c>
+      <c r="L73" s="1">
+        <v>2</v>
+      </c>
+      <c r="M73" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N73" s="13">
+        <v>150</v>
+      </c>
+      <c r="O73" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P73" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q73" s="1">
+        <v>400</v>
+      </c>
+      <c r="R73" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S73" s="13">
+        <v>1</v>
+      </c>
+      <c r="T73" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U73" s="19">
+        <f t="shared" si="7"/>
+        <v>1422848326408850</v>
+      </c>
+      <c r="V73" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W73" s="13">
+        <v>0</v>
+      </c>
+      <c r="X73" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y73" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z73" s="69"/>
+      <c r="AA73" s="78"/>
+      <c r="AB73" s="78"/>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A74" s="22">
+        <v>171</v>
+      </c>
+      <c r="B74" s="13">
+        <v>12</v>
+      </c>
+      <c r="C74" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D74" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E74" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F74" s="1">
+        <v>5</v>
+      </c>
+      <c r="G74" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H74" s="16">
+        <v>100</v>
+      </c>
+      <c r="I74" s="13">
+        <v>1</v>
+      </c>
+      <c r="J74" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K74" s="13">
+        <v>2</v>
+      </c>
+      <c r="L74" s="1">
+        <v>2</v>
+      </c>
+      <c r="M74" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N74" s="13">
+        <v>150</v>
+      </c>
+      <c r="O74" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P74" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q74" s="1">
+        <v>400</v>
+      </c>
+      <c r="R74" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S74" s="13">
+        <v>1</v>
+      </c>
+      <c r="T74" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U74" s="19">
+        <f>U73/5</f>
+        <v>284569665281770</v>
+      </c>
+      <c r="V74" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W74" s="13">
+        <v>0</v>
+      </c>
+      <c r="X74" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y74" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z74" s="69"/>
+      <c r="AA74" s="78"/>
+      <c r="AB74" s="78"/>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A75" s="22">
+        <v>172</v>
+      </c>
+      <c r="B75" s="13">
+        <v>12</v>
+      </c>
+      <c r="C75" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D75" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E75" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F75" s="1">
+        <v>5</v>
+      </c>
+      <c r="G75" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H75" s="16">
+        <v>100</v>
+      </c>
+      <c r="I75" s="13">
+        <v>1</v>
+      </c>
+      <c r="J75" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K75" s="13">
+        <v>2</v>
+      </c>
+      <c r="L75" s="1">
+        <v>2</v>
+      </c>
+      <c r="M75" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N75" s="13">
+        <v>150</v>
+      </c>
+      <c r="O75" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P75" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q75" s="1">
+        <v>400</v>
+      </c>
+      <c r="R75" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S75" s="13">
+        <v>1</v>
+      </c>
+      <c r="T75" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U75" s="19">
+        <f t="shared" si="7"/>
+        <v>56913933056354</v>
+      </c>
+      <c r="V75" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W75" s="13">
+        <v>0</v>
+      </c>
+      <c r="X75" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y75" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z75" s="69"/>
+      <c r="AA75" s="78"/>
+      <c r="AB75" s="78"/>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A76" s="22">
+        <v>173</v>
+      </c>
+      <c r="B76" s="13">
+        <v>12</v>
+      </c>
+      <c r="C76" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D76" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E76" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F76" s="1">
+        <v>5</v>
+      </c>
+      <c r="G76" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H76" s="16">
+        <v>100</v>
+      </c>
+      <c r="I76" s="13">
+        <v>1</v>
+      </c>
+      <c r="J76" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K76" s="13">
+        <v>2</v>
+      </c>
+      <c r="L76" s="1">
+        <v>2</v>
+      </c>
+      <c r="M76" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N76" s="13">
+        <v>150</v>
+      </c>
+      <c r="O76" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P76" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q76" s="1">
+        <v>400</v>
+      </c>
+      <c r="R76" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S76" s="13">
+        <v>1</v>
+      </c>
+      <c r="T76" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U76" s="19">
+        <f>U75/5</f>
+        <v>11382786611270.801</v>
+      </c>
+      <c r="V76" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W76" s="13">
+        <v>0</v>
+      </c>
+      <c r="X76" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y76" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z76" s="69"/>
+      <c r="AA76" s="78"/>
+      <c r="AB76" s="78"/>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A77" s="22">
+        <v>174</v>
+      </c>
+      <c r="B77" s="13">
+        <v>12</v>
+      </c>
+      <c r="C77" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D77" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E77" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F77" s="1">
+        <v>5</v>
+      </c>
+      <c r="G77" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H77" s="16">
+        <v>100</v>
+      </c>
+      <c r="I77" s="13">
+        <v>1</v>
+      </c>
+      <c r="J77" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K77" s="13">
+        <v>2</v>
+      </c>
+      <c r="L77" s="1">
+        <v>2</v>
+      </c>
+      <c r="M77" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N77" s="13">
+        <v>150</v>
+      </c>
+      <c r="O77" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P77" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q77" s="1">
+        <v>400</v>
+      </c>
+      <c r="R77" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S77" s="13">
+        <v>1</v>
+      </c>
+      <c r="T77" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U77" s="19">
+        <f t="shared" si="7"/>
+        <v>2276557322254.1602</v>
+      </c>
+      <c r="V77" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W77" s="13">
+        <v>0</v>
+      </c>
+      <c r="X77" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y77" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z77" s="69"/>
+      <c r="AA77" s="78"/>
+      <c r="AB77" s="78"/>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A78" s="22">
+        <v>175</v>
+      </c>
+      <c r="B78" s="13">
+        <v>12</v>
+      </c>
+      <c r="C78" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D78" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E78" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F78" s="1">
+        <v>5</v>
+      </c>
+      <c r="G78" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H78" s="16">
+        <v>100</v>
+      </c>
+      <c r="I78" s="13">
+        <v>1</v>
+      </c>
+      <c r="J78" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K78" s="13">
+        <v>2</v>
+      </c>
+      <c r="L78" s="1">
+        <v>2</v>
+      </c>
+      <c r="M78" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N78" s="13">
+        <v>150</v>
+      </c>
+      <c r="O78" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P78" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q78" s="1">
+        <v>400</v>
+      </c>
+      <c r="R78" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S78" s="13">
+        <v>1</v>
+      </c>
+      <c r="T78" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U78" s="19">
+        <f t="shared" si="7"/>
+        <v>455311464450.83203</v>
+      </c>
+      <c r="V78" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W78" s="13">
+        <v>0</v>
+      </c>
+      <c r="X78" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y78" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z78" s="69"/>
+      <c r="AA78" s="78"/>
+      <c r="AB78" s="78"/>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A79" s="22">
+        <v>176</v>
+      </c>
+      <c r="B79" s="13">
+        <v>12</v>
+      </c>
+      <c r="C79" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D79" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E79" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F79" s="1">
+        <v>5</v>
+      </c>
+      <c r="G79" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H79" s="16">
+        <v>100</v>
+      </c>
+      <c r="I79" s="13">
+        <v>1</v>
+      </c>
+      <c r="J79" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K79" s="13">
+        <v>2</v>
+      </c>
+      <c r="L79" s="1">
+        <v>2</v>
+      </c>
+      <c r="M79" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N79" s="13">
+        <v>150</v>
+      </c>
+      <c r="O79" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P79" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q79" s="1">
+        <v>400</v>
+      </c>
+      <c r="R79" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S79" s="13">
+        <v>1</v>
+      </c>
+      <c r="T79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U79" s="19">
+        <f t="shared" si="7"/>
+        <v>91062292890.166412</v>
+      </c>
+      <c r="V79" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W79" s="13">
+        <v>0</v>
+      </c>
+      <c r="X79" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y79" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z79" s="69"/>
+      <c r="AA79" s="78"/>
+      <c r="AB79" s="78"/>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A80" s="22">
+        <v>177</v>
+      </c>
+      <c r="B80" s="13">
+        <v>12</v>
+      </c>
+      <c r="C80" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D80" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E80" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F80" s="1">
+        <v>5</v>
+      </c>
+      <c r="G80" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H80" s="16">
+        <v>100</v>
+      </c>
+      <c r="I80" s="13">
+        <v>1</v>
+      </c>
+      <c r="J80" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K80" s="13">
+        <v>2</v>
+      </c>
+      <c r="L80" s="1">
+        <v>2</v>
+      </c>
+      <c r="M80" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N80" s="13">
+        <v>150</v>
+      </c>
+      <c r="O80" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P80" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q80" s="1">
+        <v>400</v>
+      </c>
+      <c r="R80" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S80" s="13">
+        <v>1</v>
+      </c>
+      <c r="T80" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U80" s="19">
+        <f t="shared" si="7"/>
+        <v>18212458578.033283</v>
+      </c>
+      <c r="V80" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W80" s="13">
+        <v>0</v>
+      </c>
+      <c r="X80" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y80" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z80" s="69"/>
+      <c r="AA80" s="78"/>
+      <c r="AB80" s="78"/>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A81" s="22">
+        <v>178</v>
+      </c>
+      <c r="B81" s="13">
+        <v>12</v>
+      </c>
+      <c r="C81" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D81" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E81" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F81" s="1">
+        <v>5</v>
+      </c>
+      <c r="G81" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H81" s="16">
+        <v>100</v>
+      </c>
+      <c r="I81" s="13">
+        <v>1</v>
+      </c>
+      <c r="J81" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K81" s="13">
+        <v>2</v>
+      </c>
+      <c r="L81" s="1">
+        <v>2</v>
+      </c>
+      <c r="M81" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N81" s="13">
+        <v>150</v>
+      </c>
+      <c r="O81" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P81" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q81" s="1">
+        <v>400</v>
+      </c>
+      <c r="R81" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S81" s="13">
+        <v>1</v>
+      </c>
+      <c r="T81" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U81" s="19">
+        <f>U80/5</f>
+        <v>3642491715.6066566</v>
+      </c>
+      <c r="V81" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W81" s="13">
+        <v>0</v>
+      </c>
+      <c r="X81" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y81" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z81" s="69"/>
+      <c r="AA81" s="78"/>
+      <c r="AB81" s="78"/>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A82" s="22">
+        <v>179</v>
+      </c>
+      <c r="B82" s="13">
+        <v>12</v>
+      </c>
+      <c r="C82" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D82" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E82" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F82" s="1">
+        <v>5</v>
+      </c>
+      <c r="G82" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H82" s="16">
+        <v>100</v>
+      </c>
+      <c r="I82" s="13">
+        <v>1</v>
+      </c>
+      <c r="J82" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K82" s="13">
+        <v>2</v>
+      </c>
+      <c r="L82" s="1">
+        <v>2</v>
+      </c>
+      <c r="M82" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N82" s="13">
+        <v>150</v>
+      </c>
+      <c r="O82" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P82" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q82" s="1">
+        <v>400</v>
+      </c>
+      <c r="R82" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S82" s="13">
+        <v>1</v>
+      </c>
+      <c r="T82" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U82" s="19">
+        <f t="shared" si="7"/>
+        <v>728498343.12133133</v>
+      </c>
+      <c r="V82" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W82" s="13">
+        <v>0</v>
+      </c>
+      <c r="X82" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y82" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z82" s="69"/>
+      <c r="AA82" s="78"/>
+      <c r="AB82" s="78"/>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A83" s="22">
+        <v>180</v>
+      </c>
+      <c r="B83" s="13">
+        <v>12</v>
+      </c>
+      <c r="C83" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D83" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E83" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F83" s="1">
+        <v>5</v>
+      </c>
+      <c r="G83" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H83" s="16">
+        <v>100</v>
+      </c>
+      <c r="I83" s="13">
+        <v>1</v>
+      </c>
+      <c r="J83" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K83" s="13">
+        <v>2</v>
+      </c>
+      <c r="L83" s="1">
+        <v>2</v>
+      </c>
+      <c r="M83" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N83" s="13">
+        <v>150</v>
+      </c>
+      <c r="O83" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P83" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q83" s="1">
+        <v>400</v>
+      </c>
+      <c r="R83" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S83" s="13">
+        <v>1</v>
+      </c>
+      <c r="T83" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U83" s="19">
+        <f t="shared" si="7"/>
+        <v>145699668.62426627</v>
+      </c>
+      <c r="V83" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W83" s="13">
+        <v>0</v>
+      </c>
+      <c r="X83" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y83" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z83" s="69"/>
+      <c r="AA83" s="78"/>
+      <c r="AB83" s="78"/>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A84" s="22">
+        <v>181</v>
+      </c>
+      <c r="B84" s="13">
+        <v>12</v>
+      </c>
+      <c r="C84" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D84" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E84" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F84" s="1">
+        <v>5</v>
+      </c>
+      <c r="G84" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H84" s="16">
+        <v>100</v>
+      </c>
+      <c r="I84" s="13">
+        <v>1</v>
+      </c>
+      <c r="J84" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K84" s="13">
+        <v>2</v>
+      </c>
+      <c r="L84" s="1">
+        <v>2</v>
+      </c>
+      <c r="M84" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N84" s="13">
+        <v>150</v>
+      </c>
+      <c r="O84" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P84" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q84" s="1">
+        <v>400</v>
+      </c>
+      <c r="R84" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S84" s="13">
+        <v>1</v>
+      </c>
+      <c r="T84" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="U84" s="19">
+        <f t="shared" si="7"/>
+        <v>29139933.724853255</v>
+      </c>
+      <c r="V84" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W84" s="13">
+        <v>0</v>
+      </c>
+      <c r="X84" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y84" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z84" s="69"/>
+      <c r="AA84" s="78"/>
+      <c r="AB84" s="78"/>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A85" s="65">
+        <v>182</v>
+      </c>
+      <c r="B85" s="36">
+        <v>12</v>
+      </c>
+      <c r="C85" s="36">
+        <v>2000</v>
+      </c>
+      <c r="D85" s="55">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E85" s="55">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F85" s="54">
+        <v>5</v>
+      </c>
+      <c r="G85" s="55">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H85" s="55">
+        <v>100</v>
+      </c>
+      <c r="I85" s="36">
+        <v>1</v>
+      </c>
+      <c r="J85" s="56">
+        <v>1E-4</v>
+      </c>
+      <c r="K85" s="36">
+        <v>2</v>
+      </c>
+      <c r="L85" s="54">
+        <v>2</v>
+      </c>
+      <c r="M85" s="55">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N85" s="36">
+        <v>3000</v>
+      </c>
+      <c r="O85" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="P85" s="36">
+        <v>300</v>
+      </c>
+      <c r="Q85" s="54">
+        <v>400</v>
+      </c>
+      <c r="R85" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="S85" s="36">
+        <v>1</v>
+      </c>
+      <c r="T85" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="U85" s="55">
+        <v>81600000000000</v>
+      </c>
+      <c r="V85" s="36">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W85" s="36">
+        <v>0</v>
+      </c>
+      <c r="X85" s="36">
+        <v>1</v>
+      </c>
+      <c r="Y85" s="54">
+        <v>1</v>
+      </c>
+      <c r="Z85" s="66" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA85" s="67"/>
+      <c r="AB85" s="67"/>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>183</v>
+      </c>
+      <c r="B86" s="15">
+        <v>12</v>
+      </c>
+      <c r="C86" s="15">
+        <v>700</v>
+      </c>
+      <c r="D86" s="52">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E86" s="52">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F86" s="51">
+        <v>5</v>
+      </c>
+      <c r="G86" s="52">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H86" s="52">
+        <v>100</v>
+      </c>
+      <c r="I86" s="15">
+        <v>1</v>
+      </c>
+      <c r="J86" s="53">
+        <v>1E-4</v>
+      </c>
+      <c r="K86" s="15">
+        <v>2</v>
+      </c>
+      <c r="L86" s="51">
+        <v>2</v>
+      </c>
+      <c r="M86" s="52">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N86" s="15">
+        <v>150</v>
+      </c>
+      <c r="O86" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P86" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q86" s="51">
+        <v>400</v>
+      </c>
+      <c r="R86" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="S86" s="15">
+        <v>1</v>
+      </c>
+      <c r="T86" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="U86" s="52">
+        <v>81600000000000</v>
+      </c>
+      <c r="V86" s="15">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W86" s="15">
+        <v>0</v>
+      </c>
+      <c r="X86" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y86" s="51">
+        <v>1</v>
+      </c>
+      <c r="Z86" s="66" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA86" s="67"/>
+      <c r="AB86" s="67"/>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>184</v>
+      </c>
+      <c r="B87" s="15">
+        <v>12</v>
+      </c>
+      <c r="C87" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D87" s="52">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E87" s="52">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F87" s="51">
+        <v>5</v>
+      </c>
+      <c r="G87" s="52">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H87" s="52">
+        <v>100</v>
+      </c>
+      <c r="I87" s="15">
+        <v>1</v>
+      </c>
+      <c r="J87" s="53">
+        <v>1E-4</v>
+      </c>
+      <c r="K87" s="15">
+        <v>2</v>
+      </c>
+      <c r="L87" s="51">
+        <v>2</v>
+      </c>
+      <c r="M87" s="52">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N87" s="15">
+        <v>150</v>
+      </c>
+      <c r="O87" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P87" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q87" s="51">
+        <v>400</v>
+      </c>
+      <c r="R87" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="S87" s="15">
+        <v>1</v>
+      </c>
+      <c r="T87" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="U87" s="52">
+        <v>81600000000000</v>
+      </c>
+      <c r="V87" s="15">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W87" s="15">
+        <v>0</v>
+      </c>
+      <c r="X87" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y87" s="51">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="U1:W1"/>
+  <mergeCells count="25">
+    <mergeCell ref="Z8:AD8"/>
+    <mergeCell ref="Z28:AB28"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="Z6:AB6"/>
+    <mergeCell ref="Z7:AB7"/>
+    <mergeCell ref="Z5:AB5"/>
+    <mergeCell ref="Z4:AB4"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="M1:Q1"/>
     <mergeCell ref="R1:T1"/>
+    <mergeCell ref="Z86:AB86"/>
+    <mergeCell ref="Z58:AB58"/>
+    <mergeCell ref="Z51:AB57"/>
+    <mergeCell ref="Z10:AB27"/>
+    <mergeCell ref="Z29:AB46"/>
+    <mergeCell ref="Z50:AB50"/>
+    <mergeCell ref="Z48:AB48"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="Z49:AB49"/>
+    <mergeCell ref="Z85:AB85"/>
+    <mergeCell ref="Z67:AB84"/>
+    <mergeCell ref="Z59:AB66"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Simulations_IDS.xlsx
+++ b/Simulations_IDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documentos_Betran\DropletEvaporation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77B02EF-8920-4D54-A30C-C563ED8F318A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276B1709-D8CD-4381-8560-FBA38DF02C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{73239687-5BB6-4FA0-A3B4-8BE280184789}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="65">
   <si>
     <t>ID</t>
   </si>
@@ -584,6 +584,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -597,27 +618,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -936,7 +936,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC78505-487D-4D76-94E1-903AFBAADA28}">
-  <dimension ref="A1:AF87"/>
+  <dimension ref="A1:AF88"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" customWidth="1"/>
@@ -966,42 +966,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="B1" s="73" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="74" t="s">
+      <c r="B1" s="71" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="75" t="s">
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="76"/>
-      <c r="M1" s="74" t="s">
+      <c r="L1" s="69"/>
+      <c r="M1" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="76"/>
-      <c r="R1" s="74" t="s">
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="75"/>
-      <c r="T1" s="75"/>
-      <c r="U1" s="75" t="s">
+      <c r="S1" s="68"/>
+      <c r="T1" s="68"/>
+      <c r="U1" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="V1" s="75"/>
-      <c r="W1" s="75"/>
-      <c r="X1" s="75"/>
-      <c r="Y1" s="76"/>
+      <c r="V1" s="68"/>
+      <c r="W1" s="68"/>
+      <c r="X1" s="68"/>
+      <c r="Y1" s="69"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1224,11 +1224,11 @@
       <c r="Y4" s="1">
         <v>1</v>
       </c>
-      <c r="Z4" s="71" t="s">
+      <c r="Z4" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="AA4" s="77"/>
-      <c r="AB4" s="77"/>
+      <c r="AA4" s="70"/>
+      <c r="AB4" s="70"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="22">
@@ -1307,11 +1307,11 @@
       <c r="Y5" s="1">
         <v>1</v>
       </c>
-      <c r="Z5" s="71" t="s">
+      <c r="Z5" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="AA5" s="77"/>
-      <c r="AB5" s="77"/>
+      <c r="AA5" s="70"/>
+      <c r="AB5" s="70"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="22">
@@ -1390,11 +1390,11 @@
       <c r="Y6" s="1">
         <v>1</v>
       </c>
-      <c r="Z6" s="71" t="s">
+      <c r="Z6" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="AA6" s="77"/>
-      <c r="AB6" s="77"/>
+      <c r="AA6" s="70"/>
+      <c r="AB6" s="70"/>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="22">
@@ -1473,11 +1473,11 @@
       <c r="Y7" s="1">
         <v>1</v>
       </c>
-      <c r="Z7" s="71" t="s">
+      <c r="Z7" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="AA7" s="77"/>
-      <c r="AB7" s="77"/>
+      <c r="AA7" s="70"/>
+      <c r="AB7" s="70"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="22">
@@ -1556,13 +1556,13 @@
       <c r="Y8" s="39">
         <v>1</v>
       </c>
-      <c r="Z8" s="71" t="s">
+      <c r="Z8" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="AA8" s="72"/>
-      <c r="AB8" s="72"/>
-      <c r="AC8" s="72"/>
-      <c r="AD8" s="72"/>
+      <c r="AA8" s="67"/>
+      <c r="AB8" s="67"/>
+      <c r="AC8" s="67"/>
+      <c r="AD8" s="67"/>
       <c r="AE8" s="20"/>
       <c r="AF8" s="20"/>
     </row>
@@ -1643,11 +1643,11 @@
       <c r="Y9" s="1">
         <v>1</v>
       </c>
-      <c r="Z9" s="71" t="s">
+      <c r="Z9" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="AA9" s="72"/>
-      <c r="AB9" s="72"/>
+      <c r="AA9" s="67"/>
+      <c r="AB9" s="67"/>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="47">
@@ -1726,11 +1726,11 @@
       <c r="Y10" s="44">
         <v>1</v>
       </c>
-      <c r="Z10" s="69" t="s">
+      <c r="Z10" s="76" t="s">
         <v>53</v>
       </c>
-      <c r="AA10" s="70"/>
-      <c r="AB10" s="70"/>
+      <c r="AA10" s="77"/>
+      <c r="AB10" s="77"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="22">
@@ -1811,9 +1811,9 @@
       <c r="Y11" s="1">
         <v>1</v>
       </c>
-      <c r="Z11" s="69"/>
-      <c r="AA11" s="70"/>
-      <c r="AB11" s="70"/>
+      <c r="Z11" s="76"/>
+      <c r="AA11" s="77"/>
+      <c r="AB11" s="77"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="22">
@@ -1893,9 +1893,9 @@
       <c r="Y12" s="1">
         <v>1</v>
       </c>
-      <c r="Z12" s="69"/>
-      <c r="AA12" s="70"/>
-      <c r="AB12" s="70"/>
+      <c r="Z12" s="76"/>
+      <c r="AA12" s="77"/>
+      <c r="AB12" s="77"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1975,9 +1975,9 @@
       <c r="Y13" s="1">
         <v>1</v>
       </c>
-      <c r="Z13" s="69"/>
-      <c r="AA13" s="70"/>
-      <c r="AB13" s="70"/>
+      <c r="Z13" s="76"/>
+      <c r="AA13" s="77"/>
+      <c r="AB13" s="77"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="23">
@@ -2057,9 +2057,9 @@
       <c r="Y14" s="1">
         <v>1</v>
       </c>
-      <c r="Z14" s="69"/>
-      <c r="AA14" s="70"/>
-      <c r="AB14" s="70"/>
+      <c r="Z14" s="76"/>
+      <c r="AA14" s="77"/>
+      <c r="AB14" s="77"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -2139,9 +2139,9 @@
       <c r="Y15" s="1">
         <v>1</v>
       </c>
-      <c r="Z15" s="69"/>
-      <c r="AA15" s="70"/>
-      <c r="AB15" s="70"/>
+      <c r="Z15" s="76"/>
+      <c r="AA15" s="77"/>
+      <c r="AB15" s="77"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="23">
@@ -2221,9 +2221,9 @@
       <c r="Y16" s="1">
         <v>1</v>
       </c>
-      <c r="Z16" s="69"/>
-      <c r="AA16" s="70"/>
-      <c r="AB16" s="70"/>
+      <c r="Z16" s="76"/>
+      <c r="AA16" s="77"/>
+      <c r="AB16" s="77"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
@@ -2303,9 +2303,9 @@
       <c r="Y17" s="1">
         <v>1</v>
       </c>
-      <c r="Z17" s="69"/>
-      <c r="AA17" s="70"/>
-      <c r="AB17" s="70"/>
+      <c r="Z17" s="76"/>
+      <c r="AA17" s="77"/>
+      <c r="AB17" s="77"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
@@ -2385,9 +2385,9 @@
       <c r="Y18" s="1">
         <v>1</v>
       </c>
-      <c r="Z18" s="69"/>
-      <c r="AA18" s="70"/>
-      <c r="AB18" s="70"/>
+      <c r="Z18" s="76"/>
+      <c r="AA18" s="77"/>
+      <c r="AB18" s="77"/>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
@@ -2467,9 +2467,9 @@
       <c r="Y19" s="1">
         <v>1</v>
       </c>
-      <c r="Z19" s="69"/>
-      <c r="AA19" s="70"/>
-      <c r="AB19" s="70"/>
+      <c r="Z19" s="76"/>
+      <c r="AA19" s="77"/>
+      <c r="AB19" s="77"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
@@ -2549,9 +2549,9 @@
       <c r="Y20" s="1">
         <v>1</v>
       </c>
-      <c r="Z20" s="69"/>
-      <c r="AA20" s="70"/>
-      <c r="AB20" s="70"/>
+      <c r="Z20" s="76"/>
+      <c r="AA20" s="77"/>
+      <c r="AB20" s="77"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
@@ -2631,9 +2631,9 @@
       <c r="Y21" s="1">
         <v>1</v>
       </c>
-      <c r="Z21" s="69"/>
-      <c r="AA21" s="70"/>
-      <c r="AB21" s="70"/>
+      <c r="Z21" s="76"/>
+      <c r="AA21" s="77"/>
+      <c r="AB21" s="77"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
@@ -2713,9 +2713,9 @@
       <c r="Y22" s="1">
         <v>1</v>
       </c>
-      <c r="Z22" s="69"/>
-      <c r="AA22" s="70"/>
-      <c r="AB22" s="70"/>
+      <c r="Z22" s="76"/>
+      <c r="AA22" s="77"/>
+      <c r="AB22" s="77"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
@@ -2795,9 +2795,9 @@
       <c r="Y23" s="1">
         <v>1</v>
       </c>
-      <c r="Z23" s="69"/>
-      <c r="AA23" s="70"/>
-      <c r="AB23" s="70"/>
+      <c r="Z23" s="76"/>
+      <c r="AA23" s="77"/>
+      <c r="AB23" s="77"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -2877,9 +2877,9 @@
       <c r="Y24" s="1">
         <v>1</v>
       </c>
-      <c r="Z24" s="69"/>
-      <c r="AA24" s="70"/>
-      <c r="AB24" s="70"/>
+      <c r="Z24" s="76"/>
+      <c r="AA24" s="77"/>
+      <c r="AB24" s="77"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
@@ -2959,9 +2959,9 @@
       <c r="Y25" s="1">
         <v>1</v>
       </c>
-      <c r="Z25" s="69"/>
-      <c r="AA25" s="70"/>
-      <c r="AB25" s="70"/>
+      <c r="Z25" s="76"/>
+      <c r="AA25" s="77"/>
+      <c r="AB25" s="77"/>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
@@ -3041,9 +3041,9 @@
       <c r="Y26" s="1">
         <v>1</v>
       </c>
-      <c r="Z26" s="69"/>
-      <c r="AA26" s="70"/>
-      <c r="AB26" s="70"/>
+      <c r="Z26" s="76"/>
+      <c r="AA26" s="77"/>
+      <c r="AB26" s="77"/>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="22">
@@ -3123,9 +3123,9 @@
       <c r="Y27" s="28">
         <v>1</v>
       </c>
-      <c r="Z27" s="69"/>
-      <c r="AA27" s="70"/>
-      <c r="AB27" s="70"/>
+      <c r="Z27" s="76"/>
+      <c r="AA27" s="77"/>
+      <c r="AB27" s="77"/>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="34">
@@ -3204,11 +3204,11 @@
       <c r="Y28" s="34">
         <v>1</v>
       </c>
-      <c r="Z28" s="71" t="s">
+      <c r="Z28" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="AA28" s="72"/>
-      <c r="AB28" s="72"/>
+      <c r="AA28" s="67"/>
+      <c r="AB28" s="67"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="22">
@@ -3288,11 +3288,11 @@
       <c r="Y29" s="1">
         <v>1</v>
       </c>
-      <c r="Z29" s="69" t="s">
+      <c r="Z29" s="76" t="s">
         <v>53</v>
       </c>
-      <c r="AA29" s="70"/>
-      <c r="AB29" s="70"/>
+      <c r="AA29" s="77"/>
+      <c r="AB29" s="77"/>
     </row>
     <row r="30" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="22">
@@ -3372,9 +3372,9 @@
       <c r="Y30" s="1">
         <v>1</v>
       </c>
-      <c r="Z30" s="69"/>
-      <c r="AA30" s="70"/>
-      <c r="AB30" s="70"/>
+      <c r="Z30" s="76"/>
+      <c r="AA30" s="77"/>
+      <c r="AB30" s="77"/>
     </row>
     <row r="31" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="23">
@@ -3454,9 +3454,9 @@
       <c r="Y31" s="1">
         <v>1</v>
       </c>
-      <c r="Z31" s="69"/>
-      <c r="AA31" s="70"/>
-      <c r="AB31" s="70"/>
+      <c r="Z31" s="76"/>
+      <c r="AA31" s="77"/>
+      <c r="AB31" s="77"/>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="23">
@@ -3536,9 +3536,9 @@
       <c r="Y32" s="1">
         <v>1</v>
       </c>
-      <c r="Z32" s="69"/>
-      <c r="AA32" s="70"/>
-      <c r="AB32" s="70"/>
+      <c r="Z32" s="76"/>
+      <c r="AA32" s="77"/>
+      <c r="AB32" s="77"/>
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A33" s="22">
@@ -3618,9 +3618,9 @@
       <c r="Y33" s="1">
         <v>1</v>
       </c>
-      <c r="Z33" s="69"/>
-      <c r="AA33" s="70"/>
-      <c r="AB33" s="70"/>
+      <c r="Z33" s="76"/>
+      <c r="AA33" s="77"/>
+      <c r="AB33" s="77"/>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34" s="22">
@@ -3700,9 +3700,9 @@
       <c r="Y34" s="1">
         <v>1</v>
       </c>
-      <c r="Z34" s="69"/>
-      <c r="AA34" s="70"/>
-      <c r="AB34" s="70"/>
+      <c r="Z34" s="76"/>
+      <c r="AA34" s="77"/>
+      <c r="AB34" s="77"/>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A35" s="22">
@@ -3782,9 +3782,9 @@
       <c r="Y35" s="1">
         <v>1</v>
       </c>
-      <c r="Z35" s="69"/>
-      <c r="AA35" s="70"/>
-      <c r="AB35" s="70"/>
+      <c r="Z35" s="76"/>
+      <c r="AA35" s="77"/>
+      <c r="AB35" s="77"/>
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A36" s="23">
@@ -3864,9 +3864,9 @@
       <c r="Y36" s="1">
         <v>1</v>
       </c>
-      <c r="Z36" s="69"/>
-      <c r="AA36" s="70"/>
-      <c r="AB36" s="70"/>
+      <c r="Z36" s="76"/>
+      <c r="AA36" s="77"/>
+      <c r="AB36" s="77"/>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A37" s="23">
@@ -3946,9 +3946,9 @@
       <c r="Y37" s="1">
         <v>1</v>
       </c>
-      <c r="Z37" s="69"/>
-      <c r="AA37" s="70"/>
-      <c r="AB37" s="70"/>
+      <c r="Z37" s="76"/>
+      <c r="AA37" s="77"/>
+      <c r="AB37" s="77"/>
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A38" s="22">
@@ -4028,9 +4028,9 @@
       <c r="Y38" s="1">
         <v>1</v>
       </c>
-      <c r="Z38" s="69"/>
-      <c r="AA38" s="70"/>
-      <c r="AB38" s="70"/>
+      <c r="Z38" s="76"/>
+      <c r="AA38" s="77"/>
+      <c r="AB38" s="77"/>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A39" s="23">
@@ -4110,9 +4110,9 @@
       <c r="Y39" s="1">
         <v>1</v>
       </c>
-      <c r="Z39" s="69"/>
-      <c r="AA39" s="70"/>
-      <c r="AB39" s="70"/>
+      <c r="Z39" s="76"/>
+      <c r="AA39" s="77"/>
+      <c r="AB39" s="77"/>
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A40" s="62">
@@ -4192,9 +4192,9 @@
       <c r="Y40" s="1">
         <v>1</v>
       </c>
-      <c r="Z40" s="69"/>
-      <c r="AA40" s="70"/>
-      <c r="AB40" s="70"/>
+      <c r="Z40" s="76"/>
+      <c r="AA40" s="77"/>
+      <c r="AB40" s="77"/>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A41" s="62">
@@ -4274,9 +4274,9 @@
       <c r="Y41" s="1">
         <v>1</v>
       </c>
-      <c r="Z41" s="69"/>
-      <c r="AA41" s="70"/>
-      <c r="AB41" s="70"/>
+      <c r="Z41" s="76"/>
+      <c r="AA41" s="77"/>
+      <c r="AB41" s="77"/>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A42" s="62">
@@ -4356,9 +4356,9 @@
       <c r="Y42" s="1">
         <v>1</v>
       </c>
-      <c r="Z42" s="69"/>
-      <c r="AA42" s="70"/>
-      <c r="AB42" s="70"/>
+      <c r="Z42" s="76"/>
+      <c r="AA42" s="77"/>
+      <c r="AB42" s="77"/>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A43" s="62">
@@ -4438,9 +4438,9 @@
       <c r="Y43" s="1">
         <v>1</v>
       </c>
-      <c r="Z43" s="69"/>
-      <c r="AA43" s="70"/>
-      <c r="AB43" s="70"/>
+      <c r="Z43" s="76"/>
+      <c r="AA43" s="77"/>
+      <c r="AB43" s="77"/>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A44" s="62">
@@ -4520,9 +4520,9 @@
       <c r="Y44" s="1">
         <v>1</v>
       </c>
-      <c r="Z44" s="69"/>
-      <c r="AA44" s="70"/>
-      <c r="AB44" s="70"/>
+      <c r="Z44" s="76"/>
+      <c r="AA44" s="77"/>
+      <c r="AB44" s="77"/>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A45" s="61">
@@ -4602,9 +4602,9 @@
       <c r="Y45" s="1">
         <v>1</v>
       </c>
-      <c r="Z45" s="69"/>
-      <c r="AA45" s="70"/>
-      <c r="AB45" s="70"/>
+      <c r="Z45" s="76"/>
+      <c r="AA45" s="77"/>
+      <c r="AB45" s="77"/>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A46" s="61">
@@ -4684,9 +4684,9 @@
       <c r="Y46" s="1">
         <v>1</v>
       </c>
-      <c r="Z46" s="69"/>
-      <c r="AA46" s="70"/>
-      <c r="AB46" s="70"/>
+      <c r="Z46" s="76"/>
+      <c r="AA46" s="77"/>
+      <c r="AB46" s="77"/>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A47" s="41">
@@ -4765,11 +4765,11 @@
       <c r="Y47" s="44">
         <v>1</v>
       </c>
-      <c r="Z47" s="71" t="s">
+      <c r="Z47" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="AA47" s="72"/>
-      <c r="AB47" s="72"/>
+      <c r="AA47" s="67"/>
+      <c r="AB47" s="67"/>
       <c r="AC47" s="20"/>
     </row>
     <row r="48" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4850,11 +4850,11 @@
       <c r="Y48" s="44">
         <v>1</v>
       </c>
-      <c r="Z48" s="66" t="s">
+      <c r="Z48" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="AA48" s="68"/>
-      <c r="AB48" s="68"/>
+      <c r="AA48" s="75"/>
+      <c r="AB48" s="75"/>
       <c r="AC48" s="24"/>
     </row>
     <row r="49" spans="1:28" x14ac:dyDescent="0.25">
@@ -4934,11 +4934,11 @@
       <c r="Y49" s="44">
         <v>1</v>
       </c>
-      <c r="Z49" s="71" t="s">
+      <c r="Z49" s="66" t="s">
         <v>58</v>
       </c>
-      <c r="AA49" s="72"/>
-      <c r="AB49" s="72"/>
+      <c r="AA49" s="67"/>
+      <c r="AB49" s="67"/>
     </row>
     <row r="50" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="41">
@@ -5016,11 +5016,11 @@
       <c r="Y50" s="41">
         <v>1</v>
       </c>
-      <c r="Z50" s="71" t="s">
+      <c r="Z50" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="AA50" s="72"/>
-      <c r="AB50" s="72"/>
+      <c r="AA50" s="67"/>
+      <c r="AB50" s="67"/>
     </row>
     <row r="51" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" s="44">
@@ -5100,11 +5100,11 @@
       <c r="Y51" s="44">
         <v>1</v>
       </c>
-      <c r="Z51" s="69" t="s">
+      <c r="Z51" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="AA51" s="70"/>
-      <c r="AB51" s="70"/>
+      <c r="AA51" s="77"/>
+      <c r="AB51" s="77"/>
     </row>
     <row r="52" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
@@ -5184,9 +5184,9 @@
       <c r="Y52" s="1">
         <v>1</v>
       </c>
-      <c r="Z52" s="69"/>
-      <c r="AA52" s="70"/>
-      <c r="AB52" s="70"/>
+      <c r="Z52" s="76"/>
+      <c r="AA52" s="77"/>
+      <c r="AB52" s="77"/>
     </row>
     <row r="53" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
@@ -5266,9 +5266,9 @@
       <c r="Y53" s="1">
         <v>1</v>
       </c>
-      <c r="Z53" s="69"/>
-      <c r="AA53" s="70"/>
-      <c r="AB53" s="70"/>
+      <c r="Z53" s="76"/>
+      <c r="AA53" s="77"/>
+      <c r="AB53" s="77"/>
     </row>
     <row r="54" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
@@ -5348,9 +5348,9 @@
       <c r="Y54" s="1">
         <v>1</v>
       </c>
-      <c r="Z54" s="69"/>
-      <c r="AA54" s="70"/>
-      <c r="AB54" s="70"/>
+      <c r="Z54" s="76"/>
+      <c r="AA54" s="77"/>
+      <c r="AB54" s="77"/>
     </row>
     <row r="55" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55" s="61">
@@ -5430,9 +5430,9 @@
       <c r="Y55" s="1">
         <v>1</v>
       </c>
-      <c r="Z55" s="69"/>
-      <c r="AA55" s="70"/>
-      <c r="AB55" s="70"/>
+      <c r="Z55" s="76"/>
+      <c r="AA55" s="77"/>
+      <c r="AB55" s="77"/>
     </row>
     <row r="56" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A56" s="61">
@@ -5512,9 +5512,9 @@
       <c r="Y56" s="1">
         <v>1</v>
       </c>
-      <c r="Z56" s="69"/>
-      <c r="AA56" s="70"/>
-      <c r="AB56" s="70"/>
+      <c r="Z56" s="76"/>
+      <c r="AA56" s="77"/>
+      <c r="AB56" s="77"/>
     </row>
     <row r="57" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A57" s="63">
@@ -5594,9 +5594,9 @@
       <c r="Y57" s="28">
         <v>1</v>
       </c>
-      <c r="Z57" s="69"/>
-      <c r="AA57" s="70"/>
-      <c r="AB57" s="70"/>
+      <c r="Z57" s="76"/>
+      <c r="AA57" s="77"/>
+      <c r="AB57" s="77"/>
     </row>
     <row r="58" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A58" s="57">
@@ -5675,11 +5675,11 @@
       <c r="Y58" s="54">
         <v>1</v>
       </c>
-      <c r="Z58" s="66" t="s">
+      <c r="Z58" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="AA58" s="68"/>
-      <c r="AB58" s="68"/>
+      <c r="AA58" s="75"/>
+      <c r="AB58" s="75"/>
     </row>
     <row r="59" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A59" s="51">
@@ -5758,11 +5758,11 @@
       <c r="Y59" s="51">
         <v>1</v>
       </c>
-      <c r="Z59" s="69" t="s">
+      <c r="Z59" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="AA59" s="70"/>
-      <c r="AB59" s="70"/>
+      <c r="AA59" s="77"/>
+      <c r="AB59" s="77"/>
     </row>
     <row r="60" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A60" s="51">
@@ -5841,9 +5841,9 @@
       <c r="Y60" s="51">
         <v>1</v>
       </c>
-      <c r="Z60" s="69"/>
-      <c r="AA60" s="70"/>
-      <c r="AB60" s="70"/>
+      <c r="Z60" s="76"/>
+      <c r="AA60" s="77"/>
+      <c r="AB60" s="77"/>
     </row>
     <row r="61" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
@@ -5922,9 +5922,9 @@
       <c r="Y61" s="51">
         <v>1</v>
       </c>
-      <c r="Z61" s="69"/>
-      <c r="AA61" s="70"/>
-      <c r="AB61" s="70"/>
+      <c r="Z61" s="76"/>
+      <c r="AA61" s="77"/>
+      <c r="AB61" s="77"/>
     </row>
     <row r="62" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A62" s="51">
@@ -6003,9 +6003,9 @@
       <c r="Y62" s="51">
         <v>1</v>
       </c>
-      <c r="Z62" s="69"/>
-      <c r="AA62" s="70"/>
-      <c r="AB62" s="70"/>
+      <c r="Z62" s="76"/>
+      <c r="AA62" s="77"/>
+      <c r="AB62" s="77"/>
     </row>
     <row r="63" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
@@ -6084,9 +6084,9 @@
       <c r="Y63" s="51">
         <v>1</v>
       </c>
-      <c r="Z63" s="69"/>
-      <c r="AA63" s="70"/>
-      <c r="AB63" s="70"/>
+      <c r="Z63" s="76"/>
+      <c r="AA63" s="77"/>
+      <c r="AB63" s="77"/>
     </row>
     <row r="64" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A64" s="51">
@@ -6165,9 +6165,9 @@
       <c r="Y64" s="51">
         <v>1</v>
       </c>
-      <c r="Z64" s="69"/>
-      <c r="AA64" s="70"/>
-      <c r="AB64" s="70"/>
+      <c r="Z64" s="76"/>
+      <c r="AA64" s="77"/>
+      <c r="AB64" s="77"/>
     </row>
     <row r="65" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
@@ -6246,9 +6246,9 @@
       <c r="Y65" s="51">
         <v>1</v>
       </c>
-      <c r="Z65" s="69"/>
-      <c r="AA65" s="70"/>
-      <c r="AB65" s="70"/>
+      <c r="Z65" s="76"/>
+      <c r="AA65" s="77"/>
+      <c r="AB65" s="77"/>
     </row>
     <row r="66" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A66" s="58">
@@ -6327,9 +6327,9 @@
       <c r="Y66" s="58">
         <v>1</v>
       </c>
-      <c r="Z66" s="69"/>
-      <c r="AA66" s="70"/>
-      <c r="AB66" s="70"/>
+      <c r="Z66" s="76"/>
+      <c r="AA66" s="77"/>
+      <c r="AB66" s="77"/>
     </row>
     <row r="67" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A67" s="47">
@@ -6397,7 +6397,7 @@
         <v>2.2232005100138279E+19</v>
       </c>
       <c r="V67" s="13">
-        <f t="shared" ref="V67:V87" si="6">30*4184</f>
+        <f t="shared" ref="V67:V88" si="6">30*4184</f>
         <v>125520</v>
       </c>
       <c r="W67" s="42">
@@ -6409,7 +6409,7 @@
       <c r="Y67" s="44">
         <v>1</v>
       </c>
-      <c r="Z67" s="69" t="s">
+      <c r="Z67" s="76" t="s">
         <v>63</v>
       </c>
       <c r="AA67" s="78"/>
@@ -6493,7 +6493,7 @@
       <c r="Y68" s="1">
         <v>1</v>
       </c>
-      <c r="Z68" s="69"/>
+      <c r="Z68" s="76"/>
       <c r="AA68" s="78"/>
       <c r="AB68" s="78"/>
     </row>
@@ -6575,7 +6575,7 @@
       <c r="Y69" s="1">
         <v>1</v>
       </c>
-      <c r="Z69" s="69"/>
+      <c r="Z69" s="76"/>
       <c r="AA69" s="78"/>
       <c r="AB69" s="78"/>
     </row>
@@ -6657,7 +6657,7 @@
       <c r="Y70" s="1">
         <v>1</v>
       </c>
-      <c r="Z70" s="69"/>
+      <c r="Z70" s="76"/>
       <c r="AA70" s="78"/>
       <c r="AB70" s="78"/>
     </row>
@@ -6739,7 +6739,7 @@
       <c r="Y71" s="1">
         <v>1</v>
       </c>
-      <c r="Z71" s="69"/>
+      <c r="Z71" s="76"/>
       <c r="AA71" s="78"/>
       <c r="AB71" s="78"/>
     </row>
@@ -6821,7 +6821,7 @@
       <c r="Y72" s="1">
         <v>1</v>
       </c>
-      <c r="Z72" s="69"/>
+      <c r="Z72" s="76"/>
       <c r="AA72" s="78"/>
       <c r="AB72" s="78"/>
     </row>
@@ -6903,7 +6903,7 @@
       <c r="Y73" s="1">
         <v>1</v>
       </c>
-      <c r="Z73" s="69"/>
+      <c r="Z73" s="76"/>
       <c r="AA73" s="78"/>
       <c r="AB73" s="78"/>
     </row>
@@ -6985,7 +6985,7 @@
       <c r="Y74" s="1">
         <v>1</v>
       </c>
-      <c r="Z74" s="69"/>
+      <c r="Z74" s="76"/>
       <c r="AA74" s="78"/>
       <c r="AB74" s="78"/>
     </row>
@@ -7067,7 +7067,7 @@
       <c r="Y75" s="1">
         <v>1</v>
       </c>
-      <c r="Z75" s="69"/>
+      <c r="Z75" s="76"/>
       <c r="AA75" s="78"/>
       <c r="AB75" s="78"/>
     </row>
@@ -7149,7 +7149,7 @@
       <c r="Y76" s="1">
         <v>1</v>
       </c>
-      <c r="Z76" s="69"/>
+      <c r="Z76" s="76"/>
       <c r="AA76" s="78"/>
       <c r="AB76" s="78"/>
     </row>
@@ -7231,7 +7231,7 @@
       <c r="Y77" s="1">
         <v>1</v>
       </c>
-      <c r="Z77" s="69"/>
+      <c r="Z77" s="76"/>
       <c r="AA77" s="78"/>
       <c r="AB77" s="78"/>
     </row>
@@ -7313,7 +7313,7 @@
       <c r="Y78" s="1">
         <v>1</v>
       </c>
-      <c r="Z78" s="69"/>
+      <c r="Z78" s="76"/>
       <c r="AA78" s="78"/>
       <c r="AB78" s="78"/>
     </row>
@@ -7395,7 +7395,7 @@
       <c r="Y79" s="1">
         <v>1</v>
       </c>
-      <c r="Z79" s="69"/>
+      <c r="Z79" s="76"/>
       <c r="AA79" s="78"/>
       <c r="AB79" s="78"/>
     </row>
@@ -7477,7 +7477,7 @@
       <c r="Y80" s="1">
         <v>1</v>
       </c>
-      <c r="Z80" s="69"/>
+      <c r="Z80" s="76"/>
       <c r="AA80" s="78"/>
       <c r="AB80" s="78"/>
     </row>
@@ -7559,7 +7559,7 @@
       <c r="Y81" s="1">
         <v>1</v>
       </c>
-      <c r="Z81" s="69"/>
+      <c r="Z81" s="76"/>
       <c r="AA81" s="78"/>
       <c r="AB81" s="78"/>
     </row>
@@ -7641,7 +7641,7 @@
       <c r="Y82" s="1">
         <v>1</v>
       </c>
-      <c r="Z82" s="69"/>
+      <c r="Z82" s="76"/>
       <c r="AA82" s="78"/>
       <c r="AB82" s="78"/>
     </row>
@@ -7723,7 +7723,7 @@
       <c r="Y83" s="1">
         <v>1</v>
       </c>
-      <c r="Z83" s="69"/>
+      <c r="Z83" s="76"/>
       <c r="AA83" s="78"/>
       <c r="AB83" s="78"/>
     </row>
@@ -7805,7 +7805,7 @@
       <c r="Y84" s="1">
         <v>1</v>
       </c>
-      <c r="Z84" s="69"/>
+      <c r="Z84" s="76"/>
       <c r="AA84" s="78"/>
       <c r="AB84" s="78"/>
     </row>
@@ -7886,11 +7886,11 @@
       <c r="Y85" s="54">
         <v>1</v>
       </c>
-      <c r="Z85" s="66" t="s">
+      <c r="Z85" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="AA85" s="67"/>
-      <c r="AB85" s="67"/>
+      <c r="AA85" s="74"/>
+      <c r="AB85" s="74"/>
     </row>
     <row r="86" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
@@ -7969,11 +7969,11 @@
       <c r="Y86" s="51">
         <v>1</v>
       </c>
-      <c r="Z86" s="66" t="s">
+      <c r="Z86" s="73" t="s">
         <v>64</v>
       </c>
-      <c r="AA86" s="67"/>
-      <c r="AB86" s="67"/>
+      <c r="AA86" s="74"/>
+      <c r="AB86" s="74"/>
     </row>
     <row r="87" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
@@ -8053,21 +8053,86 @@
         <v>1</v>
       </c>
     </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>185</v>
+      </c>
+      <c r="B88" s="15">
+        <v>12</v>
+      </c>
+      <c r="C88" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D88" s="52">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E88" s="52">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F88" s="51">
+        <v>5</v>
+      </c>
+      <c r="G88" s="52">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H88" s="52">
+        <v>100</v>
+      </c>
+      <c r="I88" s="15">
+        <v>1</v>
+      </c>
+      <c r="J88" s="53">
+        <v>1E-4</v>
+      </c>
+      <c r="K88" s="15">
+        <v>2</v>
+      </c>
+      <c r="L88" s="51">
+        <v>2</v>
+      </c>
+      <c r="M88" s="52">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N88" s="15">
+        <v>150</v>
+      </c>
+      <c r="O88" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P88" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q88" s="51">
+        <v>2000</v>
+      </c>
+      <c r="R88" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="S88" s="15">
+        <v>1</v>
+      </c>
+      <c r="T88" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="U88" s="52">
+        <v>81600000000000</v>
+      </c>
+      <c r="V88" s="15">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W88" s="15">
+        <v>0</v>
+      </c>
+      <c r="X88" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y88" s="51">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="Z8:AD8"/>
-    <mergeCell ref="Z28:AB28"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="U1:Y1"/>
-    <mergeCell ref="Z6:AB6"/>
-    <mergeCell ref="Z7:AB7"/>
-    <mergeCell ref="Z5:AB5"/>
-    <mergeCell ref="Z4:AB4"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="R1:T1"/>
     <mergeCell ref="Z86:AB86"/>
     <mergeCell ref="Z58:AB58"/>
     <mergeCell ref="Z51:AB57"/>
@@ -8080,6 +8145,19 @@
     <mergeCell ref="Z85:AB85"/>
     <mergeCell ref="Z67:AB84"/>
     <mergeCell ref="Z59:AB66"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="Z8:AD8"/>
+    <mergeCell ref="Z28:AB28"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="Z6:AB6"/>
+    <mergeCell ref="Z7:AB7"/>
+    <mergeCell ref="Z5:AB5"/>
+    <mergeCell ref="Z4:AB4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Simulations_IDS.xlsx
+++ b/Simulations_IDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documentos_Betran\DropletEvaporation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276B1709-D8CD-4381-8560-FBA38DF02C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E800F29-41CD-422B-816C-36B8A6D3B663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{73239687-5BB6-4FA0-A3B4-8BE280184789}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="69">
   <si>
     <t>ID</t>
   </si>
@@ -49,9 +49,6 @@
   </si>
   <si>
     <t>p</t>
-  </si>
-  <si>
-    <t>Fuel Names</t>
   </si>
   <si>
     <t>Spatial Discretization</t>
@@ -233,6 +230,21 @@
   <si>
     <t>No picos en CI</t>
   </si>
+  <si>
+    <t>PreMix</t>
+  </si>
+  <si>
+    <t>CI = A. Millán</t>
+  </si>
+  <si>
+    <t>CPreMix</t>
+  </si>
+  <si>
+    <t>Names</t>
+  </si>
+  <si>
+    <t>Fuel</t>
+  </si>
 </sst>
 </file>
 
@@ -253,7 +265,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -293,6 +305,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -514,7 +532,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -539,9 +557,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -582,20 +597,10 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -604,23 +609,42 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -936,7 +960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC78505-487D-4D76-94E1-903AFBAADA28}">
-  <dimension ref="A1:AF88"/>
+  <dimension ref="A1:AF93"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" customWidth="1"/>
@@ -955,9 +979,9 @@
     <col min="15" max="15" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.85546875" customWidth="1"/>
+    <col min="19" max="19" width="8.5703125" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" customWidth="1"/>
     <col min="21" max="21" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="12.5703125" style="13" bestFit="1" customWidth="1"/>
@@ -966,42 +990,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="B1" s="71" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="72" t="s">
+      <c r="B1" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="67" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="68" t="s">
+      <c r="L1" s="65"/>
+      <c r="M1" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="69"/>
-      <c r="M1" s="72" t="s">
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="69"/>
-      <c r="R1" s="72" t="s">
+      <c r="S1" s="64"/>
+      <c r="T1" s="64"/>
+      <c r="U1" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="68"/>
-      <c r="T1" s="68"/>
-      <c r="U1" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="V1" s="68"/>
-      <c r="W1" s="68"/>
-      <c r="X1" s="68"/>
-      <c r="Y1" s="69"/>
+      <c r="V1" s="64"/>
+      <c r="W1" s="64"/>
+      <c r="X1" s="64"/>
+      <c r="Y1" s="65"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1014,70 +1038,70 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="S2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="V2" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="W2" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="S2" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="U2" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="V2" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="W2" s="12" t="s">
-        <v>30</v>
-      </c>
       <c r="X2" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1085,66 +1109,68 @@
       <c r="B3" s="9"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>43</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>44</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>26</v>
-      </c>
       <c r="P3" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="R3" s="9"/>
+        <v>30</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>67</v>
+      </c>
       <c r="S3" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="T3" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="X3" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y3" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -1200,13 +1226,13 @@
         <v>400</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S4" s="4">
         <v>1</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U4" s="5">
         <v>81600000000000</v>
@@ -1224,11 +1250,13 @@
       <c r="Y4" s="1">
         <v>1</v>
       </c>
-      <c r="Z4" s="66" t="s">
-        <v>48</v>
+      <c r="Z4" s="69" t="s">
+        <v>47</v>
       </c>
       <c r="AA4" s="70"/>
       <c r="AB4" s="70"/>
+      <c r="AC4" s="71"/>
+      <c r="AD4" s="71"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="22">
@@ -1283,13 +1311,13 @@
         <v>400</v>
       </c>
       <c r="R5" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S5" s="13">
         <v>1</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U5" s="16">
         <v>81600000000000</v>
@@ -1307,11 +1335,13 @@
       <c r="Y5" s="1">
         <v>1</v>
       </c>
-      <c r="Z5" s="66" t="s">
-        <v>49</v>
+      <c r="Z5" s="69" t="s">
+        <v>48</v>
       </c>
       <c r="AA5" s="70"/>
       <c r="AB5" s="70"/>
+      <c r="AC5" s="71"/>
+      <c r="AD5" s="71"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="22">
@@ -1366,13 +1396,13 @@
         <v>400</v>
       </c>
       <c r="R6" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S6" s="13">
         <v>1</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U6" s="16">
         <v>81600000000000</v>
@@ -1390,11 +1420,13 @@
       <c r="Y6" s="1">
         <v>1</v>
       </c>
-      <c r="Z6" s="66" t="s">
-        <v>50</v>
+      <c r="Z6" s="69" t="s">
+        <v>49</v>
       </c>
       <c r="AA6" s="70"/>
       <c r="AB6" s="70"/>
+      <c r="AC6" s="71"/>
+      <c r="AD6" s="71"/>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="22">
@@ -1449,13 +1481,13 @@
         <v>400</v>
       </c>
       <c r="R7" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S7" s="13">
         <v>1</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U7" s="16">
         <v>81600000000000</v>
@@ -1473,96 +1505,98 @@
       <c r="Y7" s="1">
         <v>1</v>
       </c>
-      <c r="Z7" s="66" t="s">
-        <v>51</v>
+      <c r="Z7" s="69" t="s">
+        <v>50</v>
       </c>
       <c r="AA7" s="70"/>
       <c r="AB7" s="70"/>
+      <c r="AC7" s="71"/>
+      <c r="AD7" s="71"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="22">
         <v>105</v>
       </c>
-      <c r="B8" s="37">
-        <v>12</v>
-      </c>
-      <c r="C8" s="37">
+      <c r="B8" s="36">
+        <v>12</v>
+      </c>
+      <c r="C8" s="36">
         <v>700</v>
       </c>
-      <c r="D8" s="38">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E8" s="38">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F8" s="39">
-        <v>5</v>
-      </c>
-      <c r="G8" s="38">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H8" s="38">
+      <c r="D8" s="37">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E8" s="37">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F8" s="38">
+        <v>5</v>
+      </c>
+      <c r="G8" s="37">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H8" s="37">
         <v>100</v>
       </c>
-      <c r="I8" s="37">
-        <v>1</v>
-      </c>
-      <c r="J8" s="40">
-        <v>1E-4</v>
-      </c>
-      <c r="K8" s="37">
-        <v>2</v>
-      </c>
-      <c r="L8" s="39">
-        <v>2</v>
-      </c>
-      <c r="M8" s="38">
-        <v>4.2000000000000002E-4</v>
-      </c>
-      <c r="N8" s="37">
+      <c r="I8" s="36">
+        <v>1</v>
+      </c>
+      <c r="J8" s="39">
+        <v>1E-4</v>
+      </c>
+      <c r="K8" s="36">
+        <v>2</v>
+      </c>
+      <c r="L8" s="38">
+        <v>2</v>
+      </c>
+      <c r="M8" s="37">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N8" s="36">
         <v>150</v>
       </c>
-      <c r="O8" s="37">
-        <v>0.2</v>
-      </c>
-      <c r="P8" s="37">
-        <v>300</v>
-      </c>
-      <c r="Q8" s="39">
-        <v>400</v>
-      </c>
-      <c r="R8" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="S8" s="37">
-        <v>1</v>
-      </c>
-      <c r="T8" s="39" t="s">
-        <v>11</v>
-      </c>
-      <c r="U8" s="38">
+      <c r="O8" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="P8" s="36">
+        <v>300</v>
+      </c>
+      <c r="Q8" s="38">
+        <v>400</v>
+      </c>
+      <c r="R8" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="S8" s="36">
+        <v>1</v>
+      </c>
+      <c r="T8" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="U8" s="37">
         <v>81600000000000</v>
       </c>
-      <c r="V8" s="37">
+      <c r="V8" s="36">
         <f t="shared" si="0"/>
         <v>125520</v>
       </c>
-      <c r="W8" s="37">
-        <v>0</v>
-      </c>
-      <c r="X8" s="37">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="39">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="66" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA8" s="67"/>
-      <c r="AB8" s="67"/>
-      <c r="AC8" s="67"/>
-      <c r="AD8" s="67"/>
+      <c r="W8" s="36">
+        <v>0</v>
+      </c>
+      <c r="X8" s="36">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="38">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="69" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA8" s="72"/>
+      <c r="AB8" s="72"/>
+      <c r="AC8" s="72"/>
+      <c r="AD8" s="72"/>
       <c r="AE8" s="20"/>
       <c r="AF8" s="20"/>
     </row>
@@ -1619,13 +1653,13 @@
         <v>400</v>
       </c>
       <c r="R9" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S9" s="13">
         <v>1</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U9" s="16">
         <v>81600000000000</v>
@@ -1643,94 +1677,98 @@
       <c r="Y9" s="1">
         <v>1</v>
       </c>
-      <c r="Z9" s="66" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA9" s="67"/>
-      <c r="AB9" s="67"/>
+      <c r="Z9" s="69" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA9" s="72"/>
+      <c r="AB9" s="72"/>
+      <c r="AC9" s="71"/>
+      <c r="AD9" s="71"/>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A10" s="47">
+      <c r="A10" s="46">
         <v>107</v>
       </c>
-      <c r="B10" s="42">
-        <v>12</v>
-      </c>
-      <c r="C10" s="42">
-        <v>300</v>
-      </c>
-      <c r="D10" s="43">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E10" s="43">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F10" s="44">
-        <v>5</v>
-      </c>
-      <c r="G10" s="43">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H10" s="43">
+      <c r="B10" s="41">
+        <v>12</v>
+      </c>
+      <c r="C10" s="41">
+        <v>300</v>
+      </c>
+      <c r="D10" s="42">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E10" s="42">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F10" s="43">
+        <v>5</v>
+      </c>
+      <c r="G10" s="42">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H10" s="42">
         <v>100</v>
       </c>
-      <c r="I10" s="42">
-        <v>1</v>
-      </c>
-      <c r="J10" s="45">
-        <v>1E-4</v>
-      </c>
-      <c r="K10" s="42">
-        <v>2</v>
-      </c>
-      <c r="L10" s="44">
-        <v>2</v>
-      </c>
-      <c r="M10" s="43">
-        <v>4.2000000000000002E-4</v>
-      </c>
-      <c r="N10" s="42">
+      <c r="I10" s="41">
+        <v>1</v>
+      </c>
+      <c r="J10" s="44">
+        <v>1E-4</v>
+      </c>
+      <c r="K10" s="41">
+        <v>2</v>
+      </c>
+      <c r="L10" s="43">
+        <v>2</v>
+      </c>
+      <c r="M10" s="42">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N10" s="41">
         <v>150</v>
       </c>
-      <c r="O10" s="42">
-        <v>0.2</v>
-      </c>
-      <c r="P10" s="42">
-        <v>300</v>
-      </c>
-      <c r="Q10" s="44">
-        <v>400</v>
-      </c>
-      <c r="R10" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="S10" s="42">
-        <v>1</v>
-      </c>
-      <c r="T10" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="U10" s="43">
+      <c r="O10" s="41">
+        <v>0.2</v>
+      </c>
+      <c r="P10" s="41">
+        <v>300</v>
+      </c>
+      <c r="Q10" s="43">
+        <v>400</v>
+      </c>
+      <c r="R10" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="S10" s="41">
+        <v>1</v>
+      </c>
+      <c r="T10" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="U10" s="42">
         <v>81600000000000</v>
       </c>
-      <c r="V10" s="42">
+      <c r="V10" s="41">
         <f t="shared" si="0"/>
         <v>125520</v>
       </c>
-      <c r="W10" s="42">
-        <v>0</v>
-      </c>
-      <c r="X10" s="46">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="44">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="76" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA10" s="77"/>
-      <c r="AB10" s="77"/>
+      <c r="W10" s="41">
+        <v>0</v>
+      </c>
+      <c r="X10" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="43">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="73" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA10" s="74"/>
+      <c r="AB10" s="74"/>
+      <c r="AC10" s="71"/>
+      <c r="AD10" s="71"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="22">
@@ -1786,13 +1824,13 @@
         <v>400</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S11" s="13">
         <v>1</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U11" s="19">
         <f>U10*(4/3)</f>
@@ -1811,9 +1849,11 @@
       <c r="Y11" s="1">
         <v>1</v>
       </c>
-      <c r="Z11" s="76"/>
-      <c r="AA11" s="77"/>
-      <c r="AB11" s="77"/>
+      <c r="Z11" s="73"/>
+      <c r="AA11" s="74"/>
+      <c r="AB11" s="74"/>
+      <c r="AC11" s="71"/>
+      <c r="AD11" s="71"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="22">
@@ -1868,13 +1908,13 @@
         <v>400</v>
       </c>
       <c r="R12" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S12" s="13">
         <v>1</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U12" s="19">
         <f t="shared" ref="U12:U27" si="1">U11*(4/3)</f>
@@ -1893,9 +1933,11 @@
       <c r="Y12" s="1">
         <v>1</v>
       </c>
-      <c r="Z12" s="76"/>
-      <c r="AA12" s="77"/>
-      <c r="AB12" s="77"/>
+      <c r="Z12" s="73"/>
+      <c r="AA12" s="74"/>
+      <c r="AB12" s="74"/>
+      <c r="AC12" s="71"/>
+      <c r="AD12" s="71"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1950,13 +1992,13 @@
         <v>400</v>
       </c>
       <c r="R13" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S13" s="13">
         <v>1</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U13" s="19">
         <f t="shared" si="1"/>
@@ -1975,9 +2017,11 @@
       <c r="Y13" s="1">
         <v>1</v>
       </c>
-      <c r="Z13" s="76"/>
-      <c r="AA13" s="77"/>
-      <c r="AB13" s="77"/>
+      <c r="Z13" s="73"/>
+      <c r="AA13" s="74"/>
+      <c r="AB13" s="74"/>
+      <c r="AC13" s="71"/>
+      <c r="AD13" s="71"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="23">
@@ -2032,13 +2076,13 @@
         <v>400</v>
       </c>
       <c r="R14" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S14" s="13">
         <v>1</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U14" s="19">
         <f t="shared" si="1"/>
@@ -2057,9 +2101,11 @@
       <c r="Y14" s="1">
         <v>1</v>
       </c>
-      <c r="Z14" s="76"/>
-      <c r="AA14" s="77"/>
-      <c r="AB14" s="77"/>
+      <c r="Z14" s="73"/>
+      <c r="AA14" s="74"/>
+      <c r="AB14" s="74"/>
+      <c r="AC14" s="71"/>
+      <c r="AD14" s="71"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -2114,13 +2160,13 @@
         <v>400</v>
       </c>
       <c r="R15" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S15" s="13">
         <v>1</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U15" s="19">
         <f t="shared" si="1"/>
@@ -2139,9 +2185,11 @@
       <c r="Y15" s="1">
         <v>1</v>
       </c>
-      <c r="Z15" s="76"/>
-      <c r="AA15" s="77"/>
-      <c r="AB15" s="77"/>
+      <c r="Z15" s="73"/>
+      <c r="AA15" s="74"/>
+      <c r="AB15" s="74"/>
+      <c r="AC15" s="71"/>
+      <c r="AD15" s="71"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="23">
@@ -2196,13 +2244,13 @@
         <v>400</v>
       </c>
       <c r="R16" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S16" s="13">
         <v>1</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U16" s="19">
         <f t="shared" si="1"/>
@@ -2221,11 +2269,13 @@
       <c r="Y16" s="1">
         <v>1</v>
       </c>
-      <c r="Z16" s="76"/>
-      <c r="AA16" s="77"/>
-      <c r="AB16" s="77"/>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z16" s="73"/>
+      <c r="AA16" s="74"/>
+      <c r="AB16" s="74"/>
+      <c r="AC16" s="71"/>
+      <c r="AD16" s="71"/>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>114</v>
       </c>
@@ -2278,13 +2328,13 @@
         <v>400</v>
       </c>
       <c r="R17" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S17" s="13">
         <v>1</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U17" s="19">
         <f t="shared" si="1"/>
@@ -2303,11 +2353,13 @@
       <c r="Y17" s="1">
         <v>1</v>
       </c>
-      <c r="Z17" s="76"/>
-      <c r="AA17" s="77"/>
-      <c r="AB17" s="77"/>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z17" s="73"/>
+      <c r="AA17" s="74"/>
+      <c r="AB17" s="74"/>
+      <c r="AC17" s="71"/>
+      <c r="AD17" s="71"/>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>115</v>
       </c>
@@ -2360,13 +2412,13 @@
         <v>400</v>
       </c>
       <c r="R18" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S18" s="13">
         <v>1</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U18" s="19">
         <f t="shared" si="1"/>
@@ -2385,11 +2437,13 @@
       <c r="Y18" s="1">
         <v>1</v>
       </c>
-      <c r="Z18" s="76"/>
-      <c r="AA18" s="77"/>
-      <c r="AB18" s="77"/>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z18" s="73"/>
+      <c r="AA18" s="74"/>
+      <c r="AB18" s="74"/>
+      <c r="AC18" s="71"/>
+      <c r="AD18" s="71"/>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>116</v>
       </c>
@@ -2442,13 +2496,13 @@
         <v>400</v>
       </c>
       <c r="R19" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S19" s="13">
         <v>1</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U19" s="19">
         <f t="shared" si="1"/>
@@ -2467,11 +2521,13 @@
       <c r="Y19" s="1">
         <v>1</v>
       </c>
-      <c r="Z19" s="76"/>
-      <c r="AA19" s="77"/>
-      <c r="AB19" s="77"/>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z19" s="73"/>
+      <c r="AA19" s="74"/>
+      <c r="AB19" s="74"/>
+      <c r="AC19" s="71"/>
+      <c r="AD19" s="71"/>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>117</v>
       </c>
@@ -2524,13 +2580,13 @@
         <v>400</v>
       </c>
       <c r="R20" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S20" s="13">
         <v>1</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U20" s="19">
         <f t="shared" si="1"/>
@@ -2549,11 +2605,13 @@
       <c r="Y20" s="1">
         <v>1</v>
       </c>
-      <c r="Z20" s="76"/>
-      <c r="AA20" s="77"/>
-      <c r="AB20" s="77"/>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z20" s="73"/>
+      <c r="AA20" s="74"/>
+      <c r="AB20" s="74"/>
+      <c r="AC20" s="71"/>
+      <c r="AD20" s="71"/>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>118</v>
       </c>
@@ -2606,13 +2664,13 @@
         <v>400</v>
       </c>
       <c r="R21" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S21" s="13">
         <v>1</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U21" s="19">
         <f t="shared" si="1"/>
@@ -2631,11 +2689,13 @@
       <c r="Y21" s="1">
         <v>1</v>
       </c>
-      <c r="Z21" s="76"/>
-      <c r="AA21" s="77"/>
-      <c r="AB21" s="77"/>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z21" s="73"/>
+      <c r="AA21" s="74"/>
+      <c r="AB21" s="74"/>
+      <c r="AC21" s="71"/>
+      <c r="AD21" s="71"/>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>119</v>
       </c>
@@ -2688,13 +2748,13 @@
         <v>400</v>
       </c>
       <c r="R22" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S22" s="13">
         <v>1</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U22" s="19">
         <f t="shared" si="1"/>
@@ -2713,11 +2773,13 @@
       <c r="Y22" s="1">
         <v>1</v>
       </c>
-      <c r="Z22" s="76"/>
-      <c r="AA22" s="77"/>
-      <c r="AB22" s="77"/>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z22" s="73"/>
+      <c r="AA22" s="74"/>
+      <c r="AB22" s="74"/>
+      <c r="AC22" s="71"/>
+      <c r="AD22" s="71"/>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>120</v>
       </c>
@@ -2770,13 +2832,13 @@
         <v>400</v>
       </c>
       <c r="R23" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S23" s="13">
         <v>1</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U23" s="19">
         <f t="shared" si="1"/>
@@ -2795,11 +2857,13 @@
       <c r="Y23" s="1">
         <v>1</v>
       </c>
-      <c r="Z23" s="76"/>
-      <c r="AA23" s="77"/>
-      <c r="AB23" s="77"/>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z23" s="73"/>
+      <c r="AA23" s="74"/>
+      <c r="AB23" s="74"/>
+      <c r="AC23" s="71"/>
+      <c r="AD23" s="71"/>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>121</v>
       </c>
@@ -2852,13 +2916,13 @@
         <v>400</v>
       </c>
       <c r="R24" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S24" s="13">
         <v>1</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U24" s="19">
         <f t="shared" si="1"/>
@@ -2877,11 +2941,13 @@
       <c r="Y24" s="1">
         <v>1</v>
       </c>
-      <c r="Z24" s="76"/>
-      <c r="AA24" s="77"/>
-      <c r="AB24" s="77"/>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z24" s="73"/>
+      <c r="AA24" s="74"/>
+      <c r="AB24" s="74"/>
+      <c r="AC24" s="71"/>
+      <c r="AD24" s="71"/>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>122</v>
       </c>
@@ -2934,13 +3000,13 @@
         <v>400</v>
       </c>
       <c r="R25" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S25" s="13">
         <v>1</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U25" s="19">
         <f t="shared" si="1"/>
@@ -2959,11 +3025,13 @@
       <c r="Y25" s="1">
         <v>1</v>
       </c>
-      <c r="Z25" s="76"/>
-      <c r="AA25" s="77"/>
-      <c r="AB25" s="77"/>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z25" s="73"/>
+      <c r="AA25" s="74"/>
+      <c r="AB25" s="74"/>
+      <c r="AC25" s="71"/>
+      <c r="AD25" s="71"/>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>123</v>
       </c>
@@ -3016,13 +3084,13 @@
         <v>400</v>
       </c>
       <c r="R26" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S26" s="13">
         <v>1</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U26" s="19">
         <f t="shared" si="1"/>
@@ -3041,176 +3109,182 @@
       <c r="Y26" s="1">
         <v>1</v>
       </c>
-      <c r="Z26" s="76"/>
-      <c r="AA26" s="77"/>
-      <c r="AB26" s="77"/>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z26" s="73"/>
+      <c r="AA26" s="74"/>
+      <c r="AB26" s="74"/>
+      <c r="AC26" s="71"/>
+      <c r="AD26" s="71"/>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="22">
         <v>124</v>
       </c>
-      <c r="B27" s="25">
-        <v>12</v>
-      </c>
-      <c r="C27" s="26">
+      <c r="B27" s="24">
+        <v>12</v>
+      </c>
+      <c r="C27" s="25">
         <v>2000</v>
       </c>
-      <c r="D27" s="27">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E27" s="27">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F27" s="28">
-        <v>5</v>
-      </c>
-      <c r="G27" s="27">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H27" s="27">
+      <c r="D27" s="26">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E27" s="26">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F27" s="27">
+        <v>5</v>
+      </c>
+      <c r="G27" s="26">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H27" s="26">
         <v>100</v>
       </c>
-      <c r="I27" s="26">
-        <v>1</v>
-      </c>
-      <c r="J27" s="29">
-        <v>1E-4</v>
-      </c>
-      <c r="K27" s="26">
-        <v>2</v>
-      </c>
-      <c r="L27" s="28">
-        <v>2</v>
-      </c>
-      <c r="M27" s="27">
-        <v>4.2000000000000002E-4</v>
-      </c>
-      <c r="N27" s="26">
+      <c r="I27" s="25">
+        <v>1</v>
+      </c>
+      <c r="J27" s="28">
+        <v>1E-4</v>
+      </c>
+      <c r="K27" s="25">
+        <v>2</v>
+      </c>
+      <c r="L27" s="27">
+        <v>2</v>
+      </c>
+      <c r="M27" s="26">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N27" s="25">
         <v>150</v>
       </c>
-      <c r="O27" s="26">
-        <v>0.2</v>
-      </c>
-      <c r="P27" s="26">
-        <v>300</v>
-      </c>
-      <c r="Q27" s="28">
-        <v>400</v>
-      </c>
-      <c r="R27" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="S27" s="26">
-        <v>1</v>
-      </c>
-      <c r="T27" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="U27" s="27">
+      <c r="O27" s="25">
+        <v>0.2</v>
+      </c>
+      <c r="P27" s="25">
+        <v>300</v>
+      </c>
+      <c r="Q27" s="27">
+        <v>400</v>
+      </c>
+      <c r="R27" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="S27" s="25">
+        <v>1</v>
+      </c>
+      <c r="T27" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="U27" s="26">
         <f t="shared" si="1"/>
         <v>1.0855471240301894E+16</v>
       </c>
-      <c r="V27" s="26">
+      <c r="V27" s="25">
         <f t="shared" si="2"/>
         <v>125520</v>
       </c>
-      <c r="W27" s="26">
-        <v>0</v>
-      </c>
-      <c r="X27" s="30">
-        <v>1</v>
-      </c>
-      <c r="Y27" s="28">
-        <v>1</v>
-      </c>
-      <c r="Z27" s="76"/>
-      <c r="AA27" s="77"/>
-      <c r="AB27" s="77"/>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A28" s="34">
+      <c r="W27" s="25">
+        <v>0</v>
+      </c>
+      <c r="X27" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="73"/>
+      <c r="AA27" s="74"/>
+      <c r="AB27" s="74"/>
+      <c r="AC27" s="71"/>
+      <c r="AD27" s="71"/>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A28" s="33">
         <v>125</v>
       </c>
-      <c r="B28" s="31">
-        <v>12</v>
-      </c>
-      <c r="C28" s="32">
+      <c r="B28" s="30">
+        <v>12</v>
+      </c>
+      <c r="C28" s="31">
         <v>1000</v>
       </c>
-      <c r="D28" s="33">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E28" s="33">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F28" s="34">
-        <v>5</v>
-      </c>
-      <c r="G28" s="33">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H28" s="33">
+      <c r="D28" s="32">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E28" s="32">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F28" s="33">
+        <v>5</v>
+      </c>
+      <c r="G28" s="32">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H28" s="32">
         <v>100</v>
       </c>
-      <c r="I28" s="32">
-        <v>1</v>
-      </c>
-      <c r="J28" s="35">
-        <v>1E-4</v>
-      </c>
-      <c r="K28" s="32">
-        <v>2</v>
-      </c>
-      <c r="L28" s="34">
-        <v>2</v>
-      </c>
-      <c r="M28" s="33">
-        <v>4.2000000000000002E-4</v>
-      </c>
-      <c r="N28" s="32">
+      <c r="I28" s="31">
+        <v>1</v>
+      </c>
+      <c r="J28" s="34">
+        <v>1E-4</v>
+      </c>
+      <c r="K28" s="31">
+        <v>2</v>
+      </c>
+      <c r="L28" s="33">
+        <v>2</v>
+      </c>
+      <c r="M28" s="32">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N28" s="31">
         <v>150</v>
       </c>
-      <c r="O28" s="32">
-        <v>0.2</v>
-      </c>
-      <c r="P28" s="32">
-        <v>300</v>
-      </c>
-      <c r="Q28" s="34">
-        <v>400</v>
-      </c>
-      <c r="R28" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="S28" s="32">
-        <v>1</v>
-      </c>
-      <c r="T28" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="U28" s="33">
+      <c r="O28" s="31">
+        <v>0.2</v>
+      </c>
+      <c r="P28" s="31">
+        <v>300</v>
+      </c>
+      <c r="Q28" s="33">
+        <v>400</v>
+      </c>
+      <c r="R28" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="S28" s="31">
+        <v>1</v>
+      </c>
+      <c r="T28" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="U28" s="32">
         <v>257896296296296.25</v>
       </c>
-      <c r="V28" s="32">
+      <c r="V28" s="31">
         <f t="shared" si="2"/>
         <v>125520</v>
       </c>
-      <c r="W28" s="32">
-        <v>0</v>
-      </c>
-      <c r="X28" s="36">
-        <v>1</v>
-      </c>
-      <c r="Y28" s="34">
-        <v>1</v>
-      </c>
-      <c r="Z28" s="66" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA28" s="67"/>
-      <c r="AB28" s="67"/>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="W28" s="31">
+        <v>0</v>
+      </c>
+      <c r="X28" s="35">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="33">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA28" s="72"/>
+      <c r="AB28" s="72"/>
+      <c r="AC28" s="71"/>
+      <c r="AD28" s="71"/>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="22">
         <v>126</v>
       </c>
@@ -3263,13 +3337,13 @@
         <v>400</v>
       </c>
       <c r="R29" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S29" s="13">
         <v>1</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U29" s="19">
         <f>U27*2</f>
@@ -3288,13 +3362,15 @@
       <c r="Y29" s="1">
         <v>1</v>
       </c>
-      <c r="Z29" s="76" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA29" s="77"/>
-      <c r="AB29" s="77"/>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z29" s="73" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA29" s="74"/>
+      <c r="AB29" s="74"/>
+      <c r="AC29" s="71"/>
+      <c r="AD29" s="71"/>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="22">
         <v>127</v>
       </c>
@@ -3347,13 +3423,13 @@
         <v>400</v>
       </c>
       <c r="R30" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S30" s="13">
         <v>1</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U30" s="19">
         <f t="shared" ref="U30:U31" si="3">U28*2</f>
@@ -3372,11 +3448,13 @@
       <c r="Y30" s="1">
         <v>1</v>
       </c>
-      <c r="Z30" s="76"/>
-      <c r="AA30" s="77"/>
-      <c r="AB30" s="77"/>
-    </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z30" s="73"/>
+      <c r="AA30" s="74"/>
+      <c r="AB30" s="74"/>
+      <c r="AC30" s="71"/>
+      <c r="AD30" s="71"/>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="23">
         <v>128</v>
       </c>
@@ -3429,13 +3507,13 @@
         <v>400</v>
       </c>
       <c r="R31" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S31" s="13">
         <v>1</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U31" s="19">
         <f t="shared" si="3"/>
@@ -3454,11 +3532,13 @@
       <c r="Y31" s="1">
         <v>1</v>
       </c>
-      <c r="Z31" s="76"/>
-      <c r="AA31" s="77"/>
-      <c r="AB31" s="77"/>
-    </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z31" s="73"/>
+      <c r="AA31" s="74"/>
+      <c r="AB31" s="74"/>
+      <c r="AC31" s="71"/>
+      <c r="AD31" s="71"/>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="23">
         <v>129</v>
       </c>
@@ -3511,13 +3591,13 @@
         <v>400</v>
       </c>
       <c r="R32" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S32" s="13">
         <v>1</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U32" s="19">
         <f>U31*2</f>
@@ -3536,11 +3616,13 @@
       <c r="Y32" s="1">
         <v>1</v>
       </c>
-      <c r="Z32" s="76"/>
-      <c r="AA32" s="77"/>
-      <c r="AB32" s="77"/>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="Z32" s="73"/>
+      <c r="AA32" s="74"/>
+      <c r="AB32" s="74"/>
+      <c r="AC32" s="71"/>
+      <c r="AD32" s="71"/>
+    </row>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="22">
         <v>130</v>
       </c>
@@ -3593,13 +3675,13 @@
         <v>400</v>
       </c>
       <c r="R33" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S33" s="13">
         <v>1</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U33" s="19">
         <f t="shared" ref="U33:U45" si="4">U32*2</f>
@@ -3618,11 +3700,13 @@
       <c r="Y33" s="1">
         <v>1</v>
       </c>
-      <c r="Z33" s="76"/>
-      <c r="AA33" s="77"/>
-      <c r="AB33" s="77"/>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="Z33" s="73"/>
+      <c r="AA33" s="74"/>
+      <c r="AB33" s="74"/>
+      <c r="AC33" s="71"/>
+      <c r="AD33" s="71"/>
+    </row>
+    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="22">
         <v>131</v>
       </c>
@@ -3675,13 +3759,13 @@
         <v>400</v>
       </c>
       <c r="R34" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S34" s="13">
         <v>1</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U34" s="19">
         <f t="shared" si="4"/>
@@ -3700,11 +3784,13 @@
       <c r="Y34" s="1">
         <v>1</v>
       </c>
-      <c r="Z34" s="76"/>
-      <c r="AA34" s="77"/>
-      <c r="AB34" s="77"/>
-    </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="Z34" s="73"/>
+      <c r="AA34" s="74"/>
+      <c r="AB34" s="74"/>
+      <c r="AC34" s="71"/>
+      <c r="AD34" s="71"/>
+    </row>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="22">
         <v>132</v>
       </c>
@@ -3757,13 +3843,13 @@
         <v>400</v>
       </c>
       <c r="R35" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S35" s="13">
         <v>1</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U35" s="19">
         <f t="shared" si="4"/>
@@ -3782,11 +3868,13 @@
       <c r="Y35" s="1">
         <v>1</v>
       </c>
-      <c r="Z35" s="76"/>
-      <c r="AA35" s="77"/>
-      <c r="AB35" s="77"/>
-    </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="Z35" s="73"/>
+      <c r="AA35" s="74"/>
+      <c r="AB35" s="74"/>
+      <c r="AC35" s="71"/>
+      <c r="AD35" s="71"/>
+    </row>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="23">
         <v>133</v>
       </c>
@@ -3839,13 +3927,13 @@
         <v>400</v>
       </c>
       <c r="R36" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S36" s="13">
         <v>1</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U36" s="19">
         <f t="shared" si="4"/>
@@ -3864,11 +3952,13 @@
       <c r="Y36" s="1">
         <v>1</v>
       </c>
-      <c r="Z36" s="76"/>
-      <c r="AA36" s="77"/>
-      <c r="AB36" s="77"/>
-    </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="Z36" s="73"/>
+      <c r="AA36" s="74"/>
+      <c r="AB36" s="74"/>
+      <c r="AC36" s="71"/>
+      <c r="AD36" s="71"/>
+    </row>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="23">
         <v>134</v>
       </c>
@@ -3921,13 +4011,13 @@
         <v>400</v>
       </c>
       <c r="R37" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S37" s="13">
         <v>1</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U37" s="19">
         <f t="shared" si="4"/>
@@ -3946,11 +4036,13 @@
       <c r="Y37" s="1">
         <v>1</v>
       </c>
-      <c r="Z37" s="76"/>
-      <c r="AA37" s="77"/>
-      <c r="AB37" s="77"/>
-    </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="Z37" s="73"/>
+      <c r="AA37" s="74"/>
+      <c r="AB37" s="74"/>
+      <c r="AC37" s="71"/>
+      <c r="AD37" s="71"/>
+    </row>
+    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="22">
         <v>135</v>
       </c>
@@ -4003,13 +4095,13 @@
         <v>400</v>
       </c>
       <c r="R38" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S38" s="13">
         <v>1</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U38" s="19">
         <f t="shared" si="4"/>
@@ -4028,11 +4120,13 @@
       <c r="Y38" s="1">
         <v>1</v>
       </c>
-      <c r="Z38" s="76"/>
-      <c r="AA38" s="77"/>
-      <c r="AB38" s="77"/>
-    </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="Z38" s="73"/>
+      <c r="AA38" s="74"/>
+      <c r="AB38" s="74"/>
+      <c r="AC38" s="71"/>
+      <c r="AD38" s="71"/>
+    </row>
+    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="23">
         <v>136</v>
       </c>
@@ -4085,13 +4179,13 @@
         <v>400</v>
       </c>
       <c r="R39" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S39" s="13">
         <v>1</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U39" s="19">
         <f t="shared" si="4"/>
@@ -4110,12 +4204,14 @@
       <c r="Y39" s="1">
         <v>1</v>
       </c>
-      <c r="Z39" s="76"/>
-      <c r="AA39" s="77"/>
-      <c r="AB39" s="77"/>
-    </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A40" s="62">
+      <c r="Z39" s="73"/>
+      <c r="AA39" s="74"/>
+      <c r="AB39" s="74"/>
+      <c r="AC39" s="71"/>
+      <c r="AD39" s="71"/>
+    </row>
+    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A40" s="61">
         <v>137</v>
       </c>
       <c r="B40" s="13">
@@ -4167,13 +4263,13 @@
         <v>400</v>
       </c>
       <c r="R40" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S40" s="13">
         <v>1</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U40" s="19">
         <f t="shared" si="4"/>
@@ -4192,12 +4288,14 @@
       <c r="Y40" s="1">
         <v>1</v>
       </c>
-      <c r="Z40" s="76"/>
-      <c r="AA40" s="77"/>
-      <c r="AB40" s="77"/>
-    </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A41" s="62">
+      <c r="Z40" s="73"/>
+      <c r="AA40" s="74"/>
+      <c r="AB40" s="74"/>
+      <c r="AC40" s="71"/>
+      <c r="AD40" s="71"/>
+    </row>
+    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A41" s="61">
         <v>138</v>
       </c>
       <c r="B41" s="13">
@@ -4249,13 +4347,13 @@
         <v>400</v>
       </c>
       <c r="R41" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S41" s="13">
         <v>1</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U41" s="19">
         <f t="shared" si="4"/>
@@ -4274,12 +4372,14 @@
       <c r="Y41" s="1">
         <v>1</v>
       </c>
-      <c r="Z41" s="76"/>
-      <c r="AA41" s="77"/>
-      <c r="AB41" s="77"/>
-    </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A42" s="62">
+      <c r="Z41" s="73"/>
+      <c r="AA41" s="74"/>
+      <c r="AB41" s="74"/>
+      <c r="AC41" s="71"/>
+      <c r="AD41" s="71"/>
+    </row>
+    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A42" s="61">
         <v>139</v>
       </c>
       <c r="B42" s="13">
@@ -4331,13 +4431,13 @@
         <v>400</v>
       </c>
       <c r="R42" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S42" s="13">
         <v>1</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U42" s="19">
         <f t="shared" si="4"/>
@@ -4356,12 +4456,14 @@
       <c r="Y42" s="1">
         <v>1</v>
       </c>
-      <c r="Z42" s="76"/>
-      <c r="AA42" s="77"/>
-      <c r="AB42" s="77"/>
-    </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A43" s="62">
+      <c r="Z42" s="73"/>
+      <c r="AA42" s="74"/>
+      <c r="AB42" s="74"/>
+      <c r="AC42" s="71"/>
+      <c r="AD42" s="71"/>
+    </row>
+    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A43" s="61">
         <v>140</v>
       </c>
       <c r="B43" s="13">
@@ -4413,13 +4515,13 @@
         <v>400</v>
       </c>
       <c r="R43" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S43" s="13">
         <v>1</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U43" s="19">
         <f t="shared" si="4"/>
@@ -4438,12 +4540,14 @@
       <c r="Y43" s="1">
         <v>1</v>
       </c>
-      <c r="Z43" s="76"/>
-      <c r="AA43" s="77"/>
-      <c r="AB43" s="77"/>
-    </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A44" s="62">
+      <c r="Z43" s="73"/>
+      <c r="AA43" s="74"/>
+      <c r="AB43" s="74"/>
+      <c r="AC43" s="71"/>
+      <c r="AD43" s="71"/>
+    </row>
+    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A44" s="61">
         <v>141</v>
       </c>
       <c r="B44" s="13">
@@ -4495,13 +4599,13 @@
         <v>400</v>
       </c>
       <c r="R44" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S44" s="13">
         <v>1</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U44" s="19">
         <f t="shared" si="4"/>
@@ -4520,12 +4624,14 @@
       <c r="Y44" s="1">
         <v>1</v>
       </c>
-      <c r="Z44" s="76"/>
-      <c r="AA44" s="77"/>
-      <c r="AB44" s="77"/>
-    </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A45" s="61">
+      <c r="Z44" s="73"/>
+      <c r="AA44" s="74"/>
+      <c r="AB44" s="74"/>
+      <c r="AC44" s="71"/>
+      <c r="AD44" s="71"/>
+    </row>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A45" s="60">
         <v>142</v>
       </c>
       <c r="B45" s="13">
@@ -4577,13 +4683,13 @@
         <v>400</v>
       </c>
       <c r="R45" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S45" s="13">
         <v>1</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U45" s="19">
         <f t="shared" si="4"/>
@@ -4602,12 +4708,14 @@
       <c r="Y45" s="1">
         <v>1</v>
       </c>
-      <c r="Z45" s="76"/>
-      <c r="AA45" s="77"/>
-      <c r="AB45" s="77"/>
-    </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A46" s="61">
+      <c r="Z45" s="73"/>
+      <c r="AA45" s="74"/>
+      <c r="AB45" s="74"/>
+      <c r="AC45" s="71"/>
+      <c r="AD45" s="71"/>
+    </row>
+    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A46" s="60">
         <v>143</v>
       </c>
       <c r="B46" s="13">
@@ -4659,13 +4767,13 @@
         <v>400</v>
       </c>
       <c r="R46" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S46" s="13">
         <v>1</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U46" s="19">
         <f>U45*2</f>
@@ -4684,404 +4792,412 @@
       <c r="Y46" s="1">
         <v>1</v>
       </c>
-      <c r="Z46" s="76"/>
-      <c r="AA46" s="77"/>
-      <c r="AB46" s="77"/>
-    </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A47" s="41">
+      <c r="Z46" s="73"/>
+      <c r="AA46" s="74"/>
+      <c r="AB46" s="74"/>
+      <c r="AC46" s="71"/>
+      <c r="AD46" s="71"/>
+    </row>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A47" s="40">
         <v>144</v>
       </c>
-      <c r="B47" s="42">
-        <v>12</v>
-      </c>
-      <c r="C47" s="42">
-        <v>300</v>
-      </c>
-      <c r="D47" s="43">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E47" s="43">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F47" s="44">
-        <v>5</v>
-      </c>
-      <c r="G47" s="43">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H47" s="43">
+      <c r="B47" s="41">
+        <v>12</v>
+      </c>
+      <c r="C47" s="41">
+        <v>300</v>
+      </c>
+      <c r="D47" s="42">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E47" s="42">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F47" s="43">
+        <v>5</v>
+      </c>
+      <c r="G47" s="42">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H47" s="42">
         <v>100</v>
       </c>
-      <c r="I47" s="42">
-        <v>1</v>
-      </c>
-      <c r="J47" s="45">
-        <v>1E-4</v>
-      </c>
-      <c r="K47" s="42">
-        <v>2</v>
-      </c>
-      <c r="L47" s="44">
-        <v>2</v>
-      </c>
-      <c r="M47" s="43">
-        <v>4.2000000000000002E-4</v>
-      </c>
-      <c r="N47" s="42">
+      <c r="I47" s="41">
+        <v>1</v>
+      </c>
+      <c r="J47" s="44">
+        <v>1E-4</v>
+      </c>
+      <c r="K47" s="41">
+        <v>2</v>
+      </c>
+      <c r="L47" s="43">
+        <v>2</v>
+      </c>
+      <c r="M47" s="42">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N47" s="41">
         <v>150</v>
       </c>
-      <c r="O47" s="42">
-        <v>0.2</v>
-      </c>
-      <c r="P47" s="42">
-        <v>300</v>
-      </c>
-      <c r="Q47" s="44">
-        <v>400</v>
-      </c>
-      <c r="R47" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="S47" s="42">
-        <v>1</v>
-      </c>
-      <c r="T47" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="U47" s="43">
+      <c r="O47" s="41">
+        <v>0.2</v>
+      </c>
+      <c r="P47" s="41">
+        <v>300</v>
+      </c>
+      <c r="Q47" s="43">
+        <v>400</v>
+      </c>
+      <c r="R47" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="S47" s="41">
+        <v>1</v>
+      </c>
+      <c r="T47" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="U47" s="42">
         <v>81600000000000</v>
       </c>
-      <c r="V47" s="42">
+      <c r="V47" s="41">
         <f t="shared" si="2"/>
         <v>125520</v>
       </c>
-      <c r="W47" s="42">
-        <v>0</v>
-      </c>
-      <c r="X47" s="46">
-        <v>1</v>
-      </c>
-      <c r="Y47" s="44">
-        <v>1</v>
-      </c>
-      <c r="Z47" s="66" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA47" s="67"/>
-      <c r="AB47" s="67"/>
-      <c r="AC47" s="20"/>
-    </row>
-    <row r="48" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="41">
+      <c r="W47" s="41">
+        <v>0</v>
+      </c>
+      <c r="X47" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y47" s="43">
+        <v>1</v>
+      </c>
+      <c r="Z47" s="69" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA47" s="72"/>
+      <c r="AB47" s="72"/>
+      <c r="AC47" s="75"/>
+      <c r="AD47" s="71"/>
+    </row>
+    <row r="48" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="40">
         <v>145</v>
       </c>
-      <c r="B48" s="42">
-        <v>12</v>
-      </c>
-      <c r="C48" s="46">
+      <c r="B48" s="41">
+        <v>12</v>
+      </c>
+      <c r="C48" s="45">
         <v>2000</v>
       </c>
-      <c r="D48" s="43">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E48" s="43">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F48" s="44">
-        <v>5</v>
-      </c>
-      <c r="G48" s="43">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H48" s="43">
+      <c r="D48" s="42">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E48" s="42">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F48" s="43">
+        <v>5</v>
+      </c>
+      <c r="G48" s="42">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H48" s="42">
         <v>100</v>
       </c>
-      <c r="I48" s="42">
-        <v>1</v>
-      </c>
-      <c r="J48" s="45">
-        <v>1E-4</v>
-      </c>
-      <c r="K48" s="42">
-        <v>2</v>
-      </c>
-      <c r="L48" s="44">
-        <v>2</v>
-      </c>
-      <c r="M48" s="43">
-        <v>4.2000000000000002E-4</v>
-      </c>
-      <c r="N48" s="42">
+      <c r="I48" s="41">
+        <v>1</v>
+      </c>
+      <c r="J48" s="44">
+        <v>1E-4</v>
+      </c>
+      <c r="K48" s="41">
+        <v>2</v>
+      </c>
+      <c r="L48" s="43">
+        <v>2</v>
+      </c>
+      <c r="M48" s="42">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N48" s="41">
         <v>150</v>
       </c>
-      <c r="O48" s="42">
-        <v>0.2</v>
-      </c>
-      <c r="P48" s="42">
-        <v>300</v>
-      </c>
-      <c r="Q48" s="44">
-        <v>400</v>
-      </c>
-      <c r="R48" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="S48" s="42">
-        <v>1</v>
-      </c>
-      <c r="T48" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="U48" s="43">
+      <c r="O48" s="41">
+        <v>0.2</v>
+      </c>
+      <c r="P48" s="41">
+        <v>300</v>
+      </c>
+      <c r="Q48" s="43">
+        <v>400</v>
+      </c>
+      <c r="R48" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="S48" s="41">
+        <v>1</v>
+      </c>
+      <c r="T48" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="U48" s="42">
         <f>U29</f>
         <v>2.1710942480603788E+16</v>
       </c>
-      <c r="V48" s="42">
+      <c r="V48" s="41">
         <f t="shared" si="2"/>
         <v>125520</v>
       </c>
-      <c r="W48" s="42">
-        <v>0</v>
-      </c>
-      <c r="X48" s="46">
-        <v>1</v>
-      </c>
-      <c r="Y48" s="44">
-        <v>1</v>
-      </c>
-      <c r="Z48" s="73" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA48" s="75"/>
-      <c r="AB48" s="75"/>
-      <c r="AC48" s="24"/>
-    </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A49" s="41">
+      <c r="W48" s="41">
+        <v>0</v>
+      </c>
+      <c r="X48" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y48" s="43">
+        <v>1</v>
+      </c>
+      <c r="Z48" s="76" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA48" s="77"/>
+      <c r="AB48" s="77"/>
+      <c r="AC48" s="78"/>
+      <c r="AD48" s="71"/>
+    </row>
+    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A49" s="40">
         <v>146</v>
       </c>
-      <c r="B49" s="42">
-        <v>12</v>
-      </c>
-      <c r="C49" s="42">
-        <v>300</v>
-      </c>
-      <c r="D49" s="43">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E49" s="43">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F49" s="44">
-        <v>5</v>
-      </c>
-      <c r="G49" s="43">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H49" s="43">
+      <c r="B49" s="41">
+        <v>12</v>
+      </c>
+      <c r="C49" s="41">
+        <v>300</v>
+      </c>
+      <c r="D49" s="42">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E49" s="42">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F49" s="43">
+        <v>5</v>
+      </c>
+      <c r="G49" s="42">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H49" s="42">
         <v>100</v>
       </c>
-      <c r="I49" s="42">
-        <v>1</v>
-      </c>
-      <c r="J49" s="45">
-        <v>1E-4</v>
-      </c>
-      <c r="K49" s="42">
-        <v>2</v>
-      </c>
-      <c r="L49" s="44">
-        <v>2</v>
-      </c>
-      <c r="M49" s="43">
-        <v>4.2000000000000002E-4</v>
-      </c>
-      <c r="N49" s="42">
+      <c r="I49" s="41">
+        <v>1</v>
+      </c>
+      <c r="J49" s="44">
+        <v>1E-4</v>
+      </c>
+      <c r="K49" s="41">
+        <v>2</v>
+      </c>
+      <c r="L49" s="43">
+        <v>2</v>
+      </c>
+      <c r="M49" s="42">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N49" s="41">
         <v>150</v>
       </c>
-      <c r="O49" s="42">
-        <v>0.2</v>
-      </c>
-      <c r="P49" s="42">
-        <v>300</v>
-      </c>
-      <c r="Q49" s="44">
-        <v>400</v>
-      </c>
-      <c r="R49" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="S49" s="42">
-        <v>1</v>
-      </c>
-      <c r="T49" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="U49" s="43">
+      <c r="O49" s="41">
+        <v>0.2</v>
+      </c>
+      <c r="P49" s="41">
+        <v>300</v>
+      </c>
+      <c r="Q49" s="43">
+        <v>400</v>
+      </c>
+      <c r="R49" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="S49" s="41">
+        <v>1</v>
+      </c>
+      <c r="T49" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="U49" s="42">
         <v>81600000000</v>
       </c>
-      <c r="V49" s="42">
+      <c r="V49" s="41">
         <f t="shared" si="2"/>
         <v>125520</v>
       </c>
-      <c r="W49" s="42">
-        <v>0</v>
-      </c>
-      <c r="X49" s="46">
-        <v>1</v>
-      </c>
-      <c r="Y49" s="44">
-        <v>1</v>
-      </c>
-      <c r="Z49" s="66" t="s">
+      <c r="W49" s="41">
+        <v>0</v>
+      </c>
+      <c r="X49" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y49" s="43">
+        <v>1</v>
+      </c>
+      <c r="Z49" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA49" s="72"/>
+      <c r="AB49" s="72"/>
+      <c r="AC49" s="71"/>
+      <c r="AD49" s="71"/>
+    </row>
+    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A50" s="40">
+        <v>147</v>
+      </c>
+      <c r="B50" s="45">
+        <v>12</v>
+      </c>
+      <c r="C50" s="45">
+        <v>2000</v>
+      </c>
+      <c r="D50" s="47">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E50" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F50" s="40">
+        <v>5</v>
+      </c>
+      <c r="G50" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H50" s="47">
+        <v>100</v>
+      </c>
+      <c r="I50" s="45">
+        <v>1</v>
+      </c>
+      <c r="J50" s="48">
+        <v>1E-4</v>
+      </c>
+      <c r="K50" s="45">
+        <v>2</v>
+      </c>
+      <c r="L50" s="40">
+        <v>2</v>
+      </c>
+      <c r="M50" s="47">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N50" s="45">
+        <v>150</v>
+      </c>
+      <c r="O50" s="45">
+        <v>0.2</v>
+      </c>
+      <c r="P50" s="45">
+        <v>300</v>
+      </c>
+      <c r="Q50" s="40">
+        <v>400</v>
+      </c>
+      <c r="R50" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="S50" s="45">
+        <v>1</v>
+      </c>
+      <c r="T50" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="U50" s="49">
+        <v>81600000000000</v>
+      </c>
+      <c r="V50" s="35">
+        <v>83000</v>
+      </c>
+      <c r="W50" s="45">
+        <v>0</v>
+      </c>
+      <c r="X50" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y50" s="40">
+        <v>1</v>
+      </c>
+      <c r="Z50" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="AA49" s="67"/>
-      <c r="AB49" s="67"/>
-    </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A50" s="41">
-        <v>147</v>
-      </c>
-      <c r="B50" s="46">
-        <v>12</v>
-      </c>
-      <c r="C50" s="46">
+      <c r="AA50" s="72"/>
+      <c r="AB50" s="72"/>
+      <c r="AC50" s="71"/>
+      <c r="AD50" s="71"/>
+    </row>
+    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A51" s="43">
+        <v>148</v>
+      </c>
+      <c r="B51" s="41">
+        <v>12</v>
+      </c>
+      <c r="C51" s="45">
         <v>2000</v>
       </c>
-      <c r="D50" s="48">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E50" s="48">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F50" s="41">
-        <v>5</v>
-      </c>
-      <c r="G50" s="48">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H50" s="48">
+      <c r="D51" s="42">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E51" s="42">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F51" s="43">
+        <v>5</v>
+      </c>
+      <c r="G51" s="42">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H51" s="42">
         <v>100</v>
       </c>
-      <c r="I50" s="46">
-        <v>1</v>
-      </c>
-      <c r="J50" s="49">
-        <v>1E-4</v>
-      </c>
-      <c r="K50" s="46">
-        <v>2</v>
-      </c>
-      <c r="L50" s="41">
-        <v>2</v>
-      </c>
-      <c r="M50" s="48">
-        <v>4.2000000000000002E-4</v>
-      </c>
-      <c r="N50" s="46">
+      <c r="I51" s="41">
+        <v>1</v>
+      </c>
+      <c r="J51" s="44">
+        <v>1E-4</v>
+      </c>
+      <c r="K51" s="41">
+        <v>2</v>
+      </c>
+      <c r="L51" s="43">
+        <v>2</v>
+      </c>
+      <c r="M51" s="42">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N51" s="41">
         <v>150</v>
       </c>
-      <c r="O50" s="46">
-        <v>0.2</v>
-      </c>
-      <c r="P50" s="46">
-        <v>300</v>
-      </c>
-      <c r="Q50" s="41">
-        <v>400</v>
-      </c>
-      <c r="R50" s="46" t="s">
-        <v>38</v>
-      </c>
-      <c r="S50" s="46">
-        <v>1</v>
-      </c>
-      <c r="T50" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="U50" s="50">
-        <v>81600000000000</v>
-      </c>
-      <c r="V50" s="36">
-        <v>83000</v>
-      </c>
-      <c r="W50" s="46">
-        <v>0</v>
-      </c>
-      <c r="X50" s="46">
-        <v>1</v>
-      </c>
-      <c r="Y50" s="41">
-        <v>1</v>
-      </c>
-      <c r="Z50" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA50" s="67"/>
-      <c r="AB50" s="67"/>
-    </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A51" s="44">
-        <v>148</v>
-      </c>
-      <c r="B51" s="42">
-        <v>12</v>
-      </c>
-      <c r="C51" s="46">
-        <v>2000</v>
-      </c>
-      <c r="D51" s="43">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E51" s="43">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F51" s="44">
-        <v>5</v>
-      </c>
-      <c r="G51" s="43">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H51" s="43">
-        <v>100</v>
-      </c>
-      <c r="I51" s="42">
-        <v>1</v>
-      </c>
-      <c r="J51" s="45">
-        <v>1E-4</v>
-      </c>
-      <c r="K51" s="42">
-        <v>2</v>
-      </c>
-      <c r="L51" s="44">
-        <v>2</v>
-      </c>
-      <c r="M51" s="43">
-        <v>4.2000000000000002E-4</v>
-      </c>
-      <c r="N51" s="42">
-        <v>150</v>
-      </c>
-      <c r="O51" s="42">
-        <v>0.2</v>
-      </c>
-      <c r="P51" s="42">
-        <v>300</v>
-      </c>
-      <c r="Q51" s="44">
-        <v>400</v>
-      </c>
-      <c r="R51" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="S51" s="42">
-        <v>1</v>
-      </c>
-      <c r="T51" s="44" t="s">
-        <v>11</v>
+      <c r="O51" s="41">
+        <v>0.2</v>
+      </c>
+      <c r="P51" s="41">
+        <v>300</v>
+      </c>
+      <c r="Q51" s="43">
+        <v>400</v>
+      </c>
+      <c r="R51" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="S51" s="41">
+        <v>1</v>
+      </c>
+      <c r="T51" s="43" t="s">
+        <v>10</v>
       </c>
       <c r="U51" s="16">
         <f>U40</f>
@@ -5091,22 +5207,24 @@
         <f t="shared" si="2"/>
         <v>125520</v>
       </c>
-      <c r="W51" s="42">
-        <v>0</v>
-      </c>
-      <c r="X51" s="46">
-        <v>1</v>
-      </c>
-      <c r="Y51" s="44">
-        <v>1</v>
-      </c>
-      <c r="Z51" s="76" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA51" s="77"/>
-      <c r="AB51" s="77"/>
-    </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="W51" s="41">
+        <v>0</v>
+      </c>
+      <c r="X51" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y51" s="43">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="73" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA51" s="74"/>
+      <c r="AB51" s="74"/>
+      <c r="AC51" s="71"/>
+      <c r="AD51" s="71"/>
+    </row>
+    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>149</v>
       </c>
@@ -5159,13 +5277,13 @@
         <v>400</v>
       </c>
       <c r="R52" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S52" s="13">
         <v>1</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U52" s="16">
         <f t="shared" ref="U52:U57" si="5">U41</f>
@@ -5184,11 +5302,13 @@
       <c r="Y52" s="1">
         <v>1</v>
       </c>
-      <c r="Z52" s="76"/>
-      <c r="AA52" s="77"/>
-      <c r="AB52" s="77"/>
-    </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z52" s="73"/>
+      <c r="AA52" s="74"/>
+      <c r="AB52" s="74"/>
+      <c r="AC52" s="71"/>
+      <c r="AD52" s="71"/>
+    </row>
+    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>150</v>
       </c>
@@ -5241,13 +5361,13 @@
         <v>400</v>
       </c>
       <c r="R53" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S53" s="13">
         <v>1</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U53" s="16">
         <f t="shared" si="5"/>
@@ -5266,11 +5386,13 @@
       <c r="Y53" s="1">
         <v>1</v>
       </c>
-      <c r="Z53" s="76"/>
-      <c r="AA53" s="77"/>
-      <c r="AB53" s="77"/>
-    </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z53" s="73"/>
+      <c r="AA53" s="74"/>
+      <c r="AB53" s="74"/>
+      <c r="AC53" s="71"/>
+      <c r="AD53" s="71"/>
+    </row>
+    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>151</v>
       </c>
@@ -5323,13 +5445,13 @@
         <v>400</v>
       </c>
       <c r="R54" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S54" s="13">
         <v>1</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U54" s="16">
         <f t="shared" si="5"/>
@@ -5348,12 +5470,14 @@
       <c r="Y54" s="1">
         <v>1</v>
       </c>
-      <c r="Z54" s="76"/>
-      <c r="AA54" s="77"/>
-      <c r="AB54" s="77"/>
-    </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A55" s="61">
+      <c r="Z54" s="73"/>
+      <c r="AA54" s="74"/>
+      <c r="AB54" s="74"/>
+      <c r="AC54" s="71"/>
+      <c r="AD54" s="71"/>
+    </row>
+    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A55" s="60">
         <v>152</v>
       </c>
       <c r="B55" s="13">
@@ -5405,13 +5529,13 @@
         <v>400</v>
       </c>
       <c r="R55" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S55" s="13">
         <v>1</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U55" s="16">
         <f t="shared" si="5"/>
@@ -5430,12 +5554,14 @@
       <c r="Y55" s="1">
         <v>1</v>
       </c>
-      <c r="Z55" s="76"/>
-      <c r="AA55" s="77"/>
-      <c r="AB55" s="77"/>
-    </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A56" s="61">
+      <c r="Z55" s="73"/>
+      <c r="AA55" s="74"/>
+      <c r="AB55" s="74"/>
+      <c r="AC55" s="71"/>
+      <c r="AD55" s="71"/>
+    </row>
+    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A56" s="60">
         <v>153</v>
       </c>
       <c r="B56" s="13">
@@ -5487,13 +5613,13 @@
         <v>400</v>
       </c>
       <c r="R56" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S56" s="13">
         <v>1</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U56" s="16">
         <f t="shared" si="5"/>
@@ -5512,177 +5638,183 @@
       <c r="Y56" s="1">
         <v>1</v>
       </c>
-      <c r="Z56" s="76"/>
-      <c r="AA56" s="77"/>
-      <c r="AB56" s="77"/>
-    </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A57" s="63">
+      <c r="Z56" s="73"/>
+      <c r="AA56" s="74"/>
+      <c r="AB56" s="74"/>
+      <c r="AC56" s="71"/>
+      <c r="AD56" s="71"/>
+    </row>
+    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A57" s="62">
         <v>154</v>
       </c>
-      <c r="B57" s="26">
-        <v>12</v>
-      </c>
-      <c r="C57" s="30">
+      <c r="B57" s="25">
+        <v>12</v>
+      </c>
+      <c r="C57" s="29">
         <v>2000</v>
       </c>
-      <c r="D57" s="27">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E57" s="27">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F57" s="28">
-        <v>5</v>
-      </c>
-      <c r="G57" s="27">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H57" s="27">
+      <c r="D57" s="26">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E57" s="26">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F57" s="27">
+        <v>5</v>
+      </c>
+      <c r="G57" s="26">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H57" s="26">
         <v>100</v>
       </c>
-      <c r="I57" s="26">
-        <v>1</v>
-      </c>
-      <c r="J57" s="29">
-        <v>1E-4</v>
-      </c>
-      <c r="K57" s="26">
-        <v>2</v>
-      </c>
-      <c r="L57" s="28">
-        <v>2</v>
-      </c>
-      <c r="M57" s="27">
-        <v>4.2000000000000002E-4</v>
-      </c>
-      <c r="N57" s="26">
+      <c r="I57" s="25">
+        <v>1</v>
+      </c>
+      <c r="J57" s="28">
+        <v>1E-4</v>
+      </c>
+      <c r="K57" s="25">
+        <v>2</v>
+      </c>
+      <c r="L57" s="27">
+        <v>2</v>
+      </c>
+      <c r="M57" s="26">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N57" s="25">
         <v>150</v>
       </c>
-      <c r="O57" s="26">
-        <v>0.2</v>
-      </c>
-      <c r="P57" s="26">
-        <v>300</v>
-      </c>
-      <c r="Q57" s="28">
-        <v>400</v>
-      </c>
-      <c r="R57" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="S57" s="26">
-        <v>1</v>
-      </c>
-      <c r="T57" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="U57" s="27">
+      <c r="O57" s="25">
+        <v>0.2</v>
+      </c>
+      <c r="P57" s="25">
+        <v>300</v>
+      </c>
+      <c r="Q57" s="27">
+        <v>400</v>
+      </c>
+      <c r="R57" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="S57" s="25">
+        <v>1</v>
+      </c>
+      <c r="T57" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="U57" s="26">
         <f t="shared" si="5"/>
         <v>1.4228483264088499E+21</v>
       </c>
-      <c r="V57" s="26">
+      <c r="V57" s="25">
         <f t="shared" si="2"/>
         <v>125520</v>
       </c>
-      <c r="W57" s="26">
-        <v>0</v>
-      </c>
-      <c r="X57" s="30">
-        <v>1</v>
-      </c>
-      <c r="Y57" s="28">
-        <v>1</v>
-      </c>
-      <c r="Z57" s="76"/>
-      <c r="AA57" s="77"/>
-      <c r="AB57" s="77"/>
-    </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A58" s="57">
+      <c r="W57" s="25">
+        <v>0</v>
+      </c>
+      <c r="X57" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y57" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z57" s="73"/>
+      <c r="AA57" s="74"/>
+      <c r="AB57" s="74"/>
+      <c r="AC57" s="71"/>
+      <c r="AD57" s="71"/>
+    </row>
+    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A58" s="56">
         <v>155</v>
       </c>
-      <c r="B58" s="36">
-        <v>12</v>
-      </c>
-      <c r="C58" s="36">
+      <c r="B58" s="35">
+        <v>12</v>
+      </c>
+      <c r="C58" s="35">
         <v>2000</v>
       </c>
-      <c r="D58" s="55">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E58" s="55">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F58" s="54">
-        <v>5</v>
-      </c>
-      <c r="G58" s="55">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H58" s="55">
+      <c r="D58" s="54">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E58" s="54">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F58" s="53">
+        <v>5</v>
+      </c>
+      <c r="G58" s="54">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H58" s="54">
         <v>100</v>
       </c>
-      <c r="I58" s="36">
-        <v>1</v>
-      </c>
-      <c r="J58" s="56">
-        <v>1E-4</v>
-      </c>
-      <c r="K58" s="36">
-        <v>2</v>
-      </c>
-      <c r="L58" s="54">
-        <v>2</v>
-      </c>
-      <c r="M58" s="55">
-        <v>4.2000000000000002E-4</v>
-      </c>
-      <c r="N58" s="36">
+      <c r="I58" s="35">
+        <v>1</v>
+      </c>
+      <c r="J58" s="55">
+        <v>1E-4</v>
+      </c>
+      <c r="K58" s="35">
+        <v>2</v>
+      </c>
+      <c r="L58" s="53">
+        <v>2</v>
+      </c>
+      <c r="M58" s="54">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N58" s="35">
         <v>3000</v>
       </c>
-      <c r="O58" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="P58" s="36">
-        <v>300</v>
-      </c>
-      <c r="Q58" s="54">
-        <v>400</v>
-      </c>
-      <c r="R58" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="S58" s="36">
-        <v>1</v>
-      </c>
-      <c r="T58" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="U58" s="55">
+      <c r="O58" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="P58" s="35">
+        <v>300</v>
+      </c>
+      <c r="Q58" s="53">
+        <v>400</v>
+      </c>
+      <c r="R58" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="S58" s="35">
+        <v>1</v>
+      </c>
+      <c r="T58" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="U58" s="54">
         <v>81600000000000</v>
       </c>
-      <c r="V58" s="36">
+      <c r="V58" s="35">
         <f t="shared" si="2"/>
         <v>125520</v>
       </c>
-      <c r="W58" s="36">
-        <v>0</v>
-      </c>
-      <c r="X58" s="36">
-        <v>1</v>
-      </c>
-      <c r="Y58" s="54">
-        <v>1</v>
-      </c>
-      <c r="Z58" s="73" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA58" s="75"/>
-      <c r="AB58" s="75"/>
-    </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A59" s="51">
+      <c r="W58" s="35">
+        <v>0</v>
+      </c>
+      <c r="X58" s="35">
+        <v>1</v>
+      </c>
+      <c r="Y58" s="53">
+        <v>1</v>
+      </c>
+      <c r="Z58" s="76" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA58" s="77"/>
+      <c r="AB58" s="77"/>
+      <c r="AC58" s="71"/>
+      <c r="AD58" s="71"/>
+    </row>
+    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A59" s="50">
         <v>156</v>
       </c>
       <c r="B59" s="15">
@@ -5691,34 +5823,34 @@
       <c r="C59" s="15">
         <v>2000</v>
       </c>
-      <c r="D59" s="52">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E59" s="52">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F59" s="51">
-        <v>5</v>
-      </c>
-      <c r="G59" s="52">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H59" s="52">
+      <c r="D59" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E59" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F59" s="50">
+        <v>5</v>
+      </c>
+      <c r="G59" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H59" s="51">
         <v>100</v>
       </c>
       <c r="I59" s="15">
         <v>1</v>
       </c>
-      <c r="J59" s="53">
+      <c r="J59" s="52">
         <v>1E-4</v>
       </c>
       <c r="K59" s="15">
         <v>2</v>
       </c>
-      <c r="L59" s="51">
-        <v>2</v>
-      </c>
-      <c r="M59" s="52">
+      <c r="L59" s="50">
+        <v>2</v>
+      </c>
+      <c r="M59" s="51">
         <v>4.2000000000000002E-4</v>
       </c>
       <c r="N59" s="15">
@@ -5730,19 +5862,19 @@
       <c r="P59" s="15">
         <v>300</v>
       </c>
-      <c r="Q59" s="51">
+      <c r="Q59" s="50">
         <v>400</v>
       </c>
       <c r="R59" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S59" s="15">
         <v>1</v>
       </c>
-      <c r="T59" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="U59" s="52">
+      <c r="T59" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="U59" s="51">
         <v>81600000000000</v>
       </c>
       <c r="V59" s="15">
@@ -5755,17 +5887,19 @@
       <c r="X59" s="15">
         <v>1</v>
       </c>
-      <c r="Y59" s="51">
-        <v>1</v>
-      </c>
-      <c r="Z59" s="76" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA59" s="77"/>
-      <c r="AB59" s="77"/>
-    </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A60" s="51">
+      <c r="Y59" s="50">
+        <v>1</v>
+      </c>
+      <c r="Z59" s="73" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA59" s="74"/>
+      <c r="AB59" s="74"/>
+      <c r="AC59" s="71"/>
+      <c r="AD59" s="71"/>
+    </row>
+    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A60" s="50">
         <v>157</v>
       </c>
       <c r="B60" s="15">
@@ -5774,34 +5908,34 @@
       <c r="C60" s="15">
         <v>2000</v>
       </c>
-      <c r="D60" s="52">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E60" s="52">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F60" s="51">
-        <v>5</v>
-      </c>
-      <c r="G60" s="52">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H60" s="52">
+      <c r="D60" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E60" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F60" s="50">
+        <v>5</v>
+      </c>
+      <c r="G60" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H60" s="51">
         <v>100</v>
       </c>
       <c r="I60" s="15">
         <v>1</v>
       </c>
-      <c r="J60" s="53">
+      <c r="J60" s="52">
         <v>1E-4</v>
       </c>
       <c r="K60" s="15">
         <v>2</v>
       </c>
-      <c r="L60" s="51">
-        <v>2</v>
-      </c>
-      <c r="M60" s="52">
+      <c r="L60" s="50">
+        <v>2</v>
+      </c>
+      <c r="M60" s="51">
         <v>4.2000000000000002E-4</v>
       </c>
       <c r="N60" s="15">
@@ -5813,19 +5947,19 @@
       <c r="P60" s="15">
         <v>300</v>
       </c>
-      <c r="Q60" s="51">
+      <c r="Q60" s="50">
         <v>400</v>
       </c>
       <c r="R60" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S60" s="15">
         <v>1</v>
       </c>
-      <c r="T60" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="U60" s="52">
+      <c r="T60" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="U60" s="51">
         <v>81600000000000</v>
       </c>
       <c r="V60" s="15">
@@ -5838,14 +5972,16 @@
       <c r="X60" s="15">
         <v>1</v>
       </c>
-      <c r="Y60" s="51">
-        <v>1</v>
-      </c>
-      <c r="Z60" s="76"/>
-      <c r="AA60" s="77"/>
-      <c r="AB60" s="77"/>
-    </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Y60" s="50">
+        <v>1</v>
+      </c>
+      <c r="Z60" s="73"/>
+      <c r="AA60" s="74"/>
+      <c r="AB60" s="74"/>
+      <c r="AC60" s="71"/>
+      <c r="AD60" s="71"/>
+    </row>
+    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>158</v>
       </c>
@@ -5855,34 +5991,34 @@
       <c r="C61" s="15">
         <v>2000</v>
       </c>
-      <c r="D61" s="52">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E61" s="52">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F61" s="51">
-        <v>5</v>
-      </c>
-      <c r="G61" s="52">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H61" s="52">
+      <c r="D61" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E61" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F61" s="50">
+        <v>5</v>
+      </c>
+      <c r="G61" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H61" s="51">
         <v>100</v>
       </c>
       <c r="I61" s="15">
         <v>1</v>
       </c>
-      <c r="J61" s="53">
+      <c r="J61" s="52">
         <v>1E-4</v>
       </c>
       <c r="K61" s="15">
         <v>2</v>
       </c>
-      <c r="L61" s="51">
-        <v>2</v>
-      </c>
-      <c r="M61" s="52">
+      <c r="L61" s="50">
+        <v>2</v>
+      </c>
+      <c r="M61" s="51">
         <v>4.2000000000000002E-4</v>
       </c>
       <c r="N61" s="15">
@@ -5894,19 +6030,19 @@
       <c r="P61" s="15">
         <v>300</v>
       </c>
-      <c r="Q61" s="51">
+      <c r="Q61" s="50">
         <v>400</v>
       </c>
       <c r="R61" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S61" s="15">
         <v>1</v>
       </c>
-      <c r="T61" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="U61" s="52">
+      <c r="T61" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="U61" s="51">
         <v>81600000000000</v>
       </c>
       <c r="V61" s="15">
@@ -5919,15 +6055,17 @@
       <c r="X61" s="15">
         <v>1</v>
       </c>
-      <c r="Y61" s="51">
-        <v>1</v>
-      </c>
-      <c r="Z61" s="76"/>
-      <c r="AA61" s="77"/>
-      <c r="AB61" s="77"/>
-    </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A62" s="51">
+      <c r="Y61" s="50">
+        <v>1</v>
+      </c>
+      <c r="Z61" s="73"/>
+      <c r="AA61" s="74"/>
+      <c r="AB61" s="74"/>
+      <c r="AC61" s="71"/>
+      <c r="AD61" s="71"/>
+    </row>
+    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A62" s="50">
         <v>159</v>
       </c>
       <c r="B62" s="15">
@@ -5936,34 +6074,34 @@
       <c r="C62" s="15">
         <v>2000</v>
       </c>
-      <c r="D62" s="52">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E62" s="52">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F62" s="51">
-        <v>5</v>
-      </c>
-      <c r="G62" s="52">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H62" s="52">
+      <c r="D62" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E62" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F62" s="50">
+        <v>5</v>
+      </c>
+      <c r="G62" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H62" s="51">
         <v>100</v>
       </c>
       <c r="I62" s="15">
         <v>1</v>
       </c>
-      <c r="J62" s="53">
+      <c r="J62" s="52">
         <v>1E-4</v>
       </c>
       <c r="K62" s="15">
         <v>2</v>
       </c>
-      <c r="L62" s="51">
-        <v>2</v>
-      </c>
-      <c r="M62" s="52">
+      <c r="L62" s="50">
+        <v>2</v>
+      </c>
+      <c r="M62" s="51">
         <v>4.2000000000000002E-4</v>
       </c>
       <c r="N62" s="15">
@@ -5975,19 +6113,19 @@
       <c r="P62" s="15">
         <v>300</v>
       </c>
-      <c r="Q62" s="51">
+      <c r="Q62" s="50">
         <v>400</v>
       </c>
       <c r="R62" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S62" s="15">
         <v>1</v>
       </c>
-      <c r="T62" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="U62" s="52">
+      <c r="T62" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="U62" s="51">
         <v>81600000000000</v>
       </c>
       <c r="V62" s="15">
@@ -6000,14 +6138,16 @@
       <c r="X62" s="15">
         <v>1</v>
       </c>
-      <c r="Y62" s="51">
-        <v>1</v>
-      </c>
-      <c r="Z62" s="76"/>
-      <c r="AA62" s="77"/>
-      <c r="AB62" s="77"/>
-    </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Y62" s="50">
+        <v>1</v>
+      </c>
+      <c r="Z62" s="73"/>
+      <c r="AA62" s="74"/>
+      <c r="AB62" s="74"/>
+      <c r="AC62" s="71"/>
+      <c r="AD62" s="71"/>
+    </row>
+    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>160</v>
       </c>
@@ -6017,34 +6157,34 @@
       <c r="C63" s="15">
         <v>2000</v>
       </c>
-      <c r="D63" s="52">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E63" s="52">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F63" s="51">
-        <v>5</v>
-      </c>
-      <c r="G63" s="52">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H63" s="52">
+      <c r="D63" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E63" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F63" s="50">
+        <v>5</v>
+      </c>
+      <c r="G63" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H63" s="51">
         <v>100</v>
       </c>
       <c r="I63" s="15">
         <v>1</v>
       </c>
-      <c r="J63" s="53">
+      <c r="J63" s="52">
         <v>1E-4</v>
       </c>
       <c r="K63" s="15">
         <v>2</v>
       </c>
-      <c r="L63" s="51">
-        <v>2</v>
-      </c>
-      <c r="M63" s="52">
+      <c r="L63" s="50">
+        <v>2</v>
+      </c>
+      <c r="M63" s="51">
         <v>4.2000000000000002E-4</v>
       </c>
       <c r="N63" s="15">
@@ -6056,19 +6196,19 @@
       <c r="P63" s="15">
         <v>300</v>
       </c>
-      <c r="Q63" s="51">
+      <c r="Q63" s="50">
         <v>400</v>
       </c>
       <c r="R63" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S63" s="15">
         <v>1</v>
       </c>
-      <c r="T63" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="U63" s="52">
+      <c r="T63" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="U63" s="51">
         <v>81600000000000</v>
       </c>
       <c r="V63" s="15">
@@ -6081,15 +6221,17 @@
       <c r="X63" s="15">
         <v>1</v>
       </c>
-      <c r="Y63" s="51">
-        <v>1</v>
-      </c>
-      <c r="Z63" s="76"/>
-      <c r="AA63" s="77"/>
-      <c r="AB63" s="77"/>
-    </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A64" s="51">
+      <c r="Y63" s="50">
+        <v>1</v>
+      </c>
+      <c r="Z63" s="73"/>
+      <c r="AA63" s="74"/>
+      <c r="AB63" s="74"/>
+      <c r="AC63" s="71"/>
+      <c r="AD63" s="71"/>
+    </row>
+    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A64" s="50">
         <v>161</v>
       </c>
       <c r="B64" s="15">
@@ -6098,34 +6240,34 @@
       <c r="C64" s="15">
         <v>2000</v>
       </c>
-      <c r="D64" s="52">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E64" s="52">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F64" s="51">
-        <v>5</v>
-      </c>
-      <c r="G64" s="52">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H64" s="52">
+      <c r="D64" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E64" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F64" s="50">
+        <v>5</v>
+      </c>
+      <c r="G64" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H64" s="51">
         <v>100</v>
       </c>
       <c r="I64" s="15">
         <v>1</v>
       </c>
-      <c r="J64" s="53">
+      <c r="J64" s="52">
         <v>1E-4</v>
       </c>
       <c r="K64" s="15">
         <v>2</v>
       </c>
-      <c r="L64" s="51">
-        <v>2</v>
-      </c>
-      <c r="M64" s="52">
+      <c r="L64" s="50">
+        <v>2</v>
+      </c>
+      <c r="M64" s="51">
         <v>4.2000000000000002E-4</v>
       </c>
       <c r="N64" s="15">
@@ -6137,19 +6279,19 @@
       <c r="P64" s="15">
         <v>300</v>
       </c>
-      <c r="Q64" s="51">
+      <c r="Q64" s="50">
         <v>400</v>
       </c>
       <c r="R64" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S64" s="15">
         <v>1</v>
       </c>
-      <c r="T64" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="U64" s="52">
+      <c r="T64" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="U64" s="51">
         <v>81600000000000</v>
       </c>
       <c r="V64" s="15">
@@ -6162,14 +6304,16 @@
       <c r="X64" s="15">
         <v>1</v>
       </c>
-      <c r="Y64" s="51">
-        <v>1</v>
-      </c>
-      <c r="Z64" s="76"/>
-      <c r="AA64" s="77"/>
-      <c r="AB64" s="77"/>
-    </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Y64" s="50">
+        <v>1</v>
+      </c>
+      <c r="Z64" s="73"/>
+      <c r="AA64" s="74"/>
+      <c r="AB64" s="74"/>
+      <c r="AC64" s="71"/>
+      <c r="AD64" s="71"/>
+    </row>
+    <row r="65" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>162</v>
       </c>
@@ -6179,34 +6323,34 @@
       <c r="C65" s="15">
         <v>2000</v>
       </c>
-      <c r="D65" s="52">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E65" s="52">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F65" s="51">
-        <v>5</v>
-      </c>
-      <c r="G65" s="52">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H65" s="52">
+      <c r="D65" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E65" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F65" s="50">
+        <v>5</v>
+      </c>
+      <c r="G65" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H65" s="51">
         <v>100</v>
       </c>
       <c r="I65" s="15">
         <v>1</v>
       </c>
-      <c r="J65" s="53">
+      <c r="J65" s="52">
         <v>1E-4</v>
       </c>
       <c r="K65" s="15">
         <v>2</v>
       </c>
-      <c r="L65" s="51">
-        <v>2</v>
-      </c>
-      <c r="M65" s="52">
+      <c r="L65" s="50">
+        <v>2</v>
+      </c>
+      <c r="M65" s="51">
         <v>4.2000000000000002E-4</v>
       </c>
       <c r="N65" s="15">
@@ -6218,19 +6362,19 @@
       <c r="P65" s="15">
         <v>300</v>
       </c>
-      <c r="Q65" s="51">
+      <c r="Q65" s="50">
         <v>400</v>
       </c>
       <c r="R65" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S65" s="15">
         <v>1</v>
       </c>
-      <c r="T65" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="U65" s="52">
+      <c r="T65" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="U65" s="51">
         <v>81600000000000</v>
       </c>
       <c r="V65" s="15">
@@ -6243,179 +6387,185 @@
       <c r="X65" s="15">
         <v>1</v>
       </c>
-      <c r="Y65" s="51">
-        <v>1</v>
-      </c>
-      <c r="Z65" s="76"/>
-      <c r="AA65" s="77"/>
-      <c r="AB65" s="77"/>
-    </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A66" s="58">
+      <c r="Y65" s="50">
+        <v>1</v>
+      </c>
+      <c r="Z65" s="73"/>
+      <c r="AA65" s="74"/>
+      <c r="AB65" s="74"/>
+      <c r="AC65" s="71"/>
+      <c r="AD65" s="71"/>
+    </row>
+    <row r="66" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A66" s="57">
         <v>163</v>
       </c>
-      <c r="B66" s="30">
-        <v>12</v>
-      </c>
-      <c r="C66" s="30">
+      <c r="B66" s="29">
+        <v>12</v>
+      </c>
+      <c r="C66" s="29">
         <v>2000</v>
       </c>
-      <c r="D66" s="59">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E66" s="59">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F66" s="58">
-        <v>5</v>
-      </c>
-      <c r="G66" s="59">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H66" s="59">
+      <c r="D66" s="58">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E66" s="58">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F66" s="57">
+        <v>5</v>
+      </c>
+      <c r="G66" s="58">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H66" s="58">
         <v>100</v>
       </c>
-      <c r="I66" s="30">
-        <v>1</v>
-      </c>
-      <c r="J66" s="60">
-        <v>1E-4</v>
-      </c>
-      <c r="K66" s="30">
-        <v>2</v>
-      </c>
-      <c r="L66" s="58">
-        <v>2</v>
-      </c>
-      <c r="M66" s="59">
-        <v>4.2000000000000002E-4</v>
-      </c>
-      <c r="N66" s="30">
+      <c r="I66" s="29">
+        <v>1</v>
+      </c>
+      <c r="J66" s="59">
+        <v>1E-4</v>
+      </c>
+      <c r="K66" s="29">
+        <v>2</v>
+      </c>
+      <c r="L66" s="57">
+        <v>2</v>
+      </c>
+      <c r="M66" s="58">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N66" s="29">
         <v>150</v>
       </c>
-      <c r="O66" s="30">
-        <v>0.2</v>
-      </c>
-      <c r="P66" s="30">
-        <v>300</v>
-      </c>
-      <c r="Q66" s="58">
-        <v>400</v>
-      </c>
-      <c r="R66" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="S66" s="30">
-        <v>1</v>
-      </c>
-      <c r="T66" s="58" t="s">
-        <v>11</v>
-      </c>
-      <c r="U66" s="59">
+      <c r="O66" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="P66" s="29">
+        <v>300</v>
+      </c>
+      <c r="Q66" s="57">
+        <v>400</v>
+      </c>
+      <c r="R66" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="S66" s="29">
+        <v>1</v>
+      </c>
+      <c r="T66" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="U66" s="58">
         <v>81600000000000</v>
       </c>
-      <c r="V66" s="30">
+      <c r="V66" s="29">
         <f>50*4184</f>
         <v>209200</v>
       </c>
-      <c r="W66" s="30">
-        <v>0</v>
-      </c>
-      <c r="X66" s="30">
-        <v>1</v>
-      </c>
-      <c r="Y66" s="58">
-        <v>1</v>
-      </c>
-      <c r="Z66" s="76"/>
-      <c r="AA66" s="77"/>
-      <c r="AB66" s="77"/>
-    </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A67" s="47">
+      <c r="W66" s="29">
+        <v>0</v>
+      </c>
+      <c r="X66" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y66" s="57">
+        <v>1</v>
+      </c>
+      <c r="Z66" s="73"/>
+      <c r="AA66" s="74"/>
+      <c r="AB66" s="74"/>
+      <c r="AC66" s="71"/>
+      <c r="AD66" s="71"/>
+    </row>
+    <row r="67" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A67" s="46">
         <v>164</v>
       </c>
-      <c r="B67" s="64">
-        <v>12</v>
-      </c>
-      <c r="C67" s="46">
+      <c r="B67" s="63">
+        <v>12</v>
+      </c>
+      <c r="C67" s="45">
         <v>2000</v>
       </c>
-      <c r="D67" s="43">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E67" s="43">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F67" s="44">
-        <v>5</v>
-      </c>
-      <c r="G67" s="43">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H67" s="43">
+      <c r="D67" s="42">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E67" s="42">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F67" s="43">
+        <v>5</v>
+      </c>
+      <c r="G67" s="42">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H67" s="42">
         <v>100</v>
       </c>
-      <c r="I67" s="42">
-        <v>1</v>
-      </c>
-      <c r="J67" s="45">
-        <v>1E-4</v>
-      </c>
-      <c r="K67" s="42">
-        <v>2</v>
-      </c>
-      <c r="L67" s="44">
-        <v>2</v>
-      </c>
-      <c r="M67" s="43">
-        <v>4.2000000000000002E-4</v>
-      </c>
-      <c r="N67" s="42">
+      <c r="I67" s="41">
+        <v>1</v>
+      </c>
+      <c r="J67" s="44">
+        <v>1E-4</v>
+      </c>
+      <c r="K67" s="41">
+        <v>2</v>
+      </c>
+      <c r="L67" s="43">
+        <v>2</v>
+      </c>
+      <c r="M67" s="42">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N67" s="41">
         <v>150</v>
       </c>
-      <c r="O67" s="42">
-        <v>0.2</v>
-      </c>
-      <c r="P67" s="42">
-        <v>300</v>
-      </c>
-      <c r="Q67" s="44">
-        <v>400</v>
-      </c>
-      <c r="R67" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="S67" s="42">
-        <v>1</v>
-      </c>
-      <c r="T67" s="44" t="s">
-        <v>11</v>
+      <c r="O67" s="41">
+        <v>0.2</v>
+      </c>
+      <c r="P67" s="41">
+        <v>300</v>
+      </c>
+      <c r="Q67" s="43">
+        <v>400</v>
+      </c>
+      <c r="R67" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="S67" s="41">
+        <v>1</v>
+      </c>
+      <c r="T67" s="43" t="s">
+        <v>10</v>
       </c>
       <c r="U67" s="16">
         <f>U51</f>
         <v>2.2232005100138279E+19</v>
       </c>
       <c r="V67" s="13">
-        <f t="shared" ref="V67:V88" si="6">30*4184</f>
+        <f t="shared" ref="V67:V93" si="6">30*4184</f>
         <v>125520</v>
       </c>
-      <c r="W67" s="42">
-        <v>0</v>
-      </c>
-      <c r="X67" s="46">
-        <v>1</v>
-      </c>
-      <c r="Y67" s="44">
-        <v>1</v>
-      </c>
-      <c r="Z67" s="76" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA67" s="78"/>
-      <c r="AB67" s="78"/>
-    </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="W67" s="41">
+        <v>0</v>
+      </c>
+      <c r="X67" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y67" s="43">
+        <v>1</v>
+      </c>
+      <c r="Z67" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA67" s="79"/>
+      <c r="AB67" s="79"/>
+      <c r="AC67" s="71"/>
+      <c r="AD67" s="71"/>
+    </row>
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="22">
         <v>165</v>
       </c>
@@ -6468,13 +6618,13 @@
         <v>400</v>
       </c>
       <c r="R68" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S68" s="13">
         <v>1</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U68" s="19">
         <f>U67/5</f>
@@ -6493,11 +6643,13 @@
       <c r="Y68" s="1">
         <v>1</v>
       </c>
-      <c r="Z68" s="76"/>
-      <c r="AA68" s="78"/>
-      <c r="AB68" s="78"/>
-    </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z68" s="73"/>
+      <c r="AA68" s="79"/>
+      <c r="AB68" s="79"/>
+      <c r="AC68" s="71"/>
+      <c r="AD68" s="71"/>
+    </row>
+    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="22">
         <v>166</v>
       </c>
@@ -6550,13 +6702,13 @@
         <v>400</v>
       </c>
       <c r="R69" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S69" s="13">
         <v>1</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U69" s="19">
         <f t="shared" ref="U69:U84" si="7">U68/5</f>
@@ -6575,11 +6727,13 @@
       <c r="Y69" s="1">
         <v>1</v>
       </c>
-      <c r="Z69" s="76"/>
-      <c r="AA69" s="78"/>
-      <c r="AB69" s="78"/>
-    </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z69" s="73"/>
+      <c r="AA69" s="79"/>
+      <c r="AB69" s="79"/>
+      <c r="AC69" s="71"/>
+      <c r="AD69" s="71"/>
+    </row>
+    <row r="70" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="22">
         <v>167</v>
       </c>
@@ -6632,13 +6786,13 @@
         <v>400</v>
       </c>
       <c r="R70" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S70" s="13">
         <v>1</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U70" s="19">
         <f t="shared" si="7"/>
@@ -6657,12 +6811,14 @@
       <c r="Y70" s="1">
         <v>1</v>
       </c>
-      <c r="Z70" s="76"/>
-      <c r="AA70" s="78"/>
-      <c r="AB70" s="78"/>
-    </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A71" s="61">
+      <c r="Z70" s="73"/>
+      <c r="AA70" s="79"/>
+      <c r="AB70" s="79"/>
+      <c r="AC70" s="71"/>
+      <c r="AD70" s="71"/>
+    </row>
+    <row r="71" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A71" s="60">
         <v>168</v>
       </c>
       <c r="B71" s="13">
@@ -6714,13 +6870,13 @@
         <v>400</v>
       </c>
       <c r="R71" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S71" s="13">
         <v>1</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U71" s="19">
         <f t="shared" si="7"/>
@@ -6739,11 +6895,13 @@
       <c r="Y71" s="1">
         <v>1</v>
       </c>
-      <c r="Z71" s="76"/>
-      <c r="AA71" s="78"/>
-      <c r="AB71" s="78"/>
-    </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z71" s="73"/>
+      <c r="AA71" s="79"/>
+      <c r="AB71" s="79"/>
+      <c r="AC71" s="71"/>
+      <c r="AD71" s="71"/>
+    </row>
+    <row r="72" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="22">
         <v>169</v>
       </c>
@@ -6796,13 +6954,13 @@
         <v>400</v>
       </c>
       <c r="R72" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S72" s="13">
         <v>1</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U72" s="19">
         <f t="shared" si="7"/>
@@ -6821,11 +6979,13 @@
       <c r="Y72" s="1">
         <v>1</v>
       </c>
-      <c r="Z72" s="76"/>
-      <c r="AA72" s="78"/>
-      <c r="AB72" s="78"/>
-    </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z72" s="73"/>
+      <c r="AA72" s="79"/>
+      <c r="AB72" s="79"/>
+      <c r="AC72" s="71"/>
+      <c r="AD72" s="71"/>
+    </row>
+    <row r="73" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A73" s="22">
         <v>170</v>
       </c>
@@ -6878,13 +7038,13 @@
         <v>400</v>
       </c>
       <c r="R73" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S73" s="13">
         <v>1</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U73" s="19">
         <f t="shared" si="7"/>
@@ -6903,11 +7063,13 @@
       <c r="Y73" s="1">
         <v>1</v>
       </c>
-      <c r="Z73" s="76"/>
-      <c r="AA73" s="78"/>
-      <c r="AB73" s="78"/>
-    </row>
-    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z73" s="73"/>
+      <c r="AA73" s="79"/>
+      <c r="AB73" s="79"/>
+      <c r="AC73" s="71"/>
+      <c r="AD73" s="71"/>
+    </row>
+    <row r="74" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A74" s="22">
         <v>171</v>
       </c>
@@ -6960,13 +7122,13 @@
         <v>400</v>
       </c>
       <c r="R74" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S74" s="13">
         <v>1</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U74" s="19">
         <f>U73/5</f>
@@ -6985,11 +7147,13 @@
       <c r="Y74" s="1">
         <v>1</v>
       </c>
-      <c r="Z74" s="76"/>
-      <c r="AA74" s="78"/>
-      <c r="AB74" s="78"/>
-    </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z74" s="73"/>
+      <c r="AA74" s="79"/>
+      <c r="AB74" s="79"/>
+      <c r="AC74" s="71"/>
+      <c r="AD74" s="71"/>
+    </row>
+    <row r="75" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A75" s="22">
         <v>172</v>
       </c>
@@ -7042,13 +7206,13 @@
         <v>400</v>
       </c>
       <c r="R75" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S75" s="13">
         <v>1</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U75" s="19">
         <f t="shared" si="7"/>
@@ -7067,11 +7231,13 @@
       <c r="Y75" s="1">
         <v>1</v>
       </c>
-      <c r="Z75" s="76"/>
-      <c r="AA75" s="78"/>
-      <c r="AB75" s="78"/>
-    </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z75" s="73"/>
+      <c r="AA75" s="79"/>
+      <c r="AB75" s="79"/>
+      <c r="AC75" s="71"/>
+      <c r="AD75" s="71"/>
+    </row>
+    <row r="76" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="22">
         <v>173</v>
       </c>
@@ -7124,13 +7290,13 @@
         <v>400</v>
       </c>
       <c r="R76" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S76" s="13">
         <v>1</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U76" s="19">
         <f>U75/5</f>
@@ -7149,11 +7315,13 @@
       <c r="Y76" s="1">
         <v>1</v>
       </c>
-      <c r="Z76" s="76"/>
-      <c r="AA76" s="78"/>
-      <c r="AB76" s="78"/>
-    </row>
-    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z76" s="73"/>
+      <c r="AA76" s="79"/>
+      <c r="AB76" s="79"/>
+      <c r="AC76" s="71"/>
+      <c r="AD76" s="71"/>
+    </row>
+    <row r="77" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A77" s="22">
         <v>174</v>
       </c>
@@ -7206,13 +7374,13 @@
         <v>400</v>
       </c>
       <c r="R77" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S77" s="13">
         <v>1</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U77" s="19">
         <f t="shared" si="7"/>
@@ -7231,11 +7399,13 @@
       <c r="Y77" s="1">
         <v>1</v>
       </c>
-      <c r="Z77" s="76"/>
-      <c r="AA77" s="78"/>
-      <c r="AB77" s="78"/>
-    </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z77" s="73"/>
+      <c r="AA77" s="79"/>
+      <c r="AB77" s="79"/>
+      <c r="AC77" s="71"/>
+      <c r="AD77" s="71"/>
+    </row>
+    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A78" s="22">
         <v>175</v>
       </c>
@@ -7288,13 +7458,13 @@
         <v>400</v>
       </c>
       <c r="R78" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S78" s="13">
         <v>1</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U78" s="19">
         <f t="shared" si="7"/>
@@ -7313,11 +7483,13 @@
       <c r="Y78" s="1">
         <v>1</v>
       </c>
-      <c r="Z78" s="76"/>
-      <c r="AA78" s="78"/>
-      <c r="AB78" s="78"/>
-    </row>
-    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z78" s="73"/>
+      <c r="AA78" s="79"/>
+      <c r="AB78" s="79"/>
+      <c r="AC78" s="71"/>
+      <c r="AD78" s="71"/>
+    </row>
+    <row r="79" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A79" s="22">
         <v>176</v>
       </c>
@@ -7370,13 +7542,13 @@
         <v>400</v>
       </c>
       <c r="R79" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S79" s="13">
         <v>1</v>
       </c>
       <c r="T79" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U79" s="19">
         <f t="shared" si="7"/>
@@ -7395,11 +7567,13 @@
       <c r="Y79" s="1">
         <v>1</v>
       </c>
-      <c r="Z79" s="76"/>
-      <c r="AA79" s="78"/>
-      <c r="AB79" s="78"/>
-    </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z79" s="73"/>
+      <c r="AA79" s="79"/>
+      <c r="AB79" s="79"/>
+      <c r="AC79" s="71"/>
+      <c r="AD79" s="71"/>
+    </row>
+    <row r="80" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A80" s="22">
         <v>177</v>
       </c>
@@ -7452,13 +7626,13 @@
         <v>400</v>
       </c>
       <c r="R80" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S80" s="13">
         <v>1</v>
       </c>
       <c r="T80" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U80" s="19">
         <f t="shared" si="7"/>
@@ -7477,11 +7651,13 @@
       <c r="Y80" s="1">
         <v>1</v>
       </c>
-      <c r="Z80" s="76"/>
-      <c r="AA80" s="78"/>
-      <c r="AB80" s="78"/>
-    </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z80" s="73"/>
+      <c r="AA80" s="79"/>
+      <c r="AB80" s="79"/>
+      <c r="AC80" s="71"/>
+      <c r="AD80" s="71"/>
+    </row>
+    <row r="81" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A81" s="22">
         <v>178</v>
       </c>
@@ -7534,13 +7710,13 @@
         <v>400</v>
       </c>
       <c r="R81" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S81" s="13">
         <v>1</v>
       </c>
       <c r="T81" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U81" s="19">
         <f>U80/5</f>
@@ -7559,11 +7735,13 @@
       <c r="Y81" s="1">
         <v>1</v>
       </c>
-      <c r="Z81" s="76"/>
-      <c r="AA81" s="78"/>
-      <c r="AB81" s="78"/>
-    </row>
-    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z81" s="73"/>
+      <c r="AA81" s="79"/>
+      <c r="AB81" s="79"/>
+      <c r="AC81" s="71"/>
+      <c r="AD81" s="71"/>
+    </row>
+    <row r="82" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A82" s="22">
         <v>179</v>
       </c>
@@ -7616,13 +7794,13 @@
         <v>400</v>
       </c>
       <c r="R82" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S82" s="13">
         <v>1</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U82" s="19">
         <f t="shared" si="7"/>
@@ -7641,11 +7819,13 @@
       <c r="Y82" s="1">
         <v>1</v>
       </c>
-      <c r="Z82" s="76"/>
-      <c r="AA82" s="78"/>
-      <c r="AB82" s="78"/>
-    </row>
-    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z82" s="73"/>
+      <c r="AA82" s="79"/>
+      <c r="AB82" s="79"/>
+      <c r="AC82" s="71"/>
+      <c r="AD82" s="71"/>
+    </row>
+    <row r="83" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A83" s="22">
         <v>180</v>
       </c>
@@ -7698,13 +7878,13 @@
         <v>400</v>
       </c>
       <c r="R83" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S83" s="13">
         <v>1</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U83" s="19">
         <f t="shared" si="7"/>
@@ -7723,11 +7903,13 @@
       <c r="Y83" s="1">
         <v>1</v>
       </c>
-      <c r="Z83" s="76"/>
-      <c r="AA83" s="78"/>
-      <c r="AB83" s="78"/>
-    </row>
-    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z83" s="73"/>
+      <c r="AA83" s="79"/>
+      <c r="AB83" s="79"/>
+      <c r="AC83" s="71"/>
+      <c r="AD83" s="71"/>
+    </row>
+    <row r="84" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A84" s="22">
         <v>181</v>
       </c>
@@ -7780,13 +7962,13 @@
         <v>400</v>
       </c>
       <c r="R84" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="S84" s="13">
         <v>1</v>
       </c>
       <c r="T84" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U84" s="19">
         <f t="shared" si="7"/>
@@ -7805,359 +7987,805 @@
       <c r="Y84" s="1">
         <v>1</v>
       </c>
-      <c r="Z84" s="76"/>
-      <c r="AA84" s="78"/>
-      <c r="AB84" s="78"/>
-    </row>
-    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A85" s="65">
+      <c r="Z84" s="73"/>
+      <c r="AA84" s="79"/>
+      <c r="AB84" s="79"/>
+      <c r="AC84" s="71"/>
+      <c r="AD84" s="71"/>
+    </row>
+    <row r="85" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A85" s="68">
         <v>182</v>
       </c>
-      <c r="B85" s="36">
-        <v>12</v>
-      </c>
-      <c r="C85" s="36">
+      <c r="B85" s="35">
+        <v>12</v>
+      </c>
+      <c r="C85" s="35">
         <v>2000</v>
       </c>
-      <c r="D85" s="55">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E85" s="55">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F85" s="54">
-        <v>5</v>
-      </c>
-      <c r="G85" s="55">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H85" s="55">
+      <c r="D85" s="54">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E85" s="54">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F85" s="53">
+        <v>5</v>
+      </c>
+      <c r="G85" s="54">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H85" s="54">
         <v>100</v>
       </c>
-      <c r="I85" s="36">
-        <v>1</v>
-      </c>
-      <c r="J85" s="56">
-        <v>1E-4</v>
-      </c>
-      <c r="K85" s="36">
-        <v>2</v>
-      </c>
-      <c r="L85" s="54">
-        <v>2</v>
-      </c>
-      <c r="M85" s="55">
-        <v>4.2000000000000002E-4</v>
-      </c>
-      <c r="N85" s="36">
+      <c r="I85" s="35">
+        <v>1</v>
+      </c>
+      <c r="J85" s="55">
+        <v>1E-4</v>
+      </c>
+      <c r="K85" s="35">
+        <v>2</v>
+      </c>
+      <c r="L85" s="53">
+        <v>2</v>
+      </c>
+      <c r="M85" s="54">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N85" s="35">
         <v>3000</v>
       </c>
-      <c r="O85" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="P85" s="36">
-        <v>300</v>
-      </c>
-      <c r="Q85" s="54">
-        <v>400</v>
-      </c>
-      <c r="R85" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="S85" s="36">
-        <v>1</v>
-      </c>
-      <c r="T85" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="U85" s="55">
+      <c r="O85" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="P85" s="35">
+        <v>300</v>
+      </c>
+      <c r="Q85" s="53">
+        <v>400</v>
+      </c>
+      <c r="R85" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="S85" s="35">
+        <v>1</v>
+      </c>
+      <c r="T85" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="U85" s="54">
         <v>81600000000000</v>
       </c>
-      <c r="V85" s="36">
+      <c r="V85" s="35">
         <f t="shared" si="6"/>
         <v>125520</v>
       </c>
-      <c r="W85" s="36">
-        <v>0</v>
-      </c>
-      <c r="X85" s="36">
-        <v>1</v>
-      </c>
-      <c r="Y85" s="54">
-        <v>1</v>
-      </c>
-      <c r="Z85" s="73" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA85" s="74"/>
-      <c r="AB85" s="74"/>
-    </row>
-    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
+      <c r="W85" s="35">
+        <v>0</v>
+      </c>
+      <c r="X85" s="35">
+        <v>1</v>
+      </c>
+      <c r="Y85" s="53">
+        <v>1</v>
+      </c>
+      <c r="Z85" s="76" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA85" s="80"/>
+      <c r="AB85" s="80"/>
+      <c r="AC85" s="71"/>
+      <c r="AD85" s="71"/>
+    </row>
+    <row r="86" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="43">
         <v>183</v>
       </c>
-      <c r="B86" s="15">
-        <v>12</v>
-      </c>
-      <c r="C86" s="15">
+      <c r="B86" s="45">
+        <v>12</v>
+      </c>
+      <c r="C86" s="45">
         <v>700</v>
       </c>
-      <c r="D86" s="52">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E86" s="52">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F86" s="51">
-        <v>5</v>
-      </c>
-      <c r="G86" s="52">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H86" s="52">
+      <c r="D86" s="47">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E86" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F86" s="40">
+        <v>5</v>
+      </c>
+      <c r="G86" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H86" s="47">
         <v>100</v>
       </c>
-      <c r="I86" s="15">
-        <v>1</v>
-      </c>
-      <c r="J86" s="53">
-        <v>1E-4</v>
-      </c>
-      <c r="K86" s="15">
-        <v>2</v>
-      </c>
-      <c r="L86" s="51">
-        <v>2</v>
-      </c>
-      <c r="M86" s="52">
-        <v>4.2000000000000002E-4</v>
-      </c>
-      <c r="N86" s="15">
+      <c r="I86" s="45">
+        <v>1</v>
+      </c>
+      <c r="J86" s="48">
+        <v>1E-4</v>
+      </c>
+      <c r="K86" s="45">
+        <v>2</v>
+      </c>
+      <c r="L86" s="40">
+        <v>2</v>
+      </c>
+      <c r="M86" s="47">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N86" s="45">
         <v>150</v>
       </c>
-      <c r="O86" s="15">
-        <v>0.2</v>
-      </c>
-      <c r="P86" s="15">
-        <v>300</v>
-      </c>
-      <c r="Q86" s="51">
-        <v>400</v>
-      </c>
-      <c r="R86" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="S86" s="15">
-        <v>1</v>
-      </c>
-      <c r="T86" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="U86" s="52">
+      <c r="O86" s="45">
+        <v>0.2</v>
+      </c>
+      <c r="P86" s="45">
+        <v>300</v>
+      </c>
+      <c r="Q86" s="40">
+        <v>400</v>
+      </c>
+      <c r="R86" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="S86" s="45">
+        <v>1</v>
+      </c>
+      <c r="T86" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="U86" s="47">
         <v>81600000000000</v>
       </c>
-      <c r="V86" s="15">
+      <c r="V86" s="45">
         <f t="shared" si="6"/>
         <v>125520</v>
       </c>
-      <c r="W86" s="15">
-        <v>0</v>
-      </c>
-      <c r="X86" s="15">
-        <v>1</v>
-      </c>
-      <c r="Y86" s="51">
+      <c r="W86" s="45">
+        <v>0</v>
+      </c>
+      <c r="X86" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y86" s="40">
         <v>1</v>
       </c>
       <c r="Z86" s="73" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AA86" s="74"/>
       <c r="AB86" s="74"/>
-    </row>
-    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
+      <c r="AC86" s="71"/>
+      <c r="AD86" s="71"/>
+    </row>
+    <row r="87" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A87" s="27">
         <v>184</v>
       </c>
-      <c r="B87" s="15">
-        <v>12</v>
-      </c>
-      <c r="C87" s="15">
+      <c r="B87" s="29">
+        <v>12</v>
+      </c>
+      <c r="C87" s="29">
         <v>2000</v>
       </c>
-      <c r="D87" s="52">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E87" s="52">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F87" s="51">
-        <v>5</v>
-      </c>
-      <c r="G87" s="52">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H87" s="52">
+      <c r="D87" s="58">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E87" s="58">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F87" s="57">
+        <v>5</v>
+      </c>
+      <c r="G87" s="58">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H87" s="58">
         <v>100</v>
       </c>
-      <c r="I87" s="15">
-        <v>1</v>
-      </c>
-      <c r="J87" s="53">
-        <v>1E-4</v>
-      </c>
-      <c r="K87" s="15">
-        <v>2</v>
-      </c>
-      <c r="L87" s="51">
-        <v>2</v>
-      </c>
-      <c r="M87" s="52">
-        <v>4.2000000000000002E-4</v>
-      </c>
-      <c r="N87" s="15">
+      <c r="I87" s="29">
+        <v>1</v>
+      </c>
+      <c r="J87" s="59">
+        <v>1E-4</v>
+      </c>
+      <c r="K87" s="29">
+        <v>2</v>
+      </c>
+      <c r="L87" s="57">
+        <v>2</v>
+      </c>
+      <c r="M87" s="58">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N87" s="29">
         <v>150</v>
       </c>
-      <c r="O87" s="15">
-        <v>0.2</v>
-      </c>
-      <c r="P87" s="15">
-        <v>300</v>
-      </c>
-      <c r="Q87" s="51">
-        <v>400</v>
-      </c>
-      <c r="R87" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="S87" s="15">
-        <v>1</v>
-      </c>
-      <c r="T87" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="U87" s="52">
+      <c r="O87" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="P87" s="29">
+        <v>300</v>
+      </c>
+      <c r="Q87" s="57">
+        <v>400</v>
+      </c>
+      <c r="R87" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="S87" s="29">
+        <v>1</v>
+      </c>
+      <c r="T87" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="U87" s="58">
         <v>81600000000000</v>
       </c>
-      <c r="V87" s="15">
+      <c r="V87" s="29">
         <f t="shared" si="6"/>
         <v>125520</v>
       </c>
-      <c r="W87" s="15">
-        <v>0</v>
-      </c>
-      <c r="X87" s="15">
-        <v>1</v>
-      </c>
-      <c r="Y87" s="51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A88" s="1">
+      <c r="W87" s="29">
+        <v>0</v>
+      </c>
+      <c r="X87" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y87" s="57">
+        <v>1</v>
+      </c>
+      <c r="Z87" s="73"/>
+      <c r="AA87" s="74"/>
+      <c r="AB87" s="74"/>
+      <c r="AC87" s="71"/>
+      <c r="AD87" s="71"/>
+    </row>
+    <row r="88" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A88" s="33">
         <v>185</v>
       </c>
-      <c r="B88" s="15">
-        <v>12</v>
-      </c>
-      <c r="C88" s="15">
+      <c r="B88" s="35">
+        <v>12</v>
+      </c>
+      <c r="C88" s="35">
         <v>2000</v>
       </c>
-      <c r="D88" s="52">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E88" s="52">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F88" s="51">
-        <v>5</v>
-      </c>
-      <c r="G88" s="52">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="H88" s="52">
+      <c r="D88" s="54">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E88" s="54">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F88" s="53">
+        <v>5</v>
+      </c>
+      <c r="G88" s="54">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H88" s="54">
         <v>100</v>
       </c>
-      <c r="I88" s="15">
-        <v>1</v>
-      </c>
-      <c r="J88" s="53">
-        <v>1E-4</v>
-      </c>
-      <c r="K88" s="15">
-        <v>2</v>
-      </c>
-      <c r="L88" s="51">
-        <v>2</v>
-      </c>
-      <c r="M88" s="52">
-        <v>4.2000000000000002E-4</v>
-      </c>
-      <c r="N88" s="15">
+      <c r="I88" s="35">
+        <v>1</v>
+      </c>
+      <c r="J88" s="55">
+        <v>1E-4</v>
+      </c>
+      <c r="K88" s="35">
+        <v>2</v>
+      </c>
+      <c r="L88" s="53">
+        <v>2</v>
+      </c>
+      <c r="M88" s="54">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N88" s="35">
         <v>150</v>
       </c>
-      <c r="O88" s="15">
-        <v>0.2</v>
-      </c>
-      <c r="P88" s="15">
-        <v>300</v>
-      </c>
-      <c r="Q88" s="51">
+      <c r="O88" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="P88" s="35">
+        <v>300</v>
+      </c>
+      <c r="Q88" s="53">
         <v>2000</v>
       </c>
-      <c r="R88" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="S88" s="15">
-        <v>1</v>
-      </c>
-      <c r="T88" s="51" t="s">
-        <v>11</v>
-      </c>
-      <c r="U88" s="52">
+      <c r="R88" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="S88" s="35">
+        <v>1</v>
+      </c>
+      <c r="T88" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="U88" s="54">
         <v>81600000000000</v>
       </c>
-      <c r="V88" s="15">
+      <c r="V88" s="35">
         <f t="shared" si="6"/>
         <v>125520</v>
       </c>
-      <c r="W88" s="15">
-        <v>0</v>
-      </c>
-      <c r="X88" s="15">
-        <v>1</v>
-      </c>
-      <c r="Y88" s="51">
-        <v>1</v>
-      </c>
+      <c r="W88" s="35">
+        <v>0</v>
+      </c>
+      <c r="X88" s="35">
+        <v>1</v>
+      </c>
+      <c r="Y88" s="53">
+        <v>1</v>
+      </c>
+      <c r="Z88" s="76" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA88" s="80"/>
+      <c r="AB88" s="80"/>
+      <c r="AC88" s="71"/>
+      <c r="AD88" s="71"/>
+    </row>
+    <row r="89" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A89" s="43">
+        <v>186</v>
+      </c>
+      <c r="B89" s="45">
+        <v>12</v>
+      </c>
+      <c r="C89" s="45">
+        <v>2000</v>
+      </c>
+      <c r="D89" s="47">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E89" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F89" s="40">
+        <v>5</v>
+      </c>
+      <c r="G89" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H89" s="47">
+        <v>2</v>
+      </c>
+      <c r="I89" s="45">
+        <v>1</v>
+      </c>
+      <c r="J89" s="48">
+        <v>1E-4</v>
+      </c>
+      <c r="K89" s="45">
+        <v>10</v>
+      </c>
+      <c r="L89" s="40">
+        <v>10</v>
+      </c>
+      <c r="M89" s="47">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N89" s="45">
+        <v>1000</v>
+      </c>
+      <c r="O89" s="45">
+        <v>0.2</v>
+      </c>
+      <c r="P89" s="45">
+        <v>400</v>
+      </c>
+      <c r="Q89" s="40">
+        <v>400</v>
+      </c>
+      <c r="R89" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="S89" s="45">
+        <v>1</v>
+      </c>
+      <c r="T89" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="U89" s="47">
+        <v>81600000000000</v>
+      </c>
+      <c r="V89" s="45">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W89" s="45">
+        <v>0</v>
+      </c>
+      <c r="X89" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y89" s="40">
+        <v>1</v>
+      </c>
+      <c r="Z89" s="76" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA89" s="80"/>
+      <c r="AB89" s="80"/>
+      <c r="AC89" s="71"/>
+      <c r="AD89" s="71"/>
+    </row>
+    <row r="90" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A90" s="27">
+        <v>187</v>
+      </c>
+      <c r="B90" s="29">
+        <v>12</v>
+      </c>
+      <c r="C90" s="29">
+        <v>2000</v>
+      </c>
+      <c r="D90" s="58">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E90" s="58">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F90" s="57">
+        <v>5</v>
+      </c>
+      <c r="G90" s="58">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H90" s="58">
+        <v>2</v>
+      </c>
+      <c r="I90" s="29">
+        <v>1</v>
+      </c>
+      <c r="J90" s="59">
+        <v>1E-4</v>
+      </c>
+      <c r="K90" s="29">
+        <v>10</v>
+      </c>
+      <c r="L90" s="57">
+        <v>10</v>
+      </c>
+      <c r="M90" s="58">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N90" s="29">
+        <v>1000</v>
+      </c>
+      <c r="O90" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="P90" s="29">
+        <v>400</v>
+      </c>
+      <c r="Q90" s="57">
+        <v>400</v>
+      </c>
+      <c r="R90" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="S90" s="29">
+        <v>1</v>
+      </c>
+      <c r="T90" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="U90" s="58">
+        <v>81600000000000</v>
+      </c>
+      <c r="V90" s="29">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W90" s="29">
+        <v>0</v>
+      </c>
+      <c r="X90" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y90" s="57">
+        <v>1</v>
+      </c>
+      <c r="Z90" s="76" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA90" s="80"/>
+      <c r="AB90" s="80"/>
+      <c r="AC90" s="71"/>
+      <c r="AD90" s="71"/>
+    </row>
+    <row r="91" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A91" s="33">
+        <v>188</v>
+      </c>
+      <c r="B91" s="35">
+        <v>12</v>
+      </c>
+      <c r="C91" s="35">
+        <v>2000</v>
+      </c>
+      <c r="D91" s="54">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E91" s="54">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F91" s="53">
+        <v>5</v>
+      </c>
+      <c r="G91" s="54">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H91" s="54">
+        <v>100</v>
+      </c>
+      <c r="I91" s="35">
+        <v>1</v>
+      </c>
+      <c r="J91" s="55">
+        <v>1E-4</v>
+      </c>
+      <c r="K91" s="35">
+        <v>2</v>
+      </c>
+      <c r="L91" s="53">
+        <v>2</v>
+      </c>
+      <c r="M91" s="54">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N91" s="35">
+        <v>150</v>
+      </c>
+      <c r="O91" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="P91" s="35">
+        <v>300</v>
+      </c>
+      <c r="Q91" s="53">
+        <v>1000</v>
+      </c>
+      <c r="R91" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="S91" s="35">
+        <v>1</v>
+      </c>
+      <c r="T91" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="U91" s="54">
+        <v>81600000000000</v>
+      </c>
+      <c r="V91" s="35">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W91" s="35">
+        <v>0</v>
+      </c>
+      <c r="X91" s="35">
+        <v>1</v>
+      </c>
+      <c r="Y91" s="53">
+        <v>1</v>
+      </c>
+      <c r="Z91" s="76" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA91" s="80"/>
+      <c r="AB91" s="80"/>
+      <c r="AC91" s="71"/>
+      <c r="AD91" s="71"/>
+    </row>
+    <row r="92" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A92" s="43">
+        <v>189</v>
+      </c>
+      <c r="B92" s="45">
+        <v>12</v>
+      </c>
+      <c r="C92" s="45">
+        <v>2000</v>
+      </c>
+      <c r="D92" s="47">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E92" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F92" s="40">
+        <v>5</v>
+      </c>
+      <c r="G92" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H92" s="47">
+        <v>1</v>
+      </c>
+      <c r="I92" s="45">
+        <v>1</v>
+      </c>
+      <c r="J92" s="48">
+        <v>1E-4</v>
+      </c>
+      <c r="K92" s="45">
+        <v>2</v>
+      </c>
+      <c r="L92" s="40">
+        <v>2</v>
+      </c>
+      <c r="M92" s="47">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N92" s="45">
+        <v>1000</v>
+      </c>
+      <c r="O92" s="45">
+        <v>0.2</v>
+      </c>
+      <c r="P92" s="45">
+        <v>400</v>
+      </c>
+      <c r="Q92" s="40">
+        <v>400</v>
+      </c>
+      <c r="R92" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="S92" s="45">
+        <v>1</v>
+      </c>
+      <c r="T92" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="U92" s="47">
+        <v>81600000000000</v>
+      </c>
+      <c r="V92" s="45">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W92" s="45">
+        <v>0</v>
+      </c>
+      <c r="X92" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y92" s="40">
+        <v>1</v>
+      </c>
+      <c r="Z92" s="73" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA92" s="74"/>
+      <c r="AB92" s="74"/>
+      <c r="AC92" s="71"/>
+      <c r="AD92" s="71"/>
+    </row>
+    <row r="93" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A93" s="27">
+        <v>190</v>
+      </c>
+      <c r="B93" s="29">
+        <v>12</v>
+      </c>
+      <c r="C93" s="29">
+        <v>1000</v>
+      </c>
+      <c r="D93" s="58">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E93" s="58">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F93" s="57">
+        <v>5</v>
+      </c>
+      <c r="G93" s="58">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H93" s="58">
+        <v>1</v>
+      </c>
+      <c r="I93" s="29">
+        <v>1</v>
+      </c>
+      <c r="J93" s="59">
+        <v>1E-4</v>
+      </c>
+      <c r="K93" s="29">
+        <v>2</v>
+      </c>
+      <c r="L93" s="57">
+        <v>2</v>
+      </c>
+      <c r="M93" s="58">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N93" s="29">
+        <v>1000</v>
+      </c>
+      <c r="O93" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="P93" s="29">
+        <v>400</v>
+      </c>
+      <c r="Q93" s="57">
+        <v>400</v>
+      </c>
+      <c r="R93" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="S93" s="29">
+        <v>1</v>
+      </c>
+      <c r="T93" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="U93" s="58">
+        <v>81600000000000</v>
+      </c>
+      <c r="V93" s="29">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W93" s="29">
+        <v>0</v>
+      </c>
+      <c r="X93" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y93" s="57">
+        <v>1</v>
+      </c>
+      <c r="Z93" s="73"/>
+      <c r="AA93" s="74"/>
+      <c r="AB93" s="74"/>
+      <c r="AC93" s="71"/>
+      <c r="AD93" s="71"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="Z86:AB86"/>
-    <mergeCell ref="Z58:AB58"/>
-    <mergeCell ref="Z51:AB57"/>
+  <mergeCells count="30">
+    <mergeCell ref="Z85:AB85"/>
+    <mergeCell ref="Z67:AB84"/>
+    <mergeCell ref="Z59:AB66"/>
+    <mergeCell ref="Z92:AB93"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="Z6:AB6"/>
+    <mergeCell ref="Z7:AB7"/>
+    <mergeCell ref="Z5:AB5"/>
+    <mergeCell ref="Z4:AB4"/>
+    <mergeCell ref="Z90:AB90"/>
+    <mergeCell ref="Z91:AB91"/>
+    <mergeCell ref="Z8:AD8"/>
+    <mergeCell ref="Z28:AB28"/>
+    <mergeCell ref="Z9:AB9"/>
     <mergeCell ref="Z10:AB27"/>
     <mergeCell ref="Z29:AB46"/>
     <mergeCell ref="Z50:AB50"/>
     <mergeCell ref="Z48:AB48"/>
     <mergeCell ref="Z47:AB47"/>
     <mergeCell ref="Z49:AB49"/>
-    <mergeCell ref="Z85:AB85"/>
-    <mergeCell ref="Z67:AB84"/>
-    <mergeCell ref="Z59:AB66"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="Z8:AD8"/>
-    <mergeCell ref="Z28:AB28"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="U1:Y1"/>
-    <mergeCell ref="Z6:AB6"/>
-    <mergeCell ref="Z7:AB7"/>
-    <mergeCell ref="Z5:AB5"/>
-    <mergeCell ref="Z4:AB4"/>
+    <mergeCell ref="Z89:AB89"/>
+    <mergeCell ref="Z88:AB88"/>
+    <mergeCell ref="Z86:AB87"/>
+    <mergeCell ref="Z58:AB58"/>
+    <mergeCell ref="Z51:AB57"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Simulations_IDS.xlsx
+++ b/Simulations_IDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documentos_Betran\DropletEvaporation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E800F29-41CD-422B-816C-36B8A6D3B663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25AB51CC-01CC-4C64-AC39-FFA5DF945067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{73239687-5BB6-4FA0-A3B4-8BE280184789}"/>
   </bookViews>
@@ -37,12 +37,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="81">
   <si>
     <t>ID</t>
-  </si>
-  <si>
-    <t>Elems Liq</t>
   </si>
   <si>
     <t>Elems Gas</t>
@@ -244,6 +241,45 @@
   </si>
   <si>
     <t>Fuel</t>
+  </si>
+  <si>
+    <t>104 pero rhoCte sin picos</t>
+  </si>
+  <si>
+    <t>104 pero rhoCte sin picos, rho_g = 0.2</t>
+  </si>
+  <si>
+    <t>Elems</t>
+  </si>
+  <si>
+    <t>104 per rhoCte sin picos, rho_g = 0.2</t>
+  </si>
+  <si>
+    <t>104 per rhoCte sin picos, rho_g = 0.5</t>
+  </si>
+  <si>
+    <t>Millan rhoCte=0.5</t>
+  </si>
+  <si>
+    <t>104 pero rhoCte sin picos, rho_g = 0.5, D_gas = 5e-7</t>
+  </si>
+  <si>
+    <t>104 pero rhoCte sin picos, rho_g = 0.5, D_gas = 1e-3</t>
+  </si>
+  <si>
+    <t>183 pero D_O2 = 3*D_comun</t>
+  </si>
+  <si>
+    <t>183 pero D_Heptano = D_comun/2.85</t>
+  </si>
+  <si>
+    <t>183 pero D_Heptano = D_comun/1.5</t>
+  </si>
+  <si>
+    <t>183 pero D_i != D_i-1</t>
+  </si>
+  <si>
+    <t>183 pero D_inertes = D_comun/x</t>
   </si>
 </sst>
 </file>
@@ -532,7 +568,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -597,30 +633,36 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -629,22 +671,31 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -960,11 +1011,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC78505-487D-4D76-94E1-903AFBAADA28}">
-  <dimension ref="A1:AF93"/>
+  <dimension ref="A1:AF170"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="2.140625" style="1" bestFit="1" customWidth="1"/>
@@ -990,187 +1041,191 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="B1" s="66" t="s">
+      <c r="B1" s="81" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="67" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="64" t="s">
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="84"/>
+      <c r="K1" s="83" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="84"/>
+      <c r="M1" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="65"/>
-      <c r="M1" s="67" t="s">
+      <c r="N1" s="83"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="64"/>
-      <c r="O1" s="64"/>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="67" t="s">
+      <c r="S1" s="83"/>
+      <c r="T1" s="83"/>
+      <c r="U1" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="S1" s="64"/>
-      <c r="T1" s="64"/>
-      <c r="U1" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="V1" s="64"/>
-      <c r="W1" s="64"/>
-      <c r="X1" s="64"/>
-      <c r="Y1" s="65"/>
+      <c r="V1" s="83"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="83"/>
+      <c r="Y1" s="84"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O2" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="S2" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="V2" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="W2" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="P2" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="S2" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="U2" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="V2" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="W2" s="12" t="s">
-        <v>29</v>
-      </c>
       <c r="X2" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="11"/>
+      <c r="B3" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>42</v>
+      </c>
       <c r="D3" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>42</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>43</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="P3" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T3" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X3" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Y3" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:32" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -1226,13 +1281,13 @@
         <v>400</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S4" s="4">
         <v>1</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U4" s="5">
         <v>81600000000000</v>
@@ -1250,13 +1305,13 @@
       <c r="Y4" s="1">
         <v>1</v>
       </c>
-      <c r="Z4" s="69" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA4" s="70"/>
-      <c r="AB4" s="70"/>
-      <c r="AC4" s="71"/>
-      <c r="AD4" s="71"/>
+      <c r="Z4" s="73" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA4" s="85"/>
+      <c r="AB4" s="85"/>
+      <c r="AC4" s="65"/>
+      <c r="AD4" s="65"/>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="22">
@@ -1311,13 +1366,13 @@
         <v>400</v>
       </c>
       <c r="R5" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S5" s="13">
         <v>1</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5" s="16">
         <v>81600000000000</v>
@@ -1335,13 +1390,13 @@
       <c r="Y5" s="1">
         <v>1</v>
       </c>
-      <c r="Z5" s="69" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA5" s="70"/>
-      <c r="AB5" s="70"/>
-      <c r="AC5" s="71"/>
-      <c r="AD5" s="71"/>
+      <c r="Z5" s="73" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA5" s="85"/>
+      <c r="AB5" s="85"/>
+      <c r="AC5" s="65"/>
+      <c r="AD5" s="65"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="22">
@@ -1396,13 +1451,13 @@
         <v>400</v>
       </c>
       <c r="R6" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S6" s="13">
         <v>1</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U6" s="16">
         <v>81600000000000</v>
@@ -1420,13 +1475,13 @@
       <c r="Y6" s="1">
         <v>1</v>
       </c>
-      <c r="Z6" s="69" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA6" s="70"/>
-      <c r="AB6" s="70"/>
-      <c r="AC6" s="71"/>
-      <c r="AD6" s="71"/>
+      <c r="Z6" s="73" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA6" s="85"/>
+      <c r="AB6" s="85"/>
+      <c r="AC6" s="65"/>
+      <c r="AD6" s="65"/>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="22">
@@ -1481,13 +1536,13 @@
         <v>400</v>
       </c>
       <c r="R7" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S7" s="13">
         <v>1</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U7" s="16">
         <v>81600000000000</v>
@@ -1505,13 +1560,13 @@
       <c r="Y7" s="1">
         <v>1</v>
       </c>
-      <c r="Z7" s="69" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA7" s="70"/>
-      <c r="AB7" s="70"/>
-      <c r="AC7" s="71"/>
-      <c r="AD7" s="71"/>
+      <c r="Z7" s="73" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA7" s="85"/>
+      <c r="AB7" s="85"/>
+      <c r="AC7" s="65"/>
+      <c r="AD7" s="65"/>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="22">
@@ -1566,13 +1621,13 @@
         <v>400</v>
       </c>
       <c r="R8" s="36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S8" s="36">
         <v>1</v>
       </c>
       <c r="T8" s="38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8" s="37">
         <v>81600000000000</v>
@@ -1590,13 +1645,13 @@
       <c r="Y8" s="38">
         <v>1</v>
       </c>
-      <c r="Z8" s="69" t="s">
-        <v>54</v>
-      </c>
-      <c r="AA8" s="72"/>
-      <c r="AB8" s="72"/>
-      <c r="AC8" s="72"/>
-      <c r="AD8" s="72"/>
+      <c r="Z8" s="73" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA8" s="74"/>
+      <c r="AB8" s="74"/>
+      <c r="AC8" s="74"/>
+      <c r="AD8" s="74"/>
       <c r="AE8" s="20"/>
       <c r="AF8" s="20"/>
     </row>
@@ -1653,13 +1708,13 @@
         <v>400</v>
       </c>
       <c r="R9" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S9" s="13">
         <v>1</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U9" s="16">
         <v>81600000000000</v>
@@ -1677,13 +1732,13 @@
       <c r="Y9" s="1">
         <v>1</v>
       </c>
-      <c r="Z9" s="69" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA9" s="72"/>
-      <c r="AB9" s="72"/>
-      <c r="AC9" s="71"/>
-      <c r="AD9" s="71"/>
+      <c r="Z9" s="73" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA9" s="74"/>
+      <c r="AB9" s="74"/>
+      <c r="AC9" s="65"/>
+      <c r="AD9" s="65"/>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="46">
@@ -1738,13 +1793,13 @@
         <v>400</v>
       </c>
       <c r="R10" s="41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S10" s="41">
         <v>1</v>
       </c>
       <c r="T10" s="43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10" s="42">
         <v>81600000000000</v>
@@ -1762,13 +1817,13 @@
       <c r="Y10" s="43">
         <v>1</v>
       </c>
-      <c r="Z10" s="73" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA10" s="74"/>
-      <c r="AB10" s="74"/>
-      <c r="AC10" s="71"/>
-      <c r="AD10" s="71"/>
+      <c r="Z10" s="77" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA10" s="78"/>
+      <c r="AB10" s="78"/>
+      <c r="AC10" s="65"/>
+      <c r="AD10" s="65"/>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="22">
@@ -1824,13 +1879,13 @@
         <v>400</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S11" s="13">
         <v>1</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11" s="19">
         <f>U10*(4/3)</f>
@@ -1849,11 +1904,11 @@
       <c r="Y11" s="1">
         <v>1</v>
       </c>
-      <c r="Z11" s="73"/>
-      <c r="AA11" s="74"/>
-      <c r="AB11" s="74"/>
-      <c r="AC11" s="71"/>
-      <c r="AD11" s="71"/>
+      <c r="Z11" s="77"/>
+      <c r="AA11" s="78"/>
+      <c r="AB11" s="78"/>
+      <c r="AC11" s="65"/>
+      <c r="AD11" s="65"/>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="22">
@@ -1908,13 +1963,13 @@
         <v>400</v>
       </c>
       <c r="R12" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S12" s="13">
         <v>1</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U12" s="19">
         <f t="shared" ref="U12:U27" si="1">U11*(4/3)</f>
@@ -1933,11 +1988,11 @@
       <c r="Y12" s="1">
         <v>1</v>
       </c>
-      <c r="Z12" s="73"/>
-      <c r="AA12" s="74"/>
-      <c r="AB12" s="74"/>
-      <c r="AC12" s="71"/>
-      <c r="AD12" s="71"/>
+      <c r="Z12" s="77"/>
+      <c r="AA12" s="78"/>
+      <c r="AB12" s="78"/>
+      <c r="AC12" s="65"/>
+      <c r="AD12" s="65"/>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1992,13 +2047,13 @@
         <v>400</v>
       </c>
       <c r="R13" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S13" s="13">
         <v>1</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13" s="19">
         <f t="shared" si="1"/>
@@ -2017,11 +2072,11 @@
       <c r="Y13" s="1">
         <v>1</v>
       </c>
-      <c r="Z13" s="73"/>
-      <c r="AA13" s="74"/>
-      <c r="AB13" s="74"/>
-      <c r="AC13" s="71"/>
-      <c r="AD13" s="71"/>
+      <c r="Z13" s="77"/>
+      <c r="AA13" s="78"/>
+      <c r="AB13" s="78"/>
+      <c r="AC13" s="65"/>
+      <c r="AD13" s="65"/>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="23">
@@ -2076,13 +2131,13 @@
         <v>400</v>
       </c>
       <c r="R14" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S14" s="13">
         <v>1</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U14" s="19">
         <f t="shared" si="1"/>
@@ -2101,11 +2156,11 @@
       <c r="Y14" s="1">
         <v>1</v>
       </c>
-      <c r="Z14" s="73"/>
-      <c r="AA14" s="74"/>
-      <c r="AB14" s="74"/>
-      <c r="AC14" s="71"/>
-      <c r="AD14" s="71"/>
+      <c r="Z14" s="77"/>
+      <c r="AA14" s="78"/>
+      <c r="AB14" s="78"/>
+      <c r="AC14" s="65"/>
+      <c r="AD14" s="65"/>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -2160,13 +2215,13 @@
         <v>400</v>
       </c>
       <c r="R15" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S15" s="13">
         <v>1</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15" s="19">
         <f t="shared" si="1"/>
@@ -2185,11 +2240,11 @@
       <c r="Y15" s="1">
         <v>1</v>
       </c>
-      <c r="Z15" s="73"/>
-      <c r="AA15" s="74"/>
-      <c r="AB15" s="74"/>
-      <c r="AC15" s="71"/>
-      <c r="AD15" s="71"/>
+      <c r="Z15" s="77"/>
+      <c r="AA15" s="78"/>
+      <c r="AB15" s="78"/>
+      <c r="AC15" s="65"/>
+      <c r="AD15" s="65"/>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="23">
@@ -2244,13 +2299,13 @@
         <v>400</v>
       </c>
       <c r="R16" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S16" s="13">
         <v>1</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16" s="19">
         <f t="shared" si="1"/>
@@ -2269,11 +2324,11 @@
       <c r="Y16" s="1">
         <v>1</v>
       </c>
-      <c r="Z16" s="73"/>
-      <c r="AA16" s="74"/>
-      <c r="AB16" s="74"/>
-      <c r="AC16" s="71"/>
-      <c r="AD16" s="71"/>
+      <c r="Z16" s="77"/>
+      <c r="AA16" s="78"/>
+      <c r="AB16" s="78"/>
+      <c r="AC16" s="65"/>
+      <c r="AD16" s="65"/>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
@@ -2328,13 +2383,13 @@
         <v>400</v>
       </c>
       <c r="R17" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S17" s="13">
         <v>1</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U17" s="19">
         <f t="shared" si="1"/>
@@ -2353,11 +2408,11 @@
       <c r="Y17" s="1">
         <v>1</v>
       </c>
-      <c r="Z17" s="73"/>
-      <c r="AA17" s="74"/>
-      <c r="AB17" s="74"/>
-      <c r="AC17" s="71"/>
-      <c r="AD17" s="71"/>
+      <c r="Z17" s="77"/>
+      <c r="AA17" s="78"/>
+      <c r="AB17" s="78"/>
+      <c r="AC17" s="65"/>
+      <c r="AD17" s="65"/>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
@@ -2412,13 +2467,13 @@
         <v>400</v>
       </c>
       <c r="R18" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S18" s="13">
         <v>1</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U18" s="19">
         <f t="shared" si="1"/>
@@ -2437,11 +2492,11 @@
       <c r="Y18" s="1">
         <v>1</v>
       </c>
-      <c r="Z18" s="73"/>
-      <c r="AA18" s="74"/>
-      <c r="AB18" s="74"/>
-      <c r="AC18" s="71"/>
-      <c r="AD18" s="71"/>
+      <c r="Z18" s="77"/>
+      <c r="AA18" s="78"/>
+      <c r="AB18" s="78"/>
+      <c r="AC18" s="65"/>
+      <c r="AD18" s="65"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
@@ -2496,13 +2551,13 @@
         <v>400</v>
       </c>
       <c r="R19" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S19" s="13">
         <v>1</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U19" s="19">
         <f t="shared" si="1"/>
@@ -2521,11 +2576,11 @@
       <c r="Y19" s="1">
         <v>1</v>
       </c>
-      <c r="Z19" s="73"/>
-      <c r="AA19" s="74"/>
-      <c r="AB19" s="74"/>
-      <c r="AC19" s="71"/>
-      <c r="AD19" s="71"/>
+      <c r="Z19" s="77"/>
+      <c r="AA19" s="78"/>
+      <c r="AB19" s="78"/>
+      <c r="AC19" s="65"/>
+      <c r="AD19" s="65"/>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
@@ -2580,13 +2635,13 @@
         <v>400</v>
       </c>
       <c r="R20" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S20" s="13">
         <v>1</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U20" s="19">
         <f t="shared" si="1"/>
@@ -2605,11 +2660,11 @@
       <c r="Y20" s="1">
         <v>1</v>
       </c>
-      <c r="Z20" s="73"/>
-      <c r="AA20" s="74"/>
-      <c r="AB20" s="74"/>
-      <c r="AC20" s="71"/>
-      <c r="AD20" s="71"/>
+      <c r="Z20" s="77"/>
+      <c r="AA20" s="78"/>
+      <c r="AB20" s="78"/>
+      <c r="AC20" s="65"/>
+      <c r="AD20" s="65"/>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
@@ -2664,13 +2719,13 @@
         <v>400</v>
       </c>
       <c r="R21" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S21" s="13">
         <v>1</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U21" s="19">
         <f t="shared" si="1"/>
@@ -2689,11 +2744,11 @@
       <c r="Y21" s="1">
         <v>1</v>
       </c>
-      <c r="Z21" s="73"/>
-      <c r="AA21" s="74"/>
-      <c r="AB21" s="74"/>
-      <c r="AC21" s="71"/>
-      <c r="AD21" s="71"/>
+      <c r="Z21" s="77"/>
+      <c r="AA21" s="78"/>
+      <c r="AB21" s="78"/>
+      <c r="AC21" s="65"/>
+      <c r="AD21" s="65"/>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
@@ -2748,13 +2803,13 @@
         <v>400</v>
       </c>
       <c r="R22" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S22" s="13">
         <v>1</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U22" s="19">
         <f t="shared" si="1"/>
@@ -2773,11 +2828,11 @@
       <c r="Y22" s="1">
         <v>1</v>
       </c>
-      <c r="Z22" s="73"/>
-      <c r="AA22" s="74"/>
-      <c r="AB22" s="74"/>
-      <c r="AC22" s="71"/>
-      <c r="AD22" s="71"/>
+      <c r="Z22" s="77"/>
+      <c r="AA22" s="78"/>
+      <c r="AB22" s="78"/>
+      <c r="AC22" s="65"/>
+      <c r="AD22" s="65"/>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
@@ -2832,13 +2887,13 @@
         <v>400</v>
       </c>
       <c r="R23" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S23" s="13">
         <v>1</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U23" s="19">
         <f t="shared" si="1"/>
@@ -2857,11 +2912,11 @@
       <c r="Y23" s="1">
         <v>1</v>
       </c>
-      <c r="Z23" s="73"/>
-      <c r="AA23" s="74"/>
-      <c r="AB23" s="74"/>
-      <c r="AC23" s="71"/>
-      <c r="AD23" s="71"/>
+      <c r="Z23" s="77"/>
+      <c r="AA23" s="78"/>
+      <c r="AB23" s="78"/>
+      <c r="AC23" s="65"/>
+      <c r="AD23" s="65"/>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -2916,13 +2971,13 @@
         <v>400</v>
       </c>
       <c r="R24" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S24" s="13">
         <v>1</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U24" s="19">
         <f t="shared" si="1"/>
@@ -2941,11 +2996,11 @@
       <c r="Y24" s="1">
         <v>1</v>
       </c>
-      <c r="Z24" s="73"/>
-      <c r="AA24" s="74"/>
-      <c r="AB24" s="74"/>
-      <c r="AC24" s="71"/>
-      <c r="AD24" s="71"/>
+      <c r="Z24" s="77"/>
+      <c r="AA24" s="78"/>
+      <c r="AB24" s="78"/>
+      <c r="AC24" s="65"/>
+      <c r="AD24" s="65"/>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
@@ -3000,13 +3055,13 @@
         <v>400</v>
       </c>
       <c r="R25" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S25" s="13">
         <v>1</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U25" s="19">
         <f t="shared" si="1"/>
@@ -3025,11 +3080,11 @@
       <c r="Y25" s="1">
         <v>1</v>
       </c>
-      <c r="Z25" s="73"/>
-      <c r="AA25" s="74"/>
-      <c r="AB25" s="74"/>
-      <c r="AC25" s="71"/>
-      <c r="AD25" s="71"/>
+      <c r="Z25" s="77"/>
+      <c r="AA25" s="78"/>
+      <c r="AB25" s="78"/>
+      <c r="AC25" s="65"/>
+      <c r="AD25" s="65"/>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
@@ -3084,13 +3139,13 @@
         <v>400</v>
       </c>
       <c r="R26" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S26" s="13">
         <v>1</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U26" s="19">
         <f t="shared" si="1"/>
@@ -3109,11 +3164,11 @@
       <c r="Y26" s="1">
         <v>1</v>
       </c>
-      <c r="Z26" s="73"/>
-      <c r="AA26" s="74"/>
-      <c r="AB26" s="74"/>
-      <c r="AC26" s="71"/>
-      <c r="AD26" s="71"/>
+      <c r="Z26" s="77"/>
+      <c r="AA26" s="78"/>
+      <c r="AB26" s="78"/>
+      <c r="AC26" s="65"/>
+      <c r="AD26" s="65"/>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="22">
@@ -3168,13 +3223,13 @@
         <v>400</v>
       </c>
       <c r="R27" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S27" s="25">
         <v>1</v>
       </c>
       <c r="T27" s="27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U27" s="26">
         <f t="shared" si="1"/>
@@ -3193,11 +3248,11 @@
       <c r="Y27" s="27">
         <v>1</v>
       </c>
-      <c r="Z27" s="73"/>
-      <c r="AA27" s="74"/>
-      <c r="AB27" s="74"/>
-      <c r="AC27" s="71"/>
-      <c r="AD27" s="71"/>
+      <c r="Z27" s="77"/>
+      <c r="AA27" s="78"/>
+      <c r="AB27" s="78"/>
+      <c r="AC27" s="65"/>
+      <c r="AD27" s="65"/>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="33">
@@ -3252,13 +3307,13 @@
         <v>400</v>
       </c>
       <c r="R28" s="31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S28" s="31">
         <v>1</v>
       </c>
       <c r="T28" s="33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U28" s="32">
         <v>257896296296296.25</v>
@@ -3276,13 +3331,13 @@
       <c r="Y28" s="33">
         <v>1</v>
       </c>
-      <c r="Z28" s="69" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA28" s="72"/>
-      <c r="AB28" s="72"/>
-      <c r="AC28" s="71"/>
-      <c r="AD28" s="71"/>
+      <c r="Z28" s="73" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA28" s="74"/>
+      <c r="AB28" s="74"/>
+      <c r="AC28" s="65"/>
+      <c r="AD28" s="65"/>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="22">
@@ -3337,13 +3392,13 @@
         <v>400</v>
       </c>
       <c r="R29" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S29" s="13">
         <v>1</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U29" s="19">
         <f>U27*2</f>
@@ -3362,13 +3417,13 @@
       <c r="Y29" s="1">
         <v>1</v>
       </c>
-      <c r="Z29" s="73" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA29" s="74"/>
-      <c r="AB29" s="74"/>
-      <c r="AC29" s="71"/>
-      <c r="AD29" s="71"/>
+      <c r="Z29" s="77" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA29" s="78"/>
+      <c r="AB29" s="78"/>
+      <c r="AC29" s="65"/>
+      <c r="AD29" s="65"/>
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="22">
@@ -3423,13 +3478,13 @@
         <v>400</v>
       </c>
       <c r="R30" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S30" s="13">
         <v>1</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U30" s="19">
         <f t="shared" ref="U30:U31" si="3">U28*2</f>
@@ -3448,11 +3503,11 @@
       <c r="Y30" s="1">
         <v>1</v>
       </c>
-      <c r="Z30" s="73"/>
-      <c r="AA30" s="74"/>
-      <c r="AB30" s="74"/>
-      <c r="AC30" s="71"/>
-      <c r="AD30" s="71"/>
+      <c r="Z30" s="77"/>
+      <c r="AA30" s="78"/>
+      <c r="AB30" s="78"/>
+      <c r="AC30" s="65"/>
+      <c r="AD30" s="65"/>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="23">
@@ -3507,13 +3562,13 @@
         <v>400</v>
       </c>
       <c r="R31" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S31" s="13">
         <v>1</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U31" s="19">
         <f t="shared" si="3"/>
@@ -3532,11 +3587,11 @@
       <c r="Y31" s="1">
         <v>1</v>
       </c>
-      <c r="Z31" s="73"/>
-      <c r="AA31" s="74"/>
-      <c r="AB31" s="74"/>
-      <c r="AC31" s="71"/>
-      <c r="AD31" s="71"/>
+      <c r="Z31" s="77"/>
+      <c r="AA31" s="78"/>
+      <c r="AB31" s="78"/>
+      <c r="AC31" s="65"/>
+      <c r="AD31" s="65"/>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="23">
@@ -3591,13 +3646,13 @@
         <v>400</v>
       </c>
       <c r="R32" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S32" s="13">
         <v>1</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U32" s="19">
         <f>U31*2</f>
@@ -3616,11 +3671,11 @@
       <c r="Y32" s="1">
         <v>1</v>
       </c>
-      <c r="Z32" s="73"/>
-      <c r="AA32" s="74"/>
-      <c r="AB32" s="74"/>
-      <c r="AC32" s="71"/>
-      <c r="AD32" s="71"/>
+      <c r="Z32" s="77"/>
+      <c r="AA32" s="78"/>
+      <c r="AB32" s="78"/>
+      <c r="AC32" s="65"/>
+      <c r="AD32" s="65"/>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="22">
@@ -3675,13 +3730,13 @@
         <v>400</v>
       </c>
       <c r="R33" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S33" s="13">
         <v>1</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U33" s="19">
         <f t="shared" ref="U33:U45" si="4">U32*2</f>
@@ -3700,11 +3755,11 @@
       <c r="Y33" s="1">
         <v>1</v>
       </c>
-      <c r="Z33" s="73"/>
-      <c r="AA33" s="74"/>
-      <c r="AB33" s="74"/>
-      <c r="AC33" s="71"/>
-      <c r="AD33" s="71"/>
+      <c r="Z33" s="77"/>
+      <c r="AA33" s="78"/>
+      <c r="AB33" s="78"/>
+      <c r="AC33" s="65"/>
+      <c r="AD33" s="65"/>
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="22">
@@ -3759,13 +3814,13 @@
         <v>400</v>
       </c>
       <c r="R34" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S34" s="13">
         <v>1</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U34" s="19">
         <f t="shared" si="4"/>
@@ -3784,11 +3839,11 @@
       <c r="Y34" s="1">
         <v>1</v>
       </c>
-      <c r="Z34" s="73"/>
-      <c r="AA34" s="74"/>
-      <c r="AB34" s="74"/>
-      <c r="AC34" s="71"/>
-      <c r="AD34" s="71"/>
+      <c r="Z34" s="77"/>
+      <c r="AA34" s="78"/>
+      <c r="AB34" s="78"/>
+      <c r="AC34" s="65"/>
+      <c r="AD34" s="65"/>
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="22">
@@ -3843,13 +3898,13 @@
         <v>400</v>
       </c>
       <c r="R35" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S35" s="13">
         <v>1</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U35" s="19">
         <f t="shared" si="4"/>
@@ -3868,11 +3923,11 @@
       <c r="Y35" s="1">
         <v>1</v>
       </c>
-      <c r="Z35" s="73"/>
-      <c r="AA35" s="74"/>
-      <c r="AB35" s="74"/>
-      <c r="AC35" s="71"/>
-      <c r="AD35" s="71"/>
+      <c r="Z35" s="77"/>
+      <c r="AA35" s="78"/>
+      <c r="AB35" s="78"/>
+      <c r="AC35" s="65"/>
+      <c r="AD35" s="65"/>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="23">
@@ -3927,13 +3982,13 @@
         <v>400</v>
       </c>
       <c r="R36" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S36" s="13">
         <v>1</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U36" s="19">
         <f t="shared" si="4"/>
@@ -3952,11 +4007,11 @@
       <c r="Y36" s="1">
         <v>1</v>
       </c>
-      <c r="Z36" s="73"/>
-      <c r="AA36" s="74"/>
-      <c r="AB36" s="74"/>
-      <c r="AC36" s="71"/>
-      <c r="AD36" s="71"/>
+      <c r="Z36" s="77"/>
+      <c r="AA36" s="78"/>
+      <c r="AB36" s="78"/>
+      <c r="AC36" s="65"/>
+      <c r="AD36" s="65"/>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="23">
@@ -4011,13 +4066,13 @@
         <v>400</v>
       </c>
       <c r="R37" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S37" s="13">
         <v>1</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U37" s="19">
         <f t="shared" si="4"/>
@@ -4036,11 +4091,11 @@
       <c r="Y37" s="1">
         <v>1</v>
       </c>
-      <c r="Z37" s="73"/>
-      <c r="AA37" s="74"/>
-      <c r="AB37" s="74"/>
-      <c r="AC37" s="71"/>
-      <c r="AD37" s="71"/>
+      <c r="Z37" s="77"/>
+      <c r="AA37" s="78"/>
+      <c r="AB37" s="78"/>
+      <c r="AC37" s="65"/>
+      <c r="AD37" s="65"/>
     </row>
     <row r="38" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="22">
@@ -4095,13 +4150,13 @@
         <v>400</v>
       </c>
       <c r="R38" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S38" s="13">
         <v>1</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U38" s="19">
         <f t="shared" si="4"/>
@@ -4120,11 +4175,11 @@
       <c r="Y38" s="1">
         <v>1</v>
       </c>
-      <c r="Z38" s="73"/>
-      <c r="AA38" s="74"/>
-      <c r="AB38" s="74"/>
-      <c r="AC38" s="71"/>
-      <c r="AD38" s="71"/>
+      <c r="Z38" s="77"/>
+      <c r="AA38" s="78"/>
+      <c r="AB38" s="78"/>
+      <c r="AC38" s="65"/>
+      <c r="AD38" s="65"/>
     </row>
     <row r="39" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="23">
@@ -4179,13 +4234,13 @@
         <v>400</v>
       </c>
       <c r="R39" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S39" s="13">
         <v>1</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U39" s="19">
         <f t="shared" si="4"/>
@@ -4204,11 +4259,11 @@
       <c r="Y39" s="1">
         <v>1</v>
       </c>
-      <c r="Z39" s="73"/>
-      <c r="AA39" s="74"/>
-      <c r="AB39" s="74"/>
-      <c r="AC39" s="71"/>
-      <c r="AD39" s="71"/>
+      <c r="Z39" s="77"/>
+      <c r="AA39" s="78"/>
+      <c r="AB39" s="78"/>
+      <c r="AC39" s="65"/>
+      <c r="AD39" s="65"/>
     </row>
     <row r="40" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="61">
@@ -4263,13 +4318,13 @@
         <v>400</v>
       </c>
       <c r="R40" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S40" s="13">
         <v>1</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U40" s="19">
         <f t="shared" si="4"/>
@@ -4288,11 +4343,11 @@
       <c r="Y40" s="1">
         <v>1</v>
       </c>
-      <c r="Z40" s="73"/>
-      <c r="AA40" s="74"/>
-      <c r="AB40" s="74"/>
-      <c r="AC40" s="71"/>
-      <c r="AD40" s="71"/>
+      <c r="Z40" s="77"/>
+      <c r="AA40" s="78"/>
+      <c r="AB40" s="78"/>
+      <c r="AC40" s="65"/>
+      <c r="AD40" s="65"/>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="61">
@@ -4347,13 +4402,13 @@
         <v>400</v>
       </c>
       <c r="R41" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S41" s="13">
         <v>1</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U41" s="19">
         <f t="shared" si="4"/>
@@ -4372,11 +4427,11 @@
       <c r="Y41" s="1">
         <v>1</v>
       </c>
-      <c r="Z41" s="73"/>
-      <c r="AA41" s="74"/>
-      <c r="AB41" s="74"/>
-      <c r="AC41" s="71"/>
-      <c r="AD41" s="71"/>
+      <c r="Z41" s="77"/>
+      <c r="AA41" s="78"/>
+      <c r="AB41" s="78"/>
+      <c r="AC41" s="65"/>
+      <c r="AD41" s="65"/>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="61">
@@ -4431,13 +4486,13 @@
         <v>400</v>
       </c>
       <c r="R42" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S42" s="13">
         <v>1</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U42" s="19">
         <f t="shared" si="4"/>
@@ -4456,11 +4511,11 @@
       <c r="Y42" s="1">
         <v>1</v>
       </c>
-      <c r="Z42" s="73"/>
-      <c r="AA42" s="74"/>
-      <c r="AB42" s="74"/>
-      <c r="AC42" s="71"/>
-      <c r="AD42" s="71"/>
+      <c r="Z42" s="77"/>
+      <c r="AA42" s="78"/>
+      <c r="AB42" s="78"/>
+      <c r="AC42" s="65"/>
+      <c r="AD42" s="65"/>
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="61">
@@ -4515,13 +4570,13 @@
         <v>400</v>
       </c>
       <c r="R43" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S43" s="13">
         <v>1</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U43" s="19">
         <f t="shared" si="4"/>
@@ -4540,11 +4595,11 @@
       <c r="Y43" s="1">
         <v>1</v>
       </c>
-      <c r="Z43" s="73"/>
-      <c r="AA43" s="74"/>
-      <c r="AB43" s="74"/>
-      <c r="AC43" s="71"/>
-      <c r="AD43" s="71"/>
+      <c r="Z43" s="77"/>
+      <c r="AA43" s="78"/>
+      <c r="AB43" s="78"/>
+      <c r="AC43" s="65"/>
+      <c r="AD43" s="65"/>
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="61">
@@ -4599,13 +4654,13 @@
         <v>400</v>
       </c>
       <c r="R44" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S44" s="13">
         <v>1</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U44" s="19">
         <f t="shared" si="4"/>
@@ -4624,11 +4679,11 @@
       <c r="Y44" s="1">
         <v>1</v>
       </c>
-      <c r="Z44" s="73"/>
-      <c r="AA44" s="74"/>
-      <c r="AB44" s="74"/>
-      <c r="AC44" s="71"/>
-      <c r="AD44" s="71"/>
+      <c r="Z44" s="77"/>
+      <c r="AA44" s="78"/>
+      <c r="AB44" s="78"/>
+      <c r="AC44" s="65"/>
+      <c r="AD44" s="65"/>
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="60">
@@ -4683,13 +4738,13 @@
         <v>400</v>
       </c>
       <c r="R45" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S45" s="13">
         <v>1</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U45" s="19">
         <f t="shared" si="4"/>
@@ -4708,11 +4763,11 @@
       <c r="Y45" s="1">
         <v>1</v>
       </c>
-      <c r="Z45" s="73"/>
-      <c r="AA45" s="74"/>
-      <c r="AB45" s="74"/>
-      <c r="AC45" s="71"/>
-      <c r="AD45" s="71"/>
+      <c r="Z45" s="77"/>
+      <c r="AA45" s="78"/>
+      <c r="AB45" s="78"/>
+      <c r="AC45" s="65"/>
+      <c r="AD45" s="65"/>
     </row>
     <row r="46" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="60">
@@ -4767,13 +4822,13 @@
         <v>400</v>
       </c>
       <c r="R46" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S46" s="13">
         <v>1</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U46" s="19">
         <f>U45*2</f>
@@ -4792,11 +4847,11 @@
       <c r="Y46" s="1">
         <v>1</v>
       </c>
-      <c r="Z46" s="73"/>
-      <c r="AA46" s="74"/>
-      <c r="AB46" s="74"/>
-      <c r="AC46" s="71"/>
-      <c r="AD46" s="71"/>
+      <c r="Z46" s="77"/>
+      <c r="AA46" s="78"/>
+      <c r="AB46" s="78"/>
+      <c r="AC46" s="65"/>
+      <c r="AD46" s="65"/>
     </row>
     <row r="47" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="40">
@@ -4851,13 +4906,13 @@
         <v>400</v>
       </c>
       <c r="R47" s="41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S47" s="41">
         <v>1</v>
       </c>
       <c r="T47" s="43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U47" s="42">
         <v>81600000000000</v>
@@ -4875,13 +4930,13 @@
       <c r="Y47" s="43">
         <v>1</v>
       </c>
-      <c r="Z47" s="69" t="s">
-        <v>55</v>
-      </c>
-      <c r="AA47" s="72"/>
-      <c r="AB47" s="72"/>
-      <c r="AC47" s="75"/>
-      <c r="AD47" s="71"/>
+      <c r="Z47" s="73" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA47" s="74"/>
+      <c r="AB47" s="74"/>
+      <c r="AC47" s="66"/>
+      <c r="AD47" s="65"/>
     </row>
     <row r="48" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="40">
@@ -4936,13 +4991,13 @@
         <v>400</v>
       </c>
       <c r="R48" s="41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S48" s="41">
         <v>1</v>
       </c>
       <c r="T48" s="43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U48" s="42">
         <f>U29</f>
@@ -4961,13 +5016,13 @@
       <c r="Y48" s="43">
         <v>1</v>
       </c>
-      <c r="Z48" s="76" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA48" s="77"/>
-      <c r="AB48" s="77"/>
-      <c r="AC48" s="78"/>
-      <c r="AD48" s="71"/>
+      <c r="Z48" s="75" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA48" s="79"/>
+      <c r="AB48" s="79"/>
+      <c r="AC48" s="67"/>
+      <c r="AD48" s="65"/>
     </row>
     <row r="49" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="40">
@@ -5022,13 +5077,13 @@
         <v>400</v>
       </c>
       <c r="R49" s="41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S49" s="41">
         <v>1</v>
       </c>
       <c r="T49" s="43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U49" s="42">
         <v>81600000000</v>
@@ -5046,13 +5101,13 @@
       <c r="Y49" s="43">
         <v>1</v>
       </c>
-      <c r="Z49" s="69" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA49" s="72"/>
-      <c r="AB49" s="72"/>
-      <c r="AC49" s="71"/>
-      <c r="AD49" s="71"/>
+      <c r="Z49" s="73" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA49" s="74"/>
+      <c r="AB49" s="74"/>
+      <c r="AC49" s="65"/>
+      <c r="AD49" s="65"/>
     </row>
     <row r="50" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="40">
@@ -5107,13 +5162,13 @@
         <v>400</v>
       </c>
       <c r="R50" s="45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S50" s="45">
         <v>1</v>
       </c>
       <c r="T50" s="40" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U50" s="49">
         <v>81600000000000</v>
@@ -5130,13 +5185,13 @@
       <c r="Y50" s="40">
         <v>1</v>
       </c>
-      <c r="Z50" s="69" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA50" s="72"/>
-      <c r="AB50" s="72"/>
-      <c r="AC50" s="71"/>
-      <c r="AD50" s="71"/>
+      <c r="Z50" s="73" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA50" s="74"/>
+      <c r="AB50" s="74"/>
+      <c r="AC50" s="65"/>
+      <c r="AD50" s="65"/>
     </row>
     <row r="51" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="43">
@@ -5191,13 +5246,13 @@
         <v>400</v>
       </c>
       <c r="R51" s="41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S51" s="41">
         <v>1</v>
       </c>
       <c r="T51" s="43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U51" s="16">
         <f>U40</f>
@@ -5216,13 +5271,13 @@
       <c r="Y51" s="43">
         <v>1</v>
       </c>
-      <c r="Z51" s="73" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA51" s="74"/>
-      <c r="AB51" s="74"/>
-      <c r="AC51" s="71"/>
-      <c r="AD51" s="71"/>
+      <c r="Z51" s="77" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA51" s="78"/>
+      <c r="AB51" s="78"/>
+      <c r="AC51" s="65"/>
+      <c r="AD51" s="65"/>
     </row>
     <row r="52" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
@@ -5277,13 +5332,13 @@
         <v>400</v>
       </c>
       <c r="R52" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S52" s="13">
         <v>1</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U52" s="16">
         <f t="shared" ref="U52:U57" si="5">U41</f>
@@ -5302,11 +5357,11 @@
       <c r="Y52" s="1">
         <v>1</v>
       </c>
-      <c r="Z52" s="73"/>
-      <c r="AA52" s="74"/>
-      <c r="AB52" s="74"/>
-      <c r="AC52" s="71"/>
-      <c r="AD52" s="71"/>
+      <c r="Z52" s="77"/>
+      <c r="AA52" s="78"/>
+      <c r="AB52" s="78"/>
+      <c r="AC52" s="65"/>
+      <c r="AD52" s="65"/>
     </row>
     <row r="53" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
@@ -5361,13 +5416,13 @@
         <v>400</v>
       </c>
       <c r="R53" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S53" s="13">
         <v>1</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U53" s="16">
         <f t="shared" si="5"/>
@@ -5386,11 +5441,11 @@
       <c r="Y53" s="1">
         <v>1</v>
       </c>
-      <c r="Z53" s="73"/>
-      <c r="AA53" s="74"/>
-      <c r="AB53" s="74"/>
-      <c r="AC53" s="71"/>
-      <c r="AD53" s="71"/>
+      <c r="Z53" s="77"/>
+      <c r="AA53" s="78"/>
+      <c r="AB53" s="78"/>
+      <c r="AC53" s="65"/>
+      <c r="AD53" s="65"/>
     </row>
     <row r="54" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
@@ -5445,13 +5500,13 @@
         <v>400</v>
       </c>
       <c r="R54" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S54" s="13">
         <v>1</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U54" s="16">
         <f t="shared" si="5"/>
@@ -5470,11 +5525,11 @@
       <c r="Y54" s="1">
         <v>1</v>
       </c>
-      <c r="Z54" s="73"/>
-      <c r="AA54" s="74"/>
-      <c r="AB54" s="74"/>
-      <c r="AC54" s="71"/>
-      <c r="AD54" s="71"/>
+      <c r="Z54" s="77"/>
+      <c r="AA54" s="78"/>
+      <c r="AB54" s="78"/>
+      <c r="AC54" s="65"/>
+      <c r="AD54" s="65"/>
     </row>
     <row r="55" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="60">
@@ -5529,13 +5584,13 @@
         <v>400</v>
       </c>
       <c r="R55" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S55" s="13">
         <v>1</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U55" s="16">
         <f t="shared" si="5"/>
@@ -5554,11 +5609,11 @@
       <c r="Y55" s="1">
         <v>1</v>
       </c>
-      <c r="Z55" s="73"/>
-      <c r="AA55" s="74"/>
-      <c r="AB55" s="74"/>
-      <c r="AC55" s="71"/>
-      <c r="AD55" s="71"/>
+      <c r="Z55" s="77"/>
+      <c r="AA55" s="78"/>
+      <c r="AB55" s="78"/>
+      <c r="AC55" s="65"/>
+      <c r="AD55" s="65"/>
     </row>
     <row r="56" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="60">
@@ -5613,13 +5668,13 @@
         <v>400</v>
       </c>
       <c r="R56" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S56" s="13">
         <v>1</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U56" s="16">
         <f t="shared" si="5"/>
@@ -5638,11 +5693,11 @@
       <c r="Y56" s="1">
         <v>1</v>
       </c>
-      <c r="Z56" s="73"/>
-      <c r="AA56" s="74"/>
-      <c r="AB56" s="74"/>
-      <c r="AC56" s="71"/>
-      <c r="AD56" s="71"/>
+      <c r="Z56" s="77"/>
+      <c r="AA56" s="78"/>
+      <c r="AB56" s="78"/>
+      <c r="AC56" s="65"/>
+      <c r="AD56" s="65"/>
     </row>
     <row r="57" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="62">
@@ -5697,13 +5752,13 @@
         <v>400</v>
       </c>
       <c r="R57" s="25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S57" s="25">
         <v>1</v>
       </c>
       <c r="T57" s="27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U57" s="26">
         <f t="shared" si="5"/>
@@ -5722,11 +5777,11 @@
       <c r="Y57" s="27">
         <v>1</v>
       </c>
-      <c r="Z57" s="73"/>
-      <c r="AA57" s="74"/>
-      <c r="AB57" s="74"/>
-      <c r="AC57" s="71"/>
-      <c r="AD57" s="71"/>
+      <c r="Z57" s="77"/>
+      <c r="AA57" s="78"/>
+      <c r="AB57" s="78"/>
+      <c r="AC57" s="65"/>
+      <c r="AD57" s="65"/>
     </row>
     <row r="58" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="56">
@@ -5781,13 +5836,13 @@
         <v>400</v>
       </c>
       <c r="R58" s="35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S58" s="35">
         <v>1</v>
       </c>
       <c r="T58" s="53" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U58" s="54">
         <v>81600000000000</v>
@@ -5805,13 +5860,13 @@
       <c r="Y58" s="53">
         <v>1</v>
       </c>
-      <c r="Z58" s="76" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA58" s="77"/>
-      <c r="AB58" s="77"/>
-      <c r="AC58" s="71"/>
-      <c r="AD58" s="71"/>
+      <c r="Z58" s="75" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA58" s="79"/>
+      <c r="AB58" s="79"/>
+      <c r="AC58" s="65"/>
+      <c r="AD58" s="65"/>
     </row>
     <row r="59" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="50">
@@ -5866,13 +5921,13 @@
         <v>400</v>
       </c>
       <c r="R59" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S59" s="15">
         <v>1</v>
       </c>
       <c r="T59" s="50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U59" s="51">
         <v>81600000000000</v>
@@ -5890,13 +5945,13 @@
       <c r="Y59" s="50">
         <v>1</v>
       </c>
-      <c r="Z59" s="73" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA59" s="74"/>
-      <c r="AB59" s="74"/>
-      <c r="AC59" s="71"/>
-      <c r="AD59" s="71"/>
+      <c r="Z59" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA59" s="78"/>
+      <c r="AB59" s="78"/>
+      <c r="AC59" s="65"/>
+      <c r="AD59" s="65"/>
     </row>
     <row r="60" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="50">
@@ -5951,13 +6006,13 @@
         <v>400</v>
       </c>
       <c r="R60" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S60" s="15">
         <v>1</v>
       </c>
       <c r="T60" s="50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U60" s="51">
         <v>81600000000000</v>
@@ -5975,11 +6030,11 @@
       <c r="Y60" s="50">
         <v>1</v>
       </c>
-      <c r="Z60" s="73"/>
-      <c r="AA60" s="74"/>
-      <c r="AB60" s="74"/>
-      <c r="AC60" s="71"/>
-      <c r="AD60" s="71"/>
+      <c r="Z60" s="77"/>
+      <c r="AA60" s="78"/>
+      <c r="AB60" s="78"/>
+      <c r="AC60" s="65"/>
+      <c r="AD60" s="65"/>
     </row>
     <row r="61" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
@@ -6034,13 +6089,13 @@
         <v>400</v>
       </c>
       <c r="R61" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S61" s="15">
         <v>1</v>
       </c>
       <c r="T61" s="50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U61" s="51">
         <v>81600000000000</v>
@@ -6058,11 +6113,11 @@
       <c r="Y61" s="50">
         <v>1</v>
       </c>
-      <c r="Z61" s="73"/>
-      <c r="AA61" s="74"/>
-      <c r="AB61" s="74"/>
-      <c r="AC61" s="71"/>
-      <c r="AD61" s="71"/>
+      <c r="Z61" s="77"/>
+      <c r="AA61" s="78"/>
+      <c r="AB61" s="78"/>
+      <c r="AC61" s="65"/>
+      <c r="AD61" s="65"/>
     </row>
     <row r="62" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="50">
@@ -6117,13 +6172,13 @@
         <v>400</v>
       </c>
       <c r="R62" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S62" s="15">
         <v>1</v>
       </c>
       <c r="T62" s="50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U62" s="51">
         <v>81600000000000</v>
@@ -6141,11 +6196,11 @@
       <c r="Y62" s="50">
         <v>1</v>
       </c>
-      <c r="Z62" s="73"/>
-      <c r="AA62" s="74"/>
-      <c r="AB62" s="74"/>
-      <c r="AC62" s="71"/>
-      <c r="AD62" s="71"/>
+      <c r="Z62" s="77"/>
+      <c r="AA62" s="78"/>
+      <c r="AB62" s="78"/>
+      <c r="AC62" s="65"/>
+      <c r="AD62" s="65"/>
     </row>
     <row r="63" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
@@ -6200,13 +6255,13 @@
         <v>400</v>
       </c>
       <c r="R63" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S63" s="15">
         <v>1</v>
       </c>
       <c r="T63" s="50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U63" s="51">
         <v>81600000000000</v>
@@ -6224,11 +6279,11 @@
       <c r="Y63" s="50">
         <v>1</v>
       </c>
-      <c r="Z63" s="73"/>
-      <c r="AA63" s="74"/>
-      <c r="AB63" s="74"/>
-      <c r="AC63" s="71"/>
-      <c r="AD63" s="71"/>
+      <c r="Z63" s="77"/>
+      <c r="AA63" s="78"/>
+      <c r="AB63" s="78"/>
+      <c r="AC63" s="65"/>
+      <c r="AD63" s="65"/>
     </row>
     <row r="64" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="50">
@@ -6283,13 +6338,13 @@
         <v>400</v>
       </c>
       <c r="R64" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S64" s="15">
         <v>1</v>
       </c>
       <c r="T64" s="50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U64" s="51">
         <v>81600000000000</v>
@@ -6307,11 +6362,11 @@
       <c r="Y64" s="50">
         <v>1</v>
       </c>
-      <c r="Z64" s="73"/>
-      <c r="AA64" s="74"/>
-      <c r="AB64" s="74"/>
-      <c r="AC64" s="71"/>
-      <c r="AD64" s="71"/>
+      <c r="Z64" s="77"/>
+      <c r="AA64" s="78"/>
+      <c r="AB64" s="78"/>
+      <c r="AC64" s="65"/>
+      <c r="AD64" s="65"/>
     </row>
     <row r="65" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
@@ -6366,13 +6421,13 @@
         <v>400</v>
       </c>
       <c r="R65" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S65" s="15">
         <v>1</v>
       </c>
       <c r="T65" s="50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U65" s="51">
         <v>81600000000000</v>
@@ -6390,11 +6445,11 @@
       <c r="Y65" s="50">
         <v>1</v>
       </c>
-      <c r="Z65" s="73"/>
-      <c r="AA65" s="74"/>
-      <c r="AB65" s="74"/>
-      <c r="AC65" s="71"/>
-      <c r="AD65" s="71"/>
+      <c r="Z65" s="77"/>
+      <c r="AA65" s="78"/>
+      <c r="AB65" s="78"/>
+      <c r="AC65" s="65"/>
+      <c r="AD65" s="65"/>
     </row>
     <row r="66" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="57">
@@ -6449,13 +6504,13 @@
         <v>400</v>
       </c>
       <c r="R66" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S66" s="29">
         <v>1</v>
       </c>
       <c r="T66" s="57" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U66" s="58">
         <v>81600000000000</v>
@@ -6473,11 +6528,11 @@
       <c r="Y66" s="57">
         <v>1</v>
       </c>
-      <c r="Z66" s="73"/>
-      <c r="AA66" s="74"/>
-      <c r="AB66" s="74"/>
-      <c r="AC66" s="71"/>
-      <c r="AD66" s="71"/>
+      <c r="Z66" s="77"/>
+      <c r="AA66" s="78"/>
+      <c r="AB66" s="78"/>
+      <c r="AC66" s="65"/>
+      <c r="AD66" s="65"/>
     </row>
     <row r="67" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="46">
@@ -6532,20 +6587,20 @@
         <v>400</v>
       </c>
       <c r="R67" s="41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S67" s="41">
         <v>1</v>
       </c>
       <c r="T67" s="43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U67" s="16">
         <f>U51</f>
         <v>2.2232005100138279E+19</v>
       </c>
       <c r="V67" s="13">
-        <f t="shared" ref="V67:V93" si="6">30*4184</f>
+        <f t="shared" ref="V67:V106" si="6">30*4184</f>
         <v>125520</v>
       </c>
       <c r="W67" s="41">
@@ -6557,13 +6612,13 @@
       <c r="Y67" s="43">
         <v>1</v>
       </c>
-      <c r="Z67" s="73" t="s">
-        <v>62</v>
-      </c>
-      <c r="AA67" s="79"/>
-      <c r="AB67" s="79"/>
-      <c r="AC67" s="71"/>
-      <c r="AD67" s="71"/>
+      <c r="Z67" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA67" s="80"/>
+      <c r="AB67" s="80"/>
+      <c r="AC67" s="65"/>
+      <c r="AD67" s="65"/>
     </row>
     <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="22">
@@ -6618,13 +6673,13 @@
         <v>400</v>
       </c>
       <c r="R68" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S68" s="13">
         <v>1</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U68" s="19">
         <f>U67/5</f>
@@ -6643,11 +6698,11 @@
       <c r="Y68" s="1">
         <v>1</v>
       </c>
-      <c r="Z68" s="73"/>
-      <c r="AA68" s="79"/>
-      <c r="AB68" s="79"/>
-      <c r="AC68" s="71"/>
-      <c r="AD68" s="71"/>
+      <c r="Z68" s="77"/>
+      <c r="AA68" s="80"/>
+      <c r="AB68" s="80"/>
+      <c r="AC68" s="65"/>
+      <c r="AD68" s="65"/>
     </row>
     <row r="69" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="22">
@@ -6702,13 +6757,13 @@
         <v>400</v>
       </c>
       <c r="R69" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S69" s="13">
         <v>1</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U69" s="19">
         <f t="shared" ref="U69:U84" si="7">U68/5</f>
@@ -6727,11 +6782,11 @@
       <c r="Y69" s="1">
         <v>1</v>
       </c>
-      <c r="Z69" s="73"/>
-      <c r="AA69" s="79"/>
-      <c r="AB69" s="79"/>
-      <c r="AC69" s="71"/>
-      <c r="AD69" s="71"/>
+      <c r="Z69" s="77"/>
+      <c r="AA69" s="80"/>
+      <c r="AB69" s="80"/>
+      <c r="AC69" s="65"/>
+      <c r="AD69" s="65"/>
     </row>
     <row r="70" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="22">
@@ -6786,13 +6841,13 @@
         <v>400</v>
       </c>
       <c r="R70" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S70" s="13">
         <v>1</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U70" s="19">
         <f t="shared" si="7"/>
@@ -6811,11 +6866,11 @@
       <c r="Y70" s="1">
         <v>1</v>
       </c>
-      <c r="Z70" s="73"/>
-      <c r="AA70" s="79"/>
-      <c r="AB70" s="79"/>
-      <c r="AC70" s="71"/>
-      <c r="AD70" s="71"/>
+      <c r="Z70" s="77"/>
+      <c r="AA70" s="80"/>
+      <c r="AB70" s="80"/>
+      <c r="AC70" s="65"/>
+      <c r="AD70" s="65"/>
     </row>
     <row r="71" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="60">
@@ -6870,13 +6925,13 @@
         <v>400</v>
       </c>
       <c r="R71" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S71" s="13">
         <v>1</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U71" s="19">
         <f t="shared" si="7"/>
@@ -6895,11 +6950,11 @@
       <c r="Y71" s="1">
         <v>1</v>
       </c>
-      <c r="Z71" s="73"/>
-      <c r="AA71" s="79"/>
-      <c r="AB71" s="79"/>
-      <c r="AC71" s="71"/>
-      <c r="AD71" s="71"/>
+      <c r="Z71" s="77"/>
+      <c r="AA71" s="80"/>
+      <c r="AB71" s="80"/>
+      <c r="AC71" s="65"/>
+      <c r="AD71" s="65"/>
     </row>
     <row r="72" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="22">
@@ -6954,13 +7009,13 @@
         <v>400</v>
       </c>
       <c r="R72" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S72" s="13">
         <v>1</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U72" s="19">
         <f t="shared" si="7"/>
@@ -6979,11 +7034,11 @@
       <c r="Y72" s="1">
         <v>1</v>
       </c>
-      <c r="Z72" s="73"/>
-      <c r="AA72" s="79"/>
-      <c r="AB72" s="79"/>
-      <c r="AC72" s="71"/>
-      <c r="AD72" s="71"/>
+      <c r="Z72" s="77"/>
+      <c r="AA72" s="80"/>
+      <c r="AB72" s="80"/>
+      <c r="AC72" s="65"/>
+      <c r="AD72" s="65"/>
     </row>
     <row r="73" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A73" s="22">
@@ -7038,13 +7093,13 @@
         <v>400</v>
       </c>
       <c r="R73" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S73" s="13">
         <v>1</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U73" s="19">
         <f t="shared" si="7"/>
@@ -7063,11 +7118,11 @@
       <c r="Y73" s="1">
         <v>1</v>
       </c>
-      <c r="Z73" s="73"/>
-      <c r="AA73" s="79"/>
-      <c r="AB73" s="79"/>
-      <c r="AC73" s="71"/>
-      <c r="AD73" s="71"/>
+      <c r="Z73" s="77"/>
+      <c r="AA73" s="80"/>
+      <c r="AB73" s="80"/>
+      <c r="AC73" s="65"/>
+      <c r="AD73" s="65"/>
     </row>
     <row r="74" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A74" s="22">
@@ -7122,13 +7177,13 @@
         <v>400</v>
       </c>
       <c r="R74" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S74" s="13">
         <v>1</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U74" s="19">
         <f>U73/5</f>
@@ -7147,11 +7202,11 @@
       <c r="Y74" s="1">
         <v>1</v>
       </c>
-      <c r="Z74" s="73"/>
-      <c r="AA74" s="79"/>
-      <c r="AB74" s="79"/>
-      <c r="AC74" s="71"/>
-      <c r="AD74" s="71"/>
+      <c r="Z74" s="77"/>
+      <c r="AA74" s="80"/>
+      <c r="AB74" s="80"/>
+      <c r="AC74" s="65"/>
+      <c r="AD74" s="65"/>
     </row>
     <row r="75" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A75" s="22">
@@ -7206,13 +7261,13 @@
         <v>400</v>
       </c>
       <c r="R75" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S75" s="13">
         <v>1</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U75" s="19">
         <f t="shared" si="7"/>
@@ -7231,11 +7286,11 @@
       <c r="Y75" s="1">
         <v>1</v>
       </c>
-      <c r="Z75" s="73"/>
-      <c r="AA75" s="79"/>
-      <c r="AB75" s="79"/>
-      <c r="AC75" s="71"/>
-      <c r="AD75" s="71"/>
+      <c r="Z75" s="77"/>
+      <c r="AA75" s="80"/>
+      <c r="AB75" s="80"/>
+      <c r="AC75" s="65"/>
+      <c r="AD75" s="65"/>
     </row>
     <row r="76" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="22">
@@ -7290,13 +7345,13 @@
         <v>400</v>
       </c>
       <c r="R76" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S76" s="13">
         <v>1</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U76" s="19">
         <f>U75/5</f>
@@ -7315,11 +7370,11 @@
       <c r="Y76" s="1">
         <v>1</v>
       </c>
-      <c r="Z76" s="73"/>
-      <c r="AA76" s="79"/>
-      <c r="AB76" s="79"/>
-      <c r="AC76" s="71"/>
-      <c r="AD76" s="71"/>
+      <c r="Z76" s="77"/>
+      <c r="AA76" s="80"/>
+      <c r="AB76" s="80"/>
+      <c r="AC76" s="65"/>
+      <c r="AD76" s="65"/>
     </row>
     <row r="77" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A77" s="22">
@@ -7374,13 +7429,13 @@
         <v>400</v>
       </c>
       <c r="R77" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S77" s="13">
         <v>1</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U77" s="19">
         <f t="shared" si="7"/>
@@ -7399,11 +7454,11 @@
       <c r="Y77" s="1">
         <v>1</v>
       </c>
-      <c r="Z77" s="73"/>
-      <c r="AA77" s="79"/>
-      <c r="AB77" s="79"/>
-      <c r="AC77" s="71"/>
-      <c r="AD77" s="71"/>
+      <c r="Z77" s="77"/>
+      <c r="AA77" s="80"/>
+      <c r="AB77" s="80"/>
+      <c r="AC77" s="65"/>
+      <c r="AD77" s="65"/>
     </row>
     <row r="78" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A78" s="22">
@@ -7458,13 +7513,13 @@
         <v>400</v>
       </c>
       <c r="R78" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S78" s="13">
         <v>1</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U78" s="19">
         <f t="shared" si="7"/>
@@ -7483,11 +7538,11 @@
       <c r="Y78" s="1">
         <v>1</v>
       </c>
-      <c r="Z78" s="73"/>
-      <c r="AA78" s="79"/>
-      <c r="AB78" s="79"/>
-      <c r="AC78" s="71"/>
-      <c r="AD78" s="71"/>
+      <c r="Z78" s="77"/>
+      <c r="AA78" s="80"/>
+      <c r="AB78" s="80"/>
+      <c r="AC78" s="65"/>
+      <c r="AD78" s="65"/>
     </row>
     <row r="79" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A79" s="22">
@@ -7542,13 +7597,13 @@
         <v>400</v>
       </c>
       <c r="R79" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S79" s="13">
         <v>1</v>
       </c>
       <c r="T79" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U79" s="19">
         <f t="shared" si="7"/>
@@ -7567,11 +7622,11 @@
       <c r="Y79" s="1">
         <v>1</v>
       </c>
-      <c r="Z79" s="73"/>
-      <c r="AA79" s="79"/>
-      <c r="AB79" s="79"/>
-      <c r="AC79" s="71"/>
-      <c r="AD79" s="71"/>
+      <c r="Z79" s="77"/>
+      <c r="AA79" s="80"/>
+      <c r="AB79" s="80"/>
+      <c r="AC79" s="65"/>
+      <c r="AD79" s="65"/>
     </row>
     <row r="80" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A80" s="22">
@@ -7626,13 +7681,13 @@
         <v>400</v>
       </c>
       <c r="R80" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S80" s="13">
         <v>1</v>
       </c>
       <c r="T80" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U80" s="19">
         <f t="shared" si="7"/>
@@ -7651,11 +7706,11 @@
       <c r="Y80" s="1">
         <v>1</v>
       </c>
-      <c r="Z80" s="73"/>
-      <c r="AA80" s="79"/>
-      <c r="AB80" s="79"/>
-      <c r="AC80" s="71"/>
-      <c r="AD80" s="71"/>
+      <c r="Z80" s="77"/>
+      <c r="AA80" s="80"/>
+      <c r="AB80" s="80"/>
+      <c r="AC80" s="65"/>
+      <c r="AD80" s="65"/>
     </row>
     <row r="81" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A81" s="22">
@@ -7710,13 +7765,13 @@
         <v>400</v>
       </c>
       <c r="R81" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S81" s="13">
         <v>1</v>
       </c>
       <c r="T81" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U81" s="19">
         <f>U80/5</f>
@@ -7735,11 +7790,11 @@
       <c r="Y81" s="1">
         <v>1</v>
       </c>
-      <c r="Z81" s="73"/>
-      <c r="AA81" s="79"/>
-      <c r="AB81" s="79"/>
-      <c r="AC81" s="71"/>
-      <c r="AD81" s="71"/>
+      <c r="Z81" s="77"/>
+      <c r="AA81" s="80"/>
+      <c r="AB81" s="80"/>
+      <c r="AC81" s="65"/>
+      <c r="AD81" s="65"/>
     </row>
     <row r="82" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A82" s="22">
@@ -7794,13 +7849,13 @@
         <v>400</v>
       </c>
       <c r="R82" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S82" s="13">
         <v>1</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U82" s="19">
         <f t="shared" si="7"/>
@@ -7819,11 +7874,11 @@
       <c r="Y82" s="1">
         <v>1</v>
       </c>
-      <c r="Z82" s="73"/>
-      <c r="AA82" s="79"/>
-      <c r="AB82" s="79"/>
-      <c r="AC82" s="71"/>
-      <c r="AD82" s="71"/>
+      <c r="Z82" s="77"/>
+      <c r="AA82" s="80"/>
+      <c r="AB82" s="80"/>
+      <c r="AC82" s="65"/>
+      <c r="AD82" s="65"/>
     </row>
     <row r="83" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A83" s="22">
@@ -7878,13 +7933,13 @@
         <v>400</v>
       </c>
       <c r="R83" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S83" s="13">
         <v>1</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U83" s="19">
         <f t="shared" si="7"/>
@@ -7903,11 +7958,11 @@
       <c r="Y83" s="1">
         <v>1</v>
       </c>
-      <c r="Z83" s="73"/>
-      <c r="AA83" s="79"/>
-      <c r="AB83" s="79"/>
-      <c r="AC83" s="71"/>
-      <c r="AD83" s="71"/>
+      <c r="Z83" s="77"/>
+      <c r="AA83" s="80"/>
+      <c r="AB83" s="80"/>
+      <c r="AC83" s="65"/>
+      <c r="AD83" s="65"/>
     </row>
     <row r="84" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A84" s="22">
@@ -7962,13 +8017,13 @@
         <v>400</v>
       </c>
       <c r="R84" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S84" s="13">
         <v>1</v>
       </c>
       <c r="T84" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U84" s="19">
         <f t="shared" si="7"/>
@@ -7987,14 +8042,14 @@
       <c r="Y84" s="1">
         <v>1</v>
       </c>
-      <c r="Z84" s="73"/>
-      <c r="AA84" s="79"/>
-      <c r="AB84" s="79"/>
-      <c r="AC84" s="71"/>
-      <c r="AD84" s="71"/>
+      <c r="Z84" s="77"/>
+      <c r="AA84" s="80"/>
+      <c r="AB84" s="80"/>
+      <c r="AC84" s="65"/>
+      <c r="AD84" s="65"/>
     </row>
     <row r="85" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A85" s="68">
+      <c r="A85" s="64">
         <v>182</v>
       </c>
       <c r="B85" s="35">
@@ -8046,13 +8101,13 @@
         <v>400</v>
       </c>
       <c r="R85" s="35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S85" s="35">
         <v>1</v>
       </c>
       <c r="T85" s="53" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U85" s="54">
         <v>81600000000000</v>
@@ -8070,13 +8125,13 @@
       <c r="Y85" s="53">
         <v>1</v>
       </c>
-      <c r="Z85" s="76" t="s">
-        <v>59</v>
-      </c>
-      <c r="AA85" s="80"/>
-      <c r="AB85" s="80"/>
-      <c r="AC85" s="71"/>
-      <c r="AD85" s="71"/>
+      <c r="Z85" s="75" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA85" s="76"/>
+      <c r="AB85" s="76"/>
+      <c r="AC85" s="65"/>
+      <c r="AD85" s="65"/>
     </row>
     <row r="86" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="43">
@@ -8131,13 +8186,13 @@
         <v>400</v>
       </c>
       <c r="R86" s="45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S86" s="45">
         <v>1</v>
       </c>
       <c r="T86" s="40" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U86" s="47">
         <v>81600000000000</v>
@@ -8155,13 +8210,13 @@
       <c r="Y86" s="40">
         <v>1</v>
       </c>
-      <c r="Z86" s="73" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA86" s="74"/>
-      <c r="AB86" s="74"/>
-      <c r="AC86" s="71"/>
-      <c r="AD86" s="71"/>
+      <c r="Z86" s="77" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA86" s="78"/>
+      <c r="AB86" s="78"/>
+      <c r="AC86" s="65"/>
+      <c r="AD86" s="65"/>
     </row>
     <row r="87" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A87" s="27">
@@ -8216,13 +8271,13 @@
         <v>400</v>
       </c>
       <c r="R87" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S87" s="29">
         <v>1</v>
       </c>
       <c r="T87" s="57" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U87" s="58">
         <v>81600000000000</v>
@@ -8240,11 +8295,11 @@
       <c r="Y87" s="57">
         <v>1</v>
       </c>
-      <c r="Z87" s="73"/>
-      <c r="AA87" s="74"/>
-      <c r="AB87" s="74"/>
-      <c r="AC87" s="71"/>
-      <c r="AD87" s="71"/>
+      <c r="Z87" s="77"/>
+      <c r="AA87" s="78"/>
+      <c r="AB87" s="78"/>
+      <c r="AC87" s="65"/>
+      <c r="AD87" s="65"/>
     </row>
     <row r="88" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A88" s="33">
@@ -8299,13 +8354,13 @@
         <v>2000</v>
       </c>
       <c r="R88" s="35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S88" s="35">
         <v>1</v>
       </c>
       <c r="T88" s="53" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U88" s="54">
         <v>81600000000000</v>
@@ -8323,13 +8378,13 @@
       <c r="Y88" s="53">
         <v>1</v>
       </c>
-      <c r="Z88" s="76" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA88" s="80"/>
-      <c r="AB88" s="80"/>
-      <c r="AC88" s="71"/>
-      <c r="AD88" s="71"/>
+      <c r="Z88" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA88" s="76"/>
+      <c r="AB88" s="76"/>
+      <c r="AC88" s="65"/>
+      <c r="AD88" s="65"/>
     </row>
     <row r="89" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A89" s="43">
@@ -8384,13 +8439,13 @@
         <v>400</v>
       </c>
       <c r="R89" s="45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S89" s="45">
         <v>1</v>
       </c>
       <c r="T89" s="40" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U89" s="47">
         <v>81600000000000</v>
@@ -8408,13 +8463,13 @@
       <c r="Y89" s="40">
         <v>1</v>
       </c>
-      <c r="Z89" s="76" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA89" s="80"/>
-      <c r="AB89" s="80"/>
-      <c r="AC89" s="71"/>
-      <c r="AD89" s="71"/>
+      <c r="Z89" s="75" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA89" s="76"/>
+      <c r="AB89" s="76"/>
+      <c r="AC89" s="65"/>
+      <c r="AD89" s="65"/>
     </row>
     <row r="90" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A90" s="27">
@@ -8469,13 +8524,13 @@
         <v>400</v>
       </c>
       <c r="R90" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S90" s="29">
         <v>1</v>
       </c>
       <c r="T90" s="57" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U90" s="58">
         <v>81600000000000</v>
@@ -8493,13 +8548,13 @@
       <c r="Y90" s="57">
         <v>1</v>
       </c>
-      <c r="Z90" s="76" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA90" s="80"/>
-      <c r="AB90" s="80"/>
-      <c r="AC90" s="71"/>
-      <c r="AD90" s="71"/>
+      <c r="Z90" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA90" s="76"/>
+      <c r="AB90" s="76"/>
+      <c r="AC90" s="65"/>
+      <c r="AD90" s="65"/>
     </row>
     <row r="91" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A91" s="33">
@@ -8554,13 +8609,13 @@
         <v>1000</v>
       </c>
       <c r="R91" s="35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S91" s="35">
         <v>1</v>
       </c>
       <c r="T91" s="53" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U91" s="54">
         <v>81600000000000</v>
@@ -8578,13 +8633,13 @@
       <c r="Y91" s="53">
         <v>1</v>
       </c>
-      <c r="Z91" s="76" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA91" s="80"/>
-      <c r="AB91" s="80"/>
-      <c r="AC91" s="71"/>
-      <c r="AD91" s="71"/>
+      <c r="Z91" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA91" s="76"/>
+      <c r="AB91" s="76"/>
+      <c r="AC91" s="65"/>
+      <c r="AD91" s="65"/>
     </row>
     <row r="92" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A92" s="43">
@@ -8639,13 +8694,13 @@
         <v>400</v>
       </c>
       <c r="R92" s="45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S92" s="45">
         <v>1</v>
       </c>
       <c r="T92" s="40" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U92" s="47">
         <v>81600000000000</v>
@@ -8663,13 +8718,13 @@
       <c r="Y92" s="40">
         <v>1</v>
       </c>
-      <c r="Z92" s="73" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA92" s="74"/>
-      <c r="AB92" s="74"/>
-      <c r="AC92" s="71"/>
-      <c r="AD92" s="71"/>
+      <c r="Z92" s="77" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA92" s="78"/>
+      <c r="AB92" s="78"/>
+      <c r="AC92" s="65"/>
+      <c r="AD92" s="65"/>
     </row>
     <row r="93" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A93" s="27">
@@ -8724,13 +8779,13 @@
         <v>400</v>
       </c>
       <c r="R93" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S93" s="29">
         <v>1</v>
       </c>
       <c r="T93" s="57" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U93" s="58">
         <v>81600000000000</v>
@@ -8748,44 +8803,6206 @@
       <c r="Y93" s="57">
         <v>1</v>
       </c>
-      <c r="Z93" s="73"/>
-      <c r="AA93" s="74"/>
-      <c r="AB93" s="74"/>
-      <c r="AC93" s="71"/>
-      <c r="AD93" s="71"/>
+      <c r="Z93" s="77"/>
+      <c r="AA93" s="78"/>
+      <c r="AB93" s="78"/>
+      <c r="AC93" s="65"/>
+      <c r="AD93" s="65"/>
+    </row>
+    <row r="94" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A94" s="53">
+        <v>191</v>
+      </c>
+      <c r="B94" s="31">
+        <v>12</v>
+      </c>
+      <c r="C94" s="31">
+        <v>300</v>
+      </c>
+      <c r="D94" s="32">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E94" s="32">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F94" s="33">
+        <v>5</v>
+      </c>
+      <c r="G94" s="32">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H94" s="32">
+        <v>100</v>
+      </c>
+      <c r="I94" s="31">
+        <v>1</v>
+      </c>
+      <c r="J94" s="34">
+        <v>1E-4</v>
+      </c>
+      <c r="K94" s="31">
+        <v>2</v>
+      </c>
+      <c r="L94" s="33">
+        <v>2</v>
+      </c>
+      <c r="M94" s="32">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N94" s="31">
+        <v>150</v>
+      </c>
+      <c r="O94" s="31">
+        <v>0.2</v>
+      </c>
+      <c r="P94" s="31">
+        <v>300</v>
+      </c>
+      <c r="Q94" s="33">
+        <v>400</v>
+      </c>
+      <c r="R94" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="S94" s="31">
+        <v>1</v>
+      </c>
+      <c r="T94" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="U94" s="32">
+        <v>81600000000000</v>
+      </c>
+      <c r="V94" s="31">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W94" s="31">
+        <v>0</v>
+      </c>
+      <c r="X94" s="35">
+        <v>1</v>
+      </c>
+      <c r="Y94" s="33">
+        <v>1</v>
+      </c>
+      <c r="Z94" s="77" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA94" s="80"/>
+      <c r="AB94" s="80"/>
+    </row>
+    <row r="95" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>192</v>
+      </c>
+      <c r="B95" s="13">
+        <v>12</v>
+      </c>
+      <c r="C95" s="13">
+        <v>300</v>
+      </c>
+      <c r="D95" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E95" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F95" s="1">
+        <v>5</v>
+      </c>
+      <c r="G95" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H95" s="16">
+        <v>100</v>
+      </c>
+      <c r="I95" s="13">
+        <v>1</v>
+      </c>
+      <c r="J95" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K95" s="13">
+        <v>2</v>
+      </c>
+      <c r="L95" s="1">
+        <v>2</v>
+      </c>
+      <c r="M95" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N95" s="13">
+        <v>150</v>
+      </c>
+      <c r="O95" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P95" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q95" s="1">
+        <v>400</v>
+      </c>
+      <c r="R95" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S95" s="13">
+        <v>1</v>
+      </c>
+      <c r="T95" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U95" s="16">
+        <v>81600000000000</v>
+      </c>
+      <c r="V95" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W95" s="13">
+        <v>0</v>
+      </c>
+      <c r="X95" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y95" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z95" s="86" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA95" s="87"/>
+      <c r="AB95" s="87"/>
+    </row>
+    <row r="96" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>193</v>
+      </c>
+      <c r="B96" s="13">
+        <v>12</v>
+      </c>
+      <c r="C96" s="13">
+        <v>300</v>
+      </c>
+      <c r="D96" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E96" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F96" s="1">
+        <v>5</v>
+      </c>
+      <c r="G96" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H96" s="16">
+        <v>100</v>
+      </c>
+      <c r="I96" s="13">
+        <v>1</v>
+      </c>
+      <c r="J96" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K96" s="13">
+        <v>2</v>
+      </c>
+      <c r="L96" s="1">
+        <v>2</v>
+      </c>
+      <c r="M96" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N96" s="13">
+        <v>150</v>
+      </c>
+      <c r="O96" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P96" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q96" s="1">
+        <v>400</v>
+      </c>
+      <c r="R96" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S96" s="13">
+        <v>1</v>
+      </c>
+      <c r="T96" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U96" s="19">
+        <f>U94*0.5</f>
+        <v>40800000000000</v>
+      </c>
+      <c r="V96" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W96" s="13">
+        <v>0</v>
+      </c>
+      <c r="X96" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y96" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z96" s="86"/>
+      <c r="AA96" s="87"/>
+      <c r="AB96" s="87"/>
+    </row>
+    <row r="97" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>194</v>
+      </c>
+      <c r="B97" s="13">
+        <v>12</v>
+      </c>
+      <c r="C97" s="13">
+        <v>300</v>
+      </c>
+      <c r="D97" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E97" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F97" s="1">
+        <v>5</v>
+      </c>
+      <c r="G97" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H97" s="16">
+        <v>100</v>
+      </c>
+      <c r="I97" s="13">
+        <v>1</v>
+      </c>
+      <c r="J97" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K97" s="13">
+        <v>2</v>
+      </c>
+      <c r="L97" s="1">
+        <v>2</v>
+      </c>
+      <c r="M97" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N97" s="13">
+        <v>150</v>
+      </c>
+      <c r="O97" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P97" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q97" s="1">
+        <v>400</v>
+      </c>
+      <c r="R97" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S97" s="13">
+        <v>1</v>
+      </c>
+      <c r="T97" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U97" s="19">
+        <f t="shared" ref="U97:U106" si="8">U96*0.5</f>
+        <v>20400000000000</v>
+      </c>
+      <c r="V97" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W97" s="13">
+        <v>0</v>
+      </c>
+      <c r="X97" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y97" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z97" s="86"/>
+      <c r="AA97" s="87"/>
+      <c r="AB97" s="87"/>
+    </row>
+    <row r="98" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>195</v>
+      </c>
+      <c r="B98" s="13">
+        <v>12</v>
+      </c>
+      <c r="C98" s="13">
+        <v>300</v>
+      </c>
+      <c r="D98" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E98" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F98" s="1">
+        <v>5</v>
+      </c>
+      <c r="G98" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H98" s="16">
+        <v>100</v>
+      </c>
+      <c r="I98" s="13">
+        <v>1</v>
+      </c>
+      <c r="J98" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K98" s="13">
+        <v>2</v>
+      </c>
+      <c r="L98" s="1">
+        <v>2</v>
+      </c>
+      <c r="M98" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N98" s="13">
+        <v>150</v>
+      </c>
+      <c r="O98" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P98" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q98" s="1">
+        <v>400</v>
+      </c>
+      <c r="R98" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S98" s="13">
+        <v>1</v>
+      </c>
+      <c r="T98" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U98" s="19">
+        <f t="shared" si="8"/>
+        <v>10200000000000</v>
+      </c>
+      <c r="V98" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W98" s="13">
+        <v>0</v>
+      </c>
+      <c r="X98" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y98" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z98" s="86"/>
+      <c r="AA98" s="87"/>
+      <c r="AB98" s="87"/>
+    </row>
+    <row r="99" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>196</v>
+      </c>
+      <c r="B99" s="13">
+        <v>12</v>
+      </c>
+      <c r="C99" s="13">
+        <v>300</v>
+      </c>
+      <c r="D99" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E99" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F99" s="1">
+        <v>5</v>
+      </c>
+      <c r="G99" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H99" s="16">
+        <v>100</v>
+      </c>
+      <c r="I99" s="13">
+        <v>1</v>
+      </c>
+      <c r="J99" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K99" s="13">
+        <v>2</v>
+      </c>
+      <c r="L99" s="1">
+        <v>2</v>
+      </c>
+      <c r="M99" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N99" s="13">
+        <v>150</v>
+      </c>
+      <c r="O99" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P99" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q99" s="1">
+        <v>400</v>
+      </c>
+      <c r="R99" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S99" s="13">
+        <v>1</v>
+      </c>
+      <c r="T99" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U99" s="19">
+        <f t="shared" si="8"/>
+        <v>5100000000000</v>
+      </c>
+      <c r="V99" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W99" s="13">
+        <v>0</v>
+      </c>
+      <c r="X99" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y99" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z99" s="86"/>
+      <c r="AA99" s="87"/>
+      <c r="AB99" s="87"/>
+    </row>
+    <row r="100" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>197</v>
+      </c>
+      <c r="B100" s="13">
+        <v>12</v>
+      </c>
+      <c r="C100" s="13">
+        <v>300</v>
+      </c>
+      <c r="D100" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E100" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F100" s="1">
+        <v>5</v>
+      </c>
+      <c r="G100" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H100" s="16">
+        <v>100</v>
+      </c>
+      <c r="I100" s="13">
+        <v>1</v>
+      </c>
+      <c r="J100" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K100" s="13">
+        <v>2</v>
+      </c>
+      <c r="L100" s="1">
+        <v>2</v>
+      </c>
+      <c r="M100" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N100" s="13">
+        <v>150</v>
+      </c>
+      <c r="O100" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P100" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q100" s="1">
+        <v>400</v>
+      </c>
+      <c r="R100" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S100" s="13">
+        <v>1</v>
+      </c>
+      <c r="T100" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U100" s="19">
+        <f t="shared" si="8"/>
+        <v>2550000000000</v>
+      </c>
+      <c r="V100" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W100" s="13">
+        <v>0</v>
+      </c>
+      <c r="X100" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y100" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z100" s="86"/>
+      <c r="AA100" s="87"/>
+      <c r="AB100" s="87"/>
+    </row>
+    <row r="101" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>198</v>
+      </c>
+      <c r="B101" s="13">
+        <v>12</v>
+      </c>
+      <c r="C101" s="13">
+        <v>300</v>
+      </c>
+      <c r="D101" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E101" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F101" s="1">
+        <v>5</v>
+      </c>
+      <c r="G101" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H101" s="16">
+        <v>100</v>
+      </c>
+      <c r="I101" s="13">
+        <v>1</v>
+      </c>
+      <c r="J101" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K101" s="13">
+        <v>2</v>
+      </c>
+      <c r="L101" s="1">
+        <v>2</v>
+      </c>
+      <c r="M101" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N101" s="13">
+        <v>150</v>
+      </c>
+      <c r="O101" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P101" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q101" s="1">
+        <v>400</v>
+      </c>
+      <c r="R101" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S101" s="13">
+        <v>1</v>
+      </c>
+      <c r="T101" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U101" s="19">
+        <f t="shared" si="8"/>
+        <v>1275000000000</v>
+      </c>
+      <c r="V101" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W101" s="13">
+        <v>0</v>
+      </c>
+      <c r="X101" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y101" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z101" s="86"/>
+      <c r="AA101" s="87"/>
+      <c r="AB101" s="87"/>
+    </row>
+    <row r="102" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>199</v>
+      </c>
+      <c r="B102" s="13">
+        <v>12</v>
+      </c>
+      <c r="C102" s="13">
+        <v>300</v>
+      </c>
+      <c r="D102" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E102" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F102" s="1">
+        <v>5</v>
+      </c>
+      <c r="G102" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H102" s="16">
+        <v>100</v>
+      </c>
+      <c r="I102" s="13">
+        <v>1</v>
+      </c>
+      <c r="J102" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K102" s="13">
+        <v>2</v>
+      </c>
+      <c r="L102" s="1">
+        <v>2</v>
+      </c>
+      <c r="M102" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N102" s="13">
+        <v>150</v>
+      </c>
+      <c r="O102" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P102" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q102" s="1">
+        <v>400</v>
+      </c>
+      <c r="R102" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S102" s="13">
+        <v>1</v>
+      </c>
+      <c r="T102" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U102" s="19">
+        <f t="shared" si="8"/>
+        <v>637500000000</v>
+      </c>
+      <c r="V102" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W102" s="13">
+        <v>0</v>
+      </c>
+      <c r="X102" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y102" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z102" s="86"/>
+      <c r="AA102" s="87"/>
+      <c r="AB102" s="87"/>
+    </row>
+    <row r="103" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>200</v>
+      </c>
+      <c r="B103" s="13">
+        <v>12</v>
+      </c>
+      <c r="C103" s="13">
+        <v>300</v>
+      </c>
+      <c r="D103" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E103" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F103" s="1">
+        <v>5</v>
+      </c>
+      <c r="G103" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H103" s="16">
+        <v>100</v>
+      </c>
+      <c r="I103" s="13">
+        <v>1</v>
+      </c>
+      <c r="J103" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K103" s="13">
+        <v>2</v>
+      </c>
+      <c r="L103" s="1">
+        <v>2</v>
+      </c>
+      <c r="M103" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N103" s="13">
+        <v>150</v>
+      </c>
+      <c r="O103" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P103" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q103" s="1">
+        <v>400</v>
+      </c>
+      <c r="R103" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S103" s="13">
+        <v>1</v>
+      </c>
+      <c r="T103" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U103" s="19">
+        <f t="shared" si="8"/>
+        <v>318750000000</v>
+      </c>
+      <c r="V103" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W103" s="13">
+        <v>0</v>
+      </c>
+      <c r="X103" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y103" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z103" s="86"/>
+      <c r="AA103" s="87"/>
+      <c r="AB103" s="87"/>
+    </row>
+    <row r="104" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>201</v>
+      </c>
+      <c r="B104" s="13">
+        <v>12</v>
+      </c>
+      <c r="C104" s="13">
+        <v>300</v>
+      </c>
+      <c r="D104" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E104" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F104" s="1">
+        <v>5</v>
+      </c>
+      <c r="G104" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H104" s="16">
+        <v>100</v>
+      </c>
+      <c r="I104" s="13">
+        <v>1</v>
+      </c>
+      <c r="J104" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K104" s="13">
+        <v>2</v>
+      </c>
+      <c r="L104" s="1">
+        <v>2</v>
+      </c>
+      <c r="M104" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N104" s="13">
+        <v>150</v>
+      </c>
+      <c r="O104" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P104" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q104" s="1">
+        <v>400</v>
+      </c>
+      <c r="R104" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S104" s="13">
+        <v>1</v>
+      </c>
+      <c r="T104" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U104" s="19">
+        <f t="shared" si="8"/>
+        <v>159375000000</v>
+      </c>
+      <c r="V104" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W104" s="13">
+        <v>0</v>
+      </c>
+      <c r="X104" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y104" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z104" s="86"/>
+      <c r="AA104" s="87"/>
+      <c r="AB104" s="87"/>
+    </row>
+    <row r="105" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>202</v>
+      </c>
+      <c r="B105" s="13">
+        <v>12</v>
+      </c>
+      <c r="C105" s="13">
+        <v>300</v>
+      </c>
+      <c r="D105" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E105" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F105" s="1">
+        <v>5</v>
+      </c>
+      <c r="G105" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H105" s="16">
+        <v>100</v>
+      </c>
+      <c r="I105" s="13">
+        <v>1</v>
+      </c>
+      <c r="J105" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K105" s="13">
+        <v>2</v>
+      </c>
+      <c r="L105" s="1">
+        <v>2</v>
+      </c>
+      <c r="M105" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N105" s="13">
+        <v>150</v>
+      </c>
+      <c r="O105" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P105" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q105" s="1">
+        <v>400</v>
+      </c>
+      <c r="R105" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S105" s="13">
+        <v>1</v>
+      </c>
+      <c r="T105" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U105" s="19">
+        <f t="shared" si="8"/>
+        <v>79687500000</v>
+      </c>
+      <c r="V105" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W105" s="13">
+        <v>0</v>
+      </c>
+      <c r="X105" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y105" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z105" s="86"/>
+      <c r="AA105" s="87"/>
+      <c r="AB105" s="87"/>
+    </row>
+    <row r="106" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>203</v>
+      </c>
+      <c r="B106" s="13">
+        <v>12</v>
+      </c>
+      <c r="C106" s="13">
+        <v>300</v>
+      </c>
+      <c r="D106" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E106" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F106" s="1">
+        <v>5</v>
+      </c>
+      <c r="G106" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H106" s="16">
+        <v>100</v>
+      </c>
+      <c r="I106" s="13">
+        <v>1</v>
+      </c>
+      <c r="J106" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K106" s="13">
+        <v>2</v>
+      </c>
+      <c r="L106" s="1">
+        <v>2</v>
+      </c>
+      <c r="M106" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N106" s="13">
+        <v>150</v>
+      </c>
+      <c r="O106" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P106" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q106" s="1">
+        <v>400</v>
+      </c>
+      <c r="R106" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S106" s="13">
+        <v>1</v>
+      </c>
+      <c r="T106" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U106" s="19">
+        <f t="shared" si="8"/>
+        <v>39843750000</v>
+      </c>
+      <c r="V106" s="13">
+        <f t="shared" si="6"/>
+        <v>125520</v>
+      </c>
+      <c r="W106" s="13">
+        <v>0</v>
+      </c>
+      <c r="X106" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y106" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z106" s="86"/>
+      <c r="AA106" s="87"/>
+      <c r="AB106" s="87"/>
+    </row>
+    <row r="107" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>204</v>
+      </c>
+      <c r="B107" s="13">
+        <v>12</v>
+      </c>
+      <c r="C107" s="13">
+        <v>300</v>
+      </c>
+      <c r="D107" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E107" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F107" s="1">
+        <v>5</v>
+      </c>
+      <c r="G107" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H107" s="16">
+        <v>100</v>
+      </c>
+      <c r="I107" s="13">
+        <v>1</v>
+      </c>
+      <c r="J107" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K107" s="13">
+        <v>2</v>
+      </c>
+      <c r="L107" s="1">
+        <v>2</v>
+      </c>
+      <c r="M107" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N107" s="13">
+        <v>150</v>
+      </c>
+      <c r="O107" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P107" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q107" s="1">
+        <v>400</v>
+      </c>
+      <c r="R107" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S107" s="13">
+        <v>1</v>
+      </c>
+      <c r="T107" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U107" s="16">
+        <v>81600000000000</v>
+      </c>
+      <c r="V107" s="15">
+        <f>V106*1.2</f>
+        <v>150624</v>
+      </c>
+      <c r="W107" s="13">
+        <v>0</v>
+      </c>
+      <c r="X107" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y107" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z107" s="86"/>
+      <c r="AA107" s="87"/>
+      <c r="AB107" s="87"/>
+    </row>
+    <row r="108" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>205</v>
+      </c>
+      <c r="B108" s="13">
+        <v>12</v>
+      </c>
+      <c r="C108" s="13">
+        <v>300</v>
+      </c>
+      <c r="D108" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E108" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F108" s="1">
+        <v>5</v>
+      </c>
+      <c r="G108" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H108" s="16">
+        <v>100</v>
+      </c>
+      <c r="I108" s="13">
+        <v>1</v>
+      </c>
+      <c r="J108" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K108" s="13">
+        <v>2</v>
+      </c>
+      <c r="L108" s="1">
+        <v>2</v>
+      </c>
+      <c r="M108" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N108" s="13">
+        <v>150</v>
+      </c>
+      <c r="O108" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P108" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q108" s="1">
+        <v>400</v>
+      </c>
+      <c r="R108" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S108" s="13">
+        <v>1</v>
+      </c>
+      <c r="T108" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U108" s="16">
+        <v>81600000000000</v>
+      </c>
+      <c r="V108" s="68">
+        <f t="shared" ref="V108:V109" si="9">V107*1.2</f>
+        <v>180748.79999999999</v>
+      </c>
+      <c r="W108" s="13">
+        <v>0</v>
+      </c>
+      <c r="X108" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y108" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z108" s="86"/>
+      <c r="AA108" s="87"/>
+      <c r="AB108" s="87"/>
+    </row>
+    <row r="109" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>206</v>
+      </c>
+      <c r="B109" s="13">
+        <v>12</v>
+      </c>
+      <c r="C109" s="13">
+        <v>300</v>
+      </c>
+      <c r="D109" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E109" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F109" s="1">
+        <v>5</v>
+      </c>
+      <c r="G109" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H109" s="16">
+        <v>100</v>
+      </c>
+      <c r="I109" s="13">
+        <v>1</v>
+      </c>
+      <c r="J109" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K109" s="13">
+        <v>2</v>
+      </c>
+      <c r="L109" s="1">
+        <v>2</v>
+      </c>
+      <c r="M109" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N109" s="13">
+        <v>150</v>
+      </c>
+      <c r="O109" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P109" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q109" s="1">
+        <v>400</v>
+      </c>
+      <c r="R109" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S109" s="13">
+        <v>1</v>
+      </c>
+      <c r="T109" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U109" s="16">
+        <v>81600000000000</v>
+      </c>
+      <c r="V109" s="68">
+        <f t="shared" si="9"/>
+        <v>216898.55999999997</v>
+      </c>
+      <c r="W109" s="13">
+        <v>0</v>
+      </c>
+      <c r="X109" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y109" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z109" s="86"/>
+      <c r="AA109" s="87"/>
+      <c r="AB109" s="87"/>
+    </row>
+    <row r="110" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>207</v>
+      </c>
+      <c r="B110" s="13">
+        <v>12</v>
+      </c>
+      <c r="C110" s="13">
+        <v>300</v>
+      </c>
+      <c r="D110" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E110" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F110" s="1">
+        <v>5</v>
+      </c>
+      <c r="G110" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H110" s="16">
+        <v>100</v>
+      </c>
+      <c r="I110" s="13">
+        <v>1</v>
+      </c>
+      <c r="J110" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K110" s="13">
+        <v>2</v>
+      </c>
+      <c r="L110" s="1">
+        <v>2</v>
+      </c>
+      <c r="M110" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N110" s="13">
+        <v>150</v>
+      </c>
+      <c r="O110" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P110" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q110" s="1">
+        <v>400</v>
+      </c>
+      <c r="R110" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S110" s="13">
+        <v>1</v>
+      </c>
+      <c r="T110" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U110" s="16">
+        <v>81600000000000</v>
+      </c>
+      <c r="V110" s="68">
+        <f>V109*1.2</f>
+        <v>260278.27199999994</v>
+      </c>
+      <c r="W110" s="13">
+        <v>0</v>
+      </c>
+      <c r="X110" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y110" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z110" s="86"/>
+      <c r="AA110" s="87"/>
+      <c r="AB110" s="87"/>
+    </row>
+    <row r="111" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>208</v>
+      </c>
+      <c r="B111" s="13">
+        <v>12</v>
+      </c>
+      <c r="C111" s="13">
+        <v>300</v>
+      </c>
+      <c r="D111" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E111" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F111" s="1">
+        <v>5</v>
+      </c>
+      <c r="G111" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H111" s="16">
+        <v>100</v>
+      </c>
+      <c r="I111" s="13">
+        <v>1</v>
+      </c>
+      <c r="J111" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K111" s="13">
+        <v>2</v>
+      </c>
+      <c r="L111" s="1">
+        <v>2</v>
+      </c>
+      <c r="M111" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N111" s="13">
+        <v>150</v>
+      </c>
+      <c r="O111" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P111" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q111" s="1">
+        <v>400</v>
+      </c>
+      <c r="R111" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S111" s="13">
+        <v>1</v>
+      </c>
+      <c r="T111" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U111" s="16">
+        <v>81600000000000</v>
+      </c>
+      <c r="V111" s="68">
+        <f>V110*1.2</f>
+        <v>312333.92639999994</v>
+      </c>
+      <c r="W111" s="13">
+        <v>0</v>
+      </c>
+      <c r="X111" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y111" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z111" s="86"/>
+      <c r="AA111" s="87"/>
+      <c r="AB111" s="87"/>
+    </row>
+    <row r="112" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A112" s="43">
+        <v>209</v>
+      </c>
+      <c r="B112" s="41">
+        <v>12</v>
+      </c>
+      <c r="C112" s="41">
+        <v>300</v>
+      </c>
+      <c r="D112" s="42">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E112" s="42">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F112" s="43">
+        <v>5</v>
+      </c>
+      <c r="G112" s="42">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H112" s="42">
+        <v>100</v>
+      </c>
+      <c r="I112" s="41">
+        <v>1</v>
+      </c>
+      <c r="J112" s="44">
+        <v>1E-4</v>
+      </c>
+      <c r="K112" s="41">
+        <v>2</v>
+      </c>
+      <c r="L112" s="43">
+        <v>2</v>
+      </c>
+      <c r="M112" s="42">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N112" s="41">
+        <v>150</v>
+      </c>
+      <c r="O112" s="41">
+        <v>0.2</v>
+      </c>
+      <c r="P112" s="41">
+        <v>300</v>
+      </c>
+      <c r="Q112" s="43">
+        <v>400</v>
+      </c>
+      <c r="R112" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="S112" s="41">
+        <v>1</v>
+      </c>
+      <c r="T112" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="U112" s="42">
+        <v>81600000000000</v>
+      </c>
+      <c r="V112" s="41">
+        <f t="shared" ref="V112:V122" si="10">30*4184</f>
+        <v>125520</v>
+      </c>
+      <c r="W112" s="41">
+        <v>0</v>
+      </c>
+      <c r="X112" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y112" s="43">
+        <v>1</v>
+      </c>
+      <c r="Z112" s="77" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA112" s="80"/>
+      <c r="AB112" s="80"/>
+    </row>
+    <row r="113" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>210</v>
+      </c>
+      <c r="B113" s="13">
+        <v>12</v>
+      </c>
+      <c r="C113" s="13">
+        <v>300</v>
+      </c>
+      <c r="D113" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E113" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F113" s="1">
+        <v>5</v>
+      </c>
+      <c r="G113" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H113" s="16">
+        <v>100</v>
+      </c>
+      <c r="I113" s="13">
+        <v>1</v>
+      </c>
+      <c r="J113" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K113" s="13">
+        <v>2</v>
+      </c>
+      <c r="L113" s="1">
+        <v>2</v>
+      </c>
+      <c r="M113" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N113" s="13">
+        <v>150</v>
+      </c>
+      <c r="O113" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P113" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q113" s="1">
+        <v>400</v>
+      </c>
+      <c r="R113" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S113" s="13">
+        <v>1</v>
+      </c>
+      <c r="T113" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U113" s="19">
+        <f>1.5*U112</f>
+        <v>122400000000000</v>
+      </c>
+      <c r="V113" s="13">
+        <f t="shared" si="10"/>
+        <v>125520</v>
+      </c>
+      <c r="W113" s="13">
+        <v>0</v>
+      </c>
+      <c r="X113" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y113" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z113" s="77"/>
+      <c r="AA113" s="80"/>
+      <c r="AB113" s="80"/>
+    </row>
+    <row r="114" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>211</v>
+      </c>
+      <c r="B114" s="13">
+        <v>12</v>
+      </c>
+      <c r="C114" s="13">
+        <v>300</v>
+      </c>
+      <c r="D114" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E114" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F114" s="1">
+        <v>5</v>
+      </c>
+      <c r="G114" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H114" s="16">
+        <v>100</v>
+      </c>
+      <c r="I114" s="13">
+        <v>1</v>
+      </c>
+      <c r="J114" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K114" s="13">
+        <v>2</v>
+      </c>
+      <c r="L114" s="1">
+        <v>2</v>
+      </c>
+      <c r="M114" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N114" s="13">
+        <v>150</v>
+      </c>
+      <c r="O114" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P114" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q114" s="1">
+        <v>400</v>
+      </c>
+      <c r="R114" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S114" s="13">
+        <v>1</v>
+      </c>
+      <c r="T114" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U114" s="19">
+        <f t="shared" ref="U114:U122" si="11">1.5*U113</f>
+        <v>183600000000000</v>
+      </c>
+      <c r="V114" s="13">
+        <f t="shared" si="10"/>
+        <v>125520</v>
+      </c>
+      <c r="W114" s="13">
+        <v>0</v>
+      </c>
+      <c r="X114" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y114" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z114" s="77"/>
+      <c r="AA114" s="80"/>
+      <c r="AB114" s="80"/>
+    </row>
+    <row r="115" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>212</v>
+      </c>
+      <c r="B115" s="13">
+        <v>12</v>
+      </c>
+      <c r="C115" s="13">
+        <v>300</v>
+      </c>
+      <c r="D115" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E115" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F115" s="1">
+        <v>5</v>
+      </c>
+      <c r="G115" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H115" s="16">
+        <v>100</v>
+      </c>
+      <c r="I115" s="13">
+        <v>1</v>
+      </c>
+      <c r="J115" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K115" s="13">
+        <v>2</v>
+      </c>
+      <c r="L115" s="1">
+        <v>2</v>
+      </c>
+      <c r="M115" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N115" s="13">
+        <v>150</v>
+      </c>
+      <c r="O115" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P115" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q115" s="1">
+        <v>400</v>
+      </c>
+      <c r="R115" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S115" s="13">
+        <v>1</v>
+      </c>
+      <c r="T115" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U115" s="19">
+        <f t="shared" si="11"/>
+        <v>275400000000000</v>
+      </c>
+      <c r="V115" s="13">
+        <f t="shared" si="10"/>
+        <v>125520</v>
+      </c>
+      <c r="W115" s="13">
+        <v>0</v>
+      </c>
+      <c r="X115" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y115" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z115" s="77"/>
+      <c r="AA115" s="80"/>
+      <c r="AB115" s="80"/>
+    </row>
+    <row r="116" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>213</v>
+      </c>
+      <c r="B116" s="13">
+        <v>12</v>
+      </c>
+      <c r="C116" s="13">
+        <v>300</v>
+      </c>
+      <c r="D116" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E116" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F116" s="1">
+        <v>5</v>
+      </c>
+      <c r="G116" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H116" s="16">
+        <v>100</v>
+      </c>
+      <c r="I116" s="13">
+        <v>1</v>
+      </c>
+      <c r="J116" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K116" s="13">
+        <v>2</v>
+      </c>
+      <c r="L116" s="1">
+        <v>2</v>
+      </c>
+      <c r="M116" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N116" s="13">
+        <v>150</v>
+      </c>
+      <c r="O116" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P116" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q116" s="1">
+        <v>400</v>
+      </c>
+      <c r="R116" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S116" s="13">
+        <v>1</v>
+      </c>
+      <c r="T116" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U116" s="19">
+        <f t="shared" si="11"/>
+        <v>413100000000000</v>
+      </c>
+      <c r="V116" s="13">
+        <f t="shared" si="10"/>
+        <v>125520</v>
+      </c>
+      <c r="W116" s="13">
+        <v>0</v>
+      </c>
+      <c r="X116" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y116" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z116" s="77"/>
+      <c r="AA116" s="80"/>
+      <c r="AB116" s="80"/>
+    </row>
+    <row r="117" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>214</v>
+      </c>
+      <c r="B117" s="13">
+        <v>12</v>
+      </c>
+      <c r="C117" s="13">
+        <v>300</v>
+      </c>
+      <c r="D117" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E117" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F117" s="1">
+        <v>5</v>
+      </c>
+      <c r="G117" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H117" s="16">
+        <v>100</v>
+      </c>
+      <c r="I117" s="13">
+        <v>1</v>
+      </c>
+      <c r="J117" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K117" s="13">
+        <v>2</v>
+      </c>
+      <c r="L117" s="1">
+        <v>2</v>
+      </c>
+      <c r="M117" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N117" s="13">
+        <v>150</v>
+      </c>
+      <c r="O117" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P117" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q117" s="1">
+        <v>400</v>
+      </c>
+      <c r="R117" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S117" s="13">
+        <v>1</v>
+      </c>
+      <c r="T117" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U117" s="19">
+        <f>1.5*U116</f>
+        <v>619650000000000</v>
+      </c>
+      <c r="V117" s="13">
+        <f t="shared" si="10"/>
+        <v>125520</v>
+      </c>
+      <c r="W117" s="13">
+        <v>0</v>
+      </c>
+      <c r="X117" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y117" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z117" s="77"/>
+      <c r="AA117" s="80"/>
+      <c r="AB117" s="80"/>
+    </row>
+    <row r="118" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>215</v>
+      </c>
+      <c r="B118" s="13">
+        <v>12</v>
+      </c>
+      <c r="C118" s="13">
+        <v>300</v>
+      </c>
+      <c r="D118" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E118" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F118" s="1">
+        <v>5</v>
+      </c>
+      <c r="G118" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H118" s="16">
+        <v>100</v>
+      </c>
+      <c r="I118" s="13">
+        <v>1</v>
+      </c>
+      <c r="J118" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K118" s="13">
+        <v>2</v>
+      </c>
+      <c r="L118" s="1">
+        <v>2</v>
+      </c>
+      <c r="M118" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N118" s="13">
+        <v>150</v>
+      </c>
+      <c r="O118" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P118" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q118" s="1">
+        <v>400</v>
+      </c>
+      <c r="R118" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S118" s="13">
+        <v>1</v>
+      </c>
+      <c r="T118" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U118" s="19">
+        <f t="shared" si="11"/>
+        <v>929475000000000</v>
+      </c>
+      <c r="V118" s="13">
+        <f t="shared" si="10"/>
+        <v>125520</v>
+      </c>
+      <c r="W118" s="13">
+        <v>0</v>
+      </c>
+      <c r="X118" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y118" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z118" s="77"/>
+      <c r="AA118" s="80"/>
+      <c r="AB118" s="80"/>
+    </row>
+    <row r="119" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>216</v>
+      </c>
+      <c r="B119" s="13">
+        <v>12</v>
+      </c>
+      <c r="C119" s="13">
+        <v>300</v>
+      </c>
+      <c r="D119" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E119" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F119" s="1">
+        <v>5</v>
+      </c>
+      <c r="G119" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H119" s="16">
+        <v>100</v>
+      </c>
+      <c r="I119" s="13">
+        <v>1</v>
+      </c>
+      <c r="J119" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K119" s="13">
+        <v>2</v>
+      </c>
+      <c r="L119" s="1">
+        <v>2</v>
+      </c>
+      <c r="M119" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N119" s="13">
+        <v>150</v>
+      </c>
+      <c r="O119" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P119" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q119" s="1">
+        <v>400</v>
+      </c>
+      <c r="R119" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S119" s="13">
+        <v>1</v>
+      </c>
+      <c r="T119" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U119" s="19">
+        <f t="shared" si="11"/>
+        <v>1394212500000000</v>
+      </c>
+      <c r="V119" s="13">
+        <f t="shared" si="10"/>
+        <v>125520</v>
+      </c>
+      <c r="W119" s="13">
+        <v>0</v>
+      </c>
+      <c r="X119" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y119" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z119" s="77"/>
+      <c r="AA119" s="80"/>
+      <c r="AB119" s="80"/>
+    </row>
+    <row r="120" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>217</v>
+      </c>
+      <c r="B120" s="13">
+        <v>12</v>
+      </c>
+      <c r="C120" s="13">
+        <v>300</v>
+      </c>
+      <c r="D120" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E120" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F120" s="1">
+        <v>5</v>
+      </c>
+      <c r="G120" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H120" s="16">
+        <v>100</v>
+      </c>
+      <c r="I120" s="13">
+        <v>1</v>
+      </c>
+      <c r="J120" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K120" s="13">
+        <v>2</v>
+      </c>
+      <c r="L120" s="1">
+        <v>2</v>
+      </c>
+      <c r="M120" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N120" s="13">
+        <v>150</v>
+      </c>
+      <c r="O120" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P120" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q120" s="1">
+        <v>400</v>
+      </c>
+      <c r="R120" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S120" s="13">
+        <v>1</v>
+      </c>
+      <c r="T120" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U120" s="19">
+        <f>1.5*U119</f>
+        <v>2091318750000000</v>
+      </c>
+      <c r="V120" s="13">
+        <f t="shared" si="10"/>
+        <v>125520</v>
+      </c>
+      <c r="W120" s="13">
+        <v>0</v>
+      </c>
+      <c r="X120" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y120" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z120" s="77"/>
+      <c r="AA120" s="80"/>
+      <c r="AB120" s="80"/>
+    </row>
+    <row r="121" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>218</v>
+      </c>
+      <c r="B121" s="13">
+        <v>12</v>
+      </c>
+      <c r="C121" s="13">
+        <v>300</v>
+      </c>
+      <c r="D121" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E121" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F121" s="1">
+        <v>5</v>
+      </c>
+      <c r="G121" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H121" s="16">
+        <v>100</v>
+      </c>
+      <c r="I121" s="13">
+        <v>1</v>
+      </c>
+      <c r="J121" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K121" s="13">
+        <v>2</v>
+      </c>
+      <c r="L121" s="1">
+        <v>2</v>
+      </c>
+      <c r="M121" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N121" s="13">
+        <v>150</v>
+      </c>
+      <c r="O121" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P121" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q121" s="1">
+        <v>400</v>
+      </c>
+      <c r="R121" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S121" s="13">
+        <v>1</v>
+      </c>
+      <c r="T121" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U121" s="19">
+        <f t="shared" si="11"/>
+        <v>3136978125000000</v>
+      </c>
+      <c r="V121" s="13">
+        <f t="shared" si="10"/>
+        <v>125520</v>
+      </c>
+      <c r="W121" s="13">
+        <v>0</v>
+      </c>
+      <c r="X121" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y121" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z121" s="77"/>
+      <c r="AA121" s="80"/>
+      <c r="AB121" s="80"/>
+    </row>
+    <row r="122" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>219</v>
+      </c>
+      <c r="B122" s="13">
+        <v>12</v>
+      </c>
+      <c r="C122" s="13">
+        <v>300</v>
+      </c>
+      <c r="D122" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E122" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F122" s="1">
+        <v>5</v>
+      </c>
+      <c r="G122" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H122" s="16">
+        <v>100</v>
+      </c>
+      <c r="I122" s="13">
+        <v>1</v>
+      </c>
+      <c r="J122" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K122" s="13">
+        <v>2</v>
+      </c>
+      <c r="L122" s="1">
+        <v>2</v>
+      </c>
+      <c r="M122" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N122" s="13">
+        <v>150</v>
+      </c>
+      <c r="O122" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P122" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q122" s="1">
+        <v>400</v>
+      </c>
+      <c r="R122" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S122" s="13">
+        <v>1</v>
+      </c>
+      <c r="T122" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U122" s="19">
+        <f t="shared" si="11"/>
+        <v>4705467187500000</v>
+      </c>
+      <c r="V122" s="13">
+        <f t="shared" si="10"/>
+        <v>125520</v>
+      </c>
+      <c r="W122" s="13">
+        <v>0</v>
+      </c>
+      <c r="X122" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y122" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z122" s="77"/>
+      <c r="AA122" s="80"/>
+      <c r="AB122" s="80"/>
+    </row>
+    <row r="123" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>220</v>
+      </c>
+      <c r="B123" s="15">
+        <v>12</v>
+      </c>
+      <c r="C123" s="15">
+        <v>700</v>
+      </c>
+      <c r="D123" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E123" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F123" s="50">
+        <v>5</v>
+      </c>
+      <c r="G123" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H123" s="51">
+        <v>100</v>
+      </c>
+      <c r="I123" s="15">
+        <v>1</v>
+      </c>
+      <c r="J123" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K123" s="15">
+        <v>2</v>
+      </c>
+      <c r="L123" s="50">
+        <v>2</v>
+      </c>
+      <c r="M123" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N123" s="15">
+        <v>150</v>
+      </c>
+      <c r="O123" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P123" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q123" s="50">
+        <v>400</v>
+      </c>
+      <c r="R123" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S123" s="15">
+        <v>1</v>
+      </c>
+      <c r="T123" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U123" s="51">
+        <v>81600000000000</v>
+      </c>
+      <c r="V123" s="68">
+        <f>V122/1.2</f>
+        <v>104600</v>
+      </c>
+      <c r="W123" s="13">
+        <v>0</v>
+      </c>
+      <c r="X123" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y123" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z123" s="77"/>
+      <c r="AA123" s="80"/>
+      <c r="AB123" s="80"/>
+    </row>
+    <row r="124" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>221</v>
+      </c>
+      <c r="B124" s="15">
+        <v>12</v>
+      </c>
+      <c r="C124" s="15">
+        <v>700</v>
+      </c>
+      <c r="D124" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E124" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F124" s="50">
+        <v>5</v>
+      </c>
+      <c r="G124" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H124" s="51">
+        <v>100</v>
+      </c>
+      <c r="I124" s="15">
+        <v>1</v>
+      </c>
+      <c r="J124" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K124" s="15">
+        <v>2</v>
+      </c>
+      <c r="L124" s="50">
+        <v>2</v>
+      </c>
+      <c r="M124" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N124" s="15">
+        <v>150</v>
+      </c>
+      <c r="O124" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P124" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q124" s="50">
+        <v>400</v>
+      </c>
+      <c r="R124" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S124" s="15">
+        <v>1</v>
+      </c>
+      <c r="T124" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U124" s="51">
+        <v>81600000000000</v>
+      </c>
+      <c r="V124" s="68">
+        <f t="shared" ref="V124:V129" si="12">V123/1.2</f>
+        <v>87166.666666666672</v>
+      </c>
+      <c r="W124" s="13">
+        <v>0</v>
+      </c>
+      <c r="X124" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y124" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z124" s="77"/>
+      <c r="AA124" s="80"/>
+      <c r="AB124" s="80"/>
+    </row>
+    <row r="125" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>222</v>
+      </c>
+      <c r="B125" s="15">
+        <v>12</v>
+      </c>
+      <c r="C125" s="15">
+        <v>700</v>
+      </c>
+      <c r="D125" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E125" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F125" s="50">
+        <v>5</v>
+      </c>
+      <c r="G125" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H125" s="51">
+        <v>100</v>
+      </c>
+      <c r="I125" s="15">
+        <v>1</v>
+      </c>
+      <c r="J125" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K125" s="15">
+        <v>2</v>
+      </c>
+      <c r="L125" s="50">
+        <v>2</v>
+      </c>
+      <c r="M125" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N125" s="15">
+        <v>150</v>
+      </c>
+      <c r="O125" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P125" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q125" s="50">
+        <v>400</v>
+      </c>
+      <c r="R125" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S125" s="15">
+        <v>1</v>
+      </c>
+      <c r="T125" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U125" s="51">
+        <v>81600000000000</v>
+      </c>
+      <c r="V125" s="68">
+        <f t="shared" si="12"/>
+        <v>72638.888888888891</v>
+      </c>
+      <c r="W125" s="13">
+        <v>0</v>
+      </c>
+      <c r="X125" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y125" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z125" s="77"/>
+      <c r="AA125" s="80"/>
+      <c r="AB125" s="80"/>
+    </row>
+    <row r="126" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>223</v>
+      </c>
+      <c r="B126" s="15">
+        <v>12</v>
+      </c>
+      <c r="C126" s="15">
+        <v>700</v>
+      </c>
+      <c r="D126" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E126" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F126" s="50">
+        <v>5</v>
+      </c>
+      <c r="G126" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H126" s="51">
+        <v>100</v>
+      </c>
+      <c r="I126" s="15">
+        <v>1</v>
+      </c>
+      <c r="J126" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K126" s="15">
+        <v>2</v>
+      </c>
+      <c r="L126" s="50">
+        <v>2</v>
+      </c>
+      <c r="M126" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N126" s="15">
+        <v>150</v>
+      </c>
+      <c r="O126" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P126" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q126" s="50">
+        <v>400</v>
+      </c>
+      <c r="R126" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S126" s="15">
+        <v>1</v>
+      </c>
+      <c r="T126" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U126" s="51">
+        <v>81600000000000</v>
+      </c>
+      <c r="V126" s="68">
+        <f t="shared" si="12"/>
+        <v>60532.407407407409</v>
+      </c>
+      <c r="W126" s="13">
+        <v>0</v>
+      </c>
+      <c r="X126" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y126" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z126" s="77"/>
+      <c r="AA126" s="80"/>
+      <c r="AB126" s="80"/>
+    </row>
+    <row r="127" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>224</v>
+      </c>
+      <c r="B127" s="15">
+        <v>12</v>
+      </c>
+      <c r="C127" s="15">
+        <v>700</v>
+      </c>
+      <c r="D127" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E127" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F127" s="50">
+        <v>5</v>
+      </c>
+      <c r="G127" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H127" s="51">
+        <v>100</v>
+      </c>
+      <c r="I127" s="15">
+        <v>1</v>
+      </c>
+      <c r="J127" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K127" s="15">
+        <v>2</v>
+      </c>
+      <c r="L127" s="50">
+        <v>2</v>
+      </c>
+      <c r="M127" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N127" s="15">
+        <v>150</v>
+      </c>
+      <c r="O127" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P127" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q127" s="50">
+        <v>400</v>
+      </c>
+      <c r="R127" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S127" s="15">
+        <v>1</v>
+      </c>
+      <c r="T127" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U127" s="51">
+        <v>81600000000000</v>
+      </c>
+      <c r="V127" s="68">
+        <f t="shared" si="12"/>
+        <v>50443.672839506173</v>
+      </c>
+      <c r="W127" s="13">
+        <v>0</v>
+      </c>
+      <c r="X127" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y127" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z127" s="77"/>
+      <c r="AA127" s="80"/>
+      <c r="AB127" s="80"/>
+    </row>
+    <row r="128" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>225</v>
+      </c>
+      <c r="B128" s="15">
+        <v>12</v>
+      </c>
+      <c r="C128" s="15">
+        <v>700</v>
+      </c>
+      <c r="D128" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E128" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F128" s="50">
+        <v>5</v>
+      </c>
+      <c r="G128" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H128" s="51">
+        <v>100</v>
+      </c>
+      <c r="I128" s="15">
+        <v>1</v>
+      </c>
+      <c r="J128" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K128" s="15">
+        <v>2</v>
+      </c>
+      <c r="L128" s="50">
+        <v>2</v>
+      </c>
+      <c r="M128" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N128" s="15">
+        <v>150</v>
+      </c>
+      <c r="O128" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P128" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q128" s="50">
+        <v>400</v>
+      </c>
+      <c r="R128" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S128" s="15">
+        <v>1</v>
+      </c>
+      <c r="T128" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U128" s="51">
+        <v>81600000000000</v>
+      </c>
+      <c r="V128" s="68">
+        <f>V127/1.2</f>
+        <v>42036.394032921809</v>
+      </c>
+      <c r="W128" s="13">
+        <v>0</v>
+      </c>
+      <c r="X128" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y128" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z128" s="77"/>
+      <c r="AA128" s="80"/>
+      <c r="AB128" s="80"/>
+    </row>
+    <row r="129" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>226</v>
+      </c>
+      <c r="B129" s="15">
+        <v>12</v>
+      </c>
+      <c r="C129" s="15">
+        <v>700</v>
+      </c>
+      <c r="D129" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E129" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F129" s="50">
+        <v>5</v>
+      </c>
+      <c r="G129" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H129" s="51">
+        <v>100</v>
+      </c>
+      <c r="I129" s="15">
+        <v>1</v>
+      </c>
+      <c r="J129" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K129" s="15">
+        <v>2</v>
+      </c>
+      <c r="L129" s="50">
+        <v>2</v>
+      </c>
+      <c r="M129" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N129" s="15">
+        <v>150</v>
+      </c>
+      <c r="O129" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P129" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q129" s="50">
+        <v>400</v>
+      </c>
+      <c r="R129" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S129" s="15">
+        <v>1</v>
+      </c>
+      <c r="T129" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U129" s="51">
+        <v>81600000000000</v>
+      </c>
+      <c r="V129" s="68">
+        <f t="shared" si="12"/>
+        <v>35030.328360768173</v>
+      </c>
+      <c r="W129" s="13">
+        <v>0</v>
+      </c>
+      <c r="X129" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y129" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z129" s="77"/>
+      <c r="AA129" s="80"/>
+      <c r="AB129" s="80"/>
+    </row>
+    <row r="130" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A130" s="43">
+        <v>227</v>
+      </c>
+      <c r="B130" s="41">
+        <v>12</v>
+      </c>
+      <c r="C130" s="41">
+        <v>300</v>
+      </c>
+      <c r="D130" s="42">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E130" s="42">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F130" s="43">
+        <v>5</v>
+      </c>
+      <c r="G130" s="42">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H130" s="42">
+        <v>100</v>
+      </c>
+      <c r="I130" s="41">
+        <v>1</v>
+      </c>
+      <c r="J130" s="44">
+        <v>1E-4</v>
+      </c>
+      <c r="K130" s="41">
+        <v>2</v>
+      </c>
+      <c r="L130" s="43">
+        <v>2</v>
+      </c>
+      <c r="M130" s="42">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N130" s="41">
+        <v>150</v>
+      </c>
+      <c r="O130" s="41">
+        <v>0.2</v>
+      </c>
+      <c r="P130" s="41">
+        <v>300</v>
+      </c>
+      <c r="Q130" s="43">
+        <v>400</v>
+      </c>
+      <c r="R130" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="S130" s="41">
+        <v>1</v>
+      </c>
+      <c r="T130" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="U130" s="42">
+        <v>81600000000000</v>
+      </c>
+      <c r="V130" s="41">
+        <f t="shared" ref="V130:V140" si="13">30*4184</f>
+        <v>125520</v>
+      </c>
+      <c r="W130" s="41">
+        <v>0</v>
+      </c>
+      <c r="X130" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y130" s="43">
+        <v>1</v>
+      </c>
+      <c r="Z130" s="77" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA130" s="80"/>
+      <c r="AB130" s="80"/>
+    </row>
+    <row r="131" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>228</v>
+      </c>
+      <c r="B131" s="13">
+        <v>12</v>
+      </c>
+      <c r="C131" s="13">
+        <v>300</v>
+      </c>
+      <c r="D131" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E131" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F131" s="1">
+        <v>5</v>
+      </c>
+      <c r="G131" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H131" s="16">
+        <v>100</v>
+      </c>
+      <c r="I131" s="13">
+        <v>1</v>
+      </c>
+      <c r="J131" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K131" s="13">
+        <v>2</v>
+      </c>
+      <c r="L131" s="1">
+        <v>2</v>
+      </c>
+      <c r="M131" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N131" s="13">
+        <v>150</v>
+      </c>
+      <c r="O131" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P131" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q131" s="1">
+        <v>400</v>
+      </c>
+      <c r="R131" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S131" s="13">
+        <v>1</v>
+      </c>
+      <c r="T131" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U131" s="19">
+        <f>1.5*U130</f>
+        <v>122400000000000</v>
+      </c>
+      <c r="V131" s="13">
+        <f t="shared" si="13"/>
+        <v>125520</v>
+      </c>
+      <c r="W131" s="13">
+        <v>0</v>
+      </c>
+      <c r="X131" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y131" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z131" s="77"/>
+      <c r="AA131" s="80"/>
+      <c r="AB131" s="80"/>
+    </row>
+    <row r="132" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>229</v>
+      </c>
+      <c r="B132" s="13">
+        <v>12</v>
+      </c>
+      <c r="C132" s="13">
+        <v>300</v>
+      </c>
+      <c r="D132" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E132" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F132" s="1">
+        <v>5</v>
+      </c>
+      <c r="G132" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H132" s="16">
+        <v>100</v>
+      </c>
+      <c r="I132" s="13">
+        <v>1</v>
+      </c>
+      <c r="J132" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K132" s="13">
+        <v>2</v>
+      </c>
+      <c r="L132" s="1">
+        <v>2</v>
+      </c>
+      <c r="M132" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N132" s="13">
+        <v>150</v>
+      </c>
+      <c r="O132" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P132" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q132" s="1">
+        <v>400</v>
+      </c>
+      <c r="R132" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S132" s="13">
+        <v>1</v>
+      </c>
+      <c r="T132" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U132" s="19">
+        <f t="shared" ref="U132:U140" si="14">1.5*U131</f>
+        <v>183600000000000</v>
+      </c>
+      <c r="V132" s="13">
+        <f t="shared" si="13"/>
+        <v>125520</v>
+      </c>
+      <c r="W132" s="13">
+        <v>0</v>
+      </c>
+      <c r="X132" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y132" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z132" s="77"/>
+      <c r="AA132" s="80"/>
+      <c r="AB132" s="80"/>
+    </row>
+    <row r="133" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
+        <v>230</v>
+      </c>
+      <c r="B133" s="13">
+        <v>12</v>
+      </c>
+      <c r="C133" s="13">
+        <v>300</v>
+      </c>
+      <c r="D133" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E133" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F133" s="1">
+        <v>5</v>
+      </c>
+      <c r="G133" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H133" s="16">
+        <v>100</v>
+      </c>
+      <c r="I133" s="13">
+        <v>1</v>
+      </c>
+      <c r="J133" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K133" s="13">
+        <v>2</v>
+      </c>
+      <c r="L133" s="1">
+        <v>2</v>
+      </c>
+      <c r="M133" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N133" s="13">
+        <v>150</v>
+      </c>
+      <c r="O133" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P133" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q133" s="1">
+        <v>400</v>
+      </c>
+      <c r="R133" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S133" s="13">
+        <v>1</v>
+      </c>
+      <c r="T133" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U133" s="19">
+        <f t="shared" si="14"/>
+        <v>275400000000000</v>
+      </c>
+      <c r="V133" s="13">
+        <f t="shared" si="13"/>
+        <v>125520</v>
+      </c>
+      <c r="W133" s="13">
+        <v>0</v>
+      </c>
+      <c r="X133" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y133" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z133" s="77"/>
+      <c r="AA133" s="80"/>
+      <c r="AB133" s="80"/>
+    </row>
+    <row r="134" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
+        <v>231</v>
+      </c>
+      <c r="B134" s="13">
+        <v>12</v>
+      </c>
+      <c r="C134" s="13">
+        <v>300</v>
+      </c>
+      <c r="D134" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E134" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F134" s="1">
+        <v>5</v>
+      </c>
+      <c r="G134" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H134" s="16">
+        <v>100</v>
+      </c>
+      <c r="I134" s="13">
+        <v>1</v>
+      </c>
+      <c r="J134" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K134" s="13">
+        <v>2</v>
+      </c>
+      <c r="L134" s="1">
+        <v>2</v>
+      </c>
+      <c r="M134" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N134" s="13">
+        <v>150</v>
+      </c>
+      <c r="O134" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P134" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q134" s="1">
+        <v>400</v>
+      </c>
+      <c r="R134" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S134" s="13">
+        <v>1</v>
+      </c>
+      <c r="T134" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U134" s="19">
+        <f t="shared" si="14"/>
+        <v>413100000000000</v>
+      </c>
+      <c r="V134" s="13">
+        <f t="shared" si="13"/>
+        <v>125520</v>
+      </c>
+      <c r="W134" s="13">
+        <v>0</v>
+      </c>
+      <c r="X134" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y134" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z134" s="77"/>
+      <c r="AA134" s="80"/>
+      <c r="AB134" s="80"/>
+    </row>
+    <row r="135" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
+        <v>232</v>
+      </c>
+      <c r="B135" s="13">
+        <v>12</v>
+      </c>
+      <c r="C135" s="13">
+        <v>300</v>
+      </c>
+      <c r="D135" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E135" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F135" s="1">
+        <v>5</v>
+      </c>
+      <c r="G135" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H135" s="16">
+        <v>100</v>
+      </c>
+      <c r="I135" s="13">
+        <v>1</v>
+      </c>
+      <c r="J135" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K135" s="13">
+        <v>2</v>
+      </c>
+      <c r="L135" s="1">
+        <v>2</v>
+      </c>
+      <c r="M135" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N135" s="13">
+        <v>150</v>
+      </c>
+      <c r="O135" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P135" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q135" s="1">
+        <v>400</v>
+      </c>
+      <c r="R135" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S135" s="13">
+        <v>1</v>
+      </c>
+      <c r="T135" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U135" s="19">
+        <f>1.5*U134</f>
+        <v>619650000000000</v>
+      </c>
+      <c r="V135" s="13">
+        <f t="shared" si="13"/>
+        <v>125520</v>
+      </c>
+      <c r="W135" s="13">
+        <v>0</v>
+      </c>
+      <c r="X135" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y135" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z135" s="77"/>
+      <c r="AA135" s="80"/>
+      <c r="AB135" s="80"/>
+    </row>
+    <row r="136" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
+        <v>233</v>
+      </c>
+      <c r="B136" s="13">
+        <v>12</v>
+      </c>
+      <c r="C136" s="13">
+        <v>300</v>
+      </c>
+      <c r="D136" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E136" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F136" s="1">
+        <v>5</v>
+      </c>
+      <c r="G136" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H136" s="16">
+        <v>100</v>
+      </c>
+      <c r="I136" s="13">
+        <v>1</v>
+      </c>
+      <c r="J136" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K136" s="13">
+        <v>2</v>
+      </c>
+      <c r="L136" s="1">
+        <v>2</v>
+      </c>
+      <c r="M136" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N136" s="13">
+        <v>150</v>
+      </c>
+      <c r="O136" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P136" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q136" s="1">
+        <v>400</v>
+      </c>
+      <c r="R136" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S136" s="13">
+        <v>1</v>
+      </c>
+      <c r="T136" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U136" s="19">
+        <f t="shared" si="14"/>
+        <v>929475000000000</v>
+      </c>
+      <c r="V136" s="13">
+        <f t="shared" si="13"/>
+        <v>125520</v>
+      </c>
+      <c r="W136" s="13">
+        <v>0</v>
+      </c>
+      <c r="X136" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y136" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z136" s="77"/>
+      <c r="AA136" s="80"/>
+      <c r="AB136" s="80"/>
+    </row>
+    <row r="137" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
+        <v>234</v>
+      </c>
+      <c r="B137" s="13">
+        <v>12</v>
+      </c>
+      <c r="C137" s="13">
+        <v>300</v>
+      </c>
+      <c r="D137" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E137" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F137" s="1">
+        <v>5</v>
+      </c>
+      <c r="G137" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H137" s="16">
+        <v>100</v>
+      </c>
+      <c r="I137" s="13">
+        <v>1</v>
+      </c>
+      <c r="J137" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K137" s="13">
+        <v>2</v>
+      </c>
+      <c r="L137" s="1">
+        <v>2</v>
+      </c>
+      <c r="M137" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N137" s="13">
+        <v>150</v>
+      </c>
+      <c r="O137" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P137" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q137" s="1">
+        <v>400</v>
+      </c>
+      <c r="R137" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S137" s="13">
+        <v>1</v>
+      </c>
+      <c r="T137" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U137" s="19">
+        <f t="shared" si="14"/>
+        <v>1394212500000000</v>
+      </c>
+      <c r="V137" s="13">
+        <f t="shared" si="13"/>
+        <v>125520</v>
+      </c>
+      <c r="W137" s="13">
+        <v>0</v>
+      </c>
+      <c r="X137" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y137" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z137" s="77"/>
+      <c r="AA137" s="80"/>
+      <c r="AB137" s="80"/>
+    </row>
+    <row r="138" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
+        <v>235</v>
+      </c>
+      <c r="B138" s="13">
+        <v>12</v>
+      </c>
+      <c r="C138" s="13">
+        <v>300</v>
+      </c>
+      <c r="D138" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E138" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F138" s="1">
+        <v>5</v>
+      </c>
+      <c r="G138" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H138" s="16">
+        <v>100</v>
+      </c>
+      <c r="I138" s="13">
+        <v>1</v>
+      </c>
+      <c r="J138" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K138" s="13">
+        <v>2</v>
+      </c>
+      <c r="L138" s="1">
+        <v>2</v>
+      </c>
+      <c r="M138" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N138" s="13">
+        <v>150</v>
+      </c>
+      <c r="O138" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P138" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q138" s="1">
+        <v>400</v>
+      </c>
+      <c r="R138" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S138" s="13">
+        <v>1</v>
+      </c>
+      <c r="T138" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U138" s="19">
+        <f>1.5*U137</f>
+        <v>2091318750000000</v>
+      </c>
+      <c r="V138" s="13">
+        <f t="shared" si="13"/>
+        <v>125520</v>
+      </c>
+      <c r="W138" s="13">
+        <v>0</v>
+      </c>
+      <c r="X138" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y138" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z138" s="77"/>
+      <c r="AA138" s="80"/>
+      <c r="AB138" s="80"/>
+    </row>
+    <row r="139" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
+        <v>236</v>
+      </c>
+      <c r="B139" s="13">
+        <v>12</v>
+      </c>
+      <c r="C139" s="13">
+        <v>300</v>
+      </c>
+      <c r="D139" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E139" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F139" s="1">
+        <v>5</v>
+      </c>
+      <c r="G139" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H139" s="16">
+        <v>100</v>
+      </c>
+      <c r="I139" s="13">
+        <v>1</v>
+      </c>
+      <c r="J139" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K139" s="13">
+        <v>2</v>
+      </c>
+      <c r="L139" s="1">
+        <v>2</v>
+      </c>
+      <c r="M139" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N139" s="13">
+        <v>150</v>
+      </c>
+      <c r="O139" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P139" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q139" s="1">
+        <v>400</v>
+      </c>
+      <c r="R139" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S139" s="13">
+        <v>1</v>
+      </c>
+      <c r="T139" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U139" s="19">
+        <f t="shared" si="14"/>
+        <v>3136978125000000</v>
+      </c>
+      <c r="V139" s="13">
+        <f t="shared" si="13"/>
+        <v>125520</v>
+      </c>
+      <c r="W139" s="13">
+        <v>0</v>
+      </c>
+      <c r="X139" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y139" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z139" s="77"/>
+      <c r="AA139" s="80"/>
+      <c r="AB139" s="80"/>
+    </row>
+    <row r="140" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
+        <v>237</v>
+      </c>
+      <c r="B140" s="13">
+        <v>12</v>
+      </c>
+      <c r="C140" s="13">
+        <v>300</v>
+      </c>
+      <c r="D140" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E140" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F140" s="1">
+        <v>5</v>
+      </c>
+      <c r="G140" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H140" s="16">
+        <v>100</v>
+      </c>
+      <c r="I140" s="13">
+        <v>1</v>
+      </c>
+      <c r="J140" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K140" s="13">
+        <v>2</v>
+      </c>
+      <c r="L140" s="1">
+        <v>2</v>
+      </c>
+      <c r="M140" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N140" s="13">
+        <v>150</v>
+      </c>
+      <c r="O140" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P140" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q140" s="1">
+        <v>400</v>
+      </c>
+      <c r="R140" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S140" s="13">
+        <v>1</v>
+      </c>
+      <c r="T140" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U140" s="19">
+        <f t="shared" si="14"/>
+        <v>4705467187500000</v>
+      </c>
+      <c r="V140" s="13">
+        <f t="shared" si="13"/>
+        <v>125520</v>
+      </c>
+      <c r="W140" s="13">
+        <v>0</v>
+      </c>
+      <c r="X140" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y140" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z140" s="77"/>
+      <c r="AA140" s="80"/>
+      <c r="AB140" s="80"/>
+    </row>
+    <row r="141" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
+        <v>238</v>
+      </c>
+      <c r="B141" s="15">
+        <v>12</v>
+      </c>
+      <c r="C141" s="15">
+        <v>700</v>
+      </c>
+      <c r="D141" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E141" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F141" s="50">
+        <v>5</v>
+      </c>
+      <c r="G141" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H141" s="51">
+        <v>100</v>
+      </c>
+      <c r="I141" s="15">
+        <v>1</v>
+      </c>
+      <c r="J141" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K141" s="15">
+        <v>2</v>
+      </c>
+      <c r="L141" s="50">
+        <v>2</v>
+      </c>
+      <c r="M141" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N141" s="15">
+        <v>150</v>
+      </c>
+      <c r="O141" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P141" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q141" s="50">
+        <v>400</v>
+      </c>
+      <c r="R141" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S141" s="15">
+        <v>1</v>
+      </c>
+      <c r="T141" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U141" s="51">
+        <v>81600000000000</v>
+      </c>
+      <c r="V141" s="68">
+        <f>V140/1.2</f>
+        <v>104600</v>
+      </c>
+      <c r="W141" s="13">
+        <v>0</v>
+      </c>
+      <c r="X141" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y141" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z141" s="77"/>
+      <c r="AA141" s="80"/>
+      <c r="AB141" s="80"/>
+    </row>
+    <row r="142" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
+        <v>239</v>
+      </c>
+      <c r="B142" s="15">
+        <v>12</v>
+      </c>
+      <c r="C142" s="15">
+        <v>700</v>
+      </c>
+      <c r="D142" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E142" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F142" s="50">
+        <v>5</v>
+      </c>
+      <c r="G142" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H142" s="51">
+        <v>100</v>
+      </c>
+      <c r="I142" s="15">
+        <v>1</v>
+      </c>
+      <c r="J142" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K142" s="15">
+        <v>2</v>
+      </c>
+      <c r="L142" s="50">
+        <v>2</v>
+      </c>
+      <c r="M142" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N142" s="15">
+        <v>150</v>
+      </c>
+      <c r="O142" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P142" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q142" s="50">
+        <v>400</v>
+      </c>
+      <c r="R142" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S142" s="15">
+        <v>1</v>
+      </c>
+      <c r="T142" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U142" s="51">
+        <v>81600000000000</v>
+      </c>
+      <c r="V142" s="68">
+        <f t="shared" ref="V142:V147" si="15">V141/1.2</f>
+        <v>87166.666666666672</v>
+      </c>
+      <c r="W142" s="13">
+        <v>0</v>
+      </c>
+      <c r="X142" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y142" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z142" s="77"/>
+      <c r="AA142" s="80"/>
+      <c r="AB142" s="80"/>
+    </row>
+    <row r="143" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
+        <v>240</v>
+      </c>
+      <c r="B143" s="15">
+        <v>12</v>
+      </c>
+      <c r="C143" s="15">
+        <v>700</v>
+      </c>
+      <c r="D143" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E143" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F143" s="50">
+        <v>5</v>
+      </c>
+      <c r="G143" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H143" s="51">
+        <v>100</v>
+      </c>
+      <c r="I143" s="15">
+        <v>1</v>
+      </c>
+      <c r="J143" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K143" s="15">
+        <v>2</v>
+      </c>
+      <c r="L143" s="50">
+        <v>2</v>
+      </c>
+      <c r="M143" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N143" s="15">
+        <v>150</v>
+      </c>
+      <c r="O143" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P143" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q143" s="50">
+        <v>400</v>
+      </c>
+      <c r="R143" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S143" s="15">
+        <v>1</v>
+      </c>
+      <c r="T143" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U143" s="51">
+        <v>81600000000000</v>
+      </c>
+      <c r="V143" s="68">
+        <f t="shared" si="15"/>
+        <v>72638.888888888891</v>
+      </c>
+      <c r="W143" s="13">
+        <v>0</v>
+      </c>
+      <c r="X143" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y143" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z143" s="77"/>
+      <c r="AA143" s="80"/>
+      <c r="AB143" s="80"/>
+    </row>
+    <row r="144" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
+        <v>241</v>
+      </c>
+      <c r="B144" s="15">
+        <v>12</v>
+      </c>
+      <c r="C144" s="15">
+        <v>700</v>
+      </c>
+      <c r="D144" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E144" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F144" s="50">
+        <v>5</v>
+      </c>
+      <c r="G144" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H144" s="51">
+        <v>100</v>
+      </c>
+      <c r="I144" s="15">
+        <v>1</v>
+      </c>
+      <c r="J144" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K144" s="15">
+        <v>2</v>
+      </c>
+      <c r="L144" s="50">
+        <v>2</v>
+      </c>
+      <c r="M144" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N144" s="15">
+        <v>150</v>
+      </c>
+      <c r="O144" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P144" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q144" s="50">
+        <v>400</v>
+      </c>
+      <c r="R144" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S144" s="15">
+        <v>1</v>
+      </c>
+      <c r="T144" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U144" s="51">
+        <v>81600000000000</v>
+      </c>
+      <c r="V144" s="68">
+        <f t="shared" si="15"/>
+        <v>60532.407407407409</v>
+      </c>
+      <c r="W144" s="13">
+        <v>0</v>
+      </c>
+      <c r="X144" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y144" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z144" s="77"/>
+      <c r="AA144" s="80"/>
+      <c r="AB144" s="80"/>
+    </row>
+    <row r="145" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
+        <v>242</v>
+      </c>
+      <c r="B145" s="15">
+        <v>12</v>
+      </c>
+      <c r="C145" s="15">
+        <v>700</v>
+      </c>
+      <c r="D145" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E145" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F145" s="50">
+        <v>5</v>
+      </c>
+      <c r="G145" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H145" s="51">
+        <v>100</v>
+      </c>
+      <c r="I145" s="15">
+        <v>1</v>
+      </c>
+      <c r="J145" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K145" s="15">
+        <v>2</v>
+      </c>
+      <c r="L145" s="50">
+        <v>2</v>
+      </c>
+      <c r="M145" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N145" s="15">
+        <v>150</v>
+      </c>
+      <c r="O145" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P145" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q145" s="50">
+        <v>400</v>
+      </c>
+      <c r="R145" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S145" s="15">
+        <v>1</v>
+      </c>
+      <c r="T145" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U145" s="51">
+        <v>81600000000000</v>
+      </c>
+      <c r="V145" s="68">
+        <f t="shared" si="15"/>
+        <v>50443.672839506173</v>
+      </c>
+      <c r="W145" s="13">
+        <v>0</v>
+      </c>
+      <c r="X145" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y145" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z145" s="77"/>
+      <c r="AA145" s="80"/>
+      <c r="AB145" s="80"/>
+    </row>
+    <row r="146" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
+        <v>243</v>
+      </c>
+      <c r="B146" s="15">
+        <v>12</v>
+      </c>
+      <c r="C146" s="15">
+        <v>700</v>
+      </c>
+      <c r="D146" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E146" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F146" s="50">
+        <v>5</v>
+      </c>
+      <c r="G146" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H146" s="51">
+        <v>100</v>
+      </c>
+      <c r="I146" s="15">
+        <v>1</v>
+      </c>
+      <c r="J146" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K146" s="15">
+        <v>2</v>
+      </c>
+      <c r="L146" s="50">
+        <v>2</v>
+      </c>
+      <c r="M146" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N146" s="15">
+        <v>150</v>
+      </c>
+      <c r="O146" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P146" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q146" s="50">
+        <v>400</v>
+      </c>
+      <c r="R146" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S146" s="15">
+        <v>1</v>
+      </c>
+      <c r="T146" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U146" s="51">
+        <v>81600000000000</v>
+      </c>
+      <c r="V146" s="68">
+        <f>V145/1.2</f>
+        <v>42036.394032921809</v>
+      </c>
+      <c r="W146" s="13">
+        <v>0</v>
+      </c>
+      <c r="X146" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y146" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z146" s="77"/>
+      <c r="AA146" s="80"/>
+      <c r="AB146" s="80"/>
+    </row>
+    <row r="147" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
+        <v>244</v>
+      </c>
+      <c r="B147" s="15">
+        <v>12</v>
+      </c>
+      <c r="C147" s="15">
+        <v>700</v>
+      </c>
+      <c r="D147" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E147" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F147" s="50">
+        <v>5</v>
+      </c>
+      <c r="G147" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H147" s="51">
+        <v>100</v>
+      </c>
+      <c r="I147" s="15">
+        <v>1</v>
+      </c>
+      <c r="J147" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K147" s="15">
+        <v>2</v>
+      </c>
+      <c r="L147" s="50">
+        <v>2</v>
+      </c>
+      <c r="M147" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N147" s="15">
+        <v>150</v>
+      </c>
+      <c r="O147" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P147" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q147" s="50">
+        <v>400</v>
+      </c>
+      <c r="R147" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S147" s="15">
+        <v>1</v>
+      </c>
+      <c r="T147" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U147" s="51">
+        <v>81600000000000</v>
+      </c>
+      <c r="V147" s="68">
+        <f t="shared" si="15"/>
+        <v>35030.328360768173</v>
+      </c>
+      <c r="W147" s="13">
+        <v>0</v>
+      </c>
+      <c r="X147" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y147" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z147" s="77"/>
+      <c r="AA147" s="80"/>
+      <c r="AB147" s="80"/>
+    </row>
+    <row r="148" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="43">
+        <v>245</v>
+      </c>
+      <c r="B148" s="45">
+        <v>12</v>
+      </c>
+      <c r="C148" s="45">
+        <v>2000</v>
+      </c>
+      <c r="D148" s="47">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E148" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F148" s="40">
+        <v>5</v>
+      </c>
+      <c r="G148" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H148" s="47">
+        <v>100</v>
+      </c>
+      <c r="I148" s="45">
+        <v>1</v>
+      </c>
+      <c r="J148" s="48">
+        <v>1E-4</v>
+      </c>
+      <c r="K148" s="45">
+        <v>2</v>
+      </c>
+      <c r="L148" s="40">
+        <v>2</v>
+      </c>
+      <c r="M148" s="47">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N148" s="45">
+        <v>150</v>
+      </c>
+      <c r="O148" s="45">
+        <v>0.2</v>
+      </c>
+      <c r="P148" s="45">
+        <v>300</v>
+      </c>
+      <c r="Q148" s="40">
+        <v>1000</v>
+      </c>
+      <c r="R148" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="S148" s="45">
+        <v>1</v>
+      </c>
+      <c r="T148" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="U148" s="47">
+        <v>81600000000000</v>
+      </c>
+      <c r="V148" s="45">
+        <f t="shared" ref="V148:V150" si="16">30*4184</f>
+        <v>125520</v>
+      </c>
+      <c r="W148" s="45">
+        <v>0</v>
+      </c>
+      <c r="X148" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y148" s="40">
+        <v>1</v>
+      </c>
+      <c r="Z148" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA148" s="78"/>
+      <c r="AB148" s="78"/>
+    </row>
+    <row r="149" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
+        <v>246</v>
+      </c>
+      <c r="B149" s="15">
+        <v>12</v>
+      </c>
+      <c r="C149" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D149" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E149" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F149" s="50">
+        <v>5</v>
+      </c>
+      <c r="G149" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H149" s="51">
+        <v>100</v>
+      </c>
+      <c r="I149" s="15">
+        <v>1</v>
+      </c>
+      <c r="J149" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K149" s="15">
+        <v>2</v>
+      </c>
+      <c r="L149" s="50">
+        <v>2</v>
+      </c>
+      <c r="M149" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N149" s="15">
+        <v>150</v>
+      </c>
+      <c r="O149" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P149" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q149" s="50">
+        <v>1000</v>
+      </c>
+      <c r="R149" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S149" s="15">
+        <v>1</v>
+      </c>
+      <c r="T149" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U149" s="51">
+        <f>5*U148</f>
+        <v>408000000000000</v>
+      </c>
+      <c r="V149" s="15">
+        <f t="shared" si="16"/>
+        <v>125520</v>
+      </c>
+      <c r="W149" s="15">
+        <v>0</v>
+      </c>
+      <c r="X149" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y149" s="50">
+        <v>1</v>
+      </c>
+      <c r="Z149" s="77"/>
+      <c r="AA149" s="78"/>
+      <c r="AB149" s="78"/>
+    </row>
+    <row r="150" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
+        <v>247</v>
+      </c>
+      <c r="B150" s="15">
+        <v>12</v>
+      </c>
+      <c r="C150" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D150" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E150" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F150" s="50">
+        <v>5</v>
+      </c>
+      <c r="G150" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H150" s="51">
+        <v>100</v>
+      </c>
+      <c r="I150" s="15">
+        <v>1</v>
+      </c>
+      <c r="J150" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K150" s="15">
+        <v>2</v>
+      </c>
+      <c r="L150" s="50">
+        <v>2</v>
+      </c>
+      <c r="M150" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N150" s="15">
+        <v>150</v>
+      </c>
+      <c r="O150" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P150" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q150" s="50">
+        <v>1000</v>
+      </c>
+      <c r="R150" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S150" s="15">
+        <v>1</v>
+      </c>
+      <c r="T150" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U150" s="51">
+        <f>5*U149</f>
+        <v>2040000000000000</v>
+      </c>
+      <c r="V150" s="15">
+        <f t="shared" si="16"/>
+        <v>125520</v>
+      </c>
+      <c r="W150" s="15">
+        <v>0</v>
+      </c>
+      <c r="X150" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y150" s="50">
+        <v>1</v>
+      </c>
+      <c r="Z150" s="77"/>
+      <c r="AA150" s="78"/>
+      <c r="AB150" s="78"/>
+    </row>
+    <row r="151" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
+        <v>248</v>
+      </c>
+      <c r="B151" s="15">
+        <v>12</v>
+      </c>
+      <c r="C151" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D151" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E151" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F151" s="50">
+        <v>5</v>
+      </c>
+      <c r="G151" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H151" s="51">
+        <v>100</v>
+      </c>
+      <c r="I151" s="15">
+        <v>1</v>
+      </c>
+      <c r="J151" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K151" s="15">
+        <v>2</v>
+      </c>
+      <c r="L151" s="50">
+        <v>2</v>
+      </c>
+      <c r="M151" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N151" s="15">
+        <v>150</v>
+      </c>
+      <c r="O151" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P151" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q151" s="50">
+        <v>1000</v>
+      </c>
+      <c r="R151" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S151" s="15">
+        <v>1</v>
+      </c>
+      <c r="T151" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U151" s="51">
+        <v>81600000000000</v>
+      </c>
+      <c r="V151" s="15">
+        <f>V150/5</f>
+        <v>25104</v>
+      </c>
+      <c r="W151" s="15">
+        <v>0</v>
+      </c>
+      <c r="X151" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y151" s="50">
+        <v>1</v>
+      </c>
+      <c r="Z151" s="77"/>
+      <c r="AA151" s="78"/>
+      <c r="AB151" s="78"/>
+    </row>
+    <row r="152" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A152" s="27">
+        <v>249</v>
+      </c>
+      <c r="B152" s="15">
+        <v>12</v>
+      </c>
+      <c r="C152" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D152" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E152" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F152" s="50">
+        <v>5</v>
+      </c>
+      <c r="G152" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H152" s="51">
+        <v>100</v>
+      </c>
+      <c r="I152" s="15">
+        <v>1</v>
+      </c>
+      <c r="J152" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K152" s="15">
+        <v>2</v>
+      </c>
+      <c r="L152" s="50">
+        <v>2</v>
+      </c>
+      <c r="M152" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N152" s="15">
+        <v>150</v>
+      </c>
+      <c r="O152" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P152" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q152" s="50">
+        <v>1000</v>
+      </c>
+      <c r="R152" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S152" s="15">
+        <v>1</v>
+      </c>
+      <c r="T152" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U152" s="51">
+        <v>81600000000000</v>
+      </c>
+      <c r="V152" s="68">
+        <f>V151/5</f>
+        <v>5020.8</v>
+      </c>
+      <c r="W152" s="15">
+        <v>0</v>
+      </c>
+      <c r="X152" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y152" s="50">
+        <v>1</v>
+      </c>
+      <c r="Z152" s="77"/>
+      <c r="AA152" s="78"/>
+      <c r="AB152" s="78"/>
+    </row>
+    <row r="153" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
+        <v>250</v>
+      </c>
+      <c r="B153" s="41">
+        <v>12</v>
+      </c>
+      <c r="C153" s="41">
+        <v>300</v>
+      </c>
+      <c r="D153" s="42">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E153" s="42">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F153" s="43">
+        <v>5</v>
+      </c>
+      <c r="G153" s="42">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H153" s="42">
+        <v>100</v>
+      </c>
+      <c r="I153" s="41">
+        <v>1</v>
+      </c>
+      <c r="J153" s="44">
+        <v>1E-4</v>
+      </c>
+      <c r="K153" s="41">
+        <v>2</v>
+      </c>
+      <c r="L153" s="43">
+        <v>2</v>
+      </c>
+      <c r="M153" s="42">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N153" s="41">
+        <v>150</v>
+      </c>
+      <c r="O153" s="41">
+        <v>0.2</v>
+      </c>
+      <c r="P153" s="41">
+        <v>300</v>
+      </c>
+      <c r="Q153" s="43">
+        <v>400</v>
+      </c>
+      <c r="R153" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="S153" s="41">
+        <v>1</v>
+      </c>
+      <c r="T153" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="U153" s="42">
+        <v>81600000000000</v>
+      </c>
+      <c r="V153" s="41">
+        <f t="shared" ref="V153" si="17">30*4184</f>
+        <v>125520</v>
+      </c>
+      <c r="W153" s="41">
+        <v>0</v>
+      </c>
+      <c r="X153" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y153" s="43">
+        <v>1</v>
+      </c>
+      <c r="Z153" s="77" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA153" s="78"/>
+      <c r="AB153" s="78"/>
+    </row>
+    <row r="154" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
+        <v>251</v>
+      </c>
+      <c r="B154" s="15">
+        <v>12</v>
+      </c>
+      <c r="C154" s="15">
+        <v>700</v>
+      </c>
+      <c r="D154" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E154" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F154" s="50">
+        <v>5</v>
+      </c>
+      <c r="G154" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H154" s="51">
+        <v>100</v>
+      </c>
+      <c r="I154" s="15">
+        <v>1</v>
+      </c>
+      <c r="J154" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K154" s="15">
+        <v>2</v>
+      </c>
+      <c r="L154" s="50">
+        <v>2</v>
+      </c>
+      <c r="M154" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N154" s="15">
+        <v>150</v>
+      </c>
+      <c r="O154" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P154" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q154" s="50">
+        <v>400</v>
+      </c>
+      <c r="R154" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S154" s="15">
+        <v>1</v>
+      </c>
+      <c r="T154" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U154" s="19">
+        <f>1.5*$U$138</f>
+        <v>3136978125000000</v>
+      </c>
+      <c r="V154">
+        <f>V153</f>
+        <v>125520</v>
+      </c>
+      <c r="W154" s="13">
+        <v>0</v>
+      </c>
+      <c r="X154" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y154" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z154" s="77"/>
+      <c r="AA154" s="78"/>
+      <c r="AB154" s="78"/>
+    </row>
+    <row r="155" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
+        <v>252</v>
+      </c>
+      <c r="B155" s="13">
+        <v>12</v>
+      </c>
+      <c r="C155" s="13">
+        <v>300</v>
+      </c>
+      <c r="D155" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E155" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F155" s="1">
+        <v>5</v>
+      </c>
+      <c r="G155" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H155" s="16">
+        <v>100</v>
+      </c>
+      <c r="I155" s="13">
+        <v>1</v>
+      </c>
+      <c r="J155" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K155" s="13">
+        <v>2</v>
+      </c>
+      <c r="L155" s="1">
+        <v>2</v>
+      </c>
+      <c r="M155" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N155" s="13">
+        <v>150</v>
+      </c>
+      <c r="O155" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P155" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q155" s="1">
+        <v>400</v>
+      </c>
+      <c r="R155" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S155" s="13">
+        <v>1</v>
+      </c>
+      <c r="T155" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U155" s="19">
+        <f>1.5*$U$139</f>
+        <v>4705467187500000</v>
+      </c>
+      <c r="V155">
+        <f>V154</f>
+        <v>125520</v>
+      </c>
+      <c r="W155" s="13">
+        <v>0</v>
+      </c>
+      <c r="X155" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y155" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z155" s="77"/>
+      <c r="AA155" s="78"/>
+      <c r="AB155" s="78"/>
+    </row>
+    <row r="156" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A156" s="1">
+        <v>253</v>
+      </c>
+      <c r="B156" s="15">
+        <v>12</v>
+      </c>
+      <c r="C156" s="15">
+        <v>700</v>
+      </c>
+      <c r="D156" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E156" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F156" s="50">
+        <v>5</v>
+      </c>
+      <c r="G156" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H156" s="51">
+        <v>100</v>
+      </c>
+      <c r="I156" s="15">
+        <v>1</v>
+      </c>
+      <c r="J156" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K156" s="15">
+        <v>2</v>
+      </c>
+      <c r="L156" s="50">
+        <v>2</v>
+      </c>
+      <c r="M156" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N156" s="15">
+        <v>150</v>
+      </c>
+      <c r="O156" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P156" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q156" s="50">
+        <v>400</v>
+      </c>
+      <c r="R156" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S156" s="15">
+        <v>1</v>
+      </c>
+      <c r="T156" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U156" s="19">
+        <f>$U$153</f>
+        <v>81600000000000</v>
+      </c>
+      <c r="V156" s="69">
+        <f>$V$145</f>
+        <v>50443.672839506173</v>
+      </c>
+      <c r="W156" s="13">
+        <v>0</v>
+      </c>
+      <c r="X156" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y156" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z156" s="77"/>
+      <c r="AA156" s="78"/>
+      <c r="AB156" s="78"/>
+    </row>
+    <row r="157" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A157" s="1">
+        <v>254</v>
+      </c>
+      <c r="B157" s="15">
+        <v>12</v>
+      </c>
+      <c r="C157" s="15">
+        <v>700</v>
+      </c>
+      <c r="D157" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E157" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F157" s="50">
+        <v>5</v>
+      </c>
+      <c r="G157" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H157" s="51">
+        <v>100</v>
+      </c>
+      <c r="I157" s="15">
+        <v>1</v>
+      </c>
+      <c r="J157" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K157" s="15">
+        <v>2</v>
+      </c>
+      <c r="L157" s="50">
+        <v>2</v>
+      </c>
+      <c r="M157" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N157" s="15">
+        <v>150</v>
+      </c>
+      <c r="O157" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P157" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q157" s="50">
+        <v>400</v>
+      </c>
+      <c r="R157" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S157" s="15">
+        <v>1</v>
+      </c>
+      <c r="T157" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U157" s="19">
+        <f>$U$153</f>
+        <v>81600000000000</v>
+      </c>
+      <c r="V157" s="69">
+        <f>$V$146</f>
+        <v>42036.394032921809</v>
+      </c>
+      <c r="W157" s="13">
+        <v>0</v>
+      </c>
+      <c r="X157" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y157" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z157" s="77"/>
+      <c r="AA157" s="78"/>
+      <c r="AB157" s="78"/>
+    </row>
+    <row r="158" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A158" s="43">
+        <v>255</v>
+      </c>
+      <c r="B158" s="41">
+        <v>12</v>
+      </c>
+      <c r="C158" s="41">
+        <v>2000</v>
+      </c>
+      <c r="D158" s="42">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E158" s="42">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F158" s="43">
+        <v>5</v>
+      </c>
+      <c r="G158" s="42">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H158" s="42">
+        <v>100</v>
+      </c>
+      <c r="I158" s="41">
+        <v>1</v>
+      </c>
+      <c r="J158" s="44">
+        <v>1E-4</v>
+      </c>
+      <c r="K158" s="41">
+        <v>2</v>
+      </c>
+      <c r="L158" s="43">
+        <v>2</v>
+      </c>
+      <c r="M158" s="42">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N158" s="41">
+        <v>150</v>
+      </c>
+      <c r="O158" s="41">
+        <v>0.2</v>
+      </c>
+      <c r="P158" s="41">
+        <v>300</v>
+      </c>
+      <c r="Q158" s="43">
+        <v>400</v>
+      </c>
+      <c r="R158" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="S158" s="41">
+        <v>1</v>
+      </c>
+      <c r="T158" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="U158" s="42">
+        <v>81600000000000</v>
+      </c>
+      <c r="V158" s="41">
+        <f t="shared" ref="V158" si="18">30*4184</f>
+        <v>125520</v>
+      </c>
+      <c r="W158" s="41">
+        <v>0</v>
+      </c>
+      <c r="X158" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y158" s="43">
+        <v>1</v>
+      </c>
+      <c r="Z158" s="77" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA158" s="78"/>
+      <c r="AB158" s="78"/>
+    </row>
+    <row r="159" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A159" s="1">
+        <v>256</v>
+      </c>
+      <c r="B159" s="15">
+        <v>12</v>
+      </c>
+      <c r="C159" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D159" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E159" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F159" s="50">
+        <v>5</v>
+      </c>
+      <c r="G159" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H159" s="51">
+        <v>100</v>
+      </c>
+      <c r="I159" s="15">
+        <v>1</v>
+      </c>
+      <c r="J159" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K159" s="15">
+        <v>2</v>
+      </c>
+      <c r="L159" s="50">
+        <v>2</v>
+      </c>
+      <c r="M159" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N159" s="15">
+        <v>150</v>
+      </c>
+      <c r="O159" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P159" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q159" s="50">
+        <v>400</v>
+      </c>
+      <c r="R159" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S159" s="15">
+        <v>1</v>
+      </c>
+      <c r="T159" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U159" s="19">
+        <f>1.5*$U$138</f>
+        <v>3136978125000000</v>
+      </c>
+      <c r="V159">
+        <f>V158</f>
+        <v>125520</v>
+      </c>
+      <c r="W159" s="13">
+        <v>0</v>
+      </c>
+      <c r="X159" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y159" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z159" s="77"/>
+      <c r="AA159" s="78"/>
+      <c r="AB159" s="78"/>
+    </row>
+    <row r="160" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
+        <v>257</v>
+      </c>
+      <c r="B160" s="13">
+        <v>12</v>
+      </c>
+      <c r="C160" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D160" s="16">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E160" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F160" s="1">
+        <v>5</v>
+      </c>
+      <c r="G160" s="16">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H160" s="16">
+        <v>100</v>
+      </c>
+      <c r="I160" s="13">
+        <v>1</v>
+      </c>
+      <c r="J160" s="17">
+        <v>1E-4</v>
+      </c>
+      <c r="K160" s="13">
+        <v>2</v>
+      </c>
+      <c r="L160" s="1">
+        <v>2</v>
+      </c>
+      <c r="M160" s="16">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N160" s="13">
+        <v>150</v>
+      </c>
+      <c r="O160" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="P160" s="13">
+        <v>300</v>
+      </c>
+      <c r="Q160" s="1">
+        <v>400</v>
+      </c>
+      <c r="R160" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="S160" s="13">
+        <v>1</v>
+      </c>
+      <c r="T160" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U160" s="19">
+        <f>1.5*$U$139</f>
+        <v>4705467187500000</v>
+      </c>
+      <c r="V160">
+        <f>V159</f>
+        <v>125520</v>
+      </c>
+      <c r="W160" s="13">
+        <v>0</v>
+      </c>
+      <c r="X160" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y160" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z160" s="77"/>
+      <c r="AA160" s="78"/>
+      <c r="AB160" s="78"/>
+    </row>
+    <row r="161" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
+        <v>258</v>
+      </c>
+      <c r="B161" s="15">
+        <v>12</v>
+      </c>
+      <c r="C161" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D161" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E161" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F161" s="50">
+        <v>5</v>
+      </c>
+      <c r="G161" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H161" s="51">
+        <v>100</v>
+      </c>
+      <c r="I161" s="15">
+        <v>1</v>
+      </c>
+      <c r="J161" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K161" s="15">
+        <v>2</v>
+      </c>
+      <c r="L161" s="50">
+        <v>2</v>
+      </c>
+      <c r="M161" s="51">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N161" s="15">
+        <v>150</v>
+      </c>
+      <c r="O161" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P161" s="15">
+        <v>300</v>
+      </c>
+      <c r="Q161" s="50">
+        <v>400</v>
+      </c>
+      <c r="R161" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S161" s="15">
+        <v>1</v>
+      </c>
+      <c r="T161" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U161" s="19">
+        <f>$U$153</f>
+        <v>81600000000000</v>
+      </c>
+      <c r="V161" s="69">
+        <f>$V$145</f>
+        <v>50443.672839506173</v>
+      </c>
+      <c r="W161" s="13">
+        <v>0</v>
+      </c>
+      <c r="X161" s="15">
+        <v>1</v>
+      </c>
+      <c r="Y161" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z161" s="77"/>
+      <c r="AA161" s="78"/>
+      <c r="AB161" s="78"/>
+    </row>
+    <row r="162" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A162" s="27">
+        <v>259</v>
+      </c>
+      <c r="B162" s="29">
+        <v>12</v>
+      </c>
+      <c r="C162" s="29">
+        <v>2000</v>
+      </c>
+      <c r="D162" s="58">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E162" s="58">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F162" s="57">
+        <v>5</v>
+      </c>
+      <c r="G162" s="58">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H162" s="58">
+        <v>100</v>
+      </c>
+      <c r="I162" s="29">
+        <v>1</v>
+      </c>
+      <c r="J162" s="59">
+        <v>1E-4</v>
+      </c>
+      <c r="K162" s="29">
+        <v>2</v>
+      </c>
+      <c r="L162" s="57">
+        <v>2</v>
+      </c>
+      <c r="M162" s="58">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N162" s="29">
+        <v>150</v>
+      </c>
+      <c r="O162" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="P162" s="29">
+        <v>300</v>
+      </c>
+      <c r="Q162" s="57">
+        <v>400</v>
+      </c>
+      <c r="R162" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="S162" s="29">
+        <v>1</v>
+      </c>
+      <c r="T162" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="U162" s="26">
+        <f>$U$153</f>
+        <v>81600000000000</v>
+      </c>
+      <c r="V162" s="72">
+        <f>$V$146</f>
+        <v>42036.394032921809</v>
+      </c>
+      <c r="W162" s="25">
+        <v>0</v>
+      </c>
+      <c r="X162" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y162" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z162" s="77"/>
+      <c r="AA162" s="78"/>
+      <c r="AB162" s="78"/>
+    </row>
+    <row r="163" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A163" s="43">
+        <v>260</v>
+      </c>
+      <c r="B163" s="45">
+        <v>12</v>
+      </c>
+      <c r="C163" s="45">
+        <v>700</v>
+      </c>
+      <c r="D163" s="47">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E163" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F163" s="40">
+        <v>5</v>
+      </c>
+      <c r="G163" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H163" s="47">
+        <v>100</v>
+      </c>
+      <c r="I163" s="45">
+        <v>1</v>
+      </c>
+      <c r="J163" s="48">
+        <v>1E-4</v>
+      </c>
+      <c r="K163" s="45">
+        <v>2</v>
+      </c>
+      <c r="L163" s="40">
+        <v>2</v>
+      </c>
+      <c r="M163" s="47">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N163" s="45">
+        <v>150</v>
+      </c>
+      <c r="O163" s="45">
+        <v>0.2</v>
+      </c>
+      <c r="P163" s="45">
+        <v>300</v>
+      </c>
+      <c r="Q163" s="40">
+        <v>400</v>
+      </c>
+      <c r="R163" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="S163" s="45">
+        <v>1</v>
+      </c>
+      <c r="T163" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="U163" s="47">
+        <v>81600000000000</v>
+      </c>
+      <c r="V163" s="45">
+        <f t="shared" ref="V163:V168" si="19">30*4184</f>
+        <v>125520</v>
+      </c>
+      <c r="W163" s="45">
+        <v>0</v>
+      </c>
+      <c r="X163" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y163" s="40">
+        <v>1</v>
+      </c>
+      <c r="Z163" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA163" s="78"/>
+      <c r="AB163" s="78"/>
+    </row>
+    <row r="164" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A164" s="43">
+        <v>261</v>
+      </c>
+      <c r="B164" s="45">
+        <v>12</v>
+      </c>
+      <c r="C164" s="45">
+        <v>700</v>
+      </c>
+      <c r="D164" s="47">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E164" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F164" s="40">
+        <v>5</v>
+      </c>
+      <c r="G164" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H164" s="47">
+        <v>100</v>
+      </c>
+      <c r="I164" s="45">
+        <v>1</v>
+      </c>
+      <c r="J164" s="48">
+        <v>1E-4</v>
+      </c>
+      <c r="K164" s="45">
+        <v>2</v>
+      </c>
+      <c r="L164" s="40">
+        <v>2</v>
+      </c>
+      <c r="M164" s="47">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N164" s="45">
+        <v>150</v>
+      </c>
+      <c r="O164" s="45">
+        <v>0.2</v>
+      </c>
+      <c r="P164" s="45">
+        <v>300</v>
+      </c>
+      <c r="Q164" s="40">
+        <v>400</v>
+      </c>
+      <c r="R164" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="S164" s="45">
+        <v>1</v>
+      </c>
+      <c r="T164" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="U164" s="47">
+        <v>81600000000000</v>
+      </c>
+      <c r="V164" s="45">
+        <f t="shared" si="19"/>
+        <v>125520</v>
+      </c>
+      <c r="W164" s="45">
+        <v>0</v>
+      </c>
+      <c r="X164" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y164" s="40">
+        <v>1</v>
+      </c>
+      <c r="Z164" s="77" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA164" s="78"/>
+      <c r="AB164" s="78"/>
+    </row>
+    <row r="165" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A165" s="43">
+        <v>262</v>
+      </c>
+      <c r="B165" s="45">
+        <v>12</v>
+      </c>
+      <c r="C165" s="45">
+        <v>700</v>
+      </c>
+      <c r="D165" s="47">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E165" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F165" s="40">
+        <v>5</v>
+      </c>
+      <c r="G165" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H165" s="47">
+        <v>100</v>
+      </c>
+      <c r="I165" s="45">
+        <v>1</v>
+      </c>
+      <c r="J165" s="48">
+        <v>1E-4</v>
+      </c>
+      <c r="K165" s="45">
+        <v>2</v>
+      </c>
+      <c r="L165" s="40">
+        <v>2</v>
+      </c>
+      <c r="M165" s="47">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N165" s="45">
+        <v>150</v>
+      </c>
+      <c r="O165" s="45">
+        <v>0.2</v>
+      </c>
+      <c r="P165" s="45">
+        <v>300</v>
+      </c>
+      <c r="Q165" s="40">
+        <v>400</v>
+      </c>
+      <c r="R165" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="S165" s="45">
+        <v>1</v>
+      </c>
+      <c r="T165" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="U165" s="47">
+        <v>81600000000000</v>
+      </c>
+      <c r="V165" s="45">
+        <f t="shared" si="19"/>
+        <v>125520</v>
+      </c>
+      <c r="W165" s="45">
+        <v>0</v>
+      </c>
+      <c r="X165" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y165" s="40">
+        <v>1</v>
+      </c>
+      <c r="Z165" s="77" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA165" s="78"/>
+      <c r="AB165" s="78"/>
+    </row>
+    <row r="166" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A166" s="43">
+        <v>263</v>
+      </c>
+      <c r="B166" s="45">
+        <v>12</v>
+      </c>
+      <c r="C166" s="45">
+        <v>700</v>
+      </c>
+      <c r="D166" s="47">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E166" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F166" s="40">
+        <v>5</v>
+      </c>
+      <c r="G166" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H166" s="47">
+        <v>100</v>
+      </c>
+      <c r="I166" s="45">
+        <v>1</v>
+      </c>
+      <c r="J166" s="48">
+        <v>1E-4</v>
+      </c>
+      <c r="K166" s="45">
+        <v>2</v>
+      </c>
+      <c r="L166" s="40">
+        <v>2</v>
+      </c>
+      <c r="M166" s="47">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N166" s="45">
+        <v>150</v>
+      </c>
+      <c r="O166" s="45">
+        <v>0.2</v>
+      </c>
+      <c r="P166" s="45">
+        <v>300</v>
+      </c>
+      <c r="Q166" s="40">
+        <v>400</v>
+      </c>
+      <c r="R166" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="S166" s="45">
+        <v>1</v>
+      </c>
+      <c r="T166" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="U166" s="47">
+        <v>81600000000000</v>
+      </c>
+      <c r="V166" s="45">
+        <f t="shared" si="19"/>
+        <v>125520</v>
+      </c>
+      <c r="W166" s="45">
+        <v>0</v>
+      </c>
+      <c r="X166" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y166" s="40">
+        <v>1</v>
+      </c>
+      <c r="Z166" s="77" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA166" s="78"/>
+      <c r="AB166" s="78"/>
+    </row>
+    <row r="167" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A167" s="43">
+        <v>264</v>
+      </c>
+      <c r="B167" s="45">
+        <v>12</v>
+      </c>
+      <c r="C167" s="45">
+        <v>700</v>
+      </c>
+      <c r="D167" s="47">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E167" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F167" s="40">
+        <v>5</v>
+      </c>
+      <c r="G167" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H167" s="47">
+        <v>100</v>
+      </c>
+      <c r="I167" s="45">
+        <v>1</v>
+      </c>
+      <c r="J167" s="48">
+        <v>1E-4</v>
+      </c>
+      <c r="K167" s="45">
+        <v>2</v>
+      </c>
+      <c r="L167" s="40">
+        <v>2</v>
+      </c>
+      <c r="M167" s="47">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N167" s="45">
+        <v>150</v>
+      </c>
+      <c r="O167" s="45">
+        <v>0.2</v>
+      </c>
+      <c r="P167" s="45">
+        <v>300</v>
+      </c>
+      <c r="Q167" s="40">
+        <v>400</v>
+      </c>
+      <c r="R167" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="S167" s="45">
+        <v>1</v>
+      </c>
+      <c r="T167" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="U167" s="47">
+        <v>81600000000000</v>
+      </c>
+      <c r="V167" s="45">
+        <f t="shared" si="19"/>
+        <v>125520</v>
+      </c>
+      <c r="W167" s="45">
+        <v>0</v>
+      </c>
+      <c r="X167" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y167" s="40">
+        <v>1</v>
+      </c>
+      <c r="Z167" s="77" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA167" s="78"/>
+      <c r="AB167" s="78"/>
+    </row>
+    <row r="168" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A168" s="43">
+        <v>265</v>
+      </c>
+      <c r="B168" s="45">
+        <v>12</v>
+      </c>
+      <c r="C168" s="45">
+        <v>2000</v>
+      </c>
+      <c r="D168" s="47">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E168" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F168" s="40">
+        <v>5</v>
+      </c>
+      <c r="G168" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H168" s="47">
+        <v>100</v>
+      </c>
+      <c r="I168" s="45">
+        <v>1</v>
+      </c>
+      <c r="J168" s="48">
+        <v>1E-4</v>
+      </c>
+      <c r="K168" s="45">
+        <v>2</v>
+      </c>
+      <c r="L168" s="40">
+        <v>2</v>
+      </c>
+      <c r="M168" s="47">
+        <v>4.2000000000000002E-4</v>
+      </c>
+      <c r="N168" s="45">
+        <v>300</v>
+      </c>
+      <c r="O168" s="45">
+        <v>0.2</v>
+      </c>
+      <c r="P168" s="45">
+        <v>300</v>
+      </c>
+      <c r="Q168" s="40">
+        <v>300</v>
+      </c>
+      <c r="R168" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="S168" s="45">
+        <v>1</v>
+      </c>
+      <c r="T168" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="U168" s="47">
+        <v>81600000000000</v>
+      </c>
+      <c r="V168" s="45">
+        <f t="shared" si="19"/>
+        <v>125520</v>
+      </c>
+      <c r="W168" s="45">
+        <v>0</v>
+      </c>
+      <c r="X168" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y168" s="40">
+        <v>1</v>
+      </c>
+      <c r="Z168" s="70"/>
+      <c r="AA168" s="71"/>
+      <c r="AB168" s="71"/>
+    </row>
+    <row r="169" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z169" s="70"/>
+      <c r="AA169" s="71"/>
+      <c r="AB169" s="71"/>
+    </row>
+    <row r="170" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="Z170" s="70"/>
+      <c r="AA170" s="71"/>
+      <c r="AB170" s="71"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="Z85:AB85"/>
-    <mergeCell ref="Z67:AB84"/>
-    <mergeCell ref="Z59:AB66"/>
+  <mergeCells count="42">
+    <mergeCell ref="Z167:AB167"/>
+    <mergeCell ref="Z164:AB164"/>
+    <mergeCell ref="Z153:AB157"/>
+    <mergeCell ref="Z158:AB162"/>
     <mergeCell ref="Z92:AB93"/>
+    <mergeCell ref="Z163:AB163"/>
+    <mergeCell ref="Z165:AB165"/>
+    <mergeCell ref="Z166:AB166"/>
+    <mergeCell ref="Z90:AB90"/>
+    <mergeCell ref="Z91:AB91"/>
+    <mergeCell ref="Z148:AB152"/>
+    <mergeCell ref="Z130:AB147"/>
+    <mergeCell ref="Z112:AB129"/>
+    <mergeCell ref="Z95:AB111"/>
+    <mergeCell ref="Z94:AB94"/>
+    <mergeCell ref="Z48:AB48"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="Z49:AB49"/>
+    <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="Z6:AB6"/>
+    <mergeCell ref="Z7:AB7"/>
+    <mergeCell ref="Z5:AB5"/>
+    <mergeCell ref="Z4:AB4"/>
+    <mergeCell ref="Z8:AD8"/>
+    <mergeCell ref="Z28:AB28"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="Z10:AB27"/>
+    <mergeCell ref="Z29:AB46"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="M1:Q1"/>
     <mergeCell ref="R1:T1"/>
-    <mergeCell ref="U1:Y1"/>
-    <mergeCell ref="Z6:AB6"/>
-    <mergeCell ref="Z7:AB7"/>
-    <mergeCell ref="Z5:AB5"/>
-    <mergeCell ref="Z4:AB4"/>
-    <mergeCell ref="Z90:AB90"/>
-    <mergeCell ref="Z91:AB91"/>
-    <mergeCell ref="Z8:AD8"/>
-    <mergeCell ref="Z28:AB28"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="Z10:AB27"/>
-    <mergeCell ref="Z29:AB46"/>
     <mergeCell ref="Z50:AB50"/>
-    <mergeCell ref="Z48:AB48"/>
-    <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="Z49:AB49"/>
     <mergeCell ref="Z89:AB89"/>
     <mergeCell ref="Z88:AB88"/>
     <mergeCell ref="Z86:AB87"/>
     <mergeCell ref="Z58:AB58"/>
     <mergeCell ref="Z51:AB57"/>
+    <mergeCell ref="Z85:AB85"/>
+    <mergeCell ref="Z67:AB84"/>
+    <mergeCell ref="Z59:AB66"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Simulations_IDS.xlsx
+++ b/Simulations_IDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documentos_Betran\DropletEvaporation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E07AB97-E313-46A4-8C2E-649D0C9CFB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0A27AB-114D-4E65-B5DF-5BACE378071E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{73239687-5BB6-4FA0-A3B4-8BE280184789}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="113">
   <si>
     <t>ID</t>
   </si>
@@ -794,23 +794,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -821,20 +809,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1155,7 +1155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC78505-487D-4D76-94E1-903AFBAADA28}">
-  <dimension ref="A1:AF352"/>
+  <dimension ref="A1:AF354"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" customWidth="1"/>
@@ -1185,42 +1185,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="102" t="s">
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="104"/>
-      <c r="K1" s="103" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="104"/>
-      <c r="M1" s="102" t="s">
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="106" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="107"/>
+      <c r="M1" s="110" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="103"/>
-      <c r="O1" s="103"/>
-      <c r="P1" s="103"/>
-      <c r="Q1" s="104"/>
-      <c r="R1" s="102" t="s">
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="110" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="103"/>
-      <c r="T1" s="103"/>
-      <c r="U1" s="103" t="s">
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="V1" s="103"/>
-      <c r="W1" s="103"/>
-      <c r="X1" s="103"/>
-      <c r="Y1" s="104"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="106"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="107"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1449,7 +1449,7 @@
       <c r="Y4" s="1">
         <v>1</v>
       </c>
-      <c r="Z4" s="107" t="s">
+      <c r="Z4" s="103" t="s">
         <v>46</v>
       </c>
       <c r="AA4" s="108"/>
@@ -1534,7 +1534,7 @@
       <c r="Y5" s="1">
         <v>1</v>
       </c>
-      <c r="Z5" s="107" t="s">
+      <c r="Z5" s="103" t="s">
         <v>47</v>
       </c>
       <c r="AA5" s="108"/>
@@ -1619,7 +1619,7 @@
       <c r="Y6" s="1">
         <v>1</v>
       </c>
-      <c r="Z6" s="107" t="s">
+      <c r="Z6" s="103" t="s">
         <v>48</v>
       </c>
       <c r="AA6" s="108"/>
@@ -1704,7 +1704,7 @@
       <c r="Y7" s="1">
         <v>1</v>
       </c>
-      <c r="Z7" s="107" t="s">
+      <c r="Z7" s="103" t="s">
         <v>49</v>
       </c>
       <c r="AA7" s="108"/>
@@ -1789,13 +1789,13 @@
       <c r="Y8" s="38">
         <v>1</v>
       </c>
-      <c r="Z8" s="107" t="s">
+      <c r="Z8" s="103" t="s">
         <v>53</v>
       </c>
-      <c r="AA8" s="109"/>
-      <c r="AB8" s="109"/>
-      <c r="AC8" s="109"/>
-      <c r="AD8" s="109"/>
+      <c r="AA8" s="104"/>
+      <c r="AB8" s="104"/>
+      <c r="AC8" s="104"/>
+      <c r="AD8" s="104"/>
       <c r="AE8" s="20"/>
       <c r="AF8" s="20"/>
     </row>
@@ -1876,11 +1876,11 @@
       <c r="Y9" s="1">
         <v>1</v>
       </c>
-      <c r="Z9" s="107" t="s">
+      <c r="Z9" s="103" t="s">
         <v>50</v>
       </c>
-      <c r="AA9" s="109"/>
-      <c r="AB9" s="109"/>
+      <c r="AA9" s="104"/>
+      <c r="AB9" s="104"/>
       <c r="AC9" s="65"/>
       <c r="AD9" s="65"/>
     </row>
@@ -3475,11 +3475,11 @@
       <c r="Y28" s="33">
         <v>1</v>
       </c>
-      <c r="Z28" s="107" t="s">
+      <c r="Z28" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="AA28" s="109"/>
-      <c r="AB28" s="109"/>
+      <c r="AA28" s="104"/>
+      <c r="AB28" s="104"/>
       <c r="AC28" s="65"/>
       <c r="AD28" s="65"/>
     </row>
@@ -5074,11 +5074,11 @@
       <c r="Y47" s="43">
         <v>1</v>
       </c>
-      <c r="Z47" s="107" t="s">
+      <c r="Z47" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="AA47" s="109"/>
-      <c r="AB47" s="109"/>
+      <c r="AA47" s="104"/>
+      <c r="AB47" s="104"/>
       <c r="AC47" s="66"/>
       <c r="AD47" s="65"/>
     </row>
@@ -5160,11 +5160,11 @@
       <c r="Y48" s="43">
         <v>1</v>
       </c>
-      <c r="Z48" s="105" t="s">
+      <c r="Z48" s="101" t="s">
         <v>55</v>
       </c>
-      <c r="AA48" s="110"/>
-      <c r="AB48" s="110"/>
+      <c r="AA48" s="105"/>
+      <c r="AB48" s="105"/>
       <c r="AC48" s="67"/>
       <c r="AD48" s="65"/>
     </row>
@@ -5245,11 +5245,11 @@
       <c r="Y49" s="43">
         <v>1</v>
       </c>
-      <c r="Z49" s="107" t="s">
+      <c r="Z49" s="103" t="s">
         <v>56</v>
       </c>
-      <c r="AA49" s="109"/>
-      <c r="AB49" s="109"/>
+      <c r="AA49" s="104"/>
+      <c r="AB49" s="104"/>
       <c r="AC49" s="65"/>
       <c r="AD49" s="65"/>
     </row>
@@ -5329,11 +5329,11 @@
       <c r="Y50" s="40">
         <v>1</v>
       </c>
-      <c r="Z50" s="107" t="s">
+      <c r="Z50" s="103" t="s">
         <v>57</v>
       </c>
-      <c r="AA50" s="109"/>
-      <c r="AB50" s="109"/>
+      <c r="AA50" s="104"/>
+      <c r="AB50" s="104"/>
       <c r="AC50" s="65"/>
       <c r="AD50" s="65"/>
     </row>
@@ -6004,11 +6004,11 @@
       <c r="Y58" s="53">
         <v>1</v>
       </c>
-      <c r="Z58" s="105" t="s">
+      <c r="Z58" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="AA58" s="110"/>
-      <c r="AB58" s="110"/>
+      <c r="AA58" s="105"/>
+      <c r="AB58" s="105"/>
       <c r="AC58" s="65"/>
       <c r="AD58" s="65"/>
     </row>
@@ -8269,11 +8269,11 @@
       <c r="Y85" s="53">
         <v>1</v>
       </c>
-      <c r="Z85" s="105" t="s">
+      <c r="Z85" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="AA85" s="106"/>
-      <c r="AB85" s="106"/>
+      <c r="AA85" s="102"/>
+      <c r="AB85" s="102"/>
       <c r="AC85" s="65"/>
       <c r="AD85" s="65"/>
     </row>
@@ -8522,11 +8522,11 @@
       <c r="Y88" s="53">
         <v>1</v>
       </c>
-      <c r="Z88" s="105" t="s">
+      <c r="Z88" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="AA88" s="106"/>
-      <c r="AB88" s="106"/>
+      <c r="AA88" s="102"/>
+      <c r="AB88" s="102"/>
       <c r="AC88" s="65"/>
       <c r="AD88" s="65"/>
     </row>
@@ -8607,11 +8607,11 @@
       <c r="Y89" s="40">
         <v>1</v>
       </c>
-      <c r="Z89" s="105" t="s">
+      <c r="Z89" s="101" t="s">
         <v>63</v>
       </c>
-      <c r="AA89" s="106"/>
-      <c r="AB89" s="106"/>
+      <c r="AA89" s="102"/>
+      <c r="AB89" s="102"/>
       <c r="AC89" s="65"/>
       <c r="AD89" s="65"/>
     </row>
@@ -8692,11 +8692,11 @@
       <c r="Y90" s="57">
         <v>1</v>
       </c>
-      <c r="Z90" s="105" t="s">
+      <c r="Z90" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="AA90" s="106"/>
-      <c r="AB90" s="106"/>
+      <c r="AA90" s="102"/>
+      <c r="AB90" s="102"/>
       <c r="AC90" s="65"/>
       <c r="AD90" s="65"/>
     </row>
@@ -8777,11 +8777,11 @@
       <c r="Y91" s="53">
         <v>1</v>
       </c>
-      <c r="Z91" s="105" t="s">
+      <c r="Z91" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="AA91" s="106"/>
-      <c r="AB91" s="106"/>
+      <c r="AA91" s="102"/>
+      <c r="AB91" s="102"/>
       <c r="AC91" s="65"/>
       <c r="AD91" s="65"/>
     </row>
@@ -9113,11 +9113,11 @@
       <c r="Y95" s="1">
         <v>1</v>
       </c>
-      <c r="Z95" s="99" t="s">
+      <c r="Z95" s="111" t="s">
         <v>69</v>
       </c>
-      <c r="AA95" s="100"/>
-      <c r="AB95" s="100"/>
+      <c r="AA95" s="112"/>
+      <c r="AB95" s="112"/>
     </row>
     <row r="96" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
@@ -9197,9 +9197,9 @@
       <c r="Y96" s="1">
         <v>1</v>
       </c>
-      <c r="Z96" s="99"/>
-      <c r="AA96" s="100"/>
-      <c r="AB96" s="100"/>
+      <c r="Z96" s="111"/>
+      <c r="AA96" s="112"/>
+      <c r="AB96" s="112"/>
     </row>
     <row r="97" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
@@ -9279,9 +9279,9 @@
       <c r="Y97" s="1">
         <v>1</v>
       </c>
-      <c r="Z97" s="99"/>
-      <c r="AA97" s="100"/>
-      <c r="AB97" s="100"/>
+      <c r="Z97" s="111"/>
+      <c r="AA97" s="112"/>
+      <c r="AB97" s="112"/>
     </row>
     <row r="98" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
@@ -9361,9 +9361,9 @@
       <c r="Y98" s="1">
         <v>1</v>
       </c>
-      <c r="Z98" s="99"/>
-      <c r="AA98" s="100"/>
-      <c r="AB98" s="100"/>
+      <c r="Z98" s="111"/>
+      <c r="AA98" s="112"/>
+      <c r="AB98" s="112"/>
     </row>
     <row r="99" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
@@ -9443,9 +9443,9 @@
       <c r="Y99" s="1">
         <v>1</v>
       </c>
-      <c r="Z99" s="99"/>
-      <c r="AA99" s="100"/>
-      <c r="AB99" s="100"/>
+      <c r="Z99" s="111"/>
+      <c r="AA99" s="112"/>
+      <c r="AB99" s="112"/>
     </row>
     <row r="100" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
@@ -9525,9 +9525,9 @@
       <c r="Y100" s="1">
         <v>1</v>
       </c>
-      <c r="Z100" s="99"/>
-      <c r="AA100" s="100"/>
-      <c r="AB100" s="100"/>
+      <c r="Z100" s="111"/>
+      <c r="AA100" s="112"/>
+      <c r="AB100" s="112"/>
     </row>
     <row r="101" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
@@ -9607,9 +9607,9 @@
       <c r="Y101" s="1">
         <v>1</v>
       </c>
-      <c r="Z101" s="99"/>
-      <c r="AA101" s="100"/>
-      <c r="AB101" s="100"/>
+      <c r="Z101" s="111"/>
+      <c r="AA101" s="112"/>
+      <c r="AB101" s="112"/>
     </row>
     <row r="102" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
@@ -9689,9 +9689,9 @@
       <c r="Y102" s="1">
         <v>1</v>
       </c>
-      <c r="Z102" s="99"/>
-      <c r="AA102" s="100"/>
-      <c r="AB102" s="100"/>
+      <c r="Z102" s="111"/>
+      <c r="AA102" s="112"/>
+      <c r="AB102" s="112"/>
     </row>
     <row r="103" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
@@ -9771,9 +9771,9 @@
       <c r="Y103" s="1">
         <v>1</v>
       </c>
-      <c r="Z103" s="99"/>
-      <c r="AA103" s="100"/>
-      <c r="AB103" s="100"/>
+      <c r="Z103" s="111"/>
+      <c r="AA103" s="112"/>
+      <c r="AB103" s="112"/>
     </row>
     <row r="104" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
@@ -9853,9 +9853,9 @@
       <c r="Y104" s="1">
         <v>1</v>
       </c>
-      <c r="Z104" s="99"/>
-      <c r="AA104" s="100"/>
-      <c r="AB104" s="100"/>
+      <c r="Z104" s="111"/>
+      <c r="AA104" s="112"/>
+      <c r="AB104" s="112"/>
     </row>
     <row r="105" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
@@ -9935,9 +9935,9 @@
       <c r="Y105" s="1">
         <v>1</v>
       </c>
-      <c r="Z105" s="99"/>
-      <c r="AA105" s="100"/>
-      <c r="AB105" s="100"/>
+      <c r="Z105" s="111"/>
+      <c r="AA105" s="112"/>
+      <c r="AB105" s="112"/>
     </row>
     <row r="106" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
@@ -10017,9 +10017,9 @@
       <c r="Y106" s="1">
         <v>1</v>
       </c>
-      <c r="Z106" s="99"/>
-      <c r="AA106" s="100"/>
-      <c r="AB106" s="100"/>
+      <c r="Z106" s="111"/>
+      <c r="AA106" s="112"/>
+      <c r="AB106" s="112"/>
     </row>
     <row r="107" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
@@ -10098,9 +10098,9 @@
       <c r="Y107" s="1">
         <v>1</v>
       </c>
-      <c r="Z107" s="99"/>
-      <c r="AA107" s="100"/>
-      <c r="AB107" s="100"/>
+      <c r="Z107" s="111"/>
+      <c r="AA107" s="112"/>
+      <c r="AB107" s="112"/>
     </row>
     <row r="108" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
@@ -10179,9 +10179,9 @@
       <c r="Y108" s="1">
         <v>1</v>
       </c>
-      <c r="Z108" s="99"/>
-      <c r="AA108" s="100"/>
-      <c r="AB108" s="100"/>
+      <c r="Z108" s="111"/>
+      <c r="AA108" s="112"/>
+      <c r="AB108" s="112"/>
     </row>
     <row r="109" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
@@ -10260,9 +10260,9 @@
       <c r="Y109" s="1">
         <v>1</v>
       </c>
-      <c r="Z109" s="99"/>
-      <c r="AA109" s="100"/>
-      <c r="AB109" s="100"/>
+      <c r="Z109" s="111"/>
+      <c r="AA109" s="112"/>
+      <c r="AB109" s="112"/>
     </row>
     <row r="110" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
@@ -10341,9 +10341,9 @@
       <c r="Y110" s="1">
         <v>1</v>
       </c>
-      <c r="Z110" s="99"/>
-      <c r="AA110" s="100"/>
-      <c r="AB110" s="100"/>
+      <c r="Z110" s="111"/>
+      <c r="AA110" s="112"/>
+      <c r="AB110" s="112"/>
     </row>
     <row r="111" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
@@ -10422,9 +10422,9 @@
       <c r="Y111" s="1">
         <v>1</v>
       </c>
-      <c r="Z111" s="99"/>
-      <c r="AA111" s="100"/>
-      <c r="AB111" s="100"/>
+      <c r="Z111" s="111"/>
+      <c r="AA111" s="112"/>
+      <c r="AB111" s="112"/>
     </row>
     <row r="112" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A112" s="43">
@@ -15172,11 +15172,11 @@
       <c r="Y169" s="40">
         <v>1</v>
       </c>
-      <c r="Z169" s="99" t="s">
+      <c r="Z169" s="111" t="s">
         <v>82</v>
       </c>
-      <c r="AA169" s="100"/>
-      <c r="AB169" s="100"/>
+      <c r="AA169" s="112"/>
+      <c r="AB169" s="112"/>
     </row>
     <row r="170" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
@@ -15255,9 +15255,9 @@
       <c r="Y170" s="50">
         <v>1</v>
       </c>
-      <c r="Z170" s="99"/>
-      <c r="AA170" s="100"/>
-      <c r="AB170" s="100"/>
+      <c r="Z170" s="111"/>
+      <c r="AA170" s="112"/>
+      <c r="AB170" s="112"/>
     </row>
     <row r="171" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
@@ -15336,9 +15336,9 @@
       <c r="Y171" s="50">
         <v>1</v>
       </c>
-      <c r="Z171" s="99"/>
-      <c r="AA171" s="100"/>
-      <c r="AB171" s="100"/>
+      <c r="Z171" s="111"/>
+      <c r="AA171" s="112"/>
+      <c r="AB171" s="112"/>
     </row>
     <row r="172" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
@@ -15417,9 +15417,9 @@
       <c r="Y172" s="50">
         <v>1</v>
       </c>
-      <c r="Z172" s="99"/>
-      <c r="AA172" s="100"/>
-      <c r="AB172" s="100"/>
+      <c r="Z172" s="111"/>
+      <c r="AA172" s="112"/>
+      <c r="AB172" s="112"/>
     </row>
     <row r="173" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
@@ -15498,9 +15498,9 @@
       <c r="Y173" s="50">
         <v>1</v>
       </c>
-      <c r="Z173" s="99"/>
-      <c r="AA173" s="100"/>
-      <c r="AB173" s="100"/>
+      <c r="Z173" s="111"/>
+      <c r="AA173" s="112"/>
+      <c r="AB173" s="112"/>
     </row>
     <row r="174" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
@@ -15579,9 +15579,9 @@
       <c r="Y174" s="50">
         <v>1</v>
       </c>
-      <c r="Z174" s="99"/>
-      <c r="AA174" s="100"/>
-      <c r="AB174" s="100"/>
+      <c r="Z174" s="111"/>
+      <c r="AA174" s="112"/>
+      <c r="AB174" s="112"/>
     </row>
     <row r="175" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
@@ -15660,9 +15660,9 @@
       <c r="Y175" s="50">
         <v>1</v>
       </c>
-      <c r="Z175" s="99"/>
-      <c r="AA175" s="100"/>
-      <c r="AB175" s="100"/>
+      <c r="Z175" s="111"/>
+      <c r="AA175" s="112"/>
+      <c r="AB175" s="112"/>
     </row>
     <row r="176" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A176" s="43">
@@ -25519,11 +25519,11 @@
       <c r="Y296" s="40">
         <v>1</v>
       </c>
-      <c r="Z296" s="111" t="s">
+      <c r="Z296" s="99" t="s">
         <v>106</v>
       </c>
-      <c r="AA296" s="112"/>
-      <c r="AB296" s="112"/>
+      <c r="AA296" s="100"/>
+      <c r="AB296" s="100"/>
     </row>
     <row r="297" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
@@ -25602,9 +25602,9 @@
       <c r="Y297" s="50">
         <v>1</v>
       </c>
-      <c r="Z297" s="111"/>
-      <c r="AA297" s="112"/>
-      <c r="AB297" s="112"/>
+      <c r="Z297" s="99"/>
+      <c r="AA297" s="100"/>
+      <c r="AB297" s="100"/>
     </row>
     <row r="298" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
@@ -25683,9 +25683,9 @@
       <c r="Y298" s="50">
         <v>1</v>
       </c>
-      <c r="Z298" s="111"/>
-      <c r="AA298" s="112"/>
-      <c r="AB298" s="112"/>
+      <c r="Z298" s="99"/>
+      <c r="AA298" s="100"/>
+      <c r="AB298" s="100"/>
     </row>
     <row r="299" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
@@ -25764,9 +25764,9 @@
       <c r="Y299" s="50">
         <v>1</v>
       </c>
-      <c r="Z299" s="111"/>
-      <c r="AA299" s="112"/>
-      <c r="AB299" s="112"/>
+      <c r="Z299" s="99"/>
+      <c r="AA299" s="100"/>
+      <c r="AB299" s="100"/>
     </row>
     <row r="300" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
@@ -25845,9 +25845,9 @@
       <c r="Y300" s="50">
         <v>1</v>
       </c>
-      <c r="Z300" s="111"/>
-      <c r="AA300" s="112"/>
-      <c r="AB300" s="112"/>
+      <c r="Z300" s="99"/>
+      <c r="AA300" s="100"/>
+      <c r="AB300" s="100"/>
     </row>
     <row r="301" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
@@ -25926,9 +25926,9 @@
       <c r="Y301" s="50">
         <v>1</v>
       </c>
-      <c r="Z301" s="111"/>
-      <c r="AA301" s="112"/>
-      <c r="AB301" s="112"/>
+      <c r="Z301" s="99"/>
+      <c r="AA301" s="100"/>
+      <c r="AB301" s="100"/>
     </row>
     <row r="302" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
@@ -26007,9 +26007,9 @@
       <c r="Y302" s="50">
         <v>1</v>
       </c>
-      <c r="Z302" s="111"/>
-      <c r="AA302" s="112"/>
-      <c r="AB302" s="112"/>
+      <c r="Z302" s="99"/>
+      <c r="AA302" s="100"/>
+      <c r="AB302" s="100"/>
     </row>
     <row r="303" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
@@ -26088,9 +26088,9 @@
       <c r="Y303" s="50">
         <v>1</v>
       </c>
-      <c r="Z303" s="111"/>
-      <c r="AA303" s="112"/>
-      <c r="AB303" s="112"/>
+      <c r="Z303" s="99"/>
+      <c r="AA303" s="100"/>
+      <c r="AB303" s="100"/>
     </row>
     <row r="304" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
@@ -26169,9 +26169,9 @@
       <c r="Y304" s="50">
         <v>1</v>
       </c>
-      <c r="Z304" s="111"/>
-      <c r="AA304" s="112"/>
-      <c r="AB304" s="112"/>
+      <c r="Z304" s="99"/>
+      <c r="AA304" s="100"/>
+      <c r="AB304" s="100"/>
     </row>
     <row r="305" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
@@ -26250,9 +26250,9 @@
       <c r="Y305" s="50">
         <v>1</v>
       </c>
-      <c r="Z305" s="111"/>
-      <c r="AA305" s="112"/>
-      <c r="AB305" s="112"/>
+      <c r="Z305" s="99"/>
+      <c r="AA305" s="100"/>
+      <c r="AB305" s="100"/>
     </row>
     <row r="306" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
@@ -26331,9 +26331,9 @@
       <c r="Y306" s="50">
         <v>1</v>
       </c>
-      <c r="Z306" s="111"/>
-      <c r="AA306" s="112"/>
-      <c r="AB306" s="112"/>
+      <c r="Z306" s="99"/>
+      <c r="AA306" s="100"/>
+      <c r="AB306" s="100"/>
     </row>
     <row r="307" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
@@ -26412,9 +26412,9 @@
       <c r="Y307" s="50">
         <v>1</v>
       </c>
-      <c r="Z307" s="111"/>
-      <c r="AA307" s="112"/>
-      <c r="AB307" s="112"/>
+      <c r="Z307" s="99"/>
+      <c r="AA307" s="100"/>
+      <c r="AB307" s="100"/>
     </row>
     <row r="308" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
@@ -26493,9 +26493,9 @@
       <c r="Y308" s="50">
         <v>1</v>
       </c>
-      <c r="Z308" s="111"/>
-      <c r="AA308" s="112"/>
-      <c r="AB308" s="112"/>
+      <c r="Z308" s="99"/>
+      <c r="AA308" s="100"/>
+      <c r="AB308" s="100"/>
     </row>
     <row r="309" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
@@ -26574,9 +26574,9 @@
       <c r="Y309" s="50">
         <v>1</v>
       </c>
-      <c r="Z309" s="111"/>
-      <c r="AA309" s="112"/>
-      <c r="AB309" s="112"/>
+      <c r="Z309" s="99"/>
+      <c r="AA309" s="100"/>
+      <c r="AB309" s="100"/>
     </row>
     <row r="310" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
@@ -26655,9 +26655,9 @@
       <c r="Y310" s="50">
         <v>1</v>
       </c>
-      <c r="Z310" s="111"/>
-      <c r="AA310" s="112"/>
-      <c r="AB310" s="112"/>
+      <c r="Z310" s="99"/>
+      <c r="AA310" s="100"/>
+      <c r="AB310" s="100"/>
     </row>
     <row r="311" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
@@ -26736,9 +26736,9 @@
       <c r="Y311" s="50">
         <v>1</v>
       </c>
-      <c r="Z311" s="111"/>
-      <c r="AA311" s="112"/>
-      <c r="AB311" s="112"/>
+      <c r="Z311" s="99"/>
+      <c r="AA311" s="100"/>
+      <c r="AB311" s="100"/>
     </row>
     <row r="312" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
@@ -26817,9 +26817,9 @@
       <c r="Y312" s="50">
         <v>1</v>
       </c>
-      <c r="Z312" s="111"/>
-      <c r="AA312" s="112"/>
-      <c r="AB312" s="112"/>
+      <c r="Z312" s="99"/>
+      <c r="AA312" s="100"/>
+      <c r="AB312" s="100"/>
     </row>
     <row r="313" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A313" s="95">
@@ -26976,11 +26976,11 @@
       <c r="Y314" s="53">
         <v>1</v>
       </c>
-      <c r="Z314" s="105" t="s">
+      <c r="Z314" s="101" t="s">
         <v>107</v>
       </c>
-      <c r="AA314" s="106"/>
-      <c r="AB314" s="106"/>
+      <c r="AA314" s="102"/>
+      <c r="AB314" s="102"/>
     </row>
     <row r="315" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
@@ -29904,7 +29904,7 @@
         <v>102000000000000</v>
       </c>
       <c r="V350" s="79">
-        <f t="shared" ref="V350:V352" si="43">$V$240</f>
+        <f t="shared" ref="V350:V354" si="43">$V$240</f>
         <v>125520</v>
       </c>
       <c r="W350" s="45">
@@ -30084,75 +30084,86 @@
       <c r="AA352" s="97"/>
       <c r="AB352" s="97"/>
     </row>
+    <row r="354" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A354" s="1">
+        <v>451</v>
+      </c>
+      <c r="B354" s="15">
+        <v>12</v>
+      </c>
+      <c r="C354" s="15">
+        <v>500</v>
+      </c>
+      <c r="D354" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E354" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F354" s="50">
+        <v>5</v>
+      </c>
+      <c r="G354" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H354" s="51">
+        <v>100</v>
+      </c>
+      <c r="I354" s="15">
+        <v>1</v>
+      </c>
+      <c r="J354" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K354" s="15">
+        <v>2</v>
+      </c>
+      <c r="L354" s="50">
+        <v>2</v>
+      </c>
+      <c r="M354" s="51">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="N354" s="15">
+        <v>300</v>
+      </c>
+      <c r="O354" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P354" s="15">
+        <v>295</v>
+      </c>
+      <c r="Q354" s="50">
+        <v>1600</v>
+      </c>
+      <c r="R354" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S354" s="15">
+        <v>1</v>
+      </c>
+      <c r="T354" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U354" s="19">
+        <v>510000000000</v>
+      </c>
+      <c r="V354" s="78">
+        <f t="shared" si="43"/>
+        <v>125520</v>
+      </c>
+      <c r="W354" s="15">
+        <v>0</v>
+      </c>
+      <c r="X354" s="15">
+        <v>0.25</v>
+      </c>
+      <c r="Y354" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="83">
-    <mergeCell ref="Z326:AB343"/>
-    <mergeCell ref="Z344:AB346"/>
-    <mergeCell ref="Z252:AB262"/>
-    <mergeCell ref="Z263:AB264"/>
-    <mergeCell ref="Z315:AB317"/>
-    <mergeCell ref="Z318:AB325"/>
-    <mergeCell ref="Z295:AB295"/>
-    <mergeCell ref="Z276:AB287"/>
-    <mergeCell ref="Z288:AB289"/>
-    <mergeCell ref="Z290:AB292"/>
-    <mergeCell ref="Z265:AB275"/>
-    <mergeCell ref="Z296:AB312"/>
-    <mergeCell ref="Z314:AB314"/>
-    <mergeCell ref="Z293:AB293"/>
-    <mergeCell ref="Z164:AB164"/>
-    <mergeCell ref="Z153:AB157"/>
-    <mergeCell ref="Z50:AB50"/>
-    <mergeCell ref="Z89:AB89"/>
-    <mergeCell ref="Z88:AB88"/>
-    <mergeCell ref="Z86:AB87"/>
-    <mergeCell ref="Z58:AB58"/>
-    <mergeCell ref="Z51:AB57"/>
-    <mergeCell ref="Z85:AB85"/>
-    <mergeCell ref="Z67:AB84"/>
-    <mergeCell ref="Z59:AB66"/>
-    <mergeCell ref="Z90:AB90"/>
-    <mergeCell ref="Z91:AB91"/>
-    <mergeCell ref="U1:Y1"/>
-    <mergeCell ref="Z6:AB6"/>
-    <mergeCell ref="Z7:AB7"/>
-    <mergeCell ref="Z5:AB5"/>
-    <mergeCell ref="Z4:AB4"/>
-    <mergeCell ref="Z8:AD8"/>
-    <mergeCell ref="Z28:AB28"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="Z10:AB27"/>
-    <mergeCell ref="Z29:AB46"/>
-    <mergeCell ref="Z48:AB48"/>
-    <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="Z49:AB49"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="Z148:AB152"/>
-    <mergeCell ref="Z130:AB147"/>
-    <mergeCell ref="Z112:AB129"/>
-    <mergeCell ref="Z92:AB93"/>
-    <mergeCell ref="Z94:AB94"/>
-    <mergeCell ref="Z95:AB111"/>
-    <mergeCell ref="Z158:AB162"/>
-    <mergeCell ref="Z206:AB220"/>
-    <mergeCell ref="Z221:AB222"/>
-    <mergeCell ref="Z223:AB224"/>
-    <mergeCell ref="Z163:AB163"/>
-    <mergeCell ref="Z165:AB165"/>
-    <mergeCell ref="Z166:AB166"/>
-    <mergeCell ref="Z169:AB175"/>
-    <mergeCell ref="Z197:AB197"/>
-    <mergeCell ref="Z198:AB198"/>
-    <mergeCell ref="Z168:AB168"/>
-    <mergeCell ref="Z202:AB202"/>
-    <mergeCell ref="Z203:AB203"/>
-    <mergeCell ref="Z204:AB204"/>
-    <mergeCell ref="Z205:AB205"/>
-    <mergeCell ref="Z176:AB193"/>
     <mergeCell ref="Z350:AB352"/>
     <mergeCell ref="Z167:AB167"/>
     <mergeCell ref="Z240:AB251"/>
@@ -30169,6 +30180,73 @@
     <mergeCell ref="Z294:AB294"/>
     <mergeCell ref="Z347:AB347"/>
     <mergeCell ref="Z348:AB348"/>
+    <mergeCell ref="Z221:AB222"/>
+    <mergeCell ref="Z223:AB224"/>
+    <mergeCell ref="Z163:AB163"/>
+    <mergeCell ref="Z165:AB165"/>
+    <mergeCell ref="Z166:AB166"/>
+    <mergeCell ref="Z169:AB175"/>
+    <mergeCell ref="Z197:AB197"/>
+    <mergeCell ref="Z198:AB198"/>
+    <mergeCell ref="Z168:AB168"/>
+    <mergeCell ref="Z202:AB202"/>
+    <mergeCell ref="Z203:AB203"/>
+    <mergeCell ref="Z204:AB204"/>
+    <mergeCell ref="Z205:AB205"/>
+    <mergeCell ref="Z176:AB193"/>
+    <mergeCell ref="Z92:AB93"/>
+    <mergeCell ref="Z94:AB94"/>
+    <mergeCell ref="Z95:AB111"/>
+    <mergeCell ref="Z158:AB162"/>
+    <mergeCell ref="Z206:AB220"/>
+    <mergeCell ref="Z48:AB48"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="Z49:AB49"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="Z8:AD8"/>
+    <mergeCell ref="Z28:AB28"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="Z10:AB27"/>
+    <mergeCell ref="Z29:AB46"/>
+    <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="Z6:AB6"/>
+    <mergeCell ref="Z7:AB7"/>
+    <mergeCell ref="Z5:AB5"/>
+    <mergeCell ref="Z4:AB4"/>
+    <mergeCell ref="Z164:AB164"/>
+    <mergeCell ref="Z153:AB157"/>
+    <mergeCell ref="Z50:AB50"/>
+    <mergeCell ref="Z89:AB89"/>
+    <mergeCell ref="Z88:AB88"/>
+    <mergeCell ref="Z86:AB87"/>
+    <mergeCell ref="Z58:AB58"/>
+    <mergeCell ref="Z51:AB57"/>
+    <mergeCell ref="Z85:AB85"/>
+    <mergeCell ref="Z67:AB84"/>
+    <mergeCell ref="Z59:AB66"/>
+    <mergeCell ref="Z90:AB90"/>
+    <mergeCell ref="Z91:AB91"/>
+    <mergeCell ref="Z148:AB152"/>
+    <mergeCell ref="Z130:AB147"/>
+    <mergeCell ref="Z112:AB129"/>
+    <mergeCell ref="Z326:AB343"/>
+    <mergeCell ref="Z344:AB346"/>
+    <mergeCell ref="Z252:AB262"/>
+    <mergeCell ref="Z263:AB264"/>
+    <mergeCell ref="Z315:AB317"/>
+    <mergeCell ref="Z318:AB325"/>
+    <mergeCell ref="Z295:AB295"/>
+    <mergeCell ref="Z276:AB287"/>
+    <mergeCell ref="Z288:AB289"/>
+    <mergeCell ref="Z290:AB292"/>
+    <mergeCell ref="Z265:AB275"/>
+    <mergeCell ref="Z296:AB312"/>
+    <mergeCell ref="Z314:AB314"/>
+    <mergeCell ref="Z293:AB293"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Simulations_IDS.xlsx
+++ b/Simulations_IDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documentos_Betran\DropletEvaporation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0A27AB-114D-4E65-B5DF-5BACE378071E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F38B886-D0D0-4400-8BC1-205192D673D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{73239687-5BB6-4FA0-A3B4-8BE280184789}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="113">
   <si>
     <t>ID</t>
   </si>
@@ -682,7 +682,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -794,16 +794,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -812,8 +812,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -824,18 +827,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1155,7 +1156,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC78505-487D-4D76-94E1-903AFBAADA28}">
-  <dimension ref="A1:AF354"/>
+  <dimension ref="A1:AF355"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" customWidth="1"/>
@@ -1185,42 +1186,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="B1" s="109" t="s">
+      <c r="B1" s="105" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="110" t="s">
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="106" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="107"/>
-      <c r="M1" s="110" t="s">
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="107" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="108"/>
+      <c r="M1" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="110" t="s">
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="106"/>
-      <c r="T1" s="106"/>
-      <c r="U1" s="106" t="s">
+      <c r="S1" s="107"/>
+      <c r="T1" s="107"/>
+      <c r="U1" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="V1" s="106"/>
-      <c r="W1" s="106"/>
-      <c r="X1" s="106"/>
-      <c r="Y1" s="107"/>
+      <c r="V1" s="107"/>
+      <c r="W1" s="107"/>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="108"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1452,8 +1453,8 @@
       <c r="Z4" s="103" t="s">
         <v>46</v>
       </c>
-      <c r="AA4" s="108"/>
-      <c r="AB4" s="108"/>
+      <c r="AA4" s="109"/>
+      <c r="AB4" s="109"/>
       <c r="AC4" s="65"/>
       <c r="AD4" s="65"/>
     </row>
@@ -1537,8 +1538,8 @@
       <c r="Z5" s="103" t="s">
         <v>47</v>
       </c>
-      <c r="AA5" s="108"/>
-      <c r="AB5" s="108"/>
+      <c r="AA5" s="109"/>
+      <c r="AB5" s="109"/>
       <c r="AC5" s="65"/>
       <c r="AD5" s="65"/>
     </row>
@@ -1622,8 +1623,8 @@
       <c r="Z6" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="108"/>
-      <c r="AB6" s="108"/>
+      <c r="AA6" s="109"/>
+      <c r="AB6" s="109"/>
       <c r="AC6" s="65"/>
       <c r="AD6" s="65"/>
     </row>
@@ -1707,8 +1708,8 @@
       <c r="Z7" s="103" t="s">
         <v>49</v>
       </c>
-      <c r="AA7" s="108"/>
-      <c r="AB7" s="108"/>
+      <c r="AA7" s="109"/>
+      <c r="AB7" s="109"/>
       <c r="AC7" s="65"/>
       <c r="AD7" s="65"/>
     </row>
@@ -5163,8 +5164,8 @@
       <c r="Z48" s="101" t="s">
         <v>55</v>
       </c>
-      <c r="AA48" s="105"/>
-      <c r="AB48" s="105"/>
+      <c r="AA48" s="102"/>
+      <c r="AB48" s="102"/>
       <c r="AC48" s="67"/>
       <c r="AD48" s="65"/>
     </row>
@@ -6007,8 +6008,8 @@
       <c r="Z58" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="AA58" s="105"/>
-      <c r="AB58" s="105"/>
+      <c r="AA58" s="102"/>
+      <c r="AB58" s="102"/>
       <c r="AC58" s="65"/>
       <c r="AD58" s="65"/>
     </row>
@@ -8272,8 +8273,8 @@
       <c r="Z85" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="AA85" s="102"/>
-      <c r="AB85" s="102"/>
+      <c r="AA85" s="110"/>
+      <c r="AB85" s="110"/>
       <c r="AC85" s="65"/>
       <c r="AD85" s="65"/>
     </row>
@@ -8525,8 +8526,8 @@
       <c r="Z88" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="AA88" s="102"/>
-      <c r="AB88" s="102"/>
+      <c r="AA88" s="110"/>
+      <c r="AB88" s="110"/>
       <c r="AC88" s="65"/>
       <c r="AD88" s="65"/>
     </row>
@@ -8610,8 +8611,8 @@
       <c r="Z89" s="101" t="s">
         <v>63</v>
       </c>
-      <c r="AA89" s="102"/>
-      <c r="AB89" s="102"/>
+      <c r="AA89" s="110"/>
+      <c r="AB89" s="110"/>
       <c r="AC89" s="65"/>
       <c r="AD89" s="65"/>
     </row>
@@ -8695,8 +8696,8 @@
       <c r="Z90" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="AA90" s="102"/>
-      <c r="AB90" s="102"/>
+      <c r="AA90" s="110"/>
+      <c r="AB90" s="110"/>
       <c r="AC90" s="65"/>
       <c r="AD90" s="65"/>
     </row>
@@ -8780,8 +8781,8 @@
       <c r="Z91" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="AA91" s="102"/>
-      <c r="AB91" s="102"/>
+      <c r="AA91" s="110"/>
+      <c r="AB91" s="110"/>
       <c r="AC91" s="65"/>
       <c r="AD91" s="65"/>
     </row>
@@ -9113,11 +9114,11 @@
       <c r="Y95" s="1">
         <v>1</v>
       </c>
-      <c r="Z95" s="111" t="s">
+      <c r="Z95" s="99" t="s">
         <v>69</v>
       </c>
-      <c r="AA95" s="112"/>
-      <c r="AB95" s="112"/>
+      <c r="AA95" s="100"/>
+      <c r="AB95" s="100"/>
     </row>
     <row r="96" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
@@ -9197,9 +9198,9 @@
       <c r="Y96" s="1">
         <v>1</v>
       </c>
-      <c r="Z96" s="111"/>
-      <c r="AA96" s="112"/>
-      <c r="AB96" s="112"/>
+      <c r="Z96" s="99"/>
+      <c r="AA96" s="100"/>
+      <c r="AB96" s="100"/>
     </row>
     <row r="97" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
@@ -9279,9 +9280,9 @@
       <c r="Y97" s="1">
         <v>1</v>
       </c>
-      <c r="Z97" s="111"/>
-      <c r="AA97" s="112"/>
-      <c r="AB97" s="112"/>
+      <c r="Z97" s="99"/>
+      <c r="AA97" s="100"/>
+      <c r="AB97" s="100"/>
     </row>
     <row r="98" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
@@ -9361,9 +9362,9 @@
       <c r="Y98" s="1">
         <v>1</v>
       </c>
-      <c r="Z98" s="111"/>
-      <c r="AA98" s="112"/>
-      <c r="AB98" s="112"/>
+      <c r="Z98" s="99"/>
+      <c r="AA98" s="100"/>
+      <c r="AB98" s="100"/>
     </row>
     <row r="99" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
@@ -9443,9 +9444,9 @@
       <c r="Y99" s="1">
         <v>1</v>
       </c>
-      <c r="Z99" s="111"/>
-      <c r="AA99" s="112"/>
-      <c r="AB99" s="112"/>
+      <c r="Z99" s="99"/>
+      <c r="AA99" s="100"/>
+      <c r="AB99" s="100"/>
     </row>
     <row r="100" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
@@ -9525,9 +9526,9 @@
       <c r="Y100" s="1">
         <v>1</v>
       </c>
-      <c r="Z100" s="111"/>
-      <c r="AA100" s="112"/>
-      <c r="AB100" s="112"/>
+      <c r="Z100" s="99"/>
+      <c r="AA100" s="100"/>
+      <c r="AB100" s="100"/>
     </row>
     <row r="101" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
@@ -9607,9 +9608,9 @@
       <c r="Y101" s="1">
         <v>1</v>
       </c>
-      <c r="Z101" s="111"/>
-      <c r="AA101" s="112"/>
-      <c r="AB101" s="112"/>
+      <c r="Z101" s="99"/>
+      <c r="AA101" s="100"/>
+      <c r="AB101" s="100"/>
     </row>
     <row r="102" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
@@ -9689,9 +9690,9 @@
       <c r="Y102" s="1">
         <v>1</v>
       </c>
-      <c r="Z102" s="111"/>
-      <c r="AA102" s="112"/>
-      <c r="AB102" s="112"/>
+      <c r="Z102" s="99"/>
+      <c r="AA102" s="100"/>
+      <c r="AB102" s="100"/>
     </row>
     <row r="103" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
@@ -9771,9 +9772,9 @@
       <c r="Y103" s="1">
         <v>1</v>
       </c>
-      <c r="Z103" s="111"/>
-      <c r="AA103" s="112"/>
-      <c r="AB103" s="112"/>
+      <c r="Z103" s="99"/>
+      <c r="AA103" s="100"/>
+      <c r="AB103" s="100"/>
     </row>
     <row r="104" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
@@ -9853,9 +9854,9 @@
       <c r="Y104" s="1">
         <v>1</v>
       </c>
-      <c r="Z104" s="111"/>
-      <c r="AA104" s="112"/>
-      <c r="AB104" s="112"/>
+      <c r="Z104" s="99"/>
+      <c r="AA104" s="100"/>
+      <c r="AB104" s="100"/>
     </row>
     <row r="105" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
@@ -9935,9 +9936,9 @@
       <c r="Y105" s="1">
         <v>1</v>
       </c>
-      <c r="Z105" s="111"/>
-      <c r="AA105" s="112"/>
-      <c r="AB105" s="112"/>
+      <c r="Z105" s="99"/>
+      <c r="AA105" s="100"/>
+      <c r="AB105" s="100"/>
     </row>
     <row r="106" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
@@ -10017,9 +10018,9 @@
       <c r="Y106" s="1">
         <v>1</v>
       </c>
-      <c r="Z106" s="111"/>
-      <c r="AA106" s="112"/>
-      <c r="AB106" s="112"/>
+      <c r="Z106" s="99"/>
+      <c r="AA106" s="100"/>
+      <c r="AB106" s="100"/>
     </row>
     <row r="107" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
@@ -10098,9 +10099,9 @@
       <c r="Y107" s="1">
         <v>1</v>
       </c>
-      <c r="Z107" s="111"/>
-      <c r="AA107" s="112"/>
-      <c r="AB107" s="112"/>
+      <c r="Z107" s="99"/>
+      <c r="AA107" s="100"/>
+      <c r="AB107" s="100"/>
     </row>
     <row r="108" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
@@ -10179,9 +10180,9 @@
       <c r="Y108" s="1">
         <v>1</v>
       </c>
-      <c r="Z108" s="111"/>
-      <c r="AA108" s="112"/>
-      <c r="AB108" s="112"/>
+      <c r="Z108" s="99"/>
+      <c r="AA108" s="100"/>
+      <c r="AB108" s="100"/>
     </row>
     <row r="109" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
@@ -10260,9 +10261,9 @@
       <c r="Y109" s="1">
         <v>1</v>
       </c>
-      <c r="Z109" s="111"/>
-      <c r="AA109" s="112"/>
-      <c r="AB109" s="112"/>
+      <c r="Z109" s="99"/>
+      <c r="AA109" s="100"/>
+      <c r="AB109" s="100"/>
     </row>
     <row r="110" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
@@ -10341,9 +10342,9 @@
       <c r="Y110" s="1">
         <v>1</v>
       </c>
-      <c r="Z110" s="111"/>
-      <c r="AA110" s="112"/>
-      <c r="AB110" s="112"/>
+      <c r="Z110" s="99"/>
+      <c r="AA110" s="100"/>
+      <c r="AB110" s="100"/>
     </row>
     <row r="111" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
@@ -10422,9 +10423,9 @@
       <c r="Y111" s="1">
         <v>1</v>
       </c>
-      <c r="Z111" s="111"/>
-      <c r="AA111" s="112"/>
-      <c r="AB111" s="112"/>
+      <c r="Z111" s="99"/>
+      <c r="AA111" s="100"/>
+      <c r="AB111" s="100"/>
     </row>
     <row r="112" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A112" s="43">
@@ -15172,11 +15173,11 @@
       <c r="Y169" s="40">
         <v>1</v>
       </c>
-      <c r="Z169" s="111" t="s">
+      <c r="Z169" s="99" t="s">
         <v>82</v>
       </c>
-      <c r="AA169" s="112"/>
-      <c r="AB169" s="112"/>
+      <c r="AA169" s="100"/>
+      <c r="AB169" s="100"/>
     </row>
     <row r="170" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
@@ -15255,9 +15256,9 @@
       <c r="Y170" s="50">
         <v>1</v>
       </c>
-      <c r="Z170" s="111"/>
-      <c r="AA170" s="112"/>
-      <c r="AB170" s="112"/>
+      <c r="Z170" s="99"/>
+      <c r="AA170" s="100"/>
+      <c r="AB170" s="100"/>
     </row>
     <row r="171" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
@@ -15336,9 +15337,9 @@
       <c r="Y171" s="50">
         <v>1</v>
       </c>
-      <c r="Z171" s="111"/>
-      <c r="AA171" s="112"/>
-      <c r="AB171" s="112"/>
+      <c r="Z171" s="99"/>
+      <c r="AA171" s="100"/>
+      <c r="AB171" s="100"/>
     </row>
     <row r="172" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
@@ -15417,9 +15418,9 @@
       <c r="Y172" s="50">
         <v>1</v>
       </c>
-      <c r="Z172" s="111"/>
-      <c r="AA172" s="112"/>
-      <c r="AB172" s="112"/>
+      <c r="Z172" s="99"/>
+      <c r="AA172" s="100"/>
+      <c r="AB172" s="100"/>
     </row>
     <row r="173" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
@@ -15498,9 +15499,9 @@
       <c r="Y173" s="50">
         <v>1</v>
       </c>
-      <c r="Z173" s="111"/>
-      <c r="AA173" s="112"/>
-      <c r="AB173" s="112"/>
+      <c r="Z173" s="99"/>
+      <c r="AA173" s="100"/>
+      <c r="AB173" s="100"/>
     </row>
     <row r="174" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
@@ -15579,9 +15580,9 @@
       <c r="Y174" s="50">
         <v>1</v>
       </c>
-      <c r="Z174" s="111"/>
-      <c r="AA174" s="112"/>
-      <c r="AB174" s="112"/>
+      <c r="Z174" s="99"/>
+      <c r="AA174" s="100"/>
+      <c r="AB174" s="100"/>
     </row>
     <row r="175" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
@@ -15660,9 +15661,9 @@
       <c r="Y175" s="50">
         <v>1</v>
       </c>
-      <c r="Z175" s="111"/>
-      <c r="AA175" s="112"/>
-      <c r="AB175" s="112"/>
+      <c r="Z175" s="99"/>
+      <c r="AA175" s="100"/>
+      <c r="AB175" s="100"/>
     </row>
     <row r="176" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A176" s="43">
@@ -25519,11 +25520,11 @@
       <c r="Y296" s="40">
         <v>1</v>
       </c>
-      <c r="Z296" s="99" t="s">
+      <c r="Z296" s="111" t="s">
         <v>106</v>
       </c>
-      <c r="AA296" s="100"/>
-      <c r="AB296" s="100"/>
+      <c r="AA296" s="112"/>
+      <c r="AB296" s="112"/>
     </row>
     <row r="297" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
@@ -25602,9 +25603,9 @@
       <c r="Y297" s="50">
         <v>1</v>
       </c>
-      <c r="Z297" s="99"/>
-      <c r="AA297" s="100"/>
-      <c r="AB297" s="100"/>
+      <c r="Z297" s="111"/>
+      <c r="AA297" s="112"/>
+      <c r="AB297" s="112"/>
     </row>
     <row r="298" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
@@ -25683,9 +25684,9 @@
       <c r="Y298" s="50">
         <v>1</v>
       </c>
-      <c r="Z298" s="99"/>
-      <c r="AA298" s="100"/>
-      <c r="AB298" s="100"/>
+      <c r="Z298" s="111"/>
+      <c r="AA298" s="112"/>
+      <c r="AB298" s="112"/>
     </row>
     <row r="299" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
@@ -25764,9 +25765,9 @@
       <c r="Y299" s="50">
         <v>1</v>
       </c>
-      <c r="Z299" s="99"/>
-      <c r="AA299" s="100"/>
-      <c r="AB299" s="100"/>
+      <c r="Z299" s="111"/>
+      <c r="AA299" s="112"/>
+      <c r="AB299" s="112"/>
     </row>
     <row r="300" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
@@ -25845,9 +25846,9 @@
       <c r="Y300" s="50">
         <v>1</v>
       </c>
-      <c r="Z300" s="99"/>
-      <c r="AA300" s="100"/>
-      <c r="AB300" s="100"/>
+      <c r="Z300" s="111"/>
+      <c r="AA300" s="112"/>
+      <c r="AB300" s="112"/>
     </row>
     <row r="301" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
@@ -25926,9 +25927,9 @@
       <c r="Y301" s="50">
         <v>1</v>
       </c>
-      <c r="Z301" s="99"/>
-      <c r="AA301" s="100"/>
-      <c r="AB301" s="100"/>
+      <c r="Z301" s="111"/>
+      <c r="AA301" s="112"/>
+      <c r="AB301" s="112"/>
     </row>
     <row r="302" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
@@ -26007,9 +26008,9 @@
       <c r="Y302" s="50">
         <v>1</v>
       </c>
-      <c r="Z302" s="99"/>
-      <c r="AA302" s="100"/>
-      <c r="AB302" s="100"/>
+      <c r="Z302" s="111"/>
+      <c r="AA302" s="112"/>
+      <c r="AB302" s="112"/>
     </row>
     <row r="303" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
@@ -26088,9 +26089,9 @@
       <c r="Y303" s="50">
         <v>1</v>
       </c>
-      <c r="Z303" s="99"/>
-      <c r="AA303" s="100"/>
-      <c r="AB303" s="100"/>
+      <c r="Z303" s="111"/>
+      <c r="AA303" s="112"/>
+      <c r="AB303" s="112"/>
     </row>
     <row r="304" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
@@ -26169,9 +26170,9 @@
       <c r="Y304" s="50">
         <v>1</v>
       </c>
-      <c r="Z304" s="99"/>
-      <c r="AA304" s="100"/>
-      <c r="AB304" s="100"/>
+      <c r="Z304" s="111"/>
+      <c r="AA304" s="112"/>
+      <c r="AB304" s="112"/>
     </row>
     <row r="305" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
@@ -26250,9 +26251,9 @@
       <c r="Y305" s="50">
         <v>1</v>
       </c>
-      <c r="Z305" s="99"/>
-      <c r="AA305" s="100"/>
-      <c r="AB305" s="100"/>
+      <c r="Z305" s="111"/>
+      <c r="AA305" s="112"/>
+      <c r="AB305" s="112"/>
     </row>
     <row r="306" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
@@ -26331,9 +26332,9 @@
       <c r="Y306" s="50">
         <v>1</v>
       </c>
-      <c r="Z306" s="99"/>
-      <c r="AA306" s="100"/>
-      <c r="AB306" s="100"/>
+      <c r="Z306" s="111"/>
+      <c r="AA306" s="112"/>
+      <c r="AB306" s="112"/>
     </row>
     <row r="307" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
@@ -26412,9 +26413,9 @@
       <c r="Y307" s="50">
         <v>1</v>
       </c>
-      <c r="Z307" s="99"/>
-      <c r="AA307" s="100"/>
-      <c r="AB307" s="100"/>
+      <c r="Z307" s="111"/>
+      <c r="AA307" s="112"/>
+      <c r="AB307" s="112"/>
     </row>
     <row r="308" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
@@ -26493,9 +26494,9 @@
       <c r="Y308" s="50">
         <v>1</v>
       </c>
-      <c r="Z308" s="99"/>
-      <c r="AA308" s="100"/>
-      <c r="AB308" s="100"/>
+      <c r="Z308" s="111"/>
+      <c r="AA308" s="112"/>
+      <c r="AB308" s="112"/>
     </row>
     <row r="309" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
@@ -26574,9 +26575,9 @@
       <c r="Y309" s="50">
         <v>1</v>
       </c>
-      <c r="Z309" s="99"/>
-      <c r="AA309" s="100"/>
-      <c r="AB309" s="100"/>
+      <c r="Z309" s="111"/>
+      <c r="AA309" s="112"/>
+      <c r="AB309" s="112"/>
     </row>
     <row r="310" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
@@ -26655,9 +26656,9 @@
       <c r="Y310" s="50">
         <v>1</v>
       </c>
-      <c r="Z310" s="99"/>
-      <c r="AA310" s="100"/>
-      <c r="AB310" s="100"/>
+      <c r="Z310" s="111"/>
+      <c r="AA310" s="112"/>
+      <c r="AB310" s="112"/>
     </row>
     <row r="311" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
@@ -26736,9 +26737,9 @@
       <c r="Y311" s="50">
         <v>1</v>
       </c>
-      <c r="Z311" s="99"/>
-      <c r="AA311" s="100"/>
-      <c r="AB311" s="100"/>
+      <c r="Z311" s="111"/>
+      <c r="AA311" s="112"/>
+      <c r="AB311" s="112"/>
     </row>
     <row r="312" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
@@ -26817,9 +26818,9 @@
       <c r="Y312" s="50">
         <v>1</v>
       </c>
-      <c r="Z312" s="99"/>
-      <c r="AA312" s="100"/>
-      <c r="AB312" s="100"/>
+      <c r="Z312" s="111"/>
+      <c r="AA312" s="112"/>
+      <c r="AB312" s="112"/>
     </row>
     <row r="313" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A313" s="95">
@@ -26979,8 +26980,8 @@
       <c r="Z314" s="101" t="s">
         <v>107</v>
       </c>
-      <c r="AA314" s="102"/>
-      <c r="AB314" s="102"/>
+      <c r="AA314" s="110"/>
+      <c r="AB314" s="110"/>
     </row>
     <row r="315" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
@@ -30084,6 +30085,84 @@
       <c r="AA352" s="97"/>
       <c r="AB352" s="97"/>
     </row>
+    <row r="353" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A353" s="1">
+        <v>450</v>
+      </c>
+      <c r="B353" s="15">
+        <v>12</v>
+      </c>
+      <c r="C353" s="15">
+        <v>500</v>
+      </c>
+      <c r="D353" s="51">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E353" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F353" s="50">
+        <v>5</v>
+      </c>
+      <c r="G353" s="51">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H353" s="51">
+        <v>100</v>
+      </c>
+      <c r="I353" s="15">
+        <v>1</v>
+      </c>
+      <c r="J353" s="52">
+        <v>1E-4</v>
+      </c>
+      <c r="K353" s="15">
+        <v>2</v>
+      </c>
+      <c r="L353" s="50">
+        <v>2</v>
+      </c>
+      <c r="M353" s="51">
+        <v>2.5000000000000001E-5</v>
+      </c>
+      <c r="N353" s="15">
+        <v>300</v>
+      </c>
+      <c r="O353" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="P353" s="15">
+        <v>295</v>
+      </c>
+      <c r="Q353" s="50">
+        <v>1600</v>
+      </c>
+      <c r="R353" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="S353" s="15">
+        <v>1</v>
+      </c>
+      <c r="T353" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="U353" s="19">
+        <v>510000000000</v>
+      </c>
+      <c r="V353" s="78">
+        <f t="shared" si="43"/>
+        <v>125520</v>
+      </c>
+      <c r="W353" s="15">
+        <v>0</v>
+      </c>
+      <c r="X353" s="15">
+        <v>0.25</v>
+      </c>
+      <c r="Y353" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
     <row r="354" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
         <v>451</v>
@@ -30162,8 +30241,153 @@
         <v>1.5</v>
       </c>
     </row>
+    <row r="355" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A355" s="43">
+        <v>452</v>
+      </c>
+      <c r="B355" s="45">
+        <v>12</v>
+      </c>
+      <c r="C355" s="45">
+        <v>500</v>
+      </c>
+      <c r="D355" s="47">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E355" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F355" s="40">
+        <v>5</v>
+      </c>
+      <c r="G355" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H355" s="47">
+        <v>100</v>
+      </c>
+      <c r="I355" s="45">
+        <v>1</v>
+      </c>
+      <c r="J355" s="48">
+        <v>1E-4</v>
+      </c>
+      <c r="K355" s="45">
+        <v>2</v>
+      </c>
+      <c r="L355" s="40">
+        <v>2</v>
+      </c>
+      <c r="M355" s="47">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="N355" s="45">
+        <v>300</v>
+      </c>
+      <c r="O355" s="45">
+        <v>0.1</v>
+      </c>
+      <c r="P355" s="45">
+        <v>300</v>
+      </c>
+      <c r="Q355" s="40">
+        <v>1200</v>
+      </c>
+      <c r="R355" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="S355" s="45">
+        <v>1</v>
+      </c>
+      <c r="T355" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="U355" s="42">
+        <v>20400000000000</v>
+      </c>
+      <c r="V355" s="113">
+        <f t="shared" ref="V355" si="44">$V$225</f>
+        <v>125520</v>
+      </c>
+      <c r="W355" s="45">
+        <v>0</v>
+      </c>
+      <c r="X355" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y355" s="40">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="83">
+    <mergeCell ref="Z326:AB343"/>
+    <mergeCell ref="Z344:AB346"/>
+    <mergeCell ref="Z252:AB262"/>
+    <mergeCell ref="Z263:AB264"/>
+    <mergeCell ref="Z315:AB317"/>
+    <mergeCell ref="Z318:AB325"/>
+    <mergeCell ref="Z295:AB295"/>
+    <mergeCell ref="Z276:AB287"/>
+    <mergeCell ref="Z288:AB289"/>
+    <mergeCell ref="Z290:AB292"/>
+    <mergeCell ref="Z265:AB275"/>
+    <mergeCell ref="Z296:AB312"/>
+    <mergeCell ref="Z314:AB314"/>
+    <mergeCell ref="Z293:AB293"/>
+    <mergeCell ref="Z5:AB5"/>
+    <mergeCell ref="Z4:AB4"/>
+    <mergeCell ref="Z164:AB164"/>
+    <mergeCell ref="Z153:AB157"/>
+    <mergeCell ref="Z50:AB50"/>
+    <mergeCell ref="Z89:AB89"/>
+    <mergeCell ref="Z88:AB88"/>
+    <mergeCell ref="Z86:AB87"/>
+    <mergeCell ref="Z58:AB58"/>
+    <mergeCell ref="Z51:AB57"/>
+    <mergeCell ref="Z85:AB85"/>
+    <mergeCell ref="Z67:AB84"/>
+    <mergeCell ref="Z59:AB66"/>
+    <mergeCell ref="Z90:AB90"/>
+    <mergeCell ref="Z91:AB91"/>
+    <mergeCell ref="Z148:AB152"/>
+    <mergeCell ref="Z48:AB48"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="Z49:AB49"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="Z8:AD8"/>
+    <mergeCell ref="Z28:AB28"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="Z10:AB27"/>
+    <mergeCell ref="Z29:AB46"/>
+    <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="Z6:AB6"/>
+    <mergeCell ref="Z7:AB7"/>
+    <mergeCell ref="Z92:AB93"/>
+    <mergeCell ref="Z94:AB94"/>
+    <mergeCell ref="Z95:AB111"/>
+    <mergeCell ref="Z158:AB162"/>
+    <mergeCell ref="Z206:AB220"/>
+    <mergeCell ref="Z130:AB147"/>
+    <mergeCell ref="Z112:AB129"/>
+    <mergeCell ref="Z221:AB222"/>
+    <mergeCell ref="Z223:AB224"/>
+    <mergeCell ref="Z163:AB163"/>
+    <mergeCell ref="Z165:AB165"/>
+    <mergeCell ref="Z166:AB166"/>
+    <mergeCell ref="Z169:AB175"/>
+    <mergeCell ref="Z197:AB197"/>
+    <mergeCell ref="Z198:AB198"/>
+    <mergeCell ref="Z168:AB168"/>
+    <mergeCell ref="Z202:AB202"/>
+    <mergeCell ref="Z203:AB203"/>
+    <mergeCell ref="Z204:AB204"/>
+    <mergeCell ref="Z205:AB205"/>
+    <mergeCell ref="Z176:AB193"/>
     <mergeCell ref="Z350:AB352"/>
     <mergeCell ref="Z167:AB167"/>
     <mergeCell ref="Z240:AB251"/>
@@ -30180,73 +30404,6 @@
     <mergeCell ref="Z294:AB294"/>
     <mergeCell ref="Z347:AB347"/>
     <mergeCell ref="Z348:AB348"/>
-    <mergeCell ref="Z221:AB222"/>
-    <mergeCell ref="Z223:AB224"/>
-    <mergeCell ref="Z163:AB163"/>
-    <mergeCell ref="Z165:AB165"/>
-    <mergeCell ref="Z166:AB166"/>
-    <mergeCell ref="Z169:AB175"/>
-    <mergeCell ref="Z197:AB197"/>
-    <mergeCell ref="Z198:AB198"/>
-    <mergeCell ref="Z168:AB168"/>
-    <mergeCell ref="Z202:AB202"/>
-    <mergeCell ref="Z203:AB203"/>
-    <mergeCell ref="Z204:AB204"/>
-    <mergeCell ref="Z205:AB205"/>
-    <mergeCell ref="Z176:AB193"/>
-    <mergeCell ref="Z92:AB93"/>
-    <mergeCell ref="Z94:AB94"/>
-    <mergeCell ref="Z95:AB111"/>
-    <mergeCell ref="Z158:AB162"/>
-    <mergeCell ref="Z206:AB220"/>
-    <mergeCell ref="Z48:AB48"/>
-    <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="Z49:AB49"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="Z8:AD8"/>
-    <mergeCell ref="Z28:AB28"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="Z10:AB27"/>
-    <mergeCell ref="Z29:AB46"/>
-    <mergeCell ref="U1:Y1"/>
-    <mergeCell ref="Z6:AB6"/>
-    <mergeCell ref="Z7:AB7"/>
-    <mergeCell ref="Z5:AB5"/>
-    <mergeCell ref="Z4:AB4"/>
-    <mergeCell ref="Z164:AB164"/>
-    <mergeCell ref="Z153:AB157"/>
-    <mergeCell ref="Z50:AB50"/>
-    <mergeCell ref="Z89:AB89"/>
-    <mergeCell ref="Z88:AB88"/>
-    <mergeCell ref="Z86:AB87"/>
-    <mergeCell ref="Z58:AB58"/>
-    <mergeCell ref="Z51:AB57"/>
-    <mergeCell ref="Z85:AB85"/>
-    <mergeCell ref="Z67:AB84"/>
-    <mergeCell ref="Z59:AB66"/>
-    <mergeCell ref="Z90:AB90"/>
-    <mergeCell ref="Z91:AB91"/>
-    <mergeCell ref="Z148:AB152"/>
-    <mergeCell ref="Z130:AB147"/>
-    <mergeCell ref="Z112:AB129"/>
-    <mergeCell ref="Z326:AB343"/>
-    <mergeCell ref="Z344:AB346"/>
-    <mergeCell ref="Z252:AB262"/>
-    <mergeCell ref="Z263:AB264"/>
-    <mergeCell ref="Z315:AB317"/>
-    <mergeCell ref="Z318:AB325"/>
-    <mergeCell ref="Z295:AB295"/>
-    <mergeCell ref="Z276:AB287"/>
-    <mergeCell ref="Z288:AB289"/>
-    <mergeCell ref="Z290:AB292"/>
-    <mergeCell ref="Z265:AB275"/>
-    <mergeCell ref="Z296:AB312"/>
-    <mergeCell ref="Z314:AB314"/>
-    <mergeCell ref="Z293:AB293"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Simulations_IDS.xlsx
+++ b/Simulations_IDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documentos_Betran\DropletEvaporation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F38B886-D0D0-4400-8BC1-205192D673D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE8DCB3-12D3-40E0-91B6-F0E8E222C533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{73239687-5BB6-4FA0-A3B4-8BE280184789}"/>
   </bookViews>
@@ -397,7 +397,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -461,6 +461,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -682,7 +688,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -785,6 +791,7 @@
     <xf numFmtId="11" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -794,23 +801,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -824,19 +837,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1186,42 +1195,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="B1" s="105" t="s">
+      <c r="B1" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="106" t="s">
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="109" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="107" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="108"/>
-      <c r="M1" s="106" t="s">
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="110" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="111"/>
+      <c r="M1" s="109" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="106" t="s">
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="107"/>
-      <c r="T1" s="107"/>
-      <c r="U1" s="107" t="s">
+      <c r="S1" s="110"/>
+      <c r="T1" s="110"/>
+      <c r="U1" s="110" t="s">
         <v>8</v>
       </c>
-      <c r="V1" s="107"/>
-      <c r="W1" s="107"/>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="108"/>
+      <c r="V1" s="110"/>
+      <c r="W1" s="110"/>
+      <c r="X1" s="110"/>
+      <c r="Y1" s="111"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1450,11 +1459,11 @@
       <c r="Y4" s="1">
         <v>1</v>
       </c>
-      <c r="Z4" s="103" t="s">
+      <c r="Z4" s="104" t="s">
         <v>46</v>
       </c>
-      <c r="AA4" s="109"/>
-      <c r="AB4" s="109"/>
+      <c r="AA4" s="105"/>
+      <c r="AB4" s="105"/>
       <c r="AC4" s="65"/>
       <c r="AD4" s="65"/>
     </row>
@@ -1535,11 +1544,11 @@
       <c r="Y5" s="1">
         <v>1</v>
       </c>
-      <c r="Z5" s="103" t="s">
+      <c r="Z5" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="AA5" s="109"/>
-      <c r="AB5" s="109"/>
+      <c r="AA5" s="105"/>
+      <c r="AB5" s="105"/>
       <c r="AC5" s="65"/>
       <c r="AD5" s="65"/>
     </row>
@@ -1620,11 +1629,11 @@
       <c r="Y6" s="1">
         <v>1</v>
       </c>
-      <c r="Z6" s="103" t="s">
+      <c r="Z6" s="104" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="109"/>
-      <c r="AB6" s="109"/>
+      <c r="AA6" s="105"/>
+      <c r="AB6" s="105"/>
       <c r="AC6" s="65"/>
       <c r="AD6" s="65"/>
     </row>
@@ -1705,11 +1714,11 @@
       <c r="Y7" s="1">
         <v>1</v>
       </c>
-      <c r="Z7" s="103" t="s">
+      <c r="Z7" s="104" t="s">
         <v>49</v>
       </c>
-      <c r="AA7" s="109"/>
-      <c r="AB7" s="109"/>
+      <c r="AA7" s="105"/>
+      <c r="AB7" s="105"/>
       <c r="AC7" s="65"/>
       <c r="AD7" s="65"/>
     </row>
@@ -1790,13 +1799,13 @@
       <c r="Y8" s="38">
         <v>1</v>
       </c>
-      <c r="Z8" s="103" t="s">
+      <c r="Z8" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="AA8" s="104"/>
-      <c r="AB8" s="104"/>
-      <c r="AC8" s="104"/>
-      <c r="AD8" s="104"/>
+      <c r="AA8" s="106"/>
+      <c r="AB8" s="106"/>
+      <c r="AC8" s="106"/>
+      <c r="AD8" s="106"/>
       <c r="AE8" s="20"/>
       <c r="AF8" s="20"/>
     </row>
@@ -1877,11 +1886,11 @@
       <c r="Y9" s="1">
         <v>1</v>
       </c>
-      <c r="Z9" s="103" t="s">
+      <c r="Z9" s="104" t="s">
         <v>50</v>
       </c>
-      <c r="AA9" s="104"/>
-      <c r="AB9" s="104"/>
+      <c r="AA9" s="106"/>
+      <c r="AB9" s="106"/>
       <c r="AC9" s="65"/>
       <c r="AD9" s="65"/>
     </row>
@@ -1962,11 +1971,11 @@
       <c r="Y10" s="43">
         <v>1</v>
       </c>
-      <c r="Z10" s="96" t="s">
+      <c r="Z10" s="97" t="s">
         <v>51</v>
       </c>
-      <c r="AA10" s="97"/>
-      <c r="AB10" s="97"/>
+      <c r="AA10" s="98"/>
+      <c r="AB10" s="98"/>
       <c r="AC10" s="65"/>
       <c r="AD10" s="65"/>
     </row>
@@ -2049,9 +2058,9 @@
       <c r="Y11" s="1">
         <v>1</v>
       </c>
-      <c r="Z11" s="96"/>
-      <c r="AA11" s="97"/>
-      <c r="AB11" s="97"/>
+      <c r="Z11" s="97"/>
+      <c r="AA11" s="98"/>
+      <c r="AB11" s="98"/>
       <c r="AC11" s="65"/>
       <c r="AD11" s="65"/>
     </row>
@@ -2133,9 +2142,9 @@
       <c r="Y12" s="1">
         <v>1</v>
       </c>
-      <c r="Z12" s="96"/>
-      <c r="AA12" s="97"/>
-      <c r="AB12" s="97"/>
+      <c r="Z12" s="97"/>
+      <c r="AA12" s="98"/>
+      <c r="AB12" s="98"/>
       <c r="AC12" s="65"/>
       <c r="AD12" s="65"/>
     </row>
@@ -2217,9 +2226,9 @@
       <c r="Y13" s="1">
         <v>1</v>
       </c>
-      <c r="Z13" s="96"/>
-      <c r="AA13" s="97"/>
-      <c r="AB13" s="97"/>
+      <c r="Z13" s="97"/>
+      <c r="AA13" s="98"/>
+      <c r="AB13" s="98"/>
       <c r="AC13" s="65"/>
       <c r="AD13" s="65"/>
     </row>
@@ -2301,9 +2310,9 @@
       <c r="Y14" s="1">
         <v>1</v>
       </c>
-      <c r="Z14" s="96"/>
-      <c r="AA14" s="97"/>
-      <c r="AB14" s="97"/>
+      <c r="Z14" s="97"/>
+      <c r="AA14" s="98"/>
+      <c r="AB14" s="98"/>
       <c r="AC14" s="65"/>
       <c r="AD14" s="65"/>
     </row>
@@ -2385,9 +2394,9 @@
       <c r="Y15" s="1">
         <v>1</v>
       </c>
-      <c r="Z15" s="96"/>
-      <c r="AA15" s="97"/>
-      <c r="AB15" s="97"/>
+      <c r="Z15" s="97"/>
+      <c r="AA15" s="98"/>
+      <c r="AB15" s="98"/>
       <c r="AC15" s="65"/>
       <c r="AD15" s="65"/>
     </row>
@@ -2469,9 +2478,9 @@
       <c r="Y16" s="1">
         <v>1</v>
       </c>
-      <c r="Z16" s="96"/>
-      <c r="AA16" s="97"/>
-      <c r="AB16" s="97"/>
+      <c r="Z16" s="97"/>
+      <c r="AA16" s="98"/>
+      <c r="AB16" s="98"/>
       <c r="AC16" s="65"/>
       <c r="AD16" s="65"/>
     </row>
@@ -2553,9 +2562,9 @@
       <c r="Y17" s="1">
         <v>1</v>
       </c>
-      <c r="Z17" s="96"/>
-      <c r="AA17" s="97"/>
-      <c r="AB17" s="97"/>
+      <c r="Z17" s="97"/>
+      <c r="AA17" s="98"/>
+      <c r="AB17" s="98"/>
       <c r="AC17" s="65"/>
       <c r="AD17" s="65"/>
     </row>
@@ -2637,9 +2646,9 @@
       <c r="Y18" s="1">
         <v>1</v>
       </c>
-      <c r="Z18" s="96"/>
-      <c r="AA18" s="97"/>
-      <c r="AB18" s="97"/>
+      <c r="Z18" s="97"/>
+      <c r="AA18" s="98"/>
+      <c r="AB18" s="98"/>
       <c r="AC18" s="65"/>
       <c r="AD18" s="65"/>
     </row>
@@ -2721,9 +2730,9 @@
       <c r="Y19" s="1">
         <v>1</v>
       </c>
-      <c r="Z19" s="96"/>
-      <c r="AA19" s="97"/>
-      <c r="AB19" s="97"/>
+      <c r="Z19" s="97"/>
+      <c r="AA19" s="98"/>
+      <c r="AB19" s="98"/>
       <c r="AC19" s="65"/>
       <c r="AD19" s="65"/>
     </row>
@@ -2805,9 +2814,9 @@
       <c r="Y20" s="1">
         <v>1</v>
       </c>
-      <c r="Z20" s="96"/>
-      <c r="AA20" s="97"/>
-      <c r="AB20" s="97"/>
+      <c r="Z20" s="97"/>
+      <c r="AA20" s="98"/>
+      <c r="AB20" s="98"/>
       <c r="AC20" s="65"/>
       <c r="AD20" s="65"/>
     </row>
@@ -2889,9 +2898,9 @@
       <c r="Y21" s="1">
         <v>1</v>
       </c>
-      <c r="Z21" s="96"/>
-      <c r="AA21" s="97"/>
-      <c r="AB21" s="97"/>
+      <c r="Z21" s="97"/>
+      <c r="AA21" s="98"/>
+      <c r="AB21" s="98"/>
       <c r="AC21" s="65"/>
       <c r="AD21" s="65"/>
     </row>
@@ -2973,9 +2982,9 @@
       <c r="Y22" s="1">
         <v>1</v>
       </c>
-      <c r="Z22" s="96"/>
-      <c r="AA22" s="97"/>
-      <c r="AB22" s="97"/>
+      <c r="Z22" s="97"/>
+      <c r="AA22" s="98"/>
+      <c r="AB22" s="98"/>
       <c r="AC22" s="65"/>
       <c r="AD22" s="65"/>
     </row>
@@ -3057,9 +3066,9 @@
       <c r="Y23" s="1">
         <v>1</v>
       </c>
-      <c r="Z23" s="96"/>
-      <c r="AA23" s="97"/>
-      <c r="AB23" s="97"/>
+      <c r="Z23" s="97"/>
+      <c r="AA23" s="98"/>
+      <c r="AB23" s="98"/>
       <c r="AC23" s="65"/>
       <c r="AD23" s="65"/>
     </row>
@@ -3141,9 +3150,9 @@
       <c r="Y24" s="1">
         <v>1</v>
       </c>
-      <c r="Z24" s="96"/>
-      <c r="AA24" s="97"/>
-      <c r="AB24" s="97"/>
+      <c r="Z24" s="97"/>
+      <c r="AA24" s="98"/>
+      <c r="AB24" s="98"/>
       <c r="AC24" s="65"/>
       <c r="AD24" s="65"/>
     </row>
@@ -3225,9 +3234,9 @@
       <c r="Y25" s="1">
         <v>1</v>
       </c>
-      <c r="Z25" s="96"/>
-      <c r="AA25" s="97"/>
-      <c r="AB25" s="97"/>
+      <c r="Z25" s="97"/>
+      <c r="AA25" s="98"/>
+      <c r="AB25" s="98"/>
       <c r="AC25" s="65"/>
       <c r="AD25" s="65"/>
     </row>
@@ -3309,9 +3318,9 @@
       <c r="Y26" s="1">
         <v>1</v>
       </c>
-      <c r="Z26" s="96"/>
-      <c r="AA26" s="97"/>
-      <c r="AB26" s="97"/>
+      <c r="Z26" s="97"/>
+      <c r="AA26" s="98"/>
+      <c r="AB26" s="98"/>
       <c r="AC26" s="65"/>
       <c r="AD26" s="65"/>
     </row>
@@ -3393,9 +3402,9 @@
       <c r="Y27" s="27">
         <v>1</v>
       </c>
-      <c r="Z27" s="96"/>
-      <c r="AA27" s="97"/>
-      <c r="AB27" s="97"/>
+      <c r="Z27" s="97"/>
+      <c r="AA27" s="98"/>
+      <c r="AB27" s="98"/>
       <c r="AC27" s="65"/>
       <c r="AD27" s="65"/>
     </row>
@@ -3476,11 +3485,11 @@
       <c r="Y28" s="33">
         <v>1</v>
       </c>
-      <c r="Z28" s="103" t="s">
+      <c r="Z28" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="AA28" s="104"/>
-      <c r="AB28" s="104"/>
+      <c r="AA28" s="106"/>
+      <c r="AB28" s="106"/>
       <c r="AC28" s="65"/>
       <c r="AD28" s="65"/>
     </row>
@@ -3562,11 +3571,11 @@
       <c r="Y29" s="1">
         <v>1</v>
       </c>
-      <c r="Z29" s="96" t="s">
+      <c r="Z29" s="97" t="s">
         <v>51</v>
       </c>
-      <c r="AA29" s="97"/>
-      <c r="AB29" s="97"/>
+      <c r="AA29" s="98"/>
+      <c r="AB29" s="98"/>
       <c r="AC29" s="65"/>
       <c r="AD29" s="65"/>
     </row>
@@ -3648,9 +3657,9 @@
       <c r="Y30" s="1">
         <v>1</v>
       </c>
-      <c r="Z30" s="96"/>
-      <c r="AA30" s="97"/>
-      <c r="AB30" s="97"/>
+      <c r="Z30" s="97"/>
+      <c r="AA30" s="98"/>
+      <c r="AB30" s="98"/>
       <c r="AC30" s="65"/>
       <c r="AD30" s="65"/>
     </row>
@@ -3732,9 +3741,9 @@
       <c r="Y31" s="1">
         <v>1</v>
       </c>
-      <c r="Z31" s="96"/>
-      <c r="AA31" s="97"/>
-      <c r="AB31" s="97"/>
+      <c r="Z31" s="97"/>
+      <c r="AA31" s="98"/>
+      <c r="AB31" s="98"/>
       <c r="AC31" s="65"/>
       <c r="AD31" s="65"/>
     </row>
@@ -3816,9 +3825,9 @@
       <c r="Y32" s="1">
         <v>1</v>
       </c>
-      <c r="Z32" s="96"/>
-      <c r="AA32" s="97"/>
-      <c r="AB32" s="97"/>
+      <c r="Z32" s="97"/>
+      <c r="AA32" s="98"/>
+      <c r="AB32" s="98"/>
       <c r="AC32" s="65"/>
       <c r="AD32" s="65"/>
     </row>
@@ -3900,9 +3909,9 @@
       <c r="Y33" s="1">
         <v>1</v>
       </c>
-      <c r="Z33" s="96"/>
-      <c r="AA33" s="97"/>
-      <c r="AB33" s="97"/>
+      <c r="Z33" s="97"/>
+      <c r="AA33" s="98"/>
+      <c r="AB33" s="98"/>
       <c r="AC33" s="65"/>
       <c r="AD33" s="65"/>
     </row>
@@ -3984,9 +3993,9 @@
       <c r="Y34" s="1">
         <v>1</v>
       </c>
-      <c r="Z34" s="96"/>
-      <c r="AA34" s="97"/>
-      <c r="AB34" s="97"/>
+      <c r="Z34" s="97"/>
+      <c r="AA34" s="98"/>
+      <c r="AB34" s="98"/>
       <c r="AC34" s="65"/>
       <c r="AD34" s="65"/>
     </row>
@@ -4068,9 +4077,9 @@
       <c r="Y35" s="1">
         <v>1</v>
       </c>
-      <c r="Z35" s="96"/>
-      <c r="AA35" s="97"/>
-      <c r="AB35" s="97"/>
+      <c r="Z35" s="97"/>
+      <c r="AA35" s="98"/>
+      <c r="AB35" s="98"/>
       <c r="AC35" s="65"/>
       <c r="AD35" s="65"/>
     </row>
@@ -4152,9 +4161,9 @@
       <c r="Y36" s="1">
         <v>1</v>
       </c>
-      <c r="Z36" s="96"/>
-      <c r="AA36" s="97"/>
-      <c r="AB36" s="97"/>
+      <c r="Z36" s="97"/>
+      <c r="AA36" s="98"/>
+      <c r="AB36" s="98"/>
       <c r="AC36" s="65"/>
       <c r="AD36" s="65"/>
     </row>
@@ -4236,9 +4245,9 @@
       <c r="Y37" s="1">
         <v>1</v>
       </c>
-      <c r="Z37" s="96"/>
-      <c r="AA37" s="97"/>
-      <c r="AB37" s="97"/>
+      <c r="Z37" s="97"/>
+      <c r="AA37" s="98"/>
+      <c r="AB37" s="98"/>
       <c r="AC37" s="65"/>
       <c r="AD37" s="65"/>
     </row>
@@ -4320,9 +4329,9 @@
       <c r="Y38" s="1">
         <v>1</v>
       </c>
-      <c r="Z38" s="96"/>
-      <c r="AA38" s="97"/>
-      <c r="AB38" s="97"/>
+      <c r="Z38" s="97"/>
+      <c r="AA38" s="98"/>
+      <c r="AB38" s="98"/>
       <c r="AC38" s="65"/>
       <c r="AD38" s="65"/>
     </row>
@@ -4404,9 +4413,9 @@
       <c r="Y39" s="1">
         <v>1</v>
       </c>
-      <c r="Z39" s="96"/>
-      <c r="AA39" s="97"/>
-      <c r="AB39" s="97"/>
+      <c r="Z39" s="97"/>
+      <c r="AA39" s="98"/>
+      <c r="AB39" s="98"/>
       <c r="AC39" s="65"/>
       <c r="AD39" s="65"/>
     </row>
@@ -4488,9 +4497,9 @@
       <c r="Y40" s="1">
         <v>1</v>
       </c>
-      <c r="Z40" s="96"/>
-      <c r="AA40" s="97"/>
-      <c r="AB40" s="97"/>
+      <c r="Z40" s="97"/>
+      <c r="AA40" s="98"/>
+      <c r="AB40" s="98"/>
       <c r="AC40" s="65"/>
       <c r="AD40" s="65"/>
     </row>
@@ -4572,9 +4581,9 @@
       <c r="Y41" s="1">
         <v>1</v>
       </c>
-      <c r="Z41" s="96"/>
-      <c r="AA41" s="97"/>
-      <c r="AB41" s="97"/>
+      <c r="Z41" s="97"/>
+      <c r="AA41" s="98"/>
+      <c r="AB41" s="98"/>
       <c r="AC41" s="65"/>
       <c r="AD41" s="65"/>
     </row>
@@ -4656,9 +4665,9 @@
       <c r="Y42" s="1">
         <v>1</v>
       </c>
-      <c r="Z42" s="96"/>
-      <c r="AA42" s="97"/>
-      <c r="AB42" s="97"/>
+      <c r="Z42" s="97"/>
+      <c r="AA42" s="98"/>
+      <c r="AB42" s="98"/>
       <c r="AC42" s="65"/>
       <c r="AD42" s="65"/>
     </row>
@@ -4740,9 +4749,9 @@
       <c r="Y43" s="1">
         <v>1</v>
       </c>
-      <c r="Z43" s="96"/>
-      <c r="AA43" s="97"/>
-      <c r="AB43" s="97"/>
+      <c r="Z43" s="97"/>
+      <c r="AA43" s="98"/>
+      <c r="AB43" s="98"/>
       <c r="AC43" s="65"/>
       <c r="AD43" s="65"/>
     </row>
@@ -4824,9 +4833,9 @@
       <c r="Y44" s="1">
         <v>1</v>
       </c>
-      <c r="Z44" s="96"/>
-      <c r="AA44" s="97"/>
-      <c r="AB44" s="97"/>
+      <c r="Z44" s="97"/>
+      <c r="AA44" s="98"/>
+      <c r="AB44" s="98"/>
       <c r="AC44" s="65"/>
       <c r="AD44" s="65"/>
     </row>
@@ -4908,9 +4917,9 @@
       <c r="Y45" s="1">
         <v>1</v>
       </c>
-      <c r="Z45" s="96"/>
-      <c r="AA45" s="97"/>
-      <c r="AB45" s="97"/>
+      <c r="Z45" s="97"/>
+      <c r="AA45" s="98"/>
+      <c r="AB45" s="98"/>
       <c r="AC45" s="65"/>
       <c r="AD45" s="65"/>
     </row>
@@ -4992,9 +5001,9 @@
       <c r="Y46" s="1">
         <v>1</v>
       </c>
-      <c r="Z46" s="96"/>
-      <c r="AA46" s="97"/>
-      <c r="AB46" s="97"/>
+      <c r="Z46" s="97"/>
+      <c r="AA46" s="98"/>
+      <c r="AB46" s="98"/>
       <c r="AC46" s="65"/>
       <c r="AD46" s="65"/>
     </row>
@@ -5075,11 +5084,11 @@
       <c r="Y47" s="43">
         <v>1</v>
       </c>
-      <c r="Z47" s="103" t="s">
+      <c r="Z47" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="AA47" s="104"/>
-      <c r="AB47" s="104"/>
+      <c r="AA47" s="106"/>
+      <c r="AB47" s="106"/>
       <c r="AC47" s="66"/>
       <c r="AD47" s="65"/>
     </row>
@@ -5161,11 +5170,11 @@
       <c r="Y48" s="43">
         <v>1</v>
       </c>
-      <c r="Z48" s="101" t="s">
+      <c r="Z48" s="102" t="s">
         <v>55</v>
       </c>
-      <c r="AA48" s="102"/>
-      <c r="AB48" s="102"/>
+      <c r="AA48" s="107"/>
+      <c r="AB48" s="107"/>
       <c r="AC48" s="67"/>
       <c r="AD48" s="65"/>
     </row>
@@ -5246,11 +5255,11 @@
       <c r="Y49" s="43">
         <v>1</v>
       </c>
-      <c r="Z49" s="103" t="s">
+      <c r="Z49" s="104" t="s">
         <v>56</v>
       </c>
-      <c r="AA49" s="104"/>
-      <c r="AB49" s="104"/>
+      <c r="AA49" s="106"/>
+      <c r="AB49" s="106"/>
       <c r="AC49" s="65"/>
       <c r="AD49" s="65"/>
     </row>
@@ -5330,11 +5339,11 @@
       <c r="Y50" s="40">
         <v>1</v>
       </c>
-      <c r="Z50" s="103" t="s">
+      <c r="Z50" s="104" t="s">
         <v>57</v>
       </c>
-      <c r="AA50" s="104"/>
-      <c r="AB50" s="104"/>
+      <c r="AA50" s="106"/>
+      <c r="AB50" s="106"/>
       <c r="AC50" s="65"/>
       <c r="AD50" s="65"/>
     </row>
@@ -5416,11 +5425,11 @@
       <c r="Y51" s="43">
         <v>1</v>
       </c>
-      <c r="Z51" s="96" t="s">
+      <c r="Z51" s="97" t="s">
         <v>59</v>
       </c>
-      <c r="AA51" s="97"/>
-      <c r="AB51" s="97"/>
+      <c r="AA51" s="98"/>
+      <c r="AB51" s="98"/>
       <c r="AC51" s="65"/>
       <c r="AD51" s="65"/>
     </row>
@@ -5502,9 +5511,9 @@
       <c r="Y52" s="1">
         <v>1</v>
       </c>
-      <c r="Z52" s="96"/>
-      <c r="AA52" s="97"/>
-      <c r="AB52" s="97"/>
+      <c r="Z52" s="97"/>
+      <c r="AA52" s="98"/>
+      <c r="AB52" s="98"/>
       <c r="AC52" s="65"/>
       <c r="AD52" s="65"/>
     </row>
@@ -5586,9 +5595,9 @@
       <c r="Y53" s="1">
         <v>1</v>
       </c>
-      <c r="Z53" s="96"/>
-      <c r="AA53" s="97"/>
-      <c r="AB53" s="97"/>
+      <c r="Z53" s="97"/>
+      <c r="AA53" s="98"/>
+      <c r="AB53" s="98"/>
       <c r="AC53" s="65"/>
       <c r="AD53" s="65"/>
     </row>
@@ -5670,9 +5679,9 @@
       <c r="Y54" s="1">
         <v>1</v>
       </c>
-      <c r="Z54" s="96"/>
-      <c r="AA54" s="97"/>
-      <c r="AB54" s="97"/>
+      <c r="Z54" s="97"/>
+      <c r="AA54" s="98"/>
+      <c r="AB54" s="98"/>
       <c r="AC54" s="65"/>
       <c r="AD54" s="65"/>
     </row>
@@ -5754,9 +5763,9 @@
       <c r="Y55" s="1">
         <v>1</v>
       </c>
-      <c r="Z55" s="96"/>
-      <c r="AA55" s="97"/>
-      <c r="AB55" s="97"/>
+      <c r="Z55" s="97"/>
+      <c r="AA55" s="98"/>
+      <c r="AB55" s="98"/>
       <c r="AC55" s="65"/>
       <c r="AD55" s="65"/>
     </row>
@@ -5838,9 +5847,9 @@
       <c r="Y56" s="1">
         <v>1</v>
       </c>
-      <c r="Z56" s="96"/>
-      <c r="AA56" s="97"/>
-      <c r="AB56" s="97"/>
+      <c r="Z56" s="97"/>
+      <c r="AA56" s="98"/>
+      <c r="AB56" s="98"/>
       <c r="AC56" s="65"/>
       <c r="AD56" s="65"/>
     </row>
@@ -5922,9 +5931,9 @@
       <c r="Y57" s="27">
         <v>1</v>
       </c>
-      <c r="Z57" s="96"/>
-      <c r="AA57" s="97"/>
-      <c r="AB57" s="97"/>
+      <c r="Z57" s="97"/>
+      <c r="AA57" s="98"/>
+      <c r="AB57" s="98"/>
       <c r="AC57" s="65"/>
       <c r="AD57" s="65"/>
     </row>
@@ -6005,11 +6014,11 @@
       <c r="Y58" s="53">
         <v>1</v>
       </c>
-      <c r="Z58" s="101" t="s">
+      <c r="Z58" s="102" t="s">
         <v>58</v>
       </c>
-      <c r="AA58" s="102"/>
-      <c r="AB58" s="102"/>
+      <c r="AA58" s="107"/>
+      <c r="AB58" s="107"/>
       <c r="AC58" s="65"/>
       <c r="AD58" s="65"/>
     </row>
@@ -6090,11 +6099,11 @@
       <c r="Y59" s="50">
         <v>1</v>
       </c>
-      <c r="Z59" s="96" t="s">
+      <c r="Z59" s="97" t="s">
         <v>60</v>
       </c>
-      <c r="AA59" s="97"/>
-      <c r="AB59" s="97"/>
+      <c r="AA59" s="98"/>
+      <c r="AB59" s="98"/>
       <c r="AC59" s="65"/>
       <c r="AD59" s="65"/>
     </row>
@@ -6175,9 +6184,9 @@
       <c r="Y60" s="50">
         <v>1</v>
       </c>
-      <c r="Z60" s="96"/>
-      <c r="AA60" s="97"/>
-      <c r="AB60" s="97"/>
+      <c r="Z60" s="97"/>
+      <c r="AA60" s="98"/>
+      <c r="AB60" s="98"/>
       <c r="AC60" s="65"/>
       <c r="AD60" s="65"/>
     </row>
@@ -6258,9 +6267,9 @@
       <c r="Y61" s="50">
         <v>1</v>
       </c>
-      <c r="Z61" s="96"/>
-      <c r="AA61" s="97"/>
-      <c r="AB61" s="97"/>
+      <c r="Z61" s="97"/>
+      <c r="AA61" s="98"/>
+      <c r="AB61" s="98"/>
       <c r="AC61" s="65"/>
       <c r="AD61" s="65"/>
     </row>
@@ -6341,9 +6350,9 @@
       <c r="Y62" s="50">
         <v>1</v>
       </c>
-      <c r="Z62" s="96"/>
-      <c r="AA62" s="97"/>
-      <c r="AB62" s="97"/>
+      <c r="Z62" s="97"/>
+      <c r="AA62" s="98"/>
+      <c r="AB62" s="98"/>
       <c r="AC62" s="65"/>
       <c r="AD62" s="65"/>
     </row>
@@ -6424,9 +6433,9 @@
       <c r="Y63" s="50">
         <v>1</v>
       </c>
-      <c r="Z63" s="96"/>
-      <c r="AA63" s="97"/>
-      <c r="AB63" s="97"/>
+      <c r="Z63" s="97"/>
+      <c r="AA63" s="98"/>
+      <c r="AB63" s="98"/>
       <c r="AC63" s="65"/>
       <c r="AD63" s="65"/>
     </row>
@@ -6507,9 +6516,9 @@
       <c r="Y64" s="50">
         <v>1</v>
       </c>
-      <c r="Z64" s="96"/>
-      <c r="AA64" s="97"/>
-      <c r="AB64" s="97"/>
+      <c r="Z64" s="97"/>
+      <c r="AA64" s="98"/>
+      <c r="AB64" s="98"/>
       <c r="AC64" s="65"/>
       <c r="AD64" s="65"/>
     </row>
@@ -6590,9 +6599,9 @@
       <c r="Y65" s="50">
         <v>1</v>
       </c>
-      <c r="Z65" s="96"/>
-      <c r="AA65" s="97"/>
-      <c r="AB65" s="97"/>
+      <c r="Z65" s="97"/>
+      <c r="AA65" s="98"/>
+      <c r="AB65" s="98"/>
       <c r="AC65" s="65"/>
       <c r="AD65" s="65"/>
     </row>
@@ -6673,9 +6682,9 @@
       <c r="Y66" s="57">
         <v>1</v>
       </c>
-      <c r="Z66" s="96"/>
-      <c r="AA66" s="97"/>
-      <c r="AB66" s="97"/>
+      <c r="Z66" s="97"/>
+      <c r="AA66" s="98"/>
+      <c r="AB66" s="98"/>
       <c r="AC66" s="65"/>
       <c r="AD66" s="65"/>
     </row>
@@ -6757,11 +6766,11 @@
       <c r="Y67" s="43">
         <v>1</v>
       </c>
-      <c r="Z67" s="96" t="s">
+      <c r="Z67" s="97" t="s">
         <v>61</v>
       </c>
-      <c r="AA67" s="98"/>
-      <c r="AB67" s="98"/>
+      <c r="AA67" s="99"/>
+      <c r="AB67" s="99"/>
       <c r="AC67" s="65"/>
       <c r="AD67" s="65"/>
     </row>
@@ -6843,9 +6852,9 @@
       <c r="Y68" s="1">
         <v>1</v>
       </c>
-      <c r="Z68" s="96"/>
-      <c r="AA68" s="98"/>
-      <c r="AB68" s="98"/>
+      <c r="Z68" s="97"/>
+      <c r="AA68" s="99"/>
+      <c r="AB68" s="99"/>
       <c r="AC68" s="65"/>
       <c r="AD68" s="65"/>
     </row>
@@ -6927,9 +6936,9 @@
       <c r="Y69" s="1">
         <v>1</v>
       </c>
-      <c r="Z69" s="96"/>
-      <c r="AA69" s="98"/>
-      <c r="AB69" s="98"/>
+      <c r="Z69" s="97"/>
+      <c r="AA69" s="99"/>
+      <c r="AB69" s="99"/>
       <c r="AC69" s="65"/>
       <c r="AD69" s="65"/>
     </row>
@@ -7011,9 +7020,9 @@
       <c r="Y70" s="1">
         <v>1</v>
       </c>
-      <c r="Z70" s="96"/>
-      <c r="AA70" s="98"/>
-      <c r="AB70" s="98"/>
+      <c r="Z70" s="97"/>
+      <c r="AA70" s="99"/>
+      <c r="AB70" s="99"/>
       <c r="AC70" s="65"/>
       <c r="AD70" s="65"/>
     </row>
@@ -7095,9 +7104,9 @@
       <c r="Y71" s="1">
         <v>1</v>
       </c>
-      <c r="Z71" s="96"/>
-      <c r="AA71" s="98"/>
-      <c r="AB71" s="98"/>
+      <c r="Z71" s="97"/>
+      <c r="AA71" s="99"/>
+      <c r="AB71" s="99"/>
       <c r="AC71" s="65"/>
       <c r="AD71" s="65"/>
     </row>
@@ -7179,9 +7188,9 @@
       <c r="Y72" s="1">
         <v>1</v>
       </c>
-      <c r="Z72" s="96"/>
-      <c r="AA72" s="98"/>
-      <c r="AB72" s="98"/>
+      <c r="Z72" s="97"/>
+      <c r="AA72" s="99"/>
+      <c r="AB72" s="99"/>
       <c r="AC72" s="65"/>
       <c r="AD72" s="65"/>
     </row>
@@ -7263,9 +7272,9 @@
       <c r="Y73" s="1">
         <v>1</v>
       </c>
-      <c r="Z73" s="96"/>
-      <c r="AA73" s="98"/>
-      <c r="AB73" s="98"/>
+      <c r="Z73" s="97"/>
+      <c r="AA73" s="99"/>
+      <c r="AB73" s="99"/>
       <c r="AC73" s="65"/>
       <c r="AD73" s="65"/>
     </row>
@@ -7347,9 +7356,9 @@
       <c r="Y74" s="1">
         <v>1</v>
       </c>
-      <c r="Z74" s="96"/>
-      <c r="AA74" s="98"/>
-      <c r="AB74" s="98"/>
+      <c r="Z74" s="97"/>
+      <c r="AA74" s="99"/>
+      <c r="AB74" s="99"/>
       <c r="AC74" s="65"/>
       <c r="AD74" s="65"/>
     </row>
@@ -7431,9 +7440,9 @@
       <c r="Y75" s="1">
         <v>1</v>
       </c>
-      <c r="Z75" s="96"/>
-      <c r="AA75" s="98"/>
-      <c r="AB75" s="98"/>
+      <c r="Z75" s="97"/>
+      <c r="AA75" s="99"/>
+      <c r="AB75" s="99"/>
       <c r="AC75" s="65"/>
       <c r="AD75" s="65"/>
     </row>
@@ -7515,9 +7524,9 @@
       <c r="Y76" s="1">
         <v>1</v>
       </c>
-      <c r="Z76" s="96"/>
-      <c r="AA76" s="98"/>
-      <c r="AB76" s="98"/>
+      <c r="Z76" s="97"/>
+      <c r="AA76" s="99"/>
+      <c r="AB76" s="99"/>
       <c r="AC76" s="65"/>
       <c r="AD76" s="65"/>
     </row>
@@ -7599,9 +7608,9 @@
       <c r="Y77" s="1">
         <v>1</v>
       </c>
-      <c r="Z77" s="96"/>
-      <c r="AA77" s="98"/>
-      <c r="AB77" s="98"/>
+      <c r="Z77" s="97"/>
+      <c r="AA77" s="99"/>
+      <c r="AB77" s="99"/>
       <c r="AC77" s="65"/>
       <c r="AD77" s="65"/>
     </row>
@@ -7683,9 +7692,9 @@
       <c r="Y78" s="1">
         <v>1</v>
       </c>
-      <c r="Z78" s="96"/>
-      <c r="AA78" s="98"/>
-      <c r="AB78" s="98"/>
+      <c r="Z78" s="97"/>
+      <c r="AA78" s="99"/>
+      <c r="AB78" s="99"/>
       <c r="AC78" s="65"/>
       <c r="AD78" s="65"/>
     </row>
@@ -7767,9 +7776,9 @@
       <c r="Y79" s="1">
         <v>1</v>
       </c>
-      <c r="Z79" s="96"/>
-      <c r="AA79" s="98"/>
-      <c r="AB79" s="98"/>
+      <c r="Z79" s="97"/>
+      <c r="AA79" s="99"/>
+      <c r="AB79" s="99"/>
       <c r="AC79" s="65"/>
       <c r="AD79" s="65"/>
     </row>
@@ -7851,9 +7860,9 @@
       <c r="Y80" s="1">
         <v>1</v>
       </c>
-      <c r="Z80" s="96"/>
-      <c r="AA80" s="98"/>
-      <c r="AB80" s="98"/>
+      <c r="Z80" s="97"/>
+      <c r="AA80" s="99"/>
+      <c r="AB80" s="99"/>
       <c r="AC80" s="65"/>
       <c r="AD80" s="65"/>
     </row>
@@ -7935,9 +7944,9 @@
       <c r="Y81" s="1">
         <v>1</v>
       </c>
-      <c r="Z81" s="96"/>
-      <c r="AA81" s="98"/>
-      <c r="AB81" s="98"/>
+      <c r="Z81" s="97"/>
+      <c r="AA81" s="99"/>
+      <c r="AB81" s="99"/>
       <c r="AC81" s="65"/>
       <c r="AD81" s="65"/>
     </row>
@@ -8019,9 +8028,9 @@
       <c r="Y82" s="1">
         <v>1</v>
       </c>
-      <c r="Z82" s="96"/>
-      <c r="AA82" s="98"/>
-      <c r="AB82" s="98"/>
+      <c r="Z82" s="97"/>
+      <c r="AA82" s="99"/>
+      <c r="AB82" s="99"/>
       <c r="AC82" s="65"/>
       <c r="AD82" s="65"/>
     </row>
@@ -8103,9 +8112,9 @@
       <c r="Y83" s="1">
         <v>1</v>
       </c>
-      <c r="Z83" s="96"/>
-      <c r="AA83" s="98"/>
-      <c r="AB83" s="98"/>
+      <c r="Z83" s="97"/>
+      <c r="AA83" s="99"/>
+      <c r="AB83" s="99"/>
       <c r="AC83" s="65"/>
       <c r="AD83" s="65"/>
     </row>
@@ -8187,9 +8196,9 @@
       <c r="Y84" s="1">
         <v>1</v>
       </c>
-      <c r="Z84" s="96"/>
-      <c r="AA84" s="98"/>
-      <c r="AB84" s="98"/>
+      <c r="Z84" s="97"/>
+      <c r="AA84" s="99"/>
+      <c r="AB84" s="99"/>
       <c r="AC84" s="65"/>
       <c r="AD84" s="65"/>
     </row>
@@ -8270,11 +8279,11 @@
       <c r="Y85" s="53">
         <v>1</v>
       </c>
-      <c r="Z85" s="101" t="s">
+      <c r="Z85" s="102" t="s">
         <v>58</v>
       </c>
-      <c r="AA85" s="110"/>
-      <c r="AB85" s="110"/>
+      <c r="AA85" s="103"/>
+      <c r="AB85" s="103"/>
       <c r="AC85" s="65"/>
       <c r="AD85" s="65"/>
     </row>
@@ -8355,11 +8364,11 @@
       <c r="Y86" s="40">
         <v>1</v>
       </c>
-      <c r="Z86" s="96" t="s">
+      <c r="Z86" s="97" t="s">
         <v>62</v>
       </c>
-      <c r="AA86" s="97"/>
-      <c r="AB86" s="97"/>
+      <c r="AA86" s="98"/>
+      <c r="AB86" s="98"/>
       <c r="AC86" s="65"/>
       <c r="AD86" s="65"/>
     </row>
@@ -8440,9 +8449,9 @@
       <c r="Y87" s="57">
         <v>1</v>
       </c>
-      <c r="Z87" s="96"/>
-      <c r="AA87" s="97"/>
-      <c r="AB87" s="97"/>
+      <c r="Z87" s="97"/>
+      <c r="AA87" s="98"/>
+      <c r="AB87" s="98"/>
       <c r="AC87" s="65"/>
       <c r="AD87" s="65"/>
     </row>
@@ -8523,11 +8532,11 @@
       <c r="Y88" s="53">
         <v>1</v>
       </c>
-      <c r="Z88" s="101" t="s">
+      <c r="Z88" s="102" t="s">
         <v>64</v>
       </c>
-      <c r="AA88" s="110"/>
-      <c r="AB88" s="110"/>
+      <c r="AA88" s="103"/>
+      <c r="AB88" s="103"/>
       <c r="AC88" s="65"/>
       <c r="AD88" s="65"/>
     </row>
@@ -8608,11 +8617,11 @@
       <c r="Y89" s="40">
         <v>1</v>
       </c>
-      <c r="Z89" s="101" t="s">
+      <c r="Z89" s="102" t="s">
         <v>63</v>
       </c>
-      <c r="AA89" s="110"/>
-      <c r="AB89" s="110"/>
+      <c r="AA89" s="103"/>
+      <c r="AB89" s="103"/>
       <c r="AC89" s="65"/>
       <c r="AD89" s="65"/>
     </row>
@@ -8693,11 +8702,11 @@
       <c r="Y90" s="57">
         <v>1</v>
       </c>
-      <c r="Z90" s="101" t="s">
+      <c r="Z90" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="AA90" s="110"/>
-      <c r="AB90" s="110"/>
+      <c r="AA90" s="103"/>
+      <c r="AB90" s="103"/>
       <c r="AC90" s="65"/>
       <c r="AD90" s="65"/>
     </row>
@@ -8778,11 +8787,11 @@
       <c r="Y91" s="53">
         <v>1</v>
       </c>
-      <c r="Z91" s="101" t="s">
+      <c r="Z91" s="102" t="s">
         <v>64</v>
       </c>
-      <c r="AA91" s="110"/>
-      <c r="AB91" s="110"/>
+      <c r="AA91" s="103"/>
+      <c r="AB91" s="103"/>
       <c r="AC91" s="65"/>
       <c r="AD91" s="65"/>
     </row>
@@ -8863,11 +8872,11 @@
       <c r="Y92" s="40">
         <v>1</v>
       </c>
-      <c r="Z92" s="96" t="s">
+      <c r="Z92" s="97" t="s">
         <v>65</v>
       </c>
-      <c r="AA92" s="97"/>
-      <c r="AB92" s="97"/>
+      <c r="AA92" s="98"/>
+      <c r="AB92" s="98"/>
       <c r="AC92" s="65"/>
       <c r="AD92" s="65"/>
     </row>
@@ -8948,9 +8957,9 @@
       <c r="Y93" s="57">
         <v>1</v>
       </c>
-      <c r="Z93" s="96"/>
-      <c r="AA93" s="97"/>
-      <c r="AB93" s="97"/>
+      <c r="Z93" s="97"/>
+      <c r="AA93" s="98"/>
+      <c r="AB93" s="98"/>
       <c r="AC93" s="65"/>
       <c r="AD93" s="65"/>
     </row>
@@ -9031,11 +9040,11 @@
       <c r="Y94" s="33">
         <v>1</v>
       </c>
-      <c r="Z94" s="96" t="s">
+      <c r="Z94" s="97" t="s">
         <v>68</v>
       </c>
-      <c r="AA94" s="98"/>
-      <c r="AB94" s="98"/>
+      <c r="AA94" s="99"/>
+      <c r="AB94" s="99"/>
     </row>
     <row r="95" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
@@ -9114,11 +9123,11 @@
       <c r="Y95" s="1">
         <v>1</v>
       </c>
-      <c r="Z95" s="99" t="s">
+      <c r="Z95" s="112" t="s">
         <v>69</v>
       </c>
-      <c r="AA95" s="100"/>
-      <c r="AB95" s="100"/>
+      <c r="AA95" s="113"/>
+      <c r="AB95" s="113"/>
     </row>
     <row r="96" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
@@ -9198,9 +9207,9 @@
       <c r="Y96" s="1">
         <v>1</v>
       </c>
-      <c r="Z96" s="99"/>
-      <c r="AA96" s="100"/>
-      <c r="AB96" s="100"/>
+      <c r="Z96" s="112"/>
+      <c r="AA96" s="113"/>
+      <c r="AB96" s="113"/>
     </row>
     <row r="97" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
@@ -9280,9 +9289,9 @@
       <c r="Y97" s="1">
         <v>1</v>
       </c>
-      <c r="Z97" s="99"/>
-      <c r="AA97" s="100"/>
-      <c r="AB97" s="100"/>
+      <c r="Z97" s="112"/>
+      <c r="AA97" s="113"/>
+      <c r="AB97" s="113"/>
     </row>
     <row r="98" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
@@ -9362,9 +9371,9 @@
       <c r="Y98" s="1">
         <v>1</v>
       </c>
-      <c r="Z98" s="99"/>
-      <c r="AA98" s="100"/>
-      <c r="AB98" s="100"/>
+      <c r="Z98" s="112"/>
+      <c r="AA98" s="113"/>
+      <c r="AB98" s="113"/>
     </row>
     <row r="99" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
@@ -9444,9 +9453,9 @@
       <c r="Y99" s="1">
         <v>1</v>
       </c>
-      <c r="Z99" s="99"/>
-      <c r="AA99" s="100"/>
-      <c r="AB99" s="100"/>
+      <c r="Z99" s="112"/>
+      <c r="AA99" s="113"/>
+      <c r="AB99" s="113"/>
     </row>
     <row r="100" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
@@ -9526,9 +9535,9 @@
       <c r="Y100" s="1">
         <v>1</v>
       </c>
-      <c r="Z100" s="99"/>
-      <c r="AA100" s="100"/>
-      <c r="AB100" s="100"/>
+      <c r="Z100" s="112"/>
+      <c r="AA100" s="113"/>
+      <c r="AB100" s="113"/>
     </row>
     <row r="101" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
@@ -9608,9 +9617,9 @@
       <c r="Y101" s="1">
         <v>1</v>
       </c>
-      <c r="Z101" s="99"/>
-      <c r="AA101" s="100"/>
-      <c r="AB101" s="100"/>
+      <c r="Z101" s="112"/>
+      <c r="AA101" s="113"/>
+      <c r="AB101" s="113"/>
     </row>
     <row r="102" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
@@ -9690,9 +9699,9 @@
       <c r="Y102" s="1">
         <v>1</v>
       </c>
-      <c r="Z102" s="99"/>
-      <c r="AA102" s="100"/>
-      <c r="AB102" s="100"/>
+      <c r="Z102" s="112"/>
+      <c r="AA102" s="113"/>
+      <c r="AB102" s="113"/>
     </row>
     <row r="103" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
@@ -9772,9 +9781,9 @@
       <c r="Y103" s="1">
         <v>1</v>
       </c>
-      <c r="Z103" s="99"/>
-      <c r="AA103" s="100"/>
-      <c r="AB103" s="100"/>
+      <c r="Z103" s="112"/>
+      <c r="AA103" s="113"/>
+      <c r="AB103" s="113"/>
     </row>
     <row r="104" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
@@ -9854,9 +9863,9 @@
       <c r="Y104" s="1">
         <v>1</v>
       </c>
-      <c r="Z104" s="99"/>
-      <c r="AA104" s="100"/>
-      <c r="AB104" s="100"/>
+      <c r="Z104" s="112"/>
+      <c r="AA104" s="113"/>
+      <c r="AB104" s="113"/>
     </row>
     <row r="105" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
@@ -9936,9 +9945,9 @@
       <c r="Y105" s="1">
         <v>1</v>
       </c>
-      <c r="Z105" s="99"/>
-      <c r="AA105" s="100"/>
-      <c r="AB105" s="100"/>
+      <c r="Z105" s="112"/>
+      <c r="AA105" s="113"/>
+      <c r="AB105" s="113"/>
     </row>
     <row r="106" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
@@ -10018,9 +10027,9 @@
       <c r="Y106" s="1">
         <v>1</v>
       </c>
-      <c r="Z106" s="99"/>
-      <c r="AA106" s="100"/>
-      <c r="AB106" s="100"/>
+      <c r="Z106" s="112"/>
+      <c r="AA106" s="113"/>
+      <c r="AB106" s="113"/>
     </row>
     <row r="107" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
@@ -10099,9 +10108,9 @@
       <c r="Y107" s="1">
         <v>1</v>
       </c>
-      <c r="Z107" s="99"/>
-      <c r="AA107" s="100"/>
-      <c r="AB107" s="100"/>
+      <c r="Z107" s="112"/>
+      <c r="AA107" s="113"/>
+      <c r="AB107" s="113"/>
     </row>
     <row r="108" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
@@ -10180,9 +10189,9 @@
       <c r="Y108" s="1">
         <v>1</v>
       </c>
-      <c r="Z108" s="99"/>
-      <c r="AA108" s="100"/>
-      <c r="AB108" s="100"/>
+      <c r="Z108" s="112"/>
+      <c r="AA108" s="113"/>
+      <c r="AB108" s="113"/>
     </row>
     <row r="109" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
@@ -10261,9 +10270,9 @@
       <c r="Y109" s="1">
         <v>1</v>
       </c>
-      <c r="Z109" s="99"/>
-      <c r="AA109" s="100"/>
-      <c r="AB109" s="100"/>
+      <c r="Z109" s="112"/>
+      <c r="AA109" s="113"/>
+      <c r="AB109" s="113"/>
     </row>
     <row r="110" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
@@ -10342,9 +10351,9 @@
       <c r="Y110" s="1">
         <v>1</v>
       </c>
-      <c r="Z110" s="99"/>
-      <c r="AA110" s="100"/>
-      <c r="AB110" s="100"/>
+      <c r="Z110" s="112"/>
+      <c r="AA110" s="113"/>
+      <c r="AB110" s="113"/>
     </row>
     <row r="111" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
@@ -10423,9 +10432,9 @@
       <c r="Y111" s="1">
         <v>1</v>
       </c>
-      <c r="Z111" s="99"/>
-      <c r="AA111" s="100"/>
-      <c r="AB111" s="100"/>
+      <c r="Z111" s="112"/>
+      <c r="AA111" s="113"/>
+      <c r="AB111" s="113"/>
     </row>
     <row r="112" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A112" s="43">
@@ -10504,11 +10513,11 @@
       <c r="Y112" s="43">
         <v>1</v>
       </c>
-      <c r="Z112" s="96" t="s">
+      <c r="Z112" s="97" t="s">
         <v>71</v>
       </c>
-      <c r="AA112" s="98"/>
-      <c r="AB112" s="98"/>
+      <c r="AA112" s="99"/>
+      <c r="AB112" s="99"/>
     </row>
     <row r="113" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
@@ -10588,9 +10597,9 @@
       <c r="Y113" s="1">
         <v>1</v>
       </c>
-      <c r="Z113" s="96"/>
-      <c r="AA113" s="98"/>
-      <c r="AB113" s="98"/>
+      <c r="Z113" s="97"/>
+      <c r="AA113" s="99"/>
+      <c r="AB113" s="99"/>
     </row>
     <row r="114" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
@@ -10670,9 +10679,9 @@
       <c r="Y114" s="1">
         <v>1</v>
       </c>
-      <c r="Z114" s="96"/>
-      <c r="AA114" s="98"/>
-      <c r="AB114" s="98"/>
+      <c r="Z114" s="97"/>
+      <c r="AA114" s="99"/>
+      <c r="AB114" s="99"/>
     </row>
     <row r="115" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
@@ -10752,9 +10761,9 @@
       <c r="Y115" s="1">
         <v>1</v>
       </c>
-      <c r="Z115" s="96"/>
-      <c r="AA115" s="98"/>
-      <c r="AB115" s="98"/>
+      <c r="Z115" s="97"/>
+      <c r="AA115" s="99"/>
+      <c r="AB115" s="99"/>
     </row>
     <row r="116" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
@@ -10834,9 +10843,9 @@
       <c r="Y116" s="1">
         <v>1</v>
       </c>
-      <c r="Z116" s="96"/>
-      <c r="AA116" s="98"/>
-      <c r="AB116" s="98"/>
+      <c r="Z116" s="97"/>
+      <c r="AA116" s="99"/>
+      <c r="AB116" s="99"/>
     </row>
     <row r="117" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
@@ -10916,9 +10925,9 @@
       <c r="Y117" s="1">
         <v>1</v>
       </c>
-      <c r="Z117" s="96"/>
-      <c r="AA117" s="98"/>
-      <c r="AB117" s="98"/>
+      <c r="Z117" s="97"/>
+      <c r="AA117" s="99"/>
+      <c r="AB117" s="99"/>
     </row>
     <row r="118" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
@@ -10998,9 +11007,9 @@
       <c r="Y118" s="1">
         <v>1</v>
       </c>
-      <c r="Z118" s="96"/>
-      <c r="AA118" s="98"/>
-      <c r="AB118" s="98"/>
+      <c r="Z118" s="97"/>
+      <c r="AA118" s="99"/>
+      <c r="AB118" s="99"/>
     </row>
     <row r="119" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
@@ -11080,9 +11089,9 @@
       <c r="Y119" s="1">
         <v>1</v>
       </c>
-      <c r="Z119" s="96"/>
-      <c r="AA119" s="98"/>
-      <c r="AB119" s="98"/>
+      <c r="Z119" s="97"/>
+      <c r="AA119" s="99"/>
+      <c r="AB119" s="99"/>
     </row>
     <row r="120" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
@@ -11162,9 +11171,9 @@
       <c r="Y120" s="1">
         <v>1</v>
       </c>
-      <c r="Z120" s="96"/>
-      <c r="AA120" s="98"/>
-      <c r="AB120" s="98"/>
+      <c r="Z120" s="97"/>
+      <c r="AA120" s="99"/>
+      <c r="AB120" s="99"/>
     </row>
     <row r="121" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
@@ -11244,9 +11253,9 @@
       <c r="Y121" s="1">
         <v>1</v>
       </c>
-      <c r="Z121" s="96"/>
-      <c r="AA121" s="98"/>
-      <c r="AB121" s="98"/>
+      <c r="Z121" s="97"/>
+      <c r="AA121" s="99"/>
+      <c r="AB121" s="99"/>
     </row>
     <row r="122" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
@@ -11326,9 +11335,9 @@
       <c r="Y122" s="1">
         <v>1</v>
       </c>
-      <c r="Z122" s="96"/>
-      <c r="AA122" s="98"/>
-      <c r="AB122" s="98"/>
+      <c r="Z122" s="97"/>
+      <c r="AA122" s="99"/>
+      <c r="AB122" s="99"/>
     </row>
     <row r="123" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
@@ -11407,9 +11416,9 @@
       <c r="Y123" s="1">
         <v>1</v>
       </c>
-      <c r="Z123" s="96"/>
-      <c r="AA123" s="98"/>
-      <c r="AB123" s="98"/>
+      <c r="Z123" s="97"/>
+      <c r="AA123" s="99"/>
+      <c r="AB123" s="99"/>
     </row>
     <row r="124" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
@@ -11488,9 +11497,9 @@
       <c r="Y124" s="1">
         <v>1</v>
       </c>
-      <c r="Z124" s="96"/>
-      <c r="AA124" s="98"/>
-      <c r="AB124" s="98"/>
+      <c r="Z124" s="97"/>
+      <c r="AA124" s="99"/>
+      <c r="AB124" s="99"/>
     </row>
     <row r="125" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
@@ -11569,9 +11578,9 @@
       <c r="Y125" s="1">
         <v>1</v>
       </c>
-      <c r="Z125" s="96"/>
-      <c r="AA125" s="98"/>
-      <c r="AB125" s="98"/>
+      <c r="Z125" s="97"/>
+      <c r="AA125" s="99"/>
+      <c r="AB125" s="99"/>
     </row>
     <row r="126" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
@@ -11650,9 +11659,9 @@
       <c r="Y126" s="1">
         <v>1</v>
       </c>
-      <c r="Z126" s="96"/>
-      <c r="AA126" s="98"/>
-      <c r="AB126" s="98"/>
+      <c r="Z126" s="97"/>
+      <c r="AA126" s="99"/>
+      <c r="AB126" s="99"/>
     </row>
     <row r="127" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
@@ -11731,9 +11740,9 @@
       <c r="Y127" s="1">
         <v>1</v>
       </c>
-      <c r="Z127" s="96"/>
-      <c r="AA127" s="98"/>
-      <c r="AB127" s="98"/>
+      <c r="Z127" s="97"/>
+      <c r="AA127" s="99"/>
+      <c r="AB127" s="99"/>
     </row>
     <row r="128" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
@@ -11812,9 +11821,9 @@
       <c r="Y128" s="1">
         <v>1</v>
       </c>
-      <c r="Z128" s="96"/>
-      <c r="AA128" s="98"/>
-      <c r="AB128" s="98"/>
+      <c r="Z128" s="97"/>
+      <c r="AA128" s="99"/>
+      <c r="AB128" s="99"/>
     </row>
     <row r="129" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
@@ -11893,9 +11902,9 @@
       <c r="Y129" s="1">
         <v>1</v>
       </c>
-      <c r="Z129" s="96"/>
-      <c r="AA129" s="98"/>
-      <c r="AB129" s="98"/>
+      <c r="Z129" s="97"/>
+      <c r="AA129" s="99"/>
+      <c r="AB129" s="99"/>
     </row>
     <row r="130" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A130" s="43">
@@ -11974,11 +11983,11 @@
       <c r="Y130" s="43">
         <v>1</v>
       </c>
-      <c r="Z130" s="96" t="s">
+      <c r="Z130" s="97" t="s">
         <v>72</v>
       </c>
-      <c r="AA130" s="98"/>
-      <c r="AB130" s="98"/>
+      <c r="AA130" s="99"/>
+      <c r="AB130" s="99"/>
     </row>
     <row r="131" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
@@ -12058,9 +12067,9 @@
       <c r="Y131" s="1">
         <v>1</v>
       </c>
-      <c r="Z131" s="96"/>
-      <c r="AA131" s="98"/>
-      <c r="AB131" s="98"/>
+      <c r="Z131" s="97"/>
+      <c r="AA131" s="99"/>
+      <c r="AB131" s="99"/>
     </row>
     <row r="132" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
@@ -12140,9 +12149,9 @@
       <c r="Y132" s="1">
         <v>1</v>
       </c>
-      <c r="Z132" s="96"/>
-      <c r="AA132" s="98"/>
-      <c r="AB132" s="98"/>
+      <c r="Z132" s="97"/>
+      <c r="AA132" s="99"/>
+      <c r="AB132" s="99"/>
     </row>
     <row r="133" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
@@ -12222,9 +12231,9 @@
       <c r="Y133" s="1">
         <v>1</v>
       </c>
-      <c r="Z133" s="96"/>
-      <c r="AA133" s="98"/>
-      <c r="AB133" s="98"/>
+      <c r="Z133" s="97"/>
+      <c r="AA133" s="99"/>
+      <c r="AB133" s="99"/>
     </row>
     <row r="134" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
@@ -12304,9 +12313,9 @@
       <c r="Y134" s="1">
         <v>1</v>
       </c>
-      <c r="Z134" s="96"/>
-      <c r="AA134" s="98"/>
-      <c r="AB134" s="98"/>
+      <c r="Z134" s="97"/>
+      <c r="AA134" s="99"/>
+      <c r="AB134" s="99"/>
     </row>
     <row r="135" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
@@ -12386,9 +12395,9 @@
       <c r="Y135" s="1">
         <v>1</v>
       </c>
-      <c r="Z135" s="96"/>
-      <c r="AA135" s="98"/>
-      <c r="AB135" s="98"/>
+      <c r="Z135" s="97"/>
+      <c r="AA135" s="99"/>
+      <c r="AB135" s="99"/>
     </row>
     <row r="136" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
@@ -12468,9 +12477,9 @@
       <c r="Y136" s="1">
         <v>1</v>
       </c>
-      <c r="Z136" s="96"/>
-      <c r="AA136" s="98"/>
-      <c r="AB136" s="98"/>
+      <c r="Z136" s="97"/>
+      <c r="AA136" s="99"/>
+      <c r="AB136" s="99"/>
     </row>
     <row r="137" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
@@ -12550,9 +12559,9 @@
       <c r="Y137" s="1">
         <v>1</v>
       </c>
-      <c r="Z137" s="96"/>
-      <c r="AA137" s="98"/>
-      <c r="AB137" s="98"/>
+      <c r="Z137" s="97"/>
+      <c r="AA137" s="99"/>
+      <c r="AB137" s="99"/>
     </row>
     <row r="138" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
@@ -12632,9 +12641,9 @@
       <c r="Y138" s="1">
         <v>1</v>
       </c>
-      <c r="Z138" s="96"/>
-      <c r="AA138" s="98"/>
-      <c r="AB138" s="98"/>
+      <c r="Z138" s="97"/>
+      <c r="AA138" s="99"/>
+      <c r="AB138" s="99"/>
     </row>
     <row r="139" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
@@ -12714,9 +12723,9 @@
       <c r="Y139" s="1">
         <v>1</v>
       </c>
-      <c r="Z139" s="96"/>
-      <c r="AA139" s="98"/>
-      <c r="AB139" s="98"/>
+      <c r="Z139" s="97"/>
+      <c r="AA139" s="99"/>
+      <c r="AB139" s="99"/>
     </row>
     <row r="140" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
@@ -12796,9 +12805,9 @@
       <c r="Y140" s="1">
         <v>1</v>
       </c>
-      <c r="Z140" s="96"/>
-      <c r="AA140" s="98"/>
-      <c r="AB140" s="98"/>
+      <c r="Z140" s="97"/>
+      <c r="AA140" s="99"/>
+      <c r="AB140" s="99"/>
     </row>
     <row r="141" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
@@ -12877,9 +12886,9 @@
       <c r="Y141" s="1">
         <v>1</v>
       </c>
-      <c r="Z141" s="96"/>
-      <c r="AA141" s="98"/>
-      <c r="AB141" s="98"/>
+      <c r="Z141" s="97"/>
+      <c r="AA141" s="99"/>
+      <c r="AB141" s="99"/>
     </row>
     <row r="142" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
@@ -12958,9 +12967,9 @@
       <c r="Y142" s="1">
         <v>1</v>
       </c>
-      <c r="Z142" s="96"/>
-      <c r="AA142" s="98"/>
-      <c r="AB142" s="98"/>
+      <c r="Z142" s="97"/>
+      <c r="AA142" s="99"/>
+      <c r="AB142" s="99"/>
     </row>
     <row r="143" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
@@ -13039,9 +13048,9 @@
       <c r="Y143" s="1">
         <v>1</v>
       </c>
-      <c r="Z143" s="96"/>
-      <c r="AA143" s="98"/>
-      <c r="AB143" s="98"/>
+      <c r="Z143" s="97"/>
+      <c r="AA143" s="99"/>
+      <c r="AB143" s="99"/>
     </row>
     <row r="144" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
@@ -13120,9 +13129,9 @@
       <c r="Y144" s="1">
         <v>1</v>
       </c>
-      <c r="Z144" s="96"/>
-      <c r="AA144" s="98"/>
-      <c r="AB144" s="98"/>
+      <c r="Z144" s="97"/>
+      <c r="AA144" s="99"/>
+      <c r="AB144" s="99"/>
     </row>
     <row r="145" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
@@ -13201,9 +13210,9 @@
       <c r="Y145" s="1">
         <v>1</v>
       </c>
-      <c r="Z145" s="96"/>
-      <c r="AA145" s="98"/>
-      <c r="AB145" s="98"/>
+      <c r="Z145" s="97"/>
+      <c r="AA145" s="99"/>
+      <c r="AB145" s="99"/>
     </row>
     <row r="146" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
@@ -13282,9 +13291,9 @@
       <c r="Y146" s="1">
         <v>1</v>
       </c>
-      <c r="Z146" s="96"/>
-      <c r="AA146" s="98"/>
-      <c r="AB146" s="98"/>
+      <c r="Z146" s="97"/>
+      <c r="AA146" s="99"/>
+      <c r="AB146" s="99"/>
     </row>
     <row r="147" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
@@ -13363,9 +13372,9 @@
       <c r="Y147" s="1">
         <v>1</v>
       </c>
-      <c r="Z147" s="96"/>
-      <c r="AA147" s="98"/>
-      <c r="AB147" s="98"/>
+      <c r="Z147" s="97"/>
+      <c r="AA147" s="99"/>
+      <c r="AB147" s="99"/>
     </row>
     <row r="148" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="43">
@@ -13444,11 +13453,11 @@
       <c r="Y148" s="40">
         <v>1</v>
       </c>
-      <c r="Z148" s="96" t="s">
+      <c r="Z148" s="97" t="s">
         <v>73</v>
       </c>
-      <c r="AA148" s="97"/>
-      <c r="AB148" s="97"/>
+      <c r="AA148" s="98"/>
+      <c r="AB148" s="98"/>
     </row>
     <row r="149" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
@@ -13528,9 +13537,9 @@
       <c r="Y149" s="50">
         <v>1</v>
       </c>
-      <c r="Z149" s="96"/>
-      <c r="AA149" s="97"/>
-      <c r="AB149" s="97"/>
+      <c r="Z149" s="97"/>
+      <c r="AA149" s="98"/>
+      <c r="AB149" s="98"/>
     </row>
     <row r="150" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
@@ -13610,9 +13619,9 @@
       <c r="Y150" s="50">
         <v>1</v>
       </c>
-      <c r="Z150" s="96"/>
-      <c r="AA150" s="97"/>
-      <c r="AB150" s="97"/>
+      <c r="Z150" s="97"/>
+      <c r="AA150" s="98"/>
+      <c r="AB150" s="98"/>
     </row>
     <row r="151" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
@@ -13691,9 +13700,9 @@
       <c r="Y151" s="50">
         <v>1</v>
       </c>
-      <c r="Z151" s="96"/>
-      <c r="AA151" s="97"/>
-      <c r="AB151" s="97"/>
+      <c r="Z151" s="97"/>
+      <c r="AA151" s="98"/>
+      <c r="AB151" s="98"/>
     </row>
     <row r="152" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A152" s="27">
@@ -13772,9 +13781,9 @@
       <c r="Y152" s="50">
         <v>1</v>
       </c>
-      <c r="Z152" s="96"/>
-      <c r="AA152" s="97"/>
-      <c r="AB152" s="97"/>
+      <c r="Z152" s="97"/>
+      <c r="AA152" s="98"/>
+      <c r="AB152" s="98"/>
     </row>
     <row r="153" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
@@ -13853,11 +13862,11 @@
       <c r="Y153" s="43">
         <v>1</v>
       </c>
-      <c r="Z153" s="96" t="s">
+      <c r="Z153" s="97" t="s">
         <v>74</v>
       </c>
-      <c r="AA153" s="97"/>
-      <c r="AB153" s="97"/>
+      <c r="AA153" s="98"/>
+      <c r="AB153" s="98"/>
     </row>
     <row r="154" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
@@ -13937,9 +13946,9 @@
       <c r="Y154" s="1">
         <v>1</v>
       </c>
-      <c r="Z154" s="96"/>
-      <c r="AA154" s="97"/>
-      <c r="AB154" s="97"/>
+      <c r="Z154" s="97"/>
+      <c r="AA154" s="98"/>
+      <c r="AB154" s="98"/>
     </row>
     <row r="155" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
@@ -14019,9 +14028,9 @@
       <c r="Y155" s="1">
         <v>1</v>
       </c>
-      <c r="Z155" s="96"/>
-      <c r="AA155" s="97"/>
-      <c r="AB155" s="97"/>
+      <c r="Z155" s="97"/>
+      <c r="AA155" s="98"/>
+      <c r="AB155" s="98"/>
     </row>
     <row r="156" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
@@ -14101,9 +14110,9 @@
       <c r="Y156" s="1">
         <v>1</v>
       </c>
-      <c r="Z156" s="96"/>
-      <c r="AA156" s="97"/>
-      <c r="AB156" s="97"/>
+      <c r="Z156" s="97"/>
+      <c r="AA156" s="98"/>
+      <c r="AB156" s="98"/>
     </row>
     <row r="157" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
@@ -14183,9 +14192,9 @@
       <c r="Y157" s="1">
         <v>1</v>
       </c>
-      <c r="Z157" s="96"/>
-      <c r="AA157" s="97"/>
-      <c r="AB157" s="97"/>
+      <c r="Z157" s="97"/>
+      <c r="AA157" s="98"/>
+      <c r="AB157" s="98"/>
     </row>
     <row r="158" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A158" s="43">
@@ -14264,11 +14273,11 @@
       <c r="Y158" s="43">
         <v>1</v>
       </c>
-      <c r="Z158" s="96" t="s">
+      <c r="Z158" s="97" t="s">
         <v>75</v>
       </c>
-      <c r="AA158" s="97"/>
-      <c r="AB158" s="97"/>
+      <c r="AA158" s="98"/>
+      <c r="AB158" s="98"/>
     </row>
     <row r="159" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
@@ -14348,9 +14357,9 @@
       <c r="Y159" s="1">
         <v>1</v>
       </c>
-      <c r="Z159" s="96"/>
-      <c r="AA159" s="97"/>
-      <c r="AB159" s="97"/>
+      <c r="Z159" s="97"/>
+      <c r="AA159" s="98"/>
+      <c r="AB159" s="98"/>
     </row>
     <row r="160" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
@@ -14430,9 +14439,9 @@
       <c r="Y160" s="1">
         <v>1</v>
       </c>
-      <c r="Z160" s="96"/>
-      <c r="AA160" s="97"/>
-      <c r="AB160" s="97"/>
+      <c r="Z160" s="97"/>
+      <c r="AA160" s="98"/>
+      <c r="AB160" s="98"/>
     </row>
     <row r="161" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
@@ -14512,9 +14521,9 @@
       <c r="Y161" s="1">
         <v>1</v>
       </c>
-      <c r="Z161" s="96"/>
-      <c r="AA161" s="97"/>
-      <c r="AB161" s="97"/>
+      <c r="Z161" s="97"/>
+      <c r="AA161" s="98"/>
+      <c r="AB161" s="98"/>
     </row>
     <row r="162" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A162" s="27">
@@ -14594,9 +14603,9 @@
       <c r="Y162" s="27">
         <v>1</v>
       </c>
-      <c r="Z162" s="96"/>
-      <c r="AA162" s="97"/>
-      <c r="AB162" s="97"/>
+      <c r="Z162" s="97"/>
+      <c r="AA162" s="98"/>
+      <c r="AB162" s="98"/>
     </row>
     <row r="163" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A163" s="43">
@@ -14675,11 +14684,11 @@
       <c r="Y163" s="40">
         <v>1</v>
       </c>
-      <c r="Z163" s="96" t="s">
+      <c r="Z163" s="97" t="s">
         <v>76</v>
       </c>
-      <c r="AA163" s="97"/>
-      <c r="AB163" s="97"/>
+      <c r="AA163" s="98"/>
+      <c r="AB163" s="98"/>
     </row>
     <row r="164" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A164" s="43">
@@ -14758,11 +14767,11 @@
       <c r="Y164" s="40">
         <v>1</v>
       </c>
-      <c r="Z164" s="96" t="s">
+      <c r="Z164" s="97" t="s">
         <v>77</v>
       </c>
-      <c r="AA164" s="97"/>
-      <c r="AB164" s="97"/>
+      <c r="AA164" s="98"/>
+      <c r="AB164" s="98"/>
     </row>
     <row r="165" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A165" s="43">
@@ -14841,11 +14850,11 @@
       <c r="Y165" s="40">
         <v>1</v>
       </c>
-      <c r="Z165" s="96" t="s">
+      <c r="Z165" s="97" t="s">
         <v>78</v>
       </c>
-      <c r="AA165" s="97"/>
-      <c r="AB165" s="97"/>
+      <c r="AA165" s="98"/>
+      <c r="AB165" s="98"/>
     </row>
     <row r="166" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A166" s="43">
@@ -14924,11 +14933,11 @@
       <c r="Y166" s="40">
         <v>1</v>
       </c>
-      <c r="Z166" s="96" t="s">
+      <c r="Z166" s="97" t="s">
         <v>80</v>
       </c>
-      <c r="AA166" s="97"/>
-      <c r="AB166" s="97"/>
+      <c r="AA166" s="98"/>
+      <c r="AB166" s="98"/>
     </row>
     <row r="167" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A167" s="43">
@@ -15007,11 +15016,11 @@
       <c r="Y167" s="40">
         <v>1</v>
       </c>
-      <c r="Z167" s="96" t="s">
+      <c r="Z167" s="97" t="s">
         <v>79</v>
       </c>
-      <c r="AA167" s="97"/>
-      <c r="AB167" s="97"/>
+      <c r="AA167" s="98"/>
+      <c r="AB167" s="98"/>
     </row>
     <row r="168" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A168" s="43">
@@ -15090,11 +15099,11 @@
       <c r="Y168" s="40">
         <v>1</v>
       </c>
-      <c r="Z168" s="96" t="s">
+      <c r="Z168" s="97" t="s">
         <v>81</v>
       </c>
-      <c r="AA168" s="97"/>
-      <c r="AB168" s="97"/>
+      <c r="AA168" s="98"/>
+      <c r="AB168" s="98"/>
     </row>
     <row r="169" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="43">
@@ -15173,11 +15182,11 @@
       <c r="Y169" s="40">
         <v>1</v>
       </c>
-      <c r="Z169" s="99" t="s">
+      <c r="Z169" s="112" t="s">
         <v>82</v>
       </c>
-      <c r="AA169" s="100"/>
-      <c r="AB169" s="100"/>
+      <c r="AA169" s="113"/>
+      <c r="AB169" s="113"/>
     </row>
     <row r="170" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
@@ -15256,9 +15265,9 @@
       <c r="Y170" s="50">
         <v>1</v>
       </c>
-      <c r="Z170" s="99"/>
-      <c r="AA170" s="100"/>
-      <c r="AB170" s="100"/>
+      <c r="Z170" s="112"/>
+      <c r="AA170" s="113"/>
+      <c r="AB170" s="113"/>
     </row>
     <row r="171" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
@@ -15337,9 +15346,9 @@
       <c r="Y171" s="50">
         <v>1</v>
       </c>
-      <c r="Z171" s="99"/>
-      <c r="AA171" s="100"/>
-      <c r="AB171" s="100"/>
+      <c r="Z171" s="112"/>
+      <c r="AA171" s="113"/>
+      <c r="AB171" s="113"/>
     </row>
     <row r="172" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
@@ -15418,9 +15427,9 @@
       <c r="Y172" s="50">
         <v>1</v>
       </c>
-      <c r="Z172" s="99"/>
-      <c r="AA172" s="100"/>
-      <c r="AB172" s="100"/>
+      <c r="Z172" s="112"/>
+      <c r="AA172" s="113"/>
+      <c r="AB172" s="113"/>
     </row>
     <row r="173" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
@@ -15499,9 +15508,9 @@
       <c r="Y173" s="50">
         <v>1</v>
       </c>
-      <c r="Z173" s="99"/>
-      <c r="AA173" s="100"/>
-      <c r="AB173" s="100"/>
+      <c r="Z173" s="112"/>
+      <c r="AA173" s="113"/>
+      <c r="AB173" s="113"/>
     </row>
     <row r="174" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
@@ -15580,9 +15589,9 @@
       <c r="Y174" s="50">
         <v>1</v>
       </c>
-      <c r="Z174" s="99"/>
-      <c r="AA174" s="100"/>
-      <c r="AB174" s="100"/>
+      <c r="Z174" s="112"/>
+      <c r="AA174" s="113"/>
+      <c r="AB174" s="113"/>
     </row>
     <row r="175" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
@@ -15661,9 +15670,9 @@
       <c r="Y175" s="50">
         <v>1</v>
       </c>
-      <c r="Z175" s="99"/>
-      <c r="AA175" s="100"/>
-      <c r="AB175" s="100"/>
+      <c r="Z175" s="112"/>
+      <c r="AA175" s="113"/>
+      <c r="AB175" s="113"/>
     </row>
     <row r="176" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A176" s="43">
@@ -15742,11 +15751,11 @@
       <c r="Y176" s="40">
         <v>1</v>
       </c>
-      <c r="Z176" s="96" t="s">
+      <c r="Z176" s="97" t="s">
         <v>83</v>
       </c>
-      <c r="AA176" s="98"/>
-      <c r="AB176" s="98"/>
+      <c r="AA176" s="99"/>
+      <c r="AB176" s="99"/>
     </row>
     <row r="177" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
@@ -15826,9 +15835,9 @@
       <c r="Y177" s="50">
         <v>1</v>
       </c>
-      <c r="Z177" s="96"/>
-      <c r="AA177" s="98"/>
-      <c r="AB177" s="98"/>
+      <c r="Z177" s="97"/>
+      <c r="AA177" s="99"/>
+      <c r="AB177" s="99"/>
     </row>
     <row r="178" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
@@ -15908,9 +15917,9 @@
       <c r="Y178" s="50">
         <v>1</v>
       </c>
-      <c r="Z178" s="96"/>
-      <c r="AA178" s="98"/>
-      <c r="AB178" s="98"/>
+      <c r="Z178" s="97"/>
+      <c r="AA178" s="99"/>
+      <c r="AB178" s="99"/>
     </row>
     <row r="179" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
@@ -15990,9 +15999,9 @@
       <c r="Y179" s="50">
         <v>1</v>
       </c>
-      <c r="Z179" s="96"/>
-      <c r="AA179" s="98"/>
-      <c r="AB179" s="98"/>
+      <c r="Z179" s="97"/>
+      <c r="AA179" s="99"/>
+      <c r="AB179" s="99"/>
     </row>
     <row r="180" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
@@ -16072,9 +16081,9 @@
       <c r="Y180" s="50">
         <v>1</v>
       </c>
-      <c r="Z180" s="96"/>
-      <c r="AA180" s="98"/>
-      <c r="AB180" s="98"/>
+      <c r="Z180" s="97"/>
+      <c r="AA180" s="99"/>
+      <c r="AB180" s="99"/>
     </row>
     <row r="181" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
@@ -16154,9 +16163,9 @@
       <c r="Y181" s="50">
         <v>1</v>
       </c>
-      <c r="Z181" s="96"/>
-      <c r="AA181" s="98"/>
-      <c r="AB181" s="98"/>
+      <c r="Z181" s="97"/>
+      <c r="AA181" s="99"/>
+      <c r="AB181" s="99"/>
     </row>
     <row r="182" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
@@ -16236,9 +16245,9 @@
       <c r="Y182" s="50">
         <v>1</v>
       </c>
-      <c r="Z182" s="96"/>
-      <c r="AA182" s="98"/>
-      <c r="AB182" s="98"/>
+      <c r="Z182" s="97"/>
+      <c r="AA182" s="99"/>
+      <c r="AB182" s="99"/>
     </row>
     <row r="183" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
@@ -16318,9 +16327,9 @@
       <c r="Y183" s="50">
         <v>1</v>
       </c>
-      <c r="Z183" s="96"/>
-      <c r="AA183" s="98"/>
-      <c r="AB183" s="98"/>
+      <c r="Z183" s="97"/>
+      <c r="AA183" s="99"/>
+      <c r="AB183" s="99"/>
     </row>
     <row r="184" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
@@ -16400,9 +16409,9 @@
       <c r="Y184" s="50">
         <v>1</v>
       </c>
-      <c r="Z184" s="96"/>
-      <c r="AA184" s="98"/>
-      <c r="AB184" s="98"/>
+      <c r="Z184" s="97"/>
+      <c r="AA184" s="99"/>
+      <c r="AB184" s="99"/>
     </row>
     <row r="185" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
@@ -16482,9 +16491,9 @@
       <c r="Y185" s="50">
         <v>1</v>
       </c>
-      <c r="Z185" s="96"/>
-      <c r="AA185" s="98"/>
-      <c r="AB185" s="98"/>
+      <c r="Z185" s="97"/>
+      <c r="AA185" s="99"/>
+      <c r="AB185" s="99"/>
     </row>
     <row r="186" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
@@ -16564,9 +16573,9 @@
       <c r="Y186" s="50">
         <v>1</v>
       </c>
-      <c r="Z186" s="96"/>
-      <c r="AA186" s="98"/>
-      <c r="AB186" s="98"/>
+      <c r="Z186" s="97"/>
+      <c r="AA186" s="99"/>
+      <c r="AB186" s="99"/>
     </row>
     <row r="187" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
@@ -16646,9 +16655,9 @@
       <c r="Y187" s="50">
         <v>1</v>
       </c>
-      <c r="Z187" s="96"/>
-      <c r="AA187" s="98"/>
-      <c r="AB187" s="98"/>
+      <c r="Z187" s="97"/>
+      <c r="AA187" s="99"/>
+      <c r="AB187" s="99"/>
     </row>
     <row r="188" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
@@ -16728,9 +16737,9 @@
       <c r="Y188" s="50">
         <v>1</v>
       </c>
-      <c r="Z188" s="96"/>
-      <c r="AA188" s="98"/>
-      <c r="AB188" s="98"/>
+      <c r="Z188" s="97"/>
+      <c r="AA188" s="99"/>
+      <c r="AB188" s="99"/>
     </row>
     <row r="189" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
@@ -16810,9 +16819,9 @@
       <c r="Y189" s="50">
         <v>1</v>
       </c>
-      <c r="Z189" s="96"/>
-      <c r="AA189" s="98"/>
-      <c r="AB189" s="98"/>
+      <c r="Z189" s="97"/>
+      <c r="AA189" s="99"/>
+      <c r="AB189" s="99"/>
     </row>
     <row r="190" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
@@ -16892,9 +16901,9 @@
       <c r="Y190" s="50">
         <v>1</v>
       </c>
-      <c r="Z190" s="96"/>
-      <c r="AA190" s="98"/>
-      <c r="AB190" s="98"/>
+      <c r="Z190" s="97"/>
+      <c r="AA190" s="99"/>
+      <c r="AB190" s="99"/>
     </row>
     <row r="191" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
@@ -16974,9 +16983,9 @@
       <c r="Y191" s="50">
         <v>1</v>
       </c>
-      <c r="Z191" s="96"/>
-      <c r="AA191" s="98"/>
-      <c r="AB191" s="98"/>
+      <c r="Z191" s="97"/>
+      <c r="AA191" s="99"/>
+      <c r="AB191" s="99"/>
     </row>
     <row r="192" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
@@ -17056,9 +17065,9 @@
       <c r="Y192" s="50">
         <v>1</v>
       </c>
-      <c r="Z192" s="96"/>
-      <c r="AA192" s="98"/>
-      <c r="AB192" s="98"/>
+      <c r="Z192" s="97"/>
+      <c r="AA192" s="99"/>
+      <c r="AB192" s="99"/>
     </row>
     <row r="193" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A193" s="27">
@@ -17138,9 +17147,9 @@
       <c r="Y193" s="57">
         <v>1</v>
       </c>
-      <c r="Z193" s="96"/>
-      <c r="AA193" s="98"/>
-      <c r="AB193" s="98"/>
+      <c r="Z193" s="97"/>
+      <c r="AA193" s="99"/>
+      <c r="AB193" s="99"/>
     </row>
     <row r="194" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
@@ -17220,11 +17229,11 @@
       <c r="Y194" s="50">
         <v>1</v>
       </c>
-      <c r="Z194" s="96" t="s">
+      <c r="Z194" s="97" t="s">
         <v>84</v>
       </c>
-      <c r="AA194" s="98"/>
-      <c r="AB194" s="98"/>
+      <c r="AA194" s="99"/>
+      <c r="AB194" s="99"/>
     </row>
     <row r="195" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
@@ -17304,11 +17313,11 @@
       <c r="Y195" s="50">
         <v>1</v>
       </c>
-      <c r="Z195" s="96" t="s">
+      <c r="Z195" s="97" t="s">
         <v>85</v>
       </c>
-      <c r="AA195" s="98"/>
-      <c r="AB195" s="98"/>
+      <c r="AA195" s="99"/>
+      <c r="AB195" s="99"/>
     </row>
     <row r="196" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
@@ -17388,11 +17397,11 @@
       <c r="Y196" s="50">
         <v>1</v>
       </c>
-      <c r="Z196" s="96" t="s">
+      <c r="Z196" s="97" t="s">
         <v>86</v>
       </c>
-      <c r="AA196" s="98"/>
-      <c r="AB196" s="98"/>
+      <c r="AA196" s="99"/>
+      <c r="AB196" s="99"/>
     </row>
     <row r="197" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
@@ -17472,11 +17481,11 @@
       <c r="Y197" s="50">
         <v>1</v>
       </c>
-      <c r="Z197" s="96" t="s">
+      <c r="Z197" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="AA197" s="98"/>
-      <c r="AB197" s="98"/>
+      <c r="AA197" s="99"/>
+      <c r="AB197" s="99"/>
     </row>
     <row r="198" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
@@ -17556,11 +17565,11 @@
       <c r="Y198" s="50">
         <v>1</v>
       </c>
-      <c r="Z198" s="96" t="s">
+      <c r="Z198" s="97" t="s">
         <v>84</v>
       </c>
-      <c r="AA198" s="98"/>
-      <c r="AB198" s="98"/>
+      <c r="AA198" s="99"/>
+      <c r="AB198" s="99"/>
     </row>
     <row r="199" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
@@ -17640,11 +17649,11 @@
       <c r="Y199" s="50">
         <v>1</v>
       </c>
-      <c r="Z199" s="96" t="s">
+      <c r="Z199" s="97" t="s">
         <v>85</v>
       </c>
-      <c r="AA199" s="98"/>
-      <c r="AB199" s="98"/>
+      <c r="AA199" s="99"/>
+      <c r="AB199" s="99"/>
     </row>
     <row r="200" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A200" s="27">
@@ -17724,11 +17733,11 @@
       <c r="Y200" s="57">
         <v>1</v>
       </c>
-      <c r="Z200" s="96" t="s">
+      <c r="Z200" s="97" t="s">
         <v>85</v>
       </c>
-      <c r="AA200" s="98"/>
-      <c r="AB200" s="98"/>
+      <c r="AA200" s="99"/>
+      <c r="AB200" s="99"/>
     </row>
     <row r="201" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A201" s="27">
@@ -17807,11 +17816,11 @@
       <c r="Y201" s="57">
         <v>1</v>
       </c>
-      <c r="Z201" s="96" t="s">
+      <c r="Z201" s="97" t="s">
         <v>88</v>
       </c>
-      <c r="AA201" s="98"/>
-      <c r="AB201" s="98"/>
+      <c r="AA201" s="99"/>
+      <c r="AB201" s="99"/>
     </row>
     <row r="202" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A202" s="27">
@@ -17890,11 +17899,11 @@
       <c r="Y202" s="57">
         <v>1</v>
       </c>
-      <c r="Z202" s="96" t="s">
+      <c r="Z202" s="97" t="s">
         <v>89</v>
       </c>
-      <c r="AA202" s="98"/>
-      <c r="AB202" s="98"/>
+      <c r="AA202" s="99"/>
+      <c r="AB202" s="99"/>
     </row>
     <row r="203" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A203" s="43">
@@ -17973,11 +17982,11 @@
       <c r="Y203" s="40">
         <v>1</v>
       </c>
-      <c r="Z203" s="96" t="s">
+      <c r="Z203" s="97" t="s">
         <v>90</v>
       </c>
-      <c r="AA203" s="98"/>
-      <c r="AB203" s="98"/>
+      <c r="AA203" s="99"/>
+      <c r="AB203" s="99"/>
     </row>
     <row r="204" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A204" s="23">
@@ -18056,11 +18065,11 @@
       <c r="Y204" s="50">
         <v>1</v>
       </c>
-      <c r="Z204" s="96" t="s">
+      <c r="Z204" s="97" t="s">
         <v>91</v>
       </c>
-      <c r="AA204" s="98"/>
-      <c r="AB204" s="98"/>
+      <c r="AA204" s="99"/>
+      <c r="AB204" s="99"/>
     </row>
     <row r="205" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="23">
@@ -18139,11 +18148,11 @@
       <c r="Y205" s="50">
         <v>1</v>
       </c>
-      <c r="Z205" s="96" t="s">
+      <c r="Z205" s="97" t="s">
         <v>92</v>
       </c>
-      <c r="AA205" s="98"/>
-      <c r="AB205" s="98"/>
+      <c r="AA205" s="99"/>
+      <c r="AB205" s="99"/>
     </row>
     <row r="206" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="43">
@@ -18221,11 +18230,11 @@
       <c r="Y206" s="40">
         <v>1</v>
       </c>
-      <c r="Z206" s="96" t="s">
+      <c r="Z206" s="97" t="s">
         <v>94</v>
       </c>
-      <c r="AA206" s="97"/>
-      <c r="AB206" s="97"/>
+      <c r="AA206" s="98"/>
+      <c r="AB206" s="98"/>
     </row>
     <row r="207" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
@@ -18303,9 +18312,9 @@
       <c r="Y207" s="50">
         <v>1</v>
       </c>
-      <c r="Z207" s="96"/>
-      <c r="AA207" s="97"/>
-      <c r="AB207" s="97"/>
+      <c r="Z207" s="97"/>
+      <c r="AA207" s="98"/>
+      <c r="AB207" s="98"/>
     </row>
     <row r="208" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
@@ -18383,9 +18392,9 @@
       <c r="Y208" s="50">
         <v>1</v>
       </c>
-      <c r="Z208" s="96"/>
-      <c r="AA208" s="97"/>
-      <c r="AB208" s="97"/>
+      <c r="Z208" s="97"/>
+      <c r="AA208" s="98"/>
+      <c r="AB208" s="98"/>
     </row>
     <row r="209" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
@@ -18463,9 +18472,9 @@
       <c r="Y209" s="50">
         <v>1</v>
       </c>
-      <c r="Z209" s="96"/>
-      <c r="AA209" s="97"/>
-      <c r="AB209" s="97"/>
+      <c r="Z209" s="97"/>
+      <c r="AA209" s="98"/>
+      <c r="AB209" s="98"/>
     </row>
     <row r="210" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
@@ -18543,9 +18552,9 @@
       <c r="Y210" s="50">
         <v>1</v>
       </c>
-      <c r="Z210" s="96"/>
-      <c r="AA210" s="97"/>
-      <c r="AB210" s="97"/>
+      <c r="Z210" s="97"/>
+      <c r="AA210" s="98"/>
+      <c r="AB210" s="98"/>
     </row>
     <row r="211" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
@@ -18623,9 +18632,9 @@
       <c r="Y211" s="50">
         <v>1</v>
       </c>
-      <c r="Z211" s="96"/>
-      <c r="AA211" s="97"/>
-      <c r="AB211" s="97"/>
+      <c r="Z211" s="97"/>
+      <c r="AA211" s="98"/>
+      <c r="AB211" s="98"/>
     </row>
     <row r="212" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
@@ -18703,9 +18712,9 @@
       <c r="Y212" s="50">
         <v>1</v>
       </c>
-      <c r="Z212" s="96"/>
-      <c r="AA212" s="97"/>
-      <c r="AB212" s="97"/>
+      <c r="Z212" s="97"/>
+      <c r="AA212" s="98"/>
+      <c r="AB212" s="98"/>
     </row>
     <row r="213" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
@@ -18783,9 +18792,9 @@
       <c r="Y213" s="50">
         <v>1</v>
       </c>
-      <c r="Z213" s="96"/>
-      <c r="AA213" s="97"/>
-      <c r="AB213" s="97"/>
+      <c r="Z213" s="97"/>
+      <c r="AA213" s="98"/>
+      <c r="AB213" s="98"/>
     </row>
     <row r="214" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
@@ -18863,9 +18872,9 @@
       <c r="Y214" s="50">
         <v>1</v>
       </c>
-      <c r="Z214" s="96"/>
-      <c r="AA214" s="97"/>
-      <c r="AB214" s="97"/>
+      <c r="Z214" s="97"/>
+      <c r="AA214" s="98"/>
+      <c r="AB214" s="98"/>
     </row>
     <row r="215" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
@@ -18943,9 +18952,9 @@
       <c r="Y215" s="50">
         <v>1</v>
       </c>
-      <c r="Z215" s="96"/>
-      <c r="AA215" s="97"/>
-      <c r="AB215" s="97"/>
+      <c r="Z215" s="97"/>
+      <c r="AA215" s="98"/>
+      <c r="AB215" s="98"/>
     </row>
     <row r="216" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
@@ -19023,9 +19032,9 @@
       <c r="Y216" s="50">
         <v>1</v>
       </c>
-      <c r="Z216" s="96"/>
-      <c r="AA216" s="97"/>
-      <c r="AB216" s="97"/>
+      <c r="Z216" s="97"/>
+      <c r="AA216" s="98"/>
+      <c r="AB216" s="98"/>
     </row>
     <row r="217" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
@@ -19103,9 +19112,9 @@
       <c r="Y217" s="50">
         <v>1</v>
       </c>
-      <c r="Z217" s="96"/>
-      <c r="AA217" s="97"/>
-      <c r="AB217" s="97"/>
+      <c r="Z217" s="97"/>
+      <c r="AA217" s="98"/>
+      <c r="AB217" s="98"/>
     </row>
     <row r="218" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
@@ -19183,9 +19192,9 @@
       <c r="Y218" s="50">
         <v>1</v>
       </c>
-      <c r="Z218" s="96"/>
-      <c r="AA218" s="97"/>
-      <c r="AB218" s="97"/>
+      <c r="Z218" s="97"/>
+      <c r="AA218" s="98"/>
+      <c r="AB218" s="98"/>
     </row>
     <row r="219" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
@@ -19263,9 +19272,9 @@
       <c r="Y219" s="50">
         <v>1</v>
       </c>
-      <c r="Z219" s="96"/>
-      <c r="AA219" s="97"/>
-      <c r="AB219" s="97"/>
+      <c r="Z219" s="97"/>
+      <c r="AA219" s="98"/>
+      <c r="AB219" s="98"/>
     </row>
     <row r="220" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
@@ -19343,9 +19352,9 @@
       <c r="Y220" s="50">
         <v>1</v>
       </c>
-      <c r="Z220" s="96"/>
-      <c r="AA220" s="97"/>
-      <c r="AB220" s="97"/>
+      <c r="Z220" s="97"/>
+      <c r="AA220" s="98"/>
+      <c r="AB220" s="98"/>
     </row>
     <row r="221" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A221" s="43">
@@ -19423,11 +19432,11 @@
       <c r="Y221" s="40">
         <v>1</v>
       </c>
-      <c r="Z221" s="96" t="s">
+      <c r="Z221" s="97" t="s">
         <v>95</v>
       </c>
-      <c r="AA221" s="98"/>
-      <c r="AB221" s="98"/>
+      <c r="AA221" s="99"/>
+      <c r="AB221" s="99"/>
     </row>
     <row r="222" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
@@ -19505,9 +19514,9 @@
       <c r="Y222" s="50">
         <v>1</v>
       </c>
-      <c r="Z222" s="96"/>
-      <c r="AA222" s="98"/>
-      <c r="AB222" s="98"/>
+      <c r="Z222" s="97"/>
+      <c r="AA222" s="99"/>
+      <c r="AB222" s="99"/>
     </row>
     <row r="223" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A223" s="43">
@@ -19585,11 +19594,11 @@
       <c r="Y223" s="40">
         <v>1</v>
       </c>
-      <c r="Z223" s="96" t="s">
+      <c r="Z223" s="97" t="s">
         <v>96</v>
       </c>
-      <c r="AA223" s="98"/>
-      <c r="AB223" s="98"/>
+      <c r="AA223" s="99"/>
+      <c r="AB223" s="99"/>
     </row>
     <row r="224" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
@@ -19667,9 +19676,9 @@
       <c r="Y224" s="50">
         <v>1</v>
       </c>
-      <c r="Z224" s="96"/>
-      <c r="AA224" s="98"/>
-      <c r="AB224" s="98"/>
+      <c r="Z224" s="97"/>
+      <c r="AA224" s="99"/>
+      <c r="AB224" s="99"/>
     </row>
     <row r="225" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A225" s="43">
@@ -19747,11 +19756,11 @@
       <c r="Y225" s="40">
         <v>1</v>
       </c>
-      <c r="Z225" s="96" t="s">
+      <c r="Z225" s="97" t="s">
         <v>97</v>
       </c>
-      <c r="AA225" s="98"/>
-      <c r="AB225" s="98"/>
+      <c r="AA225" s="99"/>
+      <c r="AB225" s="99"/>
     </row>
     <row r="226" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
@@ -19830,9 +19839,9 @@
       <c r="Y226" s="50">
         <v>1</v>
       </c>
-      <c r="Z226" s="96"/>
-      <c r="AA226" s="98"/>
-      <c r="AB226" s="98"/>
+      <c r="Z226" s="97"/>
+      <c r="AA226" s="99"/>
+      <c r="AB226" s="99"/>
     </row>
     <row r="227" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
@@ -19911,9 +19920,9 @@
       <c r="Y227" s="50">
         <v>1</v>
       </c>
-      <c r="Z227" s="96"/>
-      <c r="AA227" s="98"/>
-      <c r="AB227" s="98"/>
+      <c r="Z227" s="97"/>
+      <c r="AA227" s="99"/>
+      <c r="AB227" s="99"/>
     </row>
     <row r="228" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
@@ -19992,9 +20001,9 @@
       <c r="Y228" s="50">
         <v>1</v>
       </c>
-      <c r="Z228" s="96"/>
-      <c r="AA228" s="98"/>
-      <c r="AB228" s="98"/>
+      <c r="Z228" s="97"/>
+      <c r="AA228" s="99"/>
+      <c r="AB228" s="99"/>
     </row>
     <row r="229" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
@@ -20073,9 +20082,9 @@
       <c r="Y229" s="50">
         <v>1</v>
       </c>
-      <c r="Z229" s="96"/>
-      <c r="AA229" s="98"/>
-      <c r="AB229" s="98"/>
+      <c r="Z229" s="97"/>
+      <c r="AA229" s="99"/>
+      <c r="AB229" s="99"/>
     </row>
     <row r="230" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
@@ -20154,9 +20163,9 @@
       <c r="Y230" s="50">
         <v>1</v>
       </c>
-      <c r="Z230" s="96"/>
-      <c r="AA230" s="98"/>
-      <c r="AB230" s="98"/>
+      <c r="Z230" s="97"/>
+      <c r="AA230" s="99"/>
+      <c r="AB230" s="99"/>
     </row>
     <row r="231" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
@@ -20235,9 +20244,9 @@
       <c r="Y231" s="50">
         <v>1</v>
       </c>
-      <c r="Z231" s="96"/>
-      <c r="AA231" s="98"/>
-      <c r="AB231" s="98"/>
+      <c r="Z231" s="97"/>
+      <c r="AA231" s="99"/>
+      <c r="AB231" s="99"/>
     </row>
     <row r="232" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
@@ -20316,9 +20325,9 @@
       <c r="Y232" s="50">
         <v>1</v>
       </c>
-      <c r="Z232" s="96"/>
-      <c r="AA232" s="98"/>
-      <c r="AB232" s="98"/>
+      <c r="Z232" s="97"/>
+      <c r="AA232" s="99"/>
+      <c r="AB232" s="99"/>
     </row>
     <row r="233" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="43">
@@ -20396,11 +20405,11 @@
       <c r="Y233" s="40">
         <v>1</v>
       </c>
-      <c r="Z233" s="96" t="s">
+      <c r="Z233" s="97" t="s">
         <v>95</v>
       </c>
-      <c r="AA233" s="97"/>
-      <c r="AB233" s="97"/>
+      <c r="AA233" s="98"/>
+      <c r="AB233" s="98"/>
     </row>
     <row r="234" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A234" s="27">
@@ -20478,9 +20487,9 @@
       <c r="Y234" s="57">
         <v>1</v>
       </c>
-      <c r="Z234" s="96"/>
-      <c r="AA234" s="97"/>
-      <c r="AB234" s="97"/>
+      <c r="Z234" s="97"/>
+      <c r="AA234" s="98"/>
+      <c r="AB234" s="98"/>
     </row>
     <row r="235" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
@@ -20560,11 +20569,11 @@
       <c r="Y235" s="50">
         <v>1</v>
       </c>
-      <c r="Z235" s="96" t="s">
+      <c r="Z235" s="97" t="s">
         <v>98</v>
       </c>
-      <c r="AA235" s="98"/>
-      <c r="AB235" s="98"/>
+      <c r="AA235" s="99"/>
+      <c r="AB235" s="99"/>
     </row>
     <row r="236" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
@@ -20644,9 +20653,9 @@
       <c r="Y236" s="50">
         <v>1</v>
       </c>
-      <c r="Z236" s="96"/>
-      <c r="AA236" s="98"/>
-      <c r="AB236" s="98"/>
+      <c r="Z236" s="97"/>
+      <c r="AA236" s="99"/>
+      <c r="AB236" s="99"/>
     </row>
     <row r="237" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
@@ -20726,9 +20735,9 @@
       <c r="Y237" s="50">
         <v>1</v>
       </c>
-      <c r="Z237" s="96"/>
-      <c r="AA237" s="98"/>
-      <c r="AB237" s="98"/>
+      <c r="Z237" s="97"/>
+      <c r="AA237" s="99"/>
+      <c r="AB237" s="99"/>
     </row>
     <row r="238" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A238" s="43">
@@ -20806,11 +20815,11 @@
       <c r="Y238" s="40">
         <v>1</v>
       </c>
-      <c r="Z238" s="96" t="s">
+      <c r="Z238" s="97" t="s">
         <v>99</v>
       </c>
-      <c r="AA238" s="98"/>
-      <c r="AB238" s="98"/>
+      <c r="AA238" s="99"/>
+      <c r="AB238" s="99"/>
     </row>
     <row r="239" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
@@ -20888,9 +20897,9 @@
       <c r="Y239" s="50">
         <v>1</v>
       </c>
-      <c r="Z239" s="96"/>
-      <c r="AA239" s="98"/>
-      <c r="AB239" s="98"/>
+      <c r="Z239" s="97"/>
+      <c r="AA239" s="99"/>
+      <c r="AB239" s="99"/>
     </row>
     <row r="240" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A240" s="43">
@@ -20968,11 +20977,11 @@
       <c r="Y240" s="40">
         <v>1</v>
       </c>
-      <c r="Z240" s="96" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA240" s="98"/>
-      <c r="AB240" s="98"/>
+      <c r="Z240" s="97" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA240" s="99"/>
+      <c r="AB240" s="99"/>
     </row>
     <row r="241" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
@@ -21051,9 +21060,9 @@
       <c r="Y241" s="50">
         <v>1</v>
       </c>
-      <c r="Z241" s="96"/>
-      <c r="AA241" s="98"/>
-      <c r="AB241" s="98"/>
+      <c r="Z241" s="97"/>
+      <c r="AA241" s="99"/>
+      <c r="AB241" s="99"/>
     </row>
     <row r="242" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
@@ -21132,9 +21141,9 @@
       <c r="Y242" s="50">
         <v>1</v>
       </c>
-      <c r="Z242" s="96"/>
-      <c r="AA242" s="98"/>
-      <c r="AB242" s="98"/>
+      <c r="Z242" s="97"/>
+      <c r="AA242" s="99"/>
+      <c r="AB242" s="99"/>
     </row>
     <row r="243" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
@@ -21213,9 +21222,9 @@
       <c r="Y243" s="50">
         <v>1</v>
       </c>
-      <c r="Z243" s="96"/>
-      <c r="AA243" s="98"/>
-      <c r="AB243" s="98"/>
+      <c r="Z243" s="97"/>
+      <c r="AA243" s="99"/>
+      <c r="AB243" s="99"/>
     </row>
     <row r="244" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
@@ -21294,9 +21303,9 @@
       <c r="Y244" s="50">
         <v>1</v>
       </c>
-      <c r="Z244" s="96"/>
-      <c r="AA244" s="98"/>
-      <c r="AB244" s="98"/>
+      <c r="Z244" s="97"/>
+      <c r="AA244" s="99"/>
+      <c r="AB244" s="99"/>
     </row>
     <row r="245" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
@@ -21375,9 +21384,9 @@
       <c r="Y245" s="50">
         <v>1</v>
       </c>
-      <c r="Z245" s="96"/>
-      <c r="AA245" s="98"/>
-      <c r="AB245" s="98"/>
+      <c r="Z245" s="97"/>
+      <c r="AA245" s="99"/>
+      <c r="AB245" s="99"/>
     </row>
     <row r="246" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
@@ -21456,9 +21465,9 @@
       <c r="Y246" s="50">
         <v>1</v>
       </c>
-      <c r="Z246" s="96"/>
-      <c r="AA246" s="98"/>
-      <c r="AB246" s="98"/>
+      <c r="Z246" s="97"/>
+      <c r="AA246" s="99"/>
+      <c r="AB246" s="99"/>
     </row>
     <row r="247" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
@@ -21537,9 +21546,9 @@
       <c r="Y247" s="50">
         <v>1</v>
       </c>
-      <c r="Z247" s="96"/>
-      <c r="AA247" s="98"/>
-      <c r="AB247" s="98"/>
+      <c r="Z247" s="97"/>
+      <c r="AA247" s="99"/>
+      <c r="AB247" s="99"/>
     </row>
     <row r="248" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
@@ -21618,9 +21627,9 @@
       <c r="Y248" s="50">
         <v>1</v>
       </c>
-      <c r="Z248" s="96"/>
-      <c r="AA248" s="98"/>
-      <c r="AB248" s="98"/>
+      <c r="Z248" s="97"/>
+      <c r="AA248" s="99"/>
+      <c r="AB248" s="99"/>
     </row>
     <row r="249" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
@@ -21699,9 +21708,9 @@
       <c r="Y249" s="50">
         <v>1</v>
       </c>
-      <c r="Z249" s="96"/>
-      <c r="AA249" s="98"/>
-      <c r="AB249" s="98"/>
+      <c r="Z249" s="97"/>
+      <c r="AA249" s="99"/>
+      <c r="AB249" s="99"/>
     </row>
     <row r="250" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
@@ -21780,9 +21789,9 @@
       <c r="Y250" s="50">
         <v>1</v>
       </c>
-      <c r="Z250" s="96"/>
-      <c r="AA250" s="98"/>
-      <c r="AB250" s="98"/>
+      <c r="Z250" s="97"/>
+      <c r="AA250" s="99"/>
+      <c r="AB250" s="99"/>
     </row>
     <row r="251" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
@@ -21861,9 +21870,9 @@
       <c r="Y251" s="50">
         <v>1</v>
       </c>
-      <c r="Z251" s="96"/>
-      <c r="AA251" s="98"/>
-      <c r="AB251" s="98"/>
+      <c r="Z251" s="97"/>
+      <c r="AA251" s="99"/>
+      <c r="AB251" s="99"/>
     </row>
     <row r="252" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A252" s="43">
@@ -21942,11 +21951,11 @@
       <c r="Y252" s="40">
         <v>1</v>
       </c>
-      <c r="Z252" s="96" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA252" s="97"/>
-      <c r="AB252" s="97"/>
+      <c r="Z252" s="97" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA252" s="98"/>
+      <c r="AB252" s="98"/>
     </row>
     <row r="253" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
@@ -22025,9 +22034,9 @@
       <c r="Y253" s="50">
         <v>1</v>
       </c>
-      <c r="Z253" s="96"/>
-      <c r="AA253" s="97"/>
-      <c r="AB253" s="97"/>
+      <c r="Z253" s="97"/>
+      <c r="AA253" s="98"/>
+      <c r="AB253" s="98"/>
     </row>
     <row r="254" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
@@ -22106,9 +22115,9 @@
       <c r="Y254" s="50">
         <v>1</v>
       </c>
-      <c r="Z254" s="96"/>
-      <c r="AA254" s="97"/>
-      <c r="AB254" s="97"/>
+      <c r="Z254" s="97"/>
+      <c r="AA254" s="98"/>
+      <c r="AB254" s="98"/>
     </row>
     <row r="255" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
@@ -22187,9 +22196,9 @@
       <c r="Y255" s="50">
         <v>1</v>
       </c>
-      <c r="Z255" s="96"/>
-      <c r="AA255" s="97"/>
-      <c r="AB255" s="97"/>
+      <c r="Z255" s="97"/>
+      <c r="AA255" s="98"/>
+      <c r="AB255" s="98"/>
     </row>
     <row r="256" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
@@ -22268,9 +22277,9 @@
       <c r="Y256" s="50">
         <v>1</v>
       </c>
-      <c r="Z256" s="96"/>
-      <c r="AA256" s="97"/>
-      <c r="AB256" s="97"/>
+      <c r="Z256" s="97"/>
+      <c r="AA256" s="98"/>
+      <c r="AB256" s="98"/>
     </row>
     <row r="257" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
@@ -22349,9 +22358,9 @@
       <c r="Y257" s="50">
         <v>1</v>
       </c>
-      <c r="Z257" s="96"/>
-      <c r="AA257" s="97"/>
-      <c r="AB257" s="97"/>
+      <c r="Z257" s="97"/>
+      <c r="AA257" s="98"/>
+      <c r="AB257" s="98"/>
     </row>
     <row r="258" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
@@ -22430,9 +22439,9 @@
       <c r="Y258" s="50">
         <v>1</v>
       </c>
-      <c r="Z258" s="96"/>
-      <c r="AA258" s="97"/>
-      <c r="AB258" s="97"/>
+      <c r="Z258" s="97"/>
+      <c r="AA258" s="98"/>
+      <c r="AB258" s="98"/>
     </row>
     <row r="259" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
@@ -22511,9 +22520,9 @@
       <c r="Y259" s="50">
         <v>1</v>
       </c>
-      <c r="Z259" s="96"/>
-      <c r="AA259" s="97"/>
-      <c r="AB259" s="97"/>
+      <c r="Z259" s="97"/>
+      <c r="AA259" s="98"/>
+      <c r="AB259" s="98"/>
     </row>
     <row r="260" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
@@ -22592,9 +22601,9 @@
       <c r="Y260" s="50">
         <v>1</v>
       </c>
-      <c r="Z260" s="96"/>
-      <c r="AA260" s="97"/>
-      <c r="AB260" s="97"/>
+      <c r="Z260" s="97"/>
+      <c r="AA260" s="98"/>
+      <c r="AB260" s="98"/>
     </row>
     <row r="261" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
@@ -22673,9 +22682,9 @@
       <c r="Y261" s="50">
         <v>1</v>
       </c>
-      <c r="Z261" s="96"/>
-      <c r="AA261" s="97"/>
-      <c r="AB261" s="97"/>
+      <c r="Z261" s="97"/>
+      <c r="AA261" s="98"/>
+      <c r="AB261" s="98"/>
     </row>
     <row r="262" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
@@ -22754,9 +22763,9 @@
       <c r="Y262" s="50">
         <v>1</v>
       </c>
-      <c r="Z262" s="96"/>
-      <c r="AA262" s="97"/>
-      <c r="AB262" s="97"/>
+      <c r="Z262" s="97"/>
+      <c r="AA262" s="98"/>
+      <c r="AB262" s="98"/>
     </row>
     <row r="263" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A263" s="43">
@@ -22835,11 +22844,11 @@
       <c r="Y263" s="40">
         <v>1</v>
       </c>
-      <c r="Z263" s="96" t="s">
+      <c r="Z263" s="97" t="s">
         <v>101</v>
       </c>
-      <c r="AA263" s="97"/>
-      <c r="AB263" s="97"/>
+      <c r="AA263" s="98"/>
+      <c r="AB263" s="98"/>
     </row>
     <row r="264" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
@@ -22918,9 +22927,9 @@
       <c r="Y264" s="50">
         <v>1</v>
       </c>
-      <c r="Z264" s="96"/>
-      <c r="AA264" s="97"/>
-      <c r="AB264" s="97"/>
+      <c r="Z264" s="97"/>
+      <c r="AA264" s="98"/>
+      <c r="AB264" s="98"/>
     </row>
     <row r="265" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A265" s="43">
@@ -22999,11 +23008,11 @@
       <c r="Y265" s="40">
         <v>1</v>
       </c>
-      <c r="Z265" s="96" t="s">
+      <c r="Z265" s="97" t="s">
         <v>102</v>
       </c>
-      <c r="AA265" s="98"/>
-      <c r="AB265" s="98"/>
+      <c r="AA265" s="99"/>
+      <c r="AB265" s="99"/>
     </row>
     <row r="266" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
@@ -23082,9 +23091,9 @@
       <c r="Y266" s="50">
         <v>1</v>
       </c>
-      <c r="Z266" s="96"/>
-      <c r="AA266" s="98"/>
-      <c r="AB266" s="98"/>
+      <c r="Z266" s="97"/>
+      <c r="AA266" s="99"/>
+      <c r="AB266" s="99"/>
     </row>
     <row r="267" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
@@ -23163,9 +23172,9 @@
       <c r="Y267" s="50">
         <v>1</v>
       </c>
-      <c r="Z267" s="96"/>
-      <c r="AA267" s="98"/>
-      <c r="AB267" s="98"/>
+      <c r="Z267" s="97"/>
+      <c r="AA267" s="99"/>
+      <c r="AB267" s="99"/>
     </row>
     <row r="268" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
@@ -23244,9 +23253,9 @@
       <c r="Y268" s="50">
         <v>1</v>
       </c>
-      <c r="Z268" s="96"/>
-      <c r="AA268" s="98"/>
-      <c r="AB268" s="98"/>
+      <c r="Z268" s="97"/>
+      <c r="AA268" s="99"/>
+      <c r="AB268" s="99"/>
     </row>
     <row r="269" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
@@ -23325,9 +23334,9 @@
       <c r="Y269" s="50">
         <v>1</v>
       </c>
-      <c r="Z269" s="96"/>
-      <c r="AA269" s="98"/>
-      <c r="AB269" s="98"/>
+      <c r="Z269" s="97"/>
+      <c r="AA269" s="99"/>
+      <c r="AB269" s="99"/>
     </row>
     <row r="270" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
@@ -23406,9 +23415,9 @@
       <c r="Y270" s="50">
         <v>1</v>
       </c>
-      <c r="Z270" s="96"/>
-      <c r="AA270" s="98"/>
-      <c r="AB270" s="98"/>
+      <c r="Z270" s="97"/>
+      <c r="AA270" s="99"/>
+      <c r="AB270" s="99"/>
     </row>
     <row r="271" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
@@ -23487,9 +23496,9 @@
       <c r="Y271" s="50">
         <v>1</v>
       </c>
-      <c r="Z271" s="96"/>
-      <c r="AA271" s="98"/>
-      <c r="AB271" s="98"/>
+      <c r="Z271" s="97"/>
+      <c r="AA271" s="99"/>
+      <c r="AB271" s="99"/>
     </row>
     <row r="272" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
@@ -23568,9 +23577,9 @@
       <c r="Y272" s="50">
         <v>1</v>
       </c>
-      <c r="Z272" s="96"/>
-      <c r="AA272" s="98"/>
-      <c r="AB272" s="98"/>
+      <c r="Z272" s="97"/>
+      <c r="AA272" s="99"/>
+      <c r="AB272" s="99"/>
     </row>
     <row r="273" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
@@ -23649,9 +23658,9 @@
       <c r="Y273" s="50">
         <v>1</v>
       </c>
-      <c r="Z273" s="96"/>
-      <c r="AA273" s="98"/>
-      <c r="AB273" s="98"/>
+      <c r="Z273" s="97"/>
+      <c r="AA273" s="99"/>
+      <c r="AB273" s="99"/>
     </row>
     <row r="274" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
@@ -23730,9 +23739,9 @@
       <c r="Y274" s="50">
         <v>1</v>
       </c>
-      <c r="Z274" s="96"/>
-      <c r="AA274" s="98"/>
-      <c r="AB274" s="98"/>
+      <c r="Z274" s="97"/>
+      <c r="AA274" s="99"/>
+      <c r="AB274" s="99"/>
     </row>
     <row r="275" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A275" s="27">
@@ -23811,9 +23820,9 @@
       <c r="Y275" s="57">
         <v>1</v>
       </c>
-      <c r="Z275" s="96"/>
-      <c r="AA275" s="98"/>
-      <c r="AB275" s="98"/>
+      <c r="Z275" s="97"/>
+      <c r="AA275" s="99"/>
+      <c r="AB275" s="99"/>
     </row>
     <row r="276" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="43">
@@ -23892,11 +23901,11 @@
       <c r="Y276" s="40">
         <v>1</v>
       </c>
-      <c r="Z276" s="96" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA276" s="97"/>
-      <c r="AB276" s="97"/>
+      <c r="Z276" s="97" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA276" s="98"/>
+      <c r="AB276" s="98"/>
     </row>
     <row r="277" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
@@ -23974,9 +23983,9 @@
       <c r="Y277" s="50">
         <v>1</v>
       </c>
-      <c r="Z277" s="96"/>
-      <c r="AA277" s="97"/>
-      <c r="AB277" s="97"/>
+      <c r="Z277" s="97"/>
+      <c r="AA277" s="98"/>
+      <c r="AB277" s="98"/>
     </row>
     <row r="278" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
@@ -24054,9 +24063,9 @@
       <c r="Y278" s="50">
         <v>1</v>
       </c>
-      <c r="Z278" s="96"/>
-      <c r="AA278" s="97"/>
-      <c r="AB278" s="97"/>
+      <c r="Z278" s="97"/>
+      <c r="AA278" s="98"/>
+      <c r="AB278" s="98"/>
     </row>
     <row r="279" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
@@ -24134,9 +24143,9 @@
       <c r="Y279" s="50">
         <v>1</v>
       </c>
-      <c r="Z279" s="96"/>
-      <c r="AA279" s="97"/>
-      <c r="AB279" s="97"/>
+      <c r="Z279" s="97"/>
+      <c r="AA279" s="98"/>
+      <c r="AB279" s="98"/>
     </row>
     <row r="280" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
@@ -24214,9 +24223,9 @@
       <c r="Y280" s="50">
         <v>1</v>
       </c>
-      <c r="Z280" s="96"/>
-      <c r="AA280" s="97"/>
-      <c r="AB280" s="97"/>
+      <c r="Z280" s="97"/>
+      <c r="AA280" s="98"/>
+      <c r="AB280" s="98"/>
     </row>
     <row r="281" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
@@ -24294,9 +24303,9 @@
       <c r="Y281" s="50">
         <v>1</v>
       </c>
-      <c r="Z281" s="96"/>
-      <c r="AA281" s="97"/>
-      <c r="AB281" s="97"/>
+      <c r="Z281" s="97"/>
+      <c r="AA281" s="98"/>
+      <c r="AB281" s="98"/>
     </row>
     <row r="282" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
@@ -24374,9 +24383,9 @@
       <c r="Y282" s="50">
         <v>1</v>
       </c>
-      <c r="Z282" s="96"/>
-      <c r="AA282" s="97"/>
-      <c r="AB282" s="97"/>
+      <c r="Z282" s="97"/>
+      <c r="AA282" s="98"/>
+      <c r="AB282" s="98"/>
     </row>
     <row r="283" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
@@ -24454,9 +24463,9 @@
       <c r="Y283" s="50">
         <v>1</v>
       </c>
-      <c r="Z283" s="96"/>
-      <c r="AA283" s="97"/>
-      <c r="AB283" s="97"/>
+      <c r="Z283" s="97"/>
+      <c r="AA283" s="98"/>
+      <c r="AB283" s="98"/>
     </row>
     <row r="284" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
@@ -24534,9 +24543,9 @@
       <c r="Y284" s="50">
         <v>1</v>
       </c>
-      <c r="Z284" s="96"/>
-      <c r="AA284" s="97"/>
-      <c r="AB284" s="97"/>
+      <c r="Z284" s="97"/>
+      <c r="AA284" s="98"/>
+      <c r="AB284" s="98"/>
     </row>
     <row r="285" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A285" s="43">
@@ -24615,9 +24624,9 @@
       <c r="Y285" s="40">
         <v>1</v>
       </c>
-      <c r="Z285" s="96"/>
-      <c r="AA285" s="97"/>
-      <c r="AB285" s="97"/>
+      <c r="Z285" s="97"/>
+      <c r="AA285" s="98"/>
+      <c r="AB285" s="98"/>
     </row>
     <row r="286" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
@@ -24697,9 +24706,9 @@
       <c r="Y286" s="50">
         <v>1</v>
       </c>
-      <c r="Z286" s="96"/>
-      <c r="AA286" s="97"/>
-      <c r="AB286" s="97"/>
+      <c r="Z286" s="97"/>
+      <c r="AA286" s="98"/>
+      <c r="AB286" s="98"/>
     </row>
     <row r="287" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A287" s="27">
@@ -24779,9 +24788,9 @@
       <c r="Y287" s="57">
         <v>1</v>
       </c>
-      <c r="Z287" s="96"/>
-      <c r="AA287" s="97"/>
-      <c r="AB287" s="97"/>
+      <c r="Z287" s="97"/>
+      <c r="AA287" s="98"/>
+      <c r="AB287" s="98"/>
     </row>
     <row r="288" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
@@ -24859,11 +24868,11 @@
       <c r="Y288" s="50">
         <v>1</v>
       </c>
-      <c r="Z288" s="96" t="s">
+      <c r="Z288" s="97" t="s">
         <v>101</v>
       </c>
-      <c r="AA288" s="97"/>
-      <c r="AB288" s="97"/>
+      <c r="AA288" s="98"/>
+      <c r="AB288" s="98"/>
     </row>
     <row r="289" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A289" s="27">
@@ -24942,9 +24951,9 @@
       <c r="Y289" s="57">
         <v>1</v>
       </c>
-      <c r="Z289" s="96"/>
-      <c r="AA289" s="97"/>
-      <c r="AB289" s="97"/>
+      <c r="Z289" s="97"/>
+      <c r="AA289" s="98"/>
+      <c r="AB289" s="98"/>
     </row>
     <row r="290" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
@@ -25024,11 +25033,11 @@
       <c r="Y290" s="50">
         <v>1</v>
       </c>
-      <c r="Z290" s="96" t="s">
+      <c r="Z290" s="97" t="s">
         <v>103</v>
       </c>
-      <c r="AA290" s="98"/>
-      <c r="AB290" s="98"/>
+      <c r="AA290" s="99"/>
+      <c r="AB290" s="99"/>
     </row>
     <row r="291" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
@@ -25108,9 +25117,9 @@
       <c r="Y291" s="50">
         <v>1</v>
       </c>
-      <c r="Z291" s="96"/>
-      <c r="AA291" s="98"/>
-      <c r="AB291" s="98"/>
+      <c r="Z291" s="97"/>
+      <c r="AA291" s="99"/>
+      <c r="AB291" s="99"/>
     </row>
     <row r="292" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
@@ -25190,9 +25199,9 @@
       <c r="Y292" s="50">
         <v>1</v>
       </c>
-      <c r="Z292" s="96"/>
-      <c r="AA292" s="98"/>
-      <c r="AB292" s="98"/>
+      <c r="Z292" s="97"/>
+      <c r="AA292" s="99"/>
+      <c r="AB292" s="99"/>
     </row>
     <row r="293" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A293" s="43">
@@ -25271,11 +25280,11 @@
       <c r="Y293" s="40">
         <v>1</v>
       </c>
-      <c r="Z293" s="96" t="s">
+      <c r="Z293" s="97" t="s">
         <v>104</v>
       </c>
-      <c r="AA293" s="98"/>
-      <c r="AB293" s="98"/>
+      <c r="AA293" s="99"/>
+      <c r="AB293" s="99"/>
     </row>
     <row r="294" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A294" s="43">
@@ -25354,11 +25363,11 @@
       <c r="Y294" s="40">
         <v>1</v>
       </c>
-      <c r="Z294" s="96" t="s">
+      <c r="Z294" s="97" t="s">
         <v>105</v>
       </c>
-      <c r="AA294" s="98"/>
-      <c r="AB294" s="98"/>
+      <c r="AA294" s="99"/>
+      <c r="AB294" s="99"/>
     </row>
     <row r="295" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A295" s="43">
@@ -25437,11 +25446,11 @@
       <c r="Y295" s="40">
         <v>1</v>
       </c>
-      <c r="Z295" s="96" t="s">
+      <c r="Z295" s="97" t="s">
         <v>106</v>
       </c>
-      <c r="AA295" s="98"/>
-      <c r="AB295" s="98"/>
+      <c r="AA295" s="99"/>
+      <c r="AB295" s="99"/>
     </row>
     <row r="296" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A296" s="43">
@@ -25520,11 +25529,11 @@
       <c r="Y296" s="40">
         <v>1</v>
       </c>
-      <c r="Z296" s="111" t="s">
+      <c r="Z296" s="100" t="s">
         <v>106</v>
       </c>
-      <c r="AA296" s="112"/>
-      <c r="AB296" s="112"/>
+      <c r="AA296" s="101"/>
+      <c r="AB296" s="101"/>
     </row>
     <row r="297" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
@@ -25603,9 +25612,9 @@
       <c r="Y297" s="50">
         <v>1</v>
       </c>
-      <c r="Z297" s="111"/>
-      <c r="AA297" s="112"/>
-      <c r="AB297" s="112"/>
+      <c r="Z297" s="100"/>
+      <c r="AA297" s="101"/>
+      <c r="AB297" s="101"/>
     </row>
     <row r="298" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
@@ -25684,9 +25693,9 @@
       <c r="Y298" s="50">
         <v>1</v>
       </c>
-      <c r="Z298" s="111"/>
-      <c r="AA298" s="112"/>
-      <c r="AB298" s="112"/>
+      <c r="Z298" s="100"/>
+      <c r="AA298" s="101"/>
+      <c r="AB298" s="101"/>
     </row>
     <row r="299" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
@@ -25765,9 +25774,9 @@
       <c r="Y299" s="50">
         <v>1</v>
       </c>
-      <c r="Z299" s="111"/>
-      <c r="AA299" s="112"/>
-      <c r="AB299" s="112"/>
+      <c r="Z299" s="100"/>
+      <c r="AA299" s="101"/>
+      <c r="AB299" s="101"/>
     </row>
     <row r="300" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
@@ -25846,9 +25855,9 @@
       <c r="Y300" s="50">
         <v>1</v>
       </c>
-      <c r="Z300" s="111"/>
-      <c r="AA300" s="112"/>
-      <c r="AB300" s="112"/>
+      <c r="Z300" s="100"/>
+      <c r="AA300" s="101"/>
+      <c r="AB300" s="101"/>
     </row>
     <row r="301" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
@@ -25927,9 +25936,9 @@
       <c r="Y301" s="50">
         <v>1</v>
       </c>
-      <c r="Z301" s="111"/>
-      <c r="AA301" s="112"/>
-      <c r="AB301" s="112"/>
+      <c r="Z301" s="100"/>
+      <c r="AA301" s="101"/>
+      <c r="AB301" s="101"/>
     </row>
     <row r="302" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
@@ -26008,9 +26017,9 @@
       <c r="Y302" s="50">
         <v>1</v>
       </c>
-      <c r="Z302" s="111"/>
-      <c r="AA302" s="112"/>
-      <c r="AB302" s="112"/>
+      <c r="Z302" s="100"/>
+      <c r="AA302" s="101"/>
+      <c r="AB302" s="101"/>
     </row>
     <row r="303" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
@@ -26089,9 +26098,9 @@
       <c r="Y303" s="50">
         <v>1</v>
       </c>
-      <c r="Z303" s="111"/>
-      <c r="AA303" s="112"/>
-      <c r="AB303" s="112"/>
+      <c r="Z303" s="100"/>
+      <c r="AA303" s="101"/>
+      <c r="AB303" s="101"/>
     </row>
     <row r="304" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
@@ -26170,9 +26179,9 @@
       <c r="Y304" s="50">
         <v>1</v>
       </c>
-      <c r="Z304" s="111"/>
-      <c r="AA304" s="112"/>
-      <c r="AB304" s="112"/>
+      <c r="Z304" s="100"/>
+      <c r="AA304" s="101"/>
+      <c r="AB304" s="101"/>
     </row>
     <row r="305" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
@@ -26251,9 +26260,9 @@
       <c r="Y305" s="50">
         <v>1</v>
       </c>
-      <c r="Z305" s="111"/>
-      <c r="AA305" s="112"/>
-      <c r="AB305" s="112"/>
+      <c r="Z305" s="100"/>
+      <c r="AA305" s="101"/>
+      <c r="AB305" s="101"/>
     </row>
     <row r="306" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
@@ -26332,9 +26341,9 @@
       <c r="Y306" s="50">
         <v>1</v>
       </c>
-      <c r="Z306" s="111"/>
-      <c r="AA306" s="112"/>
-      <c r="AB306" s="112"/>
+      <c r="Z306" s="100"/>
+      <c r="AA306" s="101"/>
+      <c r="AB306" s="101"/>
     </row>
     <row r="307" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
@@ -26413,9 +26422,9 @@
       <c r="Y307" s="50">
         <v>1</v>
       </c>
-      <c r="Z307" s="111"/>
-      <c r="AA307" s="112"/>
-      <c r="AB307" s="112"/>
+      <c r="Z307" s="100"/>
+      <c r="AA307" s="101"/>
+      <c r="AB307" s="101"/>
     </row>
     <row r="308" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
@@ -26494,9 +26503,9 @@
       <c r="Y308" s="50">
         <v>1</v>
       </c>
-      <c r="Z308" s="111"/>
-      <c r="AA308" s="112"/>
-      <c r="AB308" s="112"/>
+      <c r="Z308" s="100"/>
+      <c r="AA308" s="101"/>
+      <c r="AB308" s="101"/>
     </row>
     <row r="309" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
@@ -26575,9 +26584,9 @@
       <c r="Y309" s="50">
         <v>1</v>
       </c>
-      <c r="Z309" s="111"/>
-      <c r="AA309" s="112"/>
-      <c r="AB309" s="112"/>
+      <c r="Z309" s="100"/>
+      <c r="AA309" s="101"/>
+      <c r="AB309" s="101"/>
     </row>
     <row r="310" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
@@ -26656,9 +26665,9 @@
       <c r="Y310" s="50">
         <v>1</v>
       </c>
-      <c r="Z310" s="111"/>
-      <c r="AA310" s="112"/>
-      <c r="AB310" s="112"/>
+      <c r="Z310" s="100"/>
+      <c r="AA310" s="101"/>
+      <c r="AB310" s="101"/>
     </row>
     <row r="311" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
@@ -26737,9 +26746,9 @@
       <c r="Y311" s="50">
         <v>1</v>
       </c>
-      <c r="Z311" s="111"/>
-      <c r="AA311" s="112"/>
-      <c r="AB311" s="112"/>
+      <c r="Z311" s="100"/>
+      <c r="AA311" s="101"/>
+      <c r="AB311" s="101"/>
     </row>
     <row r="312" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
@@ -26818,9 +26827,9 @@
       <c r="Y312" s="50">
         <v>1</v>
       </c>
-      <c r="Z312" s="111"/>
-      <c r="AA312" s="112"/>
-      <c r="AB312" s="112"/>
+      <c r="Z312" s="100"/>
+      <c r="AA312" s="101"/>
+      <c r="AB312" s="101"/>
     </row>
     <row r="313" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A313" s="95">
@@ -26977,11 +26986,11 @@
       <c r="Y314" s="53">
         <v>1</v>
       </c>
-      <c r="Z314" s="101" t="s">
+      <c r="Z314" s="102" t="s">
         <v>107</v>
       </c>
-      <c r="AA314" s="110"/>
-      <c r="AB314" s="110"/>
+      <c r="AA314" s="103"/>
+      <c r="AB314" s="103"/>
     </row>
     <row r="315" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
@@ -27060,11 +27069,11 @@
       <c r="Y315" s="50">
         <v>1</v>
       </c>
-      <c r="Z315" s="96" t="s">
+      <c r="Z315" s="97" t="s">
         <v>108</v>
       </c>
-      <c r="AA315" s="97"/>
-      <c r="AB315" s="97"/>
+      <c r="AA315" s="98"/>
+      <c r="AB315" s="98"/>
     </row>
     <row r="316" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
@@ -27143,9 +27152,9 @@
       <c r="Y316" s="50">
         <v>1</v>
       </c>
-      <c r="Z316" s="96"/>
-      <c r="AA316" s="97"/>
-      <c r="AB316" s="97"/>
+      <c r="Z316" s="97"/>
+      <c r="AA316" s="98"/>
+      <c r="AB316" s="98"/>
     </row>
     <row r="317" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A317" s="27">
@@ -27224,9 +27233,9 @@
       <c r="Y317" s="57">
         <v>1</v>
       </c>
-      <c r="Z317" s="96"/>
-      <c r="AA317" s="97"/>
-      <c r="AB317" s="97"/>
+      <c r="Z317" s="97"/>
+      <c r="AA317" s="98"/>
+      <c r="AB317" s="98"/>
     </row>
     <row r="318" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
@@ -27305,11 +27314,11 @@
       <c r="Y318" s="50">
         <v>1</v>
       </c>
-      <c r="Z318" s="96" t="s">
+      <c r="Z318" s="97" t="s">
         <v>109</v>
       </c>
-      <c r="AA318" s="98"/>
-      <c r="AB318" s="98"/>
+      <c r="AA318" s="99"/>
+      <c r="AB318" s="99"/>
     </row>
     <row r="319" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
@@ -27388,9 +27397,9 @@
       <c r="Y319" s="50">
         <v>1</v>
       </c>
-      <c r="Z319" s="96"/>
-      <c r="AA319" s="98"/>
-      <c r="AB319" s="98"/>
+      <c r="Z319" s="97"/>
+      <c r="AA319" s="99"/>
+      <c r="AB319" s="99"/>
     </row>
     <row r="320" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
@@ -27469,9 +27478,9 @@
       <c r="Y320" s="50">
         <v>1</v>
       </c>
-      <c r="Z320" s="96"/>
-      <c r="AA320" s="98"/>
-      <c r="AB320" s="98"/>
+      <c r="Z320" s="97"/>
+      <c r="AA320" s="99"/>
+      <c r="AB320" s="99"/>
     </row>
     <row r="321" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
@@ -27550,9 +27559,9 @@
       <c r="Y321" s="50">
         <v>1</v>
       </c>
-      <c r="Z321" s="96"/>
-      <c r="AA321" s="98"/>
-      <c r="AB321" s="98"/>
+      <c r="Z321" s="97"/>
+      <c r="AA321" s="99"/>
+      <c r="AB321" s="99"/>
     </row>
     <row r="322" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
@@ -27631,9 +27640,9 @@
       <c r="Y322" s="50">
         <v>1</v>
       </c>
-      <c r="Z322" s="96"/>
-      <c r="AA322" s="98"/>
-      <c r="AB322" s="98"/>
+      <c r="Z322" s="97"/>
+      <c r="AA322" s="99"/>
+      <c r="AB322" s="99"/>
     </row>
     <row r="323" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
@@ -27712,9 +27721,9 @@
       <c r="Y323" s="50">
         <v>1</v>
       </c>
-      <c r="Z323" s="96"/>
-      <c r="AA323" s="98"/>
-      <c r="AB323" s="98"/>
+      <c r="Z323" s="97"/>
+      <c r="AA323" s="99"/>
+      <c r="AB323" s="99"/>
     </row>
     <row r="324" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
@@ -27793,9 +27802,9 @@
       <c r="Y324" s="50">
         <v>1</v>
       </c>
-      <c r="Z324" s="96"/>
-      <c r="AA324" s="98"/>
-      <c r="AB324" s="98"/>
+      <c r="Z324" s="97"/>
+      <c r="AA324" s="99"/>
+      <c r="AB324" s="99"/>
     </row>
     <row r="325" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
@@ -27874,9 +27883,9 @@
       <c r="Y325" s="50">
         <v>1</v>
       </c>
-      <c r="Z325" s="96"/>
-      <c r="AA325" s="98"/>
-      <c r="AB325" s="98"/>
+      <c r="Z325" s="97"/>
+      <c r="AA325" s="99"/>
+      <c r="AB325" s="99"/>
     </row>
     <row r="326" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="43">
@@ -27956,11 +27965,11 @@
       <c r="Y326" s="40">
         <v>1</v>
       </c>
-      <c r="Z326" s="96" t="s">
+      <c r="Z326" s="97" t="s">
         <v>110</v>
       </c>
-      <c r="AA326" s="97"/>
-      <c r="AB326" s="97"/>
+      <c r="AA326" s="98"/>
+      <c r="AB326" s="98"/>
     </row>
     <row r="327" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
@@ -28040,9 +28049,9 @@
       <c r="Y327" s="50">
         <v>1</v>
       </c>
-      <c r="Z327" s="96"/>
-      <c r="AA327" s="97"/>
-      <c r="AB327" s="97"/>
+      <c r="Z327" s="97"/>
+      <c r="AA327" s="98"/>
+      <c r="AB327" s="98"/>
     </row>
     <row r="328" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
@@ -28122,9 +28131,9 @@
       <c r="Y328" s="50">
         <v>1</v>
       </c>
-      <c r="Z328" s="96"/>
-      <c r="AA328" s="97"/>
-      <c r="AB328" s="97"/>
+      <c r="Z328" s="97"/>
+      <c r="AA328" s="98"/>
+      <c r="AB328" s="98"/>
     </row>
     <row r="329" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
@@ -28204,9 +28213,9 @@
       <c r="Y329" s="50">
         <v>1</v>
       </c>
-      <c r="Z329" s="96"/>
-      <c r="AA329" s="97"/>
-      <c r="AB329" s="97"/>
+      <c r="Z329" s="97"/>
+      <c r="AA329" s="98"/>
+      <c r="AB329" s="98"/>
     </row>
     <row r="330" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
@@ -28286,9 +28295,9 @@
       <c r="Y330" s="50">
         <v>1</v>
       </c>
-      <c r="Z330" s="96"/>
-      <c r="AA330" s="97"/>
-      <c r="AB330" s="97"/>
+      <c r="Z330" s="97"/>
+      <c r="AA330" s="98"/>
+      <c r="AB330" s="98"/>
     </row>
     <row r="331" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
@@ -28368,9 +28377,9 @@
       <c r="Y331" s="50">
         <v>1</v>
       </c>
-      <c r="Z331" s="96"/>
-      <c r="AA331" s="97"/>
-      <c r="AB331" s="97"/>
+      <c r="Z331" s="97"/>
+      <c r="AA331" s="98"/>
+      <c r="AB331" s="98"/>
     </row>
     <row r="332" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
@@ -28450,9 +28459,9 @@
       <c r="Y332" s="50">
         <v>1</v>
       </c>
-      <c r="Z332" s="96"/>
-      <c r="AA332" s="97"/>
-      <c r="AB332" s="97"/>
+      <c r="Z332" s="97"/>
+      <c r="AA332" s="98"/>
+      <c r="AB332" s="98"/>
     </row>
     <row r="333" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
@@ -28532,9 +28541,9 @@
       <c r="Y333" s="50">
         <v>1</v>
       </c>
-      <c r="Z333" s="96"/>
-      <c r="AA333" s="97"/>
-      <c r="AB333" s="97"/>
+      <c r="Z333" s="97"/>
+      <c r="AA333" s="98"/>
+      <c r="AB333" s="98"/>
     </row>
     <row r="334" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
@@ -28614,9 +28623,9 @@
       <c r="Y334" s="50">
         <v>1</v>
       </c>
-      <c r="Z334" s="96"/>
-      <c r="AA334" s="97"/>
-      <c r="AB334" s="97"/>
+      <c r="Z334" s="97"/>
+      <c r="AA334" s="98"/>
+      <c r="AB334" s="98"/>
     </row>
     <row r="335" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
@@ -28696,9 +28705,9 @@
       <c r="Y335" s="50">
         <v>1</v>
       </c>
-      <c r="Z335" s="96"/>
-      <c r="AA335" s="97"/>
-      <c r="AB335" s="97"/>
+      <c r="Z335" s="97"/>
+      <c r="AA335" s="98"/>
+      <c r="AB335" s="98"/>
     </row>
     <row r="336" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
@@ -28778,9 +28787,9 @@
       <c r="Y336" s="50">
         <v>1</v>
       </c>
-      <c r="Z336" s="96"/>
-      <c r="AA336" s="97"/>
-      <c r="AB336" s="97"/>
+      <c r="Z336" s="97"/>
+      <c r="AA336" s="98"/>
+      <c r="AB336" s="98"/>
     </row>
     <row r="337" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
@@ -28860,9 +28869,9 @@
       <c r="Y337" s="50">
         <v>1</v>
       </c>
-      <c r="Z337" s="96"/>
-      <c r="AA337" s="97"/>
-      <c r="AB337" s="97"/>
+      <c r="Z337" s="97"/>
+      <c r="AA337" s="98"/>
+      <c r="AB337" s="98"/>
     </row>
     <row r="338" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
@@ -28942,9 +28951,9 @@
       <c r="Y338" s="50">
         <v>1</v>
       </c>
-      <c r="Z338" s="96"/>
-      <c r="AA338" s="97"/>
-      <c r="AB338" s="97"/>
+      <c r="Z338" s="97"/>
+      <c r="AA338" s="98"/>
+      <c r="AB338" s="98"/>
     </row>
     <row r="339" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
@@ -29024,9 +29033,9 @@
       <c r="Y339" s="50">
         <v>1</v>
       </c>
-      <c r="Z339" s="96"/>
-      <c r="AA339" s="97"/>
-      <c r="AB339" s="97"/>
+      <c r="Z339" s="97"/>
+      <c r="AA339" s="98"/>
+      <c r="AB339" s="98"/>
     </row>
     <row r="340" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
@@ -29106,9 +29115,9 @@
       <c r="Y340" s="50">
         <v>1</v>
       </c>
-      <c r="Z340" s="96"/>
-      <c r="AA340" s="97"/>
-      <c r="AB340" s="97"/>
+      <c r="Z340" s="97"/>
+      <c r="AA340" s="98"/>
+      <c r="AB340" s="98"/>
     </row>
     <row r="341" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
@@ -29188,9 +29197,9 @@
       <c r="Y341" s="50">
         <v>1</v>
       </c>
-      <c r="Z341" s="96"/>
-      <c r="AA341" s="97"/>
-      <c r="AB341" s="97"/>
+      <c r="Z341" s="97"/>
+      <c r="AA341" s="98"/>
+      <c r="AB341" s="98"/>
     </row>
     <row r="342" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
@@ -29270,9 +29279,9 @@
       <c r="Y342" s="50">
         <v>1</v>
       </c>
-      <c r="Z342" s="96"/>
-      <c r="AA342" s="97"/>
-      <c r="AB342" s="97"/>
+      <c r="Z342" s="97"/>
+      <c r="AA342" s="98"/>
+      <c r="AB342" s="98"/>
     </row>
     <row r="343" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
@@ -29352,9 +29361,9 @@
       <c r="Y343" s="50">
         <v>1</v>
       </c>
-      <c r="Z343" s="96"/>
-      <c r="AA343" s="97"/>
-      <c r="AB343" s="97"/>
+      <c r="Z343" s="97"/>
+      <c r="AA343" s="98"/>
+      <c r="AB343" s="98"/>
     </row>
     <row r="344" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A344" s="43">
@@ -29432,11 +29441,11 @@
       <c r="Y344" s="40">
         <v>1</v>
       </c>
-      <c r="Z344" s="96" t="s">
+      <c r="Z344" s="97" t="s">
         <v>108</v>
       </c>
-      <c r="AA344" s="97"/>
-      <c r="AB344" s="97"/>
+      <c r="AA344" s="98"/>
+      <c r="AB344" s="98"/>
     </row>
     <row r="345" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
@@ -29514,9 +29523,9 @@
       <c r="Y345" s="50">
         <v>1</v>
       </c>
-      <c r="Z345" s="96"/>
-      <c r="AA345" s="97"/>
-      <c r="AB345" s="97"/>
+      <c r="Z345" s="97"/>
+      <c r="AA345" s="98"/>
+      <c r="AB345" s="98"/>
     </row>
     <row r="346" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A346" s="27">
@@ -29594,9 +29603,9 @@
       <c r="Y346" s="57">
         <v>1</v>
       </c>
-      <c r="Z346" s="96"/>
-      <c r="AA346" s="97"/>
-      <c r="AB346" s="97"/>
+      <c r="Z346" s="97"/>
+      <c r="AA346" s="98"/>
+      <c r="AB346" s="98"/>
     </row>
     <row r="347" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A347" s="33">
@@ -29674,11 +29683,11 @@
       <c r="Y347" s="57">
         <v>1</v>
       </c>
-      <c r="Z347" s="96" t="s">
+      <c r="Z347" s="97" t="s">
         <v>93</v>
       </c>
-      <c r="AA347" s="97"/>
-      <c r="AB347" s="97"/>
+      <c r="AA347" s="98"/>
+      <c r="AB347" s="98"/>
     </row>
     <row r="348" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A348" s="33">
@@ -29756,11 +29765,11 @@
       <c r="Y348" s="57">
         <v>1</v>
       </c>
-      <c r="Z348" s="96" t="s">
+      <c r="Z348" s="97" t="s">
         <v>111</v>
       </c>
-      <c r="AA348" s="98"/>
-      <c r="AB348" s="98"/>
+      <c r="AA348" s="99"/>
+      <c r="AB348" s="99"/>
     </row>
     <row r="349" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
@@ -29841,7 +29850,7 @@
       </c>
     </row>
     <row r="350" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A350" s="43">
+      <c r="A350" s="114">
         <v>447</v>
       </c>
       <c r="B350" s="45">
@@ -29917,14 +29926,14 @@
       <c r="Y350" s="40">
         <v>1</v>
       </c>
-      <c r="Z350" s="96" t="s">
+      <c r="Z350" s="97" t="s">
         <v>112</v>
       </c>
-      <c r="AA350" s="97"/>
-      <c r="AB350" s="97"/>
+      <c r="AA350" s="98"/>
+      <c r="AB350" s="98"/>
     </row>
     <row r="351" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A351" s="1">
+      <c r="A351" s="115">
         <v>448</v>
       </c>
       <c r="B351" s="15">
@@ -30000,12 +30009,12 @@
       <c r="Y351" s="50">
         <v>1</v>
       </c>
-      <c r="Z351" s="96"/>
-      <c r="AA351" s="97"/>
-      <c r="AB351" s="97"/>
+      <c r="Z351" s="97"/>
+      <c r="AA351" s="98"/>
+      <c r="AB351" s="98"/>
     </row>
     <row r="352" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A352" s="27">
+      <c r="A352" s="116">
         <v>449</v>
       </c>
       <c r="B352" s="29">
@@ -30081,9 +30090,9 @@
       <c r="Y352" s="57">
         <v>1</v>
       </c>
-      <c r="Z352" s="96"/>
-      <c r="AA352" s="97"/>
-      <c r="AB352" s="97"/>
+      <c r="Z352" s="97"/>
+      <c r="AA352" s="98"/>
+      <c r="AB352" s="98"/>
     </row>
     <row r="353" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
@@ -30305,7 +30314,7 @@
       <c r="U355" s="42">
         <v>20400000000000</v>
       </c>
-      <c r="V355" s="113">
+      <c r="V355" s="96">
         <f t="shared" ref="V355" si="44">$V$225</f>
         <v>125520</v>
       </c>
@@ -30321,20 +30330,59 @@
     </row>
   </sheetData>
   <mergeCells count="83">
-    <mergeCell ref="Z326:AB343"/>
-    <mergeCell ref="Z344:AB346"/>
-    <mergeCell ref="Z252:AB262"/>
-    <mergeCell ref="Z263:AB264"/>
-    <mergeCell ref="Z315:AB317"/>
-    <mergeCell ref="Z318:AB325"/>
-    <mergeCell ref="Z295:AB295"/>
-    <mergeCell ref="Z276:AB287"/>
-    <mergeCell ref="Z288:AB289"/>
-    <mergeCell ref="Z290:AB292"/>
-    <mergeCell ref="Z265:AB275"/>
-    <mergeCell ref="Z296:AB312"/>
-    <mergeCell ref="Z314:AB314"/>
-    <mergeCell ref="Z293:AB293"/>
+    <mergeCell ref="Z350:AB352"/>
+    <mergeCell ref="Z167:AB167"/>
+    <mergeCell ref="Z240:AB251"/>
+    <mergeCell ref="Z235:AB237"/>
+    <mergeCell ref="Z238:AB239"/>
+    <mergeCell ref="Z225:AB232"/>
+    <mergeCell ref="Z199:AB199"/>
+    <mergeCell ref="Z200:AB200"/>
+    <mergeCell ref="Z201:AB201"/>
+    <mergeCell ref="Z194:AB194"/>
+    <mergeCell ref="Z195:AB195"/>
+    <mergeCell ref="Z196:AB196"/>
+    <mergeCell ref="Z233:AB234"/>
+    <mergeCell ref="Z294:AB294"/>
+    <mergeCell ref="Z347:AB347"/>
+    <mergeCell ref="Z348:AB348"/>
+    <mergeCell ref="Z221:AB222"/>
+    <mergeCell ref="Z223:AB224"/>
+    <mergeCell ref="Z163:AB163"/>
+    <mergeCell ref="Z165:AB165"/>
+    <mergeCell ref="Z166:AB166"/>
+    <mergeCell ref="Z169:AB175"/>
+    <mergeCell ref="Z197:AB197"/>
+    <mergeCell ref="Z198:AB198"/>
+    <mergeCell ref="Z168:AB168"/>
+    <mergeCell ref="Z202:AB202"/>
+    <mergeCell ref="Z203:AB203"/>
+    <mergeCell ref="Z204:AB204"/>
+    <mergeCell ref="Z205:AB205"/>
+    <mergeCell ref="Z176:AB193"/>
+    <mergeCell ref="Z92:AB93"/>
+    <mergeCell ref="Z94:AB94"/>
+    <mergeCell ref="Z95:AB111"/>
+    <mergeCell ref="Z158:AB162"/>
+    <mergeCell ref="Z206:AB220"/>
+    <mergeCell ref="Z130:AB147"/>
+    <mergeCell ref="Z112:AB129"/>
+    <mergeCell ref="Z48:AB48"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="Z49:AB49"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="Z8:AD8"/>
+    <mergeCell ref="Z28:AB28"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="Z10:AB27"/>
+    <mergeCell ref="Z29:AB46"/>
+    <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="Z6:AB6"/>
+    <mergeCell ref="Z7:AB7"/>
     <mergeCell ref="Z5:AB5"/>
     <mergeCell ref="Z4:AB4"/>
     <mergeCell ref="Z164:AB164"/>
@@ -30351,59 +30399,20 @@
     <mergeCell ref="Z90:AB90"/>
     <mergeCell ref="Z91:AB91"/>
     <mergeCell ref="Z148:AB152"/>
-    <mergeCell ref="Z48:AB48"/>
-    <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="Z49:AB49"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="Z8:AD8"/>
-    <mergeCell ref="Z28:AB28"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="Z10:AB27"/>
-    <mergeCell ref="Z29:AB46"/>
-    <mergeCell ref="U1:Y1"/>
-    <mergeCell ref="Z6:AB6"/>
-    <mergeCell ref="Z7:AB7"/>
-    <mergeCell ref="Z92:AB93"/>
-    <mergeCell ref="Z94:AB94"/>
-    <mergeCell ref="Z95:AB111"/>
-    <mergeCell ref="Z158:AB162"/>
-    <mergeCell ref="Z206:AB220"/>
-    <mergeCell ref="Z130:AB147"/>
-    <mergeCell ref="Z112:AB129"/>
-    <mergeCell ref="Z221:AB222"/>
-    <mergeCell ref="Z223:AB224"/>
-    <mergeCell ref="Z163:AB163"/>
-    <mergeCell ref="Z165:AB165"/>
-    <mergeCell ref="Z166:AB166"/>
-    <mergeCell ref="Z169:AB175"/>
-    <mergeCell ref="Z197:AB197"/>
-    <mergeCell ref="Z198:AB198"/>
-    <mergeCell ref="Z168:AB168"/>
-    <mergeCell ref="Z202:AB202"/>
-    <mergeCell ref="Z203:AB203"/>
-    <mergeCell ref="Z204:AB204"/>
-    <mergeCell ref="Z205:AB205"/>
-    <mergeCell ref="Z176:AB193"/>
-    <mergeCell ref="Z350:AB352"/>
-    <mergeCell ref="Z167:AB167"/>
-    <mergeCell ref="Z240:AB251"/>
-    <mergeCell ref="Z235:AB237"/>
-    <mergeCell ref="Z238:AB239"/>
-    <mergeCell ref="Z225:AB232"/>
-    <mergeCell ref="Z199:AB199"/>
-    <mergeCell ref="Z200:AB200"/>
-    <mergeCell ref="Z201:AB201"/>
-    <mergeCell ref="Z194:AB194"/>
-    <mergeCell ref="Z195:AB195"/>
-    <mergeCell ref="Z196:AB196"/>
-    <mergeCell ref="Z233:AB234"/>
-    <mergeCell ref="Z294:AB294"/>
-    <mergeCell ref="Z347:AB347"/>
-    <mergeCell ref="Z348:AB348"/>
+    <mergeCell ref="Z326:AB343"/>
+    <mergeCell ref="Z344:AB346"/>
+    <mergeCell ref="Z252:AB262"/>
+    <mergeCell ref="Z263:AB264"/>
+    <mergeCell ref="Z315:AB317"/>
+    <mergeCell ref="Z318:AB325"/>
+    <mergeCell ref="Z295:AB295"/>
+    <mergeCell ref="Z276:AB287"/>
+    <mergeCell ref="Z288:AB289"/>
+    <mergeCell ref="Z290:AB292"/>
+    <mergeCell ref="Z265:AB275"/>
+    <mergeCell ref="Z296:AB312"/>
+    <mergeCell ref="Z314:AB314"/>
+    <mergeCell ref="Z293:AB293"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Simulations_IDS.xlsx
+++ b/Simulations_IDS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documentos_Betran\DropletEvaporation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE8DCB3-12D3-40E0-91B6-F0E8E222C533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A9BF5C-F61D-4A01-8A32-E4DB8D90CF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{73239687-5BB6-4FA0-A3B4-8BE280184789}"/>
   </bookViews>
@@ -792,6 +792,9 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -801,29 +804,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -837,15 +834,18 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1195,42 +1195,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="B1" s="108" t="s">
+      <c r="B1" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="109" t="s">
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="111"/>
-      <c r="K1" s="110" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="111"/>
-      <c r="M1" s="109" t="s">
+      <c r="H1" s="111"/>
+      <c r="I1" s="111"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="111" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="112"/>
+      <c r="M1" s="110" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="110"/>
-      <c r="O1" s="110"/>
-      <c r="P1" s="110"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="109" t="s">
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="110" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="110"/>
-      <c r="T1" s="110"/>
-      <c r="U1" s="110" t="s">
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="V1" s="110"/>
-      <c r="W1" s="110"/>
-      <c r="X1" s="110"/>
-      <c r="Y1" s="111"/>
+      <c r="V1" s="111"/>
+      <c r="W1" s="111"/>
+      <c r="X1" s="111"/>
+      <c r="Y1" s="112"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1459,11 +1459,11 @@
       <c r="Y4" s="1">
         <v>1</v>
       </c>
-      <c r="Z4" s="104" t="s">
+      <c r="Z4" s="107" t="s">
         <v>46</v>
       </c>
-      <c r="AA4" s="105"/>
-      <c r="AB4" s="105"/>
+      <c r="AA4" s="113"/>
+      <c r="AB4" s="113"/>
       <c r="AC4" s="65"/>
       <c r="AD4" s="65"/>
     </row>
@@ -1544,11 +1544,11 @@
       <c r="Y5" s="1">
         <v>1</v>
       </c>
-      <c r="Z5" s="104" t="s">
+      <c r="Z5" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="AA5" s="105"/>
-      <c r="AB5" s="105"/>
+      <c r="AA5" s="113"/>
+      <c r="AB5" s="113"/>
       <c r="AC5" s="65"/>
       <c r="AD5" s="65"/>
     </row>
@@ -1629,11 +1629,11 @@
       <c r="Y6" s="1">
         <v>1</v>
       </c>
-      <c r="Z6" s="104" t="s">
+      <c r="Z6" s="107" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="105"/>
-      <c r="AB6" s="105"/>
+      <c r="AA6" s="113"/>
+      <c r="AB6" s="113"/>
       <c r="AC6" s="65"/>
       <c r="AD6" s="65"/>
     </row>
@@ -1714,11 +1714,11 @@
       <c r="Y7" s="1">
         <v>1</v>
       </c>
-      <c r="Z7" s="104" t="s">
+      <c r="Z7" s="107" t="s">
         <v>49</v>
       </c>
-      <c r="AA7" s="105"/>
-      <c r="AB7" s="105"/>
+      <c r="AA7" s="113"/>
+      <c r="AB7" s="113"/>
       <c r="AC7" s="65"/>
       <c r="AD7" s="65"/>
     </row>
@@ -1799,13 +1799,13 @@
       <c r="Y8" s="38">
         <v>1</v>
       </c>
-      <c r="Z8" s="104" t="s">
+      <c r="Z8" s="107" t="s">
         <v>53</v>
       </c>
-      <c r="AA8" s="106"/>
-      <c r="AB8" s="106"/>
-      <c r="AC8" s="106"/>
-      <c r="AD8" s="106"/>
+      <c r="AA8" s="108"/>
+      <c r="AB8" s="108"/>
+      <c r="AC8" s="108"/>
+      <c r="AD8" s="108"/>
       <c r="AE8" s="20"/>
       <c r="AF8" s="20"/>
     </row>
@@ -1886,11 +1886,11 @@
       <c r="Y9" s="1">
         <v>1</v>
       </c>
-      <c r="Z9" s="104" t="s">
+      <c r="Z9" s="107" t="s">
         <v>50</v>
       </c>
-      <c r="AA9" s="106"/>
-      <c r="AB9" s="106"/>
+      <c r="AA9" s="108"/>
+      <c r="AB9" s="108"/>
       <c r="AC9" s="65"/>
       <c r="AD9" s="65"/>
     </row>
@@ -1971,11 +1971,11 @@
       <c r="Y10" s="43">
         <v>1</v>
       </c>
-      <c r="Z10" s="97" t="s">
+      <c r="Z10" s="100" t="s">
         <v>51</v>
       </c>
-      <c r="AA10" s="98"/>
-      <c r="AB10" s="98"/>
+      <c r="AA10" s="101"/>
+      <c r="AB10" s="101"/>
       <c r="AC10" s="65"/>
       <c r="AD10" s="65"/>
     </row>
@@ -2058,9 +2058,9 @@
       <c r="Y11" s="1">
         <v>1</v>
       </c>
-      <c r="Z11" s="97"/>
-      <c r="AA11" s="98"/>
-      <c r="AB11" s="98"/>
+      <c r="Z11" s="100"/>
+      <c r="AA11" s="101"/>
+      <c r="AB11" s="101"/>
       <c r="AC11" s="65"/>
       <c r="AD11" s="65"/>
     </row>
@@ -2142,9 +2142,9 @@
       <c r="Y12" s="1">
         <v>1</v>
       </c>
-      <c r="Z12" s="97"/>
-      <c r="AA12" s="98"/>
-      <c r="AB12" s="98"/>
+      <c r="Z12" s="100"/>
+      <c r="AA12" s="101"/>
+      <c r="AB12" s="101"/>
       <c r="AC12" s="65"/>
       <c r="AD12" s="65"/>
     </row>
@@ -2226,9 +2226,9 @@
       <c r="Y13" s="1">
         <v>1</v>
       </c>
-      <c r="Z13" s="97"/>
-      <c r="AA13" s="98"/>
-      <c r="AB13" s="98"/>
+      <c r="Z13" s="100"/>
+      <c r="AA13" s="101"/>
+      <c r="AB13" s="101"/>
       <c r="AC13" s="65"/>
       <c r="AD13" s="65"/>
     </row>
@@ -2310,9 +2310,9 @@
       <c r="Y14" s="1">
         <v>1</v>
       </c>
-      <c r="Z14" s="97"/>
-      <c r="AA14" s="98"/>
-      <c r="AB14" s="98"/>
+      <c r="Z14" s="100"/>
+      <c r="AA14" s="101"/>
+      <c r="AB14" s="101"/>
       <c r="AC14" s="65"/>
       <c r="AD14" s="65"/>
     </row>
@@ -2394,9 +2394,9 @@
       <c r="Y15" s="1">
         <v>1</v>
       </c>
-      <c r="Z15" s="97"/>
-      <c r="AA15" s="98"/>
-      <c r="AB15" s="98"/>
+      <c r="Z15" s="100"/>
+      <c r="AA15" s="101"/>
+      <c r="AB15" s="101"/>
       <c r="AC15" s="65"/>
       <c r="AD15" s="65"/>
     </row>
@@ -2478,9 +2478,9 @@
       <c r="Y16" s="1">
         <v>1</v>
       </c>
-      <c r="Z16" s="97"/>
-      <c r="AA16" s="98"/>
-      <c r="AB16" s="98"/>
+      <c r="Z16" s="100"/>
+      <c r="AA16" s="101"/>
+      <c r="AB16" s="101"/>
       <c r="AC16" s="65"/>
       <c r="AD16" s="65"/>
     </row>
@@ -2562,9 +2562,9 @@
       <c r="Y17" s="1">
         <v>1</v>
       </c>
-      <c r="Z17" s="97"/>
-      <c r="AA17" s="98"/>
-      <c r="AB17" s="98"/>
+      <c r="Z17" s="100"/>
+      <c r="AA17" s="101"/>
+      <c r="AB17" s="101"/>
       <c r="AC17" s="65"/>
       <c r="AD17" s="65"/>
     </row>
@@ -2646,9 +2646,9 @@
       <c r="Y18" s="1">
         <v>1</v>
       </c>
-      <c r="Z18" s="97"/>
-      <c r="AA18" s="98"/>
-      <c r="AB18" s="98"/>
+      <c r="Z18" s="100"/>
+      <c r="AA18" s="101"/>
+      <c r="AB18" s="101"/>
       <c r="AC18" s="65"/>
       <c r="AD18" s="65"/>
     </row>
@@ -2730,9 +2730,9 @@
       <c r="Y19" s="1">
         <v>1</v>
       </c>
-      <c r="Z19" s="97"/>
-      <c r="AA19" s="98"/>
-      <c r="AB19" s="98"/>
+      <c r="Z19" s="100"/>
+      <c r="AA19" s="101"/>
+      <c r="AB19" s="101"/>
       <c r="AC19" s="65"/>
       <c r="AD19" s="65"/>
     </row>
@@ -2814,9 +2814,9 @@
       <c r="Y20" s="1">
         <v>1</v>
       </c>
-      <c r="Z20" s="97"/>
-      <c r="AA20" s="98"/>
-      <c r="AB20" s="98"/>
+      <c r="Z20" s="100"/>
+      <c r="AA20" s="101"/>
+      <c r="AB20" s="101"/>
       <c r="AC20" s="65"/>
       <c r="AD20" s="65"/>
     </row>
@@ -2898,9 +2898,9 @@
       <c r="Y21" s="1">
         <v>1</v>
       </c>
-      <c r="Z21" s="97"/>
-      <c r="AA21" s="98"/>
-      <c r="AB21" s="98"/>
+      <c r="Z21" s="100"/>
+      <c r="AA21" s="101"/>
+      <c r="AB21" s="101"/>
       <c r="AC21" s="65"/>
       <c r="AD21" s="65"/>
     </row>
@@ -2982,9 +2982,9 @@
       <c r="Y22" s="1">
         <v>1</v>
       </c>
-      <c r="Z22" s="97"/>
-      <c r="AA22" s="98"/>
-      <c r="AB22" s="98"/>
+      <c r="Z22" s="100"/>
+      <c r="AA22" s="101"/>
+      <c r="AB22" s="101"/>
       <c r="AC22" s="65"/>
       <c r="AD22" s="65"/>
     </row>
@@ -3066,9 +3066,9 @@
       <c r="Y23" s="1">
         <v>1</v>
       </c>
-      <c r="Z23" s="97"/>
-      <c r="AA23" s="98"/>
-      <c r="AB23" s="98"/>
+      <c r="Z23" s="100"/>
+      <c r="AA23" s="101"/>
+      <c r="AB23" s="101"/>
       <c r="AC23" s="65"/>
       <c r="AD23" s="65"/>
     </row>
@@ -3150,9 +3150,9 @@
       <c r="Y24" s="1">
         <v>1</v>
       </c>
-      <c r="Z24" s="97"/>
-      <c r="AA24" s="98"/>
-      <c r="AB24" s="98"/>
+      <c r="Z24" s="100"/>
+      <c r="AA24" s="101"/>
+      <c r="AB24" s="101"/>
       <c r="AC24" s="65"/>
       <c r="AD24" s="65"/>
     </row>
@@ -3234,9 +3234,9 @@
       <c r="Y25" s="1">
         <v>1</v>
       </c>
-      <c r="Z25" s="97"/>
-      <c r="AA25" s="98"/>
-      <c r="AB25" s="98"/>
+      <c r="Z25" s="100"/>
+      <c r="AA25" s="101"/>
+      <c r="AB25" s="101"/>
       <c r="AC25" s="65"/>
       <c r="AD25" s="65"/>
     </row>
@@ -3318,9 +3318,9 @@
       <c r="Y26" s="1">
         <v>1</v>
       </c>
-      <c r="Z26" s="97"/>
-      <c r="AA26" s="98"/>
-      <c r="AB26" s="98"/>
+      <c r="Z26" s="100"/>
+      <c r="AA26" s="101"/>
+      <c r="AB26" s="101"/>
       <c r="AC26" s="65"/>
       <c r="AD26" s="65"/>
     </row>
@@ -3402,9 +3402,9 @@
       <c r="Y27" s="27">
         <v>1</v>
       </c>
-      <c r="Z27" s="97"/>
-      <c r="AA27" s="98"/>
-      <c r="AB27" s="98"/>
+      <c r="Z27" s="100"/>
+      <c r="AA27" s="101"/>
+      <c r="AB27" s="101"/>
       <c r="AC27" s="65"/>
       <c r="AD27" s="65"/>
     </row>
@@ -3485,11 +3485,11 @@
       <c r="Y28" s="33">
         <v>1</v>
       </c>
-      <c r="Z28" s="104" t="s">
+      <c r="Z28" s="107" t="s">
         <v>52</v>
       </c>
-      <c r="AA28" s="106"/>
-      <c r="AB28" s="106"/>
+      <c r="AA28" s="108"/>
+      <c r="AB28" s="108"/>
       <c r="AC28" s="65"/>
       <c r="AD28" s="65"/>
     </row>
@@ -3571,11 +3571,11 @@
       <c r="Y29" s="1">
         <v>1</v>
       </c>
-      <c r="Z29" s="97" t="s">
+      <c r="Z29" s="100" t="s">
         <v>51</v>
       </c>
-      <c r="AA29" s="98"/>
-      <c r="AB29" s="98"/>
+      <c r="AA29" s="101"/>
+      <c r="AB29" s="101"/>
       <c r="AC29" s="65"/>
       <c r="AD29" s="65"/>
     </row>
@@ -3657,9 +3657,9 @@
       <c r="Y30" s="1">
         <v>1</v>
       </c>
-      <c r="Z30" s="97"/>
-      <c r="AA30" s="98"/>
-      <c r="AB30" s="98"/>
+      <c r="Z30" s="100"/>
+      <c r="AA30" s="101"/>
+      <c r="AB30" s="101"/>
       <c r="AC30" s="65"/>
       <c r="AD30" s="65"/>
     </row>
@@ -3741,9 +3741,9 @@
       <c r="Y31" s="1">
         <v>1</v>
       </c>
-      <c r="Z31" s="97"/>
-      <c r="AA31" s="98"/>
-      <c r="AB31" s="98"/>
+      <c r="Z31" s="100"/>
+      <c r="AA31" s="101"/>
+      <c r="AB31" s="101"/>
       <c r="AC31" s="65"/>
       <c r="AD31" s="65"/>
     </row>
@@ -3825,9 +3825,9 @@
       <c r="Y32" s="1">
         <v>1</v>
       </c>
-      <c r="Z32" s="97"/>
-      <c r="AA32" s="98"/>
-      <c r="AB32" s="98"/>
+      <c r="Z32" s="100"/>
+      <c r="AA32" s="101"/>
+      <c r="AB32" s="101"/>
       <c r="AC32" s="65"/>
       <c r="AD32" s="65"/>
     </row>
@@ -3909,9 +3909,9 @@
       <c r="Y33" s="1">
         <v>1</v>
       </c>
-      <c r="Z33" s="97"/>
-      <c r="AA33" s="98"/>
-      <c r="AB33" s="98"/>
+      <c r="Z33" s="100"/>
+      <c r="AA33" s="101"/>
+      <c r="AB33" s="101"/>
       <c r="AC33" s="65"/>
       <c r="AD33" s="65"/>
     </row>
@@ -3993,9 +3993,9 @@
       <c r="Y34" s="1">
         <v>1</v>
       </c>
-      <c r="Z34" s="97"/>
-      <c r="AA34" s="98"/>
-      <c r="AB34" s="98"/>
+      <c r="Z34" s="100"/>
+      <c r="AA34" s="101"/>
+      <c r="AB34" s="101"/>
       <c r="AC34" s="65"/>
       <c r="AD34" s="65"/>
     </row>
@@ -4077,9 +4077,9 @@
       <c r="Y35" s="1">
         <v>1</v>
       </c>
-      <c r="Z35" s="97"/>
-      <c r="AA35" s="98"/>
-      <c r="AB35" s="98"/>
+      <c r="Z35" s="100"/>
+      <c r="AA35" s="101"/>
+      <c r="AB35" s="101"/>
       <c r="AC35" s="65"/>
       <c r="AD35" s="65"/>
     </row>
@@ -4161,9 +4161,9 @@
       <c r="Y36" s="1">
         <v>1</v>
       </c>
-      <c r="Z36" s="97"/>
-      <c r="AA36" s="98"/>
-      <c r="AB36" s="98"/>
+      <c r="Z36" s="100"/>
+      <c r="AA36" s="101"/>
+      <c r="AB36" s="101"/>
       <c r="AC36" s="65"/>
       <c r="AD36" s="65"/>
     </row>
@@ -4245,9 +4245,9 @@
       <c r="Y37" s="1">
         <v>1</v>
       </c>
-      <c r="Z37" s="97"/>
-      <c r="AA37" s="98"/>
-      <c r="AB37" s="98"/>
+      <c r="Z37" s="100"/>
+      <c r="AA37" s="101"/>
+      <c r="AB37" s="101"/>
       <c r="AC37" s="65"/>
       <c r="AD37" s="65"/>
     </row>
@@ -4329,9 +4329,9 @@
       <c r="Y38" s="1">
         <v>1</v>
       </c>
-      <c r="Z38" s="97"/>
-      <c r="AA38" s="98"/>
-      <c r="AB38" s="98"/>
+      <c r="Z38" s="100"/>
+      <c r="AA38" s="101"/>
+      <c r="AB38" s="101"/>
       <c r="AC38" s="65"/>
       <c r="AD38" s="65"/>
     </row>
@@ -4413,9 +4413,9 @@
       <c r="Y39" s="1">
         <v>1</v>
       </c>
-      <c r="Z39" s="97"/>
-      <c r="AA39" s="98"/>
-      <c r="AB39" s="98"/>
+      <c r="Z39" s="100"/>
+      <c r="AA39" s="101"/>
+      <c r="AB39" s="101"/>
       <c r="AC39" s="65"/>
       <c r="AD39" s="65"/>
     </row>
@@ -4497,9 +4497,9 @@
       <c r="Y40" s="1">
         <v>1</v>
       </c>
-      <c r="Z40" s="97"/>
-      <c r="AA40" s="98"/>
-      <c r="AB40" s="98"/>
+      <c r="Z40" s="100"/>
+      <c r="AA40" s="101"/>
+      <c r="AB40" s="101"/>
       <c r="AC40" s="65"/>
       <c r="AD40" s="65"/>
     </row>
@@ -4581,9 +4581,9 @@
       <c r="Y41" s="1">
         <v>1</v>
       </c>
-      <c r="Z41" s="97"/>
-      <c r="AA41" s="98"/>
-      <c r="AB41" s="98"/>
+      <c r="Z41" s="100"/>
+      <c r="AA41" s="101"/>
+      <c r="AB41" s="101"/>
       <c r="AC41" s="65"/>
       <c r="AD41" s="65"/>
     </row>
@@ -4665,9 +4665,9 @@
       <c r="Y42" s="1">
         <v>1</v>
       </c>
-      <c r="Z42" s="97"/>
-      <c r="AA42" s="98"/>
-      <c r="AB42" s="98"/>
+      <c r="Z42" s="100"/>
+      <c r="AA42" s="101"/>
+      <c r="AB42" s="101"/>
       <c r="AC42" s="65"/>
       <c r="AD42" s="65"/>
     </row>
@@ -4749,9 +4749,9 @@
       <c r="Y43" s="1">
         <v>1</v>
       </c>
-      <c r="Z43" s="97"/>
-      <c r="AA43" s="98"/>
-      <c r="AB43" s="98"/>
+      <c r="Z43" s="100"/>
+      <c r="AA43" s="101"/>
+      <c r="AB43" s="101"/>
       <c r="AC43" s="65"/>
       <c r="AD43" s="65"/>
     </row>
@@ -4833,9 +4833,9 @@
       <c r="Y44" s="1">
         <v>1</v>
       </c>
-      <c r="Z44" s="97"/>
-      <c r="AA44" s="98"/>
-      <c r="AB44" s="98"/>
+      <c r="Z44" s="100"/>
+      <c r="AA44" s="101"/>
+      <c r="AB44" s="101"/>
       <c r="AC44" s="65"/>
       <c r="AD44" s="65"/>
     </row>
@@ -4917,9 +4917,9 @@
       <c r="Y45" s="1">
         <v>1</v>
       </c>
-      <c r="Z45" s="97"/>
-      <c r="AA45" s="98"/>
-      <c r="AB45" s="98"/>
+      <c r="Z45" s="100"/>
+      <c r="AA45" s="101"/>
+      <c r="AB45" s="101"/>
       <c r="AC45" s="65"/>
       <c r="AD45" s="65"/>
     </row>
@@ -5001,9 +5001,9 @@
       <c r="Y46" s="1">
         <v>1</v>
       </c>
-      <c r="Z46" s="97"/>
-      <c r="AA46" s="98"/>
-      <c r="AB46" s="98"/>
+      <c r="Z46" s="100"/>
+      <c r="AA46" s="101"/>
+      <c r="AB46" s="101"/>
       <c r="AC46" s="65"/>
       <c r="AD46" s="65"/>
     </row>
@@ -5084,11 +5084,11 @@
       <c r="Y47" s="43">
         <v>1</v>
       </c>
-      <c r="Z47" s="104" t="s">
+      <c r="Z47" s="107" t="s">
         <v>54</v>
       </c>
-      <c r="AA47" s="106"/>
-      <c r="AB47" s="106"/>
+      <c r="AA47" s="108"/>
+      <c r="AB47" s="108"/>
       <c r="AC47" s="66"/>
       <c r="AD47" s="65"/>
     </row>
@@ -5170,11 +5170,11 @@
       <c r="Y48" s="43">
         <v>1</v>
       </c>
-      <c r="Z48" s="102" t="s">
+      <c r="Z48" s="105" t="s">
         <v>55</v>
       </c>
-      <c r="AA48" s="107"/>
-      <c r="AB48" s="107"/>
+      <c r="AA48" s="106"/>
+      <c r="AB48" s="106"/>
       <c r="AC48" s="67"/>
       <c r="AD48" s="65"/>
     </row>
@@ -5255,11 +5255,11 @@
       <c r="Y49" s="43">
         <v>1</v>
       </c>
-      <c r="Z49" s="104" t="s">
+      <c r="Z49" s="107" t="s">
         <v>56</v>
       </c>
-      <c r="AA49" s="106"/>
-      <c r="AB49" s="106"/>
+      <c r="AA49" s="108"/>
+      <c r="AB49" s="108"/>
       <c r="AC49" s="65"/>
       <c r="AD49" s="65"/>
     </row>
@@ -5339,11 +5339,11 @@
       <c r="Y50" s="40">
         <v>1</v>
       </c>
-      <c r="Z50" s="104" t="s">
+      <c r="Z50" s="107" t="s">
         <v>57</v>
       </c>
-      <c r="AA50" s="106"/>
-      <c r="AB50" s="106"/>
+      <c r="AA50" s="108"/>
+      <c r="AB50" s="108"/>
       <c r="AC50" s="65"/>
       <c r="AD50" s="65"/>
     </row>
@@ -5425,11 +5425,11 @@
       <c r="Y51" s="43">
         <v>1</v>
       </c>
-      <c r="Z51" s="97" t="s">
+      <c r="Z51" s="100" t="s">
         <v>59</v>
       </c>
-      <c r="AA51" s="98"/>
-      <c r="AB51" s="98"/>
+      <c r="AA51" s="101"/>
+      <c r="AB51" s="101"/>
       <c r="AC51" s="65"/>
       <c r="AD51" s="65"/>
     </row>
@@ -5511,9 +5511,9 @@
       <c r="Y52" s="1">
         <v>1</v>
       </c>
-      <c r="Z52" s="97"/>
-      <c r="AA52" s="98"/>
-      <c r="AB52" s="98"/>
+      <c r="Z52" s="100"/>
+      <c r="AA52" s="101"/>
+      <c r="AB52" s="101"/>
       <c r="AC52" s="65"/>
       <c r="AD52" s="65"/>
     </row>
@@ -5595,9 +5595,9 @@
       <c r="Y53" s="1">
         <v>1</v>
       </c>
-      <c r="Z53" s="97"/>
-      <c r="AA53" s="98"/>
-      <c r="AB53" s="98"/>
+      <c r="Z53" s="100"/>
+      <c r="AA53" s="101"/>
+      <c r="AB53" s="101"/>
       <c r="AC53" s="65"/>
       <c r="AD53" s="65"/>
     </row>
@@ -5679,9 +5679,9 @@
       <c r="Y54" s="1">
         <v>1</v>
       </c>
-      <c r="Z54" s="97"/>
-      <c r="AA54" s="98"/>
-      <c r="AB54" s="98"/>
+      <c r="Z54" s="100"/>
+      <c r="AA54" s="101"/>
+      <c r="AB54" s="101"/>
       <c r="AC54" s="65"/>
       <c r="AD54" s="65"/>
     </row>
@@ -5763,9 +5763,9 @@
       <c r="Y55" s="1">
         <v>1</v>
       </c>
-      <c r="Z55" s="97"/>
-      <c r="AA55" s="98"/>
-      <c r="AB55" s="98"/>
+      <c r="Z55" s="100"/>
+      <c r="AA55" s="101"/>
+      <c r="AB55" s="101"/>
       <c r="AC55" s="65"/>
       <c r="AD55" s="65"/>
     </row>
@@ -5847,9 +5847,9 @@
       <c r="Y56" s="1">
         <v>1</v>
       </c>
-      <c r="Z56" s="97"/>
-      <c r="AA56" s="98"/>
-      <c r="AB56" s="98"/>
+      <c r="Z56" s="100"/>
+      <c r="AA56" s="101"/>
+      <c r="AB56" s="101"/>
       <c r="AC56" s="65"/>
       <c r="AD56" s="65"/>
     </row>
@@ -5931,9 +5931,9 @@
       <c r="Y57" s="27">
         <v>1</v>
       </c>
-      <c r="Z57" s="97"/>
-      <c r="AA57" s="98"/>
-      <c r="AB57" s="98"/>
+      <c r="Z57" s="100"/>
+      <c r="AA57" s="101"/>
+      <c r="AB57" s="101"/>
       <c r="AC57" s="65"/>
       <c r="AD57" s="65"/>
     </row>
@@ -6014,11 +6014,11 @@
       <c r="Y58" s="53">
         <v>1</v>
       </c>
-      <c r="Z58" s="102" t="s">
+      <c r="Z58" s="105" t="s">
         <v>58</v>
       </c>
-      <c r="AA58" s="107"/>
-      <c r="AB58" s="107"/>
+      <c r="AA58" s="106"/>
+      <c r="AB58" s="106"/>
       <c r="AC58" s="65"/>
       <c r="AD58" s="65"/>
     </row>
@@ -6099,11 +6099,11 @@
       <c r="Y59" s="50">
         <v>1</v>
       </c>
-      <c r="Z59" s="97" t="s">
+      <c r="Z59" s="100" t="s">
         <v>60</v>
       </c>
-      <c r="AA59" s="98"/>
-      <c r="AB59" s="98"/>
+      <c r="AA59" s="101"/>
+      <c r="AB59" s="101"/>
       <c r="AC59" s="65"/>
       <c r="AD59" s="65"/>
     </row>
@@ -6184,9 +6184,9 @@
       <c r="Y60" s="50">
         <v>1</v>
       </c>
-      <c r="Z60" s="97"/>
-      <c r="AA60" s="98"/>
-      <c r="AB60" s="98"/>
+      <c r="Z60" s="100"/>
+      <c r="AA60" s="101"/>
+      <c r="AB60" s="101"/>
       <c r="AC60" s="65"/>
       <c r="AD60" s="65"/>
     </row>
@@ -6267,9 +6267,9 @@
       <c r="Y61" s="50">
         <v>1</v>
       </c>
-      <c r="Z61" s="97"/>
-      <c r="AA61" s="98"/>
-      <c r="AB61" s="98"/>
+      <c r="Z61" s="100"/>
+      <c r="AA61" s="101"/>
+      <c r="AB61" s="101"/>
       <c r="AC61" s="65"/>
       <c r="AD61" s="65"/>
     </row>
@@ -6350,9 +6350,9 @@
       <c r="Y62" s="50">
         <v>1</v>
       </c>
-      <c r="Z62" s="97"/>
-      <c r="AA62" s="98"/>
-      <c r="AB62" s="98"/>
+      <c r="Z62" s="100"/>
+      <c r="AA62" s="101"/>
+      <c r="AB62" s="101"/>
       <c r="AC62" s="65"/>
       <c r="AD62" s="65"/>
     </row>
@@ -6433,9 +6433,9 @@
       <c r="Y63" s="50">
         <v>1</v>
       </c>
-      <c r="Z63" s="97"/>
-      <c r="AA63" s="98"/>
-      <c r="AB63" s="98"/>
+      <c r="Z63" s="100"/>
+      <c r="AA63" s="101"/>
+      <c r="AB63" s="101"/>
       <c r="AC63" s="65"/>
       <c r="AD63" s="65"/>
     </row>
@@ -6516,9 +6516,9 @@
       <c r="Y64" s="50">
         <v>1</v>
       </c>
-      <c r="Z64" s="97"/>
-      <c r="AA64" s="98"/>
-      <c r="AB64" s="98"/>
+      <c r="Z64" s="100"/>
+      <c r="AA64" s="101"/>
+      <c r="AB64" s="101"/>
       <c r="AC64" s="65"/>
       <c r="AD64" s="65"/>
     </row>
@@ -6599,9 +6599,9 @@
       <c r="Y65" s="50">
         <v>1</v>
       </c>
-      <c r="Z65" s="97"/>
-      <c r="AA65" s="98"/>
-      <c r="AB65" s="98"/>
+      <c r="Z65" s="100"/>
+      <c r="AA65" s="101"/>
+      <c r="AB65" s="101"/>
       <c r="AC65" s="65"/>
       <c r="AD65" s="65"/>
     </row>
@@ -6682,9 +6682,9 @@
       <c r="Y66" s="57">
         <v>1</v>
       </c>
-      <c r="Z66" s="97"/>
-      <c r="AA66" s="98"/>
-      <c r="AB66" s="98"/>
+      <c r="Z66" s="100"/>
+      <c r="AA66" s="101"/>
+      <c r="AB66" s="101"/>
       <c r="AC66" s="65"/>
       <c r="AD66" s="65"/>
     </row>
@@ -6766,11 +6766,11 @@
       <c r="Y67" s="43">
         <v>1</v>
       </c>
-      <c r="Z67" s="97" t="s">
+      <c r="Z67" s="100" t="s">
         <v>61</v>
       </c>
-      <c r="AA67" s="99"/>
-      <c r="AB67" s="99"/>
+      <c r="AA67" s="102"/>
+      <c r="AB67" s="102"/>
       <c r="AC67" s="65"/>
       <c r="AD67" s="65"/>
     </row>
@@ -6852,9 +6852,9 @@
       <c r="Y68" s="1">
         <v>1</v>
       </c>
-      <c r="Z68" s="97"/>
-      <c r="AA68" s="99"/>
-      <c r="AB68" s="99"/>
+      <c r="Z68" s="100"/>
+      <c r="AA68" s="102"/>
+      <c r="AB68" s="102"/>
       <c r="AC68" s="65"/>
       <c r="AD68" s="65"/>
     </row>
@@ -6936,9 +6936,9 @@
       <c r="Y69" s="1">
         <v>1</v>
       </c>
-      <c r="Z69" s="97"/>
-      <c r="AA69" s="99"/>
-      <c r="AB69" s="99"/>
+      <c r="Z69" s="100"/>
+      <c r="AA69" s="102"/>
+      <c r="AB69" s="102"/>
       <c r="AC69" s="65"/>
       <c r="AD69" s="65"/>
     </row>
@@ -7020,9 +7020,9 @@
       <c r="Y70" s="1">
         <v>1</v>
       </c>
-      <c r="Z70" s="97"/>
-      <c r="AA70" s="99"/>
-      <c r="AB70" s="99"/>
+      <c r="Z70" s="100"/>
+      <c r="AA70" s="102"/>
+      <c r="AB70" s="102"/>
       <c r="AC70" s="65"/>
       <c r="AD70" s="65"/>
     </row>
@@ -7104,9 +7104,9 @@
       <c r="Y71" s="1">
         <v>1</v>
       </c>
-      <c r="Z71" s="97"/>
-      <c r="AA71" s="99"/>
-      <c r="AB71" s="99"/>
+      <c r="Z71" s="100"/>
+      <c r="AA71" s="102"/>
+      <c r="AB71" s="102"/>
       <c r="AC71" s="65"/>
       <c r="AD71" s="65"/>
     </row>
@@ -7188,9 +7188,9 @@
       <c r="Y72" s="1">
         <v>1</v>
       </c>
-      <c r="Z72" s="97"/>
-      <c r="AA72" s="99"/>
-      <c r="AB72" s="99"/>
+      <c r="Z72" s="100"/>
+      <c r="AA72" s="102"/>
+      <c r="AB72" s="102"/>
       <c r="AC72" s="65"/>
       <c r="AD72" s="65"/>
     </row>
@@ -7272,9 +7272,9 @@
       <c r="Y73" s="1">
         <v>1</v>
       </c>
-      <c r="Z73" s="97"/>
-      <c r="AA73" s="99"/>
-      <c r="AB73" s="99"/>
+      <c r="Z73" s="100"/>
+      <c r="AA73" s="102"/>
+      <c r="AB73" s="102"/>
       <c r="AC73" s="65"/>
       <c r="AD73" s="65"/>
     </row>
@@ -7356,9 +7356,9 @@
       <c r="Y74" s="1">
         <v>1</v>
       </c>
-      <c r="Z74" s="97"/>
-      <c r="AA74" s="99"/>
-      <c r="AB74" s="99"/>
+      <c r="Z74" s="100"/>
+      <c r="AA74" s="102"/>
+      <c r="AB74" s="102"/>
       <c r="AC74" s="65"/>
       <c r="AD74" s="65"/>
     </row>
@@ -7440,9 +7440,9 @@
       <c r="Y75" s="1">
         <v>1</v>
       </c>
-      <c r="Z75" s="97"/>
-      <c r="AA75" s="99"/>
-      <c r="AB75" s="99"/>
+      <c r="Z75" s="100"/>
+      <c r="AA75" s="102"/>
+      <c r="AB75" s="102"/>
       <c r="AC75" s="65"/>
       <c r="AD75" s="65"/>
     </row>
@@ -7524,9 +7524,9 @@
       <c r="Y76" s="1">
         <v>1</v>
       </c>
-      <c r="Z76" s="97"/>
-      <c r="AA76" s="99"/>
-      <c r="AB76" s="99"/>
+      <c r="Z76" s="100"/>
+      <c r="AA76" s="102"/>
+      <c r="AB76" s="102"/>
       <c r="AC76" s="65"/>
       <c r="AD76" s="65"/>
     </row>
@@ -7608,9 +7608,9 @@
       <c r="Y77" s="1">
         <v>1</v>
       </c>
-      <c r="Z77" s="97"/>
-      <c r="AA77" s="99"/>
-      <c r="AB77" s="99"/>
+      <c r="Z77" s="100"/>
+      <c r="AA77" s="102"/>
+      <c r="AB77" s="102"/>
       <c r="AC77" s="65"/>
       <c r="AD77" s="65"/>
     </row>
@@ -7692,9 +7692,9 @@
       <c r="Y78" s="1">
         <v>1</v>
       </c>
-      <c r="Z78" s="97"/>
-      <c r="AA78" s="99"/>
-      <c r="AB78" s="99"/>
+      <c r="Z78" s="100"/>
+      <c r="AA78" s="102"/>
+      <c r="AB78" s="102"/>
       <c r="AC78" s="65"/>
       <c r="AD78" s="65"/>
     </row>
@@ -7776,9 +7776,9 @@
       <c r="Y79" s="1">
         <v>1</v>
       </c>
-      <c r="Z79" s="97"/>
-      <c r="AA79" s="99"/>
-      <c r="AB79" s="99"/>
+      <c r="Z79" s="100"/>
+      <c r="AA79" s="102"/>
+      <c r="AB79" s="102"/>
       <c r="AC79" s="65"/>
       <c r="AD79" s="65"/>
     </row>
@@ -7860,9 +7860,9 @@
       <c r="Y80" s="1">
         <v>1</v>
       </c>
-      <c r="Z80" s="97"/>
-      <c r="AA80" s="99"/>
-      <c r="AB80" s="99"/>
+      <c r="Z80" s="100"/>
+      <c r="AA80" s="102"/>
+      <c r="AB80" s="102"/>
       <c r="AC80" s="65"/>
       <c r="AD80" s="65"/>
     </row>
@@ -7944,9 +7944,9 @@
       <c r="Y81" s="1">
         <v>1</v>
       </c>
-      <c r="Z81" s="97"/>
-      <c r="AA81" s="99"/>
-      <c r="AB81" s="99"/>
+      <c r="Z81" s="100"/>
+      <c r="AA81" s="102"/>
+      <c r="AB81" s="102"/>
       <c r="AC81" s="65"/>
       <c r="AD81" s="65"/>
     </row>
@@ -8028,9 +8028,9 @@
       <c r="Y82" s="1">
         <v>1</v>
       </c>
-      <c r="Z82" s="97"/>
-      <c r="AA82" s="99"/>
-      <c r="AB82" s="99"/>
+      <c r="Z82" s="100"/>
+      <c r="AA82" s="102"/>
+      <c r="AB82" s="102"/>
       <c r="AC82" s="65"/>
       <c r="AD82" s="65"/>
     </row>
@@ -8112,9 +8112,9 @@
       <c r="Y83" s="1">
         <v>1</v>
       </c>
-      <c r="Z83" s="97"/>
-      <c r="AA83" s="99"/>
-      <c r="AB83" s="99"/>
+      <c r="Z83" s="100"/>
+      <c r="AA83" s="102"/>
+      <c r="AB83" s="102"/>
       <c r="AC83" s="65"/>
       <c r="AD83" s="65"/>
     </row>
@@ -8196,9 +8196,9 @@
       <c r="Y84" s="1">
         <v>1</v>
       </c>
-      <c r="Z84" s="97"/>
-      <c r="AA84" s="99"/>
-      <c r="AB84" s="99"/>
+      <c r="Z84" s="100"/>
+      <c r="AA84" s="102"/>
+      <c r="AB84" s="102"/>
       <c r="AC84" s="65"/>
       <c r="AD84" s="65"/>
     </row>
@@ -8279,11 +8279,11 @@
       <c r="Y85" s="53">
         <v>1</v>
       </c>
-      <c r="Z85" s="102" t="s">
+      <c r="Z85" s="105" t="s">
         <v>58</v>
       </c>
-      <c r="AA85" s="103"/>
-      <c r="AB85" s="103"/>
+      <c r="AA85" s="114"/>
+      <c r="AB85" s="114"/>
       <c r="AC85" s="65"/>
       <c r="AD85" s="65"/>
     </row>
@@ -8364,11 +8364,11 @@
       <c r="Y86" s="40">
         <v>1</v>
       </c>
-      <c r="Z86" s="97" t="s">
+      <c r="Z86" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="AA86" s="98"/>
-      <c r="AB86" s="98"/>
+      <c r="AA86" s="101"/>
+      <c r="AB86" s="101"/>
       <c r="AC86" s="65"/>
       <c r="AD86" s="65"/>
     </row>
@@ -8449,9 +8449,9 @@
       <c r="Y87" s="57">
         <v>1</v>
       </c>
-      <c r="Z87" s="97"/>
-      <c r="AA87" s="98"/>
-      <c r="AB87" s="98"/>
+      <c r="Z87" s="100"/>
+      <c r="AA87" s="101"/>
+      <c r="AB87" s="101"/>
       <c r="AC87" s="65"/>
       <c r="AD87" s="65"/>
     </row>
@@ -8532,11 +8532,11 @@
       <c r="Y88" s="53">
         <v>1</v>
       </c>
-      <c r="Z88" s="102" t="s">
+      <c r="Z88" s="105" t="s">
         <v>64</v>
       </c>
-      <c r="AA88" s="103"/>
-      <c r="AB88" s="103"/>
+      <c r="AA88" s="114"/>
+      <c r="AB88" s="114"/>
       <c r="AC88" s="65"/>
       <c r="AD88" s="65"/>
     </row>
@@ -8617,11 +8617,11 @@
       <c r="Y89" s="40">
         <v>1</v>
       </c>
-      <c r="Z89" s="102" t="s">
+      <c r="Z89" s="105" t="s">
         <v>63</v>
       </c>
-      <c r="AA89" s="103"/>
-      <c r="AB89" s="103"/>
+      <c r="AA89" s="114"/>
+      <c r="AB89" s="114"/>
       <c r="AC89" s="65"/>
       <c r="AD89" s="65"/>
     </row>
@@ -8702,11 +8702,11 @@
       <c r="Y90" s="57">
         <v>1</v>
       </c>
-      <c r="Z90" s="102" t="s">
+      <c r="Z90" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="AA90" s="103"/>
-      <c r="AB90" s="103"/>
+      <c r="AA90" s="114"/>
+      <c r="AB90" s="114"/>
       <c r="AC90" s="65"/>
       <c r="AD90" s="65"/>
     </row>
@@ -8787,11 +8787,11 @@
       <c r="Y91" s="53">
         <v>1</v>
       </c>
-      <c r="Z91" s="102" t="s">
+      <c r="Z91" s="105" t="s">
         <v>64</v>
       </c>
-      <c r="AA91" s="103"/>
-      <c r="AB91" s="103"/>
+      <c r="AA91" s="114"/>
+      <c r="AB91" s="114"/>
       <c r="AC91" s="65"/>
       <c r="AD91" s="65"/>
     </row>
@@ -8872,11 +8872,11 @@
       <c r="Y92" s="40">
         <v>1</v>
       </c>
-      <c r="Z92" s="97" t="s">
+      <c r="Z92" s="100" t="s">
         <v>65</v>
       </c>
-      <c r="AA92" s="98"/>
-      <c r="AB92" s="98"/>
+      <c r="AA92" s="101"/>
+      <c r="AB92" s="101"/>
       <c r="AC92" s="65"/>
       <c r="AD92" s="65"/>
     </row>
@@ -8957,9 +8957,9 @@
       <c r="Y93" s="57">
         <v>1</v>
       </c>
-      <c r="Z93" s="97"/>
-      <c r="AA93" s="98"/>
-      <c r="AB93" s="98"/>
+      <c r="Z93" s="100"/>
+      <c r="AA93" s="101"/>
+      <c r="AB93" s="101"/>
       <c r="AC93" s="65"/>
       <c r="AD93" s="65"/>
     </row>
@@ -9040,11 +9040,11 @@
       <c r="Y94" s="33">
         <v>1</v>
       </c>
-      <c r="Z94" s="97" t="s">
+      <c r="Z94" s="100" t="s">
         <v>68</v>
       </c>
-      <c r="AA94" s="99"/>
-      <c r="AB94" s="99"/>
+      <c r="AA94" s="102"/>
+      <c r="AB94" s="102"/>
     </row>
     <row r="95" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
@@ -9123,11 +9123,11 @@
       <c r="Y95" s="1">
         <v>1</v>
       </c>
-      <c r="Z95" s="112" t="s">
+      <c r="Z95" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="AA95" s="113"/>
-      <c r="AB95" s="113"/>
+      <c r="AA95" s="104"/>
+      <c r="AB95" s="104"/>
     </row>
     <row r="96" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
@@ -9207,9 +9207,9 @@
       <c r="Y96" s="1">
         <v>1</v>
       </c>
-      <c r="Z96" s="112"/>
-      <c r="AA96" s="113"/>
-      <c r="AB96" s="113"/>
+      <c r="Z96" s="103"/>
+      <c r="AA96" s="104"/>
+      <c r="AB96" s="104"/>
     </row>
     <row r="97" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
@@ -9289,9 +9289,9 @@
       <c r="Y97" s="1">
         <v>1</v>
       </c>
-      <c r="Z97" s="112"/>
-      <c r="AA97" s="113"/>
-      <c r="AB97" s="113"/>
+      <c r="Z97" s="103"/>
+      <c r="AA97" s="104"/>
+      <c r="AB97" s="104"/>
     </row>
     <row r="98" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
@@ -9371,9 +9371,9 @@
       <c r="Y98" s="1">
         <v>1</v>
       </c>
-      <c r="Z98" s="112"/>
-      <c r="AA98" s="113"/>
-      <c r="AB98" s="113"/>
+      <c r="Z98" s="103"/>
+      <c r="AA98" s="104"/>
+      <c r="AB98" s="104"/>
     </row>
     <row r="99" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
@@ -9453,9 +9453,9 @@
       <c r="Y99" s="1">
         <v>1</v>
       </c>
-      <c r="Z99" s="112"/>
-      <c r="AA99" s="113"/>
-      <c r="AB99" s="113"/>
+      <c r="Z99" s="103"/>
+      <c r="AA99" s="104"/>
+      <c r="AB99" s="104"/>
     </row>
     <row r="100" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
@@ -9535,9 +9535,9 @@
       <c r="Y100" s="1">
         <v>1</v>
       </c>
-      <c r="Z100" s="112"/>
-      <c r="AA100" s="113"/>
-      <c r="AB100" s="113"/>
+      <c r="Z100" s="103"/>
+      <c r="AA100" s="104"/>
+      <c r="AB100" s="104"/>
     </row>
     <row r="101" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
@@ -9617,9 +9617,9 @@
       <c r="Y101" s="1">
         <v>1</v>
       </c>
-      <c r="Z101" s="112"/>
-      <c r="AA101" s="113"/>
-      <c r="AB101" s="113"/>
+      <c r="Z101" s="103"/>
+      <c r="AA101" s="104"/>
+      <c r="AB101" s="104"/>
     </row>
     <row r="102" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
@@ -9699,9 +9699,9 @@
       <c r="Y102" s="1">
         <v>1</v>
       </c>
-      <c r="Z102" s="112"/>
-      <c r="AA102" s="113"/>
-      <c r="AB102" s="113"/>
+      <c r="Z102" s="103"/>
+      <c r="AA102" s="104"/>
+      <c r="AB102" s="104"/>
     </row>
     <row r="103" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
@@ -9781,9 +9781,9 @@
       <c r="Y103" s="1">
         <v>1</v>
       </c>
-      <c r="Z103" s="112"/>
-      <c r="AA103" s="113"/>
-      <c r="AB103" s="113"/>
+      <c r="Z103" s="103"/>
+      <c r="AA103" s="104"/>
+      <c r="AB103" s="104"/>
     </row>
     <row r="104" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
@@ -9863,9 +9863,9 @@
       <c r="Y104" s="1">
         <v>1</v>
       </c>
-      <c r="Z104" s="112"/>
-      <c r="AA104" s="113"/>
-      <c r="AB104" s="113"/>
+      <c r="Z104" s="103"/>
+      <c r="AA104" s="104"/>
+      <c r="AB104" s="104"/>
     </row>
     <row r="105" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
@@ -9945,9 +9945,9 @@
       <c r="Y105" s="1">
         <v>1</v>
       </c>
-      <c r="Z105" s="112"/>
-      <c r="AA105" s="113"/>
-      <c r="AB105" s="113"/>
+      <c r="Z105" s="103"/>
+      <c r="AA105" s="104"/>
+      <c r="AB105" s="104"/>
     </row>
     <row r="106" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
@@ -10027,9 +10027,9 @@
       <c r="Y106" s="1">
         <v>1</v>
       </c>
-      <c r="Z106" s="112"/>
-      <c r="AA106" s="113"/>
-      <c r="AB106" s="113"/>
+      <c r="Z106" s="103"/>
+      <c r="AA106" s="104"/>
+      <c r="AB106" s="104"/>
     </row>
     <row r="107" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
@@ -10108,9 +10108,9 @@
       <c r="Y107" s="1">
         <v>1</v>
       </c>
-      <c r="Z107" s="112"/>
-      <c r="AA107" s="113"/>
-      <c r="AB107" s="113"/>
+      <c r="Z107" s="103"/>
+      <c r="AA107" s="104"/>
+      <c r="AB107" s="104"/>
     </row>
     <row r="108" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
@@ -10189,9 +10189,9 @@
       <c r="Y108" s="1">
         <v>1</v>
       </c>
-      <c r="Z108" s="112"/>
-      <c r="AA108" s="113"/>
-      <c r="AB108" s="113"/>
+      <c r="Z108" s="103"/>
+      <c r="AA108" s="104"/>
+      <c r="AB108" s="104"/>
     </row>
     <row r="109" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
@@ -10270,9 +10270,9 @@
       <c r="Y109" s="1">
         <v>1</v>
       </c>
-      <c r="Z109" s="112"/>
-      <c r="AA109" s="113"/>
-      <c r="AB109" s="113"/>
+      <c r="Z109" s="103"/>
+      <c r="AA109" s="104"/>
+      <c r="AB109" s="104"/>
     </row>
     <row r="110" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
@@ -10351,9 +10351,9 @@
       <c r="Y110" s="1">
         <v>1</v>
       </c>
-      <c r="Z110" s="112"/>
-      <c r="AA110" s="113"/>
-      <c r="AB110" s="113"/>
+      <c r="Z110" s="103"/>
+      <c r="AA110" s="104"/>
+      <c r="AB110" s="104"/>
     </row>
     <row r="111" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
@@ -10432,9 +10432,9 @@
       <c r="Y111" s="1">
         <v>1</v>
       </c>
-      <c r="Z111" s="112"/>
-      <c r="AA111" s="113"/>
-      <c r="AB111" s="113"/>
+      <c r="Z111" s="103"/>
+      <c r="AA111" s="104"/>
+      <c r="AB111" s="104"/>
     </row>
     <row r="112" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A112" s="43">
@@ -10513,11 +10513,11 @@
       <c r="Y112" s="43">
         <v>1</v>
       </c>
-      <c r="Z112" s="97" t="s">
+      <c r="Z112" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="AA112" s="99"/>
-      <c r="AB112" s="99"/>
+      <c r="AA112" s="102"/>
+      <c r="AB112" s="102"/>
     </row>
     <row r="113" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
@@ -10597,9 +10597,9 @@
       <c r="Y113" s="1">
         <v>1</v>
       </c>
-      <c r="Z113" s="97"/>
-      <c r="AA113" s="99"/>
-      <c r="AB113" s="99"/>
+      <c r="Z113" s="100"/>
+      <c r="AA113" s="102"/>
+      <c r="AB113" s="102"/>
     </row>
     <row r="114" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
@@ -10679,9 +10679,9 @@
       <c r="Y114" s="1">
         <v>1</v>
       </c>
-      <c r="Z114" s="97"/>
-      <c r="AA114" s="99"/>
-      <c r="AB114" s="99"/>
+      <c r="Z114" s="100"/>
+      <c r="AA114" s="102"/>
+      <c r="AB114" s="102"/>
     </row>
     <row r="115" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
@@ -10761,9 +10761,9 @@
       <c r="Y115" s="1">
         <v>1</v>
       </c>
-      <c r="Z115" s="97"/>
-      <c r="AA115" s="99"/>
-      <c r="AB115" s="99"/>
+      <c r="Z115" s="100"/>
+      <c r="AA115" s="102"/>
+      <c r="AB115" s="102"/>
     </row>
     <row r="116" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
@@ -10843,9 +10843,9 @@
       <c r="Y116" s="1">
         <v>1</v>
       </c>
-      <c r="Z116" s="97"/>
-      <c r="AA116" s="99"/>
-      <c r="AB116" s="99"/>
+      <c r="Z116" s="100"/>
+      <c r="AA116" s="102"/>
+      <c r="AB116" s="102"/>
     </row>
     <row r="117" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
@@ -10925,9 +10925,9 @@
       <c r="Y117" s="1">
         <v>1</v>
       </c>
-      <c r="Z117" s="97"/>
-      <c r="AA117" s="99"/>
-      <c r="AB117" s="99"/>
+      <c r="Z117" s="100"/>
+      <c r="AA117" s="102"/>
+      <c r="AB117" s="102"/>
     </row>
     <row r="118" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
@@ -11007,9 +11007,9 @@
       <c r="Y118" s="1">
         <v>1</v>
       </c>
-      <c r="Z118" s="97"/>
-      <c r="AA118" s="99"/>
-      <c r="AB118" s="99"/>
+      <c r="Z118" s="100"/>
+      <c r="AA118" s="102"/>
+      <c r="AB118" s="102"/>
     </row>
     <row r="119" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
@@ -11089,9 +11089,9 @@
       <c r="Y119" s="1">
         <v>1</v>
       </c>
-      <c r="Z119" s="97"/>
-      <c r="AA119" s="99"/>
-      <c r="AB119" s="99"/>
+      <c r="Z119" s="100"/>
+      <c r="AA119" s="102"/>
+      <c r="AB119" s="102"/>
     </row>
     <row r="120" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
@@ -11171,9 +11171,9 @@
       <c r="Y120" s="1">
         <v>1</v>
       </c>
-      <c r="Z120" s="97"/>
-      <c r="AA120" s="99"/>
-      <c r="AB120" s="99"/>
+      <c r="Z120" s="100"/>
+      <c r="AA120" s="102"/>
+      <c r="AB120" s="102"/>
     </row>
     <row r="121" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
@@ -11253,9 +11253,9 @@
       <c r="Y121" s="1">
         <v>1</v>
       </c>
-      <c r="Z121" s="97"/>
-      <c r="AA121" s="99"/>
-      <c r="AB121" s="99"/>
+      <c r="Z121" s="100"/>
+      <c r="AA121" s="102"/>
+      <c r="AB121" s="102"/>
     </row>
     <row r="122" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
@@ -11335,9 +11335,9 @@
       <c r="Y122" s="1">
         <v>1</v>
       </c>
-      <c r="Z122" s="97"/>
-      <c r="AA122" s="99"/>
-      <c r="AB122" s="99"/>
+      <c r="Z122" s="100"/>
+      <c r="AA122" s="102"/>
+      <c r="AB122" s="102"/>
     </row>
     <row r="123" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
@@ -11416,9 +11416,9 @@
       <c r="Y123" s="1">
         <v>1</v>
       </c>
-      <c r="Z123" s="97"/>
-      <c r="AA123" s="99"/>
-      <c r="AB123" s="99"/>
+      <c r="Z123" s="100"/>
+      <c r="AA123" s="102"/>
+      <c r="AB123" s="102"/>
     </row>
     <row r="124" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
@@ -11497,9 +11497,9 @@
       <c r="Y124" s="1">
         <v>1</v>
       </c>
-      <c r="Z124" s="97"/>
-      <c r="AA124" s="99"/>
-      <c r="AB124" s="99"/>
+      <c r="Z124" s="100"/>
+      <c r="AA124" s="102"/>
+      <c r="AB124" s="102"/>
     </row>
     <row r="125" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
@@ -11578,9 +11578,9 @@
       <c r="Y125" s="1">
         <v>1</v>
       </c>
-      <c r="Z125" s="97"/>
-      <c r="AA125" s="99"/>
-      <c r="AB125" s="99"/>
+      <c r="Z125" s="100"/>
+      <c r="AA125" s="102"/>
+      <c r="AB125" s="102"/>
     </row>
     <row r="126" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
@@ -11659,9 +11659,9 @@
       <c r="Y126" s="1">
         <v>1</v>
       </c>
-      <c r="Z126" s="97"/>
-      <c r="AA126" s="99"/>
-      <c r="AB126" s="99"/>
+      <c r="Z126" s="100"/>
+      <c r="AA126" s="102"/>
+      <c r="AB126" s="102"/>
     </row>
     <row r="127" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
@@ -11740,9 +11740,9 @@
       <c r="Y127" s="1">
         <v>1</v>
       </c>
-      <c r="Z127" s="97"/>
-      <c r="AA127" s="99"/>
-      <c r="AB127" s="99"/>
+      <c r="Z127" s="100"/>
+      <c r="AA127" s="102"/>
+      <c r="AB127" s="102"/>
     </row>
     <row r="128" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
@@ -11821,9 +11821,9 @@
       <c r="Y128" s="1">
         <v>1</v>
       </c>
-      <c r="Z128" s="97"/>
-      <c r="AA128" s="99"/>
-      <c r="AB128" s="99"/>
+      <c r="Z128" s="100"/>
+      <c r="AA128" s="102"/>
+      <c r="AB128" s="102"/>
     </row>
     <row r="129" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
@@ -11902,9 +11902,9 @@
       <c r="Y129" s="1">
         <v>1</v>
       </c>
-      <c r="Z129" s="97"/>
-      <c r="AA129" s="99"/>
-      <c r="AB129" s="99"/>
+      <c r="Z129" s="100"/>
+      <c r="AA129" s="102"/>
+      <c r="AB129" s="102"/>
     </row>
     <row r="130" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A130" s="43">
@@ -11983,11 +11983,11 @@
       <c r="Y130" s="43">
         <v>1</v>
       </c>
-      <c r="Z130" s="97" t="s">
+      <c r="Z130" s="100" t="s">
         <v>72</v>
       </c>
-      <c r="AA130" s="99"/>
-      <c r="AB130" s="99"/>
+      <c r="AA130" s="102"/>
+      <c r="AB130" s="102"/>
     </row>
     <row r="131" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
@@ -12067,9 +12067,9 @@
       <c r="Y131" s="1">
         <v>1</v>
       </c>
-      <c r="Z131" s="97"/>
-      <c r="AA131" s="99"/>
-      <c r="AB131" s="99"/>
+      <c r="Z131" s="100"/>
+      <c r="AA131" s="102"/>
+      <c r="AB131" s="102"/>
     </row>
     <row r="132" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
@@ -12149,9 +12149,9 @@
       <c r="Y132" s="1">
         <v>1</v>
       </c>
-      <c r="Z132" s="97"/>
-      <c r="AA132" s="99"/>
-      <c r="AB132" s="99"/>
+      <c r="Z132" s="100"/>
+      <c r="AA132" s="102"/>
+      <c r="AB132" s="102"/>
     </row>
     <row r="133" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
@@ -12231,9 +12231,9 @@
       <c r="Y133" s="1">
         <v>1</v>
       </c>
-      <c r="Z133" s="97"/>
-      <c r="AA133" s="99"/>
-      <c r="AB133" s="99"/>
+      <c r="Z133" s="100"/>
+      <c r="AA133" s="102"/>
+      <c r="AB133" s="102"/>
     </row>
     <row r="134" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
@@ -12313,9 +12313,9 @@
       <c r="Y134" s="1">
         <v>1</v>
       </c>
-      <c r="Z134" s="97"/>
-      <c r="AA134" s="99"/>
-      <c r="AB134" s="99"/>
+      <c r="Z134" s="100"/>
+      <c r="AA134" s="102"/>
+      <c r="AB134" s="102"/>
     </row>
     <row r="135" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
@@ -12395,9 +12395,9 @@
       <c r="Y135" s="1">
         <v>1</v>
       </c>
-      <c r="Z135" s="97"/>
-      <c r="AA135" s="99"/>
-      <c r="AB135" s="99"/>
+      <c r="Z135" s="100"/>
+      <c r="AA135" s="102"/>
+      <c r="AB135" s="102"/>
     </row>
     <row r="136" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
@@ -12477,9 +12477,9 @@
       <c r="Y136" s="1">
         <v>1</v>
       </c>
-      <c r="Z136" s="97"/>
-      <c r="AA136" s="99"/>
-      <c r="AB136" s="99"/>
+      <c r="Z136" s="100"/>
+      <c r="AA136" s="102"/>
+      <c r="AB136" s="102"/>
     </row>
     <row r="137" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
@@ -12559,9 +12559,9 @@
       <c r="Y137" s="1">
         <v>1</v>
       </c>
-      <c r="Z137" s="97"/>
-      <c r="AA137" s="99"/>
-      <c r="AB137" s="99"/>
+      <c r="Z137" s="100"/>
+      <c r="AA137" s="102"/>
+      <c r="AB137" s="102"/>
     </row>
     <row r="138" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
@@ -12641,9 +12641,9 @@
       <c r="Y138" s="1">
         <v>1</v>
       </c>
-      <c r="Z138" s="97"/>
-      <c r="AA138" s="99"/>
-      <c r="AB138" s="99"/>
+      <c r="Z138" s="100"/>
+      <c r="AA138" s="102"/>
+      <c r="AB138" s="102"/>
     </row>
     <row r="139" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
@@ -12723,9 +12723,9 @@
       <c r="Y139" s="1">
         <v>1</v>
       </c>
-      <c r="Z139" s="97"/>
-      <c r="AA139" s="99"/>
-      <c r="AB139" s="99"/>
+      <c r="Z139" s="100"/>
+      <c r="AA139" s="102"/>
+      <c r="AB139" s="102"/>
     </row>
     <row r="140" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
@@ -12805,9 +12805,9 @@
       <c r="Y140" s="1">
         <v>1</v>
       </c>
-      <c r="Z140" s="97"/>
-      <c r="AA140" s="99"/>
-      <c r="AB140" s="99"/>
+      <c r="Z140" s="100"/>
+      <c r="AA140" s="102"/>
+      <c r="AB140" s="102"/>
     </row>
     <row r="141" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
@@ -12886,9 +12886,9 @@
       <c r="Y141" s="1">
         <v>1</v>
       </c>
-      <c r="Z141" s="97"/>
-      <c r="AA141" s="99"/>
-      <c r="AB141" s="99"/>
+      <c r="Z141" s="100"/>
+      <c r="AA141" s="102"/>
+      <c r="AB141" s="102"/>
     </row>
     <row r="142" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
@@ -12967,9 +12967,9 @@
       <c r="Y142" s="1">
         <v>1</v>
       </c>
-      <c r="Z142" s="97"/>
-      <c r="AA142" s="99"/>
-      <c r="AB142" s="99"/>
+      <c r="Z142" s="100"/>
+      <c r="AA142" s="102"/>
+      <c r="AB142" s="102"/>
     </row>
     <row r="143" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
@@ -13048,9 +13048,9 @@
       <c r="Y143" s="1">
         <v>1</v>
       </c>
-      <c r="Z143" s="97"/>
-      <c r="AA143" s="99"/>
-      <c r="AB143" s="99"/>
+      <c r="Z143" s="100"/>
+      <c r="AA143" s="102"/>
+      <c r="AB143" s="102"/>
     </row>
     <row r="144" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
@@ -13129,9 +13129,9 @@
       <c r="Y144" s="1">
         <v>1</v>
       </c>
-      <c r="Z144" s="97"/>
-      <c r="AA144" s="99"/>
-      <c r="AB144" s="99"/>
+      <c r="Z144" s="100"/>
+      <c r="AA144" s="102"/>
+      <c r="AB144" s="102"/>
     </row>
     <row r="145" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
@@ -13210,9 +13210,9 @@
       <c r="Y145" s="1">
         <v>1</v>
       </c>
-      <c r="Z145" s="97"/>
-      <c r="AA145" s="99"/>
-      <c r="AB145" s="99"/>
+      <c r="Z145" s="100"/>
+      <c r="AA145" s="102"/>
+      <c r="AB145" s="102"/>
     </row>
     <row r="146" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
@@ -13291,9 +13291,9 @@
       <c r="Y146" s="1">
         <v>1</v>
       </c>
-      <c r="Z146" s="97"/>
-      <c r="AA146" s="99"/>
-      <c r="AB146" s="99"/>
+      <c r="Z146" s="100"/>
+      <c r="AA146" s="102"/>
+      <c r="AB146" s="102"/>
     </row>
     <row r="147" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
@@ -13372,9 +13372,9 @@
       <c r="Y147" s="1">
         <v>1</v>
       </c>
-      <c r="Z147" s="97"/>
-      <c r="AA147" s="99"/>
-      <c r="AB147" s="99"/>
+      <c r="Z147" s="100"/>
+      <c r="AA147" s="102"/>
+      <c r="AB147" s="102"/>
     </row>
     <row r="148" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="43">
@@ -13453,11 +13453,11 @@
       <c r="Y148" s="40">
         <v>1</v>
       </c>
-      <c r="Z148" s="97" t="s">
+      <c r="Z148" s="100" t="s">
         <v>73</v>
       </c>
-      <c r="AA148" s="98"/>
-      <c r="AB148" s="98"/>
+      <c r="AA148" s="101"/>
+      <c r="AB148" s="101"/>
     </row>
     <row r="149" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
@@ -13537,9 +13537,9 @@
       <c r="Y149" s="50">
         <v>1</v>
       </c>
-      <c r="Z149" s="97"/>
-      <c r="AA149" s="98"/>
-      <c r="AB149" s="98"/>
+      <c r="Z149" s="100"/>
+      <c r="AA149" s="101"/>
+      <c r="AB149" s="101"/>
     </row>
     <row r="150" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
@@ -13619,9 +13619,9 @@
       <c r="Y150" s="50">
         <v>1</v>
       </c>
-      <c r="Z150" s="97"/>
-      <c r="AA150" s="98"/>
-      <c r="AB150" s="98"/>
+      <c r="Z150" s="100"/>
+      <c r="AA150" s="101"/>
+      <c r="AB150" s="101"/>
     </row>
     <row r="151" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
@@ -13700,9 +13700,9 @@
       <c r="Y151" s="50">
         <v>1</v>
       </c>
-      <c r="Z151" s="97"/>
-      <c r="AA151" s="98"/>
-      <c r="AB151" s="98"/>
+      <c r="Z151" s="100"/>
+      <c r="AA151" s="101"/>
+      <c r="AB151" s="101"/>
     </row>
     <row r="152" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A152" s="27">
@@ -13781,9 +13781,9 @@
       <c r="Y152" s="50">
         <v>1</v>
       </c>
-      <c r="Z152" s="97"/>
-      <c r="AA152" s="98"/>
-      <c r="AB152" s="98"/>
+      <c r="Z152" s="100"/>
+      <c r="AA152" s="101"/>
+      <c r="AB152" s="101"/>
     </row>
     <row r="153" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
@@ -13862,11 +13862,11 @@
       <c r="Y153" s="43">
         <v>1</v>
       </c>
-      <c r="Z153" s="97" t="s">
+      <c r="Z153" s="100" t="s">
         <v>74</v>
       </c>
-      <c r="AA153" s="98"/>
-      <c r="AB153" s="98"/>
+      <c r="AA153" s="101"/>
+      <c r="AB153" s="101"/>
     </row>
     <row r="154" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
@@ -13946,9 +13946,9 @@
       <c r="Y154" s="1">
         <v>1</v>
       </c>
-      <c r="Z154" s="97"/>
-      <c r="AA154" s="98"/>
-      <c r="AB154" s="98"/>
+      <c r="Z154" s="100"/>
+      <c r="AA154" s="101"/>
+      <c r="AB154" s="101"/>
     </row>
     <row r="155" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
@@ -14028,9 +14028,9 @@
       <c r="Y155" s="1">
         <v>1</v>
       </c>
-      <c r="Z155" s="97"/>
-      <c r="AA155" s="98"/>
-      <c r="AB155" s="98"/>
+      <c r="Z155" s="100"/>
+      <c r="AA155" s="101"/>
+      <c r="AB155" s="101"/>
     </row>
     <row r="156" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
@@ -14110,9 +14110,9 @@
       <c r="Y156" s="1">
         <v>1</v>
       </c>
-      <c r="Z156" s="97"/>
-      <c r="AA156" s="98"/>
-      <c r="AB156" s="98"/>
+      <c r="Z156" s="100"/>
+      <c r="AA156" s="101"/>
+      <c r="AB156" s="101"/>
     </row>
     <row r="157" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
@@ -14192,9 +14192,9 @@
       <c r="Y157" s="1">
         <v>1</v>
       </c>
-      <c r="Z157" s="97"/>
-      <c r="AA157" s="98"/>
-      <c r="AB157" s="98"/>
+      <c r="Z157" s="100"/>
+      <c r="AA157" s="101"/>
+      <c r="AB157" s="101"/>
     </row>
     <row r="158" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A158" s="43">
@@ -14273,11 +14273,11 @@
       <c r="Y158" s="43">
         <v>1</v>
       </c>
-      <c r="Z158" s="97" t="s">
+      <c r="Z158" s="100" t="s">
         <v>75</v>
       </c>
-      <c r="AA158" s="98"/>
-      <c r="AB158" s="98"/>
+      <c r="AA158" s="101"/>
+      <c r="AB158" s="101"/>
     </row>
     <row r="159" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
@@ -14357,9 +14357,9 @@
       <c r="Y159" s="1">
         <v>1</v>
       </c>
-      <c r="Z159" s="97"/>
-      <c r="AA159" s="98"/>
-      <c r="AB159" s="98"/>
+      <c r="Z159" s="100"/>
+      <c r="AA159" s="101"/>
+      <c r="AB159" s="101"/>
     </row>
     <row r="160" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
@@ -14439,9 +14439,9 @@
       <c r="Y160" s="1">
         <v>1</v>
       </c>
-      <c r="Z160" s="97"/>
-      <c r="AA160" s="98"/>
-      <c r="AB160" s="98"/>
+      <c r="Z160" s="100"/>
+      <c r="AA160" s="101"/>
+      <c r="AB160" s="101"/>
     </row>
     <row r="161" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
@@ -14521,9 +14521,9 @@
       <c r="Y161" s="1">
         <v>1</v>
       </c>
-      <c r="Z161" s="97"/>
-      <c r="AA161" s="98"/>
-      <c r="AB161" s="98"/>
+      <c r="Z161" s="100"/>
+      <c r="AA161" s="101"/>
+      <c r="AB161" s="101"/>
     </row>
     <row r="162" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A162" s="27">
@@ -14603,9 +14603,9 @@
       <c r="Y162" s="27">
         <v>1</v>
       </c>
-      <c r="Z162" s="97"/>
-      <c r="AA162" s="98"/>
-      <c r="AB162" s="98"/>
+      <c r="Z162" s="100"/>
+      <c r="AA162" s="101"/>
+      <c r="AB162" s="101"/>
     </row>
     <row r="163" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A163" s="43">
@@ -14684,11 +14684,11 @@
       <c r="Y163" s="40">
         <v>1</v>
       </c>
-      <c r="Z163" s="97" t="s">
+      <c r="Z163" s="100" t="s">
         <v>76</v>
       </c>
-      <c r="AA163" s="98"/>
-      <c r="AB163" s="98"/>
+      <c r="AA163" s="101"/>
+      <c r="AB163" s="101"/>
     </row>
     <row r="164" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A164" s="43">
@@ -14767,11 +14767,11 @@
       <c r="Y164" s="40">
         <v>1</v>
       </c>
-      <c r="Z164" s="97" t="s">
+      <c r="Z164" s="100" t="s">
         <v>77</v>
       </c>
-      <c r="AA164" s="98"/>
-      <c r="AB164" s="98"/>
+      <c r="AA164" s="101"/>
+      <c r="AB164" s="101"/>
     </row>
     <row r="165" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A165" s="43">
@@ -14850,11 +14850,11 @@
       <c r="Y165" s="40">
         <v>1</v>
       </c>
-      <c r="Z165" s="97" t="s">
+      <c r="Z165" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="AA165" s="98"/>
-      <c r="AB165" s="98"/>
+      <c r="AA165" s="101"/>
+      <c r="AB165" s="101"/>
     </row>
     <row r="166" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A166" s="43">
@@ -14933,11 +14933,11 @@
       <c r="Y166" s="40">
         <v>1</v>
       </c>
-      <c r="Z166" s="97" t="s">
+      <c r="Z166" s="100" t="s">
         <v>80</v>
       </c>
-      <c r="AA166" s="98"/>
-      <c r="AB166" s="98"/>
+      <c r="AA166" s="101"/>
+      <c r="AB166" s="101"/>
     </row>
     <row r="167" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A167" s="43">
@@ -15016,11 +15016,11 @@
       <c r="Y167" s="40">
         <v>1</v>
       </c>
-      <c r="Z167" s="97" t="s">
+      <c r="Z167" s="100" t="s">
         <v>79</v>
       </c>
-      <c r="AA167" s="98"/>
-      <c r="AB167" s="98"/>
+      <c r="AA167" s="101"/>
+      <c r="AB167" s="101"/>
     </row>
     <row r="168" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A168" s="43">
@@ -15099,11 +15099,11 @@
       <c r="Y168" s="40">
         <v>1</v>
       </c>
-      <c r="Z168" s="97" t="s">
+      <c r="Z168" s="100" t="s">
         <v>81</v>
       </c>
-      <c r="AA168" s="98"/>
-      <c r="AB168" s="98"/>
+      <c r="AA168" s="101"/>
+      <c r="AB168" s="101"/>
     </row>
     <row r="169" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="43">
@@ -15182,11 +15182,11 @@
       <c r="Y169" s="40">
         <v>1</v>
       </c>
-      <c r="Z169" s="112" t="s">
+      <c r="Z169" s="103" t="s">
         <v>82</v>
       </c>
-      <c r="AA169" s="113"/>
-      <c r="AB169" s="113"/>
+      <c r="AA169" s="104"/>
+      <c r="AB169" s="104"/>
     </row>
     <row r="170" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
@@ -15265,9 +15265,9 @@
       <c r="Y170" s="50">
         <v>1</v>
       </c>
-      <c r="Z170" s="112"/>
-      <c r="AA170" s="113"/>
-      <c r="AB170" s="113"/>
+      <c r="Z170" s="103"/>
+      <c r="AA170" s="104"/>
+      <c r="AB170" s="104"/>
     </row>
     <row r="171" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
@@ -15346,9 +15346,9 @@
       <c r="Y171" s="50">
         <v>1</v>
       </c>
-      <c r="Z171" s="112"/>
-      <c r="AA171" s="113"/>
-      <c r="AB171" s="113"/>
+      <c r="Z171" s="103"/>
+      <c r="AA171" s="104"/>
+      <c r="AB171" s="104"/>
     </row>
     <row r="172" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
@@ -15427,9 +15427,9 @@
       <c r="Y172" s="50">
         <v>1</v>
       </c>
-      <c r="Z172" s="112"/>
-      <c r="AA172" s="113"/>
-      <c r="AB172" s="113"/>
+      <c r="Z172" s="103"/>
+      <c r="AA172" s="104"/>
+      <c r="AB172" s="104"/>
     </row>
     <row r="173" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
@@ -15508,9 +15508,9 @@
       <c r="Y173" s="50">
         <v>1</v>
       </c>
-      <c r="Z173" s="112"/>
-      <c r="AA173" s="113"/>
-      <c r="AB173" s="113"/>
+      <c r="Z173" s="103"/>
+      <c r="AA173" s="104"/>
+      <c r="AB173" s="104"/>
     </row>
     <row r="174" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
@@ -15589,9 +15589,9 @@
       <c r="Y174" s="50">
         <v>1</v>
       </c>
-      <c r="Z174" s="112"/>
-      <c r="AA174" s="113"/>
-      <c r="AB174" s="113"/>
+      <c r="Z174" s="103"/>
+      <c r="AA174" s="104"/>
+      <c r="AB174" s="104"/>
     </row>
     <row r="175" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
@@ -15670,9 +15670,9 @@
       <c r="Y175" s="50">
         <v>1</v>
       </c>
-      <c r="Z175" s="112"/>
-      <c r="AA175" s="113"/>
-      <c r="AB175" s="113"/>
+      <c r="Z175" s="103"/>
+      <c r="AA175" s="104"/>
+      <c r="AB175" s="104"/>
     </row>
     <row r="176" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A176" s="43">
@@ -15751,11 +15751,11 @@
       <c r="Y176" s="40">
         <v>1</v>
       </c>
-      <c r="Z176" s="97" t="s">
+      <c r="Z176" s="100" t="s">
         <v>83</v>
       </c>
-      <c r="AA176" s="99"/>
-      <c r="AB176" s="99"/>
+      <c r="AA176" s="102"/>
+      <c r="AB176" s="102"/>
     </row>
     <row r="177" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
@@ -15835,9 +15835,9 @@
       <c r="Y177" s="50">
         <v>1</v>
       </c>
-      <c r="Z177" s="97"/>
-      <c r="AA177" s="99"/>
-      <c r="AB177" s="99"/>
+      <c r="Z177" s="100"/>
+      <c r="AA177" s="102"/>
+      <c r="AB177" s="102"/>
     </row>
     <row r="178" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
@@ -15917,9 +15917,9 @@
       <c r="Y178" s="50">
         <v>1</v>
       </c>
-      <c r="Z178" s="97"/>
-      <c r="AA178" s="99"/>
-      <c r="AB178" s="99"/>
+      <c r="Z178" s="100"/>
+      <c r="AA178" s="102"/>
+      <c r="AB178" s="102"/>
     </row>
     <row r="179" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
@@ -15999,9 +15999,9 @@
       <c r="Y179" s="50">
         <v>1</v>
       </c>
-      <c r="Z179" s="97"/>
-      <c r="AA179" s="99"/>
-      <c r="AB179" s="99"/>
+      <c r="Z179" s="100"/>
+      <c r="AA179" s="102"/>
+      <c r="AB179" s="102"/>
     </row>
     <row r="180" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
@@ -16081,9 +16081,9 @@
       <c r="Y180" s="50">
         <v>1</v>
       </c>
-      <c r="Z180" s="97"/>
-      <c r="AA180" s="99"/>
-      <c r="AB180" s="99"/>
+      <c r="Z180" s="100"/>
+      <c r="AA180" s="102"/>
+      <c r="AB180" s="102"/>
     </row>
     <row r="181" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
@@ -16163,9 +16163,9 @@
       <c r="Y181" s="50">
         <v>1</v>
       </c>
-      <c r="Z181" s="97"/>
-      <c r="AA181" s="99"/>
-      <c r="AB181" s="99"/>
+      <c r="Z181" s="100"/>
+      <c r="AA181" s="102"/>
+      <c r="AB181" s="102"/>
     </row>
     <row r="182" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
@@ -16245,9 +16245,9 @@
       <c r="Y182" s="50">
         <v>1</v>
       </c>
-      <c r="Z182" s="97"/>
-      <c r="AA182" s="99"/>
-      <c r="AB182" s="99"/>
+      <c r="Z182" s="100"/>
+      <c r="AA182" s="102"/>
+      <c r="AB182" s="102"/>
     </row>
     <row r="183" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
@@ -16327,9 +16327,9 @@
       <c r="Y183" s="50">
         <v>1</v>
       </c>
-      <c r="Z183" s="97"/>
-      <c r="AA183" s="99"/>
-      <c r="AB183" s="99"/>
+      <c r="Z183" s="100"/>
+      <c r="AA183" s="102"/>
+      <c r="AB183" s="102"/>
     </row>
     <row r="184" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
@@ -16409,9 +16409,9 @@
       <c r="Y184" s="50">
         <v>1</v>
       </c>
-      <c r="Z184" s="97"/>
-      <c r="AA184" s="99"/>
-      <c r="AB184" s="99"/>
+      <c r="Z184" s="100"/>
+      <c r="AA184" s="102"/>
+      <c r="AB184" s="102"/>
     </row>
     <row r="185" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
@@ -16491,9 +16491,9 @@
       <c r="Y185" s="50">
         <v>1</v>
       </c>
-      <c r="Z185" s="97"/>
-      <c r="AA185" s="99"/>
-      <c r="AB185" s="99"/>
+      <c r="Z185" s="100"/>
+      <c r="AA185" s="102"/>
+      <c r="AB185" s="102"/>
     </row>
     <row r="186" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
@@ -16573,9 +16573,9 @@
       <c r="Y186" s="50">
         <v>1</v>
       </c>
-      <c r="Z186" s="97"/>
-      <c r="AA186" s="99"/>
-      <c r="AB186" s="99"/>
+      <c r="Z186" s="100"/>
+      <c r="AA186" s="102"/>
+      <c r="AB186" s="102"/>
     </row>
     <row r="187" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
@@ -16655,9 +16655,9 @@
       <c r="Y187" s="50">
         <v>1</v>
       </c>
-      <c r="Z187" s="97"/>
-      <c r="AA187" s="99"/>
-      <c r="AB187" s="99"/>
+      <c r="Z187" s="100"/>
+      <c r="AA187" s="102"/>
+      <c r="AB187" s="102"/>
     </row>
     <row r="188" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
@@ -16737,9 +16737,9 @@
       <c r="Y188" s="50">
         <v>1</v>
       </c>
-      <c r="Z188" s="97"/>
-      <c r="AA188" s="99"/>
-      <c r="AB188" s="99"/>
+      <c r="Z188" s="100"/>
+      <c r="AA188" s="102"/>
+      <c r="AB188" s="102"/>
     </row>
     <row r="189" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
@@ -16819,9 +16819,9 @@
       <c r="Y189" s="50">
         <v>1</v>
       </c>
-      <c r="Z189" s="97"/>
-      <c r="AA189" s="99"/>
-      <c r="AB189" s="99"/>
+      <c r="Z189" s="100"/>
+      <c r="AA189" s="102"/>
+      <c r="AB189" s="102"/>
     </row>
     <row r="190" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
@@ -16901,9 +16901,9 @@
       <c r="Y190" s="50">
         <v>1</v>
       </c>
-      <c r="Z190" s="97"/>
-      <c r="AA190" s="99"/>
-      <c r="AB190" s="99"/>
+      <c r="Z190" s="100"/>
+      <c r="AA190" s="102"/>
+      <c r="AB190" s="102"/>
     </row>
     <row r="191" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
@@ -16983,9 +16983,9 @@
       <c r="Y191" s="50">
         <v>1</v>
       </c>
-      <c r="Z191" s="97"/>
-      <c r="AA191" s="99"/>
-      <c r="AB191" s="99"/>
+      <c r="Z191" s="100"/>
+      <c r="AA191" s="102"/>
+      <c r="AB191" s="102"/>
     </row>
     <row r="192" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
@@ -17065,9 +17065,9 @@
       <c r="Y192" s="50">
         <v>1</v>
       </c>
-      <c r="Z192" s="97"/>
-      <c r="AA192" s="99"/>
-      <c r="AB192" s="99"/>
+      <c r="Z192" s="100"/>
+      <c r="AA192" s="102"/>
+      <c r="AB192" s="102"/>
     </row>
     <row r="193" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A193" s="27">
@@ -17147,9 +17147,9 @@
       <c r="Y193" s="57">
         <v>1</v>
       </c>
-      <c r="Z193" s="97"/>
-      <c r="AA193" s="99"/>
-      <c r="AB193" s="99"/>
+      <c r="Z193" s="100"/>
+      <c r="AA193" s="102"/>
+      <c r="AB193" s="102"/>
     </row>
     <row r="194" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
@@ -17229,11 +17229,11 @@
       <c r="Y194" s="50">
         <v>1</v>
       </c>
-      <c r="Z194" s="97" t="s">
+      <c r="Z194" s="100" t="s">
         <v>84</v>
       </c>
-      <c r="AA194" s="99"/>
-      <c r="AB194" s="99"/>
+      <c r="AA194" s="102"/>
+      <c r="AB194" s="102"/>
     </row>
     <row r="195" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
@@ -17313,11 +17313,11 @@
       <c r="Y195" s="50">
         <v>1</v>
       </c>
-      <c r="Z195" s="97" t="s">
+      <c r="Z195" s="100" t="s">
         <v>85</v>
       </c>
-      <c r="AA195" s="99"/>
-      <c r="AB195" s="99"/>
+      <c r="AA195" s="102"/>
+      <c r="AB195" s="102"/>
     </row>
     <row r="196" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
@@ -17397,11 +17397,11 @@
       <c r="Y196" s="50">
         <v>1</v>
       </c>
-      <c r="Z196" s="97" t="s">
+      <c r="Z196" s="100" t="s">
         <v>86</v>
       </c>
-      <c r="AA196" s="99"/>
-      <c r="AB196" s="99"/>
+      <c r="AA196" s="102"/>
+      <c r="AB196" s="102"/>
     </row>
     <row r="197" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
@@ -17481,11 +17481,11 @@
       <c r="Y197" s="50">
         <v>1</v>
       </c>
-      <c r="Z197" s="97" t="s">
+      <c r="Z197" s="100" t="s">
         <v>87</v>
       </c>
-      <c r="AA197" s="99"/>
-      <c r="AB197" s="99"/>
+      <c r="AA197" s="102"/>
+      <c r="AB197" s="102"/>
     </row>
     <row r="198" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
@@ -17565,11 +17565,11 @@
       <c r="Y198" s="50">
         <v>1</v>
       </c>
-      <c r="Z198" s="97" t="s">
+      <c r="Z198" s="100" t="s">
         <v>84</v>
       </c>
-      <c r="AA198" s="99"/>
-      <c r="AB198" s="99"/>
+      <c r="AA198" s="102"/>
+      <c r="AB198" s="102"/>
     </row>
     <row r="199" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
@@ -17649,11 +17649,11 @@
       <c r="Y199" s="50">
         <v>1</v>
       </c>
-      <c r="Z199" s="97" t="s">
+      <c r="Z199" s="100" t="s">
         <v>85</v>
       </c>
-      <c r="AA199" s="99"/>
-      <c r="AB199" s="99"/>
+      <c r="AA199" s="102"/>
+      <c r="AB199" s="102"/>
     </row>
     <row r="200" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A200" s="27">
@@ -17733,11 +17733,11 @@
       <c r="Y200" s="57">
         <v>1</v>
       </c>
-      <c r="Z200" s="97" t="s">
+      <c r="Z200" s="100" t="s">
         <v>85</v>
       </c>
-      <c r="AA200" s="99"/>
-      <c r="AB200" s="99"/>
+      <c r="AA200" s="102"/>
+      <c r="AB200" s="102"/>
     </row>
     <row r="201" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A201" s="27">
@@ -17816,11 +17816,11 @@
       <c r="Y201" s="57">
         <v>1</v>
       </c>
-      <c r="Z201" s="97" t="s">
+      <c r="Z201" s="100" t="s">
         <v>88</v>
       </c>
-      <c r="AA201" s="99"/>
-      <c r="AB201" s="99"/>
+      <c r="AA201" s="102"/>
+      <c r="AB201" s="102"/>
     </row>
     <row r="202" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A202" s="27">
@@ -17899,11 +17899,11 @@
       <c r="Y202" s="57">
         <v>1</v>
       </c>
-      <c r="Z202" s="97" t="s">
+      <c r="Z202" s="100" t="s">
         <v>89</v>
       </c>
-      <c r="AA202" s="99"/>
-      <c r="AB202" s="99"/>
+      <c r="AA202" s="102"/>
+      <c r="AB202" s="102"/>
     </row>
     <row r="203" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A203" s="43">
@@ -17982,11 +17982,11 @@
       <c r="Y203" s="40">
         <v>1</v>
       </c>
-      <c r="Z203" s="97" t="s">
+      <c r="Z203" s="100" t="s">
         <v>90</v>
       </c>
-      <c r="AA203" s="99"/>
-      <c r="AB203" s="99"/>
+      <c r="AA203" s="102"/>
+      <c r="AB203" s="102"/>
     </row>
     <row r="204" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A204" s="23">
@@ -18065,11 +18065,11 @@
       <c r="Y204" s="50">
         <v>1</v>
       </c>
-      <c r="Z204" s="97" t="s">
+      <c r="Z204" s="100" t="s">
         <v>91</v>
       </c>
-      <c r="AA204" s="99"/>
-      <c r="AB204" s="99"/>
+      <c r="AA204" s="102"/>
+      <c r="AB204" s="102"/>
     </row>
     <row r="205" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="23">
@@ -18148,11 +18148,11 @@
       <c r="Y205" s="50">
         <v>1</v>
       </c>
-      <c r="Z205" s="97" t="s">
+      <c r="Z205" s="100" t="s">
         <v>92</v>
       </c>
-      <c r="AA205" s="99"/>
-      <c r="AB205" s="99"/>
+      <c r="AA205" s="102"/>
+      <c r="AB205" s="102"/>
     </row>
     <row r="206" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="43">
@@ -18230,11 +18230,11 @@
       <c r="Y206" s="40">
         <v>1</v>
       </c>
-      <c r="Z206" s="97" t="s">
+      <c r="Z206" s="100" t="s">
         <v>94</v>
       </c>
-      <c r="AA206" s="98"/>
-      <c r="AB206" s="98"/>
+      <c r="AA206" s="101"/>
+      <c r="AB206" s="101"/>
     </row>
     <row r="207" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
@@ -18312,9 +18312,9 @@
       <c r="Y207" s="50">
         <v>1</v>
       </c>
-      <c r="Z207" s="97"/>
-      <c r="AA207" s="98"/>
-      <c r="AB207" s="98"/>
+      <c r="Z207" s="100"/>
+      <c r="AA207" s="101"/>
+      <c r="AB207" s="101"/>
     </row>
     <row r="208" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
@@ -18392,9 +18392,9 @@
       <c r="Y208" s="50">
         <v>1</v>
       </c>
-      <c r="Z208" s="97"/>
-      <c r="AA208" s="98"/>
-      <c r="AB208" s="98"/>
+      <c r="Z208" s="100"/>
+      <c r="AA208" s="101"/>
+      <c r="AB208" s="101"/>
     </row>
     <row r="209" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
@@ -18472,9 +18472,9 @@
       <c r="Y209" s="50">
         <v>1</v>
       </c>
-      <c r="Z209" s="97"/>
-      <c r="AA209" s="98"/>
-      <c r="AB209" s="98"/>
+      <c r="Z209" s="100"/>
+      <c r="AA209" s="101"/>
+      <c r="AB209" s="101"/>
     </row>
     <row r="210" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
@@ -18552,9 +18552,9 @@
       <c r="Y210" s="50">
         <v>1</v>
       </c>
-      <c r="Z210" s="97"/>
-      <c r="AA210" s="98"/>
-      <c r="AB210" s="98"/>
+      <c r="Z210" s="100"/>
+      <c r="AA210" s="101"/>
+      <c r="AB210" s="101"/>
     </row>
     <row r="211" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
@@ -18632,9 +18632,9 @@
       <c r="Y211" s="50">
         <v>1</v>
       </c>
-      <c r="Z211" s="97"/>
-      <c r="AA211" s="98"/>
-      <c r="AB211" s="98"/>
+      <c r="Z211" s="100"/>
+      <c r="AA211" s="101"/>
+      <c r="AB211" s="101"/>
     </row>
     <row r="212" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
@@ -18712,9 +18712,9 @@
       <c r="Y212" s="50">
         <v>1</v>
       </c>
-      <c r="Z212" s="97"/>
-      <c r="AA212" s="98"/>
-      <c r="AB212" s="98"/>
+      <c r="Z212" s="100"/>
+      <c r="AA212" s="101"/>
+      <c r="AB212" s="101"/>
     </row>
     <row r="213" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
@@ -18792,9 +18792,9 @@
       <c r="Y213" s="50">
         <v>1</v>
       </c>
-      <c r="Z213" s="97"/>
-      <c r="AA213" s="98"/>
-      <c r="AB213" s="98"/>
+      <c r="Z213" s="100"/>
+      <c r="AA213" s="101"/>
+      <c r="AB213" s="101"/>
     </row>
     <row r="214" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
@@ -18872,9 +18872,9 @@
       <c r="Y214" s="50">
         <v>1</v>
       </c>
-      <c r="Z214" s="97"/>
-      <c r="AA214" s="98"/>
-      <c r="AB214" s="98"/>
+      <c r="Z214" s="100"/>
+      <c r="AA214" s="101"/>
+      <c r="AB214" s="101"/>
     </row>
     <row r="215" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
@@ -18952,9 +18952,9 @@
       <c r="Y215" s="50">
         <v>1</v>
       </c>
-      <c r="Z215" s="97"/>
-      <c r="AA215" s="98"/>
-      <c r="AB215" s="98"/>
+      <c r="Z215" s="100"/>
+      <c r="AA215" s="101"/>
+      <c r="AB215" s="101"/>
     </row>
     <row r="216" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
@@ -19032,9 +19032,9 @@
       <c r="Y216" s="50">
         <v>1</v>
       </c>
-      <c r="Z216" s="97"/>
-      <c r="AA216" s="98"/>
-      <c r="AB216" s="98"/>
+      <c r="Z216" s="100"/>
+      <c r="AA216" s="101"/>
+      <c r="AB216" s="101"/>
     </row>
     <row r="217" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
@@ -19112,9 +19112,9 @@
       <c r="Y217" s="50">
         <v>1</v>
       </c>
-      <c r="Z217" s="97"/>
-      <c r="AA217" s="98"/>
-      <c r="AB217" s="98"/>
+      <c r="Z217" s="100"/>
+      <c r="AA217" s="101"/>
+      <c r="AB217" s="101"/>
     </row>
     <row r="218" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
@@ -19192,9 +19192,9 @@
       <c r="Y218" s="50">
         <v>1</v>
       </c>
-      <c r="Z218" s="97"/>
-      <c r="AA218" s="98"/>
-      <c r="AB218" s="98"/>
+      <c r="Z218" s="100"/>
+      <c r="AA218" s="101"/>
+      <c r="AB218" s="101"/>
     </row>
     <row r="219" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
@@ -19272,9 +19272,9 @@
       <c r="Y219" s="50">
         <v>1</v>
       </c>
-      <c r="Z219" s="97"/>
-      <c r="AA219" s="98"/>
-      <c r="AB219" s="98"/>
+      <c r="Z219" s="100"/>
+      <c r="AA219" s="101"/>
+      <c r="AB219" s="101"/>
     </row>
     <row r="220" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
@@ -19352,9 +19352,9 @@
       <c r="Y220" s="50">
         <v>1</v>
       </c>
-      <c r="Z220" s="97"/>
-      <c r="AA220" s="98"/>
-      <c r="AB220" s="98"/>
+      <c r="Z220" s="100"/>
+      <c r="AA220" s="101"/>
+      <c r="AB220" s="101"/>
     </row>
     <row r="221" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A221" s="43">
@@ -19432,11 +19432,11 @@
       <c r="Y221" s="40">
         <v>1</v>
       </c>
-      <c r="Z221" s="97" t="s">
+      <c r="Z221" s="100" t="s">
         <v>95</v>
       </c>
-      <c r="AA221" s="99"/>
-      <c r="AB221" s="99"/>
+      <c r="AA221" s="102"/>
+      <c r="AB221" s="102"/>
     </row>
     <row r="222" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
@@ -19514,9 +19514,9 @@
       <c r="Y222" s="50">
         <v>1</v>
       </c>
-      <c r="Z222" s="97"/>
-      <c r="AA222" s="99"/>
-      <c r="AB222" s="99"/>
+      <c r="Z222" s="100"/>
+      <c r="AA222" s="102"/>
+      <c r="AB222" s="102"/>
     </row>
     <row r="223" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A223" s="43">
@@ -19594,11 +19594,11 @@
       <c r="Y223" s="40">
         <v>1</v>
       </c>
-      <c r="Z223" s="97" t="s">
+      <c r="Z223" s="100" t="s">
         <v>96</v>
       </c>
-      <c r="AA223" s="99"/>
-      <c r="AB223" s="99"/>
+      <c r="AA223" s="102"/>
+      <c r="AB223" s="102"/>
     </row>
     <row r="224" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
@@ -19676,9 +19676,9 @@
       <c r="Y224" s="50">
         <v>1</v>
       </c>
-      <c r="Z224" s="97"/>
-      <c r="AA224" s="99"/>
-      <c r="AB224" s="99"/>
+      <c r="Z224" s="100"/>
+      <c r="AA224" s="102"/>
+      <c r="AB224" s="102"/>
     </row>
     <row r="225" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A225" s="43">
@@ -19756,11 +19756,11 @@
       <c r="Y225" s="40">
         <v>1</v>
       </c>
-      <c r="Z225" s="97" t="s">
+      <c r="Z225" s="100" t="s">
         <v>97</v>
       </c>
-      <c r="AA225" s="99"/>
-      <c r="AB225" s="99"/>
+      <c r="AA225" s="102"/>
+      <c r="AB225" s="102"/>
     </row>
     <row r="226" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
@@ -19839,9 +19839,9 @@
       <c r="Y226" s="50">
         <v>1</v>
       </c>
-      <c r="Z226" s="97"/>
-      <c r="AA226" s="99"/>
-      <c r="AB226" s="99"/>
+      <c r="Z226" s="100"/>
+      <c r="AA226" s="102"/>
+      <c r="AB226" s="102"/>
     </row>
     <row r="227" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
@@ -19920,9 +19920,9 @@
       <c r="Y227" s="50">
         <v>1</v>
       </c>
-      <c r="Z227" s="97"/>
-      <c r="AA227" s="99"/>
-      <c r="AB227" s="99"/>
+      <c r="Z227" s="100"/>
+      <c r="AA227" s="102"/>
+      <c r="AB227" s="102"/>
     </row>
     <row r="228" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
@@ -20001,9 +20001,9 @@
       <c r="Y228" s="50">
         <v>1</v>
       </c>
-      <c r="Z228" s="97"/>
-      <c r="AA228" s="99"/>
-      <c r="AB228" s="99"/>
+      <c r="Z228" s="100"/>
+      <c r="AA228" s="102"/>
+      <c r="AB228" s="102"/>
     </row>
     <row r="229" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
@@ -20082,9 +20082,9 @@
       <c r="Y229" s="50">
         <v>1</v>
       </c>
-      <c r="Z229" s="97"/>
-      <c r="AA229" s="99"/>
-      <c r="AB229" s="99"/>
+      <c r="Z229" s="100"/>
+      <c r="AA229" s="102"/>
+      <c r="AB229" s="102"/>
     </row>
     <row r="230" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
@@ -20163,9 +20163,9 @@
       <c r="Y230" s="50">
         <v>1</v>
       </c>
-      <c r="Z230" s="97"/>
-      <c r="AA230" s="99"/>
-      <c r="AB230" s="99"/>
+      <c r="Z230" s="100"/>
+      <c r="AA230" s="102"/>
+      <c r="AB230" s="102"/>
     </row>
     <row r="231" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
@@ -20244,9 +20244,9 @@
       <c r="Y231" s="50">
         <v>1</v>
       </c>
-      <c r="Z231" s="97"/>
-      <c r="AA231" s="99"/>
-      <c r="AB231" s="99"/>
+      <c r="Z231" s="100"/>
+      <c r="AA231" s="102"/>
+      <c r="AB231" s="102"/>
     </row>
     <row r="232" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
@@ -20325,9 +20325,9 @@
       <c r="Y232" s="50">
         <v>1</v>
       </c>
-      <c r="Z232" s="97"/>
-      <c r="AA232" s="99"/>
-      <c r="AB232" s="99"/>
+      <c r="Z232" s="100"/>
+      <c r="AA232" s="102"/>
+      <c r="AB232" s="102"/>
     </row>
     <row r="233" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="43">
@@ -20405,11 +20405,11 @@
       <c r="Y233" s="40">
         <v>1</v>
       </c>
-      <c r="Z233" s="97" t="s">
+      <c r="Z233" s="100" t="s">
         <v>95</v>
       </c>
-      <c r="AA233" s="98"/>
-      <c r="AB233" s="98"/>
+      <c r="AA233" s="101"/>
+      <c r="AB233" s="101"/>
     </row>
     <row r="234" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A234" s="27">
@@ -20487,9 +20487,9 @@
       <c r="Y234" s="57">
         <v>1</v>
       </c>
-      <c r="Z234" s="97"/>
-      <c r="AA234" s="98"/>
-      <c r="AB234" s="98"/>
+      <c r="Z234" s="100"/>
+      <c r="AA234" s="101"/>
+      <c r="AB234" s="101"/>
     </row>
     <row r="235" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
@@ -20569,11 +20569,11 @@
       <c r="Y235" s="50">
         <v>1</v>
       </c>
-      <c r="Z235" s="97" t="s">
+      <c r="Z235" s="100" t="s">
         <v>98</v>
       </c>
-      <c r="AA235" s="99"/>
-      <c r="AB235" s="99"/>
+      <c r="AA235" s="102"/>
+      <c r="AB235" s="102"/>
     </row>
     <row r="236" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
@@ -20653,9 +20653,9 @@
       <c r="Y236" s="50">
         <v>1</v>
       </c>
-      <c r="Z236" s="97"/>
-      <c r="AA236" s="99"/>
-      <c r="AB236" s="99"/>
+      <c r="Z236" s="100"/>
+      <c r="AA236" s="102"/>
+      <c r="AB236" s="102"/>
     </row>
     <row r="237" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
@@ -20735,9 +20735,9 @@
       <c r="Y237" s="50">
         <v>1</v>
       </c>
-      <c r="Z237" s="97"/>
-      <c r="AA237" s="99"/>
-      <c r="AB237" s="99"/>
+      <c r="Z237" s="100"/>
+      <c r="AA237" s="102"/>
+      <c r="AB237" s="102"/>
     </row>
     <row r="238" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A238" s="43">
@@ -20815,11 +20815,11 @@
       <c r="Y238" s="40">
         <v>1</v>
       </c>
-      <c r="Z238" s="97" t="s">
+      <c r="Z238" s="100" t="s">
         <v>99</v>
       </c>
-      <c r="AA238" s="99"/>
-      <c r="AB238" s="99"/>
+      <c r="AA238" s="102"/>
+      <c r="AB238" s="102"/>
     </row>
     <row r="239" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
@@ -20897,9 +20897,9 @@
       <c r="Y239" s="50">
         <v>1</v>
       </c>
-      <c r="Z239" s="97"/>
-      <c r="AA239" s="99"/>
-      <c r="AB239" s="99"/>
+      <c r="Z239" s="100"/>
+      <c r="AA239" s="102"/>
+      <c r="AB239" s="102"/>
     </row>
     <row r="240" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A240" s="43">
@@ -20977,11 +20977,11 @@
       <c r="Y240" s="40">
         <v>1</v>
       </c>
-      <c r="Z240" s="97" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA240" s="99"/>
-      <c r="AB240" s="99"/>
+      <c r="Z240" s="100" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA240" s="102"/>
+      <c r="AB240" s="102"/>
     </row>
     <row r="241" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
@@ -21060,9 +21060,9 @@
       <c r="Y241" s="50">
         <v>1</v>
       </c>
-      <c r="Z241" s="97"/>
-      <c r="AA241" s="99"/>
-      <c r="AB241" s="99"/>
+      <c r="Z241" s="100"/>
+      <c r="AA241" s="102"/>
+      <c r="AB241" s="102"/>
     </row>
     <row r="242" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
@@ -21141,9 +21141,9 @@
       <c r="Y242" s="50">
         <v>1</v>
       </c>
-      <c r="Z242" s="97"/>
-      <c r="AA242" s="99"/>
-      <c r="AB242" s="99"/>
+      <c r="Z242" s="100"/>
+      <c r="AA242" s="102"/>
+      <c r="AB242" s="102"/>
     </row>
     <row r="243" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
@@ -21222,9 +21222,9 @@
       <c r="Y243" s="50">
         <v>1</v>
       </c>
-      <c r="Z243" s="97"/>
-      <c r="AA243" s="99"/>
-      <c r="AB243" s="99"/>
+      <c r="Z243" s="100"/>
+      <c r="AA243" s="102"/>
+      <c r="AB243" s="102"/>
     </row>
     <row r="244" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
@@ -21303,9 +21303,9 @@
       <c r="Y244" s="50">
         <v>1</v>
       </c>
-      <c r="Z244" s="97"/>
-      <c r="AA244" s="99"/>
-      <c r="AB244" s="99"/>
+      <c r="Z244" s="100"/>
+      <c r="AA244" s="102"/>
+      <c r="AB244" s="102"/>
     </row>
     <row r="245" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
@@ -21384,9 +21384,9 @@
       <c r="Y245" s="50">
         <v>1</v>
       </c>
-      <c r="Z245" s="97"/>
-      <c r="AA245" s="99"/>
-      <c r="AB245" s="99"/>
+      <c r="Z245" s="100"/>
+      <c r="AA245" s="102"/>
+      <c r="AB245" s="102"/>
     </row>
     <row r="246" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
@@ -21465,9 +21465,9 @@
       <c r="Y246" s="50">
         <v>1</v>
       </c>
-      <c r="Z246" s="97"/>
-      <c r="AA246" s="99"/>
-      <c r="AB246" s="99"/>
+      <c r="Z246" s="100"/>
+      <c r="AA246" s="102"/>
+      <c r="AB246" s="102"/>
     </row>
     <row r="247" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
@@ -21546,9 +21546,9 @@
       <c r="Y247" s="50">
         <v>1</v>
       </c>
-      <c r="Z247" s="97"/>
-      <c r="AA247" s="99"/>
-      <c r="AB247" s="99"/>
+      <c r="Z247" s="100"/>
+      <c r="AA247" s="102"/>
+      <c r="AB247" s="102"/>
     </row>
     <row r="248" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
@@ -21627,9 +21627,9 @@
       <c r="Y248" s="50">
         <v>1</v>
       </c>
-      <c r="Z248" s="97"/>
-      <c r="AA248" s="99"/>
-      <c r="AB248" s="99"/>
+      <c r="Z248" s="100"/>
+      <c r="AA248" s="102"/>
+      <c r="AB248" s="102"/>
     </row>
     <row r="249" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
@@ -21708,9 +21708,9 @@
       <c r="Y249" s="50">
         <v>1</v>
       </c>
-      <c r="Z249" s="97"/>
-      <c r="AA249" s="99"/>
-      <c r="AB249" s="99"/>
+      <c r="Z249" s="100"/>
+      <c r="AA249" s="102"/>
+      <c r="AB249" s="102"/>
     </row>
     <row r="250" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
@@ -21789,9 +21789,9 @@
       <c r="Y250" s="50">
         <v>1</v>
       </c>
-      <c r="Z250" s="97"/>
-      <c r="AA250" s="99"/>
-      <c r="AB250" s="99"/>
+      <c r="Z250" s="100"/>
+      <c r="AA250" s="102"/>
+      <c r="AB250" s="102"/>
     </row>
     <row r="251" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
@@ -21870,9 +21870,9 @@
       <c r="Y251" s="50">
         <v>1</v>
       </c>
-      <c r="Z251" s="97"/>
-      <c r="AA251" s="99"/>
-      <c r="AB251" s="99"/>
+      <c r="Z251" s="100"/>
+      <c r="AA251" s="102"/>
+      <c r="AB251" s="102"/>
     </row>
     <row r="252" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A252" s="43">
@@ -21951,11 +21951,11 @@
       <c r="Y252" s="40">
         <v>1</v>
       </c>
-      <c r="Z252" s="97" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA252" s="98"/>
-      <c r="AB252" s="98"/>
+      <c r="Z252" s="100" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA252" s="101"/>
+      <c r="AB252" s="101"/>
     </row>
     <row r="253" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
@@ -22034,9 +22034,9 @@
       <c r="Y253" s="50">
         <v>1</v>
       </c>
-      <c r="Z253" s="97"/>
-      <c r="AA253" s="98"/>
-      <c r="AB253" s="98"/>
+      <c r="Z253" s="100"/>
+      <c r="AA253" s="101"/>
+      <c r="AB253" s="101"/>
     </row>
     <row r="254" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
@@ -22115,9 +22115,9 @@
       <c r="Y254" s="50">
         <v>1</v>
       </c>
-      <c r="Z254" s="97"/>
-      <c r="AA254" s="98"/>
-      <c r="AB254" s="98"/>
+      <c r="Z254" s="100"/>
+      <c r="AA254" s="101"/>
+      <c r="AB254" s="101"/>
     </row>
     <row r="255" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
@@ -22196,9 +22196,9 @@
       <c r="Y255" s="50">
         <v>1</v>
       </c>
-      <c r="Z255" s="97"/>
-      <c r="AA255" s="98"/>
-      <c r="AB255" s="98"/>
+      <c r="Z255" s="100"/>
+      <c r="AA255" s="101"/>
+      <c r="AB255" s="101"/>
     </row>
     <row r="256" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
@@ -22277,9 +22277,9 @@
       <c r="Y256" s="50">
         <v>1</v>
       </c>
-      <c r="Z256" s="97"/>
-      <c r="AA256" s="98"/>
-      <c r="AB256" s="98"/>
+      <c r="Z256" s="100"/>
+      <c r="AA256" s="101"/>
+      <c r="AB256" s="101"/>
     </row>
     <row r="257" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
@@ -22358,9 +22358,9 @@
       <c r="Y257" s="50">
         <v>1</v>
       </c>
-      <c r="Z257" s="97"/>
-      <c r="AA257" s="98"/>
-      <c r="AB257" s="98"/>
+      <c r="Z257" s="100"/>
+      <c r="AA257" s="101"/>
+      <c r="AB257" s="101"/>
     </row>
     <row r="258" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
@@ -22439,9 +22439,9 @@
       <c r="Y258" s="50">
         <v>1</v>
       </c>
-      <c r="Z258" s="97"/>
-      <c r="AA258" s="98"/>
-      <c r="AB258" s="98"/>
+      <c r="Z258" s="100"/>
+      <c r="AA258" s="101"/>
+      <c r="AB258" s="101"/>
     </row>
     <row r="259" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
@@ -22520,9 +22520,9 @@
       <c r="Y259" s="50">
         <v>1</v>
       </c>
-      <c r="Z259" s="97"/>
-      <c r="AA259" s="98"/>
-      <c r="AB259" s="98"/>
+      <c r="Z259" s="100"/>
+      <c r="AA259" s="101"/>
+      <c r="AB259" s="101"/>
     </row>
     <row r="260" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
@@ -22601,9 +22601,9 @@
       <c r="Y260" s="50">
         <v>1</v>
       </c>
-      <c r="Z260" s="97"/>
-      <c r="AA260" s="98"/>
-      <c r="AB260" s="98"/>
+      <c r="Z260" s="100"/>
+      <c r="AA260" s="101"/>
+      <c r="AB260" s="101"/>
     </row>
     <row r="261" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
@@ -22682,9 +22682,9 @@
       <c r="Y261" s="50">
         <v>1</v>
       </c>
-      <c r="Z261" s="97"/>
-      <c r="AA261" s="98"/>
-      <c r="AB261" s="98"/>
+      <c r="Z261" s="100"/>
+      <c r="AA261" s="101"/>
+      <c r="AB261" s="101"/>
     </row>
     <row r="262" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
@@ -22763,9 +22763,9 @@
       <c r="Y262" s="50">
         <v>1</v>
       </c>
-      <c r="Z262" s="97"/>
-      <c r="AA262" s="98"/>
-      <c r="AB262" s="98"/>
+      <c r="Z262" s="100"/>
+      <c r="AA262" s="101"/>
+      <c r="AB262" s="101"/>
     </row>
     <row r="263" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A263" s="43">
@@ -22844,11 +22844,11 @@
       <c r="Y263" s="40">
         <v>1</v>
       </c>
-      <c r="Z263" s="97" t="s">
+      <c r="Z263" s="100" t="s">
         <v>101</v>
       </c>
-      <c r="AA263" s="98"/>
-      <c r="AB263" s="98"/>
+      <c r="AA263" s="101"/>
+      <c r="AB263" s="101"/>
     </row>
     <row r="264" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
@@ -22927,9 +22927,9 @@
       <c r="Y264" s="50">
         <v>1</v>
       </c>
-      <c r="Z264" s="97"/>
-      <c r="AA264" s="98"/>
-      <c r="AB264" s="98"/>
+      <c r="Z264" s="100"/>
+      <c r="AA264" s="101"/>
+      <c r="AB264" s="101"/>
     </row>
     <row r="265" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A265" s="43">
@@ -23008,11 +23008,11 @@
       <c r="Y265" s="40">
         <v>1</v>
       </c>
-      <c r="Z265" s="97" t="s">
+      <c r="Z265" s="100" t="s">
         <v>102</v>
       </c>
-      <c r="AA265" s="99"/>
-      <c r="AB265" s="99"/>
+      <c r="AA265" s="102"/>
+      <c r="AB265" s="102"/>
     </row>
     <row r="266" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
@@ -23091,9 +23091,9 @@
       <c r="Y266" s="50">
         <v>1</v>
       </c>
-      <c r="Z266" s="97"/>
-      <c r="AA266" s="99"/>
-      <c r="AB266" s="99"/>
+      <c r="Z266" s="100"/>
+      <c r="AA266" s="102"/>
+      <c r="AB266" s="102"/>
     </row>
     <row r="267" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
@@ -23172,9 +23172,9 @@
       <c r="Y267" s="50">
         <v>1</v>
       </c>
-      <c r="Z267" s="97"/>
-      <c r="AA267" s="99"/>
-      <c r="AB267" s="99"/>
+      <c r="Z267" s="100"/>
+      <c r="AA267" s="102"/>
+      <c r="AB267" s="102"/>
     </row>
     <row r="268" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
@@ -23253,9 +23253,9 @@
       <c r="Y268" s="50">
         <v>1</v>
       </c>
-      <c r="Z268" s="97"/>
-      <c r="AA268" s="99"/>
-      <c r="AB268" s="99"/>
+      <c r="Z268" s="100"/>
+      <c r="AA268" s="102"/>
+      <c r="AB268" s="102"/>
     </row>
     <row r="269" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
@@ -23334,9 +23334,9 @@
       <c r="Y269" s="50">
         <v>1</v>
       </c>
-      <c r="Z269" s="97"/>
-      <c r="AA269" s="99"/>
-      <c r="AB269" s="99"/>
+      <c r="Z269" s="100"/>
+      <c r="AA269" s="102"/>
+      <c r="AB269" s="102"/>
     </row>
     <row r="270" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
@@ -23415,9 +23415,9 @@
       <c r="Y270" s="50">
         <v>1</v>
       </c>
-      <c r="Z270" s="97"/>
-      <c r="AA270" s="99"/>
-      <c r="AB270" s="99"/>
+      <c r="Z270" s="100"/>
+      <c r="AA270" s="102"/>
+      <c r="AB270" s="102"/>
     </row>
     <row r="271" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
@@ -23496,9 +23496,9 @@
       <c r="Y271" s="50">
         <v>1</v>
       </c>
-      <c r="Z271" s="97"/>
-      <c r="AA271" s="99"/>
-      <c r="AB271" s="99"/>
+      <c r="Z271" s="100"/>
+      <c r="AA271" s="102"/>
+      <c r="AB271" s="102"/>
     </row>
     <row r="272" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
@@ -23577,9 +23577,9 @@
       <c r="Y272" s="50">
         <v>1</v>
       </c>
-      <c r="Z272" s="97"/>
-      <c r="AA272" s="99"/>
-      <c r="AB272" s="99"/>
+      <c r="Z272" s="100"/>
+      <c r="AA272" s="102"/>
+      <c r="AB272" s="102"/>
     </row>
     <row r="273" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
@@ -23658,9 +23658,9 @@
       <c r="Y273" s="50">
         <v>1</v>
       </c>
-      <c r="Z273" s="97"/>
-      <c r="AA273" s="99"/>
-      <c r="AB273" s="99"/>
+      <c r="Z273" s="100"/>
+      <c r="AA273" s="102"/>
+      <c r="AB273" s="102"/>
     </row>
     <row r="274" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
@@ -23739,9 +23739,9 @@
       <c r="Y274" s="50">
         <v>1</v>
       </c>
-      <c r="Z274" s="97"/>
-      <c r="AA274" s="99"/>
-      <c r="AB274" s="99"/>
+      <c r="Z274" s="100"/>
+      <c r="AA274" s="102"/>
+      <c r="AB274" s="102"/>
     </row>
     <row r="275" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A275" s="27">
@@ -23820,9 +23820,9 @@
       <c r="Y275" s="57">
         <v>1</v>
       </c>
-      <c r="Z275" s="97"/>
-      <c r="AA275" s="99"/>
-      <c r="AB275" s="99"/>
+      <c r="Z275" s="100"/>
+      <c r="AA275" s="102"/>
+      <c r="AB275" s="102"/>
     </row>
     <row r="276" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="43">
@@ -23901,11 +23901,11 @@
       <c r="Y276" s="40">
         <v>1</v>
       </c>
-      <c r="Z276" s="97" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA276" s="98"/>
-      <c r="AB276" s="98"/>
+      <c r="Z276" s="100" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA276" s="101"/>
+      <c r="AB276" s="101"/>
     </row>
     <row r="277" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
@@ -23983,9 +23983,9 @@
       <c r="Y277" s="50">
         <v>1</v>
       </c>
-      <c r="Z277" s="97"/>
-      <c r="AA277" s="98"/>
-      <c r="AB277" s="98"/>
+      <c r="Z277" s="100"/>
+      <c r="AA277" s="101"/>
+      <c r="AB277" s="101"/>
     </row>
     <row r="278" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
@@ -24063,9 +24063,9 @@
       <c r="Y278" s="50">
         <v>1</v>
       </c>
-      <c r="Z278" s="97"/>
-      <c r="AA278" s="98"/>
-      <c r="AB278" s="98"/>
+      <c r="Z278" s="100"/>
+      <c r="AA278" s="101"/>
+      <c r="AB278" s="101"/>
     </row>
     <row r="279" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
@@ -24143,9 +24143,9 @@
       <c r="Y279" s="50">
         <v>1</v>
       </c>
-      <c r="Z279" s="97"/>
-      <c r="AA279" s="98"/>
-      <c r="AB279" s="98"/>
+      <c r="Z279" s="100"/>
+      <c r="AA279" s="101"/>
+      <c r="AB279" s="101"/>
     </row>
     <row r="280" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
@@ -24223,9 +24223,9 @@
       <c r="Y280" s="50">
         <v>1</v>
       </c>
-      <c r="Z280" s="97"/>
-      <c r="AA280" s="98"/>
-      <c r="AB280" s="98"/>
+      <c r="Z280" s="100"/>
+      <c r="AA280" s="101"/>
+      <c r="AB280" s="101"/>
     </row>
     <row r="281" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
@@ -24303,9 +24303,9 @@
       <c r="Y281" s="50">
         <v>1</v>
       </c>
-      <c r="Z281" s="97"/>
-      <c r="AA281" s="98"/>
-      <c r="AB281" s="98"/>
+      <c r="Z281" s="100"/>
+      <c r="AA281" s="101"/>
+      <c r="AB281" s="101"/>
     </row>
     <row r="282" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
@@ -24383,9 +24383,9 @@
       <c r="Y282" s="50">
         <v>1</v>
       </c>
-      <c r="Z282" s="97"/>
-      <c r="AA282" s="98"/>
-      <c r="AB282" s="98"/>
+      <c r="Z282" s="100"/>
+      <c r="AA282" s="101"/>
+      <c r="AB282" s="101"/>
     </row>
     <row r="283" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
@@ -24463,9 +24463,9 @@
       <c r="Y283" s="50">
         <v>1</v>
       </c>
-      <c r="Z283" s="97"/>
-      <c r="AA283" s="98"/>
-      <c r="AB283" s="98"/>
+      <c r="Z283" s="100"/>
+      <c r="AA283" s="101"/>
+      <c r="AB283" s="101"/>
     </row>
     <row r="284" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
@@ -24543,9 +24543,9 @@
       <c r="Y284" s="50">
         <v>1</v>
       </c>
-      <c r="Z284" s="97"/>
-      <c r="AA284" s="98"/>
-      <c r="AB284" s="98"/>
+      <c r="Z284" s="100"/>
+      <c r="AA284" s="101"/>
+      <c r="AB284" s="101"/>
     </row>
     <row r="285" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A285" s="43">
@@ -24624,9 +24624,9 @@
       <c r="Y285" s="40">
         <v>1</v>
       </c>
-      <c r="Z285" s="97"/>
-      <c r="AA285" s="98"/>
-      <c r="AB285" s="98"/>
+      <c r="Z285" s="100"/>
+      <c r="AA285" s="101"/>
+      <c r="AB285" s="101"/>
     </row>
     <row r="286" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
@@ -24706,9 +24706,9 @@
       <c r="Y286" s="50">
         <v>1</v>
       </c>
-      <c r="Z286" s="97"/>
-      <c r="AA286" s="98"/>
-      <c r="AB286" s="98"/>
+      <c r="Z286" s="100"/>
+      <c r="AA286" s="101"/>
+      <c r="AB286" s="101"/>
     </row>
     <row r="287" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A287" s="27">
@@ -24788,9 +24788,9 @@
       <c r="Y287" s="57">
         <v>1</v>
       </c>
-      <c r="Z287" s="97"/>
-      <c r="AA287" s="98"/>
-      <c r="AB287" s="98"/>
+      <c r="Z287" s="100"/>
+      <c r="AA287" s="101"/>
+      <c r="AB287" s="101"/>
     </row>
     <row r="288" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
@@ -24868,11 +24868,11 @@
       <c r="Y288" s="50">
         <v>1</v>
       </c>
-      <c r="Z288" s="97" t="s">
+      <c r="Z288" s="100" t="s">
         <v>101</v>
       </c>
-      <c r="AA288" s="98"/>
-      <c r="AB288" s="98"/>
+      <c r="AA288" s="101"/>
+      <c r="AB288" s="101"/>
     </row>
     <row r="289" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A289" s="27">
@@ -24951,9 +24951,9 @@
       <c r="Y289" s="57">
         <v>1</v>
       </c>
-      <c r="Z289" s="97"/>
-      <c r="AA289" s="98"/>
-      <c r="AB289" s="98"/>
+      <c r="Z289" s="100"/>
+      <c r="AA289" s="101"/>
+      <c r="AB289" s="101"/>
     </row>
     <row r="290" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
@@ -25033,11 +25033,11 @@
       <c r="Y290" s="50">
         <v>1</v>
       </c>
-      <c r="Z290" s="97" t="s">
+      <c r="Z290" s="100" t="s">
         <v>103</v>
       </c>
-      <c r="AA290" s="99"/>
-      <c r="AB290" s="99"/>
+      <c r="AA290" s="102"/>
+      <c r="AB290" s="102"/>
     </row>
     <row r="291" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
@@ -25117,9 +25117,9 @@
       <c r="Y291" s="50">
         <v>1</v>
       </c>
-      <c r="Z291" s="97"/>
-      <c r="AA291" s="99"/>
-      <c r="AB291" s="99"/>
+      <c r="Z291" s="100"/>
+      <c r="AA291" s="102"/>
+      <c r="AB291" s="102"/>
     </row>
     <row r="292" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
@@ -25199,9 +25199,9 @@
       <c r="Y292" s="50">
         <v>1</v>
       </c>
-      <c r="Z292" s="97"/>
-      <c r="AA292" s="99"/>
-      <c r="AB292" s="99"/>
+      <c r="Z292" s="100"/>
+      <c r="AA292" s="102"/>
+      <c r="AB292" s="102"/>
     </row>
     <row r="293" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A293" s="43">
@@ -25280,11 +25280,11 @@
       <c r="Y293" s="40">
         <v>1</v>
       </c>
-      <c r="Z293" s="97" t="s">
+      <c r="Z293" s="100" t="s">
         <v>104</v>
       </c>
-      <c r="AA293" s="99"/>
-      <c r="AB293" s="99"/>
+      <c r="AA293" s="102"/>
+      <c r="AB293" s="102"/>
     </row>
     <row r="294" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A294" s="43">
@@ -25363,11 +25363,11 @@
       <c r="Y294" s="40">
         <v>1</v>
       </c>
-      <c r="Z294" s="97" t="s">
+      <c r="Z294" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="AA294" s="99"/>
-      <c r="AB294" s="99"/>
+      <c r="AA294" s="102"/>
+      <c r="AB294" s="102"/>
     </row>
     <row r="295" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A295" s="43">
@@ -25446,11 +25446,11 @@
       <c r="Y295" s="40">
         <v>1</v>
       </c>
-      <c r="Z295" s="97" t="s">
+      <c r="Z295" s="100" t="s">
         <v>106</v>
       </c>
-      <c r="AA295" s="99"/>
-      <c r="AB295" s="99"/>
+      <c r="AA295" s="102"/>
+      <c r="AB295" s="102"/>
     </row>
     <row r="296" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A296" s="43">
@@ -25529,11 +25529,11 @@
       <c r="Y296" s="40">
         <v>1</v>
       </c>
-      <c r="Z296" s="100" t="s">
+      <c r="Z296" s="115" t="s">
         <v>106</v>
       </c>
-      <c r="AA296" s="101"/>
-      <c r="AB296" s="101"/>
+      <c r="AA296" s="116"/>
+      <c r="AB296" s="116"/>
     </row>
     <row r="297" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
@@ -25612,9 +25612,9 @@
       <c r="Y297" s="50">
         <v>1</v>
       </c>
-      <c r="Z297" s="100"/>
-      <c r="AA297" s="101"/>
-      <c r="AB297" s="101"/>
+      <c r="Z297" s="115"/>
+      <c r="AA297" s="116"/>
+      <c r="AB297" s="116"/>
     </row>
     <row r="298" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
@@ -25693,9 +25693,9 @@
       <c r="Y298" s="50">
         <v>1</v>
       </c>
-      <c r="Z298" s="100"/>
-      <c r="AA298" s="101"/>
-      <c r="AB298" s="101"/>
+      <c r="Z298" s="115"/>
+      <c r="AA298" s="116"/>
+      <c r="AB298" s="116"/>
     </row>
     <row r="299" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
@@ -25774,9 +25774,9 @@
       <c r="Y299" s="50">
         <v>1</v>
       </c>
-      <c r="Z299" s="100"/>
-      <c r="AA299" s="101"/>
-      <c r="AB299" s="101"/>
+      <c r="Z299" s="115"/>
+      <c r="AA299" s="116"/>
+      <c r="AB299" s="116"/>
     </row>
     <row r="300" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
@@ -25855,9 +25855,9 @@
       <c r="Y300" s="50">
         <v>1</v>
       </c>
-      <c r="Z300" s="100"/>
-      <c r="AA300" s="101"/>
-      <c r="AB300" s="101"/>
+      <c r="Z300" s="115"/>
+      <c r="AA300" s="116"/>
+      <c r="AB300" s="116"/>
     </row>
     <row r="301" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
@@ -25936,9 +25936,9 @@
       <c r="Y301" s="50">
         <v>1</v>
       </c>
-      <c r="Z301" s="100"/>
-      <c r="AA301" s="101"/>
-      <c r="AB301" s="101"/>
+      <c r="Z301" s="115"/>
+      <c r="AA301" s="116"/>
+      <c r="AB301" s="116"/>
     </row>
     <row r="302" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
@@ -26017,9 +26017,9 @@
       <c r="Y302" s="50">
         <v>1</v>
       </c>
-      <c r="Z302" s="100"/>
-      <c r="AA302" s="101"/>
-      <c r="AB302" s="101"/>
+      <c r="Z302" s="115"/>
+      <c r="AA302" s="116"/>
+      <c r="AB302" s="116"/>
     </row>
     <row r="303" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
@@ -26098,9 +26098,9 @@
       <c r="Y303" s="50">
         <v>1</v>
       </c>
-      <c r="Z303" s="100"/>
-      <c r="AA303" s="101"/>
-      <c r="AB303" s="101"/>
+      <c r="Z303" s="115"/>
+      <c r="AA303" s="116"/>
+      <c r="AB303" s="116"/>
     </row>
     <row r="304" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
@@ -26179,9 +26179,9 @@
       <c r="Y304" s="50">
         <v>1</v>
       </c>
-      <c r="Z304" s="100"/>
-      <c r="AA304" s="101"/>
-      <c r="AB304" s="101"/>
+      <c r="Z304" s="115"/>
+      <c r="AA304" s="116"/>
+      <c r="AB304" s="116"/>
     </row>
     <row r="305" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
@@ -26260,9 +26260,9 @@
       <c r="Y305" s="50">
         <v>1</v>
       </c>
-      <c r="Z305" s="100"/>
-      <c r="AA305" s="101"/>
-      <c r="AB305" s="101"/>
+      <c r="Z305" s="115"/>
+      <c r="AA305" s="116"/>
+      <c r="AB305" s="116"/>
     </row>
     <row r="306" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
@@ -26341,9 +26341,9 @@
       <c r="Y306" s="50">
         <v>1</v>
       </c>
-      <c r="Z306" s="100"/>
-      <c r="AA306" s="101"/>
-      <c r="AB306" s="101"/>
+      <c r="Z306" s="115"/>
+      <c r="AA306" s="116"/>
+      <c r="AB306" s="116"/>
     </row>
     <row r="307" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
@@ -26422,9 +26422,9 @@
       <c r="Y307" s="50">
         <v>1</v>
       </c>
-      <c r="Z307" s="100"/>
-      <c r="AA307" s="101"/>
-      <c r="AB307" s="101"/>
+      <c r="Z307" s="115"/>
+      <c r="AA307" s="116"/>
+      <c r="AB307" s="116"/>
     </row>
     <row r="308" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
@@ -26503,9 +26503,9 @@
       <c r="Y308" s="50">
         <v>1</v>
       </c>
-      <c r="Z308" s="100"/>
-      <c r="AA308" s="101"/>
-      <c r="AB308" s="101"/>
+      <c r="Z308" s="115"/>
+      <c r="AA308" s="116"/>
+      <c r="AB308" s="116"/>
     </row>
     <row r="309" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
@@ -26584,9 +26584,9 @@
       <c r="Y309" s="50">
         <v>1</v>
       </c>
-      <c r="Z309" s="100"/>
-      <c r="AA309" s="101"/>
-      <c r="AB309" s="101"/>
+      <c r="Z309" s="115"/>
+      <c r="AA309" s="116"/>
+      <c r="AB309" s="116"/>
     </row>
     <row r="310" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
@@ -26665,9 +26665,9 @@
       <c r="Y310" s="50">
         <v>1</v>
       </c>
-      <c r="Z310" s="100"/>
-      <c r="AA310" s="101"/>
-      <c r="AB310" s="101"/>
+      <c r="Z310" s="115"/>
+      <c r="AA310" s="116"/>
+      <c r="AB310" s="116"/>
     </row>
     <row r="311" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
@@ -26746,9 +26746,9 @@
       <c r="Y311" s="50">
         <v>1</v>
       </c>
-      <c r="Z311" s="100"/>
-      <c r="AA311" s="101"/>
-      <c r="AB311" s="101"/>
+      <c r="Z311" s="115"/>
+      <c r="AA311" s="116"/>
+      <c r="AB311" s="116"/>
     </row>
     <row r="312" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
@@ -26827,9 +26827,9 @@
       <c r="Y312" s="50">
         <v>1</v>
       </c>
-      <c r="Z312" s="100"/>
-      <c r="AA312" s="101"/>
-      <c r="AB312" s="101"/>
+      <c r="Z312" s="115"/>
+      <c r="AA312" s="116"/>
+      <c r="AB312" s="116"/>
     </row>
     <row r="313" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A313" s="95">
@@ -26986,11 +26986,11 @@
       <c r="Y314" s="53">
         <v>1</v>
       </c>
-      <c r="Z314" s="102" t="s">
+      <c r="Z314" s="105" t="s">
         <v>107</v>
       </c>
-      <c r="AA314" s="103"/>
-      <c r="AB314" s="103"/>
+      <c r="AA314" s="114"/>
+      <c r="AB314" s="114"/>
     </row>
     <row r="315" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
@@ -27069,11 +27069,11 @@
       <c r="Y315" s="50">
         <v>1</v>
       </c>
-      <c r="Z315" s="97" t="s">
+      <c r="Z315" s="100" t="s">
         <v>108</v>
       </c>
-      <c r="AA315" s="98"/>
-      <c r="AB315" s="98"/>
+      <c r="AA315" s="101"/>
+      <c r="AB315" s="101"/>
     </row>
     <row r="316" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
@@ -27152,9 +27152,9 @@
       <c r="Y316" s="50">
         <v>1</v>
       </c>
-      <c r="Z316" s="97"/>
-      <c r="AA316" s="98"/>
-      <c r="AB316" s="98"/>
+      <c r="Z316" s="100"/>
+      <c r="AA316" s="101"/>
+      <c r="AB316" s="101"/>
     </row>
     <row r="317" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A317" s="27">
@@ -27233,9 +27233,9 @@
       <c r="Y317" s="57">
         <v>1</v>
       </c>
-      <c r="Z317" s="97"/>
-      <c r="AA317" s="98"/>
-      <c r="AB317" s="98"/>
+      <c r="Z317" s="100"/>
+      <c r="AA317" s="101"/>
+      <c r="AB317" s="101"/>
     </row>
     <row r="318" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
@@ -27314,11 +27314,11 @@
       <c r="Y318" s="50">
         <v>1</v>
       </c>
-      <c r="Z318" s="97" t="s">
+      <c r="Z318" s="100" t="s">
         <v>109</v>
       </c>
-      <c r="AA318" s="99"/>
-      <c r="AB318" s="99"/>
+      <c r="AA318" s="102"/>
+      <c r="AB318" s="102"/>
     </row>
     <row r="319" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
@@ -27397,9 +27397,9 @@
       <c r="Y319" s="50">
         <v>1</v>
       </c>
-      <c r="Z319" s="97"/>
-      <c r="AA319" s="99"/>
-      <c r="AB319" s="99"/>
+      <c r="Z319" s="100"/>
+      <c r="AA319" s="102"/>
+      <c r="AB319" s="102"/>
     </row>
     <row r="320" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
@@ -27478,9 +27478,9 @@
       <c r="Y320" s="50">
         <v>1</v>
       </c>
-      <c r="Z320" s="97"/>
-      <c r="AA320" s="99"/>
-      <c r="AB320" s="99"/>
+      <c r="Z320" s="100"/>
+      <c r="AA320" s="102"/>
+      <c r="AB320" s="102"/>
     </row>
     <row r="321" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
@@ -27559,9 +27559,9 @@
       <c r="Y321" s="50">
         <v>1</v>
       </c>
-      <c r="Z321" s="97"/>
-      <c r="AA321" s="99"/>
-      <c r="AB321" s="99"/>
+      <c r="Z321" s="100"/>
+      <c r="AA321" s="102"/>
+      <c r="AB321" s="102"/>
     </row>
     <row r="322" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
@@ -27640,9 +27640,9 @@
       <c r="Y322" s="50">
         <v>1</v>
       </c>
-      <c r="Z322" s="97"/>
-      <c r="AA322" s="99"/>
-      <c r="AB322" s="99"/>
+      <c r="Z322" s="100"/>
+      <c r="AA322" s="102"/>
+      <c r="AB322" s="102"/>
     </row>
     <row r="323" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
@@ -27721,9 +27721,9 @@
       <c r="Y323" s="50">
         <v>1</v>
       </c>
-      <c r="Z323" s="97"/>
-      <c r="AA323" s="99"/>
-      <c r="AB323" s="99"/>
+      <c r="Z323" s="100"/>
+      <c r="AA323" s="102"/>
+      <c r="AB323" s="102"/>
     </row>
     <row r="324" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
@@ -27802,9 +27802,9 @@
       <c r="Y324" s="50">
         <v>1</v>
       </c>
-      <c r="Z324" s="97"/>
-      <c r="AA324" s="99"/>
-      <c r="AB324" s="99"/>
+      <c r="Z324" s="100"/>
+      <c r="AA324" s="102"/>
+      <c r="AB324" s="102"/>
     </row>
     <row r="325" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
@@ -27883,9 +27883,9 @@
       <c r="Y325" s="50">
         <v>1</v>
       </c>
-      <c r="Z325" s="97"/>
-      <c r="AA325" s="99"/>
-      <c r="AB325" s="99"/>
+      <c r="Z325" s="100"/>
+      <c r="AA325" s="102"/>
+      <c r="AB325" s="102"/>
     </row>
     <row r="326" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="43">
@@ -27965,11 +27965,11 @@
       <c r="Y326" s="40">
         <v>1</v>
       </c>
-      <c r="Z326" s="97" t="s">
+      <c r="Z326" s="100" t="s">
         <v>110</v>
       </c>
-      <c r="AA326" s="98"/>
-      <c r="AB326" s="98"/>
+      <c r="AA326" s="101"/>
+      <c r="AB326" s="101"/>
     </row>
     <row r="327" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
@@ -28049,9 +28049,9 @@
       <c r="Y327" s="50">
         <v>1</v>
       </c>
-      <c r="Z327" s="97"/>
-      <c r="AA327" s="98"/>
-      <c r="AB327" s="98"/>
+      <c r="Z327" s="100"/>
+      <c r="AA327" s="101"/>
+      <c r="AB327" s="101"/>
     </row>
     <row r="328" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
@@ -28131,9 +28131,9 @@
       <c r="Y328" s="50">
         <v>1</v>
       </c>
-      <c r="Z328" s="97"/>
-      <c r="AA328" s="98"/>
-      <c r="AB328" s="98"/>
+      <c r="Z328" s="100"/>
+      <c r="AA328" s="101"/>
+      <c r="AB328" s="101"/>
     </row>
     <row r="329" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
@@ -28213,9 +28213,9 @@
       <c r="Y329" s="50">
         <v>1</v>
       </c>
-      <c r="Z329" s="97"/>
-      <c r="AA329" s="98"/>
-      <c r="AB329" s="98"/>
+      <c r="Z329" s="100"/>
+      <c r="AA329" s="101"/>
+      <c r="AB329" s="101"/>
     </row>
     <row r="330" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
@@ -28295,9 +28295,9 @@
       <c r="Y330" s="50">
         <v>1</v>
       </c>
-      <c r="Z330" s="97"/>
-      <c r="AA330" s="98"/>
-      <c r="AB330" s="98"/>
+      <c r="Z330" s="100"/>
+      <c r="AA330" s="101"/>
+      <c r="AB330" s="101"/>
     </row>
     <row r="331" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
@@ -28377,9 +28377,9 @@
       <c r="Y331" s="50">
         <v>1</v>
       </c>
-      <c r="Z331" s="97"/>
-      <c r="AA331" s="98"/>
-      <c r="AB331" s="98"/>
+      <c r="Z331" s="100"/>
+      <c r="AA331" s="101"/>
+      <c r="AB331" s="101"/>
     </row>
     <row r="332" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
@@ -28459,9 +28459,9 @@
       <c r="Y332" s="50">
         <v>1</v>
       </c>
-      <c r="Z332" s="97"/>
-      <c r="AA332" s="98"/>
-      <c r="AB332" s="98"/>
+      <c r="Z332" s="100"/>
+      <c r="AA332" s="101"/>
+      <c r="AB332" s="101"/>
     </row>
     <row r="333" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
@@ -28541,9 +28541,9 @@
       <c r="Y333" s="50">
         <v>1</v>
       </c>
-      <c r="Z333" s="97"/>
-      <c r="AA333" s="98"/>
-      <c r="AB333" s="98"/>
+      <c r="Z333" s="100"/>
+      <c r="AA333" s="101"/>
+      <c r="AB333" s="101"/>
     </row>
     <row r="334" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
@@ -28623,9 +28623,9 @@
       <c r="Y334" s="50">
         <v>1</v>
       </c>
-      <c r="Z334" s="97"/>
-      <c r="AA334" s="98"/>
-      <c r="AB334" s="98"/>
+      <c r="Z334" s="100"/>
+      <c r="AA334" s="101"/>
+      <c r="AB334" s="101"/>
     </row>
     <row r="335" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
@@ -28705,9 +28705,9 @@
       <c r="Y335" s="50">
         <v>1</v>
       </c>
-      <c r="Z335" s="97"/>
-      <c r="AA335" s="98"/>
-      <c r="AB335" s="98"/>
+      <c r="Z335" s="100"/>
+      <c r="AA335" s="101"/>
+      <c r="AB335" s="101"/>
     </row>
     <row r="336" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
@@ -28787,9 +28787,9 @@
       <c r="Y336" s="50">
         <v>1</v>
       </c>
-      <c r="Z336" s="97"/>
-      <c r="AA336" s="98"/>
-      <c r="AB336" s="98"/>
+      <c r="Z336" s="100"/>
+      <c r="AA336" s="101"/>
+      <c r="AB336" s="101"/>
     </row>
     <row r="337" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
@@ -28869,9 +28869,9 @@
       <c r="Y337" s="50">
         <v>1</v>
       </c>
-      <c r="Z337" s="97"/>
-      <c r="AA337" s="98"/>
-      <c r="AB337" s="98"/>
+      <c r="Z337" s="100"/>
+      <c r="AA337" s="101"/>
+      <c r="AB337" s="101"/>
     </row>
     <row r="338" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
@@ -28951,9 +28951,9 @@
       <c r="Y338" s="50">
         <v>1</v>
       </c>
-      <c r="Z338" s="97"/>
-      <c r="AA338" s="98"/>
-      <c r="AB338" s="98"/>
+      <c r="Z338" s="100"/>
+      <c r="AA338" s="101"/>
+      <c r="AB338" s="101"/>
     </row>
     <row r="339" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
@@ -29033,9 +29033,9 @@
       <c r="Y339" s="50">
         <v>1</v>
       </c>
-      <c r="Z339" s="97"/>
-      <c r="AA339" s="98"/>
-      <c r="AB339" s="98"/>
+      <c r="Z339" s="100"/>
+      <c r="AA339" s="101"/>
+      <c r="AB339" s="101"/>
     </row>
     <row r="340" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
@@ -29115,9 +29115,9 @@
       <c r="Y340" s="50">
         <v>1</v>
       </c>
-      <c r="Z340" s="97"/>
-      <c r="AA340" s="98"/>
-      <c r="AB340" s="98"/>
+      <c r="Z340" s="100"/>
+      <c r="AA340" s="101"/>
+      <c r="AB340" s="101"/>
     </row>
     <row r="341" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
@@ -29197,9 +29197,9 @@
       <c r="Y341" s="50">
         <v>1</v>
       </c>
-      <c r="Z341" s="97"/>
-      <c r="AA341" s="98"/>
-      <c r="AB341" s="98"/>
+      <c r="Z341" s="100"/>
+      <c r="AA341" s="101"/>
+      <c r="AB341" s="101"/>
     </row>
     <row r="342" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
@@ -29279,9 +29279,9 @@
       <c r="Y342" s="50">
         <v>1</v>
       </c>
-      <c r="Z342" s="97"/>
-      <c r="AA342" s="98"/>
-      <c r="AB342" s="98"/>
+      <c r="Z342" s="100"/>
+      <c r="AA342" s="101"/>
+      <c r="AB342" s="101"/>
     </row>
     <row r="343" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
@@ -29361,9 +29361,9 @@
       <c r="Y343" s="50">
         <v>1</v>
       </c>
-      <c r="Z343" s="97"/>
-      <c r="AA343" s="98"/>
-      <c r="AB343" s="98"/>
+      <c r="Z343" s="100"/>
+      <c r="AA343" s="101"/>
+      <c r="AB343" s="101"/>
     </row>
     <row r="344" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A344" s="43">
@@ -29441,11 +29441,11 @@
       <c r="Y344" s="40">
         <v>1</v>
       </c>
-      <c r="Z344" s="97" t="s">
+      <c r="Z344" s="100" t="s">
         <v>108</v>
       </c>
-      <c r="AA344" s="98"/>
-      <c r="AB344" s="98"/>
+      <c r="AA344" s="101"/>
+      <c r="AB344" s="101"/>
     </row>
     <row r="345" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
@@ -29523,9 +29523,9 @@
       <c r="Y345" s="50">
         <v>1</v>
       </c>
-      <c r="Z345" s="97"/>
-      <c r="AA345" s="98"/>
-      <c r="AB345" s="98"/>
+      <c r="Z345" s="100"/>
+      <c r="AA345" s="101"/>
+      <c r="AB345" s="101"/>
     </row>
     <row r="346" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A346" s="27">
@@ -29603,9 +29603,9 @@
       <c r="Y346" s="57">
         <v>1</v>
       </c>
-      <c r="Z346" s="97"/>
-      <c r="AA346" s="98"/>
-      <c r="AB346" s="98"/>
+      <c r="Z346" s="100"/>
+      <c r="AA346" s="101"/>
+      <c r="AB346" s="101"/>
     </row>
     <row r="347" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A347" s="33">
@@ -29683,11 +29683,11 @@
       <c r="Y347" s="57">
         <v>1</v>
       </c>
-      <c r="Z347" s="97" t="s">
+      <c r="Z347" s="100" t="s">
         <v>93</v>
       </c>
-      <c r="AA347" s="98"/>
-      <c r="AB347" s="98"/>
+      <c r="AA347" s="101"/>
+      <c r="AB347" s="101"/>
     </row>
     <row r="348" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A348" s="33">
@@ -29765,11 +29765,11 @@
       <c r="Y348" s="57">
         <v>1</v>
       </c>
-      <c r="Z348" s="97" t="s">
+      <c r="Z348" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="AA348" s="99"/>
-      <c r="AB348" s="99"/>
+      <c r="AA348" s="102"/>
+      <c r="AB348" s="102"/>
     </row>
     <row r="349" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
@@ -29850,7 +29850,7 @@
       </c>
     </row>
     <row r="350" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A350" s="114">
+      <c r="A350" s="97">
         <v>447</v>
       </c>
       <c r="B350" s="45">
@@ -29926,14 +29926,14 @@
       <c r="Y350" s="40">
         <v>1</v>
       </c>
-      <c r="Z350" s="97" t="s">
+      <c r="Z350" s="100" t="s">
         <v>112</v>
       </c>
-      <c r="AA350" s="98"/>
-      <c r="AB350" s="98"/>
+      <c r="AA350" s="101"/>
+      <c r="AB350" s="101"/>
     </row>
     <row r="351" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A351" s="115">
+      <c r="A351" s="98">
         <v>448</v>
       </c>
       <c r="B351" s="15">
@@ -30009,12 +30009,12 @@
       <c r="Y351" s="50">
         <v>1</v>
       </c>
-      <c r="Z351" s="97"/>
-      <c r="AA351" s="98"/>
-      <c r="AB351" s="98"/>
+      <c r="Z351" s="100"/>
+      <c r="AA351" s="101"/>
+      <c r="AB351" s="101"/>
     </row>
     <row r="352" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A352" s="116">
+      <c r="A352" s="99">
         <v>449</v>
       </c>
       <c r="B352" s="29">
@@ -30090,9 +30090,9 @@
       <c r="Y352" s="57">
         <v>1</v>
       </c>
-      <c r="Z352" s="97"/>
-      <c r="AA352" s="98"/>
-      <c r="AB352" s="98"/>
+      <c r="Z352" s="100"/>
+      <c r="AA352" s="101"/>
+      <c r="AB352" s="101"/>
     </row>
     <row r="353" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
@@ -30330,6 +30330,73 @@
     </row>
   </sheetData>
   <mergeCells count="83">
+    <mergeCell ref="Z326:AB343"/>
+    <mergeCell ref="Z344:AB346"/>
+    <mergeCell ref="Z252:AB262"/>
+    <mergeCell ref="Z263:AB264"/>
+    <mergeCell ref="Z315:AB317"/>
+    <mergeCell ref="Z318:AB325"/>
+    <mergeCell ref="Z295:AB295"/>
+    <mergeCell ref="Z276:AB287"/>
+    <mergeCell ref="Z288:AB289"/>
+    <mergeCell ref="Z290:AB292"/>
+    <mergeCell ref="Z265:AB275"/>
+    <mergeCell ref="Z296:AB312"/>
+    <mergeCell ref="Z314:AB314"/>
+    <mergeCell ref="Z293:AB293"/>
+    <mergeCell ref="Z5:AB5"/>
+    <mergeCell ref="Z4:AB4"/>
+    <mergeCell ref="Z164:AB164"/>
+    <mergeCell ref="Z153:AB157"/>
+    <mergeCell ref="Z50:AB50"/>
+    <mergeCell ref="Z89:AB89"/>
+    <mergeCell ref="Z88:AB88"/>
+    <mergeCell ref="Z86:AB87"/>
+    <mergeCell ref="Z58:AB58"/>
+    <mergeCell ref="Z51:AB57"/>
+    <mergeCell ref="Z85:AB85"/>
+    <mergeCell ref="Z67:AB84"/>
+    <mergeCell ref="Z59:AB66"/>
+    <mergeCell ref="Z90:AB90"/>
+    <mergeCell ref="Z91:AB91"/>
+    <mergeCell ref="Z148:AB152"/>
+    <mergeCell ref="Z48:AB48"/>
+    <mergeCell ref="Z47:AB47"/>
+    <mergeCell ref="Z49:AB49"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="Z8:AD8"/>
+    <mergeCell ref="Z28:AB28"/>
+    <mergeCell ref="Z9:AB9"/>
+    <mergeCell ref="Z10:AB27"/>
+    <mergeCell ref="Z29:AB46"/>
+    <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="Z6:AB6"/>
+    <mergeCell ref="Z7:AB7"/>
+    <mergeCell ref="Z92:AB93"/>
+    <mergeCell ref="Z94:AB94"/>
+    <mergeCell ref="Z95:AB111"/>
+    <mergeCell ref="Z158:AB162"/>
+    <mergeCell ref="Z206:AB220"/>
+    <mergeCell ref="Z130:AB147"/>
+    <mergeCell ref="Z112:AB129"/>
+    <mergeCell ref="Z221:AB222"/>
+    <mergeCell ref="Z223:AB224"/>
+    <mergeCell ref="Z163:AB163"/>
+    <mergeCell ref="Z165:AB165"/>
+    <mergeCell ref="Z166:AB166"/>
+    <mergeCell ref="Z169:AB175"/>
+    <mergeCell ref="Z197:AB197"/>
+    <mergeCell ref="Z198:AB198"/>
+    <mergeCell ref="Z168:AB168"/>
+    <mergeCell ref="Z202:AB202"/>
+    <mergeCell ref="Z203:AB203"/>
+    <mergeCell ref="Z204:AB204"/>
+    <mergeCell ref="Z205:AB205"/>
+    <mergeCell ref="Z176:AB193"/>
     <mergeCell ref="Z350:AB352"/>
     <mergeCell ref="Z167:AB167"/>
     <mergeCell ref="Z240:AB251"/>
@@ -30346,73 +30413,6 @@
     <mergeCell ref="Z294:AB294"/>
     <mergeCell ref="Z347:AB347"/>
     <mergeCell ref="Z348:AB348"/>
-    <mergeCell ref="Z221:AB222"/>
-    <mergeCell ref="Z223:AB224"/>
-    <mergeCell ref="Z163:AB163"/>
-    <mergeCell ref="Z165:AB165"/>
-    <mergeCell ref="Z166:AB166"/>
-    <mergeCell ref="Z169:AB175"/>
-    <mergeCell ref="Z197:AB197"/>
-    <mergeCell ref="Z198:AB198"/>
-    <mergeCell ref="Z168:AB168"/>
-    <mergeCell ref="Z202:AB202"/>
-    <mergeCell ref="Z203:AB203"/>
-    <mergeCell ref="Z204:AB204"/>
-    <mergeCell ref="Z205:AB205"/>
-    <mergeCell ref="Z176:AB193"/>
-    <mergeCell ref="Z92:AB93"/>
-    <mergeCell ref="Z94:AB94"/>
-    <mergeCell ref="Z95:AB111"/>
-    <mergeCell ref="Z158:AB162"/>
-    <mergeCell ref="Z206:AB220"/>
-    <mergeCell ref="Z130:AB147"/>
-    <mergeCell ref="Z112:AB129"/>
-    <mergeCell ref="Z48:AB48"/>
-    <mergeCell ref="Z47:AB47"/>
-    <mergeCell ref="Z49:AB49"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="Z8:AD8"/>
-    <mergeCell ref="Z28:AB28"/>
-    <mergeCell ref="Z9:AB9"/>
-    <mergeCell ref="Z10:AB27"/>
-    <mergeCell ref="Z29:AB46"/>
-    <mergeCell ref="U1:Y1"/>
-    <mergeCell ref="Z6:AB6"/>
-    <mergeCell ref="Z7:AB7"/>
-    <mergeCell ref="Z5:AB5"/>
-    <mergeCell ref="Z4:AB4"/>
-    <mergeCell ref="Z164:AB164"/>
-    <mergeCell ref="Z153:AB157"/>
-    <mergeCell ref="Z50:AB50"/>
-    <mergeCell ref="Z89:AB89"/>
-    <mergeCell ref="Z88:AB88"/>
-    <mergeCell ref="Z86:AB87"/>
-    <mergeCell ref="Z58:AB58"/>
-    <mergeCell ref="Z51:AB57"/>
-    <mergeCell ref="Z85:AB85"/>
-    <mergeCell ref="Z67:AB84"/>
-    <mergeCell ref="Z59:AB66"/>
-    <mergeCell ref="Z90:AB90"/>
-    <mergeCell ref="Z91:AB91"/>
-    <mergeCell ref="Z148:AB152"/>
-    <mergeCell ref="Z326:AB343"/>
-    <mergeCell ref="Z344:AB346"/>
-    <mergeCell ref="Z252:AB262"/>
-    <mergeCell ref="Z263:AB264"/>
-    <mergeCell ref="Z315:AB317"/>
-    <mergeCell ref="Z318:AB325"/>
-    <mergeCell ref="Z295:AB295"/>
-    <mergeCell ref="Z276:AB287"/>
-    <mergeCell ref="Z288:AB289"/>
-    <mergeCell ref="Z290:AB292"/>
-    <mergeCell ref="Z265:AB275"/>
-    <mergeCell ref="Z296:AB312"/>
-    <mergeCell ref="Z314:AB314"/>
-    <mergeCell ref="Z293:AB293"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Simulations_IDS.xlsx
+++ b/Simulations_IDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documentos_Betran\DropletEvaporation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A9BF5C-F61D-4A01-8A32-E4DB8D90CF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A6D236-E2B9-4DAA-A6EB-3F6F9534F44D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{73239687-5BB6-4FA0-A3B4-8BE280184789}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{73239687-5BB6-4FA0-A3B4-8BE280184789}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="115">
   <si>
     <t>ID</t>
   </si>
@@ -376,6 +376,12 @@
   </si>
   <si>
     <t>Trio de pruebas de siempre con nuevas Difusividades</t>
+  </si>
+  <si>
+    <t>Alejandro sin radiación</t>
+  </si>
+  <si>
+    <t>Alejandro con su radiación</t>
   </si>
 </sst>
 </file>
@@ -796,6 +802,12 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -816,9 +828,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -833,9 +842,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1165,7 +1171,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFC78505-487D-4D76-94E1-903AFBAADA28}">
-  <dimension ref="A1:AF355"/>
+  <dimension ref="A1:AF357"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" customWidth="1"/>
@@ -1195,42 +1201,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="B1" s="109" t="s">
+      <c r="B1" s="110" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="110" t="s">
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="111"/>
-      <c r="I1" s="111"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="111" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="112"/>
-      <c r="M1" s="110" t="s">
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="112" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="113"/>
+      <c r="M1" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="110" t="s">
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="113"/>
+      <c r="R1" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111" t="s">
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112" t="s">
         <v>8</v>
       </c>
-      <c r="V1" s="111"/>
-      <c r="W1" s="111"/>
-      <c r="X1" s="111"/>
-      <c r="Y1" s="112"/>
+      <c r="V1" s="112"/>
+      <c r="W1" s="112"/>
+      <c r="X1" s="112"/>
+      <c r="Y1" s="113"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1459,11 +1465,11 @@
       <c r="Y4" s="1">
         <v>1</v>
       </c>
-      <c r="Z4" s="107" t="s">
+      <c r="Z4" s="100" t="s">
         <v>46</v>
       </c>
-      <c r="AA4" s="113"/>
-      <c r="AB4" s="113"/>
+      <c r="AA4" s="101"/>
+      <c r="AB4" s="101"/>
       <c r="AC4" s="65"/>
       <c r="AD4" s="65"/>
     </row>
@@ -1544,11 +1550,11 @@
       <c r="Y5" s="1">
         <v>1</v>
       </c>
-      <c r="Z5" s="107" t="s">
+      <c r="Z5" s="100" t="s">
         <v>47</v>
       </c>
-      <c r="AA5" s="113"/>
-      <c r="AB5" s="113"/>
+      <c r="AA5" s="101"/>
+      <c r="AB5" s="101"/>
       <c r="AC5" s="65"/>
       <c r="AD5" s="65"/>
     </row>
@@ -1629,11 +1635,11 @@
       <c r="Y6" s="1">
         <v>1</v>
       </c>
-      <c r="Z6" s="107" t="s">
+      <c r="Z6" s="100" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="113"/>
-      <c r="AB6" s="113"/>
+      <c r="AA6" s="101"/>
+      <c r="AB6" s="101"/>
       <c r="AC6" s="65"/>
       <c r="AD6" s="65"/>
     </row>
@@ -1714,11 +1720,11 @@
       <c r="Y7" s="1">
         <v>1</v>
       </c>
-      <c r="Z7" s="107" t="s">
+      <c r="Z7" s="100" t="s">
         <v>49</v>
       </c>
-      <c r="AA7" s="113"/>
-      <c r="AB7" s="113"/>
+      <c r="AA7" s="101"/>
+      <c r="AB7" s="101"/>
       <c r="AC7" s="65"/>
       <c r="AD7" s="65"/>
     </row>
@@ -1799,13 +1805,13 @@
       <c r="Y8" s="38">
         <v>1</v>
       </c>
-      <c r="Z8" s="107" t="s">
+      <c r="Z8" s="100" t="s">
         <v>53</v>
       </c>
-      <c r="AA8" s="108"/>
-      <c r="AB8" s="108"/>
-      <c r="AC8" s="108"/>
-      <c r="AD8" s="108"/>
+      <c r="AA8" s="109"/>
+      <c r="AB8" s="109"/>
+      <c r="AC8" s="109"/>
+      <c r="AD8" s="109"/>
       <c r="AE8" s="20"/>
       <c r="AF8" s="20"/>
     </row>
@@ -1886,11 +1892,11 @@
       <c r="Y9" s="1">
         <v>1</v>
       </c>
-      <c r="Z9" s="107" t="s">
+      <c r="Z9" s="100" t="s">
         <v>50</v>
       </c>
-      <c r="AA9" s="108"/>
-      <c r="AB9" s="108"/>
+      <c r="AA9" s="109"/>
+      <c r="AB9" s="109"/>
       <c r="AC9" s="65"/>
       <c r="AD9" s="65"/>
     </row>
@@ -1971,11 +1977,11 @@
       <c r="Y10" s="43">
         <v>1</v>
       </c>
-      <c r="Z10" s="100" t="s">
+      <c r="Z10" s="102" t="s">
         <v>51</v>
       </c>
-      <c r="AA10" s="101"/>
-      <c r="AB10" s="101"/>
+      <c r="AA10" s="103"/>
+      <c r="AB10" s="103"/>
       <c r="AC10" s="65"/>
       <c r="AD10" s="65"/>
     </row>
@@ -2058,9 +2064,9 @@
       <c r="Y11" s="1">
         <v>1</v>
       </c>
-      <c r="Z11" s="100"/>
-      <c r="AA11" s="101"/>
-      <c r="AB11" s="101"/>
+      <c r="Z11" s="102"/>
+      <c r="AA11" s="103"/>
+      <c r="AB11" s="103"/>
       <c r="AC11" s="65"/>
       <c r="AD11" s="65"/>
     </row>
@@ -2142,9 +2148,9 @@
       <c r="Y12" s="1">
         <v>1</v>
       </c>
-      <c r="Z12" s="100"/>
-      <c r="AA12" s="101"/>
-      <c r="AB12" s="101"/>
+      <c r="Z12" s="102"/>
+      <c r="AA12" s="103"/>
+      <c r="AB12" s="103"/>
       <c r="AC12" s="65"/>
       <c r="AD12" s="65"/>
     </row>
@@ -2226,9 +2232,9 @@
       <c r="Y13" s="1">
         <v>1</v>
       </c>
-      <c r="Z13" s="100"/>
-      <c r="AA13" s="101"/>
-      <c r="AB13" s="101"/>
+      <c r="Z13" s="102"/>
+      <c r="AA13" s="103"/>
+      <c r="AB13" s="103"/>
       <c r="AC13" s="65"/>
       <c r="AD13" s="65"/>
     </row>
@@ -2310,9 +2316,9 @@
       <c r="Y14" s="1">
         <v>1</v>
       </c>
-      <c r="Z14" s="100"/>
-      <c r="AA14" s="101"/>
-      <c r="AB14" s="101"/>
+      <c r="Z14" s="102"/>
+      <c r="AA14" s="103"/>
+      <c r="AB14" s="103"/>
       <c r="AC14" s="65"/>
       <c r="AD14" s="65"/>
     </row>
@@ -2394,9 +2400,9 @@
       <c r="Y15" s="1">
         <v>1</v>
       </c>
-      <c r="Z15" s="100"/>
-      <c r="AA15" s="101"/>
-      <c r="AB15" s="101"/>
+      <c r="Z15" s="102"/>
+      <c r="AA15" s="103"/>
+      <c r="AB15" s="103"/>
       <c r="AC15" s="65"/>
       <c r="AD15" s="65"/>
     </row>
@@ -2478,9 +2484,9 @@
       <c r="Y16" s="1">
         <v>1</v>
       </c>
-      <c r="Z16" s="100"/>
-      <c r="AA16" s="101"/>
-      <c r="AB16" s="101"/>
+      <c r="Z16" s="102"/>
+      <c r="AA16" s="103"/>
+      <c r="AB16" s="103"/>
       <c r="AC16" s="65"/>
       <c r="AD16" s="65"/>
     </row>
@@ -2562,9 +2568,9 @@
       <c r="Y17" s="1">
         <v>1</v>
       </c>
-      <c r="Z17" s="100"/>
-      <c r="AA17" s="101"/>
-      <c r="AB17" s="101"/>
+      <c r="Z17" s="102"/>
+      <c r="AA17" s="103"/>
+      <c r="AB17" s="103"/>
       <c r="AC17" s="65"/>
       <c r="AD17" s="65"/>
     </row>
@@ -2646,9 +2652,9 @@
       <c r="Y18" s="1">
         <v>1</v>
       </c>
-      <c r="Z18" s="100"/>
-      <c r="AA18" s="101"/>
-      <c r="AB18" s="101"/>
+      <c r="Z18" s="102"/>
+      <c r="AA18" s="103"/>
+      <c r="AB18" s="103"/>
       <c r="AC18" s="65"/>
       <c r="AD18" s="65"/>
     </row>
@@ -2730,9 +2736,9 @@
       <c r="Y19" s="1">
         <v>1</v>
       </c>
-      <c r="Z19" s="100"/>
-      <c r="AA19" s="101"/>
-      <c r="AB19" s="101"/>
+      <c r="Z19" s="102"/>
+      <c r="AA19" s="103"/>
+      <c r="AB19" s="103"/>
       <c r="AC19" s="65"/>
       <c r="AD19" s="65"/>
     </row>
@@ -2814,9 +2820,9 @@
       <c r="Y20" s="1">
         <v>1</v>
       </c>
-      <c r="Z20" s="100"/>
-      <c r="AA20" s="101"/>
-      <c r="AB20" s="101"/>
+      <c r="Z20" s="102"/>
+      <c r="AA20" s="103"/>
+      <c r="AB20" s="103"/>
       <c r="AC20" s="65"/>
       <c r="AD20" s="65"/>
     </row>
@@ -2898,9 +2904,9 @@
       <c r="Y21" s="1">
         <v>1</v>
       </c>
-      <c r="Z21" s="100"/>
-      <c r="AA21" s="101"/>
-      <c r="AB21" s="101"/>
+      <c r="Z21" s="102"/>
+      <c r="AA21" s="103"/>
+      <c r="AB21" s="103"/>
       <c r="AC21" s="65"/>
       <c r="AD21" s="65"/>
     </row>
@@ -2982,9 +2988,9 @@
       <c r="Y22" s="1">
         <v>1</v>
       </c>
-      <c r="Z22" s="100"/>
-      <c r="AA22" s="101"/>
-      <c r="AB22" s="101"/>
+      <c r="Z22" s="102"/>
+      <c r="AA22" s="103"/>
+      <c r="AB22" s="103"/>
       <c r="AC22" s="65"/>
       <c r="AD22" s="65"/>
     </row>
@@ -3066,9 +3072,9 @@
       <c r="Y23" s="1">
         <v>1</v>
       </c>
-      <c r="Z23" s="100"/>
-      <c r="AA23" s="101"/>
-      <c r="AB23" s="101"/>
+      <c r="Z23" s="102"/>
+      <c r="AA23" s="103"/>
+      <c r="AB23" s="103"/>
       <c r="AC23" s="65"/>
       <c r="AD23" s="65"/>
     </row>
@@ -3150,9 +3156,9 @@
       <c r="Y24" s="1">
         <v>1</v>
       </c>
-      <c r="Z24" s="100"/>
-      <c r="AA24" s="101"/>
-      <c r="AB24" s="101"/>
+      <c r="Z24" s="102"/>
+      <c r="AA24" s="103"/>
+      <c r="AB24" s="103"/>
       <c r="AC24" s="65"/>
       <c r="AD24" s="65"/>
     </row>
@@ -3234,9 +3240,9 @@
       <c r="Y25" s="1">
         <v>1</v>
       </c>
-      <c r="Z25" s="100"/>
-      <c r="AA25" s="101"/>
-      <c r="AB25" s="101"/>
+      <c r="Z25" s="102"/>
+      <c r="AA25" s="103"/>
+      <c r="AB25" s="103"/>
       <c r="AC25" s="65"/>
       <c r="AD25" s="65"/>
     </row>
@@ -3318,9 +3324,9 @@
       <c r="Y26" s="1">
         <v>1</v>
       </c>
-      <c r="Z26" s="100"/>
-      <c r="AA26" s="101"/>
-      <c r="AB26" s="101"/>
+      <c r="Z26" s="102"/>
+      <c r="AA26" s="103"/>
+      <c r="AB26" s="103"/>
       <c r="AC26" s="65"/>
       <c r="AD26" s="65"/>
     </row>
@@ -3402,9 +3408,9 @@
       <c r="Y27" s="27">
         <v>1</v>
       </c>
-      <c r="Z27" s="100"/>
-      <c r="AA27" s="101"/>
-      <c r="AB27" s="101"/>
+      <c r="Z27" s="102"/>
+      <c r="AA27" s="103"/>
+      <c r="AB27" s="103"/>
       <c r="AC27" s="65"/>
       <c r="AD27" s="65"/>
     </row>
@@ -3485,11 +3491,11 @@
       <c r="Y28" s="33">
         <v>1</v>
       </c>
-      <c r="Z28" s="107" t="s">
+      <c r="Z28" s="100" t="s">
         <v>52</v>
       </c>
-      <c r="AA28" s="108"/>
-      <c r="AB28" s="108"/>
+      <c r="AA28" s="109"/>
+      <c r="AB28" s="109"/>
       <c r="AC28" s="65"/>
       <c r="AD28" s="65"/>
     </row>
@@ -3571,11 +3577,11 @@
       <c r="Y29" s="1">
         <v>1</v>
       </c>
-      <c r="Z29" s="100" t="s">
+      <c r="Z29" s="102" t="s">
         <v>51</v>
       </c>
-      <c r="AA29" s="101"/>
-      <c r="AB29" s="101"/>
+      <c r="AA29" s="103"/>
+      <c r="AB29" s="103"/>
       <c r="AC29" s="65"/>
       <c r="AD29" s="65"/>
     </row>
@@ -3657,9 +3663,9 @@
       <c r="Y30" s="1">
         <v>1</v>
       </c>
-      <c r="Z30" s="100"/>
-      <c r="AA30" s="101"/>
-      <c r="AB30" s="101"/>
+      <c r="Z30" s="102"/>
+      <c r="AA30" s="103"/>
+      <c r="AB30" s="103"/>
       <c r="AC30" s="65"/>
       <c r="AD30" s="65"/>
     </row>
@@ -3741,9 +3747,9 @@
       <c r="Y31" s="1">
         <v>1</v>
       </c>
-      <c r="Z31" s="100"/>
-      <c r="AA31" s="101"/>
-      <c r="AB31" s="101"/>
+      <c r="Z31" s="102"/>
+      <c r="AA31" s="103"/>
+      <c r="AB31" s="103"/>
       <c r="AC31" s="65"/>
       <c r="AD31" s="65"/>
     </row>
@@ -3825,9 +3831,9 @@
       <c r="Y32" s="1">
         <v>1</v>
       </c>
-      <c r="Z32" s="100"/>
-      <c r="AA32" s="101"/>
-      <c r="AB32" s="101"/>
+      <c r="Z32" s="102"/>
+      <c r="AA32" s="103"/>
+      <c r="AB32" s="103"/>
       <c r="AC32" s="65"/>
       <c r="AD32" s="65"/>
     </row>
@@ -3909,9 +3915,9 @@
       <c r="Y33" s="1">
         <v>1</v>
       </c>
-      <c r="Z33" s="100"/>
-      <c r="AA33" s="101"/>
-      <c r="AB33" s="101"/>
+      <c r="Z33" s="102"/>
+      <c r="AA33" s="103"/>
+      <c r="AB33" s="103"/>
       <c r="AC33" s="65"/>
       <c r="AD33" s="65"/>
     </row>
@@ -3993,9 +3999,9 @@
       <c r="Y34" s="1">
         <v>1</v>
       </c>
-      <c r="Z34" s="100"/>
-      <c r="AA34" s="101"/>
-      <c r="AB34" s="101"/>
+      <c r="Z34" s="102"/>
+      <c r="AA34" s="103"/>
+      <c r="AB34" s="103"/>
       <c r="AC34" s="65"/>
       <c r="AD34" s="65"/>
     </row>
@@ -4077,9 +4083,9 @@
       <c r="Y35" s="1">
         <v>1</v>
       </c>
-      <c r="Z35" s="100"/>
-      <c r="AA35" s="101"/>
-      <c r="AB35" s="101"/>
+      <c r="Z35" s="102"/>
+      <c r="AA35" s="103"/>
+      <c r="AB35" s="103"/>
       <c r="AC35" s="65"/>
       <c r="AD35" s="65"/>
     </row>
@@ -4161,9 +4167,9 @@
       <c r="Y36" s="1">
         <v>1</v>
       </c>
-      <c r="Z36" s="100"/>
-      <c r="AA36" s="101"/>
-      <c r="AB36" s="101"/>
+      <c r="Z36" s="102"/>
+      <c r="AA36" s="103"/>
+      <c r="AB36" s="103"/>
       <c r="AC36" s="65"/>
       <c r="AD36" s="65"/>
     </row>
@@ -4245,9 +4251,9 @@
       <c r="Y37" s="1">
         <v>1</v>
       </c>
-      <c r="Z37" s="100"/>
-      <c r="AA37" s="101"/>
-      <c r="AB37" s="101"/>
+      <c r="Z37" s="102"/>
+      <c r="AA37" s="103"/>
+      <c r="AB37" s="103"/>
       <c r="AC37" s="65"/>
       <c r="AD37" s="65"/>
     </row>
@@ -4329,9 +4335,9 @@
       <c r="Y38" s="1">
         <v>1</v>
       </c>
-      <c r="Z38" s="100"/>
-      <c r="AA38" s="101"/>
-      <c r="AB38" s="101"/>
+      <c r="Z38" s="102"/>
+      <c r="AA38" s="103"/>
+      <c r="AB38" s="103"/>
       <c r="AC38" s="65"/>
       <c r="AD38" s="65"/>
     </row>
@@ -4413,9 +4419,9 @@
       <c r="Y39" s="1">
         <v>1</v>
       </c>
-      <c r="Z39" s="100"/>
-      <c r="AA39" s="101"/>
-      <c r="AB39" s="101"/>
+      <c r="Z39" s="102"/>
+      <c r="AA39" s="103"/>
+      <c r="AB39" s="103"/>
       <c r="AC39" s="65"/>
       <c r="AD39" s="65"/>
     </row>
@@ -4497,9 +4503,9 @@
       <c r="Y40" s="1">
         <v>1</v>
       </c>
-      <c r="Z40" s="100"/>
-      <c r="AA40" s="101"/>
-      <c r="AB40" s="101"/>
+      <c r="Z40" s="102"/>
+      <c r="AA40" s="103"/>
+      <c r="AB40" s="103"/>
       <c r="AC40" s="65"/>
       <c r="AD40" s="65"/>
     </row>
@@ -4581,9 +4587,9 @@
       <c r="Y41" s="1">
         <v>1</v>
       </c>
-      <c r="Z41" s="100"/>
-      <c r="AA41" s="101"/>
-      <c r="AB41" s="101"/>
+      <c r="Z41" s="102"/>
+      <c r="AA41" s="103"/>
+      <c r="AB41" s="103"/>
       <c r="AC41" s="65"/>
       <c r="AD41" s="65"/>
     </row>
@@ -4665,9 +4671,9 @@
       <c r="Y42" s="1">
         <v>1</v>
       </c>
-      <c r="Z42" s="100"/>
-      <c r="AA42" s="101"/>
-      <c r="AB42" s="101"/>
+      <c r="Z42" s="102"/>
+      <c r="AA42" s="103"/>
+      <c r="AB42" s="103"/>
       <c r="AC42" s="65"/>
       <c r="AD42" s="65"/>
     </row>
@@ -4749,9 +4755,9 @@
       <c r="Y43" s="1">
         <v>1</v>
       </c>
-      <c r="Z43" s="100"/>
-      <c r="AA43" s="101"/>
-      <c r="AB43" s="101"/>
+      <c r="Z43" s="102"/>
+      <c r="AA43" s="103"/>
+      <c r="AB43" s="103"/>
       <c r="AC43" s="65"/>
       <c r="AD43" s="65"/>
     </row>
@@ -4833,9 +4839,9 @@
       <c r="Y44" s="1">
         <v>1</v>
       </c>
-      <c r="Z44" s="100"/>
-      <c r="AA44" s="101"/>
-      <c r="AB44" s="101"/>
+      <c r="Z44" s="102"/>
+      <c r="AA44" s="103"/>
+      <c r="AB44" s="103"/>
       <c r="AC44" s="65"/>
       <c r="AD44" s="65"/>
     </row>
@@ -4917,9 +4923,9 @@
       <c r="Y45" s="1">
         <v>1</v>
       </c>
-      <c r="Z45" s="100"/>
-      <c r="AA45" s="101"/>
-      <c r="AB45" s="101"/>
+      <c r="Z45" s="102"/>
+      <c r="AA45" s="103"/>
+      <c r="AB45" s="103"/>
       <c r="AC45" s="65"/>
       <c r="AD45" s="65"/>
     </row>
@@ -5001,9 +5007,9 @@
       <c r="Y46" s="1">
         <v>1</v>
       </c>
-      <c r="Z46" s="100"/>
-      <c r="AA46" s="101"/>
-      <c r="AB46" s="101"/>
+      <c r="Z46" s="102"/>
+      <c r="AA46" s="103"/>
+      <c r="AB46" s="103"/>
       <c r="AC46" s="65"/>
       <c r="AD46" s="65"/>
     </row>
@@ -5084,11 +5090,11 @@
       <c r="Y47" s="43">
         <v>1</v>
       </c>
-      <c r="Z47" s="107" t="s">
+      <c r="Z47" s="100" t="s">
         <v>54</v>
       </c>
-      <c r="AA47" s="108"/>
-      <c r="AB47" s="108"/>
+      <c r="AA47" s="109"/>
+      <c r="AB47" s="109"/>
       <c r="AC47" s="66"/>
       <c r="AD47" s="65"/>
     </row>
@@ -5170,11 +5176,11 @@
       <c r="Y48" s="43">
         <v>1</v>
       </c>
-      <c r="Z48" s="105" t="s">
+      <c r="Z48" s="107" t="s">
         <v>55</v>
       </c>
-      <c r="AA48" s="106"/>
-      <c r="AB48" s="106"/>
+      <c r="AA48" s="108"/>
+      <c r="AB48" s="108"/>
       <c r="AC48" s="67"/>
       <c r="AD48" s="65"/>
     </row>
@@ -5255,11 +5261,11 @@
       <c r="Y49" s="43">
         <v>1</v>
       </c>
-      <c r="Z49" s="107" t="s">
+      <c r="Z49" s="100" t="s">
         <v>56</v>
       </c>
-      <c r="AA49" s="108"/>
-      <c r="AB49" s="108"/>
+      <c r="AA49" s="109"/>
+      <c r="AB49" s="109"/>
       <c r="AC49" s="65"/>
       <c r="AD49" s="65"/>
     </row>
@@ -5339,11 +5345,11 @@
       <c r="Y50" s="40">
         <v>1</v>
       </c>
-      <c r="Z50" s="107" t="s">
+      <c r="Z50" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="AA50" s="108"/>
-      <c r="AB50" s="108"/>
+      <c r="AA50" s="109"/>
+      <c r="AB50" s="109"/>
       <c r="AC50" s="65"/>
       <c r="AD50" s="65"/>
     </row>
@@ -5425,11 +5431,11 @@
       <c r="Y51" s="43">
         <v>1</v>
       </c>
-      <c r="Z51" s="100" t="s">
+      <c r="Z51" s="102" t="s">
         <v>59</v>
       </c>
-      <c r="AA51" s="101"/>
-      <c r="AB51" s="101"/>
+      <c r="AA51" s="103"/>
+      <c r="AB51" s="103"/>
       <c r="AC51" s="65"/>
       <c r="AD51" s="65"/>
     </row>
@@ -5511,9 +5517,9 @@
       <c r="Y52" s="1">
         <v>1</v>
       </c>
-      <c r="Z52" s="100"/>
-      <c r="AA52" s="101"/>
-      <c r="AB52" s="101"/>
+      <c r="Z52" s="102"/>
+      <c r="AA52" s="103"/>
+      <c r="AB52" s="103"/>
       <c r="AC52" s="65"/>
       <c r="AD52" s="65"/>
     </row>
@@ -5595,9 +5601,9 @@
       <c r="Y53" s="1">
         <v>1</v>
       </c>
-      <c r="Z53" s="100"/>
-      <c r="AA53" s="101"/>
-      <c r="AB53" s="101"/>
+      <c r="Z53" s="102"/>
+      <c r="AA53" s="103"/>
+      <c r="AB53" s="103"/>
       <c r="AC53" s="65"/>
       <c r="AD53" s="65"/>
     </row>
@@ -5679,9 +5685,9 @@
       <c r="Y54" s="1">
         <v>1</v>
       </c>
-      <c r="Z54" s="100"/>
-      <c r="AA54" s="101"/>
-      <c r="AB54" s="101"/>
+      <c r="Z54" s="102"/>
+      <c r="AA54" s="103"/>
+      <c r="AB54" s="103"/>
       <c r="AC54" s="65"/>
       <c r="AD54" s="65"/>
     </row>
@@ -5763,9 +5769,9 @@
       <c r="Y55" s="1">
         <v>1</v>
       </c>
-      <c r="Z55" s="100"/>
-      <c r="AA55" s="101"/>
-      <c r="AB55" s="101"/>
+      <c r="Z55" s="102"/>
+      <c r="AA55" s="103"/>
+      <c r="AB55" s="103"/>
       <c r="AC55" s="65"/>
       <c r="AD55" s="65"/>
     </row>
@@ -5847,9 +5853,9 @@
       <c r="Y56" s="1">
         <v>1</v>
       </c>
-      <c r="Z56" s="100"/>
-      <c r="AA56" s="101"/>
-      <c r="AB56" s="101"/>
+      <c r="Z56" s="102"/>
+      <c r="AA56" s="103"/>
+      <c r="AB56" s="103"/>
       <c r="AC56" s="65"/>
       <c r="AD56" s="65"/>
     </row>
@@ -5931,9 +5937,9 @@
       <c r="Y57" s="27">
         <v>1</v>
       </c>
-      <c r="Z57" s="100"/>
-      <c r="AA57" s="101"/>
-      <c r="AB57" s="101"/>
+      <c r="Z57" s="102"/>
+      <c r="AA57" s="103"/>
+      <c r="AB57" s="103"/>
       <c r="AC57" s="65"/>
       <c r="AD57" s="65"/>
     </row>
@@ -6014,11 +6020,11 @@
       <c r="Y58" s="53">
         <v>1</v>
       </c>
-      <c r="Z58" s="105" t="s">
+      <c r="Z58" s="107" t="s">
         <v>58</v>
       </c>
-      <c r="AA58" s="106"/>
-      <c r="AB58" s="106"/>
+      <c r="AA58" s="108"/>
+      <c r="AB58" s="108"/>
       <c r="AC58" s="65"/>
       <c r="AD58" s="65"/>
     </row>
@@ -6099,11 +6105,11 @@
       <c r="Y59" s="50">
         <v>1</v>
       </c>
-      <c r="Z59" s="100" t="s">
+      <c r="Z59" s="102" t="s">
         <v>60</v>
       </c>
-      <c r="AA59" s="101"/>
-      <c r="AB59" s="101"/>
+      <c r="AA59" s="103"/>
+      <c r="AB59" s="103"/>
       <c r="AC59" s="65"/>
       <c r="AD59" s="65"/>
     </row>
@@ -6184,9 +6190,9 @@
       <c r="Y60" s="50">
         <v>1</v>
       </c>
-      <c r="Z60" s="100"/>
-      <c r="AA60" s="101"/>
-      <c r="AB60" s="101"/>
+      <c r="Z60" s="102"/>
+      <c r="AA60" s="103"/>
+      <c r="AB60" s="103"/>
       <c r="AC60" s="65"/>
       <c r="AD60" s="65"/>
     </row>
@@ -6267,9 +6273,9 @@
       <c r="Y61" s="50">
         <v>1</v>
       </c>
-      <c r="Z61" s="100"/>
-      <c r="AA61" s="101"/>
-      <c r="AB61" s="101"/>
+      <c r="Z61" s="102"/>
+      <c r="AA61" s="103"/>
+      <c r="AB61" s="103"/>
       <c r="AC61" s="65"/>
       <c r="AD61" s="65"/>
     </row>
@@ -6350,9 +6356,9 @@
       <c r="Y62" s="50">
         <v>1</v>
       </c>
-      <c r="Z62" s="100"/>
-      <c r="AA62" s="101"/>
-      <c r="AB62" s="101"/>
+      <c r="Z62" s="102"/>
+      <c r="AA62" s="103"/>
+      <c r="AB62" s="103"/>
       <c r="AC62" s="65"/>
       <c r="AD62" s="65"/>
     </row>
@@ -6433,9 +6439,9 @@
       <c r="Y63" s="50">
         <v>1</v>
       </c>
-      <c r="Z63" s="100"/>
-      <c r="AA63" s="101"/>
-      <c r="AB63" s="101"/>
+      <c r="Z63" s="102"/>
+      <c r="AA63" s="103"/>
+      <c r="AB63" s="103"/>
       <c r="AC63" s="65"/>
       <c r="AD63" s="65"/>
     </row>
@@ -6516,9 +6522,9 @@
       <c r="Y64" s="50">
         <v>1</v>
       </c>
-      <c r="Z64" s="100"/>
-      <c r="AA64" s="101"/>
-      <c r="AB64" s="101"/>
+      <c r="Z64" s="102"/>
+      <c r="AA64" s="103"/>
+      <c r="AB64" s="103"/>
       <c r="AC64" s="65"/>
       <c r="AD64" s="65"/>
     </row>
@@ -6599,9 +6605,9 @@
       <c r="Y65" s="50">
         <v>1</v>
       </c>
-      <c r="Z65" s="100"/>
-      <c r="AA65" s="101"/>
-      <c r="AB65" s="101"/>
+      <c r="Z65" s="102"/>
+      <c r="AA65" s="103"/>
+      <c r="AB65" s="103"/>
       <c r="AC65" s="65"/>
       <c r="AD65" s="65"/>
     </row>
@@ -6682,9 +6688,9 @@
       <c r="Y66" s="57">
         <v>1</v>
       </c>
-      <c r="Z66" s="100"/>
-      <c r="AA66" s="101"/>
-      <c r="AB66" s="101"/>
+      <c r="Z66" s="102"/>
+      <c r="AA66" s="103"/>
+      <c r="AB66" s="103"/>
       <c r="AC66" s="65"/>
       <c r="AD66" s="65"/>
     </row>
@@ -6766,11 +6772,11 @@
       <c r="Y67" s="43">
         <v>1</v>
       </c>
-      <c r="Z67" s="100" t="s">
+      <c r="Z67" s="102" t="s">
         <v>61</v>
       </c>
-      <c r="AA67" s="102"/>
-      <c r="AB67" s="102"/>
+      <c r="AA67" s="104"/>
+      <c r="AB67" s="104"/>
       <c r="AC67" s="65"/>
       <c r="AD67" s="65"/>
     </row>
@@ -6852,9 +6858,9 @@
       <c r="Y68" s="1">
         <v>1</v>
       </c>
-      <c r="Z68" s="100"/>
-      <c r="AA68" s="102"/>
-      <c r="AB68" s="102"/>
+      <c r="Z68" s="102"/>
+      <c r="AA68" s="104"/>
+      <c r="AB68" s="104"/>
       <c r="AC68" s="65"/>
       <c r="AD68" s="65"/>
     </row>
@@ -6936,9 +6942,9 @@
       <c r="Y69" s="1">
         <v>1</v>
       </c>
-      <c r="Z69" s="100"/>
-      <c r="AA69" s="102"/>
-      <c r="AB69" s="102"/>
+      <c r="Z69" s="102"/>
+      <c r="AA69" s="104"/>
+      <c r="AB69" s="104"/>
       <c r="AC69" s="65"/>
       <c r="AD69" s="65"/>
     </row>
@@ -7020,9 +7026,9 @@
       <c r="Y70" s="1">
         <v>1</v>
       </c>
-      <c r="Z70" s="100"/>
-      <c r="AA70" s="102"/>
-      <c r="AB70" s="102"/>
+      <c r="Z70" s="102"/>
+      <c r="AA70" s="104"/>
+      <c r="AB70" s="104"/>
       <c r="AC70" s="65"/>
       <c r="AD70" s="65"/>
     </row>
@@ -7104,9 +7110,9 @@
       <c r="Y71" s="1">
         <v>1</v>
       </c>
-      <c r="Z71" s="100"/>
-      <c r="AA71" s="102"/>
-      <c r="AB71" s="102"/>
+      <c r="Z71" s="102"/>
+      <c r="AA71" s="104"/>
+      <c r="AB71" s="104"/>
       <c r="AC71" s="65"/>
       <c r="AD71" s="65"/>
     </row>
@@ -7188,9 +7194,9 @@
       <c r="Y72" s="1">
         <v>1</v>
       </c>
-      <c r="Z72" s="100"/>
-      <c r="AA72" s="102"/>
-      <c r="AB72" s="102"/>
+      <c r="Z72" s="102"/>
+      <c r="AA72" s="104"/>
+      <c r="AB72" s="104"/>
       <c r="AC72" s="65"/>
       <c r="AD72" s="65"/>
     </row>
@@ -7272,9 +7278,9 @@
       <c r="Y73" s="1">
         <v>1</v>
       </c>
-      <c r="Z73" s="100"/>
-      <c r="AA73" s="102"/>
-      <c r="AB73" s="102"/>
+      <c r="Z73" s="102"/>
+      <c r="AA73" s="104"/>
+      <c r="AB73" s="104"/>
       <c r="AC73" s="65"/>
       <c r="AD73" s="65"/>
     </row>
@@ -7356,9 +7362,9 @@
       <c r="Y74" s="1">
         <v>1</v>
       </c>
-      <c r="Z74" s="100"/>
-      <c r="AA74" s="102"/>
-      <c r="AB74" s="102"/>
+      <c r="Z74" s="102"/>
+      <c r="AA74" s="104"/>
+      <c r="AB74" s="104"/>
       <c r="AC74" s="65"/>
       <c r="AD74" s="65"/>
     </row>
@@ -7440,9 +7446,9 @@
       <c r="Y75" s="1">
         <v>1</v>
       </c>
-      <c r="Z75" s="100"/>
-      <c r="AA75" s="102"/>
-      <c r="AB75" s="102"/>
+      <c r="Z75" s="102"/>
+      <c r="AA75" s="104"/>
+      <c r="AB75" s="104"/>
       <c r="AC75" s="65"/>
       <c r="AD75" s="65"/>
     </row>
@@ -7524,9 +7530,9 @@
       <c r="Y76" s="1">
         <v>1</v>
       </c>
-      <c r="Z76" s="100"/>
-      <c r="AA76" s="102"/>
-      <c r="AB76" s="102"/>
+      <c r="Z76" s="102"/>
+      <c r="AA76" s="104"/>
+      <c r="AB76" s="104"/>
       <c r="AC76" s="65"/>
       <c r="AD76" s="65"/>
     </row>
@@ -7608,9 +7614,9 @@
       <c r="Y77" s="1">
         <v>1</v>
       </c>
-      <c r="Z77" s="100"/>
-      <c r="AA77" s="102"/>
-      <c r="AB77" s="102"/>
+      <c r="Z77" s="102"/>
+      <c r="AA77" s="104"/>
+      <c r="AB77" s="104"/>
       <c r="AC77" s="65"/>
       <c r="AD77" s="65"/>
     </row>
@@ -7692,9 +7698,9 @@
       <c r="Y78" s="1">
         <v>1</v>
       </c>
-      <c r="Z78" s="100"/>
-      <c r="AA78" s="102"/>
-      <c r="AB78" s="102"/>
+      <c r="Z78" s="102"/>
+      <c r="AA78" s="104"/>
+      <c r="AB78" s="104"/>
       <c r="AC78" s="65"/>
       <c r="AD78" s="65"/>
     </row>
@@ -7776,9 +7782,9 @@
       <c r="Y79" s="1">
         <v>1</v>
       </c>
-      <c r="Z79" s="100"/>
-      <c r="AA79" s="102"/>
-      <c r="AB79" s="102"/>
+      <c r="Z79" s="102"/>
+      <c r="AA79" s="104"/>
+      <c r="AB79" s="104"/>
       <c r="AC79" s="65"/>
       <c r="AD79" s="65"/>
     </row>
@@ -7860,9 +7866,9 @@
       <c r="Y80" s="1">
         <v>1</v>
       </c>
-      <c r="Z80" s="100"/>
-      <c r="AA80" s="102"/>
-      <c r="AB80" s="102"/>
+      <c r="Z80" s="102"/>
+      <c r="AA80" s="104"/>
+      <c r="AB80" s="104"/>
       <c r="AC80" s="65"/>
       <c r="AD80" s="65"/>
     </row>
@@ -7944,9 +7950,9 @@
       <c r="Y81" s="1">
         <v>1</v>
       </c>
-      <c r="Z81" s="100"/>
-      <c r="AA81" s="102"/>
-      <c r="AB81" s="102"/>
+      <c r="Z81" s="102"/>
+      <c r="AA81" s="104"/>
+      <c r="AB81" s="104"/>
       <c r="AC81" s="65"/>
       <c r="AD81" s="65"/>
     </row>
@@ -8028,9 +8034,9 @@
       <c r="Y82" s="1">
         <v>1</v>
       </c>
-      <c r="Z82" s="100"/>
-      <c r="AA82" s="102"/>
-      <c r="AB82" s="102"/>
+      <c r="Z82" s="102"/>
+      <c r="AA82" s="104"/>
+      <c r="AB82" s="104"/>
       <c r="AC82" s="65"/>
       <c r="AD82" s="65"/>
     </row>
@@ -8112,9 +8118,9 @@
       <c r="Y83" s="1">
         <v>1</v>
       </c>
-      <c r="Z83" s="100"/>
-      <c r="AA83" s="102"/>
-      <c r="AB83" s="102"/>
+      <c r="Z83" s="102"/>
+      <c r="AA83" s="104"/>
+      <c r="AB83" s="104"/>
       <c r="AC83" s="65"/>
       <c r="AD83" s="65"/>
     </row>
@@ -8196,9 +8202,9 @@
       <c r="Y84" s="1">
         <v>1</v>
       </c>
-      <c r="Z84" s="100"/>
-      <c r="AA84" s="102"/>
-      <c r="AB84" s="102"/>
+      <c r="Z84" s="102"/>
+      <c r="AA84" s="104"/>
+      <c r="AB84" s="104"/>
       <c r="AC84" s="65"/>
       <c r="AD84" s="65"/>
     </row>
@@ -8279,7 +8285,7 @@
       <c r="Y85" s="53">
         <v>1</v>
       </c>
-      <c r="Z85" s="105" t="s">
+      <c r="Z85" s="107" t="s">
         <v>58</v>
       </c>
       <c r="AA85" s="114"/>
@@ -8364,11 +8370,11 @@
       <c r="Y86" s="40">
         <v>1</v>
       </c>
-      <c r="Z86" s="100" t="s">
+      <c r="Z86" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="AA86" s="101"/>
-      <c r="AB86" s="101"/>
+      <c r="AA86" s="103"/>
+      <c r="AB86" s="103"/>
       <c r="AC86" s="65"/>
       <c r="AD86" s="65"/>
     </row>
@@ -8449,9 +8455,9 @@
       <c r="Y87" s="57">
         <v>1</v>
       </c>
-      <c r="Z87" s="100"/>
-      <c r="AA87" s="101"/>
-      <c r="AB87" s="101"/>
+      <c r="Z87" s="102"/>
+      <c r="AA87" s="103"/>
+      <c r="AB87" s="103"/>
       <c r="AC87" s="65"/>
       <c r="AD87" s="65"/>
     </row>
@@ -8532,7 +8538,7 @@
       <c r="Y88" s="53">
         <v>1</v>
       </c>
-      <c r="Z88" s="105" t="s">
+      <c r="Z88" s="107" t="s">
         <v>64</v>
       </c>
       <c r="AA88" s="114"/>
@@ -8617,7 +8623,7 @@
       <c r="Y89" s="40">
         <v>1</v>
       </c>
-      <c r="Z89" s="105" t="s">
+      <c r="Z89" s="107" t="s">
         <v>63</v>
       </c>
       <c r="AA89" s="114"/>
@@ -8702,7 +8708,7 @@
       <c r="Y90" s="57">
         <v>1</v>
       </c>
-      <c r="Z90" s="105" t="s">
+      <c r="Z90" s="107" t="s">
         <v>65</v>
       </c>
       <c r="AA90" s="114"/>
@@ -8787,7 +8793,7 @@
       <c r="Y91" s="53">
         <v>1</v>
       </c>
-      <c r="Z91" s="105" t="s">
+      <c r="Z91" s="107" t="s">
         <v>64</v>
       </c>
       <c r="AA91" s="114"/>
@@ -8872,11 +8878,11 @@
       <c r="Y92" s="40">
         <v>1</v>
       </c>
-      <c r="Z92" s="100" t="s">
+      <c r="Z92" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="AA92" s="101"/>
-      <c r="AB92" s="101"/>
+      <c r="AA92" s="103"/>
+      <c r="AB92" s="103"/>
       <c r="AC92" s="65"/>
       <c r="AD92" s="65"/>
     </row>
@@ -8957,9 +8963,9 @@
       <c r="Y93" s="57">
         <v>1</v>
       </c>
-      <c r="Z93" s="100"/>
-      <c r="AA93" s="101"/>
-      <c r="AB93" s="101"/>
+      <c r="Z93" s="102"/>
+      <c r="AA93" s="103"/>
+      <c r="AB93" s="103"/>
       <c r="AC93" s="65"/>
       <c r="AD93" s="65"/>
     </row>
@@ -9040,11 +9046,11 @@
       <c r="Y94" s="33">
         <v>1</v>
       </c>
-      <c r="Z94" s="100" t="s">
+      <c r="Z94" s="102" t="s">
         <v>68</v>
       </c>
-      <c r="AA94" s="102"/>
-      <c r="AB94" s="102"/>
+      <c r="AA94" s="104"/>
+      <c r="AB94" s="104"/>
     </row>
     <row r="95" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
@@ -9123,11 +9129,11 @@
       <c r="Y95" s="1">
         <v>1</v>
       </c>
-      <c r="Z95" s="103" t="s">
+      <c r="Z95" s="105" t="s">
         <v>69</v>
       </c>
-      <c r="AA95" s="104"/>
-      <c r="AB95" s="104"/>
+      <c r="AA95" s="106"/>
+      <c r="AB95" s="106"/>
     </row>
     <row r="96" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
@@ -9207,9 +9213,9 @@
       <c r="Y96" s="1">
         <v>1</v>
       </c>
-      <c r="Z96" s="103"/>
-      <c r="AA96" s="104"/>
-      <c r="AB96" s="104"/>
+      <c r="Z96" s="105"/>
+      <c r="AA96" s="106"/>
+      <c r="AB96" s="106"/>
     </row>
     <row r="97" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
@@ -9289,9 +9295,9 @@
       <c r="Y97" s="1">
         <v>1</v>
       </c>
-      <c r="Z97" s="103"/>
-      <c r="AA97" s="104"/>
-      <c r="AB97" s="104"/>
+      <c r="Z97" s="105"/>
+      <c r="AA97" s="106"/>
+      <c r="AB97" s="106"/>
     </row>
     <row r="98" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
@@ -9371,9 +9377,9 @@
       <c r="Y98" s="1">
         <v>1</v>
       </c>
-      <c r="Z98" s="103"/>
-      <c r="AA98" s="104"/>
-      <c r="AB98" s="104"/>
+      <c r="Z98" s="105"/>
+      <c r="AA98" s="106"/>
+      <c r="AB98" s="106"/>
     </row>
     <row r="99" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
@@ -9453,9 +9459,9 @@
       <c r="Y99" s="1">
         <v>1</v>
       </c>
-      <c r="Z99" s="103"/>
-      <c r="AA99" s="104"/>
-      <c r="AB99" s="104"/>
+      <c r="Z99" s="105"/>
+      <c r="AA99" s="106"/>
+      <c r="AB99" s="106"/>
     </row>
     <row r="100" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
@@ -9535,9 +9541,9 @@
       <c r="Y100" s="1">
         <v>1</v>
       </c>
-      <c r="Z100" s="103"/>
-      <c r="AA100" s="104"/>
-      <c r="AB100" s="104"/>
+      <c r="Z100" s="105"/>
+      <c r="AA100" s="106"/>
+      <c r="AB100" s="106"/>
     </row>
     <row r="101" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
@@ -9617,9 +9623,9 @@
       <c r="Y101" s="1">
         <v>1</v>
       </c>
-      <c r="Z101" s="103"/>
-      <c r="AA101" s="104"/>
-      <c r="AB101" s="104"/>
+      <c r="Z101" s="105"/>
+      <c r="AA101" s="106"/>
+      <c r="AB101" s="106"/>
     </row>
     <row r="102" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
@@ -9699,9 +9705,9 @@
       <c r="Y102" s="1">
         <v>1</v>
       </c>
-      <c r="Z102" s="103"/>
-      <c r="AA102" s="104"/>
-      <c r="AB102" s="104"/>
+      <c r="Z102" s="105"/>
+      <c r="AA102" s="106"/>
+      <c r="AB102" s="106"/>
     </row>
     <row r="103" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
@@ -9781,9 +9787,9 @@
       <c r="Y103" s="1">
         <v>1</v>
       </c>
-      <c r="Z103" s="103"/>
-      <c r="AA103" s="104"/>
-      <c r="AB103" s="104"/>
+      <c r="Z103" s="105"/>
+      <c r="AA103" s="106"/>
+      <c r="AB103" s="106"/>
     </row>
     <row r="104" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
@@ -9863,9 +9869,9 @@
       <c r="Y104" s="1">
         <v>1</v>
       </c>
-      <c r="Z104" s="103"/>
-      <c r="AA104" s="104"/>
-      <c r="AB104" s="104"/>
+      <c r="Z104" s="105"/>
+      <c r="AA104" s="106"/>
+      <c r="AB104" s="106"/>
     </row>
     <row r="105" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
@@ -9945,9 +9951,9 @@
       <c r="Y105" s="1">
         <v>1</v>
       </c>
-      <c r="Z105" s="103"/>
-      <c r="AA105" s="104"/>
-      <c r="AB105" s="104"/>
+      <c r="Z105" s="105"/>
+      <c r="AA105" s="106"/>
+      <c r="AB105" s="106"/>
     </row>
     <row r="106" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
@@ -10027,9 +10033,9 @@
       <c r="Y106" s="1">
         <v>1</v>
       </c>
-      <c r="Z106" s="103"/>
-      <c r="AA106" s="104"/>
-      <c r="AB106" s="104"/>
+      <c r="Z106" s="105"/>
+      <c r="AA106" s="106"/>
+      <c r="AB106" s="106"/>
     </row>
     <row r="107" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
@@ -10108,9 +10114,9 @@
       <c r="Y107" s="1">
         <v>1</v>
       </c>
-      <c r="Z107" s="103"/>
-      <c r="AA107" s="104"/>
-      <c r="AB107" s="104"/>
+      <c r="Z107" s="105"/>
+      <c r="AA107" s="106"/>
+      <c r="AB107" s="106"/>
     </row>
     <row r="108" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
@@ -10189,9 +10195,9 @@
       <c r="Y108" s="1">
         <v>1</v>
       </c>
-      <c r="Z108" s="103"/>
-      <c r="AA108" s="104"/>
-      <c r="AB108" s="104"/>
+      <c r="Z108" s="105"/>
+      <c r="AA108" s="106"/>
+      <c r="AB108" s="106"/>
     </row>
     <row r="109" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
@@ -10270,9 +10276,9 @@
       <c r="Y109" s="1">
         <v>1</v>
       </c>
-      <c r="Z109" s="103"/>
-      <c r="AA109" s="104"/>
-      <c r="AB109" s="104"/>
+      <c r="Z109" s="105"/>
+      <c r="AA109" s="106"/>
+      <c r="AB109" s="106"/>
     </row>
     <row r="110" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
@@ -10351,9 +10357,9 @@
       <c r="Y110" s="1">
         <v>1</v>
       </c>
-      <c r="Z110" s="103"/>
-      <c r="AA110" s="104"/>
-      <c r="AB110" s="104"/>
+      <c r="Z110" s="105"/>
+      <c r="AA110" s="106"/>
+      <c r="AB110" s="106"/>
     </row>
     <row r="111" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
@@ -10432,9 +10438,9 @@
       <c r="Y111" s="1">
         <v>1</v>
       </c>
-      <c r="Z111" s="103"/>
-      <c r="AA111" s="104"/>
-      <c r="AB111" s="104"/>
+      <c r="Z111" s="105"/>
+      <c r="AA111" s="106"/>
+      <c r="AB111" s="106"/>
     </row>
     <row r="112" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A112" s="43">
@@ -10513,11 +10519,11 @@
       <c r="Y112" s="43">
         <v>1</v>
       </c>
-      <c r="Z112" s="100" t="s">
+      <c r="Z112" s="102" t="s">
         <v>71</v>
       </c>
-      <c r="AA112" s="102"/>
-      <c r="AB112" s="102"/>
+      <c r="AA112" s="104"/>
+      <c r="AB112" s="104"/>
     </row>
     <row r="113" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
@@ -10597,9 +10603,9 @@
       <c r="Y113" s="1">
         <v>1</v>
       </c>
-      <c r="Z113" s="100"/>
-      <c r="AA113" s="102"/>
-      <c r="AB113" s="102"/>
+      <c r="Z113" s="102"/>
+      <c r="AA113" s="104"/>
+      <c r="AB113" s="104"/>
     </row>
     <row r="114" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
@@ -10679,9 +10685,9 @@
       <c r="Y114" s="1">
         <v>1</v>
       </c>
-      <c r="Z114" s="100"/>
-      <c r="AA114" s="102"/>
-      <c r="AB114" s="102"/>
+      <c r="Z114" s="102"/>
+      <c r="AA114" s="104"/>
+      <c r="AB114" s="104"/>
     </row>
     <row r="115" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
@@ -10761,9 +10767,9 @@
       <c r="Y115" s="1">
         <v>1</v>
       </c>
-      <c r="Z115" s="100"/>
-      <c r="AA115" s="102"/>
-      <c r="AB115" s="102"/>
+      <c r="Z115" s="102"/>
+      <c r="AA115" s="104"/>
+      <c r="AB115" s="104"/>
     </row>
     <row r="116" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
@@ -10843,9 +10849,9 @@
       <c r="Y116" s="1">
         <v>1</v>
       </c>
-      <c r="Z116" s="100"/>
-      <c r="AA116" s="102"/>
-      <c r="AB116" s="102"/>
+      <c r="Z116" s="102"/>
+      <c r="AA116" s="104"/>
+      <c r="AB116" s="104"/>
     </row>
     <row r="117" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
@@ -10925,9 +10931,9 @@
       <c r="Y117" s="1">
         <v>1</v>
       </c>
-      <c r="Z117" s="100"/>
-      <c r="AA117" s="102"/>
-      <c r="AB117" s="102"/>
+      <c r="Z117" s="102"/>
+      <c r="AA117" s="104"/>
+      <c r="AB117" s="104"/>
     </row>
     <row r="118" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
@@ -11007,9 +11013,9 @@
       <c r="Y118" s="1">
         <v>1</v>
       </c>
-      <c r="Z118" s="100"/>
-      <c r="AA118" s="102"/>
-      <c r="AB118" s="102"/>
+      <c r="Z118" s="102"/>
+      <c r="AA118" s="104"/>
+      <c r="AB118" s="104"/>
     </row>
     <row r="119" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
@@ -11089,9 +11095,9 @@
       <c r="Y119" s="1">
         <v>1</v>
       </c>
-      <c r="Z119" s="100"/>
-      <c r="AA119" s="102"/>
-      <c r="AB119" s="102"/>
+      <c r="Z119" s="102"/>
+      <c r="AA119" s="104"/>
+      <c r="AB119" s="104"/>
     </row>
     <row r="120" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
@@ -11171,9 +11177,9 @@
       <c r="Y120" s="1">
         <v>1</v>
       </c>
-      <c r="Z120" s="100"/>
-      <c r="AA120" s="102"/>
-      <c r="AB120" s="102"/>
+      <c r="Z120" s="102"/>
+      <c r="AA120" s="104"/>
+      <c r="AB120" s="104"/>
     </row>
     <row r="121" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
@@ -11253,9 +11259,9 @@
       <c r="Y121" s="1">
         <v>1</v>
       </c>
-      <c r="Z121" s="100"/>
-      <c r="AA121" s="102"/>
-      <c r="AB121" s="102"/>
+      <c r="Z121" s="102"/>
+      <c r="AA121" s="104"/>
+      <c r="AB121" s="104"/>
     </row>
     <row r="122" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
@@ -11335,9 +11341,9 @@
       <c r="Y122" s="1">
         <v>1</v>
       </c>
-      <c r="Z122" s="100"/>
-      <c r="AA122" s="102"/>
-      <c r="AB122" s="102"/>
+      <c r="Z122" s="102"/>
+      <c r="AA122" s="104"/>
+      <c r="AB122" s="104"/>
     </row>
     <row r="123" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
@@ -11416,9 +11422,9 @@
       <c r="Y123" s="1">
         <v>1</v>
       </c>
-      <c r="Z123" s="100"/>
-      <c r="AA123" s="102"/>
-      <c r="AB123" s="102"/>
+      <c r="Z123" s="102"/>
+      <c r="AA123" s="104"/>
+      <c r="AB123" s="104"/>
     </row>
     <row r="124" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
@@ -11497,9 +11503,9 @@
       <c r="Y124" s="1">
         <v>1</v>
       </c>
-      <c r="Z124" s="100"/>
-      <c r="AA124" s="102"/>
-      <c r="AB124" s="102"/>
+      <c r="Z124" s="102"/>
+      <c r="AA124" s="104"/>
+      <c r="AB124" s="104"/>
     </row>
     <row r="125" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
@@ -11578,9 +11584,9 @@
       <c r="Y125" s="1">
         <v>1</v>
       </c>
-      <c r="Z125" s="100"/>
-      <c r="AA125" s="102"/>
-      <c r="AB125" s="102"/>
+      <c r="Z125" s="102"/>
+      <c r="AA125" s="104"/>
+      <c r="AB125" s="104"/>
     </row>
     <row r="126" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
@@ -11659,9 +11665,9 @@
       <c r="Y126" s="1">
         <v>1</v>
       </c>
-      <c r="Z126" s="100"/>
-      <c r="AA126" s="102"/>
-      <c r="AB126" s="102"/>
+      <c r="Z126" s="102"/>
+      <c r="AA126" s="104"/>
+      <c r="AB126" s="104"/>
     </row>
     <row r="127" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
@@ -11740,9 +11746,9 @@
       <c r="Y127" s="1">
         <v>1</v>
       </c>
-      <c r="Z127" s="100"/>
-      <c r="AA127" s="102"/>
-      <c r="AB127" s="102"/>
+      <c r="Z127" s="102"/>
+      <c r="AA127" s="104"/>
+      <c r="AB127" s="104"/>
     </row>
     <row r="128" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
@@ -11821,9 +11827,9 @@
       <c r="Y128" s="1">
         <v>1</v>
       </c>
-      <c r="Z128" s="100"/>
-      <c r="AA128" s="102"/>
-      <c r="AB128" s="102"/>
+      <c r="Z128" s="102"/>
+      <c r="AA128" s="104"/>
+      <c r="AB128" s="104"/>
     </row>
     <row r="129" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
@@ -11902,9 +11908,9 @@
       <c r="Y129" s="1">
         <v>1</v>
       </c>
-      <c r="Z129" s="100"/>
-      <c r="AA129" s="102"/>
-      <c r="AB129" s="102"/>
+      <c r="Z129" s="102"/>
+      <c r="AA129" s="104"/>
+      <c r="AB129" s="104"/>
     </row>
     <row r="130" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A130" s="43">
@@ -11983,11 +11989,11 @@
       <c r="Y130" s="43">
         <v>1</v>
       </c>
-      <c r="Z130" s="100" t="s">
+      <c r="Z130" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="AA130" s="102"/>
-      <c r="AB130" s="102"/>
+      <c r="AA130" s="104"/>
+      <c r="AB130" s="104"/>
     </row>
     <row r="131" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
@@ -12067,9 +12073,9 @@
       <c r="Y131" s="1">
         <v>1</v>
       </c>
-      <c r="Z131" s="100"/>
-      <c r="AA131" s="102"/>
-      <c r="AB131" s="102"/>
+      <c r="Z131" s="102"/>
+      <c r="AA131" s="104"/>
+      <c r="AB131" s="104"/>
     </row>
     <row r="132" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
@@ -12149,9 +12155,9 @@
       <c r="Y132" s="1">
         <v>1</v>
       </c>
-      <c r="Z132" s="100"/>
-      <c r="AA132" s="102"/>
-      <c r="AB132" s="102"/>
+      <c r="Z132" s="102"/>
+      <c r="AA132" s="104"/>
+      <c r="AB132" s="104"/>
     </row>
     <row r="133" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
@@ -12231,9 +12237,9 @@
       <c r="Y133" s="1">
         <v>1</v>
       </c>
-      <c r="Z133" s="100"/>
-      <c r="AA133" s="102"/>
-      <c r="AB133" s="102"/>
+      <c r="Z133" s="102"/>
+      <c r="AA133" s="104"/>
+      <c r="AB133" s="104"/>
     </row>
     <row r="134" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
@@ -12313,9 +12319,9 @@
       <c r="Y134" s="1">
         <v>1</v>
       </c>
-      <c r="Z134" s="100"/>
-      <c r="AA134" s="102"/>
-      <c r="AB134" s="102"/>
+      <c r="Z134" s="102"/>
+      <c r="AA134" s="104"/>
+      <c r="AB134" s="104"/>
     </row>
     <row r="135" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
@@ -12395,9 +12401,9 @@
       <c r="Y135" s="1">
         <v>1</v>
       </c>
-      <c r="Z135" s="100"/>
-      <c r="AA135" s="102"/>
-      <c r="AB135" s="102"/>
+      <c r="Z135" s="102"/>
+      <c r="AA135" s="104"/>
+      <c r="AB135" s="104"/>
     </row>
     <row r="136" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
@@ -12477,9 +12483,9 @@
       <c r="Y136" s="1">
         <v>1</v>
       </c>
-      <c r="Z136" s="100"/>
-      <c r="AA136" s="102"/>
-      <c r="AB136" s="102"/>
+      <c r="Z136" s="102"/>
+      <c r="AA136" s="104"/>
+      <c r="AB136" s="104"/>
     </row>
     <row r="137" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
@@ -12559,9 +12565,9 @@
       <c r="Y137" s="1">
         <v>1</v>
       </c>
-      <c r="Z137" s="100"/>
-      <c r="AA137" s="102"/>
-      <c r="AB137" s="102"/>
+      <c r="Z137" s="102"/>
+      <c r="AA137" s="104"/>
+      <c r="AB137" s="104"/>
     </row>
     <row r="138" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
@@ -12641,9 +12647,9 @@
       <c r="Y138" s="1">
         <v>1</v>
       </c>
-      <c r="Z138" s="100"/>
-      <c r="AA138" s="102"/>
-      <c r="AB138" s="102"/>
+      <c r="Z138" s="102"/>
+      <c r="AA138" s="104"/>
+      <c r="AB138" s="104"/>
     </row>
     <row r="139" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
@@ -12723,9 +12729,9 @@
       <c r="Y139" s="1">
         <v>1</v>
       </c>
-      <c r="Z139" s="100"/>
-      <c r="AA139" s="102"/>
-      <c r="AB139" s="102"/>
+      <c r="Z139" s="102"/>
+      <c r="AA139" s="104"/>
+      <c r="AB139" s="104"/>
     </row>
     <row r="140" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
@@ -12805,9 +12811,9 @@
       <c r="Y140" s="1">
         <v>1</v>
       </c>
-      <c r="Z140" s="100"/>
-      <c r="AA140" s="102"/>
-      <c r="AB140" s="102"/>
+      <c r="Z140" s="102"/>
+      <c r="AA140" s="104"/>
+      <c r="AB140" s="104"/>
     </row>
     <row r="141" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
@@ -12886,9 +12892,9 @@
       <c r="Y141" s="1">
         <v>1</v>
       </c>
-      <c r="Z141" s="100"/>
-      <c r="AA141" s="102"/>
-      <c r="AB141" s="102"/>
+      <c r="Z141" s="102"/>
+      <c r="AA141" s="104"/>
+      <c r="AB141" s="104"/>
     </row>
     <row r="142" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
@@ -12967,9 +12973,9 @@
       <c r="Y142" s="1">
         <v>1</v>
       </c>
-      <c r="Z142" s="100"/>
-      <c r="AA142" s="102"/>
-      <c r="AB142" s="102"/>
+      <c r="Z142" s="102"/>
+      <c r="AA142" s="104"/>
+      <c r="AB142" s="104"/>
     </row>
     <row r="143" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
@@ -13048,9 +13054,9 @@
       <c r="Y143" s="1">
         <v>1</v>
       </c>
-      <c r="Z143" s="100"/>
-      <c r="AA143" s="102"/>
-      <c r="AB143" s="102"/>
+      <c r="Z143" s="102"/>
+      <c r="AA143" s="104"/>
+      <c r="AB143" s="104"/>
     </row>
     <row r="144" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
@@ -13129,9 +13135,9 @@
       <c r="Y144" s="1">
         <v>1</v>
       </c>
-      <c r="Z144" s="100"/>
-      <c r="AA144" s="102"/>
-      <c r="AB144" s="102"/>
+      <c r="Z144" s="102"/>
+      <c r="AA144" s="104"/>
+      <c r="AB144" s="104"/>
     </row>
     <row r="145" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
@@ -13210,9 +13216,9 @@
       <c r="Y145" s="1">
         <v>1</v>
       </c>
-      <c r="Z145" s="100"/>
-      <c r="AA145" s="102"/>
-      <c r="AB145" s="102"/>
+      <c r="Z145" s="102"/>
+      <c r="AA145" s="104"/>
+      <c r="AB145" s="104"/>
     </row>
     <row r="146" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
@@ -13291,9 +13297,9 @@
       <c r="Y146" s="1">
         <v>1</v>
       </c>
-      <c r="Z146" s="100"/>
-      <c r="AA146" s="102"/>
-      <c r="AB146" s="102"/>
+      <c r="Z146" s="102"/>
+      <c r="AA146" s="104"/>
+      <c r="AB146" s="104"/>
     </row>
     <row r="147" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
@@ -13372,9 +13378,9 @@
       <c r="Y147" s="1">
         <v>1</v>
       </c>
-      <c r="Z147" s="100"/>
-      <c r="AA147" s="102"/>
-      <c r="AB147" s="102"/>
+      <c r="Z147" s="102"/>
+      <c r="AA147" s="104"/>
+      <c r="AB147" s="104"/>
     </row>
     <row r="148" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="43">
@@ -13453,11 +13459,11 @@
       <c r="Y148" s="40">
         <v>1</v>
       </c>
-      <c r="Z148" s="100" t="s">
+      <c r="Z148" s="102" t="s">
         <v>73</v>
       </c>
-      <c r="AA148" s="101"/>
-      <c r="AB148" s="101"/>
+      <c r="AA148" s="103"/>
+      <c r="AB148" s="103"/>
     </row>
     <row r="149" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
@@ -13537,9 +13543,9 @@
       <c r="Y149" s="50">
         <v>1</v>
       </c>
-      <c r="Z149" s="100"/>
-      <c r="AA149" s="101"/>
-      <c r="AB149" s="101"/>
+      <c r="Z149" s="102"/>
+      <c r="AA149" s="103"/>
+      <c r="AB149" s="103"/>
     </row>
     <row r="150" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
@@ -13619,9 +13625,9 @@
       <c r="Y150" s="50">
         <v>1</v>
       </c>
-      <c r="Z150" s="100"/>
-      <c r="AA150" s="101"/>
-      <c r="AB150" s="101"/>
+      <c r="Z150" s="102"/>
+      <c r="AA150" s="103"/>
+      <c r="AB150" s="103"/>
     </row>
     <row r="151" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
@@ -13700,9 +13706,9 @@
       <c r="Y151" s="50">
         <v>1</v>
       </c>
-      <c r="Z151" s="100"/>
-      <c r="AA151" s="101"/>
-      <c r="AB151" s="101"/>
+      <c r="Z151" s="102"/>
+      <c r="AA151" s="103"/>
+      <c r="AB151" s="103"/>
     </row>
     <row r="152" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A152" s="27">
@@ -13781,9 +13787,9 @@
       <c r="Y152" s="50">
         <v>1</v>
       </c>
-      <c r="Z152" s="100"/>
-      <c r="AA152" s="101"/>
-      <c r="AB152" s="101"/>
+      <c r="Z152" s="102"/>
+      <c r="AA152" s="103"/>
+      <c r="AB152" s="103"/>
     </row>
     <row r="153" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
@@ -13862,11 +13868,11 @@
       <c r="Y153" s="43">
         <v>1</v>
       </c>
-      <c r="Z153" s="100" t="s">
+      <c r="Z153" s="102" t="s">
         <v>74</v>
       </c>
-      <c r="AA153" s="101"/>
-      <c r="AB153" s="101"/>
+      <c r="AA153" s="103"/>
+      <c r="AB153" s="103"/>
     </row>
     <row r="154" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
@@ -13946,9 +13952,9 @@
       <c r="Y154" s="1">
         <v>1</v>
       </c>
-      <c r="Z154" s="100"/>
-      <c r="AA154" s="101"/>
-      <c r="AB154" s="101"/>
+      <c r="Z154" s="102"/>
+      <c r="AA154" s="103"/>
+      <c r="AB154" s="103"/>
     </row>
     <row r="155" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
@@ -14028,9 +14034,9 @@
       <c r="Y155" s="1">
         <v>1</v>
       </c>
-      <c r="Z155" s="100"/>
-      <c r="AA155" s="101"/>
-      <c r="AB155" s="101"/>
+      <c r="Z155" s="102"/>
+      <c r="AA155" s="103"/>
+      <c r="AB155" s="103"/>
     </row>
     <row r="156" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
@@ -14110,9 +14116,9 @@
       <c r="Y156" s="1">
         <v>1</v>
       </c>
-      <c r="Z156" s="100"/>
-      <c r="AA156" s="101"/>
-      <c r="AB156" s="101"/>
+      <c r="Z156" s="102"/>
+      <c r="AA156" s="103"/>
+      <c r="AB156" s="103"/>
     </row>
     <row r="157" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
@@ -14192,9 +14198,9 @@
       <c r="Y157" s="1">
         <v>1</v>
       </c>
-      <c r="Z157" s="100"/>
-      <c r="AA157" s="101"/>
-      <c r="AB157" s="101"/>
+      <c r="Z157" s="102"/>
+      <c r="AA157" s="103"/>
+      <c r="AB157" s="103"/>
     </row>
     <row r="158" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A158" s="43">
@@ -14273,11 +14279,11 @@
       <c r="Y158" s="43">
         <v>1</v>
       </c>
-      <c r="Z158" s="100" t="s">
+      <c r="Z158" s="102" t="s">
         <v>75</v>
       </c>
-      <c r="AA158" s="101"/>
-      <c r="AB158" s="101"/>
+      <c r="AA158" s="103"/>
+      <c r="AB158" s="103"/>
     </row>
     <row r="159" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
@@ -14357,9 +14363,9 @@
       <c r="Y159" s="1">
         <v>1</v>
       </c>
-      <c r="Z159" s="100"/>
-      <c r="AA159" s="101"/>
-      <c r="AB159" s="101"/>
+      <c r="Z159" s="102"/>
+      <c r="AA159" s="103"/>
+      <c r="AB159" s="103"/>
     </row>
     <row r="160" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
@@ -14439,9 +14445,9 @@
       <c r="Y160" s="1">
         <v>1</v>
       </c>
-      <c r="Z160" s="100"/>
-      <c r="AA160" s="101"/>
-      <c r="AB160" s="101"/>
+      <c r="Z160" s="102"/>
+      <c r="AA160" s="103"/>
+      <c r="AB160" s="103"/>
     </row>
     <row r="161" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
@@ -14521,9 +14527,9 @@
       <c r="Y161" s="1">
         <v>1</v>
       </c>
-      <c r="Z161" s="100"/>
-      <c r="AA161" s="101"/>
-      <c r="AB161" s="101"/>
+      <c r="Z161" s="102"/>
+      <c r="AA161" s="103"/>
+      <c r="AB161" s="103"/>
     </row>
     <row r="162" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A162" s="27">
@@ -14603,9 +14609,9 @@
       <c r="Y162" s="27">
         <v>1</v>
       </c>
-      <c r="Z162" s="100"/>
-      <c r="AA162" s="101"/>
-      <c r="AB162" s="101"/>
+      <c r="Z162" s="102"/>
+      <c r="AA162" s="103"/>
+      <c r="AB162" s="103"/>
     </row>
     <row r="163" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A163" s="43">
@@ -14684,11 +14690,11 @@
       <c r="Y163" s="40">
         <v>1</v>
       </c>
-      <c r="Z163" s="100" t="s">
+      <c r="Z163" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="AA163" s="101"/>
-      <c r="AB163" s="101"/>
+      <c r="AA163" s="103"/>
+      <c r="AB163" s="103"/>
     </row>
     <row r="164" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A164" s="43">
@@ -14767,11 +14773,11 @@
       <c r="Y164" s="40">
         <v>1</v>
       </c>
-      <c r="Z164" s="100" t="s">
+      <c r="Z164" s="102" t="s">
         <v>77</v>
       </c>
-      <c r="AA164" s="101"/>
-      <c r="AB164" s="101"/>
+      <c r="AA164" s="103"/>
+      <c r="AB164" s="103"/>
     </row>
     <row r="165" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A165" s="43">
@@ -14850,11 +14856,11 @@
       <c r="Y165" s="40">
         <v>1</v>
       </c>
-      <c r="Z165" s="100" t="s">
+      <c r="Z165" s="102" t="s">
         <v>78</v>
       </c>
-      <c r="AA165" s="101"/>
-      <c r="AB165" s="101"/>
+      <c r="AA165" s="103"/>
+      <c r="AB165" s="103"/>
     </row>
     <row r="166" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A166" s="43">
@@ -14933,11 +14939,11 @@
       <c r="Y166" s="40">
         <v>1</v>
       </c>
-      <c r="Z166" s="100" t="s">
+      <c r="Z166" s="102" t="s">
         <v>80</v>
       </c>
-      <c r="AA166" s="101"/>
-      <c r="AB166" s="101"/>
+      <c r="AA166" s="103"/>
+      <c r="AB166" s="103"/>
     </row>
     <row r="167" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A167" s="43">
@@ -15016,11 +15022,11 @@
       <c r="Y167" s="40">
         <v>1</v>
       </c>
-      <c r="Z167" s="100" t="s">
+      <c r="Z167" s="102" t="s">
         <v>79</v>
       </c>
-      <c r="AA167" s="101"/>
-      <c r="AB167" s="101"/>
+      <c r="AA167" s="103"/>
+      <c r="AB167" s="103"/>
     </row>
     <row r="168" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A168" s="43">
@@ -15099,11 +15105,11 @@
       <c r="Y168" s="40">
         <v>1</v>
       </c>
-      <c r="Z168" s="100" t="s">
+      <c r="Z168" s="102" t="s">
         <v>81</v>
       </c>
-      <c r="AA168" s="101"/>
-      <c r="AB168" s="101"/>
+      <c r="AA168" s="103"/>
+      <c r="AB168" s="103"/>
     </row>
     <row r="169" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="43">
@@ -15182,11 +15188,11 @@
       <c r="Y169" s="40">
         <v>1</v>
       </c>
-      <c r="Z169" s="103" t="s">
+      <c r="Z169" s="105" t="s">
         <v>82</v>
       </c>
-      <c r="AA169" s="104"/>
-      <c r="AB169" s="104"/>
+      <c r="AA169" s="106"/>
+      <c r="AB169" s="106"/>
     </row>
     <row r="170" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
@@ -15265,9 +15271,9 @@
       <c r="Y170" s="50">
         <v>1</v>
       </c>
-      <c r="Z170" s="103"/>
-      <c r="AA170" s="104"/>
-      <c r="AB170" s="104"/>
+      <c r="Z170" s="105"/>
+      <c r="AA170" s="106"/>
+      <c r="AB170" s="106"/>
     </row>
     <row r="171" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
@@ -15346,9 +15352,9 @@
       <c r="Y171" s="50">
         <v>1</v>
       </c>
-      <c r="Z171" s="103"/>
-      <c r="AA171" s="104"/>
-      <c r="AB171" s="104"/>
+      <c r="Z171" s="105"/>
+      <c r="AA171" s="106"/>
+      <c r="AB171" s="106"/>
     </row>
     <row r="172" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
@@ -15427,9 +15433,9 @@
       <c r="Y172" s="50">
         <v>1</v>
       </c>
-      <c r="Z172" s="103"/>
-      <c r="AA172" s="104"/>
-      <c r="AB172" s="104"/>
+      <c r="Z172" s="105"/>
+      <c r="AA172" s="106"/>
+      <c r="AB172" s="106"/>
     </row>
     <row r="173" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
@@ -15508,9 +15514,9 @@
       <c r="Y173" s="50">
         <v>1</v>
       </c>
-      <c r="Z173" s="103"/>
-      <c r="AA173" s="104"/>
-      <c r="AB173" s="104"/>
+      <c r="Z173" s="105"/>
+      <c r="AA173" s="106"/>
+      <c r="AB173" s="106"/>
     </row>
     <row r="174" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
@@ -15589,9 +15595,9 @@
       <c r="Y174" s="50">
         <v>1</v>
       </c>
-      <c r="Z174" s="103"/>
-      <c r="AA174" s="104"/>
-      <c r="AB174" s="104"/>
+      <c r="Z174" s="105"/>
+      <c r="AA174" s="106"/>
+      <c r="AB174" s="106"/>
     </row>
     <row r="175" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
@@ -15670,9 +15676,9 @@
       <c r="Y175" s="50">
         <v>1</v>
       </c>
-      <c r="Z175" s="103"/>
-      <c r="AA175" s="104"/>
-      <c r="AB175" s="104"/>
+      <c r="Z175" s="105"/>
+      <c r="AA175" s="106"/>
+      <c r="AB175" s="106"/>
     </row>
     <row r="176" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A176" s="43">
@@ -15751,11 +15757,11 @@
       <c r="Y176" s="40">
         <v>1</v>
       </c>
-      <c r="Z176" s="100" t="s">
+      <c r="Z176" s="102" t="s">
         <v>83</v>
       </c>
-      <c r="AA176" s="102"/>
-      <c r="AB176" s="102"/>
+      <c r="AA176" s="104"/>
+      <c r="AB176" s="104"/>
     </row>
     <row r="177" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
@@ -15835,9 +15841,9 @@
       <c r="Y177" s="50">
         <v>1</v>
       </c>
-      <c r="Z177" s="100"/>
-      <c r="AA177" s="102"/>
-      <c r="AB177" s="102"/>
+      <c r="Z177" s="102"/>
+      <c r="AA177" s="104"/>
+      <c r="AB177" s="104"/>
     </row>
     <row r="178" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
@@ -15917,9 +15923,9 @@
       <c r="Y178" s="50">
         <v>1</v>
       </c>
-      <c r="Z178" s="100"/>
-      <c r="AA178" s="102"/>
-      <c r="AB178" s="102"/>
+      <c r="Z178" s="102"/>
+      <c r="AA178" s="104"/>
+      <c r="AB178" s="104"/>
     </row>
     <row r="179" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
@@ -15999,9 +16005,9 @@
       <c r="Y179" s="50">
         <v>1</v>
       </c>
-      <c r="Z179" s="100"/>
-      <c r="AA179" s="102"/>
-      <c r="AB179" s="102"/>
+      <c r="Z179" s="102"/>
+      <c r="AA179" s="104"/>
+      <c r="AB179" s="104"/>
     </row>
     <row r="180" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
@@ -16081,9 +16087,9 @@
       <c r="Y180" s="50">
         <v>1</v>
       </c>
-      <c r="Z180" s="100"/>
-      <c r="AA180" s="102"/>
-      <c r="AB180" s="102"/>
+      <c r="Z180" s="102"/>
+      <c r="AA180" s="104"/>
+      <c r="AB180" s="104"/>
     </row>
     <row r="181" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
@@ -16163,9 +16169,9 @@
       <c r="Y181" s="50">
         <v>1</v>
       </c>
-      <c r="Z181" s="100"/>
-      <c r="AA181" s="102"/>
-      <c r="AB181" s="102"/>
+      <c r="Z181" s="102"/>
+      <c r="AA181" s="104"/>
+      <c r="AB181" s="104"/>
     </row>
     <row r="182" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
@@ -16245,9 +16251,9 @@
       <c r="Y182" s="50">
         <v>1</v>
       </c>
-      <c r="Z182" s="100"/>
-      <c r="AA182" s="102"/>
-      <c r="AB182" s="102"/>
+      <c r="Z182" s="102"/>
+      <c r="AA182" s="104"/>
+      <c r="AB182" s="104"/>
     </row>
     <row r="183" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
@@ -16327,9 +16333,9 @@
       <c r="Y183" s="50">
         <v>1</v>
       </c>
-      <c r="Z183" s="100"/>
-      <c r="AA183" s="102"/>
-      <c r="AB183" s="102"/>
+      <c r="Z183" s="102"/>
+      <c r="AA183" s="104"/>
+      <c r="AB183" s="104"/>
     </row>
     <row r="184" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
@@ -16409,9 +16415,9 @@
       <c r="Y184" s="50">
         <v>1</v>
       </c>
-      <c r="Z184" s="100"/>
-      <c r="AA184" s="102"/>
-      <c r="AB184" s="102"/>
+      <c r="Z184" s="102"/>
+      <c r="AA184" s="104"/>
+      <c r="AB184" s="104"/>
     </row>
     <row r="185" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
@@ -16491,9 +16497,9 @@
       <c r="Y185" s="50">
         <v>1</v>
       </c>
-      <c r="Z185" s="100"/>
-      <c r="AA185" s="102"/>
-      <c r="AB185" s="102"/>
+      <c r="Z185" s="102"/>
+      <c r="AA185" s="104"/>
+      <c r="AB185" s="104"/>
     </row>
     <row r="186" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
@@ -16573,9 +16579,9 @@
       <c r="Y186" s="50">
         <v>1</v>
       </c>
-      <c r="Z186" s="100"/>
-      <c r="AA186" s="102"/>
-      <c r="AB186" s="102"/>
+      <c r="Z186" s="102"/>
+      <c r="AA186" s="104"/>
+      <c r="AB186" s="104"/>
     </row>
     <row r="187" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
@@ -16655,9 +16661,9 @@
       <c r="Y187" s="50">
         <v>1</v>
       </c>
-      <c r="Z187" s="100"/>
-      <c r="AA187" s="102"/>
-      <c r="AB187" s="102"/>
+      <c r="Z187" s="102"/>
+      <c r="AA187" s="104"/>
+      <c r="AB187" s="104"/>
     </row>
     <row r="188" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
@@ -16737,9 +16743,9 @@
       <c r="Y188" s="50">
         <v>1</v>
       </c>
-      <c r="Z188" s="100"/>
-      <c r="AA188" s="102"/>
-      <c r="AB188" s="102"/>
+      <c r="Z188" s="102"/>
+      <c r="AA188" s="104"/>
+      <c r="AB188" s="104"/>
     </row>
     <row r="189" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
@@ -16819,9 +16825,9 @@
       <c r="Y189" s="50">
         <v>1</v>
       </c>
-      <c r="Z189" s="100"/>
-      <c r="AA189" s="102"/>
-      <c r="AB189" s="102"/>
+      <c r="Z189" s="102"/>
+      <c r="AA189" s="104"/>
+      <c r="AB189" s="104"/>
     </row>
     <row r="190" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
@@ -16901,9 +16907,9 @@
       <c r="Y190" s="50">
         <v>1</v>
       </c>
-      <c r="Z190" s="100"/>
-      <c r="AA190" s="102"/>
-      <c r="AB190" s="102"/>
+      <c r="Z190" s="102"/>
+      <c r="AA190" s="104"/>
+      <c r="AB190" s="104"/>
     </row>
     <row r="191" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
@@ -16983,9 +16989,9 @@
       <c r="Y191" s="50">
         <v>1</v>
       </c>
-      <c r="Z191" s="100"/>
-      <c r="AA191" s="102"/>
-      <c r="AB191" s="102"/>
+      <c r="Z191" s="102"/>
+      <c r="AA191" s="104"/>
+      <c r="AB191" s="104"/>
     </row>
     <row r="192" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
@@ -17065,9 +17071,9 @@
       <c r="Y192" s="50">
         <v>1</v>
       </c>
-      <c r="Z192" s="100"/>
-      <c r="AA192" s="102"/>
-      <c r="AB192" s="102"/>
+      <c r="Z192" s="102"/>
+      <c r="AA192" s="104"/>
+      <c r="AB192" s="104"/>
     </row>
     <row r="193" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A193" s="27">
@@ -17147,9 +17153,9 @@
       <c r="Y193" s="57">
         <v>1</v>
       </c>
-      <c r="Z193" s="100"/>
-      <c r="AA193" s="102"/>
-      <c r="AB193" s="102"/>
+      <c r="Z193" s="102"/>
+      <c r="AA193" s="104"/>
+      <c r="AB193" s="104"/>
     </row>
     <row r="194" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
@@ -17229,11 +17235,11 @@
       <c r="Y194" s="50">
         <v>1</v>
       </c>
-      <c r="Z194" s="100" t="s">
+      <c r="Z194" s="102" t="s">
         <v>84</v>
       </c>
-      <c r="AA194" s="102"/>
-      <c r="AB194" s="102"/>
+      <c r="AA194" s="104"/>
+      <c r="AB194" s="104"/>
     </row>
     <row r="195" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
@@ -17313,11 +17319,11 @@
       <c r="Y195" s="50">
         <v>1</v>
       </c>
-      <c r="Z195" s="100" t="s">
+      <c r="Z195" s="102" t="s">
         <v>85</v>
       </c>
-      <c r="AA195" s="102"/>
-      <c r="AB195" s="102"/>
+      <c r="AA195" s="104"/>
+      <c r="AB195" s="104"/>
     </row>
     <row r="196" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
@@ -17397,11 +17403,11 @@
       <c r="Y196" s="50">
         <v>1</v>
       </c>
-      <c r="Z196" s="100" t="s">
+      <c r="Z196" s="102" t="s">
         <v>86</v>
       </c>
-      <c r="AA196" s="102"/>
-      <c r="AB196" s="102"/>
+      <c r="AA196" s="104"/>
+      <c r="AB196" s="104"/>
     </row>
     <row r="197" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
@@ -17481,11 +17487,11 @@
       <c r="Y197" s="50">
         <v>1</v>
       </c>
-      <c r="Z197" s="100" t="s">
+      <c r="Z197" s="102" t="s">
         <v>87</v>
       </c>
-      <c r="AA197" s="102"/>
-      <c r="AB197" s="102"/>
+      <c r="AA197" s="104"/>
+      <c r="AB197" s="104"/>
     </row>
     <row r="198" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
@@ -17565,11 +17571,11 @@
       <c r="Y198" s="50">
         <v>1</v>
       </c>
-      <c r="Z198" s="100" t="s">
+      <c r="Z198" s="102" t="s">
         <v>84</v>
       </c>
-      <c r="AA198" s="102"/>
-      <c r="AB198" s="102"/>
+      <c r="AA198" s="104"/>
+      <c r="AB198" s="104"/>
     </row>
     <row r="199" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
@@ -17649,11 +17655,11 @@
       <c r="Y199" s="50">
         <v>1</v>
       </c>
-      <c r="Z199" s="100" t="s">
+      <c r="Z199" s="102" t="s">
         <v>85</v>
       </c>
-      <c r="AA199" s="102"/>
-      <c r="AB199" s="102"/>
+      <c r="AA199" s="104"/>
+      <c r="AB199" s="104"/>
     </row>
     <row r="200" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A200" s="27">
@@ -17733,11 +17739,11 @@
       <c r="Y200" s="57">
         <v>1</v>
       </c>
-      <c r="Z200" s="100" t="s">
+      <c r="Z200" s="102" t="s">
         <v>85</v>
       </c>
-      <c r="AA200" s="102"/>
-      <c r="AB200" s="102"/>
+      <c r="AA200" s="104"/>
+      <c r="AB200" s="104"/>
     </row>
     <row r="201" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A201" s="27">
@@ -17816,11 +17822,11 @@
       <c r="Y201" s="57">
         <v>1</v>
       </c>
-      <c r="Z201" s="100" t="s">
+      <c r="Z201" s="102" t="s">
         <v>88</v>
       </c>
-      <c r="AA201" s="102"/>
-      <c r="AB201" s="102"/>
+      <c r="AA201" s="104"/>
+      <c r="AB201" s="104"/>
     </row>
     <row r="202" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A202" s="27">
@@ -17899,11 +17905,11 @@
       <c r="Y202" s="57">
         <v>1</v>
       </c>
-      <c r="Z202" s="100" t="s">
+      <c r="Z202" s="102" t="s">
         <v>89</v>
       </c>
-      <c r="AA202" s="102"/>
-      <c r="AB202" s="102"/>
+      <c r="AA202" s="104"/>
+      <c r="AB202" s="104"/>
     </row>
     <row r="203" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A203" s="43">
@@ -17982,11 +17988,11 @@
       <c r="Y203" s="40">
         <v>1</v>
       </c>
-      <c r="Z203" s="100" t="s">
+      <c r="Z203" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="AA203" s="102"/>
-      <c r="AB203" s="102"/>
+      <c r="AA203" s="104"/>
+      <c r="AB203" s="104"/>
     </row>
     <row r="204" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A204" s="23">
@@ -18065,11 +18071,11 @@
       <c r="Y204" s="50">
         <v>1</v>
       </c>
-      <c r="Z204" s="100" t="s">
+      <c r="Z204" s="102" t="s">
         <v>91</v>
       </c>
-      <c r="AA204" s="102"/>
-      <c r="AB204" s="102"/>
+      <c r="AA204" s="104"/>
+      <c r="AB204" s="104"/>
     </row>
     <row r="205" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="23">
@@ -18148,11 +18154,11 @@
       <c r="Y205" s="50">
         <v>1</v>
       </c>
-      <c r="Z205" s="100" t="s">
+      <c r="Z205" s="102" t="s">
         <v>92</v>
       </c>
-      <c r="AA205" s="102"/>
-      <c r="AB205" s="102"/>
+      <c r="AA205" s="104"/>
+      <c r="AB205" s="104"/>
     </row>
     <row r="206" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="43">
@@ -18230,11 +18236,11 @@
       <c r="Y206" s="40">
         <v>1</v>
       </c>
-      <c r="Z206" s="100" t="s">
+      <c r="Z206" s="102" t="s">
         <v>94</v>
       </c>
-      <c r="AA206" s="101"/>
-      <c r="AB206" s="101"/>
+      <c r="AA206" s="103"/>
+      <c r="AB206" s="103"/>
     </row>
     <row r="207" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
@@ -18312,9 +18318,9 @@
       <c r="Y207" s="50">
         <v>1</v>
       </c>
-      <c r="Z207" s="100"/>
-      <c r="AA207" s="101"/>
-      <c r="AB207" s="101"/>
+      <c r="Z207" s="102"/>
+      <c r="AA207" s="103"/>
+      <c r="AB207" s="103"/>
     </row>
     <row r="208" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
@@ -18392,9 +18398,9 @@
       <c r="Y208" s="50">
         <v>1</v>
       </c>
-      <c r="Z208" s="100"/>
-      <c r="AA208" s="101"/>
-      <c r="AB208" s="101"/>
+      <c r="Z208" s="102"/>
+      <c r="AA208" s="103"/>
+      <c r="AB208" s="103"/>
     </row>
     <row r="209" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
@@ -18472,9 +18478,9 @@
       <c r="Y209" s="50">
         <v>1</v>
       </c>
-      <c r="Z209" s="100"/>
-      <c r="AA209" s="101"/>
-      <c r="AB209" s="101"/>
+      <c r="Z209" s="102"/>
+      <c r="AA209" s="103"/>
+      <c r="AB209" s="103"/>
     </row>
     <row r="210" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
@@ -18552,9 +18558,9 @@
       <c r="Y210" s="50">
         <v>1</v>
       </c>
-      <c r="Z210" s="100"/>
-      <c r="AA210" s="101"/>
-      <c r="AB210" s="101"/>
+      <c r="Z210" s="102"/>
+      <c r="AA210" s="103"/>
+      <c r="AB210" s="103"/>
     </row>
     <row r="211" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
@@ -18632,9 +18638,9 @@
       <c r="Y211" s="50">
         <v>1</v>
       </c>
-      <c r="Z211" s="100"/>
-      <c r="AA211" s="101"/>
-      <c r="AB211" s="101"/>
+      <c r="Z211" s="102"/>
+      <c r="AA211" s="103"/>
+      <c r="AB211" s="103"/>
     </row>
     <row r="212" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
@@ -18712,9 +18718,9 @@
       <c r="Y212" s="50">
         <v>1</v>
       </c>
-      <c r="Z212" s="100"/>
-      <c r="AA212" s="101"/>
-      <c r="AB212" s="101"/>
+      <c r="Z212" s="102"/>
+      <c r="AA212" s="103"/>
+      <c r="AB212" s="103"/>
     </row>
     <row r="213" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
@@ -18792,9 +18798,9 @@
       <c r="Y213" s="50">
         <v>1</v>
       </c>
-      <c r="Z213" s="100"/>
-      <c r="AA213" s="101"/>
-      <c r="AB213" s="101"/>
+      <c r="Z213" s="102"/>
+      <c r="AA213" s="103"/>
+      <c r="AB213" s="103"/>
     </row>
     <row r="214" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
@@ -18872,9 +18878,9 @@
       <c r="Y214" s="50">
         <v>1</v>
       </c>
-      <c r="Z214" s="100"/>
-      <c r="AA214" s="101"/>
-      <c r="AB214" s="101"/>
+      <c r="Z214" s="102"/>
+      <c r="AA214" s="103"/>
+      <c r="AB214" s="103"/>
     </row>
     <row r="215" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
@@ -18952,9 +18958,9 @@
       <c r="Y215" s="50">
         <v>1</v>
       </c>
-      <c r="Z215" s="100"/>
-      <c r="AA215" s="101"/>
-      <c r="AB215" s="101"/>
+      <c r="Z215" s="102"/>
+      <c r="AA215" s="103"/>
+      <c r="AB215" s="103"/>
     </row>
     <row r="216" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
@@ -19032,9 +19038,9 @@
       <c r="Y216" s="50">
         <v>1</v>
       </c>
-      <c r="Z216" s="100"/>
-      <c r="AA216" s="101"/>
-      <c r="AB216" s="101"/>
+      <c r="Z216" s="102"/>
+      <c r="AA216" s="103"/>
+      <c r="AB216" s="103"/>
     </row>
     <row r="217" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
@@ -19112,9 +19118,9 @@
       <c r="Y217" s="50">
         <v>1</v>
       </c>
-      <c r="Z217" s="100"/>
-      <c r="AA217" s="101"/>
-      <c r="AB217" s="101"/>
+      <c r="Z217" s="102"/>
+      <c r="AA217" s="103"/>
+      <c r="AB217" s="103"/>
     </row>
     <row r="218" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
@@ -19192,9 +19198,9 @@
       <c r="Y218" s="50">
         <v>1</v>
       </c>
-      <c r="Z218" s="100"/>
-      <c r="AA218" s="101"/>
-      <c r="AB218" s="101"/>
+      <c r="Z218" s="102"/>
+      <c r="AA218" s="103"/>
+      <c r="AB218" s="103"/>
     </row>
     <row r="219" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
@@ -19272,9 +19278,9 @@
       <c r="Y219" s="50">
         <v>1</v>
       </c>
-      <c r="Z219" s="100"/>
-      <c r="AA219" s="101"/>
-      <c r="AB219" s="101"/>
+      <c r="Z219" s="102"/>
+      <c r="AA219" s="103"/>
+      <c r="AB219" s="103"/>
     </row>
     <row r="220" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
@@ -19352,9 +19358,9 @@
       <c r="Y220" s="50">
         <v>1</v>
       </c>
-      <c r="Z220" s="100"/>
-      <c r="AA220" s="101"/>
-      <c r="AB220" s="101"/>
+      <c r="Z220" s="102"/>
+      <c r="AA220" s="103"/>
+      <c r="AB220" s="103"/>
     </row>
     <row r="221" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A221" s="43">
@@ -19432,11 +19438,11 @@
       <c r="Y221" s="40">
         <v>1</v>
       </c>
-      <c r="Z221" s="100" t="s">
+      <c r="Z221" s="102" t="s">
         <v>95</v>
       </c>
-      <c r="AA221" s="102"/>
-      <c r="AB221" s="102"/>
+      <c r="AA221" s="104"/>
+      <c r="AB221" s="104"/>
     </row>
     <row r="222" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
@@ -19514,9 +19520,9 @@
       <c r="Y222" s="50">
         <v>1</v>
       </c>
-      <c r="Z222" s="100"/>
-      <c r="AA222" s="102"/>
-      <c r="AB222" s="102"/>
+      <c r="Z222" s="102"/>
+      <c r="AA222" s="104"/>
+      <c r="AB222" s="104"/>
     </row>
     <row r="223" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A223" s="43">
@@ -19594,11 +19600,11 @@
       <c r="Y223" s="40">
         <v>1</v>
       </c>
-      <c r="Z223" s="100" t="s">
+      <c r="Z223" s="102" t="s">
         <v>96</v>
       </c>
-      <c r="AA223" s="102"/>
-      <c r="AB223" s="102"/>
+      <c r="AA223" s="104"/>
+      <c r="AB223" s="104"/>
     </row>
     <row r="224" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
@@ -19676,9 +19682,9 @@
       <c r="Y224" s="50">
         <v>1</v>
       </c>
-      <c r="Z224" s="100"/>
-      <c r="AA224" s="102"/>
-      <c r="AB224" s="102"/>
+      <c r="Z224" s="102"/>
+      <c r="AA224" s="104"/>
+      <c r="AB224" s="104"/>
     </row>
     <row r="225" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A225" s="43">
@@ -19756,11 +19762,11 @@
       <c r="Y225" s="40">
         <v>1</v>
       </c>
-      <c r="Z225" s="100" t="s">
+      <c r="Z225" s="102" t="s">
         <v>97</v>
       </c>
-      <c r="AA225" s="102"/>
-      <c r="AB225" s="102"/>
+      <c r="AA225" s="104"/>
+      <c r="AB225" s="104"/>
     </row>
     <row r="226" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
@@ -19839,9 +19845,9 @@
       <c r="Y226" s="50">
         <v>1</v>
       </c>
-      <c r="Z226" s="100"/>
-      <c r="AA226" s="102"/>
-      <c r="AB226" s="102"/>
+      <c r="Z226" s="102"/>
+      <c r="AA226" s="104"/>
+      <c r="AB226" s="104"/>
     </row>
     <row r="227" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
@@ -19920,9 +19926,9 @@
       <c r="Y227" s="50">
         <v>1</v>
       </c>
-      <c r="Z227" s="100"/>
-      <c r="AA227" s="102"/>
-      <c r="AB227" s="102"/>
+      <c r="Z227" s="102"/>
+      <c r="AA227" s="104"/>
+      <c r="AB227" s="104"/>
     </row>
     <row r="228" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
@@ -20001,9 +20007,9 @@
       <c r="Y228" s="50">
         <v>1</v>
       </c>
-      <c r="Z228" s="100"/>
-      <c r="AA228" s="102"/>
-      <c r="AB228" s="102"/>
+      <c r="Z228" s="102"/>
+      <c r="AA228" s="104"/>
+      <c r="AB228" s="104"/>
     </row>
     <row r="229" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
@@ -20082,9 +20088,9 @@
       <c r="Y229" s="50">
         <v>1</v>
       </c>
-      <c r="Z229" s="100"/>
-      <c r="AA229" s="102"/>
-      <c r="AB229" s="102"/>
+      <c r="Z229" s="102"/>
+      <c r="AA229" s="104"/>
+      <c r="AB229" s="104"/>
     </row>
     <row r="230" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
@@ -20163,9 +20169,9 @@
       <c r="Y230" s="50">
         <v>1</v>
       </c>
-      <c r="Z230" s="100"/>
-      <c r="AA230" s="102"/>
-      <c r="AB230" s="102"/>
+      <c r="Z230" s="102"/>
+      <c r="AA230" s="104"/>
+      <c r="AB230" s="104"/>
     </row>
     <row r="231" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
@@ -20244,9 +20250,9 @@
       <c r="Y231" s="50">
         <v>1</v>
       </c>
-      <c r="Z231" s="100"/>
-      <c r="AA231" s="102"/>
-      <c r="AB231" s="102"/>
+      <c r="Z231" s="102"/>
+      <c r="AA231" s="104"/>
+      <c r="AB231" s="104"/>
     </row>
     <row r="232" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
@@ -20325,9 +20331,9 @@
       <c r="Y232" s="50">
         <v>1</v>
       </c>
-      <c r="Z232" s="100"/>
-      <c r="AA232" s="102"/>
-      <c r="AB232" s="102"/>
+      <c r="Z232" s="102"/>
+      <c r="AA232" s="104"/>
+      <c r="AB232" s="104"/>
     </row>
     <row r="233" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="43">
@@ -20405,11 +20411,11 @@
       <c r="Y233" s="40">
         <v>1</v>
       </c>
-      <c r="Z233" s="100" t="s">
+      <c r="Z233" s="102" t="s">
         <v>95</v>
       </c>
-      <c r="AA233" s="101"/>
-      <c r="AB233" s="101"/>
+      <c r="AA233" s="103"/>
+      <c r="AB233" s="103"/>
     </row>
     <row r="234" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A234" s="27">
@@ -20487,9 +20493,9 @@
       <c r="Y234" s="57">
         <v>1</v>
       </c>
-      <c r="Z234" s="100"/>
-      <c r="AA234" s="101"/>
-      <c r="AB234" s="101"/>
+      <c r="Z234" s="102"/>
+      <c r="AA234" s="103"/>
+      <c r="AB234" s="103"/>
     </row>
     <row r="235" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
@@ -20569,11 +20575,11 @@
       <c r="Y235" s="50">
         <v>1</v>
       </c>
-      <c r="Z235" s="100" t="s">
+      <c r="Z235" s="102" t="s">
         <v>98</v>
       </c>
-      <c r="AA235" s="102"/>
-      <c r="AB235" s="102"/>
+      <c r="AA235" s="104"/>
+      <c r="AB235" s="104"/>
     </row>
     <row r="236" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
@@ -20653,9 +20659,9 @@
       <c r="Y236" s="50">
         <v>1</v>
       </c>
-      <c r="Z236" s="100"/>
-      <c r="AA236" s="102"/>
-      <c r="AB236" s="102"/>
+      <c r="Z236" s="102"/>
+      <c r="AA236" s="104"/>
+      <c r="AB236" s="104"/>
     </row>
     <row r="237" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
@@ -20735,9 +20741,9 @@
       <c r="Y237" s="50">
         <v>1</v>
       </c>
-      <c r="Z237" s="100"/>
-      <c r="AA237" s="102"/>
-      <c r="AB237" s="102"/>
+      <c r="Z237" s="102"/>
+      <c r="AA237" s="104"/>
+      <c r="AB237" s="104"/>
     </row>
     <row r="238" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A238" s="43">
@@ -20815,11 +20821,11 @@
       <c r="Y238" s="40">
         <v>1</v>
       </c>
-      <c r="Z238" s="100" t="s">
+      <c r="Z238" s="102" t="s">
         <v>99</v>
       </c>
-      <c r="AA238" s="102"/>
-      <c r="AB238" s="102"/>
+      <c r="AA238" s="104"/>
+      <c r="AB238" s="104"/>
     </row>
     <row r="239" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
@@ -20897,9 +20903,9 @@
       <c r="Y239" s="50">
         <v>1</v>
       </c>
-      <c r="Z239" s="100"/>
-      <c r="AA239" s="102"/>
-      <c r="AB239" s="102"/>
+      <c r="Z239" s="102"/>
+      <c r="AA239" s="104"/>
+      <c r="AB239" s="104"/>
     </row>
     <row r="240" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A240" s="43">
@@ -20977,11 +20983,11 @@
       <c r="Y240" s="40">
         <v>1</v>
       </c>
-      <c r="Z240" s="100" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA240" s="102"/>
-      <c r="AB240" s="102"/>
+      <c r="Z240" s="102" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA240" s="104"/>
+      <c r="AB240" s="104"/>
     </row>
     <row r="241" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
@@ -21060,9 +21066,9 @@
       <c r="Y241" s="50">
         <v>1</v>
       </c>
-      <c r="Z241" s="100"/>
-      <c r="AA241" s="102"/>
-      <c r="AB241" s="102"/>
+      <c r="Z241" s="102"/>
+      <c r="AA241" s="104"/>
+      <c r="AB241" s="104"/>
     </row>
     <row r="242" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
@@ -21141,9 +21147,9 @@
       <c r="Y242" s="50">
         <v>1</v>
       </c>
-      <c r="Z242" s="100"/>
-      <c r="AA242" s="102"/>
-      <c r="AB242" s="102"/>
+      <c r="Z242" s="102"/>
+      <c r="AA242" s="104"/>
+      <c r="AB242" s="104"/>
     </row>
     <row r="243" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
@@ -21222,9 +21228,9 @@
       <c r="Y243" s="50">
         <v>1</v>
       </c>
-      <c r="Z243" s="100"/>
-      <c r="AA243" s="102"/>
-      <c r="AB243" s="102"/>
+      <c r="Z243" s="102"/>
+      <c r="AA243" s="104"/>
+      <c r="AB243" s="104"/>
     </row>
     <row r="244" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
@@ -21303,9 +21309,9 @@
       <c r="Y244" s="50">
         <v>1</v>
       </c>
-      <c r="Z244" s="100"/>
-      <c r="AA244" s="102"/>
-      <c r="AB244" s="102"/>
+      <c r="Z244" s="102"/>
+      <c r="AA244" s="104"/>
+      <c r="AB244" s="104"/>
     </row>
     <row r="245" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
@@ -21384,9 +21390,9 @@
       <c r="Y245" s="50">
         <v>1</v>
       </c>
-      <c r="Z245" s="100"/>
-      <c r="AA245" s="102"/>
-      <c r="AB245" s="102"/>
+      <c r="Z245" s="102"/>
+      <c r="AA245" s="104"/>
+      <c r="AB245" s="104"/>
     </row>
     <row r="246" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
@@ -21465,9 +21471,9 @@
       <c r="Y246" s="50">
         <v>1</v>
       </c>
-      <c r="Z246" s="100"/>
-      <c r="AA246" s="102"/>
-      <c r="AB246" s="102"/>
+      <c r="Z246" s="102"/>
+      <c r="AA246" s="104"/>
+      <c r="AB246" s="104"/>
     </row>
     <row r="247" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
@@ -21546,9 +21552,9 @@
       <c r="Y247" s="50">
         <v>1</v>
       </c>
-      <c r="Z247" s="100"/>
-      <c r="AA247" s="102"/>
-      <c r="AB247" s="102"/>
+      <c r="Z247" s="102"/>
+      <c r="AA247" s="104"/>
+      <c r="AB247" s="104"/>
     </row>
     <row r="248" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
@@ -21627,9 +21633,9 @@
       <c r="Y248" s="50">
         <v>1</v>
       </c>
-      <c r="Z248" s="100"/>
-      <c r="AA248" s="102"/>
-      <c r="AB248" s="102"/>
+      <c r="Z248" s="102"/>
+      <c r="AA248" s="104"/>
+      <c r="AB248" s="104"/>
     </row>
     <row r="249" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
@@ -21708,9 +21714,9 @@
       <c r="Y249" s="50">
         <v>1</v>
       </c>
-      <c r="Z249" s="100"/>
-      <c r="AA249" s="102"/>
-      <c r="AB249" s="102"/>
+      <c r="Z249" s="102"/>
+      <c r="AA249" s="104"/>
+      <c r="AB249" s="104"/>
     </row>
     <row r="250" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
@@ -21789,9 +21795,9 @@
       <c r="Y250" s="50">
         <v>1</v>
       </c>
-      <c r="Z250" s="100"/>
-      <c r="AA250" s="102"/>
-      <c r="AB250" s="102"/>
+      <c r="Z250" s="102"/>
+      <c r="AA250" s="104"/>
+      <c r="AB250" s="104"/>
     </row>
     <row r="251" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
@@ -21870,9 +21876,9 @@
       <c r="Y251" s="50">
         <v>1</v>
       </c>
-      <c r="Z251" s="100"/>
-      <c r="AA251" s="102"/>
-      <c r="AB251" s="102"/>
+      <c r="Z251" s="102"/>
+      <c r="AA251" s="104"/>
+      <c r="AB251" s="104"/>
     </row>
     <row r="252" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A252" s="43">
@@ -21951,11 +21957,11 @@
       <c r="Y252" s="40">
         <v>1</v>
       </c>
-      <c r="Z252" s="100" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA252" s="101"/>
-      <c r="AB252" s="101"/>
+      <c r="Z252" s="102" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA252" s="103"/>
+      <c r="AB252" s="103"/>
     </row>
     <row r="253" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
@@ -22034,9 +22040,9 @@
       <c r="Y253" s="50">
         <v>1</v>
       </c>
-      <c r="Z253" s="100"/>
-      <c r="AA253" s="101"/>
-      <c r="AB253" s="101"/>
+      <c r="Z253" s="102"/>
+      <c r="AA253" s="103"/>
+      <c r="AB253" s="103"/>
     </row>
     <row r="254" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
@@ -22115,9 +22121,9 @@
       <c r="Y254" s="50">
         <v>1</v>
       </c>
-      <c r="Z254" s="100"/>
-      <c r="AA254" s="101"/>
-      <c r="AB254" s="101"/>
+      <c r="Z254" s="102"/>
+      <c r="AA254" s="103"/>
+      <c r="AB254" s="103"/>
     </row>
     <row r="255" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
@@ -22196,9 +22202,9 @@
       <c r="Y255" s="50">
         <v>1</v>
       </c>
-      <c r="Z255" s="100"/>
-      <c r="AA255" s="101"/>
-      <c r="AB255" s="101"/>
+      <c r="Z255" s="102"/>
+      <c r="AA255" s="103"/>
+      <c r="AB255" s="103"/>
     </row>
     <row r="256" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
@@ -22277,9 +22283,9 @@
       <c r="Y256" s="50">
         <v>1</v>
       </c>
-      <c r="Z256" s="100"/>
-      <c r="AA256" s="101"/>
-      <c r="AB256" s="101"/>
+      <c r="Z256" s="102"/>
+      <c r="AA256" s="103"/>
+      <c r="AB256" s="103"/>
     </row>
     <row r="257" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
@@ -22358,9 +22364,9 @@
       <c r="Y257" s="50">
         <v>1</v>
       </c>
-      <c r="Z257" s="100"/>
-      <c r="AA257" s="101"/>
-      <c r="AB257" s="101"/>
+      <c r="Z257" s="102"/>
+      <c r="AA257" s="103"/>
+      <c r="AB257" s="103"/>
     </row>
     <row r="258" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
@@ -22439,9 +22445,9 @@
       <c r="Y258" s="50">
         <v>1</v>
       </c>
-      <c r="Z258" s="100"/>
-      <c r="AA258" s="101"/>
-      <c r="AB258" s="101"/>
+      <c r="Z258" s="102"/>
+      <c r="AA258" s="103"/>
+      <c r="AB258" s="103"/>
     </row>
     <row r="259" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
@@ -22520,9 +22526,9 @@
       <c r="Y259" s="50">
         <v>1</v>
       </c>
-      <c r="Z259" s="100"/>
-      <c r="AA259" s="101"/>
-      <c r="AB259" s="101"/>
+      <c r="Z259" s="102"/>
+      <c r="AA259" s="103"/>
+      <c r="AB259" s="103"/>
     </row>
     <row r="260" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
@@ -22601,9 +22607,9 @@
       <c r="Y260" s="50">
         <v>1</v>
       </c>
-      <c r="Z260" s="100"/>
-      <c r="AA260" s="101"/>
-      <c r="AB260" s="101"/>
+      <c r="Z260" s="102"/>
+      <c r="AA260" s="103"/>
+      <c r="AB260" s="103"/>
     </row>
     <row r="261" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
@@ -22682,9 +22688,9 @@
       <c r="Y261" s="50">
         <v>1</v>
       </c>
-      <c r="Z261" s="100"/>
-      <c r="AA261" s="101"/>
-      <c r="AB261" s="101"/>
+      <c r="Z261" s="102"/>
+      <c r="AA261" s="103"/>
+      <c r="AB261" s="103"/>
     </row>
     <row r="262" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
@@ -22763,9 +22769,9 @@
       <c r="Y262" s="50">
         <v>1</v>
       </c>
-      <c r="Z262" s="100"/>
-      <c r="AA262" s="101"/>
-      <c r="AB262" s="101"/>
+      <c r="Z262" s="102"/>
+      <c r="AA262" s="103"/>
+      <c r="AB262" s="103"/>
     </row>
     <row r="263" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A263" s="43">
@@ -22844,11 +22850,11 @@
       <c r="Y263" s="40">
         <v>1</v>
       </c>
-      <c r="Z263" s="100" t="s">
+      <c r="Z263" s="102" t="s">
         <v>101</v>
       </c>
-      <c r="AA263" s="101"/>
-      <c r="AB263" s="101"/>
+      <c r="AA263" s="103"/>
+      <c r="AB263" s="103"/>
     </row>
     <row r="264" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
@@ -22927,9 +22933,9 @@
       <c r="Y264" s="50">
         <v>1</v>
       </c>
-      <c r="Z264" s="100"/>
-      <c r="AA264" s="101"/>
-      <c r="AB264" s="101"/>
+      <c r="Z264" s="102"/>
+      <c r="AA264" s="103"/>
+      <c r="AB264" s="103"/>
     </row>
     <row r="265" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A265" s="43">
@@ -23008,11 +23014,11 @@
       <c r="Y265" s="40">
         <v>1</v>
       </c>
-      <c r="Z265" s="100" t="s">
+      <c r="Z265" s="102" t="s">
         <v>102</v>
       </c>
-      <c r="AA265" s="102"/>
-      <c r="AB265" s="102"/>
+      <c r="AA265" s="104"/>
+      <c r="AB265" s="104"/>
     </row>
     <row r="266" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
@@ -23091,9 +23097,9 @@
       <c r="Y266" s="50">
         <v>1</v>
       </c>
-      <c r="Z266" s="100"/>
-      <c r="AA266" s="102"/>
-      <c r="AB266" s="102"/>
+      <c r="Z266" s="102"/>
+      <c r="AA266" s="104"/>
+      <c r="AB266" s="104"/>
     </row>
     <row r="267" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
@@ -23172,9 +23178,9 @@
       <c r="Y267" s="50">
         <v>1</v>
       </c>
-      <c r="Z267" s="100"/>
-      <c r="AA267" s="102"/>
-      <c r="AB267" s="102"/>
+      <c r="Z267" s="102"/>
+      <c r="AA267" s="104"/>
+      <c r="AB267" s="104"/>
     </row>
     <row r="268" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
@@ -23253,9 +23259,9 @@
       <c r="Y268" s="50">
         <v>1</v>
       </c>
-      <c r="Z268" s="100"/>
-      <c r="AA268" s="102"/>
-      <c r="AB268" s="102"/>
+      <c r="Z268" s="102"/>
+      <c r="AA268" s="104"/>
+      <c r="AB268" s="104"/>
     </row>
     <row r="269" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
@@ -23334,9 +23340,9 @@
       <c r="Y269" s="50">
         <v>1</v>
       </c>
-      <c r="Z269" s="100"/>
-      <c r="AA269" s="102"/>
-      <c r="AB269" s="102"/>
+      <c r="Z269" s="102"/>
+      <c r="AA269" s="104"/>
+      <c r="AB269" s="104"/>
     </row>
     <row r="270" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
@@ -23415,9 +23421,9 @@
       <c r="Y270" s="50">
         <v>1</v>
       </c>
-      <c r="Z270" s="100"/>
-      <c r="AA270" s="102"/>
-      <c r="AB270" s="102"/>
+      <c r="Z270" s="102"/>
+      <c r="AA270" s="104"/>
+      <c r="AB270" s="104"/>
     </row>
     <row r="271" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
@@ -23496,9 +23502,9 @@
       <c r="Y271" s="50">
         <v>1</v>
       </c>
-      <c r="Z271" s="100"/>
-      <c r="AA271" s="102"/>
-      <c r="AB271" s="102"/>
+      <c r="Z271" s="102"/>
+      <c r="AA271" s="104"/>
+      <c r="AB271" s="104"/>
     </row>
     <row r="272" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
@@ -23577,9 +23583,9 @@
       <c r="Y272" s="50">
         <v>1</v>
       </c>
-      <c r="Z272" s="100"/>
-      <c r="AA272" s="102"/>
-      <c r="AB272" s="102"/>
+      <c r="Z272" s="102"/>
+      <c r="AA272" s="104"/>
+      <c r="AB272" s="104"/>
     </row>
     <row r="273" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
@@ -23658,9 +23664,9 @@
       <c r="Y273" s="50">
         <v>1</v>
       </c>
-      <c r="Z273" s="100"/>
-      <c r="AA273" s="102"/>
-      <c r="AB273" s="102"/>
+      <c r="Z273" s="102"/>
+      <c r="AA273" s="104"/>
+      <c r="AB273" s="104"/>
     </row>
     <row r="274" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
@@ -23739,9 +23745,9 @@
       <c r="Y274" s="50">
         <v>1</v>
       </c>
-      <c r="Z274" s="100"/>
-      <c r="AA274" s="102"/>
-      <c r="AB274" s="102"/>
+      <c r="Z274" s="102"/>
+      <c r="AA274" s="104"/>
+      <c r="AB274" s="104"/>
     </row>
     <row r="275" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A275" s="27">
@@ -23820,9 +23826,9 @@
       <c r="Y275" s="57">
         <v>1</v>
       </c>
-      <c r="Z275" s="100"/>
-      <c r="AA275" s="102"/>
-      <c r="AB275" s="102"/>
+      <c r="Z275" s="102"/>
+      <c r="AA275" s="104"/>
+      <c r="AB275" s="104"/>
     </row>
     <row r="276" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="43">
@@ -23901,11 +23907,11 @@
       <c r="Y276" s="40">
         <v>1</v>
       </c>
-      <c r="Z276" s="100" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA276" s="101"/>
-      <c r="AB276" s="101"/>
+      <c r="Z276" s="102" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA276" s="103"/>
+      <c r="AB276" s="103"/>
     </row>
     <row r="277" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
@@ -23983,9 +23989,9 @@
       <c r="Y277" s="50">
         <v>1</v>
       </c>
-      <c r="Z277" s="100"/>
-      <c r="AA277" s="101"/>
-      <c r="AB277" s="101"/>
+      <c r="Z277" s="102"/>
+      <c r="AA277" s="103"/>
+      <c r="AB277" s="103"/>
     </row>
     <row r="278" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
@@ -24063,9 +24069,9 @@
       <c r="Y278" s="50">
         <v>1</v>
       </c>
-      <c r="Z278" s="100"/>
-      <c r="AA278" s="101"/>
-      <c r="AB278" s="101"/>
+      <c r="Z278" s="102"/>
+      <c r="AA278" s="103"/>
+      <c r="AB278" s="103"/>
     </row>
     <row r="279" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
@@ -24143,9 +24149,9 @@
       <c r="Y279" s="50">
         <v>1</v>
       </c>
-      <c r="Z279" s="100"/>
-      <c r="AA279" s="101"/>
-      <c r="AB279" s="101"/>
+      <c r="Z279" s="102"/>
+      <c r="AA279" s="103"/>
+      <c r="AB279" s="103"/>
     </row>
     <row r="280" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
@@ -24223,9 +24229,9 @@
       <c r="Y280" s="50">
         <v>1</v>
       </c>
-      <c r="Z280" s="100"/>
-      <c r="AA280" s="101"/>
-      <c r="AB280" s="101"/>
+      <c r="Z280" s="102"/>
+      <c r="AA280" s="103"/>
+      <c r="AB280" s="103"/>
     </row>
     <row r="281" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
@@ -24303,9 +24309,9 @@
       <c r="Y281" s="50">
         <v>1</v>
       </c>
-      <c r="Z281" s="100"/>
-      <c r="AA281" s="101"/>
-      <c r="AB281" s="101"/>
+      <c r="Z281" s="102"/>
+      <c r="AA281" s="103"/>
+      <c r="AB281" s="103"/>
     </row>
     <row r="282" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
@@ -24383,9 +24389,9 @@
       <c r="Y282" s="50">
         <v>1</v>
       </c>
-      <c r="Z282" s="100"/>
-      <c r="AA282" s="101"/>
-      <c r="AB282" s="101"/>
+      <c r="Z282" s="102"/>
+      <c r="AA282" s="103"/>
+      <c r="AB282" s="103"/>
     </row>
     <row r="283" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
@@ -24463,9 +24469,9 @@
       <c r="Y283" s="50">
         <v>1</v>
       </c>
-      <c r="Z283" s="100"/>
-      <c r="AA283" s="101"/>
-      <c r="AB283" s="101"/>
+      <c r="Z283" s="102"/>
+      <c r="AA283" s="103"/>
+      <c r="AB283" s="103"/>
     </row>
     <row r="284" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
@@ -24543,9 +24549,9 @@
       <c r="Y284" s="50">
         <v>1</v>
       </c>
-      <c r="Z284" s="100"/>
-      <c r="AA284" s="101"/>
-      <c r="AB284" s="101"/>
+      <c r="Z284" s="102"/>
+      <c r="AA284" s="103"/>
+      <c r="AB284" s="103"/>
     </row>
     <row r="285" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A285" s="43">
@@ -24624,9 +24630,9 @@
       <c r="Y285" s="40">
         <v>1</v>
       </c>
-      <c r="Z285" s="100"/>
-      <c r="AA285" s="101"/>
-      <c r="AB285" s="101"/>
+      <c r="Z285" s="102"/>
+      <c r="AA285" s="103"/>
+      <c r="AB285" s="103"/>
     </row>
     <row r="286" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
@@ -24706,9 +24712,9 @@
       <c r="Y286" s="50">
         <v>1</v>
       </c>
-      <c r="Z286" s="100"/>
-      <c r="AA286" s="101"/>
-      <c r="AB286" s="101"/>
+      <c r="Z286" s="102"/>
+      <c r="AA286" s="103"/>
+      <c r="AB286" s="103"/>
     </row>
     <row r="287" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A287" s="27">
@@ -24788,9 +24794,9 @@
       <c r="Y287" s="57">
         <v>1</v>
       </c>
-      <c r="Z287" s="100"/>
-      <c r="AA287" s="101"/>
-      <c r="AB287" s="101"/>
+      <c r="Z287" s="102"/>
+      <c r="AA287" s="103"/>
+      <c r="AB287" s="103"/>
     </row>
     <row r="288" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
@@ -24868,11 +24874,11 @@
       <c r="Y288" s="50">
         <v>1</v>
       </c>
-      <c r="Z288" s="100" t="s">
+      <c r="Z288" s="102" t="s">
         <v>101</v>
       </c>
-      <c r="AA288" s="101"/>
-      <c r="AB288" s="101"/>
+      <c r="AA288" s="103"/>
+      <c r="AB288" s="103"/>
     </row>
     <row r="289" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A289" s="27">
@@ -24951,9 +24957,9 @@
       <c r="Y289" s="57">
         <v>1</v>
       </c>
-      <c r="Z289" s="100"/>
-      <c r="AA289" s="101"/>
-      <c r="AB289" s="101"/>
+      <c r="Z289" s="102"/>
+      <c r="AA289" s="103"/>
+      <c r="AB289" s="103"/>
     </row>
     <row r="290" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
@@ -25033,11 +25039,11 @@
       <c r="Y290" s="50">
         <v>1</v>
       </c>
-      <c r="Z290" s="100" t="s">
+      <c r="Z290" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="AA290" s="102"/>
-      <c r="AB290" s="102"/>
+      <c r="AA290" s="104"/>
+      <c r="AB290" s="104"/>
     </row>
     <row r="291" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
@@ -25117,9 +25123,9 @@
       <c r="Y291" s="50">
         <v>1</v>
       </c>
-      <c r="Z291" s="100"/>
-      <c r="AA291" s="102"/>
-      <c r="AB291" s="102"/>
+      <c r="Z291" s="102"/>
+      <c r="AA291" s="104"/>
+      <c r="AB291" s="104"/>
     </row>
     <row r="292" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
@@ -25199,9 +25205,9 @@
       <c r="Y292" s="50">
         <v>1</v>
       </c>
-      <c r="Z292" s="100"/>
-      <c r="AA292" s="102"/>
-      <c r="AB292" s="102"/>
+      <c r="Z292" s="102"/>
+      <c r="AA292" s="104"/>
+      <c r="AB292" s="104"/>
     </row>
     <row r="293" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A293" s="43">
@@ -25280,11 +25286,11 @@
       <c r="Y293" s="40">
         <v>1</v>
       </c>
-      <c r="Z293" s="100" t="s">
+      <c r="Z293" s="102" t="s">
         <v>104</v>
       </c>
-      <c r="AA293" s="102"/>
-      <c r="AB293" s="102"/>
+      <c r="AA293" s="104"/>
+      <c r="AB293" s="104"/>
     </row>
     <row r="294" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A294" s="43">
@@ -25363,11 +25369,11 @@
       <c r="Y294" s="40">
         <v>1</v>
       </c>
-      <c r="Z294" s="100" t="s">
+      <c r="Z294" s="102" t="s">
         <v>105</v>
       </c>
-      <c r="AA294" s="102"/>
-      <c r="AB294" s="102"/>
+      <c r="AA294" s="104"/>
+      <c r="AB294" s="104"/>
     </row>
     <row r="295" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A295" s="43">
@@ -25446,11 +25452,11 @@
       <c r="Y295" s="40">
         <v>1</v>
       </c>
-      <c r="Z295" s="100" t="s">
+      <c r="Z295" s="102" t="s">
         <v>106</v>
       </c>
-      <c r="AA295" s="102"/>
-      <c r="AB295" s="102"/>
+      <c r="AA295" s="104"/>
+      <c r="AB295" s="104"/>
     </row>
     <row r="296" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A296" s="43">
@@ -26986,7 +26992,7 @@
       <c r="Y314" s="53">
         <v>1</v>
       </c>
-      <c r="Z314" s="105" t="s">
+      <c r="Z314" s="107" t="s">
         <v>107</v>
       </c>
       <c r="AA314" s="114"/>
@@ -27069,11 +27075,11 @@
       <c r="Y315" s="50">
         <v>1</v>
       </c>
-      <c r="Z315" s="100" t="s">
+      <c r="Z315" s="102" t="s">
         <v>108</v>
       </c>
-      <c r="AA315" s="101"/>
-      <c r="AB315" s="101"/>
+      <c r="AA315" s="103"/>
+      <c r="AB315" s="103"/>
     </row>
     <row r="316" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
@@ -27152,9 +27158,9 @@
       <c r="Y316" s="50">
         <v>1</v>
       </c>
-      <c r="Z316" s="100"/>
-      <c r="AA316" s="101"/>
-      <c r="AB316" s="101"/>
+      <c r="Z316" s="102"/>
+      <c r="AA316" s="103"/>
+      <c r="AB316" s="103"/>
     </row>
     <row r="317" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A317" s="27">
@@ -27233,9 +27239,9 @@
       <c r="Y317" s="57">
         <v>1</v>
       </c>
-      <c r="Z317" s="100"/>
-      <c r="AA317" s="101"/>
-      <c r="AB317" s="101"/>
+      <c r="Z317" s="102"/>
+      <c r="AA317" s="103"/>
+      <c r="AB317" s="103"/>
     </row>
     <row r="318" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
@@ -27314,11 +27320,11 @@
       <c r="Y318" s="50">
         <v>1</v>
       </c>
-      <c r="Z318" s="100" t="s">
+      <c r="Z318" s="102" t="s">
         <v>109</v>
       </c>
-      <c r="AA318" s="102"/>
-      <c r="AB318" s="102"/>
+      <c r="AA318" s="104"/>
+      <c r="AB318" s="104"/>
     </row>
     <row r="319" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
@@ -27397,9 +27403,9 @@
       <c r="Y319" s="50">
         <v>1</v>
       </c>
-      <c r="Z319" s="100"/>
-      <c r="AA319" s="102"/>
-      <c r="AB319" s="102"/>
+      <c r="Z319" s="102"/>
+      <c r="AA319" s="104"/>
+      <c r="AB319" s="104"/>
     </row>
     <row r="320" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
@@ -27478,9 +27484,9 @@
       <c r="Y320" s="50">
         <v>1</v>
       </c>
-      <c r="Z320" s="100"/>
-      <c r="AA320" s="102"/>
-      <c r="AB320" s="102"/>
+      <c r="Z320" s="102"/>
+      <c r="AA320" s="104"/>
+      <c r="AB320" s="104"/>
     </row>
     <row r="321" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
@@ -27559,9 +27565,9 @@
       <c r="Y321" s="50">
         <v>1</v>
       </c>
-      <c r="Z321" s="100"/>
-      <c r="AA321" s="102"/>
-      <c r="AB321" s="102"/>
+      <c r="Z321" s="102"/>
+      <c r="AA321" s="104"/>
+      <c r="AB321" s="104"/>
     </row>
     <row r="322" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
@@ -27640,9 +27646,9 @@
       <c r="Y322" s="50">
         <v>1</v>
       </c>
-      <c r="Z322" s="100"/>
-      <c r="AA322" s="102"/>
-      <c r="AB322" s="102"/>
+      <c r="Z322" s="102"/>
+      <c r="AA322" s="104"/>
+      <c r="AB322" s="104"/>
     </row>
     <row r="323" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
@@ -27721,9 +27727,9 @@
       <c r="Y323" s="50">
         <v>1</v>
       </c>
-      <c r="Z323" s="100"/>
-      <c r="AA323" s="102"/>
-      <c r="AB323" s="102"/>
+      <c r="Z323" s="102"/>
+      <c r="AA323" s="104"/>
+      <c r="AB323" s="104"/>
     </row>
     <row r="324" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
@@ -27802,9 +27808,9 @@
       <c r="Y324" s="50">
         <v>1</v>
       </c>
-      <c r="Z324" s="100"/>
-      <c r="AA324" s="102"/>
-      <c r="AB324" s="102"/>
+      <c r="Z324" s="102"/>
+      <c r="AA324" s="104"/>
+      <c r="AB324" s="104"/>
     </row>
     <row r="325" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
@@ -27883,9 +27889,9 @@
       <c r="Y325" s="50">
         <v>1</v>
       </c>
-      <c r="Z325" s="100"/>
-      <c r="AA325" s="102"/>
-      <c r="AB325" s="102"/>
+      <c r="Z325" s="102"/>
+      <c r="AA325" s="104"/>
+      <c r="AB325" s="104"/>
     </row>
     <row r="326" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="43">
@@ -27965,11 +27971,11 @@
       <c r="Y326" s="40">
         <v>1</v>
       </c>
-      <c r="Z326" s="100" t="s">
+      <c r="Z326" s="102" t="s">
         <v>110</v>
       </c>
-      <c r="AA326" s="101"/>
-      <c r="AB326" s="101"/>
+      <c r="AA326" s="103"/>
+      <c r="AB326" s="103"/>
     </row>
     <row r="327" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
@@ -28049,9 +28055,9 @@
       <c r="Y327" s="50">
         <v>1</v>
       </c>
-      <c r="Z327" s="100"/>
-      <c r="AA327" s="101"/>
-      <c r="AB327" s="101"/>
+      <c r="Z327" s="102"/>
+      <c r="AA327" s="103"/>
+      <c r="AB327" s="103"/>
     </row>
     <row r="328" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
@@ -28131,9 +28137,9 @@
       <c r="Y328" s="50">
         <v>1</v>
       </c>
-      <c r="Z328" s="100"/>
-      <c r="AA328" s="101"/>
-      <c r="AB328" s="101"/>
+      <c r="Z328" s="102"/>
+      <c r="AA328" s="103"/>
+      <c r="AB328" s="103"/>
     </row>
     <row r="329" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
@@ -28213,9 +28219,9 @@
       <c r="Y329" s="50">
         <v>1</v>
       </c>
-      <c r="Z329" s="100"/>
-      <c r="AA329" s="101"/>
-      <c r="AB329" s="101"/>
+      <c r="Z329" s="102"/>
+      <c r="AA329" s="103"/>
+      <c r="AB329" s="103"/>
     </row>
     <row r="330" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
@@ -28295,9 +28301,9 @@
       <c r="Y330" s="50">
         <v>1</v>
       </c>
-      <c r="Z330" s="100"/>
-      <c r="AA330" s="101"/>
-      <c r="AB330" s="101"/>
+      <c r="Z330" s="102"/>
+      <c r="AA330" s="103"/>
+      <c r="AB330" s="103"/>
     </row>
     <row r="331" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
@@ -28377,9 +28383,9 @@
       <c r="Y331" s="50">
         <v>1</v>
       </c>
-      <c r="Z331" s="100"/>
-      <c r="AA331" s="101"/>
-      <c r="AB331" s="101"/>
+      <c r="Z331" s="102"/>
+      <c r="AA331" s="103"/>
+      <c r="AB331" s="103"/>
     </row>
     <row r="332" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
@@ -28459,9 +28465,9 @@
       <c r="Y332" s="50">
         <v>1</v>
       </c>
-      <c r="Z332" s="100"/>
-      <c r="AA332" s="101"/>
-      <c r="AB332" s="101"/>
+      <c r="Z332" s="102"/>
+      <c r="AA332" s="103"/>
+      <c r="AB332" s="103"/>
     </row>
     <row r="333" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
@@ -28541,9 +28547,9 @@
       <c r="Y333" s="50">
         <v>1</v>
       </c>
-      <c r="Z333" s="100"/>
-      <c r="AA333" s="101"/>
-      <c r="AB333" s="101"/>
+      <c r="Z333" s="102"/>
+      <c r="AA333" s="103"/>
+      <c r="AB333" s="103"/>
     </row>
     <row r="334" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
@@ -28623,9 +28629,9 @@
       <c r="Y334" s="50">
         <v>1</v>
       </c>
-      <c r="Z334" s="100"/>
-      <c r="AA334" s="101"/>
-      <c r="AB334" s="101"/>
+      <c r="Z334" s="102"/>
+      <c r="AA334" s="103"/>
+      <c r="AB334" s="103"/>
     </row>
     <row r="335" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
@@ -28705,9 +28711,9 @@
       <c r="Y335" s="50">
         <v>1</v>
       </c>
-      <c r="Z335" s="100"/>
-      <c r="AA335" s="101"/>
-      <c r="AB335" s="101"/>
+      <c r="Z335" s="102"/>
+      <c r="AA335" s="103"/>
+      <c r="AB335" s="103"/>
     </row>
     <row r="336" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
@@ -28787,9 +28793,9 @@
       <c r="Y336" s="50">
         <v>1</v>
       </c>
-      <c r="Z336" s="100"/>
-      <c r="AA336" s="101"/>
-      <c r="AB336" s="101"/>
+      <c r="Z336" s="102"/>
+      <c r="AA336" s="103"/>
+      <c r="AB336" s="103"/>
     </row>
     <row r="337" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
@@ -28869,9 +28875,9 @@
       <c r="Y337" s="50">
         <v>1</v>
       </c>
-      <c r="Z337" s="100"/>
-      <c r="AA337" s="101"/>
-      <c r="AB337" s="101"/>
+      <c r="Z337" s="102"/>
+      <c r="AA337" s="103"/>
+      <c r="AB337" s="103"/>
     </row>
     <row r="338" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
@@ -28951,9 +28957,9 @@
       <c r="Y338" s="50">
         <v>1</v>
       </c>
-      <c r="Z338" s="100"/>
-      <c r="AA338" s="101"/>
-      <c r="AB338" s="101"/>
+      <c r="Z338" s="102"/>
+      <c r="AA338" s="103"/>
+      <c r="AB338" s="103"/>
     </row>
     <row r="339" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
@@ -29033,9 +29039,9 @@
       <c r="Y339" s="50">
         <v>1</v>
       </c>
-      <c r="Z339" s="100"/>
-      <c r="AA339" s="101"/>
-      <c r="AB339" s="101"/>
+      <c r="Z339" s="102"/>
+      <c r="AA339" s="103"/>
+      <c r="AB339" s="103"/>
     </row>
     <row r="340" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
@@ -29115,9 +29121,9 @@
       <c r="Y340" s="50">
         <v>1</v>
       </c>
-      <c r="Z340" s="100"/>
-      <c r="AA340" s="101"/>
-      <c r="AB340" s="101"/>
+      <c r="Z340" s="102"/>
+      <c r="AA340" s="103"/>
+      <c r="AB340" s="103"/>
     </row>
     <row r="341" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
@@ -29197,9 +29203,9 @@
       <c r="Y341" s="50">
         <v>1</v>
       </c>
-      <c r="Z341" s="100"/>
-      <c r="AA341" s="101"/>
-      <c r="AB341" s="101"/>
+      <c r="Z341" s="102"/>
+      <c r="AA341" s="103"/>
+      <c r="AB341" s="103"/>
     </row>
     <row r="342" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
@@ -29279,9 +29285,9 @@
       <c r="Y342" s="50">
         <v>1</v>
       </c>
-      <c r="Z342" s="100"/>
-      <c r="AA342" s="101"/>
-      <c r="AB342" s="101"/>
+      <c r="Z342" s="102"/>
+      <c r="AA342" s="103"/>
+      <c r="AB342" s="103"/>
     </row>
     <row r="343" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
@@ -29361,9 +29367,9 @@
       <c r="Y343" s="50">
         <v>1</v>
       </c>
-      <c r="Z343" s="100"/>
-      <c r="AA343" s="101"/>
-      <c r="AB343" s="101"/>
+      <c r="Z343" s="102"/>
+      <c r="AA343" s="103"/>
+      <c r="AB343" s="103"/>
     </row>
     <row r="344" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A344" s="43">
@@ -29441,11 +29447,11 @@
       <c r="Y344" s="40">
         <v>1</v>
       </c>
-      <c r="Z344" s="100" t="s">
+      <c r="Z344" s="102" t="s">
         <v>108</v>
       </c>
-      <c r="AA344" s="101"/>
-      <c r="AB344" s="101"/>
+      <c r="AA344" s="103"/>
+      <c r="AB344" s="103"/>
     </row>
     <row r="345" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
@@ -29523,9 +29529,9 @@
       <c r="Y345" s="50">
         <v>1</v>
       </c>
-      <c r="Z345" s="100"/>
-      <c r="AA345" s="101"/>
-      <c r="AB345" s="101"/>
+      <c r="Z345" s="102"/>
+      <c r="AA345" s="103"/>
+      <c r="AB345" s="103"/>
     </row>
     <row r="346" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A346" s="27">
@@ -29603,9 +29609,9 @@
       <c r="Y346" s="57">
         <v>1</v>
       </c>
-      <c r="Z346" s="100"/>
-      <c r="AA346" s="101"/>
-      <c r="AB346" s="101"/>
+      <c r="Z346" s="102"/>
+      <c r="AA346" s="103"/>
+      <c r="AB346" s="103"/>
     </row>
     <row r="347" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A347" s="33">
@@ -29683,11 +29689,11 @@
       <c r="Y347" s="57">
         <v>1</v>
       </c>
-      <c r="Z347" s="100" t="s">
+      <c r="Z347" s="102" t="s">
         <v>93</v>
       </c>
-      <c r="AA347" s="101"/>
-      <c r="AB347" s="101"/>
+      <c r="AA347" s="103"/>
+      <c r="AB347" s="103"/>
     </row>
     <row r="348" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A348" s="33">
@@ -29765,11 +29771,11 @@
       <c r="Y348" s="57">
         <v>1</v>
       </c>
-      <c r="Z348" s="100" t="s">
+      <c r="Z348" s="102" t="s">
         <v>111</v>
       </c>
-      <c r="AA348" s="102"/>
-      <c r="AB348" s="102"/>
+      <c r="AA348" s="104"/>
+      <c r="AB348" s="104"/>
     </row>
     <row r="349" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
@@ -29926,11 +29932,11 @@
       <c r="Y350" s="40">
         <v>1</v>
       </c>
-      <c r="Z350" s="100" t="s">
+      <c r="Z350" s="102" t="s">
         <v>112</v>
       </c>
-      <c r="AA350" s="101"/>
-      <c r="AB350" s="101"/>
+      <c r="AA350" s="103"/>
+      <c r="AB350" s="103"/>
     </row>
     <row r="351" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A351" s="98">
@@ -30009,9 +30015,9 @@
       <c r="Y351" s="50">
         <v>1</v>
       </c>
-      <c r="Z351" s="100"/>
-      <c r="AA351" s="101"/>
-      <c r="AB351" s="101"/>
+      <c r="Z351" s="102"/>
+      <c r="AA351" s="103"/>
+      <c r="AB351" s="103"/>
     </row>
     <row r="352" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A352" s="99">
@@ -30090,11 +30096,11 @@
       <c r="Y352" s="57">
         <v>1</v>
       </c>
-      <c r="Z352" s="100"/>
-      <c r="AA352" s="101"/>
-      <c r="AB352" s="101"/>
-    </row>
-    <row r="353" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z352" s="102"/>
+      <c r="AA352" s="103"/>
+      <c r="AB352" s="103"/>
+    </row>
+    <row r="353" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
         <v>450</v>
       </c>
@@ -30172,7 +30178,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="354" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
         <v>451</v>
       </c>
@@ -30250,7 +30256,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="355" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A355" s="43">
         <v>452</v>
       </c>
@@ -30315,7 +30321,7 @@
         <v>20400000000000</v>
       </c>
       <c r="V355" s="96">
-        <f t="shared" ref="V355" si="44">$V$225</f>
+        <f t="shared" ref="V355:V357" si="44">$V$225</f>
         <v>125520</v>
       </c>
       <c r="W355" s="45">
@@ -30327,9 +30333,181 @@
       <c r="Y355" s="40">
         <v>1</v>
       </c>
+      <c r="Z355" s="100" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA355" s="101"/>
+      <c r="AB355" s="101"/>
+    </row>
+    <row r="356" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A356" s="43">
+        <v>453</v>
+      </c>
+      <c r="B356" s="45">
+        <v>12</v>
+      </c>
+      <c r="C356" s="45">
+        <v>500</v>
+      </c>
+      <c r="D356" s="47">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E356" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F356" s="40">
+        <v>5</v>
+      </c>
+      <c r="G356" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H356" s="47">
+        <v>100</v>
+      </c>
+      <c r="I356" s="45">
+        <v>1</v>
+      </c>
+      <c r="J356" s="48">
+        <v>1E-4</v>
+      </c>
+      <c r="K356" s="45">
+        <v>2</v>
+      </c>
+      <c r="L356" s="40">
+        <v>2</v>
+      </c>
+      <c r="M356" s="47">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="N356" s="45">
+        <v>300</v>
+      </c>
+      <c r="O356" s="45">
+        <v>0.1</v>
+      </c>
+      <c r="P356" s="45">
+        <v>300</v>
+      </c>
+      <c r="Q356" s="40">
+        <v>1200</v>
+      </c>
+      <c r="R356" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="S356" s="45">
+        <v>1</v>
+      </c>
+      <c r="T356" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="U356" s="42">
+        <v>20400000000000</v>
+      </c>
+      <c r="V356" s="96">
+        <f t="shared" si="44"/>
+        <v>125520</v>
+      </c>
+      <c r="W356" s="45">
+        <v>0</v>
+      </c>
+      <c r="X356" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y356" s="40">
+        <v>1</v>
+      </c>
+      <c r="Z356" s="100" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA356" s="101"/>
+      <c r="AB356" s="101"/>
+    </row>
+    <row r="357" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A357" s="43">
+        <v>454</v>
+      </c>
+      <c r="B357" s="45">
+        <v>12</v>
+      </c>
+      <c r="C357" s="45">
+        <v>500</v>
+      </c>
+      <c r="D357" s="47">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E357" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F357" s="40">
+        <v>5</v>
+      </c>
+      <c r="G357" s="47">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="H357" s="47">
+        <v>100</v>
+      </c>
+      <c r="I357" s="45">
+        <v>1</v>
+      </c>
+      <c r="J357" s="48">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="K357" s="45">
+        <v>2</v>
+      </c>
+      <c r="L357" s="40">
+        <v>2</v>
+      </c>
+      <c r="M357" s="47">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="N357" s="45">
+        <v>300</v>
+      </c>
+      <c r="O357" s="45">
+        <v>0.1</v>
+      </c>
+      <c r="P357" s="45">
+        <v>300</v>
+      </c>
+      <c r="Q357" s="40">
+        <v>1200</v>
+      </c>
+      <c r="R357" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="S357" s="45">
+        <v>1</v>
+      </c>
+      <c r="T357" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="U357" s="42">
+        <v>20400000000000</v>
+      </c>
+      <c r="V357" s="96">
+        <f t="shared" si="44"/>
+        <v>125520</v>
+      </c>
+      <c r="W357" s="45">
+        <v>0</v>
+      </c>
+      <c r="X357" s="45">
+        <v>1</v>
+      </c>
+      <c r="Y357" s="40">
+        <v>1</v>
+      </c>
+      <c r="Z357" s="100" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA357" s="101"/>
+      <c r="AB357" s="101"/>
     </row>
   </sheetData>
-  <mergeCells count="83">
+  <mergeCells count="86">
+    <mergeCell ref="Z357:AB357"/>
     <mergeCell ref="Z326:AB343"/>
     <mergeCell ref="Z344:AB346"/>
     <mergeCell ref="Z252:AB262"/>
@@ -30344,6 +30522,7 @@
     <mergeCell ref="Z296:AB312"/>
     <mergeCell ref="Z314:AB314"/>
     <mergeCell ref="Z293:AB293"/>
+    <mergeCell ref="Z347:AB347"/>
     <mergeCell ref="Z5:AB5"/>
     <mergeCell ref="Z4:AB4"/>
     <mergeCell ref="Z164:AB164"/>
@@ -30383,6 +30562,7 @@
     <mergeCell ref="Z206:AB220"/>
     <mergeCell ref="Z130:AB147"/>
     <mergeCell ref="Z112:AB129"/>
+    <mergeCell ref="Z348:AB348"/>
     <mergeCell ref="Z221:AB222"/>
     <mergeCell ref="Z223:AB224"/>
     <mergeCell ref="Z163:AB163"/>
@@ -30397,6 +30577,8 @@
     <mergeCell ref="Z204:AB204"/>
     <mergeCell ref="Z205:AB205"/>
     <mergeCell ref="Z176:AB193"/>
+    <mergeCell ref="Z355:AB355"/>
+    <mergeCell ref="Z356:AB356"/>
     <mergeCell ref="Z350:AB352"/>
     <mergeCell ref="Z167:AB167"/>
     <mergeCell ref="Z240:AB251"/>
@@ -30411,8 +30593,6 @@
     <mergeCell ref="Z196:AB196"/>
     <mergeCell ref="Z233:AB234"/>
     <mergeCell ref="Z294:AB294"/>
-    <mergeCell ref="Z347:AB347"/>
-    <mergeCell ref="Z348:AB348"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
